--- a/artfynd/A 32983-2023 artfynd.xlsx
+++ b/artfynd/A 32983-2023 artfynd.xlsx
@@ -7203,10 +7203,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>120074881</v>
+        <v>120075012</v>
       </c>
       <c r="B66" t="n">
-        <v>79144</v>
+        <v>78263</v>
       </c>
       <c r="C66" t="inlineStr">
         <is>
@@ -7219,21 +7219,21 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>6453</v>
+        <v>228912</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
@@ -7243,10 +7243,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>478184</v>
+        <v>478055</v>
       </c>
       <c r="R66" t="n">
-        <v>6827728</v>
+        <v>6827786</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7305,10 +7305,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>120075012</v>
+        <v>120074914</v>
       </c>
       <c r="B67" t="n">
-        <v>78263</v>
+        <v>78560</v>
       </c>
       <c r="C67" t="inlineStr">
         <is>
@@ -7321,21 +7321,21 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>228912</v>
+        <v>185</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
@@ -7345,10 +7345,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>478055</v>
+        <v>478169</v>
       </c>
       <c r="R67" t="n">
-        <v>6827786</v>
+        <v>6827680</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7407,10 +7407,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>120074914</v>
+        <v>120075039</v>
       </c>
       <c r="B68" t="n">
-        <v>78560</v>
+        <v>78262</v>
       </c>
       <c r="C68" t="inlineStr">
         <is>
@@ -7423,21 +7423,21 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>185</v>
+        <v>6446</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
@@ -7447,10 +7447,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>478169</v>
+        <v>478238</v>
       </c>
       <c r="R68" t="n">
-        <v>6827680</v>
+        <v>6827752</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7509,7 +7509,7 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>120075039</v>
+        <v>120075045</v>
       </c>
       <c r="B69" t="n">
         <v>78262</v>
@@ -7549,10 +7549,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>478238</v>
+        <v>478070</v>
       </c>
       <c r="R69" t="n">
-        <v>6827752</v>
+        <v>6827723</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -7611,7 +7611,7 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>120075045</v>
+        <v>120075040</v>
       </c>
       <c r="B70" t="n">
         <v>78262</v>
@@ -7651,10 +7651,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>478070</v>
+        <v>478250</v>
       </c>
       <c r="R70" t="n">
-        <v>6827723</v>
+        <v>6827802</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -7713,10 +7713,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>120075040</v>
+        <v>120075087</v>
       </c>
       <c r="B71" t="n">
-        <v>78262</v>
+        <v>78526</v>
       </c>
       <c r="C71" t="inlineStr">
         <is>
@@ -7729,21 +7729,21 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
@@ -7753,10 +7753,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>478250</v>
+        <v>478145</v>
       </c>
       <c r="R71" t="n">
-        <v>6827802</v>
+        <v>6827485</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -7815,7 +7815,7 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>120075087</v>
+        <v>120075138</v>
       </c>
       <c r="B72" t="n">
         <v>78526</v>
@@ -7855,10 +7855,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>478145</v>
+        <v>478294</v>
       </c>
       <c r="R72" t="n">
-        <v>6827485</v>
+        <v>6827781</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -7917,10 +7917,10 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>120075138</v>
+        <v>120075004</v>
       </c>
       <c r="B73" t="n">
-        <v>78526</v>
+        <v>78263</v>
       </c>
       <c r="C73" t="inlineStr">
         <is>
@@ -7933,21 +7933,21 @@
         </is>
       </c>
       <c r="E73" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
@@ -7957,10 +7957,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>478294</v>
+        <v>478212</v>
       </c>
       <c r="R73" t="n">
-        <v>6827781</v>
+        <v>6827573</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -8019,10 +8019,10 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>120075004</v>
+        <v>120074925</v>
       </c>
       <c r="B74" t="n">
-        <v>78263</v>
+        <v>78560</v>
       </c>
       <c r="C74" t="inlineStr">
         <is>
@@ -8035,21 +8035,21 @@
         </is>
       </c>
       <c r="E74" t="n">
-        <v>228912</v>
+        <v>185</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
@@ -8059,10 +8059,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>478212</v>
+        <v>478088</v>
       </c>
       <c r="R74" t="n">
-        <v>6827573</v>
+        <v>6827834</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -8121,10 +8121,10 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>120074925</v>
+        <v>120075067</v>
       </c>
       <c r="B75" t="n">
-        <v>78560</v>
+        <v>78526</v>
       </c>
       <c r="C75" t="inlineStr">
         <is>
@@ -8137,21 +8137,21 @@
         </is>
       </c>
       <c r="E75" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
@@ -8161,10 +8161,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>478088</v>
+        <v>478164</v>
       </c>
       <c r="R75" t="n">
-        <v>6827834</v>
+        <v>6827661</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -8223,10 +8223,10 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>120075067</v>
+        <v>120074946</v>
       </c>
       <c r="B76" t="n">
-        <v>78526</v>
+        <v>79144</v>
       </c>
       <c r="C76" t="inlineStr">
         <is>
@@ -8239,21 +8239,21 @@
         </is>
       </c>
       <c r="E76" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
@@ -8263,10 +8263,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>478164</v>
+        <v>478056</v>
       </c>
       <c r="R76" t="n">
-        <v>6827661</v>
+        <v>6827754</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -8325,7 +8325,7 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>120074946</v>
+        <v>120074881</v>
       </c>
       <c r="B77" t="n">
         <v>79144</v>
@@ -8365,10 +8365,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>478056</v>
+        <v>478184</v>
       </c>
       <c r="R77" t="n">
-        <v>6827754</v>
+        <v>6827728</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>

--- a/artfynd/A 32983-2023 artfynd.xlsx
+++ b/artfynd/A 32983-2023 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>120074929</v>
+        <v>120074886</v>
       </c>
       <c r="B2" t="n">
-        <v>78560</v>
+        <v>79144</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>185</v>
+        <v>6453</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>478045</v>
+        <v>478125</v>
       </c>
       <c r="R2" t="n">
-        <v>6827724</v>
+        <v>6827604</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -777,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>120075028</v>
+        <v>120074943</v>
       </c>
       <c r="B3" t="n">
-        <v>78262</v>
+        <v>79144</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -793,21 +793,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6446</v>
+        <v>6453</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -817,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>478137</v>
+        <v>478073</v>
       </c>
       <c r="R3" t="n">
-        <v>6827553</v>
+        <v>6827827</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -879,7 +879,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>120075013</v>
+        <v>120075007</v>
       </c>
       <c r="B4" t="n">
         <v>78263</v>
@@ -919,10 +919,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>478239</v>
+        <v>478285</v>
       </c>
       <c r="R4" t="n">
-        <v>6827752</v>
+        <v>6827770</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -981,10 +981,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>120074941</v>
+        <v>120074998</v>
       </c>
       <c r="B5" t="n">
-        <v>79144</v>
+        <v>78263</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -997,21 +997,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6453</v>
+        <v>228912</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1021,10 +1021,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>478069</v>
+        <v>478172</v>
       </c>
       <c r="R5" t="n">
-        <v>6827854</v>
+        <v>6827640</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1083,10 +1083,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>120075063</v>
+        <v>120075217</v>
       </c>
       <c r="B6" t="n">
-        <v>78526</v>
+        <v>78171</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1099,21 +1099,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>353</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1123,10 +1123,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>478201</v>
+        <v>478264</v>
       </c>
       <c r="R6" t="n">
-        <v>6827693</v>
+        <v>6827839</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1185,10 +1185,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>120075136</v>
+        <v>120075208</v>
       </c>
       <c r="B7" t="n">
-        <v>78526</v>
+        <v>78171</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1201,21 +1201,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6425</v>
+        <v>353</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1225,10 +1225,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>478290</v>
+        <v>478158</v>
       </c>
       <c r="R7" t="n">
-        <v>6827758</v>
+        <v>6827519</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1287,7 +1287,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>120075216</v>
+        <v>120075202</v>
       </c>
       <c r="B8" t="n">
         <v>78171</v>
@@ -1327,10 +1327,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>478294</v>
+        <v>478218</v>
       </c>
       <c r="R8" t="n">
-        <v>6827790</v>
+        <v>6827721</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1389,10 +1389,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>120075242</v>
+        <v>120074986</v>
       </c>
       <c r="B9" t="n">
-        <v>77910</v>
+        <v>79608</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1405,21 +1405,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6437</v>
+        <v>2081</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1429,10 +1429,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>478136</v>
+        <v>478096</v>
       </c>
       <c r="R9" t="n">
-        <v>6827556</v>
+        <v>6827549</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1491,10 +1491,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>120075231</v>
+        <v>120075075</v>
       </c>
       <c r="B10" t="n">
-        <v>78171</v>
+        <v>78526</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1507,21 +1507,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>353</v>
+        <v>6425</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1531,10 +1531,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>478067</v>
+        <v>478139</v>
       </c>
       <c r="R10" t="n">
-        <v>6827863</v>
+        <v>6827554</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1593,7 +1593,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>120075167</v>
+        <v>120075157</v>
       </c>
       <c r="B11" t="n">
         <v>78526</v>
@@ -1633,10 +1633,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>478105</v>
+        <v>478103</v>
       </c>
       <c r="R11" t="n">
-        <v>6827851</v>
+        <v>6827718</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1695,7 +1695,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>120075131</v>
+        <v>120075073</v>
       </c>
       <c r="B12" t="n">
         <v>78526</v>
@@ -1735,10 +1735,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>478258</v>
+        <v>478116</v>
       </c>
       <c r="R12" t="n">
-        <v>6827731</v>
+        <v>6827617</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1797,7 +1797,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>120075140</v>
+        <v>120075097</v>
       </c>
       <c r="B13" t="n">
         <v>78526</v>
@@ -1837,10 +1837,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>478310</v>
+        <v>478248</v>
       </c>
       <c r="R13" t="n">
-        <v>6827797</v>
+        <v>6827593</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1899,10 +1899,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>120075042</v>
+        <v>120075067</v>
       </c>
       <c r="B14" t="n">
-        <v>78262</v>
+        <v>78526</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1915,21 +1915,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1939,10 +1939,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>478074</v>
+        <v>478164</v>
       </c>
       <c r="R14" t="n">
-        <v>6827775</v>
+        <v>6827661</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2001,10 +2001,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>120075232</v>
+        <v>120074928</v>
       </c>
       <c r="B15" t="n">
-        <v>78171</v>
+        <v>78560</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2017,21 +2017,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>353</v>
+        <v>185</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2041,10 +2041,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>478051</v>
+        <v>478059</v>
       </c>
       <c r="R15" t="n">
-        <v>6827739</v>
+        <v>6827740</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2103,10 +2103,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>120075085</v>
+        <v>120075227</v>
       </c>
       <c r="B16" t="n">
-        <v>78526</v>
+        <v>78171</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2119,21 +2119,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6425</v>
+        <v>353</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2143,10 +2143,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>478094</v>
+        <v>478088</v>
       </c>
       <c r="R16" t="n">
-        <v>6827504</v>
+        <v>6827834</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2205,10 +2205,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>120075075</v>
+        <v>120075197</v>
       </c>
       <c r="B17" t="n">
-        <v>78526</v>
+        <v>91840</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2217,38 +2217,47 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr"/>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="P17" t="inlineStr">
         <is>
           <t>Hevoslamm, Dlr</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>478139</v>
+        <v>478077</v>
       </c>
       <c r="R17" t="n">
-        <v>6827554</v>
+        <v>6827805</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2307,10 +2316,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>120074939</v>
+        <v>120075042</v>
       </c>
       <c r="B18" t="n">
-        <v>79144</v>
+        <v>78262</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2323,21 +2332,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6453</v>
+        <v>6446</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2347,10 +2356,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>478091</v>
+        <v>478074</v>
       </c>
       <c r="R18" t="n">
-        <v>6827838</v>
+        <v>6827775</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2409,10 +2418,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>120075015</v>
+        <v>120075092</v>
       </c>
       <c r="B19" t="n">
-        <v>79607</v>
+        <v>78526</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2425,21 +2434,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2449,10 +2458,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>478114</v>
+        <v>478167</v>
       </c>
       <c r="R19" t="n">
-        <v>6827633</v>
+        <v>6827561</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2511,10 +2520,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>120075003</v>
+        <v>120075174</v>
       </c>
       <c r="B20" t="n">
-        <v>78263</v>
+        <v>78526</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2527,21 +2536,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2551,10 +2560,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>478137</v>
+        <v>478057</v>
       </c>
       <c r="R20" t="n">
-        <v>6827553</v>
+        <v>6827749</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2613,10 +2622,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>120074943</v>
+        <v>120075135</v>
       </c>
       <c r="B21" t="n">
-        <v>79144</v>
+        <v>78526</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2629,21 +2638,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2653,10 +2662,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>478073</v>
+        <v>478291</v>
       </c>
       <c r="R21" t="n">
-        <v>6827827</v>
+        <v>6827744</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2715,10 +2724,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>120075202</v>
+        <v>120075038</v>
       </c>
       <c r="B22" t="n">
-        <v>78171</v>
+        <v>78262</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2731,21 +2740,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>353</v>
+        <v>6446</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2755,10 +2764,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>478218</v>
+        <v>478261</v>
       </c>
       <c r="R22" t="n">
-        <v>6827721</v>
+        <v>6827731</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2817,10 +2826,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>120075163</v>
+        <v>120074948</v>
       </c>
       <c r="B23" t="n">
-        <v>78526</v>
+        <v>79144</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -2833,21 +2842,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2857,10 +2866,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>478102</v>
+        <v>478070</v>
       </c>
       <c r="R23" t="n">
-        <v>6827800</v>
+        <v>6827723</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2919,10 +2928,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>120075009</v>
+        <v>120074891</v>
       </c>
       <c r="B24" t="n">
-        <v>78263</v>
+        <v>79144</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -2935,21 +2944,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>228912</v>
+        <v>6453</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -2959,10 +2968,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>478151</v>
+        <v>478212</v>
       </c>
       <c r="R24" t="n">
-        <v>6827745</v>
+        <v>6827573</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3021,7 +3030,7 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>120075201</v>
+        <v>120075230</v>
       </c>
       <c r="B25" t="n">
         <v>78171</v>
@@ -3061,10 +3070,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>478182</v>
+        <v>478064</v>
       </c>
       <c r="R25" t="n">
-        <v>6827728</v>
+        <v>6827866</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3123,7 +3132,7 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>120075177</v>
+        <v>120075137</v>
       </c>
       <c r="B26" t="n">
         <v>78526</v>
@@ -3163,10 +3172,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>478075</v>
+        <v>478288</v>
       </c>
       <c r="R26" t="n">
-        <v>6827717</v>
+        <v>6827763</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3225,10 +3234,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>120075230</v>
+        <v>120075071</v>
       </c>
       <c r="B27" t="n">
-        <v>78171</v>
+        <v>78526</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3241,21 +3250,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>353</v>
+        <v>6425</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3265,10 +3274,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>478064</v>
+        <v>478116</v>
       </c>
       <c r="R27" t="n">
-        <v>6827866</v>
+        <v>6827633</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3327,10 +3336,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>120075214</v>
+        <v>120075088</v>
       </c>
       <c r="B28" t="n">
-        <v>78171</v>
+        <v>78526</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3343,21 +3352,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>353</v>
+        <v>6425</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3367,10 +3376,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>478266</v>
+        <v>478151</v>
       </c>
       <c r="R28" t="n">
-        <v>6827724</v>
+        <v>6827509</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3429,10 +3438,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>120074945</v>
+        <v>120075008</v>
       </c>
       <c r="B29" t="n">
-        <v>79144</v>
+        <v>78263</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3445,21 +3454,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6453</v>
+        <v>228912</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3469,10 +3478,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>478061</v>
+        <v>478299</v>
       </c>
       <c r="R29" t="n">
-        <v>6827770</v>
+        <v>6827805</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3531,10 +3540,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>120074885</v>
+        <v>120074915</v>
       </c>
       <c r="B30" t="n">
-        <v>79144</v>
+        <v>78560</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3547,21 +3556,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6453</v>
+        <v>185</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3571,10 +3580,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>478115</v>
+        <v>478102</v>
       </c>
       <c r="R30" t="n">
-        <v>6827614</v>
+        <v>6827555</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3633,7 +3642,7 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>120075176</v>
+        <v>120075147</v>
       </c>
       <c r="B31" t="n">
         <v>78526</v>
@@ -3673,10 +3682,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>478066</v>
+        <v>478153</v>
       </c>
       <c r="R31" t="n">
-        <v>6827732</v>
+        <v>6827728</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3735,10 +3744,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>120074907</v>
+        <v>120075167</v>
       </c>
       <c r="B32" t="n">
-        <v>79144</v>
+        <v>78526</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -3751,21 +3760,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3775,10 +3784,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>478263</v>
+        <v>478105</v>
       </c>
       <c r="R32" t="n">
-        <v>6827838</v>
+        <v>6827851</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3837,10 +3846,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>120075081</v>
+        <v>120075026</v>
       </c>
       <c r="B33" t="n">
-        <v>78526</v>
+        <v>78262</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -3853,21 +3862,21 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -3877,10 +3886,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>478096</v>
+        <v>478161</v>
       </c>
       <c r="R33" t="n">
-        <v>6827550</v>
+        <v>6827592</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -3939,10 +3948,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>120075001</v>
+        <v>120075039</v>
       </c>
       <c r="B34" t="n">
-        <v>78263</v>
+        <v>78262</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -3955,21 +3964,21 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>228912</v>
+        <v>6446</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -3979,10 +3988,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>478125</v>
+        <v>478238</v>
       </c>
       <c r="R34" t="n">
-        <v>6827604</v>
+        <v>6827752</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4041,7 +4050,7 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>120074948</v>
+        <v>120074905</v>
       </c>
       <c r="B35" t="n">
         <v>79144</v>
@@ -4081,10 +4090,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>478070</v>
+        <v>478285</v>
       </c>
       <c r="R35" t="n">
-        <v>6827723</v>
+        <v>6827770</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4143,10 +4152,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>120074892</v>
+        <v>120075028</v>
       </c>
       <c r="B36" t="n">
-        <v>79144</v>
+        <v>78262</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4159,21 +4168,21 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6453</v>
+        <v>6446</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4183,10 +4192,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>478243</v>
+        <v>478137</v>
       </c>
       <c r="R36" t="n">
-        <v>6827585</v>
+        <v>6827553</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4245,10 +4254,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>120075094</v>
+        <v>120074906</v>
       </c>
       <c r="B37" t="n">
-        <v>78526</v>
+        <v>79144</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4261,21 +4270,21 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4285,10 +4294,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>478205</v>
+        <v>478294</v>
       </c>
       <c r="R37" t="n">
-        <v>6827556</v>
+        <v>6827790</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4347,10 +4356,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>120075064</v>
+        <v>120075214</v>
       </c>
       <c r="B38" t="n">
-        <v>78526</v>
+        <v>78171</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4363,21 +4372,21 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6425</v>
+        <v>353</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4387,10 +4396,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>478192</v>
+        <v>478266</v>
       </c>
       <c r="R38" t="n">
-        <v>6827690</v>
+        <v>6827724</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4449,10 +4458,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>120075083</v>
+        <v>120075207</v>
       </c>
       <c r="B39" t="n">
-        <v>78526</v>
+        <v>78171</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4465,21 +4474,21 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6425</v>
+        <v>353</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4489,10 +4498,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>478097</v>
+        <v>478157</v>
       </c>
       <c r="R39" t="n">
-        <v>6827527</v>
+        <v>6827509</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4551,7 +4560,7 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>120075120</v>
+        <v>120075136</v>
       </c>
       <c r="B40" t="n">
         <v>78526</v>
@@ -4591,10 +4600,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>478223</v>
+        <v>478290</v>
       </c>
       <c r="R40" t="n">
-        <v>6827657</v>
+        <v>6827758</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4653,7 +4662,7 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>120075074</v>
+        <v>120075089</v>
       </c>
       <c r="B41" t="n">
         <v>78526</v>
@@ -4693,10 +4702,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>478138</v>
+        <v>478153</v>
       </c>
       <c r="R41" t="n">
-        <v>6827599</v>
+        <v>6827517</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4755,7 +4764,7 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>120075175</v>
+        <v>120075177</v>
       </c>
       <c r="B42" t="n">
         <v>78526</v>
@@ -4795,10 +4804,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>478059</v>
+        <v>478075</v>
       </c>
       <c r="R42" t="n">
-        <v>6827739</v>
+        <v>6827717</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4857,10 +4866,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>120074882</v>
+        <v>120075077</v>
       </c>
       <c r="B43" t="n">
-        <v>79144</v>
+        <v>78526</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -4873,21 +4882,21 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -4897,10 +4906,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>478162</v>
+        <v>478124</v>
       </c>
       <c r="R43" t="n">
-        <v>6827593</v>
+        <v>6827560</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -4959,10 +4968,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>120075046</v>
+        <v>120074883</v>
       </c>
       <c r="B44" t="n">
-        <v>78262</v>
+        <v>79144</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -4975,21 +4984,21 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>6446</v>
+        <v>6453</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -4999,10 +5008,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>478285</v>
+        <v>478142</v>
       </c>
       <c r="R44" t="n">
-        <v>6827770</v>
+        <v>6827623</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5061,10 +5070,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>120074927</v>
+        <v>120075045</v>
       </c>
       <c r="B45" t="n">
-        <v>78560</v>
+        <v>78262</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5077,21 +5086,21 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>185</v>
+        <v>6446</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5101,10 +5110,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>478073</v>
+        <v>478070</v>
       </c>
       <c r="R45" t="n">
-        <v>6827836</v>
+        <v>6827723</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5163,10 +5172,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>120075142</v>
+        <v>120074946</v>
       </c>
       <c r="B46" t="n">
-        <v>78526</v>
+        <v>79144</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -5179,21 +5188,21 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5203,10 +5212,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>478313</v>
+        <v>478056</v>
       </c>
       <c r="R46" t="n">
-        <v>6827798</v>
+        <v>6827754</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5265,7 +5274,7 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>120075071</v>
+        <v>120075139</v>
       </c>
       <c r="B47" t="n">
         <v>78526</v>
@@ -5305,10 +5314,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>478116</v>
+        <v>478294</v>
       </c>
       <c r="R47" t="n">
-        <v>6827633</v>
+        <v>6827803</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5367,10 +5376,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>120074930</v>
+        <v>120075159</v>
       </c>
       <c r="B48" t="n">
-        <v>79144</v>
+        <v>78526</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -5383,21 +5392,21 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5407,10 +5416,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>478299</v>
+        <v>478100</v>
       </c>
       <c r="R48" t="n">
-        <v>6827805</v>
+        <v>6827729</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5469,10 +5478,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>120075035</v>
+        <v>120075166</v>
       </c>
       <c r="B49" t="n">
-        <v>78262</v>
+        <v>78526</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -5485,21 +5494,21 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5509,10 +5518,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>478273</v>
+        <v>478092</v>
       </c>
       <c r="R49" t="n">
-        <v>6827711</v>
+        <v>6827839</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5571,7 +5580,7 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>120075173</v>
+        <v>120075120</v>
       </c>
       <c r="B50" t="n">
         <v>78526</v>
@@ -5611,10 +5620,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>478052</v>
+        <v>478223</v>
       </c>
       <c r="R50" t="n">
-        <v>6827754</v>
+        <v>6827657</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5673,7 +5682,7 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>120075065</v>
+        <v>120075078</v>
       </c>
       <c r="B51" t="n">
         <v>78526</v>
@@ -5713,10 +5722,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>478169</v>
+        <v>478116</v>
       </c>
       <c r="R51" t="n">
-        <v>6827679</v>
+        <v>6827567</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5775,7 +5784,7 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>120075082</v>
+        <v>120075128</v>
       </c>
       <c r="B52" t="n">
         <v>78526</v>
@@ -5815,10 +5824,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>478097</v>
+        <v>478275</v>
       </c>
       <c r="R52" t="n">
-        <v>6827544</v>
+        <v>6827710</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -5877,10 +5886,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>120075026</v>
+        <v>120075063</v>
       </c>
       <c r="B53" t="n">
-        <v>78262</v>
+        <v>78526</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -5893,21 +5902,21 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -5917,10 +5926,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>478161</v>
+        <v>478201</v>
       </c>
       <c r="R53" t="n">
-        <v>6827592</v>
+        <v>6827693</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -5979,10 +5988,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>120075165</v>
+        <v>120075043</v>
       </c>
       <c r="B54" t="n">
-        <v>78526</v>
+        <v>78262</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
@@ -5995,21 +6004,21 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -6019,10 +6028,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>478078</v>
+        <v>478103</v>
       </c>
       <c r="R54" t="n">
-        <v>6827834</v>
+        <v>6827803</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6081,10 +6090,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>120075196</v>
+        <v>120074941</v>
       </c>
       <c r="B55" t="n">
-        <v>78526</v>
+        <v>79144</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
@@ -6097,21 +6106,21 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -6121,10 +6130,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>478288</v>
+        <v>478069</v>
       </c>
       <c r="R55" t="n">
-        <v>6827682</v>
+        <v>6827854</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6183,10 +6192,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>120075132</v>
+        <v>120074917</v>
       </c>
       <c r="B56" t="n">
-        <v>78526</v>
+        <v>78560</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
@@ -6199,21 +6208,21 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -6223,10 +6232,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>478240</v>
+        <v>478095</v>
       </c>
       <c r="R56" t="n">
-        <v>6827754</v>
+        <v>6827533</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6285,10 +6294,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>120074999</v>
+        <v>120075205</v>
       </c>
       <c r="B57" t="n">
-        <v>78263</v>
+        <v>78171</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
@@ -6301,21 +6310,21 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>228912</v>
+        <v>353</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -6325,10 +6334,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>478161</v>
+        <v>478117</v>
       </c>
       <c r="R57" t="n">
-        <v>6827592</v>
+        <v>6827612</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6387,10 +6396,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>120075146</v>
+        <v>120075201</v>
       </c>
       <c r="B58" t="n">
-        <v>78526</v>
+        <v>78171</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
@@ -6403,21 +6412,21 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>6425</v>
+        <v>353</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
@@ -6427,10 +6436,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>478154</v>
+        <v>478182</v>
       </c>
       <c r="R58" t="n">
-        <v>6827747</v>
+        <v>6827728</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6489,10 +6498,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>120075069</v>
+        <v>120074922</v>
       </c>
       <c r="B59" t="n">
-        <v>78526</v>
+        <v>78560</v>
       </c>
       <c r="C59" t="inlineStr">
         <is>
@@ -6505,21 +6514,21 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
@@ -6529,10 +6538,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>478157</v>
+        <v>478103</v>
       </c>
       <c r="R59" t="n">
-        <v>6827611</v>
+        <v>6827718</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6591,10 +6600,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>120075234</v>
+        <v>120075003</v>
       </c>
       <c r="B60" t="n">
-        <v>78171</v>
+        <v>78263</v>
       </c>
       <c r="C60" t="inlineStr">
         <is>
@@ -6607,21 +6616,21 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>353</v>
+        <v>228912</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
@@ -6631,10 +6640,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>478069</v>
+        <v>478137</v>
       </c>
       <c r="R60" t="n">
-        <v>6827741</v>
+        <v>6827553</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -6693,10 +6702,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>120075008</v>
+        <v>120074952</v>
       </c>
       <c r="B61" t="n">
-        <v>78263</v>
+        <v>79115</v>
       </c>
       <c r="C61" t="inlineStr">
         <is>
@@ -6709,21 +6718,21 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>228912</v>
+        <v>229821</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
@@ -6733,10 +6742,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>478299</v>
+        <v>478120</v>
       </c>
       <c r="R61" t="n">
-        <v>6827805</v>
+        <v>6827605</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -6795,10 +6804,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>120074912</v>
+        <v>120075025</v>
       </c>
       <c r="B62" t="n">
-        <v>78560</v>
+        <v>78262</v>
       </c>
       <c r="C62" t="inlineStr">
         <is>
@@ -6811,21 +6820,21 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>185</v>
+        <v>6446</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
@@ -6835,10 +6844,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>478149</v>
+        <v>478171</v>
       </c>
       <c r="R62" t="n">
-        <v>6827714</v>
+        <v>6827642</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -6897,10 +6906,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>120075207</v>
+        <v>120075086</v>
       </c>
       <c r="B63" t="n">
-        <v>78171</v>
+        <v>78526</v>
       </c>
       <c r="C63" t="inlineStr">
         <is>
@@ -6913,21 +6922,21 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>353</v>
+        <v>6425</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
@@ -6937,10 +6946,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>478157</v>
+        <v>478104</v>
       </c>
       <c r="R63" t="n">
-        <v>6827509</v>
+        <v>6827495</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -6999,7 +7008,7 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>120074933</v>
+        <v>120074889</v>
       </c>
       <c r="B64" t="n">
         <v>79144</v>
@@ -7039,10 +7048,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>478189</v>
+        <v>478163</v>
       </c>
       <c r="R64" t="n">
-        <v>6827761</v>
+        <v>6827536</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -7101,10 +7110,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>120074952</v>
+        <v>120074942</v>
       </c>
       <c r="B65" t="n">
-        <v>79115</v>
+        <v>79144</v>
       </c>
       <c r="C65" t="inlineStr">
         <is>
@@ -7117,21 +7126,21 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>229821</v>
+        <v>6453</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
@@ -7141,10 +7150,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>478120</v>
+        <v>478065</v>
       </c>
       <c r="R65" t="n">
-        <v>6827605</v>
+        <v>6827842</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7203,10 +7212,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>120075012</v>
+        <v>120074947</v>
       </c>
       <c r="B66" t="n">
-        <v>78263</v>
+        <v>79144</v>
       </c>
       <c r="C66" t="inlineStr">
         <is>
@@ -7219,21 +7228,21 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>228912</v>
+        <v>6453</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
@@ -7243,10 +7252,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>478055</v>
+        <v>478061</v>
       </c>
       <c r="R66" t="n">
-        <v>6827786</v>
+        <v>6827751</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7305,10 +7314,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>120074914</v>
+        <v>120074934</v>
       </c>
       <c r="B67" t="n">
-        <v>78560</v>
+        <v>79144</v>
       </c>
       <c r="C67" t="inlineStr">
         <is>
@@ -7321,21 +7330,21 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>185</v>
+        <v>6453</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
@@ -7348,7 +7357,7 @@
         <v>478169</v>
       </c>
       <c r="R67" t="n">
-        <v>6827680</v>
+        <v>6827760</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7407,10 +7416,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>120075039</v>
+        <v>120075216</v>
       </c>
       <c r="B68" t="n">
-        <v>78262</v>
+        <v>78171</v>
       </c>
       <c r="C68" t="inlineStr">
         <is>
@@ -7423,21 +7432,21 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>6446</v>
+        <v>353</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
@@ -7447,10 +7456,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>478238</v>
+        <v>478294</v>
       </c>
       <c r="R68" t="n">
-        <v>6827752</v>
+        <v>6827790</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7509,10 +7518,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>120075045</v>
+        <v>120075084</v>
       </c>
       <c r="B69" t="n">
-        <v>78262</v>
+        <v>78526</v>
       </c>
       <c r="C69" t="inlineStr">
         <is>
@@ -7525,21 +7534,21 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
@@ -7549,10 +7558,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>478070</v>
+        <v>478098</v>
       </c>
       <c r="R69" t="n">
-        <v>6827723</v>
+        <v>6827520</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -7611,10 +7620,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>120075040</v>
+        <v>120075068</v>
       </c>
       <c r="B70" t="n">
-        <v>78262</v>
+        <v>78526</v>
       </c>
       <c r="C70" t="inlineStr">
         <is>
@@ -7627,21 +7636,21 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
@@ -7651,10 +7660,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>478250</v>
+        <v>478174</v>
       </c>
       <c r="R70" t="n">
-        <v>6827802</v>
+        <v>6827656</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -7713,10 +7722,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>120075087</v>
+        <v>120074930</v>
       </c>
       <c r="B71" t="n">
-        <v>78526</v>
+        <v>79144</v>
       </c>
       <c r="C71" t="inlineStr">
         <is>
@@ -7729,21 +7738,21 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
@@ -7753,10 +7762,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>478145</v>
+        <v>478299</v>
       </c>
       <c r="R71" t="n">
-        <v>6827485</v>
+        <v>6827805</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -7815,10 +7824,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>120075138</v>
+        <v>120075035</v>
       </c>
       <c r="B72" t="n">
-        <v>78526</v>
+        <v>78262</v>
       </c>
       <c r="C72" t="inlineStr">
         <is>
@@ -7831,21 +7840,21 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
@@ -7855,10 +7864,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>478294</v>
+        <v>478273</v>
       </c>
       <c r="R72" t="n">
-        <v>6827781</v>
+        <v>6827711</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -7917,10 +7926,10 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>120075004</v>
+        <v>120074892</v>
       </c>
       <c r="B73" t="n">
-        <v>78263</v>
+        <v>79144</v>
       </c>
       <c r="C73" t="inlineStr">
         <is>
@@ -7933,21 +7942,21 @@
         </is>
       </c>
       <c r="E73" t="n">
-        <v>228912</v>
+        <v>6453</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
@@ -7957,10 +7966,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>478212</v>
+        <v>478243</v>
       </c>
       <c r="R73" t="n">
-        <v>6827573</v>
+        <v>6827585</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -8019,10 +8028,10 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>120074925</v>
+        <v>120074944</v>
       </c>
       <c r="B74" t="n">
-        <v>78560</v>
+        <v>79144</v>
       </c>
       <c r="C74" t="inlineStr">
         <is>
@@ -8035,21 +8044,21 @@
         </is>
       </c>
       <c r="E74" t="n">
-        <v>185</v>
+        <v>6453</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
@@ -8059,10 +8068,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>478088</v>
+        <v>478056</v>
       </c>
       <c r="R74" t="n">
-        <v>6827834</v>
+        <v>6827785</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -8121,10 +8130,10 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>120075067</v>
+        <v>120075019</v>
       </c>
       <c r="B75" t="n">
-        <v>78526</v>
+        <v>79607</v>
       </c>
       <c r="C75" t="inlineStr">
         <is>
@@ -8137,21 +8146,21 @@
         </is>
       </c>
       <c r="E75" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
@@ -8161,10 +8170,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>478164</v>
+        <v>478227</v>
       </c>
       <c r="R75" t="n">
-        <v>6827661</v>
+        <v>6827655</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -8223,10 +8232,10 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>120074946</v>
+        <v>120075000</v>
       </c>
       <c r="B76" t="n">
-        <v>79144</v>
+        <v>78263</v>
       </c>
       <c r="C76" t="inlineStr">
         <is>
@@ -8239,21 +8248,21 @@
         </is>
       </c>
       <c r="E76" t="n">
-        <v>6453</v>
+        <v>228912</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
@@ -8263,10 +8272,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>478056</v>
+        <v>478121</v>
       </c>
       <c r="R76" t="n">
-        <v>6827754</v>
+        <v>6827607</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -8325,10 +8334,10 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>120074881</v>
+        <v>120075037</v>
       </c>
       <c r="B77" t="n">
-        <v>79144</v>
+        <v>78262</v>
       </c>
       <c r="C77" t="inlineStr">
         <is>
@@ -8341,21 +8350,21 @@
         </is>
       </c>
       <c r="E77" t="n">
-        <v>6453</v>
+        <v>6446</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
@@ -8365,10 +8374,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>478184</v>
+        <v>478265</v>
       </c>
       <c r="R77" t="n">
-        <v>6827728</v>
+        <v>6827716</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -8427,10 +8436,10 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>120075025</v>
+        <v>120075215</v>
       </c>
       <c r="B78" t="n">
-        <v>78262</v>
+        <v>78171</v>
       </c>
       <c r="C78" t="inlineStr">
         <is>
@@ -8443,21 +8452,21 @@
         </is>
       </c>
       <c r="E78" t="n">
-        <v>6446</v>
+        <v>353</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
@@ -8467,10 +8476,10 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>478171</v>
+        <v>478239</v>
       </c>
       <c r="R78" t="n">
-        <v>6827642</v>
+        <v>6827752</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -8529,10 +8538,10 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>120074931</v>
+        <v>120074925</v>
       </c>
       <c r="B79" t="n">
-        <v>79144</v>
+        <v>78560</v>
       </c>
       <c r="C79" t="inlineStr">
         <is>
@@ -8545,21 +8554,21 @@
         </is>
       </c>
       <c r="E79" t="n">
-        <v>6453</v>
+        <v>185</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
@@ -8569,10 +8578,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>478261</v>
+        <v>478088</v>
       </c>
       <c r="R79" t="n">
-        <v>6827822</v>
+        <v>6827834</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -8631,10 +8640,10 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>120075010</v>
+        <v>120075176</v>
       </c>
       <c r="B80" t="n">
-        <v>78263</v>
+        <v>78526</v>
       </c>
       <c r="C80" t="inlineStr">
         <is>
@@ -8647,21 +8656,21 @@
         </is>
       </c>
       <c r="E80" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
@@ -8671,10 +8680,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>478074</v>
+        <v>478066</v>
       </c>
       <c r="R80" t="n">
-        <v>6827772</v>
+        <v>6827732</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -8733,7 +8742,7 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>120075073</v>
+        <v>120075162</v>
       </c>
       <c r="B81" t="n">
         <v>78526</v>
@@ -8773,10 +8782,10 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>478116</v>
+        <v>478080</v>
       </c>
       <c r="R81" t="n">
-        <v>6827617</v>
+        <v>6827808</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -8835,10 +8844,10 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>120075203</v>
+        <v>120075095</v>
       </c>
       <c r="B82" t="n">
-        <v>78171</v>
+        <v>78526</v>
       </c>
       <c r="C82" t="inlineStr">
         <is>
@@ -8851,21 +8860,21 @@
         </is>
       </c>
       <c r="E82" t="n">
-        <v>353</v>
+        <v>6425</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
@@ -8875,10 +8884,10 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>478125</v>
+        <v>478219</v>
       </c>
       <c r="R82" t="n">
-        <v>6827631</v>
+        <v>6827572</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -8937,7 +8946,7 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>120075172</v>
+        <v>120075171</v>
       </c>
       <c r="B83" t="n">
         <v>78526</v>
@@ -8977,10 +8986,10 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>478055</v>
+        <v>478073</v>
       </c>
       <c r="R83" t="n">
-        <v>6827768</v>
+        <v>6827831</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -9039,10 +9048,10 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>120075011</v>
+        <v>120075062</v>
       </c>
       <c r="B84" t="n">
-        <v>78263</v>
+        <v>78526</v>
       </c>
       <c r="C84" t="inlineStr">
         <is>
@@ -9055,21 +9064,21 @@
         </is>
       </c>
       <c r="E84" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
@@ -9079,10 +9088,10 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>478103</v>
+        <v>478221</v>
       </c>
       <c r="R84" t="n">
-        <v>6827803</v>
+        <v>6827719</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -9141,10 +9150,10 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>120075089</v>
+        <v>120075016</v>
       </c>
       <c r="B85" t="n">
-        <v>78526</v>
+        <v>79607</v>
       </c>
       <c r="C85" t="inlineStr">
         <is>
@@ -9157,21 +9166,21 @@
         </is>
       </c>
       <c r="E85" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
@@ -9181,10 +9190,10 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>478153</v>
+        <v>478096</v>
       </c>
       <c r="R85" t="n">
-        <v>6827517</v>
+        <v>6827549</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -9243,10 +9252,10 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>120074938</v>
+        <v>120075046</v>
       </c>
       <c r="B86" t="n">
-        <v>79144</v>
+        <v>78262</v>
       </c>
       <c r="C86" t="inlineStr">
         <is>
@@ -9259,21 +9268,21 @@
         </is>
       </c>
       <c r="E86" t="n">
-        <v>6453</v>
+        <v>6446</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I86" t="inlineStr"/>
@@ -9283,10 +9292,10 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>478097</v>
+        <v>478285</v>
       </c>
       <c r="R86" t="n">
-        <v>6827756</v>
+        <v>6827770</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>
@@ -9345,10 +9354,10 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>120075061</v>
+        <v>120074885</v>
       </c>
       <c r="B87" t="n">
-        <v>78526</v>
+        <v>79144</v>
       </c>
       <c r="C87" t="inlineStr">
         <is>
@@ -9361,21 +9370,21 @@
         </is>
       </c>
       <c r="E87" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I87" t="inlineStr"/>
@@ -9385,10 +9394,10 @@
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>478160</v>
+        <v>478115</v>
       </c>
       <c r="R87" t="n">
-        <v>6827710</v>
+        <v>6827614</v>
       </c>
       <c r="S87" t="n">
         <v>10</v>
@@ -9447,10 +9456,10 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>120075029</v>
+        <v>120075196</v>
       </c>
       <c r="B88" t="n">
-        <v>78262</v>
+        <v>78526</v>
       </c>
       <c r="C88" t="inlineStr">
         <is>
@@ -9463,21 +9472,21 @@
         </is>
       </c>
       <c r="E88" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I88" t="inlineStr"/>
@@ -9487,10 +9496,10 @@
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>478115</v>
+        <v>478288</v>
       </c>
       <c r="R88" t="n">
-        <v>6827564</v>
+        <v>6827682</v>
       </c>
       <c r="S88" t="n">
         <v>10</v>
@@ -9549,7 +9558,7 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>120075164</v>
+        <v>120075121</v>
       </c>
       <c r="B89" t="n">
         <v>78526</v>
@@ -9589,10 +9598,10 @@
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>478092</v>
+        <v>478232</v>
       </c>
       <c r="R89" t="n">
-        <v>6827810</v>
+        <v>6827659</v>
       </c>
       <c r="S89" t="n">
         <v>10</v>
@@ -9651,10 +9660,10 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>120074915</v>
+        <v>120075144</v>
       </c>
       <c r="B90" t="n">
-        <v>78560</v>
+        <v>78526</v>
       </c>
       <c r="C90" t="inlineStr">
         <is>
@@ -9667,21 +9676,21 @@
         </is>
       </c>
       <c r="E90" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I90" t="inlineStr"/>
@@ -9691,10 +9700,10 @@
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>478102</v>
+        <v>478261</v>
       </c>
       <c r="R90" t="n">
-        <v>6827555</v>
+        <v>6827822</v>
       </c>
       <c r="S90" t="n">
         <v>10</v>
@@ -9753,7 +9762,7 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>120075062</v>
+        <v>120075145</v>
       </c>
       <c r="B91" t="n">
         <v>78526</v>
@@ -9793,10 +9802,10 @@
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>478221</v>
+        <v>478226</v>
       </c>
       <c r="R91" t="n">
-        <v>6827719</v>
+        <v>6827777</v>
       </c>
       <c r="S91" t="n">
         <v>10</v>
@@ -9855,10 +9864,10 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>120074906</v>
+        <v>120075027</v>
       </c>
       <c r="B92" t="n">
-        <v>79144</v>
+        <v>78262</v>
       </c>
       <c r="C92" t="inlineStr">
         <is>
@@ -9871,21 +9880,21 @@
         </is>
       </c>
       <c r="E92" t="n">
-        <v>6453</v>
+        <v>6446</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I92" t="inlineStr"/>
@@ -9895,10 +9904,10 @@
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>478294</v>
+        <v>478144</v>
       </c>
       <c r="R92" t="n">
-        <v>6827790</v>
+        <v>6827593</v>
       </c>
       <c r="S92" t="n">
         <v>10</v>
@@ -9957,10 +9966,10 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>120074887</v>
+        <v>120074914</v>
       </c>
       <c r="B93" t="n">
-        <v>79144</v>
+        <v>78560</v>
       </c>
       <c r="C93" t="inlineStr">
         <is>
@@ -9973,21 +9982,21 @@
         </is>
       </c>
       <c r="E93" t="n">
-        <v>6453</v>
+        <v>185</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I93" t="inlineStr"/>
@@ -9997,10 +10006,10 @@
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>478144</v>
+        <v>478169</v>
       </c>
       <c r="R93" t="n">
-        <v>6827593</v>
+        <v>6827680</v>
       </c>
       <c r="S93" t="n">
         <v>10</v>
@@ -10059,10 +10068,10 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>120074928</v>
+        <v>120075204</v>
       </c>
       <c r="B94" t="n">
-        <v>78560</v>
+        <v>78171</v>
       </c>
       <c r="C94" t="inlineStr">
         <is>
@@ -10075,21 +10084,21 @@
         </is>
       </c>
       <c r="E94" t="n">
-        <v>185</v>
+        <v>353</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I94" t="inlineStr"/>
@@ -10099,10 +10108,10 @@
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>478059</v>
+        <v>478115</v>
       </c>
       <c r="R94" t="n">
-        <v>6827740</v>
+        <v>6827614</v>
       </c>
       <c r="S94" t="n">
         <v>10</v>
@@ -10161,10 +10170,10 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>120075239</v>
+        <v>120075013</v>
       </c>
       <c r="B95" t="n">
-        <v>77458</v>
+        <v>78263</v>
       </c>
       <c r="C95" t="inlineStr">
         <is>
@@ -10177,21 +10186,21 @@
         </is>
       </c>
       <c r="E95" t="n">
-        <v>6487</v>
+        <v>228912</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Blågrå svartspik</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Chaenothecopsis fennica</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>(Laurila) Tibell</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I95" t="inlineStr"/>
@@ -10201,10 +10210,10 @@
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>478137</v>
+        <v>478239</v>
       </c>
       <c r="R95" t="n">
-        <v>6827554</v>
+        <v>6827752</v>
       </c>
       <c r="S95" t="n">
         <v>10</v>
@@ -10263,10 +10272,10 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>120075160</v>
+        <v>120075231</v>
       </c>
       <c r="B96" t="n">
-        <v>78526</v>
+        <v>78171</v>
       </c>
       <c r="C96" t="inlineStr">
         <is>
@@ -10279,21 +10288,21 @@
         </is>
       </c>
       <c r="E96" t="n">
-        <v>6425</v>
+        <v>353</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I96" t="inlineStr"/>
@@ -10303,10 +10312,10 @@
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>478097</v>
+        <v>478067</v>
       </c>
       <c r="R96" t="n">
-        <v>6827744</v>
+        <v>6827863</v>
       </c>
       <c r="S96" t="n">
         <v>10</v>
@@ -10365,10 +10374,10 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>120074922</v>
+        <v>120075223</v>
       </c>
       <c r="B97" t="n">
-        <v>78560</v>
+        <v>78171</v>
       </c>
       <c r="C97" t="inlineStr">
         <is>
@@ -10381,21 +10390,21 @@
         </is>
       </c>
       <c r="E97" t="n">
-        <v>185</v>
+        <v>353</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I97" t="inlineStr"/>
@@ -10405,10 +10414,10 @@
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>478103</v>
+        <v>478076</v>
       </c>
       <c r="R97" t="n">
-        <v>6827718</v>
+        <v>6827777</v>
       </c>
       <c r="S97" t="n">
         <v>10</v>
@@ -10467,10 +10476,10 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>120075208</v>
+        <v>120075146</v>
       </c>
       <c r="B98" t="n">
-        <v>78171</v>
+        <v>78526</v>
       </c>
       <c r="C98" t="inlineStr">
         <is>
@@ -10483,21 +10492,21 @@
         </is>
       </c>
       <c r="E98" t="n">
-        <v>353</v>
+        <v>6425</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I98" t="inlineStr"/>
@@ -10507,10 +10516,10 @@
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>478158</v>
+        <v>478154</v>
       </c>
       <c r="R98" t="n">
-        <v>6827519</v>
+        <v>6827747</v>
       </c>
       <c r="S98" t="n">
         <v>10</v>
@@ -10569,10 +10578,10 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>120075037</v>
+        <v>120075130</v>
       </c>
       <c r="B99" t="n">
-        <v>78262</v>
+        <v>78526</v>
       </c>
       <c r="C99" t="inlineStr">
         <is>
@@ -10585,21 +10594,21 @@
         </is>
       </c>
       <c r="E99" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I99" t="inlineStr"/>
@@ -10609,10 +10618,10 @@
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>478265</v>
+        <v>478264</v>
       </c>
       <c r="R99" t="n">
-        <v>6827716</v>
+        <v>6827733</v>
       </c>
       <c r="S99" t="n">
         <v>10</v>
@@ -10671,7 +10680,7 @@
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>120075086</v>
+        <v>120075134</v>
       </c>
       <c r="B100" t="n">
         <v>78526</v>
@@ -10711,10 +10720,10 @@
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>478104</v>
+        <v>478266</v>
       </c>
       <c r="R100" t="n">
-        <v>6827495</v>
+        <v>6827765</v>
       </c>
       <c r="S100" t="n">
         <v>10</v>
@@ -10773,7 +10782,7 @@
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>120075139</v>
+        <v>120075066</v>
       </c>
       <c r="B101" t="n">
         <v>78526</v>
@@ -10813,10 +10822,10 @@
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>478294</v>
+        <v>478160</v>
       </c>
       <c r="R101" t="n">
-        <v>6827803</v>
+        <v>6827680</v>
       </c>
       <c r="S101" t="n">
         <v>10</v>
@@ -10875,10 +10884,10 @@
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>120075159</v>
+        <v>120074887</v>
       </c>
       <c r="B102" t="n">
-        <v>78526</v>
+        <v>79144</v>
       </c>
       <c r="C102" t="inlineStr">
         <is>
@@ -10891,21 +10900,21 @@
         </is>
       </c>
       <c r="E102" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I102" t="inlineStr"/>
@@ -10915,10 +10924,10 @@
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>478100</v>
+        <v>478144</v>
       </c>
       <c r="R102" t="n">
-        <v>6827729</v>
+        <v>6827593</v>
       </c>
       <c r="S102" t="n">
         <v>10</v>
@@ -10977,10 +10986,10 @@
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>120075205</v>
+        <v>120074882</v>
       </c>
       <c r="B103" t="n">
-        <v>78171</v>
+        <v>79144</v>
       </c>
       <c r="C103" t="inlineStr">
         <is>
@@ -10993,21 +11002,21 @@
         </is>
       </c>
       <c r="E103" t="n">
-        <v>353</v>
+        <v>6453</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I103" t="inlineStr"/>
@@ -11017,10 +11026,10 @@
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>478117</v>
+        <v>478162</v>
       </c>
       <c r="R103" t="n">
-        <v>6827612</v>
+        <v>6827593</v>
       </c>
       <c r="S103" t="n">
         <v>10</v>
@@ -11079,7 +11088,7 @@
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>120075088</v>
+        <v>120075192</v>
       </c>
       <c r="B104" t="n">
         <v>78526</v>
@@ -11119,10 +11128,10 @@
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>478151</v>
+        <v>478282</v>
       </c>
       <c r="R104" t="n">
-        <v>6827509</v>
+        <v>6827683</v>
       </c>
       <c r="S104" t="n">
         <v>10</v>
@@ -11181,10 +11190,10 @@
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>120075024</v>
+        <v>120075143</v>
       </c>
       <c r="B105" t="n">
-        <v>78262</v>
+        <v>78526</v>
       </c>
       <c r="C105" t="inlineStr">
         <is>
@@ -11197,21 +11206,21 @@
         </is>
       </c>
       <c r="E105" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I105" t="inlineStr"/>
@@ -11221,10 +11230,10 @@
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>478165</v>
+        <v>478301</v>
       </c>
       <c r="R105" t="n">
-        <v>6827712</v>
+        <v>6827814</v>
       </c>
       <c r="S105" t="n">
         <v>10</v>
@@ -11283,10 +11292,10 @@
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>120074905</v>
+        <v>120075064</v>
       </c>
       <c r="B106" t="n">
-        <v>79144</v>
+        <v>78526</v>
       </c>
       <c r="C106" t="inlineStr">
         <is>
@@ -11299,21 +11308,21 @@
         </is>
       </c>
       <c r="E106" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I106" t="inlineStr"/>
@@ -11323,10 +11332,10 @@
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>478285</v>
+        <v>478192</v>
       </c>
       <c r="R106" t="n">
-        <v>6827770</v>
+        <v>6827690</v>
       </c>
       <c r="S106" t="n">
         <v>10</v>
@@ -11385,10 +11394,10 @@
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>120075048</v>
+        <v>120075175</v>
       </c>
       <c r="B107" t="n">
-        <v>56514</v>
+        <v>78526</v>
       </c>
       <c r="C107" t="inlineStr">
         <is>
@@ -11401,39 +11410,34 @@
         </is>
       </c>
       <c r="E107" t="n">
-        <v>102612</v>
+        <v>6425</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I107" t="inlineStr"/>
-      <c r="M107" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
       <c r="P107" t="inlineStr">
         <is>
           <t>Hevoslamm, Dlr</t>
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>478070</v>
+        <v>478059</v>
       </c>
       <c r="R107" t="n">
-        <v>6827723</v>
+        <v>6827739</v>
       </c>
       <c r="S107" t="n">
         <v>10</v>
@@ -11492,10 +11496,10 @@
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>120075070</v>
+        <v>120075224</v>
       </c>
       <c r="B108" t="n">
-        <v>78526</v>
+        <v>78171</v>
       </c>
       <c r="C108" t="inlineStr">
         <is>
@@ -11508,21 +11512,21 @@
         </is>
       </c>
       <c r="E108" t="n">
-        <v>6425</v>
+        <v>353</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I108" t="inlineStr"/>
@@ -11532,10 +11536,10 @@
         </is>
       </c>
       <c r="Q108" t="n">
-        <v>478135</v>
+        <v>478081</v>
       </c>
       <c r="R108" t="n">
-        <v>6827625</v>
+        <v>6827789</v>
       </c>
       <c r="S108" t="n">
         <v>10</v>
@@ -11594,10 +11598,10 @@
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>120075129</v>
+        <v>120074956</v>
       </c>
       <c r="B109" t="n">
-        <v>78526</v>
+        <v>57310</v>
       </c>
       <c r="C109" t="inlineStr">
         <is>
@@ -11610,34 +11614,39 @@
         </is>
       </c>
       <c r="E109" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I109" t="inlineStr"/>
+      <c r="M109" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P109" t="inlineStr">
         <is>
           <t>Hevoslamm, Dlr</t>
         </is>
       </c>
       <c r="Q109" t="n">
-        <v>478265</v>
+        <v>478278</v>
       </c>
       <c r="R109" t="n">
-        <v>6827707</v>
+        <v>6827832</v>
       </c>
       <c r="S109" t="n">
         <v>10</v>
@@ -11670,6 +11679,11 @@
       <c r="AA109" t="inlineStr">
         <is>
           <t>2024-09-27</t>
+        </is>
+      </c>
+      <c r="AC109" t="inlineStr">
+        <is>
+          <t>Färska ringhack (tall)</t>
         </is>
       </c>
       <c r="AD109" t="b">
@@ -11696,10 +11710,10 @@
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>120075068</v>
+        <v>120075009</v>
       </c>
       <c r="B110" t="n">
-        <v>78526</v>
+        <v>78263</v>
       </c>
       <c r="C110" t="inlineStr">
         <is>
@@ -11712,21 +11726,21 @@
         </is>
       </c>
       <c r="E110" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I110" t="inlineStr"/>
@@ -11736,10 +11750,10 @@
         </is>
       </c>
       <c r="Q110" t="n">
-        <v>478174</v>
+        <v>478151</v>
       </c>
       <c r="R110" t="n">
-        <v>6827656</v>
+        <v>6827745</v>
       </c>
       <c r="S110" t="n">
         <v>10</v>
@@ -11798,10 +11812,10 @@
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>120075016</v>
+        <v>120074996</v>
       </c>
       <c r="B111" t="n">
-        <v>79607</v>
+        <v>78263</v>
       </c>
       <c r="C111" t="inlineStr">
         <is>
@@ -11814,21 +11828,21 @@
         </is>
       </c>
       <c r="E111" t="n">
-        <v>6458</v>
+        <v>228912</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I111" t="inlineStr"/>
@@ -11838,10 +11852,10 @@
         </is>
       </c>
       <c r="Q111" t="n">
-        <v>478096</v>
+        <v>478165</v>
       </c>
       <c r="R111" t="n">
-        <v>6827549</v>
+        <v>6827712</v>
       </c>
       <c r="S111" t="n">
         <v>10</v>
@@ -11900,7 +11914,7 @@
     </row>
     <row r="112">
       <c r="A112" t="n">
-        <v>120075166</v>
+        <v>120075065</v>
       </c>
       <c r="B112" t="n">
         <v>78526</v>
@@ -11940,10 +11954,10 @@
         </is>
       </c>
       <c r="Q112" t="n">
-        <v>478092</v>
+        <v>478169</v>
       </c>
       <c r="R112" t="n">
-        <v>6827839</v>
+        <v>6827679</v>
       </c>
       <c r="S112" t="n">
         <v>10</v>
@@ -12002,10 +12016,10 @@
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>120075224</v>
+        <v>120075024</v>
       </c>
       <c r="B113" t="n">
-        <v>78171</v>
+        <v>78262</v>
       </c>
       <c r="C113" t="inlineStr">
         <is>
@@ -12018,21 +12032,21 @@
         </is>
       </c>
       <c r="E113" t="n">
-        <v>353</v>
+        <v>6446</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I113" t="inlineStr"/>
@@ -12042,10 +12056,10 @@
         </is>
       </c>
       <c r="Q113" t="n">
-        <v>478081</v>
+        <v>478165</v>
       </c>
       <c r="R113" t="n">
-        <v>6827789</v>
+        <v>6827712</v>
       </c>
       <c r="S113" t="n">
         <v>10</v>
@@ -12104,7 +12118,7 @@
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>120074934</v>
+        <v>120074935</v>
       </c>
       <c r="B114" t="n">
         <v>79144</v>
@@ -12144,10 +12158,10 @@
         </is>
       </c>
       <c r="Q114" t="n">
-        <v>478169</v>
+        <v>478150</v>
       </c>
       <c r="R114" t="n">
-        <v>6827760</v>
+        <v>6827745</v>
       </c>
       <c r="S114" t="n">
         <v>10</v>
@@ -12206,10 +12220,10 @@
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>120075060</v>
+        <v>120074945</v>
       </c>
       <c r="B115" t="n">
-        <v>78526</v>
+        <v>79144</v>
       </c>
       <c r="C115" t="inlineStr">
         <is>
@@ -12222,21 +12236,21 @@
         </is>
       </c>
       <c r="E115" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I115" t="inlineStr"/>
@@ -12246,10 +12260,10 @@
         </is>
       </c>
       <c r="Q115" t="n">
-        <v>478087</v>
+        <v>478061</v>
       </c>
       <c r="R115" t="n">
-        <v>6827718</v>
+        <v>6827770</v>
       </c>
       <c r="S115" t="n">
         <v>10</v>
@@ -12308,10 +12322,10 @@
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>120075084</v>
+        <v>120075219</v>
       </c>
       <c r="B116" t="n">
-        <v>78526</v>
+        <v>78171</v>
       </c>
       <c r="C116" t="inlineStr">
         <is>
@@ -12324,21 +12338,21 @@
         </is>
       </c>
       <c r="E116" t="n">
-        <v>6425</v>
+        <v>353</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I116" t="inlineStr"/>
@@ -12348,10 +12362,10 @@
         </is>
       </c>
       <c r="Q116" t="n">
-        <v>478098</v>
+        <v>478169</v>
       </c>
       <c r="R116" t="n">
-        <v>6827520</v>
+        <v>6827760</v>
       </c>
       <c r="S116" t="n">
         <v>10</v>
@@ -12410,10 +12424,10 @@
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>120075219</v>
+        <v>120075132</v>
       </c>
       <c r="B117" t="n">
-        <v>78171</v>
+        <v>78526</v>
       </c>
       <c r="C117" t="inlineStr">
         <is>
@@ -12426,21 +12440,21 @@
         </is>
       </c>
       <c r="E117" t="n">
-        <v>353</v>
+        <v>6425</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I117" t="inlineStr"/>
@@ -12450,10 +12464,10 @@
         </is>
       </c>
       <c r="Q117" t="n">
-        <v>478169</v>
+        <v>478240</v>
       </c>
       <c r="R117" t="n">
-        <v>6827760</v>
+        <v>6827754</v>
       </c>
       <c r="S117" t="n">
         <v>10</v>
@@ -12512,7 +12526,7 @@
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>120075161</v>
+        <v>120075094</v>
       </c>
       <c r="B118" t="n">
         <v>78526</v>
@@ -12552,10 +12566,10 @@
         </is>
       </c>
       <c r="Q118" t="n">
-        <v>478082</v>
+        <v>478205</v>
       </c>
       <c r="R118" t="n">
-        <v>6827766</v>
+        <v>6827556</v>
       </c>
       <c r="S118" t="n">
         <v>10</v>
@@ -12614,10 +12628,10 @@
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>120075227</v>
+        <v>120075082</v>
       </c>
       <c r="B119" t="n">
-        <v>78171</v>
+        <v>78526</v>
       </c>
       <c r="C119" t="inlineStr">
         <is>
@@ -12630,21 +12644,21 @@
         </is>
       </c>
       <c r="E119" t="n">
-        <v>353</v>
+        <v>6425</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I119" t="inlineStr"/>
@@ -12654,10 +12668,10 @@
         </is>
       </c>
       <c r="Q119" t="n">
-        <v>478088</v>
+        <v>478097</v>
       </c>
       <c r="R119" t="n">
-        <v>6827834</v>
+        <v>6827544</v>
       </c>
       <c r="S119" t="n">
         <v>10</v>
@@ -12716,10 +12730,10 @@
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>120074891</v>
+        <v>120074912</v>
       </c>
       <c r="B120" t="n">
-        <v>79144</v>
+        <v>78560</v>
       </c>
       <c r="C120" t="inlineStr">
         <is>
@@ -12732,21 +12746,21 @@
         </is>
       </c>
       <c r="E120" t="n">
-        <v>6453</v>
+        <v>185</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I120" t="inlineStr"/>
@@ -12756,10 +12770,10 @@
         </is>
       </c>
       <c r="Q120" t="n">
-        <v>478212</v>
+        <v>478149</v>
       </c>
       <c r="R120" t="n">
-        <v>6827573</v>
+        <v>6827714</v>
       </c>
       <c r="S120" t="n">
         <v>10</v>
@@ -12818,10 +12832,10 @@
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>120075092</v>
+        <v>120075029</v>
       </c>
       <c r="B121" t="n">
-        <v>78526</v>
+        <v>78262</v>
       </c>
       <c r="C121" t="inlineStr">
         <is>
@@ -12834,21 +12848,21 @@
         </is>
       </c>
       <c r="E121" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I121" t="inlineStr"/>
@@ -12858,10 +12872,10 @@
         </is>
       </c>
       <c r="Q121" t="n">
-        <v>478167</v>
+        <v>478115</v>
       </c>
       <c r="R121" t="n">
-        <v>6827561</v>
+        <v>6827564</v>
       </c>
       <c r="S121" t="n">
         <v>10</v>
@@ -12920,10 +12934,10 @@
     </row>
     <row r="122">
       <c r="A122" t="n">
-        <v>120075192</v>
+        <v>120075044</v>
       </c>
       <c r="B122" t="n">
-        <v>78526</v>
+        <v>78262</v>
       </c>
       <c r="C122" t="inlineStr">
         <is>
@@ -12936,21 +12950,21 @@
         </is>
       </c>
       <c r="E122" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I122" t="inlineStr"/>
@@ -12960,10 +12974,10 @@
         </is>
       </c>
       <c r="Q122" t="n">
-        <v>478282</v>
+        <v>478060</v>
       </c>
       <c r="R122" t="n">
-        <v>6827683</v>
+        <v>6827770</v>
       </c>
       <c r="S122" t="n">
         <v>10</v>
@@ -13022,10 +13036,10 @@
     </row>
     <row r="123">
       <c r="A123" t="n">
-        <v>120075127</v>
+        <v>120075239</v>
       </c>
       <c r="B123" t="n">
-        <v>78526</v>
+        <v>77458</v>
       </c>
       <c r="C123" t="inlineStr">
         <is>
@@ -13038,21 +13052,21 @@
         </is>
       </c>
       <c r="E123" t="n">
-        <v>6425</v>
+        <v>6487</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Blågrå svartspik</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenothecopsis fennica</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Laurila) Tibell</t>
         </is>
       </c>
       <c r="I123" t="inlineStr"/>
@@ -13062,10 +13076,10 @@
         </is>
       </c>
       <c r="Q123" t="n">
-        <v>478292</v>
+        <v>478137</v>
       </c>
       <c r="R123" t="n">
-        <v>6827708</v>
+        <v>6827554</v>
       </c>
       <c r="S123" t="n">
         <v>10</v>
@@ -13124,10 +13138,10 @@
     </row>
     <row r="124">
       <c r="A124" t="n">
-        <v>120075027</v>
+        <v>120075012</v>
       </c>
       <c r="B124" t="n">
-        <v>78262</v>
+        <v>78263</v>
       </c>
       <c r="C124" t="inlineStr">
         <is>
@@ -13140,21 +13154,21 @@
         </is>
       </c>
       <c r="E124" t="n">
-        <v>6446</v>
+        <v>228912</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I124" t="inlineStr"/>
@@ -13164,10 +13178,10 @@
         </is>
       </c>
       <c r="Q124" t="n">
-        <v>478144</v>
+        <v>478055</v>
       </c>
       <c r="R124" t="n">
-        <v>6827593</v>
+        <v>6827786</v>
       </c>
       <c r="S124" t="n">
         <v>10</v>
@@ -13226,10 +13240,10 @@
     </row>
     <row r="125">
       <c r="A125" t="n">
-        <v>120075043</v>
+        <v>120075081</v>
       </c>
       <c r="B125" t="n">
-        <v>78262</v>
+        <v>78526</v>
       </c>
       <c r="C125" t="inlineStr">
         <is>
@@ -13242,21 +13256,21 @@
         </is>
       </c>
       <c r="E125" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I125" t="inlineStr"/>
@@ -13266,10 +13280,10 @@
         </is>
       </c>
       <c r="Q125" t="n">
-        <v>478103</v>
+        <v>478096</v>
       </c>
       <c r="R125" t="n">
-        <v>6827803</v>
+        <v>6827550</v>
       </c>
       <c r="S125" t="n">
         <v>10</v>
@@ -13328,10 +13342,10 @@
     </row>
     <row r="126">
       <c r="A126" t="n">
-        <v>120075223</v>
+        <v>120075090</v>
       </c>
       <c r="B126" t="n">
-        <v>78171</v>
+        <v>78526</v>
       </c>
       <c r="C126" t="inlineStr">
         <is>
@@ -13344,21 +13358,21 @@
         </is>
       </c>
       <c r="E126" t="n">
-        <v>353</v>
+        <v>6425</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H126" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I126" t="inlineStr"/>
@@ -13368,10 +13382,10 @@
         </is>
       </c>
       <c r="Q126" t="n">
-        <v>478076</v>
+        <v>478161</v>
       </c>
       <c r="R126" t="n">
-        <v>6827777</v>
+        <v>6827528</v>
       </c>
       <c r="S126" t="n">
         <v>10</v>
@@ -13430,10 +13444,10 @@
     </row>
     <row r="127">
       <c r="A127" t="n">
-        <v>120075206</v>
+        <v>120075083</v>
       </c>
       <c r="B127" t="n">
-        <v>78171</v>
+        <v>78526</v>
       </c>
       <c r="C127" t="inlineStr">
         <is>
@@ -13446,21 +13460,21 @@
         </is>
       </c>
       <c r="E127" t="n">
-        <v>353</v>
+        <v>6425</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H127" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I127" t="inlineStr"/>
@@ -13470,10 +13484,10 @@
         </is>
       </c>
       <c r="Q127" t="n">
-        <v>478125</v>
+        <v>478097</v>
       </c>
       <c r="R127" t="n">
-        <v>6827604</v>
+        <v>6827527</v>
       </c>
       <c r="S127" t="n">
         <v>10</v>
@@ -13532,10 +13546,10 @@
     </row>
     <row r="128">
       <c r="A128" t="n">
-        <v>120074956</v>
+        <v>120074904</v>
       </c>
       <c r="B128" t="n">
-        <v>57310</v>
+        <v>79144</v>
       </c>
       <c r="C128" t="inlineStr">
         <is>
@@ -13548,39 +13562,34 @@
         </is>
       </c>
       <c r="E128" t="n">
-        <v>100109</v>
+        <v>6453</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H128" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I128" t="inlineStr"/>
-      <c r="M128" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P128" t="inlineStr">
         <is>
           <t>Hevoslamm, Dlr</t>
         </is>
       </c>
       <c r="Q128" t="n">
-        <v>478278</v>
+        <v>478262</v>
       </c>
       <c r="R128" t="n">
-        <v>6827832</v>
+        <v>6827730</v>
       </c>
       <c r="S128" t="n">
         <v>10</v>
@@ -13613,11 +13622,6 @@
       <c r="AA128" t="inlineStr">
         <is>
           <t>2024-09-27</t>
-        </is>
-      </c>
-      <c r="AC128" t="inlineStr">
-        <is>
-          <t>Färska ringhack (tall)</t>
         </is>
       </c>
       <c r="AD128" t="b">
@@ -13644,10 +13648,10 @@
     </row>
     <row r="129">
       <c r="A129" t="n">
-        <v>120075226</v>
+        <v>120075040</v>
       </c>
       <c r="B129" t="n">
-        <v>78171</v>
+        <v>78262</v>
       </c>
       <c r="C129" t="inlineStr">
         <is>
@@ -13660,21 +13664,21 @@
         </is>
       </c>
       <c r="E129" t="n">
-        <v>353</v>
+        <v>6446</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H129" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I129" t="inlineStr"/>
@@ -13684,10 +13688,10 @@
         </is>
       </c>
       <c r="Q129" t="n">
-        <v>478098</v>
+        <v>478250</v>
       </c>
       <c r="R129" t="n">
-        <v>6827815</v>
+        <v>6827802</v>
       </c>
       <c r="S129" t="n">
         <v>10</v>
@@ -13746,10 +13750,10 @@
     </row>
     <row r="130">
       <c r="A130" t="n">
-        <v>120075197</v>
+        <v>120074881</v>
       </c>
       <c r="B130" t="n">
-        <v>91840</v>
+        <v>79144</v>
       </c>
       <c r="C130" t="inlineStr">
         <is>
@@ -13758,47 +13762,38 @@
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E130" t="n">
-        <v>4364</v>
+        <v>6453</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H130" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I130" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J130" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I130" t="inlineStr"/>
       <c r="P130" t="inlineStr">
         <is>
           <t>Hevoslamm, Dlr</t>
         </is>
       </c>
       <c r="Q130" t="n">
-        <v>478077</v>
+        <v>478184</v>
       </c>
       <c r="R130" t="n">
-        <v>6827805</v>
+        <v>6827728</v>
       </c>
       <c r="S130" t="n">
         <v>10</v>
@@ -13857,10 +13852,10 @@
     </row>
     <row r="131">
       <c r="A131" t="n">
-        <v>120074917</v>
+        <v>120075054</v>
       </c>
       <c r="B131" t="n">
-        <v>78560</v>
+        <v>90580</v>
       </c>
       <c r="C131" t="inlineStr">
         <is>
@@ -13873,21 +13868,21 @@
         </is>
       </c>
       <c r="E131" t="n">
-        <v>185</v>
+        <v>5432</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H131" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I131" t="inlineStr"/>
@@ -13897,10 +13892,10 @@
         </is>
       </c>
       <c r="Q131" t="n">
-        <v>478095</v>
+        <v>478126</v>
       </c>
       <c r="R131" t="n">
-        <v>6827533</v>
+        <v>6827477</v>
       </c>
       <c r="S131" t="n">
         <v>10</v>
@@ -13959,10 +13954,10 @@
     </row>
     <row r="132">
       <c r="A132" t="n">
-        <v>120075225</v>
+        <v>120075010</v>
       </c>
       <c r="B132" t="n">
-        <v>78171</v>
+        <v>78263</v>
       </c>
       <c r="C132" t="inlineStr">
         <is>
@@ -13975,21 +13970,21 @@
         </is>
       </c>
       <c r="E132" t="n">
-        <v>353</v>
+        <v>228912</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H132" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I132" t="inlineStr"/>
@@ -13999,10 +13994,10 @@
         </is>
       </c>
       <c r="Q132" t="n">
-        <v>478075</v>
+        <v>478074</v>
       </c>
       <c r="R132" t="n">
-        <v>6827798</v>
+        <v>6827772</v>
       </c>
       <c r="S132" t="n">
         <v>10</v>
@@ -14061,10 +14056,10 @@
     </row>
     <row r="133">
       <c r="A133" t="n">
-        <v>120075000</v>
+        <v>120075226</v>
       </c>
       <c r="B133" t="n">
-        <v>78263</v>
+        <v>78171</v>
       </c>
       <c r="C133" t="inlineStr">
         <is>
@@ -14077,21 +14072,21 @@
         </is>
       </c>
       <c r="E133" t="n">
-        <v>228912</v>
+        <v>353</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H133" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I133" t="inlineStr"/>
@@ -14101,10 +14096,10 @@
         </is>
       </c>
       <c r="Q133" t="n">
-        <v>478121</v>
+        <v>478098</v>
       </c>
       <c r="R133" t="n">
-        <v>6827607</v>
+        <v>6827815</v>
       </c>
       <c r="S133" t="n">
         <v>10</v>
@@ -14163,10 +14158,10 @@
     </row>
     <row r="134">
       <c r="A134" t="n">
-        <v>120075157</v>
+        <v>120074929</v>
       </c>
       <c r="B134" t="n">
-        <v>78526</v>
+        <v>78560</v>
       </c>
       <c r="C134" t="inlineStr">
         <is>
@@ -14179,21 +14174,21 @@
         </is>
       </c>
       <c r="E134" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H134" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I134" t="inlineStr"/>
@@ -14203,10 +14198,10 @@
         </is>
       </c>
       <c r="Q134" t="n">
-        <v>478103</v>
+        <v>478045</v>
       </c>
       <c r="R134" t="n">
-        <v>6827718</v>
+        <v>6827724</v>
       </c>
       <c r="S134" t="n">
         <v>10</v>
@@ -14265,10 +14260,10 @@
     </row>
     <row r="135">
       <c r="A135" t="n">
-        <v>120074889</v>
+        <v>120074997</v>
       </c>
       <c r="B135" t="n">
-        <v>79144</v>
+        <v>78263</v>
       </c>
       <c r="C135" t="inlineStr">
         <is>
@@ -14281,21 +14276,21 @@
         </is>
       </c>
       <c r="E135" t="n">
-        <v>6453</v>
+        <v>228912</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H135" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I135" t="inlineStr"/>
@@ -14305,10 +14300,10 @@
         </is>
       </c>
       <c r="Q135" t="n">
-        <v>478163</v>
+        <v>478218</v>
       </c>
       <c r="R135" t="n">
-        <v>6827536</v>
+        <v>6827733</v>
       </c>
       <c r="S135" t="n">
         <v>10</v>
@@ -14367,10 +14362,10 @@
     </row>
     <row r="136">
       <c r="A136" t="n">
-        <v>120075217</v>
+        <v>120074927</v>
       </c>
       <c r="B136" t="n">
-        <v>78171</v>
+        <v>78560</v>
       </c>
       <c r="C136" t="inlineStr">
         <is>
@@ -14383,21 +14378,21 @@
         </is>
       </c>
       <c r="E136" t="n">
-        <v>353</v>
+        <v>185</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H136" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I136" t="inlineStr"/>
@@ -14407,10 +14402,10 @@
         </is>
       </c>
       <c r="Q136" t="n">
-        <v>478264</v>
+        <v>478073</v>
       </c>
       <c r="R136" t="n">
-        <v>6827839</v>
+        <v>6827836</v>
       </c>
       <c r="S136" t="n">
         <v>10</v>
@@ -14469,10 +14464,10 @@
     </row>
     <row r="137">
       <c r="A137" t="n">
-        <v>120074935</v>
+        <v>120075225</v>
       </c>
       <c r="B137" t="n">
-        <v>79144</v>
+        <v>78171</v>
       </c>
       <c r="C137" t="inlineStr">
         <is>
@@ -14485,21 +14480,21 @@
         </is>
       </c>
       <c r="E137" t="n">
-        <v>6453</v>
+        <v>353</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H137" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I137" t="inlineStr"/>
@@ -14509,10 +14504,10 @@
         </is>
       </c>
       <c r="Q137" t="n">
-        <v>478150</v>
+        <v>478075</v>
       </c>
       <c r="R137" t="n">
-        <v>6827745</v>
+        <v>6827798</v>
       </c>
       <c r="S137" t="n">
         <v>10</v>
@@ -14571,10 +14566,10 @@
     </row>
     <row r="138">
       <c r="A138" t="n">
-        <v>120075097</v>
+        <v>120075206</v>
       </c>
       <c r="B138" t="n">
-        <v>78526</v>
+        <v>78171</v>
       </c>
       <c r="C138" t="inlineStr">
         <is>
@@ -14587,21 +14582,21 @@
         </is>
       </c>
       <c r="E138" t="n">
-        <v>6425</v>
+        <v>353</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H138" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I138" t="inlineStr"/>
@@ -14611,10 +14606,10 @@
         </is>
       </c>
       <c r="Q138" t="n">
-        <v>478248</v>
+        <v>478125</v>
       </c>
       <c r="R138" t="n">
-        <v>6827593</v>
+        <v>6827604</v>
       </c>
       <c r="S138" t="n">
         <v>10</v>
@@ -14673,10 +14668,10 @@
     </row>
     <row r="139">
       <c r="A139" t="n">
-        <v>120074942</v>
+        <v>120075085</v>
       </c>
       <c r="B139" t="n">
-        <v>79144</v>
+        <v>78526</v>
       </c>
       <c r="C139" t="inlineStr">
         <is>
@@ -14689,21 +14684,21 @@
         </is>
       </c>
       <c r="E139" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H139" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I139" t="inlineStr"/>
@@ -14713,10 +14708,10 @@
         </is>
       </c>
       <c r="Q139" t="n">
-        <v>478065</v>
+        <v>478094</v>
       </c>
       <c r="R139" t="n">
-        <v>6827842</v>
+        <v>6827504</v>
       </c>
       <c r="S139" t="n">
         <v>10</v>
@@ -14775,7 +14770,7 @@
     </row>
     <row r="140">
       <c r="A140" t="n">
-        <v>120075066</v>
+        <v>120075163</v>
       </c>
       <c r="B140" t="n">
         <v>78526</v>
@@ -14815,10 +14810,10 @@
         </is>
       </c>
       <c r="Q140" t="n">
-        <v>478160</v>
+        <v>478102</v>
       </c>
       <c r="R140" t="n">
-        <v>6827680</v>
+        <v>6827800</v>
       </c>
       <c r="S140" t="n">
         <v>10</v>
@@ -14877,10 +14872,10 @@
     </row>
     <row r="141">
       <c r="A141" t="n">
-        <v>120074947</v>
+        <v>120075127</v>
       </c>
       <c r="B141" t="n">
-        <v>79144</v>
+        <v>78526</v>
       </c>
       <c r="C141" t="inlineStr">
         <is>
@@ -14893,21 +14888,21 @@
         </is>
       </c>
       <c r="E141" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H141" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I141" t="inlineStr"/>
@@ -14917,10 +14912,10 @@
         </is>
       </c>
       <c r="Q141" t="n">
-        <v>478061</v>
+        <v>478292</v>
       </c>
       <c r="R141" t="n">
-        <v>6827751</v>
+        <v>6827708</v>
       </c>
       <c r="S141" t="n">
         <v>10</v>
@@ -14979,10 +14974,10 @@
     </row>
     <row r="142">
       <c r="A142" t="n">
-        <v>120075198</v>
+        <v>120075160</v>
       </c>
       <c r="B142" t="n">
-        <v>91840</v>
+        <v>78526</v>
       </c>
       <c r="C142" t="inlineStr">
         <is>
@@ -14991,25 +14986,25 @@
       </c>
       <c r="D142" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E142" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H142" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I142" t="inlineStr"/>
@@ -15019,10 +15014,10 @@
         </is>
       </c>
       <c r="Q142" t="n">
-        <v>478163</v>
+        <v>478097</v>
       </c>
       <c r="R142" t="n">
-        <v>6827530</v>
+        <v>6827744</v>
       </c>
       <c r="S142" t="n">
         <v>10</v>
@@ -15081,7 +15076,7 @@
     </row>
     <row r="143">
       <c r="A143" t="n">
-        <v>120075168</v>
+        <v>120075138</v>
       </c>
       <c r="B143" t="n">
         <v>78526</v>
@@ -15121,10 +15116,10 @@
         </is>
       </c>
       <c r="Q143" t="n">
-        <v>478086</v>
+        <v>478294</v>
       </c>
       <c r="R143" t="n">
-        <v>6827868</v>
+        <v>6827781</v>
       </c>
       <c r="S143" t="n">
         <v>10</v>
@@ -15183,7 +15178,7 @@
     </row>
     <row r="144">
       <c r="A144" t="n">
-        <v>120075121</v>
+        <v>120075161</v>
       </c>
       <c r="B144" t="n">
         <v>78526</v>
@@ -15223,10 +15218,10 @@
         </is>
       </c>
       <c r="Q144" t="n">
-        <v>478232</v>
+        <v>478082</v>
       </c>
       <c r="R144" t="n">
-        <v>6827659</v>
+        <v>6827766</v>
       </c>
       <c r="S144" t="n">
         <v>10</v>
@@ -15285,7 +15280,7 @@
     </row>
     <row r="145">
       <c r="A145" t="n">
-        <v>120074883</v>
+        <v>120074938</v>
       </c>
       <c r="B145" t="n">
         <v>79144</v>
@@ -15325,10 +15320,10 @@
         </is>
       </c>
       <c r="Q145" t="n">
-        <v>478142</v>
+        <v>478097</v>
       </c>
       <c r="R145" t="n">
-        <v>6827623</v>
+        <v>6827756</v>
       </c>
       <c r="S145" t="n">
         <v>10</v>
@@ -15387,10 +15382,10 @@
     </row>
     <row r="146">
       <c r="A146" t="n">
-        <v>120074886</v>
+        <v>120075047</v>
       </c>
       <c r="B146" t="n">
-        <v>79144</v>
+        <v>78262</v>
       </c>
       <c r="C146" t="inlineStr">
         <is>
@@ -15403,21 +15398,21 @@
         </is>
       </c>
       <c r="E146" t="n">
-        <v>6453</v>
+        <v>6446</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H146" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I146" t="inlineStr"/>
@@ -15427,10 +15422,10 @@
         </is>
       </c>
       <c r="Q146" t="n">
-        <v>478125</v>
+        <v>478212</v>
       </c>
       <c r="R146" t="n">
-        <v>6827604</v>
+        <v>6827573</v>
       </c>
       <c r="S146" t="n">
         <v>10</v>
@@ -15489,10 +15484,10 @@
     </row>
     <row r="147">
       <c r="A147" t="n">
-        <v>120074998</v>
+        <v>120075061</v>
       </c>
       <c r="B147" t="n">
-        <v>78263</v>
+        <v>78526</v>
       </c>
       <c r="C147" t="inlineStr">
         <is>
@@ -15505,21 +15500,21 @@
         </is>
       </c>
       <c r="E147" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G147" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H147" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I147" t="inlineStr"/>
@@ -15529,10 +15524,10 @@
         </is>
       </c>
       <c r="Q147" t="n">
-        <v>478172</v>
+        <v>478160</v>
       </c>
       <c r="R147" t="n">
-        <v>6827640</v>
+        <v>6827710</v>
       </c>
       <c r="S147" t="n">
         <v>10</v>
@@ -15591,10 +15586,10 @@
     </row>
     <row r="148">
       <c r="A148" t="n">
-        <v>120074997</v>
+        <v>120075060</v>
       </c>
       <c r="B148" t="n">
-        <v>78263</v>
+        <v>78526</v>
       </c>
       <c r="C148" t="inlineStr">
         <is>
@@ -15607,21 +15602,21 @@
         </is>
       </c>
       <c r="E148" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G148" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H148" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I148" t="inlineStr"/>
@@ -15631,10 +15626,10 @@
         </is>
       </c>
       <c r="Q148" t="n">
-        <v>478218</v>
+        <v>478087</v>
       </c>
       <c r="R148" t="n">
-        <v>6827733</v>
+        <v>6827718</v>
       </c>
       <c r="S148" t="n">
         <v>10</v>
@@ -15693,10 +15688,10 @@
     </row>
     <row r="149">
       <c r="A149" t="n">
-        <v>120075236</v>
+        <v>120075140</v>
       </c>
       <c r="B149" t="n">
-        <v>78171</v>
+        <v>78526</v>
       </c>
       <c r="C149" t="inlineStr">
         <is>
@@ -15709,21 +15704,21 @@
         </is>
       </c>
       <c r="E149" t="n">
-        <v>353</v>
+        <v>6425</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G149" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H149" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I149" t="inlineStr"/>
@@ -15733,10 +15728,10 @@
         </is>
       </c>
       <c r="Q149" t="n">
-        <v>478062</v>
+        <v>478310</v>
       </c>
       <c r="R149" t="n">
-        <v>6827740</v>
+        <v>6827797</v>
       </c>
       <c r="S149" t="n">
         <v>10</v>
@@ -15795,10 +15790,10 @@
     </row>
     <row r="150">
       <c r="A150" t="n">
-        <v>120075162</v>
+        <v>120074888</v>
       </c>
       <c r="B150" t="n">
-        <v>78526</v>
+        <v>79144</v>
       </c>
       <c r="C150" t="inlineStr">
         <is>
@@ -15811,21 +15806,21 @@
         </is>
       </c>
       <c r="E150" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G150" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H150" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I150" t="inlineStr"/>
@@ -15835,10 +15830,10 @@
         </is>
       </c>
       <c r="Q150" t="n">
-        <v>478080</v>
+        <v>478139</v>
       </c>
       <c r="R150" t="n">
-        <v>6827808</v>
+        <v>6827554</v>
       </c>
       <c r="S150" t="n">
         <v>10</v>
@@ -15897,10 +15892,10 @@
     </row>
     <row r="151">
       <c r="A151" t="n">
-        <v>120075143</v>
+        <v>120074933</v>
       </c>
       <c r="B151" t="n">
-        <v>78526</v>
+        <v>79144</v>
       </c>
       <c r="C151" t="inlineStr">
         <is>
@@ -15913,21 +15908,21 @@
         </is>
       </c>
       <c r="E151" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G151" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H151" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I151" t="inlineStr"/>
@@ -15937,10 +15932,10 @@
         </is>
       </c>
       <c r="Q151" t="n">
-        <v>478301</v>
+        <v>478189</v>
       </c>
       <c r="R151" t="n">
-        <v>6827814</v>
+        <v>6827761</v>
       </c>
       <c r="S151" t="n">
         <v>10</v>
@@ -15999,10 +15994,10 @@
     </row>
     <row r="152">
       <c r="A152" t="n">
-        <v>120075147</v>
+        <v>120075048</v>
       </c>
       <c r="B152" t="n">
-        <v>78526</v>
+        <v>56514</v>
       </c>
       <c r="C152" t="inlineStr">
         <is>
@@ -16015,34 +16010,39 @@
         </is>
       </c>
       <c r="E152" t="n">
-        <v>6425</v>
+        <v>102612</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G152" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H152" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I152" t="inlineStr"/>
+      <c r="M152" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="P152" t="inlineStr">
         <is>
           <t>Hevoslamm, Dlr</t>
         </is>
       </c>
       <c r="Q152" t="n">
-        <v>478153</v>
+        <v>478070</v>
       </c>
       <c r="R152" t="n">
-        <v>6827728</v>
+        <v>6827723</v>
       </c>
       <c r="S152" t="n">
         <v>10</v>
@@ -16101,10 +16101,10 @@
     </row>
     <row r="153">
       <c r="A153" t="n">
-        <v>120075095</v>
+        <v>120075198</v>
       </c>
       <c r="B153" t="n">
-        <v>78526</v>
+        <v>91840</v>
       </c>
       <c r="C153" t="inlineStr">
         <is>
@@ -16113,25 +16113,25 @@
       </c>
       <c r="D153" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E153" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G153" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H153" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I153" t="inlineStr"/>
@@ -16141,10 +16141,10 @@
         </is>
       </c>
       <c r="Q153" t="n">
-        <v>478219</v>
+        <v>478163</v>
       </c>
       <c r="R153" t="n">
-        <v>6827572</v>
+        <v>6827530</v>
       </c>
       <c r="S153" t="n">
         <v>10</v>
@@ -16203,10 +16203,10 @@
     </row>
     <row r="154">
       <c r="A154" t="n">
-        <v>120075090</v>
+        <v>120075011</v>
       </c>
       <c r="B154" t="n">
-        <v>78526</v>
+        <v>78263</v>
       </c>
       <c r="C154" t="inlineStr">
         <is>
@@ -16219,21 +16219,21 @@
         </is>
       </c>
       <c r="E154" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G154" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H154" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I154" t="inlineStr"/>
@@ -16243,10 +16243,10 @@
         </is>
       </c>
       <c r="Q154" t="n">
-        <v>478161</v>
+        <v>478103</v>
       </c>
       <c r="R154" t="n">
-        <v>6827528</v>
+        <v>6827803</v>
       </c>
       <c r="S154" t="n">
         <v>10</v>
@@ -16305,10 +16305,10 @@
     </row>
     <row r="155">
       <c r="A155" t="n">
-        <v>120075038</v>
+        <v>120075001</v>
       </c>
       <c r="B155" t="n">
-        <v>78262</v>
+        <v>78263</v>
       </c>
       <c r="C155" t="inlineStr">
         <is>
@@ -16321,21 +16321,21 @@
         </is>
       </c>
       <c r="E155" t="n">
-        <v>6446</v>
+        <v>228912</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G155" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H155" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I155" t="inlineStr"/>
@@ -16345,10 +16345,10 @@
         </is>
       </c>
       <c r="Q155" t="n">
-        <v>478261</v>
+        <v>478125</v>
       </c>
       <c r="R155" t="n">
-        <v>6827731</v>
+        <v>6827604</v>
       </c>
       <c r="S155" t="n">
         <v>10</v>
@@ -16407,7 +16407,7 @@
     </row>
     <row r="156">
       <c r="A156" t="n">
-        <v>120074904</v>
+        <v>120074939</v>
       </c>
       <c r="B156" t="n">
         <v>79144</v>
@@ -16447,10 +16447,10 @@
         </is>
       </c>
       <c r="Q156" t="n">
-        <v>478262</v>
+        <v>478091</v>
       </c>
       <c r="R156" t="n">
-        <v>6827730</v>
+        <v>6827838</v>
       </c>
       <c r="S156" t="n">
         <v>10</v>
@@ -16509,7 +16509,7 @@
     </row>
     <row r="157">
       <c r="A157" t="n">
-        <v>120075019</v>
+        <v>120075015</v>
       </c>
       <c r="B157" t="n">
         <v>79607</v>
@@ -16549,10 +16549,10 @@
         </is>
       </c>
       <c r="Q157" t="n">
-        <v>478227</v>
+        <v>478114</v>
       </c>
       <c r="R157" t="n">
-        <v>6827655</v>
+        <v>6827633</v>
       </c>
       <c r="S157" t="n">
         <v>10</v>
@@ -16611,10 +16611,10 @@
     </row>
     <row r="158">
       <c r="A158" t="n">
-        <v>120075078</v>
+        <v>120074961</v>
       </c>
       <c r="B158" t="n">
-        <v>78526</v>
+        <v>90582</v>
       </c>
       <c r="C158" t="inlineStr">
         <is>
@@ -16627,21 +16627,21 @@
         </is>
       </c>
       <c r="E158" t="n">
-        <v>6425</v>
+        <v>5442</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G158" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H158" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I158" t="inlineStr"/>
@@ -16651,10 +16651,10 @@
         </is>
       </c>
       <c r="Q158" t="n">
-        <v>478116</v>
+        <v>478230</v>
       </c>
       <c r="R158" t="n">
-        <v>6827567</v>
+        <v>6827780</v>
       </c>
       <c r="S158" t="n">
         <v>10</v>
@@ -16713,7 +16713,7 @@
     </row>
     <row r="159">
       <c r="A159" t="n">
-        <v>120075007</v>
+        <v>120074999</v>
       </c>
       <c r="B159" t="n">
         <v>78263</v>
@@ -16753,10 +16753,10 @@
         </is>
       </c>
       <c r="Q159" t="n">
-        <v>478285</v>
+        <v>478161</v>
       </c>
       <c r="R159" t="n">
-        <v>6827770</v>
+        <v>6827592</v>
       </c>
       <c r="S159" t="n">
         <v>10</v>
@@ -16815,10 +16815,10 @@
     </row>
     <row r="160">
       <c r="A160" t="n">
-        <v>120075145</v>
+        <v>120075004</v>
       </c>
       <c r="B160" t="n">
-        <v>78526</v>
+        <v>78263</v>
       </c>
       <c r="C160" t="inlineStr">
         <is>
@@ -16831,21 +16831,21 @@
         </is>
       </c>
       <c r="E160" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G160" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H160" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I160" t="inlineStr"/>
@@ -16855,10 +16855,10 @@
         </is>
       </c>
       <c r="Q160" t="n">
-        <v>478226</v>
+        <v>478212</v>
       </c>
       <c r="R160" t="n">
-        <v>6827777</v>
+        <v>6827573</v>
       </c>
       <c r="S160" t="n">
         <v>10</v>
@@ -17019,10 +17019,10 @@
     </row>
     <row r="162">
       <c r="A162" t="n">
-        <v>120075204</v>
+        <v>120075173</v>
       </c>
       <c r="B162" t="n">
-        <v>78171</v>
+        <v>78526</v>
       </c>
       <c r="C162" t="inlineStr">
         <is>
@@ -17035,21 +17035,21 @@
         </is>
       </c>
       <c r="E162" t="n">
-        <v>353</v>
+        <v>6425</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G162" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H162" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I162" t="inlineStr"/>
@@ -17059,10 +17059,10 @@
         </is>
       </c>
       <c r="Q162" t="n">
-        <v>478115</v>
+        <v>478052</v>
       </c>
       <c r="R162" t="n">
-        <v>6827614</v>
+        <v>6827754</v>
       </c>
       <c r="S162" t="n">
         <v>10</v>
@@ -17121,10 +17121,10 @@
     </row>
     <row r="163">
       <c r="A163" t="n">
-        <v>120074944</v>
+        <v>120075069</v>
       </c>
       <c r="B163" t="n">
-        <v>79144</v>
+        <v>78526</v>
       </c>
       <c r="C163" t="inlineStr">
         <is>
@@ -17137,21 +17137,21 @@
         </is>
       </c>
       <c r="E163" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G163" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H163" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I163" t="inlineStr"/>
@@ -17161,10 +17161,10 @@
         </is>
       </c>
       <c r="Q163" t="n">
-        <v>478056</v>
+        <v>478157</v>
       </c>
       <c r="R163" t="n">
-        <v>6827785</v>
+        <v>6827611</v>
       </c>
       <c r="S163" t="n">
         <v>10</v>
@@ -17223,10 +17223,10 @@
     </row>
     <row r="164">
       <c r="A164" t="n">
-        <v>120074961</v>
+        <v>120075087</v>
       </c>
       <c r="B164" t="n">
-        <v>90582</v>
+        <v>78526</v>
       </c>
       <c r="C164" t="inlineStr">
         <is>
@@ -17239,21 +17239,21 @@
         </is>
       </c>
       <c r="E164" t="n">
-        <v>5442</v>
+        <v>6425</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G164" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H164" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I164" t="inlineStr"/>
@@ -17263,10 +17263,10 @@
         </is>
       </c>
       <c r="Q164" t="n">
-        <v>478230</v>
+        <v>478145</v>
       </c>
       <c r="R164" t="n">
-        <v>6827780</v>
+        <v>6827485</v>
       </c>
       <c r="S164" t="n">
         <v>10</v>
@@ -17325,10 +17325,10 @@
     </row>
     <row r="165">
       <c r="A165" t="n">
-        <v>120074996</v>
+        <v>120075164</v>
       </c>
       <c r="B165" t="n">
-        <v>78263</v>
+        <v>78526</v>
       </c>
       <c r="C165" t="inlineStr">
         <is>
@@ -17341,21 +17341,21 @@
         </is>
       </c>
       <c r="E165" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G165" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H165" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I165" t="inlineStr"/>
@@ -17365,10 +17365,10 @@
         </is>
       </c>
       <c r="Q165" t="n">
-        <v>478165</v>
+        <v>478092</v>
       </c>
       <c r="R165" t="n">
-        <v>6827712</v>
+        <v>6827810</v>
       </c>
       <c r="S165" t="n">
         <v>10</v>
@@ -17427,10 +17427,10 @@
     </row>
     <row r="166">
       <c r="A166" t="n">
-        <v>120074932</v>
+        <v>120075131</v>
       </c>
       <c r="B166" t="n">
-        <v>79144</v>
+        <v>78526</v>
       </c>
       <c r="C166" t="inlineStr">
         <is>
@@ -17443,21 +17443,21 @@
         </is>
       </c>
       <c r="E166" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G166" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H166" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I166" t="inlineStr"/>
@@ -17467,10 +17467,10 @@
         </is>
       </c>
       <c r="Q166" t="n">
-        <v>478250</v>
+        <v>478258</v>
       </c>
       <c r="R166" t="n">
-        <v>6827802</v>
+        <v>6827731</v>
       </c>
       <c r="S166" t="n">
         <v>10</v>
@@ -17529,7 +17529,7 @@
     </row>
     <row r="167">
       <c r="A167" t="n">
-        <v>120075135</v>
+        <v>120075070</v>
       </c>
       <c r="B167" t="n">
         <v>78526</v>
@@ -17569,10 +17569,10 @@
         </is>
       </c>
       <c r="Q167" t="n">
-        <v>478291</v>
+        <v>478135</v>
       </c>
       <c r="R167" t="n">
-        <v>6827744</v>
+        <v>6827625</v>
       </c>
       <c r="S167" t="n">
         <v>10</v>
@@ -17631,10 +17631,10 @@
     </row>
     <row r="168">
       <c r="A168" t="n">
-        <v>120075215</v>
+        <v>120075168</v>
       </c>
       <c r="B168" t="n">
-        <v>78171</v>
+        <v>78526</v>
       </c>
       <c r="C168" t="inlineStr">
         <is>
@@ -17647,21 +17647,21 @@
         </is>
       </c>
       <c r="E168" t="n">
-        <v>353</v>
+        <v>6425</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G168" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H168" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I168" t="inlineStr"/>
@@ -17671,10 +17671,10 @@
         </is>
       </c>
       <c r="Q168" t="n">
-        <v>478239</v>
+        <v>478086</v>
       </c>
       <c r="R168" t="n">
-        <v>6827752</v>
+        <v>6827868</v>
       </c>
       <c r="S168" t="n">
         <v>10</v>
@@ -17733,7 +17733,7 @@
     </row>
     <row r="169">
       <c r="A169" t="n">
-        <v>120075130</v>
+        <v>120075129</v>
       </c>
       <c r="B169" t="n">
         <v>78526</v>
@@ -17773,10 +17773,10 @@
         </is>
       </c>
       <c r="Q169" t="n">
-        <v>478264</v>
+        <v>478265</v>
       </c>
       <c r="R169" t="n">
-        <v>6827733</v>
+        <v>6827707</v>
       </c>
       <c r="S169" t="n">
         <v>10</v>
@@ -17835,7 +17835,7 @@
     </row>
     <row r="170">
       <c r="A170" t="n">
-        <v>120075128</v>
+        <v>120075165</v>
       </c>
       <c r="B170" t="n">
         <v>78526</v>
@@ -17875,10 +17875,10 @@
         </is>
       </c>
       <c r="Q170" t="n">
-        <v>478275</v>
+        <v>478078</v>
       </c>
       <c r="R170" t="n">
-        <v>6827710</v>
+        <v>6827834</v>
       </c>
       <c r="S170" t="n">
         <v>10</v>
@@ -17937,7 +17937,7 @@
     </row>
     <row r="171">
       <c r="A171" t="n">
-        <v>120075077</v>
+        <v>120075142</v>
       </c>
       <c r="B171" t="n">
         <v>78526</v>
@@ -17977,10 +17977,10 @@
         </is>
       </c>
       <c r="Q171" t="n">
-        <v>478124</v>
+        <v>478313</v>
       </c>
       <c r="R171" t="n">
-        <v>6827560</v>
+        <v>6827798</v>
       </c>
       <c r="S171" t="n">
         <v>10</v>
@@ -18039,10 +18039,10 @@
     </row>
     <row r="172">
       <c r="A172" t="n">
-        <v>120074986</v>
+        <v>120075074</v>
       </c>
       <c r="B172" t="n">
-        <v>79608</v>
+        <v>78526</v>
       </c>
       <c r="C172" t="inlineStr">
         <is>
@@ -18055,21 +18055,21 @@
         </is>
       </c>
       <c r="E172" t="n">
-        <v>2081</v>
+        <v>6425</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G172" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H172" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I172" t="inlineStr"/>
@@ -18079,10 +18079,10 @@
         </is>
       </c>
       <c r="Q172" t="n">
-        <v>478096</v>
+        <v>478138</v>
       </c>
       <c r="R172" t="n">
-        <v>6827549</v>
+        <v>6827599</v>
       </c>
       <c r="S172" t="n">
         <v>10</v>
@@ -18141,10 +18141,10 @@
     </row>
     <row r="173">
       <c r="A173" t="n">
-        <v>120075174</v>
+        <v>120075236</v>
       </c>
       <c r="B173" t="n">
-        <v>78526</v>
+        <v>78171</v>
       </c>
       <c r="C173" t="inlineStr">
         <is>
@@ -18157,21 +18157,21 @@
         </is>
       </c>
       <c r="E173" t="n">
-        <v>6425</v>
+        <v>353</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G173" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H173" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I173" t="inlineStr"/>
@@ -18181,10 +18181,10 @@
         </is>
       </c>
       <c r="Q173" t="n">
-        <v>478057</v>
+        <v>478062</v>
       </c>
       <c r="R173" t="n">
-        <v>6827749</v>
+        <v>6827740</v>
       </c>
       <c r="S173" t="n">
         <v>10</v>
@@ -18243,10 +18243,10 @@
     </row>
     <row r="174">
       <c r="A174" t="n">
-        <v>120074888</v>
+        <v>120075203</v>
       </c>
       <c r="B174" t="n">
-        <v>79144</v>
+        <v>78171</v>
       </c>
       <c r="C174" t="inlineStr">
         <is>
@@ -18259,21 +18259,21 @@
         </is>
       </c>
       <c r="E174" t="n">
-        <v>6453</v>
+        <v>353</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G174" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H174" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I174" t="inlineStr"/>
@@ -18283,10 +18283,10 @@
         </is>
       </c>
       <c r="Q174" t="n">
-        <v>478139</v>
+        <v>478125</v>
       </c>
       <c r="R174" t="n">
-        <v>6827554</v>
+        <v>6827631</v>
       </c>
       <c r="S174" t="n">
         <v>10</v>
@@ -18345,10 +18345,10 @@
     </row>
     <row r="175">
       <c r="A175" t="n">
-        <v>120075137</v>
+        <v>120074907</v>
       </c>
       <c r="B175" t="n">
-        <v>78526</v>
+        <v>79144</v>
       </c>
       <c r="C175" t="inlineStr">
         <is>
@@ -18361,21 +18361,21 @@
         </is>
       </c>
       <c r="E175" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G175" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H175" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I175" t="inlineStr"/>
@@ -18385,10 +18385,10 @@
         </is>
       </c>
       <c r="Q175" t="n">
-        <v>478288</v>
+        <v>478263</v>
       </c>
       <c r="R175" t="n">
-        <v>6827763</v>
+        <v>6827838</v>
       </c>
       <c r="S175" t="n">
         <v>10</v>
@@ -18447,10 +18447,10 @@
     </row>
     <row r="176">
       <c r="A176" t="n">
-        <v>120075054</v>
+        <v>120074932</v>
       </c>
       <c r="B176" t="n">
-        <v>90580</v>
+        <v>79144</v>
       </c>
       <c r="C176" t="inlineStr">
         <is>
@@ -18463,21 +18463,21 @@
         </is>
       </c>
       <c r="E176" t="n">
-        <v>5432</v>
+        <v>6453</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G176" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H176" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I176" t="inlineStr"/>
@@ -18487,10 +18487,10 @@
         </is>
       </c>
       <c r="Q176" t="n">
-        <v>478126</v>
+        <v>478250</v>
       </c>
       <c r="R176" t="n">
-        <v>6827477</v>
+        <v>6827802</v>
       </c>
       <c r="S176" t="n">
         <v>10</v>
@@ -18549,10 +18549,10 @@
     </row>
     <row r="177">
       <c r="A177" t="n">
-        <v>120075044</v>
+        <v>120075232</v>
       </c>
       <c r="B177" t="n">
-        <v>78262</v>
+        <v>78171</v>
       </c>
       <c r="C177" t="inlineStr">
         <is>
@@ -18565,21 +18565,21 @@
         </is>
       </c>
       <c r="E177" t="n">
-        <v>6446</v>
+        <v>353</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G177" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H177" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I177" t="inlineStr"/>
@@ -18589,10 +18589,10 @@
         </is>
       </c>
       <c r="Q177" t="n">
-        <v>478060</v>
+        <v>478051</v>
       </c>
       <c r="R177" t="n">
-        <v>6827770</v>
+        <v>6827739</v>
       </c>
       <c r="S177" t="n">
         <v>10</v>
@@ -18651,10 +18651,10 @@
     </row>
     <row r="178">
       <c r="A178" t="n">
-        <v>120075134</v>
+        <v>120075234</v>
       </c>
       <c r="B178" t="n">
-        <v>78526</v>
+        <v>78171</v>
       </c>
       <c r="C178" t="inlineStr">
         <is>
@@ -18667,21 +18667,21 @@
         </is>
       </c>
       <c r="E178" t="n">
-        <v>6425</v>
+        <v>353</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G178" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H178" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I178" t="inlineStr"/>
@@ -18691,10 +18691,10 @@
         </is>
       </c>
       <c r="Q178" t="n">
-        <v>478266</v>
+        <v>478069</v>
       </c>
       <c r="R178" t="n">
-        <v>6827765</v>
+        <v>6827741</v>
       </c>
       <c r="S178" t="n">
         <v>10</v>
@@ -18753,10 +18753,10 @@
     </row>
     <row r="179">
       <c r="A179" t="n">
-        <v>120075144</v>
+        <v>120075242</v>
       </c>
       <c r="B179" t="n">
-        <v>78526</v>
+        <v>77910</v>
       </c>
       <c r="C179" t="inlineStr">
         <is>
@@ -18769,21 +18769,21 @@
         </is>
       </c>
       <c r="E179" t="n">
-        <v>6425</v>
+        <v>6437</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G179" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H179" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I179" t="inlineStr"/>
@@ -18793,10 +18793,10 @@
         </is>
       </c>
       <c r="Q179" t="n">
-        <v>478261</v>
+        <v>478136</v>
       </c>
       <c r="R179" t="n">
-        <v>6827822</v>
+        <v>6827556</v>
       </c>
       <c r="S179" t="n">
         <v>10</v>
@@ -18855,7 +18855,7 @@
     </row>
     <row r="180">
       <c r="A180" t="n">
-        <v>120075171</v>
+        <v>120075172</v>
       </c>
       <c r="B180" t="n">
         <v>78526</v>
@@ -18895,10 +18895,10 @@
         </is>
       </c>
       <c r="Q180" t="n">
-        <v>478073</v>
+        <v>478055</v>
       </c>
       <c r="R180" t="n">
-        <v>6827831</v>
+        <v>6827768</v>
       </c>
       <c r="S180" t="n">
         <v>10</v>
@@ -18957,10 +18957,10 @@
     </row>
     <row r="181">
       <c r="A181" t="n">
-        <v>120075047</v>
+        <v>120074931</v>
       </c>
       <c r="B181" t="n">
-        <v>78262</v>
+        <v>79144</v>
       </c>
       <c r="C181" t="inlineStr">
         <is>
@@ -18973,21 +18973,21 @@
         </is>
       </c>
       <c r="E181" t="n">
-        <v>6446</v>
+        <v>6453</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G181" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H181" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I181" t="inlineStr"/>
@@ -18997,10 +18997,10 @@
         </is>
       </c>
       <c r="Q181" t="n">
-        <v>478212</v>
+        <v>478261</v>
       </c>
       <c r="R181" t="n">
-        <v>6827573</v>
+        <v>6827822</v>
       </c>
       <c r="S181" t="n">
         <v>10</v>

--- a/artfynd/A 32983-2023 artfynd.xlsx
+++ b/artfynd/A 32983-2023 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>120074886</v>
+        <v>120074986</v>
       </c>
       <c r="B2" t="n">
-        <v>79144</v>
+        <v>79608</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6453</v>
+        <v>2081</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>478125</v>
+        <v>478096</v>
       </c>
       <c r="R2" t="n">
-        <v>6827604</v>
+        <v>6827549</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -777,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>120074943</v>
+        <v>120075217</v>
       </c>
       <c r="B3" t="n">
-        <v>79144</v>
+        <v>78171</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -793,21 +793,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6453</v>
+        <v>353</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -817,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>478073</v>
+        <v>478264</v>
       </c>
       <c r="R3" t="n">
-        <v>6827827</v>
+        <v>6827839</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -879,10 +879,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>120075007</v>
+        <v>120075208</v>
       </c>
       <c r="B4" t="n">
-        <v>78263</v>
+        <v>78171</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -895,21 +895,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>228912</v>
+        <v>353</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -919,10 +919,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>478285</v>
+        <v>478158</v>
       </c>
       <c r="R4" t="n">
-        <v>6827770</v>
+        <v>6827519</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -981,10 +981,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>120074998</v>
+        <v>120075202</v>
       </c>
       <c r="B5" t="n">
-        <v>78263</v>
+        <v>78171</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -997,21 +997,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>228912</v>
+        <v>353</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1021,10 +1021,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>478172</v>
+        <v>478218</v>
       </c>
       <c r="R5" t="n">
-        <v>6827640</v>
+        <v>6827721</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1083,10 +1083,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>120075217</v>
+        <v>120075075</v>
       </c>
       <c r="B6" t="n">
-        <v>78171</v>
+        <v>78526</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1099,21 +1099,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>353</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1123,10 +1123,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>478264</v>
+        <v>478139</v>
       </c>
       <c r="R6" t="n">
-        <v>6827839</v>
+        <v>6827554</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1185,10 +1185,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>120075208</v>
+        <v>120075157</v>
       </c>
       <c r="B7" t="n">
-        <v>78171</v>
+        <v>78526</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1201,21 +1201,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>353</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1225,10 +1225,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>478158</v>
+        <v>478103</v>
       </c>
       <c r="R7" t="n">
-        <v>6827519</v>
+        <v>6827718</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1287,10 +1287,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>120075202</v>
+        <v>120075073</v>
       </c>
       <c r="B8" t="n">
-        <v>78171</v>
+        <v>78526</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1303,21 +1303,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>353</v>
+        <v>6425</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1327,10 +1327,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>478218</v>
+        <v>478116</v>
       </c>
       <c r="R8" t="n">
-        <v>6827721</v>
+        <v>6827617</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1389,10 +1389,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>120074986</v>
+        <v>120075097</v>
       </c>
       <c r="B9" t="n">
-        <v>79608</v>
+        <v>78526</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1405,21 +1405,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>2081</v>
+        <v>6425</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1429,10 +1429,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>478096</v>
+        <v>478248</v>
       </c>
       <c r="R9" t="n">
-        <v>6827549</v>
+        <v>6827593</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1491,7 +1491,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>120075075</v>
+        <v>120075067</v>
       </c>
       <c r="B10" t="n">
         <v>78526</v>
@@ -1531,10 +1531,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>478139</v>
+        <v>478164</v>
       </c>
       <c r="R10" t="n">
-        <v>6827554</v>
+        <v>6827661</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1593,10 +1593,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>120075157</v>
+        <v>120074886</v>
       </c>
       <c r="B11" t="n">
-        <v>78526</v>
+        <v>79144</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1609,21 +1609,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1633,10 +1633,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>478103</v>
+        <v>478125</v>
       </c>
       <c r="R11" t="n">
-        <v>6827718</v>
+        <v>6827604</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1695,10 +1695,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>120075073</v>
+        <v>120074943</v>
       </c>
       <c r="B12" t="n">
-        <v>78526</v>
+        <v>79144</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1711,21 +1711,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1735,10 +1735,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>478116</v>
+        <v>478073</v>
       </c>
       <c r="R12" t="n">
-        <v>6827617</v>
+        <v>6827827</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1797,10 +1797,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>120075097</v>
+        <v>120075007</v>
       </c>
       <c r="B13" t="n">
-        <v>78526</v>
+        <v>78263</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1813,21 +1813,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1837,10 +1837,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>478248</v>
+        <v>478285</v>
       </c>
       <c r="R13" t="n">
-        <v>6827593</v>
+        <v>6827770</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1899,10 +1899,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>120075067</v>
+        <v>120074998</v>
       </c>
       <c r="B14" t="n">
-        <v>78526</v>
+        <v>78263</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1915,21 +1915,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1939,10 +1939,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>478164</v>
+        <v>478172</v>
       </c>
       <c r="R14" t="n">
-        <v>6827661</v>
+        <v>6827640</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -7416,10 +7416,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>120075216</v>
+        <v>120074930</v>
       </c>
       <c r="B68" t="n">
-        <v>78171</v>
+        <v>79144</v>
       </c>
       <c r="C68" t="inlineStr">
         <is>
@@ -7432,21 +7432,21 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>353</v>
+        <v>6453</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
@@ -7456,10 +7456,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>478294</v>
+        <v>478299</v>
       </c>
       <c r="R68" t="n">
-        <v>6827790</v>
+        <v>6827805</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7518,10 +7518,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>120075084</v>
+        <v>120075035</v>
       </c>
       <c r="B69" t="n">
-        <v>78526</v>
+        <v>78262</v>
       </c>
       <c r="C69" t="inlineStr">
         <is>
@@ -7534,21 +7534,21 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
@@ -7558,10 +7558,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>478098</v>
+        <v>478273</v>
       </c>
       <c r="R69" t="n">
-        <v>6827520</v>
+        <v>6827711</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -7620,10 +7620,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>120075068</v>
+        <v>120074892</v>
       </c>
       <c r="B70" t="n">
-        <v>78526</v>
+        <v>79144</v>
       </c>
       <c r="C70" t="inlineStr">
         <is>
@@ -7636,21 +7636,21 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
@@ -7660,10 +7660,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>478174</v>
+        <v>478243</v>
       </c>
       <c r="R70" t="n">
-        <v>6827656</v>
+        <v>6827585</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -7722,7 +7722,7 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>120074930</v>
+        <v>120074944</v>
       </c>
       <c r="B71" t="n">
         <v>79144</v>
@@ -7762,10 +7762,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>478299</v>
+        <v>478056</v>
       </c>
       <c r="R71" t="n">
-        <v>6827805</v>
+        <v>6827785</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -7824,10 +7824,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>120075035</v>
+        <v>120075019</v>
       </c>
       <c r="B72" t="n">
-        <v>78262</v>
+        <v>79607</v>
       </c>
       <c r="C72" t="inlineStr">
         <is>
@@ -7840,21 +7840,21 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>6446</v>
+        <v>6458</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
@@ -7864,10 +7864,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>478273</v>
+        <v>478227</v>
       </c>
       <c r="R72" t="n">
-        <v>6827711</v>
+        <v>6827655</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -7926,10 +7926,10 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>120074892</v>
+        <v>120075037</v>
       </c>
       <c r="B73" t="n">
-        <v>79144</v>
+        <v>78262</v>
       </c>
       <c r="C73" t="inlineStr">
         <is>
@@ -7942,21 +7942,21 @@
         </is>
       </c>
       <c r="E73" t="n">
-        <v>6453</v>
+        <v>6446</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
@@ -7966,10 +7966,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>478243</v>
+        <v>478265</v>
       </c>
       <c r="R73" t="n">
-        <v>6827585</v>
+        <v>6827716</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -8028,10 +8028,10 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>120074944</v>
+        <v>120075216</v>
       </c>
       <c r="B74" t="n">
-        <v>79144</v>
+        <v>78171</v>
       </c>
       <c r="C74" t="inlineStr">
         <is>
@@ -8044,21 +8044,21 @@
         </is>
       </c>
       <c r="E74" t="n">
-        <v>6453</v>
+        <v>353</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
@@ -8068,10 +8068,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>478056</v>
+        <v>478294</v>
       </c>
       <c r="R74" t="n">
-        <v>6827785</v>
+        <v>6827790</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -8130,10 +8130,10 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>120075019</v>
+        <v>120075084</v>
       </c>
       <c r="B75" t="n">
-        <v>79607</v>
+        <v>78526</v>
       </c>
       <c r="C75" t="inlineStr">
         <is>
@@ -8146,21 +8146,21 @@
         </is>
       </c>
       <c r="E75" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
@@ -8170,10 +8170,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>478227</v>
+        <v>478098</v>
       </c>
       <c r="R75" t="n">
-        <v>6827655</v>
+        <v>6827520</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -8232,10 +8232,10 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>120075000</v>
+        <v>120075068</v>
       </c>
       <c r="B76" t="n">
-        <v>78263</v>
+        <v>78526</v>
       </c>
       <c r="C76" t="inlineStr">
         <is>
@@ -8248,21 +8248,21 @@
         </is>
       </c>
       <c r="E76" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
@@ -8272,10 +8272,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>478121</v>
+        <v>478174</v>
       </c>
       <c r="R76" t="n">
-        <v>6827607</v>
+        <v>6827656</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -8334,10 +8334,10 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>120075037</v>
+        <v>120075000</v>
       </c>
       <c r="B77" t="n">
-        <v>78262</v>
+        <v>78263</v>
       </c>
       <c r="C77" t="inlineStr">
         <is>
@@ -8350,21 +8350,21 @@
         </is>
       </c>
       <c r="E77" t="n">
-        <v>6446</v>
+        <v>228912</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
@@ -8374,10 +8374,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>478265</v>
+        <v>478121</v>
       </c>
       <c r="R77" t="n">
-        <v>6827716</v>
+        <v>6827607</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -11088,10 +11088,10 @@
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>120075192</v>
+        <v>120075009</v>
       </c>
       <c r="B104" t="n">
-        <v>78526</v>
+        <v>78263</v>
       </c>
       <c r="C104" t="inlineStr">
         <is>
@@ -11104,21 +11104,21 @@
         </is>
       </c>
       <c r="E104" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I104" t="inlineStr"/>
@@ -11128,10 +11128,10 @@
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>478282</v>
+        <v>478151</v>
       </c>
       <c r="R104" t="n">
-        <v>6827683</v>
+        <v>6827745</v>
       </c>
       <c r="S104" t="n">
         <v>10</v>
@@ -11190,10 +11190,10 @@
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>120075143</v>
+        <v>120075224</v>
       </c>
       <c r="B105" t="n">
-        <v>78526</v>
+        <v>78171</v>
       </c>
       <c r="C105" t="inlineStr">
         <is>
@@ -11206,21 +11206,21 @@
         </is>
       </c>
       <c r="E105" t="n">
-        <v>6425</v>
+        <v>353</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I105" t="inlineStr"/>
@@ -11230,10 +11230,10 @@
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>478301</v>
+        <v>478081</v>
       </c>
       <c r="R105" t="n">
-        <v>6827814</v>
+        <v>6827789</v>
       </c>
       <c r="S105" t="n">
         <v>10</v>
@@ -11292,7 +11292,7 @@
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>120075064</v>
+        <v>120075192</v>
       </c>
       <c r="B106" t="n">
         <v>78526</v>
@@ -11332,10 +11332,10 @@
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>478192</v>
+        <v>478282</v>
       </c>
       <c r="R106" t="n">
-        <v>6827690</v>
+        <v>6827683</v>
       </c>
       <c r="S106" t="n">
         <v>10</v>
@@ -11394,7 +11394,7 @@
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>120075175</v>
+        <v>120075143</v>
       </c>
       <c r="B107" t="n">
         <v>78526</v>
@@ -11434,10 +11434,10 @@
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>478059</v>
+        <v>478301</v>
       </c>
       <c r="R107" t="n">
-        <v>6827739</v>
+        <v>6827814</v>
       </c>
       <c r="S107" t="n">
         <v>10</v>
@@ -11496,10 +11496,10 @@
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>120075224</v>
+        <v>120075064</v>
       </c>
       <c r="B108" t="n">
-        <v>78171</v>
+        <v>78526</v>
       </c>
       <c r="C108" t="inlineStr">
         <is>
@@ -11512,21 +11512,21 @@
         </is>
       </c>
       <c r="E108" t="n">
-        <v>353</v>
+        <v>6425</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I108" t="inlineStr"/>
@@ -11536,10 +11536,10 @@
         </is>
       </c>
       <c r="Q108" t="n">
-        <v>478081</v>
+        <v>478192</v>
       </c>
       <c r="R108" t="n">
-        <v>6827789</v>
+        <v>6827690</v>
       </c>
       <c r="S108" t="n">
         <v>10</v>
@@ -11598,10 +11598,10 @@
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>120074956</v>
+        <v>120075175</v>
       </c>
       <c r="B109" t="n">
-        <v>57310</v>
+        <v>78526</v>
       </c>
       <c r="C109" t="inlineStr">
         <is>
@@ -11614,39 +11614,34 @@
         </is>
       </c>
       <c r="E109" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I109" t="inlineStr"/>
-      <c r="M109" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P109" t="inlineStr">
         <is>
           <t>Hevoslamm, Dlr</t>
         </is>
       </c>
       <c r="Q109" t="n">
-        <v>478278</v>
+        <v>478059</v>
       </c>
       <c r="R109" t="n">
-        <v>6827832</v>
+        <v>6827739</v>
       </c>
       <c r="S109" t="n">
         <v>10</v>
@@ -11679,11 +11674,6 @@
       <c r="AA109" t="inlineStr">
         <is>
           <t>2024-09-27</t>
-        </is>
-      </c>
-      <c r="AC109" t="inlineStr">
-        <is>
-          <t>Färska ringhack (tall)</t>
         </is>
       </c>
       <c r="AD109" t="b">
@@ -11710,10 +11700,10 @@
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>120075009</v>
+        <v>120074956</v>
       </c>
       <c r="B110" t="n">
-        <v>78263</v>
+        <v>57310</v>
       </c>
       <c r="C110" t="inlineStr">
         <is>
@@ -11726,34 +11716,39 @@
         </is>
       </c>
       <c r="E110" t="n">
-        <v>228912</v>
+        <v>100109</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I110" t="inlineStr"/>
+      <c r="M110" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P110" t="inlineStr">
         <is>
           <t>Hevoslamm, Dlr</t>
         </is>
       </c>
       <c r="Q110" t="n">
-        <v>478151</v>
+        <v>478278</v>
       </c>
       <c r="R110" t="n">
-        <v>6827745</v>
+        <v>6827832</v>
       </c>
       <c r="S110" t="n">
         <v>10</v>
@@ -11786,6 +11781,11 @@
       <c r="AA110" t="inlineStr">
         <is>
           <t>2024-09-27</t>
+        </is>
+      </c>
+      <c r="AC110" t="inlineStr">
+        <is>
+          <t>Färska ringhack (tall)</t>
         </is>
       </c>
       <c r="AD110" t="b">
@@ -11812,10 +11812,10 @@
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>120074996</v>
+        <v>120075219</v>
       </c>
       <c r="B111" t="n">
-        <v>78263</v>
+        <v>78171</v>
       </c>
       <c r="C111" t="inlineStr">
         <is>
@@ -11828,21 +11828,21 @@
         </is>
       </c>
       <c r="E111" t="n">
-        <v>228912</v>
+        <v>353</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I111" t="inlineStr"/>
@@ -11852,10 +11852,10 @@
         </is>
       </c>
       <c r="Q111" t="n">
-        <v>478165</v>
+        <v>478169</v>
       </c>
       <c r="R111" t="n">
-        <v>6827712</v>
+        <v>6827760</v>
       </c>
       <c r="S111" t="n">
         <v>10</v>
@@ -12322,10 +12322,10 @@
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>120075219</v>
+        <v>120074996</v>
       </c>
       <c r="B116" t="n">
-        <v>78171</v>
+        <v>78263</v>
       </c>
       <c r="C116" t="inlineStr">
         <is>
@@ -12338,21 +12338,21 @@
         </is>
       </c>
       <c r="E116" t="n">
-        <v>353</v>
+        <v>228912</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I116" t="inlineStr"/>
@@ -12362,10 +12362,10 @@
         </is>
       </c>
       <c r="Q116" t="n">
-        <v>478169</v>
+        <v>478165</v>
       </c>
       <c r="R116" t="n">
-        <v>6827760</v>
+        <v>6827712</v>
       </c>
       <c r="S116" t="n">
         <v>10</v>
@@ -12424,10 +12424,10 @@
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>120075132</v>
+        <v>120074912</v>
       </c>
       <c r="B117" t="n">
-        <v>78526</v>
+        <v>78560</v>
       </c>
       <c r="C117" t="inlineStr">
         <is>
@@ -12440,21 +12440,21 @@
         </is>
       </c>
       <c r="E117" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I117" t="inlineStr"/>
@@ -12464,10 +12464,10 @@
         </is>
       </c>
       <c r="Q117" t="n">
-        <v>478240</v>
+        <v>478149</v>
       </c>
       <c r="R117" t="n">
-        <v>6827754</v>
+        <v>6827714</v>
       </c>
       <c r="S117" t="n">
         <v>10</v>
@@ -12526,7 +12526,7 @@
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>120075094</v>
+        <v>120075132</v>
       </c>
       <c r="B118" t="n">
         <v>78526</v>
@@ -12566,10 +12566,10 @@
         </is>
       </c>
       <c r="Q118" t="n">
-        <v>478205</v>
+        <v>478240</v>
       </c>
       <c r="R118" t="n">
-        <v>6827556</v>
+        <v>6827754</v>
       </c>
       <c r="S118" t="n">
         <v>10</v>
@@ -12628,7 +12628,7 @@
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>120075082</v>
+        <v>120075094</v>
       </c>
       <c r="B119" t="n">
         <v>78526</v>
@@ -12668,10 +12668,10 @@
         </is>
       </c>
       <c r="Q119" t="n">
-        <v>478097</v>
+        <v>478205</v>
       </c>
       <c r="R119" t="n">
-        <v>6827544</v>
+        <v>6827556</v>
       </c>
       <c r="S119" t="n">
         <v>10</v>
@@ -12730,10 +12730,10 @@
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>120074912</v>
+        <v>120075082</v>
       </c>
       <c r="B120" t="n">
-        <v>78560</v>
+        <v>78526</v>
       </c>
       <c r="C120" t="inlineStr">
         <is>
@@ -12746,21 +12746,21 @@
         </is>
       </c>
       <c r="E120" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I120" t="inlineStr"/>
@@ -12770,10 +12770,10 @@
         </is>
       </c>
       <c r="Q120" t="n">
-        <v>478149</v>
+        <v>478097</v>
       </c>
       <c r="R120" t="n">
-        <v>6827714</v>
+        <v>6827544</v>
       </c>
       <c r="S120" t="n">
         <v>10</v>
@@ -13852,10 +13852,10 @@
     </row>
     <row r="131">
       <c r="A131" t="n">
-        <v>120075054</v>
+        <v>120075226</v>
       </c>
       <c r="B131" t="n">
-        <v>90580</v>
+        <v>78171</v>
       </c>
       <c r="C131" t="inlineStr">
         <is>
@@ -13868,21 +13868,21 @@
         </is>
       </c>
       <c r="E131" t="n">
-        <v>5432</v>
+        <v>353</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H131" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I131" t="inlineStr"/>
@@ -13892,10 +13892,10 @@
         </is>
       </c>
       <c r="Q131" t="n">
-        <v>478126</v>
+        <v>478098</v>
       </c>
       <c r="R131" t="n">
-        <v>6827477</v>
+        <v>6827815</v>
       </c>
       <c r="S131" t="n">
         <v>10</v>
@@ -13954,10 +13954,10 @@
     </row>
     <row r="132">
       <c r="A132" t="n">
-        <v>120075010</v>
+        <v>120074929</v>
       </c>
       <c r="B132" t="n">
-        <v>78263</v>
+        <v>78560</v>
       </c>
       <c r="C132" t="inlineStr">
         <is>
@@ -13970,21 +13970,21 @@
         </is>
       </c>
       <c r="E132" t="n">
-        <v>228912</v>
+        <v>185</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H132" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I132" t="inlineStr"/>
@@ -13994,10 +13994,10 @@
         </is>
       </c>
       <c r="Q132" t="n">
-        <v>478074</v>
+        <v>478045</v>
       </c>
       <c r="R132" t="n">
-        <v>6827772</v>
+        <v>6827724</v>
       </c>
       <c r="S132" t="n">
         <v>10</v>
@@ -14056,10 +14056,10 @@
     </row>
     <row r="133">
       <c r="A133" t="n">
-        <v>120075226</v>
+        <v>120075054</v>
       </c>
       <c r="B133" t="n">
-        <v>78171</v>
+        <v>90580</v>
       </c>
       <c r="C133" t="inlineStr">
         <is>
@@ -14072,21 +14072,21 @@
         </is>
       </c>
       <c r="E133" t="n">
-        <v>353</v>
+        <v>5432</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H133" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I133" t="inlineStr"/>
@@ -14096,10 +14096,10 @@
         </is>
       </c>
       <c r="Q133" t="n">
-        <v>478098</v>
+        <v>478126</v>
       </c>
       <c r="R133" t="n">
-        <v>6827815</v>
+        <v>6827477</v>
       </c>
       <c r="S133" t="n">
         <v>10</v>
@@ -14158,10 +14158,10 @@
     </row>
     <row r="134">
       <c r="A134" t="n">
-        <v>120074929</v>
+        <v>120075010</v>
       </c>
       <c r="B134" t="n">
-        <v>78560</v>
+        <v>78263</v>
       </c>
       <c r="C134" t="inlineStr">
         <is>
@@ -14174,21 +14174,21 @@
         </is>
       </c>
       <c r="E134" t="n">
-        <v>185</v>
+        <v>228912</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H134" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I134" t="inlineStr"/>
@@ -14198,10 +14198,10 @@
         </is>
       </c>
       <c r="Q134" t="n">
-        <v>478045</v>
+        <v>478074</v>
       </c>
       <c r="R134" t="n">
-        <v>6827724</v>
+        <v>6827772</v>
       </c>
       <c r="S134" t="n">
         <v>10</v>
@@ -15484,10 +15484,10 @@
     </row>
     <row r="147">
       <c r="A147" t="n">
-        <v>120075061</v>
+        <v>120075198</v>
       </c>
       <c r="B147" t="n">
-        <v>78526</v>
+        <v>91840</v>
       </c>
       <c r="C147" t="inlineStr">
         <is>
@@ -15496,25 +15496,25 @@
       </c>
       <c r="D147" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E147" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G147" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H147" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I147" t="inlineStr"/>
@@ -15524,10 +15524,10 @@
         </is>
       </c>
       <c r="Q147" t="n">
-        <v>478160</v>
+        <v>478163</v>
       </c>
       <c r="R147" t="n">
-        <v>6827710</v>
+        <v>6827530</v>
       </c>
       <c r="S147" t="n">
         <v>10</v>
@@ -15586,7 +15586,7 @@
     </row>
     <row r="148">
       <c r="A148" t="n">
-        <v>120075060</v>
+        <v>120075061</v>
       </c>
       <c r="B148" t="n">
         <v>78526</v>
@@ -15626,10 +15626,10 @@
         </is>
       </c>
       <c r="Q148" t="n">
-        <v>478087</v>
+        <v>478160</v>
       </c>
       <c r="R148" t="n">
-        <v>6827718</v>
+        <v>6827710</v>
       </c>
       <c r="S148" t="n">
         <v>10</v>
@@ -15688,7 +15688,7 @@
     </row>
     <row r="149">
       <c r="A149" t="n">
-        <v>120075140</v>
+        <v>120075060</v>
       </c>
       <c r="B149" t="n">
         <v>78526</v>
@@ -15728,10 +15728,10 @@
         </is>
       </c>
       <c r="Q149" t="n">
-        <v>478310</v>
+        <v>478087</v>
       </c>
       <c r="R149" t="n">
-        <v>6827797</v>
+        <v>6827718</v>
       </c>
       <c r="S149" t="n">
         <v>10</v>
@@ -15790,10 +15790,10 @@
     </row>
     <row r="150">
       <c r="A150" t="n">
-        <v>120074888</v>
+        <v>120075140</v>
       </c>
       <c r="B150" t="n">
-        <v>79144</v>
+        <v>78526</v>
       </c>
       <c r="C150" t="inlineStr">
         <is>
@@ -15806,21 +15806,21 @@
         </is>
       </c>
       <c r="E150" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G150" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H150" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I150" t="inlineStr"/>
@@ -15830,10 +15830,10 @@
         </is>
       </c>
       <c r="Q150" t="n">
-        <v>478139</v>
+        <v>478310</v>
       </c>
       <c r="R150" t="n">
-        <v>6827554</v>
+        <v>6827797</v>
       </c>
       <c r="S150" t="n">
         <v>10</v>
@@ -15892,10 +15892,10 @@
     </row>
     <row r="151">
       <c r="A151" t="n">
-        <v>120074933</v>
+        <v>120075048</v>
       </c>
       <c r="B151" t="n">
-        <v>79144</v>
+        <v>56514</v>
       </c>
       <c r="C151" t="inlineStr">
         <is>
@@ -15908,34 +15908,39 @@
         </is>
       </c>
       <c r="E151" t="n">
-        <v>6453</v>
+        <v>102612</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G151" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H151" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I151" t="inlineStr"/>
+      <c r="M151" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="P151" t="inlineStr">
         <is>
           <t>Hevoslamm, Dlr</t>
         </is>
       </c>
       <c r="Q151" t="n">
-        <v>478189</v>
+        <v>478070</v>
       </c>
       <c r="R151" t="n">
-        <v>6827761</v>
+        <v>6827723</v>
       </c>
       <c r="S151" t="n">
         <v>10</v>
@@ -15994,10 +15999,10 @@
     </row>
     <row r="152">
       <c r="A152" t="n">
-        <v>120075048</v>
+        <v>120074888</v>
       </c>
       <c r="B152" t="n">
-        <v>56514</v>
+        <v>79144</v>
       </c>
       <c r="C152" t="inlineStr">
         <is>
@@ -16010,39 +16015,34 @@
         </is>
       </c>
       <c r="E152" t="n">
-        <v>102612</v>
+        <v>6453</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G152" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H152" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I152" t="inlineStr"/>
-      <c r="M152" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
       <c r="P152" t="inlineStr">
         <is>
           <t>Hevoslamm, Dlr</t>
         </is>
       </c>
       <c r="Q152" t="n">
-        <v>478070</v>
+        <v>478139</v>
       </c>
       <c r="R152" t="n">
-        <v>6827723</v>
+        <v>6827554</v>
       </c>
       <c r="S152" t="n">
         <v>10</v>
@@ -16101,10 +16101,10 @@
     </row>
     <row r="153">
       <c r="A153" t="n">
-        <v>120075198</v>
+        <v>120074933</v>
       </c>
       <c r="B153" t="n">
-        <v>91840</v>
+        <v>79144</v>
       </c>
       <c r="C153" t="inlineStr">
         <is>
@@ -16113,25 +16113,25 @@
       </c>
       <c r="D153" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E153" t="n">
-        <v>4364</v>
+        <v>6453</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G153" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H153" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I153" t="inlineStr"/>
@@ -16141,10 +16141,10 @@
         </is>
       </c>
       <c r="Q153" t="n">
-        <v>478163</v>
+        <v>478189</v>
       </c>
       <c r="R153" t="n">
-        <v>6827530</v>
+        <v>6827761</v>
       </c>
       <c r="S153" t="n">
         <v>10</v>
@@ -16407,10 +16407,10 @@
     </row>
     <row r="156">
       <c r="A156" t="n">
-        <v>120074939</v>
+        <v>120075133</v>
       </c>
       <c r="B156" t="n">
-        <v>79144</v>
+        <v>78526</v>
       </c>
       <c r="C156" t="inlineStr">
         <is>
@@ -16423,21 +16423,21 @@
         </is>
       </c>
       <c r="E156" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G156" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H156" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I156" t="inlineStr"/>
@@ -16447,10 +16447,10 @@
         </is>
       </c>
       <c r="Q156" t="n">
-        <v>478091</v>
+        <v>478258</v>
       </c>
       <c r="R156" t="n">
-        <v>6827838</v>
+        <v>6827753</v>
       </c>
       <c r="S156" t="n">
         <v>10</v>
@@ -16509,10 +16509,10 @@
     </row>
     <row r="157">
       <c r="A157" t="n">
-        <v>120075015</v>
+        <v>120075173</v>
       </c>
       <c r="B157" t="n">
-        <v>79607</v>
+        <v>78526</v>
       </c>
       <c r="C157" t="inlineStr">
         <is>
@@ -16525,21 +16525,21 @@
         </is>
       </c>
       <c r="E157" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G157" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H157" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I157" t="inlineStr"/>
@@ -16549,10 +16549,10 @@
         </is>
       </c>
       <c r="Q157" t="n">
-        <v>478114</v>
+        <v>478052</v>
       </c>
       <c r="R157" t="n">
-        <v>6827633</v>
+        <v>6827754</v>
       </c>
       <c r="S157" t="n">
         <v>10</v>
@@ -16611,10 +16611,10 @@
     </row>
     <row r="158">
       <c r="A158" t="n">
-        <v>120074961</v>
+        <v>120075069</v>
       </c>
       <c r="B158" t="n">
-        <v>90582</v>
+        <v>78526</v>
       </c>
       <c r="C158" t="inlineStr">
         <is>
@@ -16627,21 +16627,21 @@
         </is>
       </c>
       <c r="E158" t="n">
-        <v>5442</v>
+        <v>6425</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G158" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H158" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I158" t="inlineStr"/>
@@ -16651,10 +16651,10 @@
         </is>
       </c>
       <c r="Q158" t="n">
-        <v>478230</v>
+        <v>478157</v>
       </c>
       <c r="R158" t="n">
-        <v>6827780</v>
+        <v>6827611</v>
       </c>
       <c r="S158" t="n">
         <v>10</v>
@@ -16713,10 +16713,10 @@
     </row>
     <row r="159">
       <c r="A159" t="n">
-        <v>120074999</v>
+        <v>120075087</v>
       </c>
       <c r="B159" t="n">
-        <v>78263</v>
+        <v>78526</v>
       </c>
       <c r="C159" t="inlineStr">
         <is>
@@ -16729,21 +16729,21 @@
         </is>
       </c>
       <c r="E159" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G159" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H159" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I159" t="inlineStr"/>
@@ -16753,10 +16753,10 @@
         </is>
       </c>
       <c r="Q159" t="n">
-        <v>478161</v>
+        <v>478145</v>
       </c>
       <c r="R159" t="n">
-        <v>6827592</v>
+        <v>6827485</v>
       </c>
       <c r="S159" t="n">
         <v>10</v>
@@ -16815,10 +16815,10 @@
     </row>
     <row r="160">
       <c r="A160" t="n">
-        <v>120075004</v>
+        <v>120075164</v>
       </c>
       <c r="B160" t="n">
-        <v>78263</v>
+        <v>78526</v>
       </c>
       <c r="C160" t="inlineStr">
         <is>
@@ -16831,21 +16831,21 @@
         </is>
       </c>
       <c r="E160" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G160" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H160" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I160" t="inlineStr"/>
@@ -16855,10 +16855,10 @@
         </is>
       </c>
       <c r="Q160" t="n">
-        <v>478212</v>
+        <v>478092</v>
       </c>
       <c r="R160" t="n">
-        <v>6827573</v>
+        <v>6827810</v>
       </c>
       <c r="S160" t="n">
         <v>10</v>
@@ -16917,7 +16917,7 @@
     </row>
     <row r="161">
       <c r="A161" t="n">
-        <v>120075133</v>
+        <v>120075131</v>
       </c>
       <c r="B161" t="n">
         <v>78526</v>
@@ -16960,7 +16960,7 @@
         <v>478258</v>
       </c>
       <c r="R161" t="n">
-        <v>6827753</v>
+        <v>6827731</v>
       </c>
       <c r="S161" t="n">
         <v>10</v>
@@ -17019,7 +17019,7 @@
     </row>
     <row r="162">
       <c r="A162" t="n">
-        <v>120075173</v>
+        <v>120075070</v>
       </c>
       <c r="B162" t="n">
         <v>78526</v>
@@ -17059,10 +17059,10 @@
         </is>
       </c>
       <c r="Q162" t="n">
-        <v>478052</v>
+        <v>478135</v>
       </c>
       <c r="R162" t="n">
-        <v>6827754</v>
+        <v>6827625</v>
       </c>
       <c r="S162" t="n">
         <v>10</v>
@@ -17121,7 +17121,7 @@
     </row>
     <row r="163">
       <c r="A163" t="n">
-        <v>120075069</v>
+        <v>120075168</v>
       </c>
       <c r="B163" t="n">
         <v>78526</v>
@@ -17161,10 +17161,10 @@
         </is>
       </c>
       <c r="Q163" t="n">
-        <v>478157</v>
+        <v>478086</v>
       </c>
       <c r="R163" t="n">
-        <v>6827611</v>
+        <v>6827868</v>
       </c>
       <c r="S163" t="n">
         <v>10</v>
@@ -17223,7 +17223,7 @@
     </row>
     <row r="164">
       <c r="A164" t="n">
-        <v>120075087</v>
+        <v>120075129</v>
       </c>
       <c r="B164" t="n">
         <v>78526</v>
@@ -17263,10 +17263,10 @@
         </is>
       </c>
       <c r="Q164" t="n">
-        <v>478145</v>
+        <v>478265</v>
       </c>
       <c r="R164" t="n">
-        <v>6827485</v>
+        <v>6827707</v>
       </c>
       <c r="S164" t="n">
         <v>10</v>
@@ -17325,10 +17325,10 @@
     </row>
     <row r="165">
       <c r="A165" t="n">
-        <v>120075164</v>
+        <v>120074939</v>
       </c>
       <c r="B165" t="n">
-        <v>78526</v>
+        <v>79144</v>
       </c>
       <c r="C165" t="inlineStr">
         <is>
@@ -17341,21 +17341,21 @@
         </is>
       </c>
       <c r="E165" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G165" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H165" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I165" t="inlineStr"/>
@@ -17365,10 +17365,10 @@
         </is>
       </c>
       <c r="Q165" t="n">
-        <v>478092</v>
+        <v>478091</v>
       </c>
       <c r="R165" t="n">
-        <v>6827810</v>
+        <v>6827838</v>
       </c>
       <c r="S165" t="n">
         <v>10</v>
@@ -17427,10 +17427,10 @@
     </row>
     <row r="166">
       <c r="A166" t="n">
-        <v>120075131</v>
+        <v>120075015</v>
       </c>
       <c r="B166" t="n">
-        <v>78526</v>
+        <v>79607</v>
       </c>
       <c r="C166" t="inlineStr">
         <is>
@@ -17443,21 +17443,21 @@
         </is>
       </c>
       <c r="E166" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G166" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H166" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I166" t="inlineStr"/>
@@ -17467,10 +17467,10 @@
         </is>
       </c>
       <c r="Q166" t="n">
-        <v>478258</v>
+        <v>478114</v>
       </c>
       <c r="R166" t="n">
-        <v>6827731</v>
+        <v>6827633</v>
       </c>
       <c r="S166" t="n">
         <v>10</v>
@@ -17529,10 +17529,10 @@
     </row>
     <row r="167">
       <c r="A167" t="n">
-        <v>120075070</v>
+        <v>120074961</v>
       </c>
       <c r="B167" t="n">
-        <v>78526</v>
+        <v>90582</v>
       </c>
       <c r="C167" t="inlineStr">
         <is>
@@ -17545,21 +17545,21 @@
         </is>
       </c>
       <c r="E167" t="n">
-        <v>6425</v>
+        <v>5442</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G167" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H167" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I167" t="inlineStr"/>
@@ -17569,10 +17569,10 @@
         </is>
       </c>
       <c r="Q167" t="n">
-        <v>478135</v>
+        <v>478230</v>
       </c>
       <c r="R167" t="n">
-        <v>6827625</v>
+        <v>6827780</v>
       </c>
       <c r="S167" t="n">
         <v>10</v>
@@ -17631,10 +17631,10 @@
     </row>
     <row r="168">
       <c r="A168" t="n">
-        <v>120075168</v>
+        <v>120074999</v>
       </c>
       <c r="B168" t="n">
-        <v>78526</v>
+        <v>78263</v>
       </c>
       <c r="C168" t="inlineStr">
         <is>
@@ -17647,21 +17647,21 @@
         </is>
       </c>
       <c r="E168" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G168" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H168" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I168" t="inlineStr"/>
@@ -17671,10 +17671,10 @@
         </is>
       </c>
       <c r="Q168" t="n">
-        <v>478086</v>
+        <v>478161</v>
       </c>
       <c r="R168" t="n">
-        <v>6827868</v>
+        <v>6827592</v>
       </c>
       <c r="S168" t="n">
         <v>10</v>
@@ -17733,10 +17733,10 @@
     </row>
     <row r="169">
       <c r="A169" t="n">
-        <v>120075129</v>
+        <v>120075004</v>
       </c>
       <c r="B169" t="n">
-        <v>78526</v>
+        <v>78263</v>
       </c>
       <c r="C169" t="inlineStr">
         <is>
@@ -17749,21 +17749,21 @@
         </is>
       </c>
       <c r="E169" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G169" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H169" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I169" t="inlineStr"/>
@@ -17773,10 +17773,10 @@
         </is>
       </c>
       <c r="Q169" t="n">
-        <v>478265</v>
+        <v>478212</v>
       </c>
       <c r="R169" t="n">
-        <v>6827707</v>
+        <v>6827573</v>
       </c>
       <c r="S169" t="n">
         <v>10</v>

--- a/artfynd/A 32983-2023 artfynd.xlsx
+++ b/artfynd/A 32983-2023 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>120074986</v>
+        <v>120075208</v>
       </c>
       <c r="B2" t="n">
-        <v>79608</v>
+        <v>78171</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>2081</v>
+        <v>353</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>478096</v>
+        <v>478158</v>
       </c>
       <c r="R2" t="n">
-        <v>6827549</v>
+        <v>6827519</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -777,7 +777,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>120075217</v>
+        <v>120075203</v>
       </c>
       <c r="B3" t="n">
         <v>78171</v>
@@ -817,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>478264</v>
+        <v>478125</v>
       </c>
       <c r="R3" t="n">
-        <v>6827839</v>
+        <v>6827631</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -879,10 +879,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>120075208</v>
+        <v>120075011</v>
       </c>
       <c r="B4" t="n">
-        <v>78171</v>
+        <v>78263</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -895,21 +895,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>353</v>
+        <v>228912</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -919,10 +919,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>478158</v>
+        <v>478103</v>
       </c>
       <c r="R4" t="n">
-        <v>6827519</v>
+        <v>6827803</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -981,10 +981,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>120075202</v>
+        <v>120075013</v>
       </c>
       <c r="B5" t="n">
-        <v>78171</v>
+        <v>78263</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -997,21 +997,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>353</v>
+        <v>228912</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1021,10 +1021,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>478218</v>
+        <v>478239</v>
       </c>
       <c r="R5" t="n">
-        <v>6827721</v>
+        <v>6827752</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1083,7 +1083,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>120075075</v>
+        <v>120075192</v>
       </c>
       <c r="B6" t="n">
         <v>78526</v>
@@ -1123,10 +1123,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>478139</v>
+        <v>478282</v>
       </c>
       <c r="R6" t="n">
-        <v>6827554</v>
+        <v>6827683</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1185,7 +1185,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>120075157</v>
+        <v>120075159</v>
       </c>
       <c r="B7" t="n">
         <v>78526</v>
@@ -1225,10 +1225,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>478103</v>
+        <v>478100</v>
       </c>
       <c r="R7" t="n">
-        <v>6827718</v>
+        <v>6827729</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1287,7 +1287,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>120075073</v>
+        <v>120075069</v>
       </c>
       <c r="B8" t="n">
         <v>78526</v>
@@ -1327,10 +1327,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>478116</v>
+        <v>478157</v>
       </c>
       <c r="R8" t="n">
-        <v>6827617</v>
+        <v>6827611</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1389,10 +1389,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>120075097</v>
+        <v>120074892</v>
       </c>
       <c r="B9" t="n">
-        <v>78526</v>
+        <v>79144</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1405,21 +1405,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1429,10 +1429,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>478248</v>
+        <v>478243</v>
       </c>
       <c r="R9" t="n">
-        <v>6827593</v>
+        <v>6827585</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1491,10 +1491,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>120075067</v>
+        <v>120074933</v>
       </c>
       <c r="B10" t="n">
-        <v>78526</v>
+        <v>79144</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1507,21 +1507,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1531,10 +1531,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>478164</v>
+        <v>478189</v>
       </c>
       <c r="R10" t="n">
-        <v>6827661</v>
+        <v>6827761</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1593,10 +1593,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>120074886</v>
+        <v>120075164</v>
       </c>
       <c r="B11" t="n">
-        <v>79144</v>
+        <v>78526</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1609,21 +1609,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1633,10 +1633,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>478125</v>
+        <v>478092</v>
       </c>
       <c r="R11" t="n">
-        <v>6827604</v>
+        <v>6827810</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1695,10 +1695,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>120074943</v>
+        <v>120075078</v>
       </c>
       <c r="B12" t="n">
-        <v>79144</v>
+        <v>78526</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1711,21 +1711,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1735,10 +1735,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>478073</v>
+        <v>478116</v>
       </c>
       <c r="R12" t="n">
-        <v>6827827</v>
+        <v>6827567</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1797,10 +1797,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>120075007</v>
+        <v>120074934</v>
       </c>
       <c r="B13" t="n">
-        <v>78263</v>
+        <v>79144</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1813,21 +1813,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>228912</v>
+        <v>6453</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1837,10 +1837,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>478285</v>
+        <v>478169</v>
       </c>
       <c r="R13" t="n">
-        <v>6827770</v>
+        <v>6827760</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1899,10 +1899,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>120074998</v>
+        <v>120075024</v>
       </c>
       <c r="B14" t="n">
-        <v>78263</v>
+        <v>78262</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1915,21 +1915,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>228912</v>
+        <v>6446</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1939,10 +1939,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>478172</v>
+        <v>478165</v>
       </c>
       <c r="R14" t="n">
-        <v>6827640</v>
+        <v>6827712</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2001,10 +2001,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>120074928</v>
+        <v>120075236</v>
       </c>
       <c r="B15" t="n">
-        <v>78560</v>
+        <v>78171</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2017,21 +2017,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>185</v>
+        <v>353</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2041,7 +2041,7 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>478059</v>
+        <v>478062</v>
       </c>
       <c r="R15" t="n">
         <v>6827740</v>
@@ -2103,10 +2103,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>120075227</v>
+        <v>120075009</v>
       </c>
       <c r="B16" t="n">
-        <v>78171</v>
+        <v>78263</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2119,21 +2119,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>353</v>
+        <v>228912</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2143,10 +2143,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>478088</v>
+        <v>478151</v>
       </c>
       <c r="R16" t="n">
-        <v>6827834</v>
+        <v>6827745</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2205,10 +2205,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>120075197</v>
+        <v>120075004</v>
       </c>
       <c r="B17" t="n">
-        <v>91840</v>
+        <v>78263</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2217,47 +2217,38 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>4364</v>
+        <v>228912</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J17" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
           <t>Hevoslamm, Dlr</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>478077</v>
+        <v>478212</v>
       </c>
       <c r="R17" t="n">
-        <v>6827805</v>
+        <v>6827573</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2316,10 +2307,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>120075042</v>
+        <v>120075226</v>
       </c>
       <c r="B18" t="n">
-        <v>78262</v>
+        <v>78171</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2332,21 +2323,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6446</v>
+        <v>353</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2356,10 +2347,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>478074</v>
+        <v>478098</v>
       </c>
       <c r="R18" t="n">
-        <v>6827775</v>
+        <v>6827815</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2418,10 +2409,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>120075092</v>
+        <v>120074928</v>
       </c>
       <c r="B19" t="n">
-        <v>78526</v>
+        <v>78560</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2434,21 +2425,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2458,10 +2449,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>478167</v>
+        <v>478059</v>
       </c>
       <c r="R19" t="n">
-        <v>6827561</v>
+        <v>6827740</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2520,10 +2511,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>120075174</v>
+        <v>120074914</v>
       </c>
       <c r="B20" t="n">
-        <v>78526</v>
+        <v>78560</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2536,21 +2527,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2560,10 +2551,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>478057</v>
+        <v>478169</v>
       </c>
       <c r="R20" t="n">
-        <v>6827749</v>
+        <v>6827680</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2622,7 +2613,7 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>120075135</v>
+        <v>120075085</v>
       </c>
       <c r="B21" t="n">
         <v>78526</v>
@@ -2662,10 +2653,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>478291</v>
+        <v>478094</v>
       </c>
       <c r="R21" t="n">
-        <v>6827744</v>
+        <v>6827504</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2724,10 +2715,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>120075038</v>
+        <v>120075161</v>
       </c>
       <c r="B22" t="n">
-        <v>78262</v>
+        <v>78526</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2740,21 +2731,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2764,10 +2755,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>478261</v>
+        <v>478082</v>
       </c>
       <c r="R22" t="n">
-        <v>6827731</v>
+        <v>6827766</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2826,10 +2817,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>120074948</v>
+        <v>120075039</v>
       </c>
       <c r="B23" t="n">
-        <v>79144</v>
+        <v>78262</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -2842,21 +2833,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6453</v>
+        <v>6446</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2866,10 +2857,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>478070</v>
+        <v>478238</v>
       </c>
       <c r="R23" t="n">
-        <v>6827723</v>
+        <v>6827752</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2928,10 +2919,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>120074891</v>
+        <v>120075038</v>
       </c>
       <c r="B24" t="n">
-        <v>79144</v>
+        <v>78262</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -2944,21 +2935,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6453</v>
+        <v>6446</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -2968,10 +2959,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>478212</v>
+        <v>478261</v>
       </c>
       <c r="R24" t="n">
-        <v>6827573</v>
+        <v>6827731</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3030,10 +3021,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>120075230</v>
+        <v>120075019</v>
       </c>
       <c r="B25" t="n">
-        <v>78171</v>
+        <v>79607</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3046,21 +3037,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>353</v>
+        <v>6458</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3070,10 +3061,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>478064</v>
+        <v>478227</v>
       </c>
       <c r="R25" t="n">
-        <v>6827866</v>
+        <v>6827655</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3132,10 +3123,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>120075137</v>
+        <v>120075197</v>
       </c>
       <c r="B26" t="n">
-        <v>78526</v>
+        <v>91840</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3144,38 +3135,47 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr"/>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="P26" t="inlineStr">
         <is>
           <t>Hevoslamm, Dlr</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>478288</v>
+        <v>478077</v>
       </c>
       <c r="R26" t="n">
-        <v>6827763</v>
+        <v>6827805</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3234,7 +3234,7 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>120075071</v>
+        <v>120075087</v>
       </c>
       <c r="B27" t="n">
         <v>78526</v>
@@ -3274,10 +3274,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>478116</v>
+        <v>478145</v>
       </c>
       <c r="R27" t="n">
-        <v>6827633</v>
+        <v>6827485</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3336,7 +3336,7 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>120075088</v>
+        <v>120075134</v>
       </c>
       <c r="B28" t="n">
         <v>78526</v>
@@ -3376,10 +3376,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>478151</v>
+        <v>478266</v>
       </c>
       <c r="R28" t="n">
-        <v>6827509</v>
+        <v>6827765</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3438,10 +3438,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>120075008</v>
+        <v>120074905</v>
       </c>
       <c r="B29" t="n">
-        <v>78263</v>
+        <v>79144</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3454,21 +3454,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>228912</v>
+        <v>6453</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3478,10 +3478,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>478299</v>
+        <v>478285</v>
       </c>
       <c r="R29" t="n">
-        <v>6827805</v>
+        <v>6827770</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3540,10 +3540,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>120074915</v>
+        <v>120074891</v>
       </c>
       <c r="B30" t="n">
-        <v>78560</v>
+        <v>79144</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3556,21 +3556,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>185</v>
+        <v>6453</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3580,10 +3580,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>478102</v>
+        <v>478212</v>
       </c>
       <c r="R30" t="n">
-        <v>6827555</v>
+        <v>6827573</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3642,10 +3642,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>120075147</v>
+        <v>120075000</v>
       </c>
       <c r="B31" t="n">
-        <v>78526</v>
+        <v>78263</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3658,21 +3658,21 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3682,10 +3682,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>478153</v>
+        <v>478121</v>
       </c>
       <c r="R31" t="n">
-        <v>6827728</v>
+        <v>6827607</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3744,10 +3744,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>120075167</v>
+        <v>120074929</v>
       </c>
       <c r="B32" t="n">
-        <v>78526</v>
+        <v>78560</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -3760,21 +3760,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3784,10 +3784,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>478105</v>
+        <v>478045</v>
       </c>
       <c r="R32" t="n">
-        <v>6827851</v>
+        <v>6827724</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3846,10 +3846,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>120075026</v>
+        <v>120075227</v>
       </c>
       <c r="B33" t="n">
-        <v>78262</v>
+        <v>78171</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -3862,21 +3862,21 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6446</v>
+        <v>353</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -3886,10 +3886,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>478161</v>
+        <v>478088</v>
       </c>
       <c r="R33" t="n">
-        <v>6827592</v>
+        <v>6827834</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -3948,10 +3948,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>120075039</v>
+        <v>120075202</v>
       </c>
       <c r="B34" t="n">
-        <v>78262</v>
+        <v>78171</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -3964,21 +3964,21 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6446</v>
+        <v>353</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -3988,10 +3988,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>478238</v>
+        <v>478218</v>
       </c>
       <c r="R34" t="n">
-        <v>6827752</v>
+        <v>6827721</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4050,10 +4050,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>120074905</v>
+        <v>120075162</v>
       </c>
       <c r="B35" t="n">
-        <v>79144</v>
+        <v>78526</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4066,21 +4066,21 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4090,10 +4090,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>478285</v>
+        <v>478080</v>
       </c>
       <c r="R35" t="n">
-        <v>6827770</v>
+        <v>6827808</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4152,10 +4152,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>120075028</v>
+        <v>120075239</v>
       </c>
       <c r="B36" t="n">
-        <v>78262</v>
+        <v>77458</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4168,21 +4168,21 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6446</v>
+        <v>6487</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Blågrå svartspik</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Chaenothecopsis fennica</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Laurila) Tibell</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4195,7 +4195,7 @@
         <v>478137</v>
       </c>
       <c r="R36" t="n">
-        <v>6827553</v>
+        <v>6827554</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4254,10 +4254,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>120074906</v>
+        <v>120075048</v>
       </c>
       <c r="B37" t="n">
-        <v>79144</v>
+        <v>56514</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4270,34 +4270,39 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6453</v>
+        <v>102612</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
+      <c r="M37" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="P37" t="inlineStr">
         <is>
           <t>Hevoslamm, Dlr</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>478294</v>
+        <v>478070</v>
       </c>
       <c r="R37" t="n">
-        <v>6827790</v>
+        <v>6827723</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4356,10 +4361,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>120075214</v>
+        <v>120074952</v>
       </c>
       <c r="B38" t="n">
-        <v>78171</v>
+        <v>79115</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4372,21 +4377,21 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>353</v>
+        <v>229821</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4396,10 +4401,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>478266</v>
+        <v>478120</v>
       </c>
       <c r="R38" t="n">
-        <v>6827724</v>
+        <v>6827605</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4458,10 +4463,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>120075207</v>
+        <v>120074931</v>
       </c>
       <c r="B39" t="n">
-        <v>78171</v>
+        <v>79144</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4474,21 +4479,21 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>353</v>
+        <v>6453</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4498,10 +4503,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>478157</v>
+        <v>478261</v>
       </c>
       <c r="R39" t="n">
-        <v>6827509</v>
+        <v>6827822</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4560,10 +4565,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>120075136</v>
+        <v>120075015</v>
       </c>
       <c r="B40" t="n">
-        <v>78526</v>
+        <v>79607</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -4576,21 +4581,21 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4600,10 +4605,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>478290</v>
+        <v>478114</v>
       </c>
       <c r="R40" t="n">
-        <v>6827758</v>
+        <v>6827633</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4662,7 +4667,7 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>120075089</v>
+        <v>120075131</v>
       </c>
       <c r="B41" t="n">
         <v>78526</v>
@@ -4702,10 +4707,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>478153</v>
+        <v>478258</v>
       </c>
       <c r="R41" t="n">
-        <v>6827517</v>
+        <v>6827731</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4764,7 +4769,7 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>120075177</v>
+        <v>120075128</v>
       </c>
       <c r="B42" t="n">
         <v>78526</v>
@@ -4804,10 +4809,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>478075</v>
+        <v>478275</v>
       </c>
       <c r="R42" t="n">
-        <v>6827717</v>
+        <v>6827710</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4866,10 +4871,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>120075077</v>
+        <v>120075043</v>
       </c>
       <c r="B43" t="n">
-        <v>78526</v>
+        <v>78262</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -4882,21 +4887,21 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -4906,10 +4911,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>478124</v>
+        <v>478103</v>
       </c>
       <c r="R43" t="n">
-        <v>6827560</v>
+        <v>6827803</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -4968,7 +4973,7 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>120074883</v>
+        <v>120074889</v>
       </c>
       <c r="B44" t="n">
         <v>79144</v>
@@ -5008,10 +5013,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>478142</v>
+        <v>478163</v>
       </c>
       <c r="R44" t="n">
-        <v>6827623</v>
+        <v>6827536</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5070,10 +5075,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>120075045</v>
+        <v>120075012</v>
       </c>
       <c r="B45" t="n">
-        <v>78262</v>
+        <v>78263</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5086,21 +5091,21 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>6446</v>
+        <v>228912</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5110,10 +5115,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>478070</v>
+        <v>478055</v>
       </c>
       <c r="R45" t="n">
-        <v>6827723</v>
+        <v>6827786</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5172,10 +5177,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>120074946</v>
+        <v>120075003</v>
       </c>
       <c r="B46" t="n">
-        <v>79144</v>
+        <v>78263</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -5188,21 +5193,21 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>6453</v>
+        <v>228912</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5212,10 +5217,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>478056</v>
+        <v>478137</v>
       </c>
       <c r="R46" t="n">
-        <v>6827754</v>
+        <v>6827553</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5274,7 +5279,7 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>120075139</v>
+        <v>120075168</v>
       </c>
       <c r="B47" t="n">
         <v>78526</v>
@@ -5314,10 +5319,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>478294</v>
+        <v>478086</v>
       </c>
       <c r="R47" t="n">
-        <v>6827803</v>
+        <v>6827868</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5376,10 +5381,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>120075159</v>
+        <v>120075224</v>
       </c>
       <c r="B48" t="n">
-        <v>78526</v>
+        <v>78171</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -5392,21 +5397,21 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>6425</v>
+        <v>353</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5416,10 +5421,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>478100</v>
+        <v>478081</v>
       </c>
       <c r="R48" t="n">
-        <v>6827729</v>
+        <v>6827789</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5478,10 +5483,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>120075166</v>
+        <v>120075219</v>
       </c>
       <c r="B49" t="n">
-        <v>78526</v>
+        <v>78171</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -5494,21 +5499,21 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>6425</v>
+        <v>353</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5518,10 +5523,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>478092</v>
+        <v>478169</v>
       </c>
       <c r="R49" t="n">
-        <v>6827839</v>
+        <v>6827760</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5580,7 +5585,7 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>120075120</v>
+        <v>120075139</v>
       </c>
       <c r="B50" t="n">
         <v>78526</v>
@@ -5620,10 +5625,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>478223</v>
+        <v>478294</v>
       </c>
       <c r="R50" t="n">
-        <v>6827657</v>
+        <v>6827803</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5682,7 +5687,7 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>120075078</v>
+        <v>120075082</v>
       </c>
       <c r="B51" t="n">
         <v>78526</v>
@@ -5722,10 +5727,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>478116</v>
+        <v>478097</v>
       </c>
       <c r="R51" t="n">
-        <v>6827567</v>
+        <v>6827544</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5784,7 +5789,7 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>120075128</v>
+        <v>120075175</v>
       </c>
       <c r="B52" t="n">
         <v>78526</v>
@@ -5824,10 +5829,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>478275</v>
+        <v>478059</v>
       </c>
       <c r="R52" t="n">
-        <v>6827710</v>
+        <v>6827739</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -5886,7 +5891,7 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>120075063</v>
+        <v>120075172</v>
       </c>
       <c r="B53" t="n">
         <v>78526</v>
@@ -5926,10 +5931,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>478201</v>
+        <v>478055</v>
       </c>
       <c r="R53" t="n">
-        <v>6827693</v>
+        <v>6827768</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -5988,10 +5993,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>120075043</v>
+        <v>120075234</v>
       </c>
       <c r="B54" t="n">
-        <v>78262</v>
+        <v>78171</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
@@ -6004,21 +6009,21 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>6446</v>
+        <v>353</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -6028,10 +6033,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>478103</v>
+        <v>478069</v>
       </c>
       <c r="R54" t="n">
-        <v>6827803</v>
+        <v>6827741</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6090,10 +6095,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>120074941</v>
+        <v>120075230</v>
       </c>
       <c r="B55" t="n">
-        <v>79144</v>
+        <v>78171</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
@@ -6106,21 +6111,21 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>6453</v>
+        <v>353</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -6130,10 +6135,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>478069</v>
+        <v>478064</v>
       </c>
       <c r="R55" t="n">
-        <v>6827854</v>
+        <v>6827866</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6192,10 +6197,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>120074917</v>
+        <v>120074881</v>
       </c>
       <c r="B56" t="n">
-        <v>78560</v>
+        <v>79144</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
@@ -6208,21 +6213,21 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>185</v>
+        <v>6453</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -6232,10 +6237,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>478095</v>
+        <v>478184</v>
       </c>
       <c r="R56" t="n">
-        <v>6827533</v>
+        <v>6827728</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6294,10 +6299,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>120075205</v>
+        <v>120075029</v>
       </c>
       <c r="B57" t="n">
-        <v>78171</v>
+        <v>78262</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
@@ -6310,21 +6315,21 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>353</v>
+        <v>6446</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -6334,10 +6339,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>478117</v>
+        <v>478115</v>
       </c>
       <c r="R57" t="n">
-        <v>6827612</v>
+        <v>6827564</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6396,10 +6401,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>120075201</v>
+        <v>120074887</v>
       </c>
       <c r="B58" t="n">
-        <v>78171</v>
+        <v>79144</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
@@ -6412,21 +6417,21 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>353</v>
+        <v>6453</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
@@ -6436,10 +6441,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>478182</v>
+        <v>478144</v>
       </c>
       <c r="R58" t="n">
-        <v>6827728</v>
+        <v>6827593</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6498,10 +6503,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>120074922</v>
+        <v>120075001</v>
       </c>
       <c r="B59" t="n">
-        <v>78560</v>
+        <v>78263</v>
       </c>
       <c r="C59" t="inlineStr">
         <is>
@@ -6514,21 +6519,21 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>185</v>
+        <v>228912</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
@@ -6538,10 +6543,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>478103</v>
+        <v>478125</v>
       </c>
       <c r="R59" t="n">
-        <v>6827718</v>
+        <v>6827604</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6600,10 +6605,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>120075003</v>
+        <v>120074986</v>
       </c>
       <c r="B60" t="n">
-        <v>78263</v>
+        <v>79608</v>
       </c>
       <c r="C60" t="inlineStr">
         <is>
@@ -6616,21 +6621,21 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>228912</v>
+        <v>2081</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
@@ -6640,10 +6645,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>478137</v>
+        <v>478096</v>
       </c>
       <c r="R60" t="n">
-        <v>6827553</v>
+        <v>6827549</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -6702,10 +6707,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>120074952</v>
+        <v>120075242</v>
       </c>
       <c r="B61" t="n">
-        <v>79115</v>
+        <v>77910</v>
       </c>
       <c r="C61" t="inlineStr">
         <is>
@@ -6718,21 +6723,21 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>229821</v>
+        <v>6437</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
@@ -6742,10 +6747,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>478120</v>
+        <v>478136</v>
       </c>
       <c r="R61" t="n">
-        <v>6827605</v>
+        <v>6827556</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -6804,10 +6809,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>120075025</v>
+        <v>120075071</v>
       </c>
       <c r="B62" t="n">
-        <v>78262</v>
+        <v>78526</v>
       </c>
       <c r="C62" t="inlineStr">
         <is>
@@ -6820,21 +6825,21 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
@@ -6844,10 +6849,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>478171</v>
+        <v>478116</v>
       </c>
       <c r="R62" t="n">
-        <v>6827642</v>
+        <v>6827633</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -6906,7 +6911,7 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>120075086</v>
+        <v>120075130</v>
       </c>
       <c r="B63" t="n">
         <v>78526</v>
@@ -6946,10 +6951,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>478104</v>
+        <v>478264</v>
       </c>
       <c r="R63" t="n">
-        <v>6827495</v>
+        <v>6827733</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -7008,10 +7013,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>120074889</v>
+        <v>120075070</v>
       </c>
       <c r="B64" t="n">
-        <v>79144</v>
+        <v>78526</v>
       </c>
       <c r="C64" t="inlineStr">
         <is>
@@ -7024,21 +7029,21 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
@@ -7048,10 +7053,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>478163</v>
+        <v>478135</v>
       </c>
       <c r="R64" t="n">
-        <v>6827536</v>
+        <v>6827625</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -7110,10 +7115,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>120074942</v>
+        <v>120075074</v>
       </c>
       <c r="B65" t="n">
-        <v>79144</v>
+        <v>78526</v>
       </c>
       <c r="C65" t="inlineStr">
         <is>
@@ -7126,21 +7131,21 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
@@ -7150,10 +7155,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>478065</v>
+        <v>478138</v>
       </c>
       <c r="R65" t="n">
-        <v>6827842</v>
+        <v>6827599</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7212,10 +7217,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>120074947</v>
+        <v>120075092</v>
       </c>
       <c r="B66" t="n">
-        <v>79144</v>
+        <v>78526</v>
       </c>
       <c r="C66" t="inlineStr">
         <is>
@@ -7228,21 +7233,21 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
@@ -7252,10 +7257,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>478061</v>
+        <v>478167</v>
       </c>
       <c r="R66" t="n">
-        <v>6827751</v>
+        <v>6827561</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7314,10 +7319,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>120074934</v>
+        <v>120075171</v>
       </c>
       <c r="B67" t="n">
-        <v>79144</v>
+        <v>78526</v>
       </c>
       <c r="C67" t="inlineStr">
         <is>
@@ -7330,21 +7335,21 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
@@ -7354,10 +7359,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>478169</v>
+        <v>478073</v>
       </c>
       <c r="R67" t="n">
-        <v>6827760</v>
+        <v>6827831</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7416,10 +7421,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>120074930</v>
+        <v>120075046</v>
       </c>
       <c r="B68" t="n">
-        <v>79144</v>
+        <v>78262</v>
       </c>
       <c r="C68" t="inlineStr">
         <is>
@@ -7432,21 +7437,21 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>6453</v>
+        <v>6446</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
@@ -7456,10 +7461,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>478299</v>
+        <v>478285</v>
       </c>
       <c r="R68" t="n">
-        <v>6827805</v>
+        <v>6827770</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7518,10 +7523,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>120075035</v>
+        <v>120075054</v>
       </c>
       <c r="B69" t="n">
-        <v>78262</v>
+        <v>90580</v>
       </c>
       <c r="C69" t="inlineStr">
         <is>
@@ -7534,21 +7539,21 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>6446</v>
+        <v>5432</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
@@ -7558,10 +7563,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>478273</v>
+        <v>478126</v>
       </c>
       <c r="R69" t="n">
-        <v>6827711</v>
+        <v>6827477</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -7620,10 +7625,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>120074892</v>
+        <v>120075010</v>
       </c>
       <c r="B70" t="n">
-        <v>79144</v>
+        <v>78263</v>
       </c>
       <c r="C70" t="inlineStr">
         <is>
@@ -7636,21 +7641,21 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>6453</v>
+        <v>228912</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
@@ -7660,10 +7665,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>478243</v>
+        <v>478074</v>
       </c>
       <c r="R70" t="n">
-        <v>6827585</v>
+        <v>6827772</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -7722,10 +7727,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>120074944</v>
+        <v>120075127</v>
       </c>
       <c r="B71" t="n">
-        <v>79144</v>
+        <v>78526</v>
       </c>
       <c r="C71" t="inlineStr">
         <is>
@@ -7738,21 +7743,21 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
@@ -7762,10 +7767,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>478056</v>
+        <v>478292</v>
       </c>
       <c r="R71" t="n">
-        <v>6827785</v>
+        <v>6827708</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -7824,10 +7829,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>120075019</v>
+        <v>120075157</v>
       </c>
       <c r="B72" t="n">
-        <v>79607</v>
+        <v>78526</v>
       </c>
       <c r="C72" t="inlineStr">
         <is>
@@ -7840,21 +7845,21 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
@@ -7864,10 +7869,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>478227</v>
+        <v>478103</v>
       </c>
       <c r="R72" t="n">
-        <v>6827655</v>
+        <v>6827718</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -7926,10 +7931,10 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>120075037</v>
+        <v>120074938</v>
       </c>
       <c r="B73" t="n">
-        <v>78262</v>
+        <v>79144</v>
       </c>
       <c r="C73" t="inlineStr">
         <is>
@@ -7942,21 +7947,21 @@
         </is>
       </c>
       <c r="E73" t="n">
-        <v>6446</v>
+        <v>6453</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
@@ -7966,10 +7971,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>478265</v>
+        <v>478097</v>
       </c>
       <c r="R73" t="n">
-        <v>6827716</v>
+        <v>6827756</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -8028,10 +8033,10 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>120075216</v>
+        <v>120075045</v>
       </c>
       <c r="B74" t="n">
-        <v>78171</v>
+        <v>78262</v>
       </c>
       <c r="C74" t="inlineStr">
         <is>
@@ -8044,21 +8049,21 @@
         </is>
       </c>
       <c r="E74" t="n">
-        <v>353</v>
+        <v>6446</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
@@ -8068,10 +8073,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>478294</v>
+        <v>478070</v>
       </c>
       <c r="R74" t="n">
-        <v>6827790</v>
+        <v>6827723</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -8130,7 +8135,7 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>120075084</v>
+        <v>120075176</v>
       </c>
       <c r="B75" t="n">
         <v>78526</v>
@@ -8170,10 +8175,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>478098</v>
+        <v>478066</v>
       </c>
       <c r="R75" t="n">
-        <v>6827520</v>
+        <v>6827732</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -8232,7 +8237,7 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>120075068</v>
+        <v>120075089</v>
       </c>
       <c r="B76" t="n">
         <v>78526</v>
@@ -8272,10 +8277,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>478174</v>
+        <v>478153</v>
       </c>
       <c r="R76" t="n">
-        <v>6827656</v>
+        <v>6827517</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -8334,10 +8339,10 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>120075000</v>
+        <v>120075138</v>
       </c>
       <c r="B77" t="n">
-        <v>78263</v>
+        <v>78526</v>
       </c>
       <c r="C77" t="inlineStr">
         <is>
@@ -8350,21 +8355,21 @@
         </is>
       </c>
       <c r="E77" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
@@ -8374,10 +8379,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>478121</v>
+        <v>478294</v>
       </c>
       <c r="R77" t="n">
-        <v>6827607</v>
+        <v>6827781</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -8436,10 +8441,10 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>120075215</v>
+        <v>120075120</v>
       </c>
       <c r="B78" t="n">
-        <v>78171</v>
+        <v>78526</v>
       </c>
       <c r="C78" t="inlineStr">
         <is>
@@ -8452,21 +8457,21 @@
         </is>
       </c>
       <c r="E78" t="n">
-        <v>353</v>
+        <v>6425</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
@@ -8476,10 +8481,10 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>478239</v>
+        <v>478223</v>
       </c>
       <c r="R78" t="n">
-        <v>6827752</v>
+        <v>6827657</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -8538,10 +8543,10 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>120074925</v>
+        <v>120075140</v>
       </c>
       <c r="B79" t="n">
-        <v>78560</v>
+        <v>78526</v>
       </c>
       <c r="C79" t="inlineStr">
         <is>
@@ -8554,21 +8559,21 @@
         </is>
       </c>
       <c r="E79" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
@@ -8578,10 +8583,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>478088</v>
+        <v>478310</v>
       </c>
       <c r="R79" t="n">
-        <v>6827834</v>
+        <v>6827797</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -8640,7 +8645,7 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>120075176</v>
+        <v>120075073</v>
       </c>
       <c r="B80" t="n">
         <v>78526</v>
@@ -8680,10 +8685,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>478066</v>
+        <v>478116</v>
       </c>
       <c r="R80" t="n">
-        <v>6827732</v>
+        <v>6827617</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -8742,7 +8747,7 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>120075162</v>
+        <v>120075097</v>
       </c>
       <c r="B81" t="n">
         <v>78526</v>
@@ -8782,10 +8787,10 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>478080</v>
+        <v>478248</v>
       </c>
       <c r="R81" t="n">
-        <v>6827808</v>
+        <v>6827593</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -8844,7 +8849,7 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>120075095</v>
+        <v>120075129</v>
       </c>
       <c r="B82" t="n">
         <v>78526</v>
@@ -8884,10 +8889,10 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>478219</v>
+        <v>478265</v>
       </c>
       <c r="R82" t="n">
-        <v>6827572</v>
+        <v>6827707</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -8946,7 +8951,7 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>120075171</v>
+        <v>120075062</v>
       </c>
       <c r="B83" t="n">
         <v>78526</v>
@@ -8986,10 +8991,10 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>478073</v>
+        <v>478221</v>
       </c>
       <c r="R83" t="n">
-        <v>6827831</v>
+        <v>6827719</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -9048,10 +9053,10 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>120075062</v>
+        <v>120075027</v>
       </c>
       <c r="B84" t="n">
-        <v>78526</v>
+        <v>78262</v>
       </c>
       <c r="C84" t="inlineStr">
         <is>
@@ -9064,21 +9069,21 @@
         </is>
       </c>
       <c r="E84" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
@@ -9088,10 +9093,10 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>478221</v>
+        <v>478144</v>
       </c>
       <c r="R84" t="n">
-        <v>6827719</v>
+        <v>6827593</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -9150,10 +9155,10 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>120075016</v>
+        <v>120075136</v>
       </c>
       <c r="B85" t="n">
-        <v>79607</v>
+        <v>78526</v>
       </c>
       <c r="C85" t="inlineStr">
         <is>
@@ -9166,21 +9171,21 @@
         </is>
       </c>
       <c r="E85" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
@@ -9190,10 +9195,10 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>478096</v>
+        <v>478290</v>
       </c>
       <c r="R85" t="n">
-        <v>6827549</v>
+        <v>6827758</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -9252,10 +9257,10 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>120075046</v>
+        <v>120075133</v>
       </c>
       <c r="B86" t="n">
-        <v>78262</v>
+        <v>78526</v>
       </c>
       <c r="C86" t="inlineStr">
         <is>
@@ -9268,21 +9273,21 @@
         </is>
       </c>
       <c r="E86" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I86" t="inlineStr"/>
@@ -9292,10 +9297,10 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>478285</v>
+        <v>478258</v>
       </c>
       <c r="R86" t="n">
-        <v>6827770</v>
+        <v>6827753</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>
@@ -9354,10 +9359,10 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>120074885</v>
+        <v>120075204</v>
       </c>
       <c r="B87" t="n">
-        <v>79144</v>
+        <v>78171</v>
       </c>
       <c r="C87" t="inlineStr">
         <is>
@@ -9370,21 +9375,21 @@
         </is>
       </c>
       <c r="E87" t="n">
-        <v>6453</v>
+        <v>353</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I87" t="inlineStr"/>
@@ -9456,7 +9461,7 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>120075196</v>
+        <v>120075075</v>
       </c>
       <c r="B88" t="n">
         <v>78526</v>
@@ -9496,10 +9501,10 @@
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>478288</v>
+        <v>478139</v>
       </c>
       <c r="R88" t="n">
-        <v>6827682</v>
+        <v>6827554</v>
       </c>
       <c r="S88" t="n">
         <v>10</v>
@@ -9558,7 +9563,7 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>120075121</v>
+        <v>120075064</v>
       </c>
       <c r="B89" t="n">
         <v>78526</v>
@@ -9598,10 +9603,10 @@
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>478232</v>
+        <v>478192</v>
       </c>
       <c r="R89" t="n">
-        <v>6827659</v>
+        <v>6827690</v>
       </c>
       <c r="S89" t="n">
         <v>10</v>
@@ -9660,7 +9665,7 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>120075144</v>
+        <v>120075145</v>
       </c>
       <c r="B90" t="n">
         <v>78526</v>
@@ -9700,10 +9705,10 @@
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>478261</v>
+        <v>478226</v>
       </c>
       <c r="R90" t="n">
-        <v>6827822</v>
+        <v>6827777</v>
       </c>
       <c r="S90" t="n">
         <v>10</v>
@@ -9762,10 +9767,10 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>120075145</v>
+        <v>120074961</v>
       </c>
       <c r="B91" t="n">
-        <v>78526</v>
+        <v>90582</v>
       </c>
       <c r="C91" t="inlineStr">
         <is>
@@ -9778,21 +9783,21 @@
         </is>
       </c>
       <c r="E91" t="n">
-        <v>6425</v>
+        <v>5442</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I91" t="inlineStr"/>
@@ -9802,10 +9807,10 @@
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>478226</v>
+        <v>478230</v>
       </c>
       <c r="R91" t="n">
-        <v>6827777</v>
+        <v>6827780</v>
       </c>
       <c r="S91" t="n">
         <v>10</v>
@@ -9864,10 +9869,10 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>120075027</v>
+        <v>120074883</v>
       </c>
       <c r="B92" t="n">
-        <v>78262</v>
+        <v>79144</v>
       </c>
       <c r="C92" t="inlineStr">
         <is>
@@ -9880,21 +9885,21 @@
         </is>
       </c>
       <c r="E92" t="n">
-        <v>6446</v>
+        <v>6453</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I92" t="inlineStr"/>
@@ -9904,10 +9909,10 @@
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>478144</v>
+        <v>478142</v>
       </c>
       <c r="R92" t="n">
-        <v>6827593</v>
+        <v>6827623</v>
       </c>
       <c r="S92" t="n">
         <v>10</v>
@@ -9966,10 +9971,10 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>120074914</v>
+        <v>120074904</v>
       </c>
       <c r="B93" t="n">
-        <v>78560</v>
+        <v>79144</v>
       </c>
       <c r="C93" t="inlineStr">
         <is>
@@ -9982,21 +9987,21 @@
         </is>
       </c>
       <c r="E93" t="n">
-        <v>185</v>
+        <v>6453</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I93" t="inlineStr"/>
@@ -10006,10 +10011,10 @@
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>478169</v>
+        <v>478262</v>
       </c>
       <c r="R93" t="n">
-        <v>6827680</v>
+        <v>6827730</v>
       </c>
       <c r="S93" t="n">
         <v>10</v>
@@ -10068,10 +10073,10 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>120075204</v>
+        <v>120074886</v>
       </c>
       <c r="B94" t="n">
-        <v>78171</v>
+        <v>79144</v>
       </c>
       <c r="C94" t="inlineStr">
         <is>
@@ -10084,21 +10089,21 @@
         </is>
       </c>
       <c r="E94" t="n">
-        <v>353</v>
+        <v>6453</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I94" t="inlineStr"/>
@@ -10108,10 +10113,10 @@
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>478115</v>
+        <v>478125</v>
       </c>
       <c r="R94" t="n">
-        <v>6827614</v>
+        <v>6827604</v>
       </c>
       <c r="S94" t="n">
         <v>10</v>
@@ -10170,10 +10175,10 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>120075013</v>
+        <v>120075037</v>
       </c>
       <c r="B95" t="n">
-        <v>78263</v>
+        <v>78262</v>
       </c>
       <c r="C95" t="inlineStr">
         <is>
@@ -10186,21 +10191,21 @@
         </is>
       </c>
       <c r="E95" t="n">
-        <v>228912</v>
+        <v>6446</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I95" t="inlineStr"/>
@@ -10210,10 +10215,10 @@
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>478239</v>
+        <v>478265</v>
       </c>
       <c r="R95" t="n">
-        <v>6827752</v>
+        <v>6827716</v>
       </c>
       <c r="S95" t="n">
         <v>10</v>
@@ -10272,10 +10277,10 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>120075231</v>
+        <v>120074997</v>
       </c>
       <c r="B96" t="n">
-        <v>78171</v>
+        <v>78263</v>
       </c>
       <c r="C96" t="inlineStr">
         <is>
@@ -10288,21 +10293,21 @@
         </is>
       </c>
       <c r="E96" t="n">
-        <v>353</v>
+        <v>228912</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I96" t="inlineStr"/>
@@ -10312,10 +10317,10 @@
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>478067</v>
+        <v>478218</v>
       </c>
       <c r="R96" t="n">
-        <v>6827863</v>
+        <v>6827733</v>
       </c>
       <c r="S96" t="n">
         <v>10</v>
@@ -10374,7 +10379,7 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>120075223</v>
+        <v>120075214</v>
       </c>
       <c r="B97" t="n">
         <v>78171</v>
@@ -10414,10 +10419,10 @@
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>478076</v>
+        <v>478266</v>
       </c>
       <c r="R97" t="n">
-        <v>6827777</v>
+        <v>6827724</v>
       </c>
       <c r="S97" t="n">
         <v>10</v>
@@ -10476,10 +10481,10 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>120075146</v>
+        <v>120075025</v>
       </c>
       <c r="B98" t="n">
-        <v>78526</v>
+        <v>78262</v>
       </c>
       <c r="C98" t="inlineStr">
         <is>
@@ -10492,21 +10497,21 @@
         </is>
       </c>
       <c r="E98" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I98" t="inlineStr"/>
@@ -10516,10 +10521,10 @@
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>478154</v>
+        <v>478171</v>
       </c>
       <c r="R98" t="n">
-        <v>6827747</v>
+        <v>6827642</v>
       </c>
       <c r="S98" t="n">
         <v>10</v>
@@ -10578,10 +10583,10 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>120075130</v>
+        <v>120074930</v>
       </c>
       <c r="B99" t="n">
-        <v>78526</v>
+        <v>79144</v>
       </c>
       <c r="C99" t="inlineStr">
         <is>
@@ -10594,21 +10599,21 @@
         </is>
       </c>
       <c r="E99" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I99" t="inlineStr"/>
@@ -10618,10 +10623,10 @@
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>478264</v>
+        <v>478299</v>
       </c>
       <c r="R99" t="n">
-        <v>6827733</v>
+        <v>6827805</v>
       </c>
       <c r="S99" t="n">
         <v>10</v>
@@ -10680,10 +10685,10 @@
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>120075134</v>
+        <v>120075198</v>
       </c>
       <c r="B100" t="n">
-        <v>78526</v>
+        <v>91840</v>
       </c>
       <c r="C100" t="inlineStr">
         <is>
@@ -10692,25 +10697,25 @@
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E100" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I100" t="inlineStr"/>
@@ -10720,10 +10725,10 @@
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>478266</v>
+        <v>478163</v>
       </c>
       <c r="R100" t="n">
-        <v>6827765</v>
+        <v>6827530</v>
       </c>
       <c r="S100" t="n">
         <v>10</v>
@@ -10782,7 +10787,7 @@
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>120075066</v>
+        <v>120075061</v>
       </c>
       <c r="B101" t="n">
         <v>78526</v>
@@ -10825,7 +10830,7 @@
         <v>478160</v>
       </c>
       <c r="R101" t="n">
-        <v>6827680</v>
+        <v>6827710</v>
       </c>
       <c r="S101" t="n">
         <v>10</v>
@@ -10884,10 +10889,10 @@
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>120074887</v>
+        <v>120075167</v>
       </c>
       <c r="B102" t="n">
-        <v>79144</v>
+        <v>78526</v>
       </c>
       <c r="C102" t="inlineStr">
         <is>
@@ -10900,21 +10905,21 @@
         </is>
       </c>
       <c r="E102" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I102" t="inlineStr"/>
@@ -10924,10 +10929,10 @@
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>478144</v>
+        <v>478105</v>
       </c>
       <c r="R102" t="n">
-        <v>6827593</v>
+        <v>6827851</v>
       </c>
       <c r="S102" t="n">
         <v>10</v>
@@ -10986,10 +10991,10 @@
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>120074882</v>
+        <v>120075088</v>
       </c>
       <c r="B103" t="n">
-        <v>79144</v>
+        <v>78526</v>
       </c>
       <c r="C103" t="inlineStr">
         <is>
@@ -11002,21 +11007,21 @@
         </is>
       </c>
       <c r="E103" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I103" t="inlineStr"/>
@@ -11026,10 +11031,10 @@
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>478162</v>
+        <v>478151</v>
       </c>
       <c r="R103" t="n">
-        <v>6827593</v>
+        <v>6827509</v>
       </c>
       <c r="S103" t="n">
         <v>10</v>
@@ -11088,10 +11093,10 @@
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>120075009</v>
+        <v>120075063</v>
       </c>
       <c r="B104" t="n">
-        <v>78263</v>
+        <v>78526</v>
       </c>
       <c r="C104" t="inlineStr">
         <is>
@@ -11104,21 +11109,21 @@
         </is>
       </c>
       <c r="E104" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I104" t="inlineStr"/>
@@ -11128,10 +11133,10 @@
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>478151</v>
+        <v>478201</v>
       </c>
       <c r="R104" t="n">
-        <v>6827745</v>
+        <v>6827693</v>
       </c>
       <c r="S104" t="n">
         <v>10</v>
@@ -11190,10 +11195,10 @@
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>120075224</v>
+        <v>120075066</v>
       </c>
       <c r="B105" t="n">
-        <v>78171</v>
+        <v>78526</v>
       </c>
       <c r="C105" t="inlineStr">
         <is>
@@ -11206,21 +11211,21 @@
         </is>
       </c>
       <c r="E105" t="n">
-        <v>353</v>
+        <v>6425</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I105" t="inlineStr"/>
@@ -11230,10 +11235,10 @@
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>478081</v>
+        <v>478160</v>
       </c>
       <c r="R105" t="n">
-        <v>6827789</v>
+        <v>6827680</v>
       </c>
       <c r="S105" t="n">
         <v>10</v>
@@ -11292,10 +11297,10 @@
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>120075192</v>
+        <v>120074906</v>
       </c>
       <c r="B106" t="n">
-        <v>78526</v>
+        <v>79144</v>
       </c>
       <c r="C106" t="inlineStr">
         <is>
@@ -11308,21 +11313,21 @@
         </is>
       </c>
       <c r="E106" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I106" t="inlineStr"/>
@@ -11332,10 +11337,10 @@
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>478282</v>
+        <v>478294</v>
       </c>
       <c r="R106" t="n">
-        <v>6827683</v>
+        <v>6827790</v>
       </c>
       <c r="S106" t="n">
         <v>10</v>
@@ -11394,10 +11399,10 @@
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>120075143</v>
+        <v>120074996</v>
       </c>
       <c r="B107" t="n">
-        <v>78526</v>
+        <v>78263</v>
       </c>
       <c r="C107" t="inlineStr">
         <is>
@@ -11410,21 +11415,21 @@
         </is>
       </c>
       <c r="E107" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I107" t="inlineStr"/>
@@ -11434,10 +11439,10 @@
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>478301</v>
+        <v>478165</v>
       </c>
       <c r="R107" t="n">
-        <v>6827814</v>
+        <v>6827712</v>
       </c>
       <c r="S107" t="n">
         <v>10</v>
@@ -11496,10 +11501,10 @@
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>120075064</v>
+        <v>120075216</v>
       </c>
       <c r="B108" t="n">
-        <v>78526</v>
+        <v>78171</v>
       </c>
       <c r="C108" t="inlineStr">
         <is>
@@ -11512,21 +11517,21 @@
         </is>
       </c>
       <c r="E108" t="n">
-        <v>6425</v>
+        <v>353</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I108" t="inlineStr"/>
@@ -11536,10 +11541,10 @@
         </is>
       </c>
       <c r="Q108" t="n">
-        <v>478192</v>
+        <v>478294</v>
       </c>
       <c r="R108" t="n">
-        <v>6827690</v>
+        <v>6827790</v>
       </c>
       <c r="S108" t="n">
         <v>10</v>
@@ -11598,10 +11603,10 @@
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>120075175</v>
+        <v>120074922</v>
       </c>
       <c r="B109" t="n">
-        <v>78526</v>
+        <v>78560</v>
       </c>
       <c r="C109" t="inlineStr">
         <is>
@@ -11614,21 +11619,21 @@
         </is>
       </c>
       <c r="E109" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I109" t="inlineStr"/>
@@ -11638,10 +11643,10 @@
         </is>
       </c>
       <c r="Q109" t="n">
-        <v>478059</v>
+        <v>478103</v>
       </c>
       <c r="R109" t="n">
-        <v>6827739</v>
+        <v>6827718</v>
       </c>
       <c r="S109" t="n">
         <v>10</v>
@@ -11700,10 +11705,10 @@
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>120074956</v>
+        <v>120075196</v>
       </c>
       <c r="B110" t="n">
-        <v>57310</v>
+        <v>78526</v>
       </c>
       <c r="C110" t="inlineStr">
         <is>
@@ -11716,39 +11721,34 @@
         </is>
       </c>
       <c r="E110" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I110" t="inlineStr"/>
-      <c r="M110" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P110" t="inlineStr">
         <is>
           <t>Hevoslamm, Dlr</t>
         </is>
       </c>
       <c r="Q110" t="n">
-        <v>478278</v>
+        <v>478288</v>
       </c>
       <c r="R110" t="n">
-        <v>6827832</v>
+        <v>6827682</v>
       </c>
       <c r="S110" t="n">
         <v>10</v>
@@ -11781,11 +11781,6 @@
       <c r="AA110" t="inlineStr">
         <is>
           <t>2024-09-27</t>
-        </is>
-      </c>
-      <c r="AC110" t="inlineStr">
-        <is>
-          <t>Färska ringhack (tall)</t>
         </is>
       </c>
       <c r="AD110" t="b">
@@ -11812,10 +11807,10 @@
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>120075219</v>
+        <v>120075132</v>
       </c>
       <c r="B111" t="n">
-        <v>78171</v>
+        <v>78526</v>
       </c>
       <c r="C111" t="inlineStr">
         <is>
@@ -11828,21 +11823,21 @@
         </is>
       </c>
       <c r="E111" t="n">
-        <v>353</v>
+        <v>6425</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I111" t="inlineStr"/>
@@ -11852,10 +11847,10 @@
         </is>
       </c>
       <c r="Q111" t="n">
-        <v>478169</v>
+        <v>478240</v>
       </c>
       <c r="R111" t="n">
-        <v>6827760</v>
+        <v>6827754</v>
       </c>
       <c r="S111" t="n">
         <v>10</v>
@@ -11914,7 +11909,7 @@
     </row>
     <row r="112">
       <c r="A112" t="n">
-        <v>120075065</v>
+        <v>120075173</v>
       </c>
       <c r="B112" t="n">
         <v>78526</v>
@@ -11954,10 +11949,10 @@
         </is>
       </c>
       <c r="Q112" t="n">
-        <v>478169</v>
+        <v>478052</v>
       </c>
       <c r="R112" t="n">
-        <v>6827679</v>
+        <v>6827754</v>
       </c>
       <c r="S112" t="n">
         <v>10</v>
@@ -12016,10 +12011,10 @@
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>120075024</v>
+        <v>120075065</v>
       </c>
       <c r="B113" t="n">
-        <v>78262</v>
+        <v>78526</v>
       </c>
       <c r="C113" t="inlineStr">
         <is>
@@ -12032,21 +12027,21 @@
         </is>
       </c>
       <c r="E113" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I113" t="inlineStr"/>
@@ -12056,10 +12051,10 @@
         </is>
       </c>
       <c r="Q113" t="n">
-        <v>478165</v>
+        <v>478169</v>
       </c>
       <c r="R113" t="n">
-        <v>6827712</v>
+        <v>6827679</v>
       </c>
       <c r="S113" t="n">
         <v>10</v>
@@ -12118,10 +12113,10 @@
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>120074935</v>
+        <v>120075094</v>
       </c>
       <c r="B114" t="n">
-        <v>79144</v>
+        <v>78526</v>
       </c>
       <c r="C114" t="inlineStr">
         <is>
@@ -12134,21 +12129,21 @@
         </is>
       </c>
       <c r="E114" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I114" t="inlineStr"/>
@@ -12158,10 +12153,10 @@
         </is>
       </c>
       <c r="Q114" t="n">
-        <v>478150</v>
+        <v>478205</v>
       </c>
       <c r="R114" t="n">
-        <v>6827745</v>
+        <v>6827556</v>
       </c>
       <c r="S114" t="n">
         <v>10</v>
@@ -12220,10 +12215,10 @@
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>120074945</v>
+        <v>120075177</v>
       </c>
       <c r="B115" t="n">
-        <v>79144</v>
+        <v>78526</v>
       </c>
       <c r="C115" t="inlineStr">
         <is>
@@ -12236,21 +12231,21 @@
         </is>
       </c>
       <c r="E115" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I115" t="inlineStr"/>
@@ -12260,10 +12255,10 @@
         </is>
       </c>
       <c r="Q115" t="n">
-        <v>478061</v>
+        <v>478075</v>
       </c>
       <c r="R115" t="n">
-        <v>6827770</v>
+        <v>6827717</v>
       </c>
       <c r="S115" t="n">
         <v>10</v>
@@ -12322,10 +12317,10 @@
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>120074996</v>
+        <v>120075083</v>
       </c>
       <c r="B116" t="n">
-        <v>78263</v>
+        <v>78526</v>
       </c>
       <c r="C116" t="inlineStr">
         <is>
@@ -12338,21 +12333,21 @@
         </is>
       </c>
       <c r="E116" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I116" t="inlineStr"/>
@@ -12362,10 +12357,10 @@
         </is>
       </c>
       <c r="Q116" t="n">
-        <v>478165</v>
+        <v>478097</v>
       </c>
       <c r="R116" t="n">
-        <v>6827712</v>
+        <v>6827527</v>
       </c>
       <c r="S116" t="n">
         <v>10</v>
@@ -12424,10 +12419,10 @@
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>120074912</v>
+        <v>120075144</v>
       </c>
       <c r="B117" t="n">
-        <v>78560</v>
+        <v>78526</v>
       </c>
       <c r="C117" t="inlineStr">
         <is>
@@ -12440,21 +12435,21 @@
         </is>
       </c>
       <c r="E117" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I117" t="inlineStr"/>
@@ -12464,10 +12459,10 @@
         </is>
       </c>
       <c r="Q117" t="n">
-        <v>478149</v>
+        <v>478261</v>
       </c>
       <c r="R117" t="n">
-        <v>6827714</v>
+        <v>6827822</v>
       </c>
       <c r="S117" t="n">
         <v>10</v>
@@ -12526,7 +12521,7 @@
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>120075132</v>
+        <v>120075068</v>
       </c>
       <c r="B118" t="n">
         <v>78526</v>
@@ -12566,10 +12561,10 @@
         </is>
       </c>
       <c r="Q118" t="n">
-        <v>478240</v>
+        <v>478174</v>
       </c>
       <c r="R118" t="n">
-        <v>6827754</v>
+        <v>6827656</v>
       </c>
       <c r="S118" t="n">
         <v>10</v>
@@ -12628,10 +12623,10 @@
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>120075094</v>
+        <v>120074885</v>
       </c>
       <c r="B119" t="n">
-        <v>78526</v>
+        <v>79144</v>
       </c>
       <c r="C119" t="inlineStr">
         <is>
@@ -12644,21 +12639,21 @@
         </is>
       </c>
       <c r="E119" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I119" t="inlineStr"/>
@@ -12668,10 +12663,10 @@
         </is>
       </c>
       <c r="Q119" t="n">
-        <v>478205</v>
+        <v>478115</v>
       </c>
       <c r="R119" t="n">
-        <v>6827556</v>
+        <v>6827614</v>
       </c>
       <c r="S119" t="n">
         <v>10</v>
@@ -12730,10 +12725,10 @@
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>120075082</v>
+        <v>120075040</v>
       </c>
       <c r="B120" t="n">
-        <v>78526</v>
+        <v>78262</v>
       </c>
       <c r="C120" t="inlineStr">
         <is>
@@ -12746,21 +12741,21 @@
         </is>
       </c>
       <c r="E120" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I120" t="inlineStr"/>
@@ -12770,10 +12765,10 @@
         </is>
       </c>
       <c r="Q120" t="n">
-        <v>478097</v>
+        <v>478250</v>
       </c>
       <c r="R120" t="n">
-        <v>6827544</v>
+        <v>6827802</v>
       </c>
       <c r="S120" t="n">
         <v>10</v>
@@ -12832,7 +12827,7 @@
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>120075029</v>
+        <v>120075035</v>
       </c>
       <c r="B121" t="n">
         <v>78262</v>
@@ -12872,10 +12867,10 @@
         </is>
       </c>
       <c r="Q121" t="n">
-        <v>478115</v>
+        <v>478273</v>
       </c>
       <c r="R121" t="n">
-        <v>6827564</v>
+        <v>6827711</v>
       </c>
       <c r="S121" t="n">
         <v>10</v>
@@ -12934,10 +12929,10 @@
     </row>
     <row r="122">
       <c r="A122" t="n">
-        <v>120075044</v>
+        <v>120074932</v>
       </c>
       <c r="B122" t="n">
-        <v>78262</v>
+        <v>79144</v>
       </c>
       <c r="C122" t="inlineStr">
         <is>
@@ -12950,21 +12945,21 @@
         </is>
       </c>
       <c r="E122" t="n">
-        <v>6446</v>
+        <v>6453</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I122" t="inlineStr"/>
@@ -12974,10 +12969,10 @@
         </is>
       </c>
       <c r="Q122" t="n">
-        <v>478060</v>
+        <v>478250</v>
       </c>
       <c r="R122" t="n">
-        <v>6827770</v>
+        <v>6827802</v>
       </c>
       <c r="S122" t="n">
         <v>10</v>
@@ -13036,10 +13031,10 @@
     </row>
     <row r="123">
       <c r="A123" t="n">
-        <v>120075239</v>
+        <v>120074943</v>
       </c>
       <c r="B123" t="n">
-        <v>77458</v>
+        <v>79144</v>
       </c>
       <c r="C123" t="inlineStr">
         <is>
@@ -13052,21 +13047,21 @@
         </is>
       </c>
       <c r="E123" t="n">
-        <v>6487</v>
+        <v>6453</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Blågrå svartspik</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>Chaenothecopsis fennica</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t>(Laurila) Tibell</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I123" t="inlineStr"/>
@@ -13076,10 +13071,10 @@
         </is>
       </c>
       <c r="Q123" t="n">
-        <v>478137</v>
+        <v>478073</v>
       </c>
       <c r="R123" t="n">
-        <v>6827554</v>
+        <v>6827827</v>
       </c>
       <c r="S123" t="n">
         <v>10</v>
@@ -13138,7 +13133,7 @@
     </row>
     <row r="124">
       <c r="A124" t="n">
-        <v>120075012</v>
+        <v>120074998</v>
       </c>
       <c r="B124" t="n">
         <v>78263</v>
@@ -13178,10 +13173,10 @@
         </is>
       </c>
       <c r="Q124" t="n">
-        <v>478055</v>
+        <v>478172</v>
       </c>
       <c r="R124" t="n">
-        <v>6827786</v>
+        <v>6827640</v>
       </c>
       <c r="S124" t="n">
         <v>10</v>
@@ -13240,7 +13235,7 @@
     </row>
     <row r="125">
       <c r="A125" t="n">
-        <v>120075081</v>
+        <v>120075165</v>
       </c>
       <c r="B125" t="n">
         <v>78526</v>
@@ -13280,10 +13275,10 @@
         </is>
       </c>
       <c r="Q125" t="n">
-        <v>478096</v>
+        <v>478078</v>
       </c>
       <c r="R125" t="n">
-        <v>6827550</v>
+        <v>6827834</v>
       </c>
       <c r="S125" t="n">
         <v>10</v>
@@ -13342,7 +13337,7 @@
     </row>
     <row r="126">
       <c r="A126" t="n">
-        <v>120075090</v>
+        <v>120075166</v>
       </c>
       <c r="B126" t="n">
         <v>78526</v>
@@ -13382,10 +13377,10 @@
         </is>
       </c>
       <c r="Q126" t="n">
-        <v>478161</v>
+        <v>478092</v>
       </c>
       <c r="R126" t="n">
-        <v>6827528</v>
+        <v>6827839</v>
       </c>
       <c r="S126" t="n">
         <v>10</v>
@@ -13444,7 +13439,7 @@
     </row>
     <row r="127">
       <c r="A127" t="n">
-        <v>120075083</v>
+        <v>120075146</v>
       </c>
       <c r="B127" t="n">
         <v>78526</v>
@@ -13484,10 +13479,10 @@
         </is>
       </c>
       <c r="Q127" t="n">
-        <v>478097</v>
+        <v>478154</v>
       </c>
       <c r="R127" t="n">
-        <v>6827527</v>
+        <v>6827747</v>
       </c>
       <c r="S127" t="n">
         <v>10</v>
@@ -13546,10 +13541,10 @@
     </row>
     <row r="128">
       <c r="A128" t="n">
-        <v>120074904</v>
+        <v>120075232</v>
       </c>
       <c r="B128" t="n">
-        <v>79144</v>
+        <v>78171</v>
       </c>
       <c r="C128" t="inlineStr">
         <is>
@@ -13562,21 +13557,21 @@
         </is>
       </c>
       <c r="E128" t="n">
-        <v>6453</v>
+        <v>353</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H128" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I128" t="inlineStr"/>
@@ -13586,10 +13581,10 @@
         </is>
       </c>
       <c r="Q128" t="n">
-        <v>478262</v>
+        <v>478051</v>
       </c>
       <c r="R128" t="n">
-        <v>6827730</v>
+        <v>6827739</v>
       </c>
       <c r="S128" t="n">
         <v>10</v>
@@ -13648,10 +13643,10 @@
     </row>
     <row r="129">
       <c r="A129" t="n">
-        <v>120075040</v>
+        <v>120075225</v>
       </c>
       <c r="B129" t="n">
-        <v>78262</v>
+        <v>78171</v>
       </c>
       <c r="C129" t="inlineStr">
         <is>
@@ -13664,21 +13659,21 @@
         </is>
       </c>
       <c r="E129" t="n">
-        <v>6446</v>
+        <v>353</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H129" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I129" t="inlineStr"/>
@@ -13688,10 +13683,10 @@
         </is>
       </c>
       <c r="Q129" t="n">
-        <v>478250</v>
+        <v>478075</v>
       </c>
       <c r="R129" t="n">
-        <v>6827802</v>
+        <v>6827798</v>
       </c>
       <c r="S129" t="n">
         <v>10</v>
@@ -13750,10 +13745,10 @@
     </row>
     <row r="130">
       <c r="A130" t="n">
-        <v>120074881</v>
+        <v>120075205</v>
       </c>
       <c r="B130" t="n">
-        <v>79144</v>
+        <v>78171</v>
       </c>
       <c r="C130" t="inlineStr">
         <is>
@@ -13766,21 +13761,21 @@
         </is>
       </c>
       <c r="E130" t="n">
-        <v>6453</v>
+        <v>353</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H130" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I130" t="inlineStr"/>
@@ -13790,10 +13785,10 @@
         </is>
       </c>
       <c r="Q130" t="n">
-        <v>478184</v>
+        <v>478117</v>
       </c>
       <c r="R130" t="n">
-        <v>6827728</v>
+        <v>6827612</v>
       </c>
       <c r="S130" t="n">
         <v>10</v>
@@ -13852,10 +13847,10 @@
     </row>
     <row r="131">
       <c r="A131" t="n">
-        <v>120075226</v>
+        <v>120075016</v>
       </c>
       <c r="B131" t="n">
-        <v>78171</v>
+        <v>79607</v>
       </c>
       <c r="C131" t="inlineStr">
         <is>
@@ -13868,21 +13863,21 @@
         </is>
       </c>
       <c r="E131" t="n">
-        <v>353</v>
+        <v>6458</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H131" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I131" t="inlineStr"/>
@@ -13892,10 +13887,10 @@
         </is>
       </c>
       <c r="Q131" t="n">
-        <v>478098</v>
+        <v>478096</v>
       </c>
       <c r="R131" t="n">
-        <v>6827815</v>
+        <v>6827549</v>
       </c>
       <c r="S131" t="n">
         <v>10</v>
@@ -13954,10 +13949,10 @@
     </row>
     <row r="132">
       <c r="A132" t="n">
-        <v>120074929</v>
+        <v>120074948</v>
       </c>
       <c r="B132" t="n">
-        <v>78560</v>
+        <v>79144</v>
       </c>
       <c r="C132" t="inlineStr">
         <is>
@@ -13970,21 +13965,21 @@
         </is>
       </c>
       <c r="E132" t="n">
-        <v>185</v>
+        <v>6453</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H132" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I132" t="inlineStr"/>
@@ -13994,10 +13989,10 @@
         </is>
       </c>
       <c r="Q132" t="n">
-        <v>478045</v>
+        <v>478070</v>
       </c>
       <c r="R132" t="n">
-        <v>6827724</v>
+        <v>6827723</v>
       </c>
       <c r="S132" t="n">
         <v>10</v>
@@ -14056,10 +14051,10 @@
     </row>
     <row r="133">
       <c r="A133" t="n">
-        <v>120075054</v>
+        <v>120074947</v>
       </c>
       <c r="B133" t="n">
-        <v>90580</v>
+        <v>79144</v>
       </c>
       <c r="C133" t="inlineStr">
         <is>
@@ -14072,21 +14067,21 @@
         </is>
       </c>
       <c r="E133" t="n">
-        <v>5432</v>
+        <v>6453</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H133" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I133" t="inlineStr"/>
@@ -14096,10 +14091,10 @@
         </is>
       </c>
       <c r="Q133" t="n">
-        <v>478126</v>
+        <v>478061</v>
       </c>
       <c r="R133" t="n">
-        <v>6827477</v>
+        <v>6827751</v>
       </c>
       <c r="S133" t="n">
         <v>10</v>
@@ -14158,10 +14153,10 @@
     </row>
     <row r="134">
       <c r="A134" t="n">
-        <v>120075010</v>
+        <v>120074944</v>
       </c>
       <c r="B134" t="n">
-        <v>78263</v>
+        <v>79144</v>
       </c>
       <c r="C134" t="inlineStr">
         <is>
@@ -14174,21 +14169,21 @@
         </is>
       </c>
       <c r="E134" t="n">
-        <v>228912</v>
+        <v>6453</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H134" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I134" t="inlineStr"/>
@@ -14198,10 +14193,10 @@
         </is>
       </c>
       <c r="Q134" t="n">
-        <v>478074</v>
+        <v>478056</v>
       </c>
       <c r="R134" t="n">
-        <v>6827772</v>
+        <v>6827785</v>
       </c>
       <c r="S134" t="n">
         <v>10</v>
@@ -14260,10 +14255,10 @@
     </row>
     <row r="135">
       <c r="A135" t="n">
-        <v>120074997</v>
+        <v>120075044</v>
       </c>
       <c r="B135" t="n">
-        <v>78263</v>
+        <v>78262</v>
       </c>
       <c r="C135" t="inlineStr">
         <is>
@@ -14276,21 +14271,21 @@
         </is>
       </c>
       <c r="E135" t="n">
-        <v>228912</v>
+        <v>6446</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H135" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I135" t="inlineStr"/>
@@ -14300,10 +14295,10 @@
         </is>
       </c>
       <c r="Q135" t="n">
-        <v>478218</v>
+        <v>478060</v>
       </c>
       <c r="R135" t="n">
-        <v>6827733</v>
+        <v>6827770</v>
       </c>
       <c r="S135" t="n">
         <v>10</v>
@@ -14362,10 +14357,10 @@
     </row>
     <row r="136">
       <c r="A136" t="n">
-        <v>120074927</v>
+        <v>120074941</v>
       </c>
       <c r="B136" t="n">
-        <v>78560</v>
+        <v>79144</v>
       </c>
       <c r="C136" t="inlineStr">
         <is>
@@ -14378,21 +14373,21 @@
         </is>
       </c>
       <c r="E136" t="n">
-        <v>185</v>
+        <v>6453</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H136" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I136" t="inlineStr"/>
@@ -14402,10 +14397,10 @@
         </is>
       </c>
       <c r="Q136" t="n">
-        <v>478073</v>
+        <v>478069</v>
       </c>
       <c r="R136" t="n">
-        <v>6827836</v>
+        <v>6827854</v>
       </c>
       <c r="S136" t="n">
         <v>10</v>
@@ -14464,10 +14459,10 @@
     </row>
     <row r="137">
       <c r="A137" t="n">
-        <v>120075225</v>
+        <v>120074935</v>
       </c>
       <c r="B137" t="n">
-        <v>78171</v>
+        <v>79144</v>
       </c>
       <c r="C137" t="inlineStr">
         <is>
@@ -14480,21 +14475,21 @@
         </is>
       </c>
       <c r="E137" t="n">
-        <v>353</v>
+        <v>6453</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H137" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I137" t="inlineStr"/>
@@ -14504,10 +14499,10 @@
         </is>
       </c>
       <c r="Q137" t="n">
-        <v>478075</v>
+        <v>478150</v>
       </c>
       <c r="R137" t="n">
-        <v>6827798</v>
+        <v>6827745</v>
       </c>
       <c r="S137" t="n">
         <v>10</v>
@@ -14566,10 +14561,10 @@
     </row>
     <row r="138">
       <c r="A138" t="n">
-        <v>120075206</v>
+        <v>120074945</v>
       </c>
       <c r="B138" t="n">
-        <v>78171</v>
+        <v>79144</v>
       </c>
       <c r="C138" t="inlineStr">
         <is>
@@ -14582,21 +14577,21 @@
         </is>
       </c>
       <c r="E138" t="n">
-        <v>353</v>
+        <v>6453</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H138" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I138" t="inlineStr"/>
@@ -14606,10 +14601,10 @@
         </is>
       </c>
       <c r="Q138" t="n">
-        <v>478125</v>
+        <v>478061</v>
       </c>
       <c r="R138" t="n">
-        <v>6827604</v>
+        <v>6827770</v>
       </c>
       <c r="S138" t="n">
         <v>10</v>
@@ -14668,10 +14663,10 @@
     </row>
     <row r="139">
       <c r="A139" t="n">
-        <v>120075085</v>
+        <v>120075047</v>
       </c>
       <c r="B139" t="n">
-        <v>78526</v>
+        <v>78262</v>
       </c>
       <c r="C139" t="inlineStr">
         <is>
@@ -14684,21 +14679,21 @@
         </is>
       </c>
       <c r="E139" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H139" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I139" t="inlineStr"/>
@@ -14708,10 +14703,10 @@
         </is>
       </c>
       <c r="Q139" t="n">
-        <v>478094</v>
+        <v>478212</v>
       </c>
       <c r="R139" t="n">
-        <v>6827504</v>
+        <v>6827573</v>
       </c>
       <c r="S139" t="n">
         <v>10</v>
@@ -14770,7 +14765,7 @@
     </row>
     <row r="140">
       <c r="A140" t="n">
-        <v>120075163</v>
+        <v>120075135</v>
       </c>
       <c r="B140" t="n">
         <v>78526</v>
@@ -14810,10 +14805,10 @@
         </is>
       </c>
       <c r="Q140" t="n">
-        <v>478102</v>
+        <v>478291</v>
       </c>
       <c r="R140" t="n">
-        <v>6827800</v>
+        <v>6827744</v>
       </c>
       <c r="S140" t="n">
         <v>10</v>
@@ -14872,7 +14867,7 @@
     </row>
     <row r="141">
       <c r="A141" t="n">
-        <v>120075127</v>
+        <v>120075081</v>
       </c>
       <c r="B141" t="n">
         <v>78526</v>
@@ -14912,10 +14907,10 @@
         </is>
       </c>
       <c r="Q141" t="n">
-        <v>478292</v>
+        <v>478096</v>
       </c>
       <c r="R141" t="n">
-        <v>6827708</v>
+        <v>6827550</v>
       </c>
       <c r="S141" t="n">
         <v>10</v>
@@ -14974,7 +14969,7 @@
     </row>
     <row r="142">
       <c r="A142" t="n">
-        <v>120075160</v>
+        <v>120075137</v>
       </c>
       <c r="B142" t="n">
         <v>78526</v>
@@ -15014,10 +15009,10 @@
         </is>
       </c>
       <c r="Q142" t="n">
-        <v>478097</v>
+        <v>478288</v>
       </c>
       <c r="R142" t="n">
-        <v>6827744</v>
+        <v>6827763</v>
       </c>
       <c r="S142" t="n">
         <v>10</v>
@@ -15076,7 +15071,7 @@
     </row>
     <row r="143">
       <c r="A143" t="n">
-        <v>120075138</v>
+        <v>120075143</v>
       </c>
       <c r="B143" t="n">
         <v>78526</v>
@@ -15116,10 +15111,10 @@
         </is>
       </c>
       <c r="Q143" t="n">
-        <v>478294</v>
+        <v>478301</v>
       </c>
       <c r="R143" t="n">
-        <v>6827781</v>
+        <v>6827814</v>
       </c>
       <c r="S143" t="n">
         <v>10</v>
@@ -15178,7 +15173,7 @@
     </row>
     <row r="144">
       <c r="A144" t="n">
-        <v>120075161</v>
+        <v>120075086</v>
       </c>
       <c r="B144" t="n">
         <v>78526</v>
@@ -15218,10 +15213,10 @@
         </is>
       </c>
       <c r="Q144" t="n">
-        <v>478082</v>
+        <v>478104</v>
       </c>
       <c r="R144" t="n">
-        <v>6827766</v>
+        <v>6827495</v>
       </c>
       <c r="S144" t="n">
         <v>10</v>
@@ -15280,10 +15275,10 @@
     </row>
     <row r="145">
       <c r="A145" t="n">
-        <v>120074938</v>
+        <v>120075028</v>
       </c>
       <c r="B145" t="n">
-        <v>79144</v>
+        <v>78262</v>
       </c>
       <c r="C145" t="inlineStr">
         <is>
@@ -15296,21 +15291,21 @@
         </is>
       </c>
       <c r="E145" t="n">
-        <v>6453</v>
+        <v>6446</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H145" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I145" t="inlineStr"/>
@@ -15320,10 +15315,10 @@
         </is>
       </c>
       <c r="Q145" t="n">
-        <v>478097</v>
+        <v>478137</v>
       </c>
       <c r="R145" t="n">
-        <v>6827756</v>
+        <v>6827553</v>
       </c>
       <c r="S145" t="n">
         <v>10</v>
@@ -15382,10 +15377,10 @@
     </row>
     <row r="146">
       <c r="A146" t="n">
-        <v>120075047</v>
+        <v>120074882</v>
       </c>
       <c r="B146" t="n">
-        <v>78262</v>
+        <v>79144</v>
       </c>
       <c r="C146" t="inlineStr">
         <is>
@@ -15398,21 +15393,21 @@
         </is>
       </c>
       <c r="E146" t="n">
-        <v>6446</v>
+        <v>6453</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H146" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I146" t="inlineStr"/>
@@ -15422,10 +15417,10 @@
         </is>
       </c>
       <c r="Q146" t="n">
-        <v>478212</v>
+        <v>478162</v>
       </c>
       <c r="R146" t="n">
-        <v>6827573</v>
+        <v>6827593</v>
       </c>
       <c r="S146" t="n">
         <v>10</v>
@@ -15484,10 +15479,10 @@
     </row>
     <row r="147">
       <c r="A147" t="n">
-        <v>120075198</v>
+        <v>120074946</v>
       </c>
       <c r="B147" t="n">
-        <v>91840</v>
+        <v>79144</v>
       </c>
       <c r="C147" t="inlineStr">
         <is>
@@ -15496,25 +15491,25 @@
       </c>
       <c r="D147" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E147" t="n">
-        <v>4364</v>
+        <v>6453</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G147" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H147" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I147" t="inlineStr"/>
@@ -15524,10 +15519,10 @@
         </is>
       </c>
       <c r="Q147" t="n">
-        <v>478163</v>
+        <v>478056</v>
       </c>
       <c r="R147" t="n">
-        <v>6827530</v>
+        <v>6827754</v>
       </c>
       <c r="S147" t="n">
         <v>10</v>
@@ -15586,10 +15581,10 @@
     </row>
     <row r="148">
       <c r="A148" t="n">
-        <v>120075061</v>
+        <v>120074917</v>
       </c>
       <c r="B148" t="n">
-        <v>78526</v>
+        <v>78560</v>
       </c>
       <c r="C148" t="inlineStr">
         <is>
@@ -15602,21 +15597,21 @@
         </is>
       </c>
       <c r="E148" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G148" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H148" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I148" t="inlineStr"/>
@@ -15626,10 +15621,10 @@
         </is>
       </c>
       <c r="Q148" t="n">
-        <v>478160</v>
+        <v>478095</v>
       </c>
       <c r="R148" t="n">
-        <v>6827710</v>
+        <v>6827533</v>
       </c>
       <c r="S148" t="n">
         <v>10</v>
@@ -15688,10 +15683,10 @@
     </row>
     <row r="149">
       <c r="A149" t="n">
-        <v>120075060</v>
+        <v>120074912</v>
       </c>
       <c r="B149" t="n">
-        <v>78526</v>
+        <v>78560</v>
       </c>
       <c r="C149" t="inlineStr">
         <is>
@@ -15704,21 +15699,21 @@
         </is>
       </c>
       <c r="E149" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G149" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H149" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I149" t="inlineStr"/>
@@ -15728,10 +15723,10 @@
         </is>
       </c>
       <c r="Q149" t="n">
-        <v>478087</v>
+        <v>478149</v>
       </c>
       <c r="R149" t="n">
-        <v>6827718</v>
+        <v>6827714</v>
       </c>
       <c r="S149" t="n">
         <v>10</v>
@@ -15790,10 +15785,10 @@
     </row>
     <row r="150">
       <c r="A150" t="n">
-        <v>120075140</v>
+        <v>120075026</v>
       </c>
       <c r="B150" t="n">
-        <v>78526</v>
+        <v>78262</v>
       </c>
       <c r="C150" t="inlineStr">
         <is>
@@ -15806,21 +15801,21 @@
         </is>
       </c>
       <c r="E150" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G150" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H150" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I150" t="inlineStr"/>
@@ -15830,10 +15825,10 @@
         </is>
       </c>
       <c r="Q150" t="n">
-        <v>478310</v>
+        <v>478161</v>
       </c>
       <c r="R150" t="n">
-        <v>6827797</v>
+        <v>6827592</v>
       </c>
       <c r="S150" t="n">
         <v>10</v>
@@ -15892,10 +15887,10 @@
     </row>
     <row r="151">
       <c r="A151" t="n">
-        <v>120075048</v>
+        <v>120074939</v>
       </c>
       <c r="B151" t="n">
-        <v>56514</v>
+        <v>79144</v>
       </c>
       <c r="C151" t="inlineStr">
         <is>
@@ -15908,39 +15903,34 @@
         </is>
       </c>
       <c r="E151" t="n">
-        <v>102612</v>
+        <v>6453</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G151" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H151" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I151" t="inlineStr"/>
-      <c r="M151" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
       <c r="P151" t="inlineStr">
         <is>
           <t>Hevoslamm, Dlr</t>
         </is>
       </c>
       <c r="Q151" t="n">
-        <v>478070</v>
+        <v>478091</v>
       </c>
       <c r="R151" t="n">
-        <v>6827723</v>
+        <v>6827838</v>
       </c>
       <c r="S151" t="n">
         <v>10</v>
@@ -15999,10 +15989,10 @@
     </row>
     <row r="152">
       <c r="A152" t="n">
-        <v>120074888</v>
+        <v>120075007</v>
       </c>
       <c r="B152" t="n">
-        <v>79144</v>
+        <v>78263</v>
       </c>
       <c r="C152" t="inlineStr">
         <is>
@@ -16015,21 +16005,21 @@
         </is>
       </c>
       <c r="E152" t="n">
-        <v>6453</v>
+        <v>228912</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G152" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H152" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I152" t="inlineStr"/>
@@ -16039,10 +16029,10 @@
         </is>
       </c>
       <c r="Q152" t="n">
-        <v>478139</v>
+        <v>478285</v>
       </c>
       <c r="R152" t="n">
-        <v>6827554</v>
+        <v>6827770</v>
       </c>
       <c r="S152" t="n">
         <v>10</v>
@@ -16101,10 +16091,10 @@
     </row>
     <row r="153">
       <c r="A153" t="n">
-        <v>120074933</v>
+        <v>120075231</v>
       </c>
       <c r="B153" t="n">
-        <v>79144</v>
+        <v>78171</v>
       </c>
       <c r="C153" t="inlineStr">
         <is>
@@ -16117,21 +16107,21 @@
         </is>
       </c>
       <c r="E153" t="n">
-        <v>6453</v>
+        <v>353</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G153" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H153" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I153" t="inlineStr"/>
@@ -16141,10 +16131,10 @@
         </is>
       </c>
       <c r="Q153" t="n">
-        <v>478189</v>
+        <v>478067</v>
       </c>
       <c r="R153" t="n">
-        <v>6827761</v>
+        <v>6827863</v>
       </c>
       <c r="S153" t="n">
         <v>10</v>
@@ -16203,10 +16193,10 @@
     </row>
     <row r="154">
       <c r="A154" t="n">
-        <v>120075011</v>
+        <v>120074925</v>
       </c>
       <c r="B154" t="n">
-        <v>78263</v>
+        <v>78560</v>
       </c>
       <c r="C154" t="inlineStr">
         <is>
@@ -16219,21 +16209,21 @@
         </is>
       </c>
       <c r="E154" t="n">
-        <v>228912</v>
+        <v>185</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G154" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H154" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I154" t="inlineStr"/>
@@ -16243,10 +16233,10 @@
         </is>
       </c>
       <c r="Q154" t="n">
-        <v>478103</v>
+        <v>478088</v>
       </c>
       <c r="R154" t="n">
-        <v>6827803</v>
+        <v>6827834</v>
       </c>
       <c r="S154" t="n">
         <v>10</v>
@@ -16305,10 +16295,10 @@
     </row>
     <row r="155">
       <c r="A155" t="n">
-        <v>120075001</v>
+        <v>120075217</v>
       </c>
       <c r="B155" t="n">
-        <v>78263</v>
+        <v>78171</v>
       </c>
       <c r="C155" t="inlineStr">
         <is>
@@ -16321,21 +16311,21 @@
         </is>
       </c>
       <c r="E155" t="n">
-        <v>228912</v>
+        <v>353</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G155" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H155" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I155" t="inlineStr"/>
@@ -16345,10 +16335,10 @@
         </is>
       </c>
       <c r="Q155" t="n">
-        <v>478125</v>
+        <v>478264</v>
       </c>
       <c r="R155" t="n">
-        <v>6827604</v>
+        <v>6827839</v>
       </c>
       <c r="S155" t="n">
         <v>10</v>
@@ -16407,7 +16397,7 @@
     </row>
     <row r="156">
       <c r="A156" t="n">
-        <v>120075133</v>
+        <v>120075142</v>
       </c>
       <c r="B156" t="n">
         <v>78526</v>
@@ -16447,10 +16437,10 @@
         </is>
       </c>
       <c r="Q156" t="n">
-        <v>478258</v>
+        <v>478313</v>
       </c>
       <c r="R156" t="n">
-        <v>6827753</v>
+        <v>6827798</v>
       </c>
       <c r="S156" t="n">
         <v>10</v>
@@ -16509,7 +16499,7 @@
     </row>
     <row r="157">
       <c r="A157" t="n">
-        <v>120075173</v>
+        <v>120075147</v>
       </c>
       <c r="B157" t="n">
         <v>78526</v>
@@ -16549,10 +16539,10 @@
         </is>
       </c>
       <c r="Q157" t="n">
-        <v>478052</v>
+        <v>478153</v>
       </c>
       <c r="R157" t="n">
-        <v>6827754</v>
+        <v>6827728</v>
       </c>
       <c r="S157" t="n">
         <v>10</v>
@@ -16611,7 +16601,7 @@
     </row>
     <row r="158">
       <c r="A158" t="n">
-        <v>120075069</v>
+        <v>120075060</v>
       </c>
       <c r="B158" t="n">
         <v>78526</v>
@@ -16651,10 +16641,10 @@
         </is>
       </c>
       <c r="Q158" t="n">
-        <v>478157</v>
+        <v>478087</v>
       </c>
       <c r="R158" t="n">
-        <v>6827611</v>
+        <v>6827718</v>
       </c>
       <c r="S158" t="n">
         <v>10</v>
@@ -16713,7 +16703,7 @@
     </row>
     <row r="159">
       <c r="A159" t="n">
-        <v>120075087</v>
+        <v>120075077</v>
       </c>
       <c r="B159" t="n">
         <v>78526</v>
@@ -16753,10 +16743,10 @@
         </is>
       </c>
       <c r="Q159" t="n">
-        <v>478145</v>
+        <v>478124</v>
       </c>
       <c r="R159" t="n">
-        <v>6827485</v>
+        <v>6827560</v>
       </c>
       <c r="S159" t="n">
         <v>10</v>
@@ -16815,7 +16805,7 @@
     </row>
     <row r="160">
       <c r="A160" t="n">
-        <v>120075164</v>
+        <v>120075174</v>
       </c>
       <c r="B160" t="n">
         <v>78526</v>
@@ -16855,10 +16845,10 @@
         </is>
       </c>
       <c r="Q160" t="n">
-        <v>478092</v>
+        <v>478057</v>
       </c>
       <c r="R160" t="n">
-        <v>6827810</v>
+        <v>6827749</v>
       </c>
       <c r="S160" t="n">
         <v>10</v>
@@ -16917,10 +16907,10 @@
     </row>
     <row r="161">
       <c r="A161" t="n">
-        <v>120075131</v>
+        <v>120075215</v>
       </c>
       <c r="B161" t="n">
-        <v>78526</v>
+        <v>78171</v>
       </c>
       <c r="C161" t="inlineStr">
         <is>
@@ -16933,21 +16923,21 @@
         </is>
       </c>
       <c r="E161" t="n">
-        <v>6425</v>
+        <v>353</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G161" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H161" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I161" t="inlineStr"/>
@@ -16957,10 +16947,10 @@
         </is>
       </c>
       <c r="Q161" t="n">
-        <v>478258</v>
+        <v>478239</v>
       </c>
       <c r="R161" t="n">
-        <v>6827731</v>
+        <v>6827752</v>
       </c>
       <c r="S161" t="n">
         <v>10</v>
@@ -17019,10 +17009,10 @@
     </row>
     <row r="162">
       <c r="A162" t="n">
-        <v>120075070</v>
+        <v>120075206</v>
       </c>
       <c r="B162" t="n">
-        <v>78526</v>
+        <v>78171</v>
       </c>
       <c r="C162" t="inlineStr">
         <is>
@@ -17035,21 +17025,21 @@
         </is>
       </c>
       <c r="E162" t="n">
-        <v>6425</v>
+        <v>353</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G162" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H162" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I162" t="inlineStr"/>
@@ -17059,10 +17049,10 @@
         </is>
       </c>
       <c r="Q162" t="n">
-        <v>478135</v>
+        <v>478125</v>
       </c>
       <c r="R162" t="n">
-        <v>6827625</v>
+        <v>6827604</v>
       </c>
       <c r="S162" t="n">
         <v>10</v>
@@ -17121,7 +17111,7 @@
     </row>
     <row r="163">
       <c r="A163" t="n">
-        <v>120075168</v>
+        <v>120075090</v>
       </c>
       <c r="B163" t="n">
         <v>78526</v>
@@ -17161,10 +17151,10 @@
         </is>
       </c>
       <c r="Q163" t="n">
-        <v>478086</v>
+        <v>478161</v>
       </c>
       <c r="R163" t="n">
-        <v>6827868</v>
+        <v>6827528</v>
       </c>
       <c r="S163" t="n">
         <v>10</v>
@@ -17223,7 +17213,7 @@
     </row>
     <row r="164">
       <c r="A164" t="n">
-        <v>120075129</v>
+        <v>120075160</v>
       </c>
       <c r="B164" t="n">
         <v>78526</v>
@@ -17263,10 +17253,10 @@
         </is>
       </c>
       <c r="Q164" t="n">
-        <v>478265</v>
+        <v>478097</v>
       </c>
       <c r="R164" t="n">
-        <v>6827707</v>
+        <v>6827744</v>
       </c>
       <c r="S164" t="n">
         <v>10</v>
@@ -17325,10 +17315,10 @@
     </row>
     <row r="165">
       <c r="A165" t="n">
-        <v>120074939</v>
+        <v>120075121</v>
       </c>
       <c r="B165" t="n">
-        <v>79144</v>
+        <v>78526</v>
       </c>
       <c r="C165" t="inlineStr">
         <is>
@@ -17341,21 +17331,21 @@
         </is>
       </c>
       <c r="E165" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G165" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H165" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I165" t="inlineStr"/>
@@ -17365,10 +17355,10 @@
         </is>
       </c>
       <c r="Q165" t="n">
-        <v>478091</v>
+        <v>478232</v>
       </c>
       <c r="R165" t="n">
-        <v>6827838</v>
+        <v>6827659</v>
       </c>
       <c r="S165" t="n">
         <v>10</v>
@@ -17427,10 +17417,10 @@
     </row>
     <row r="166">
       <c r="A166" t="n">
-        <v>120075015</v>
+        <v>120075067</v>
       </c>
       <c r="B166" t="n">
-        <v>79607</v>
+        <v>78526</v>
       </c>
       <c r="C166" t="inlineStr">
         <is>
@@ -17443,21 +17433,21 @@
         </is>
       </c>
       <c r="E166" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G166" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H166" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I166" t="inlineStr"/>
@@ -17467,10 +17457,10 @@
         </is>
       </c>
       <c r="Q166" t="n">
-        <v>478114</v>
+        <v>478164</v>
       </c>
       <c r="R166" t="n">
-        <v>6827633</v>
+        <v>6827661</v>
       </c>
       <c r="S166" t="n">
         <v>10</v>
@@ -17529,10 +17519,10 @@
     </row>
     <row r="167">
       <c r="A167" t="n">
-        <v>120074961</v>
+        <v>120075223</v>
       </c>
       <c r="B167" t="n">
-        <v>90582</v>
+        <v>78171</v>
       </c>
       <c r="C167" t="inlineStr">
         <is>
@@ -17545,21 +17535,21 @@
         </is>
       </c>
       <c r="E167" t="n">
-        <v>5442</v>
+        <v>353</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G167" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H167" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I167" t="inlineStr"/>
@@ -17569,10 +17559,10 @@
         </is>
       </c>
       <c r="Q167" t="n">
-        <v>478230</v>
+        <v>478076</v>
       </c>
       <c r="R167" t="n">
-        <v>6827780</v>
+        <v>6827777</v>
       </c>
       <c r="S167" t="n">
         <v>10</v>
@@ -17631,10 +17621,10 @@
     </row>
     <row r="168">
       <c r="A168" t="n">
-        <v>120074999</v>
+        <v>120075042</v>
       </c>
       <c r="B168" t="n">
-        <v>78263</v>
+        <v>78262</v>
       </c>
       <c r="C168" t="inlineStr">
         <is>
@@ -17647,21 +17637,21 @@
         </is>
       </c>
       <c r="E168" t="n">
-        <v>228912</v>
+        <v>6446</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G168" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H168" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I168" t="inlineStr"/>
@@ -17671,10 +17661,10 @@
         </is>
       </c>
       <c r="Q168" t="n">
-        <v>478161</v>
+        <v>478074</v>
       </c>
       <c r="R168" t="n">
-        <v>6827592</v>
+        <v>6827775</v>
       </c>
       <c r="S168" t="n">
         <v>10</v>
@@ -17733,10 +17723,10 @@
     </row>
     <row r="169">
       <c r="A169" t="n">
-        <v>120075004</v>
+        <v>120074888</v>
       </c>
       <c r="B169" t="n">
-        <v>78263</v>
+        <v>79144</v>
       </c>
       <c r="C169" t="inlineStr">
         <is>
@@ -17749,21 +17739,21 @@
         </is>
       </c>
       <c r="E169" t="n">
-        <v>228912</v>
+        <v>6453</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G169" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H169" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I169" t="inlineStr"/>
@@ -17773,10 +17763,10 @@
         </is>
       </c>
       <c r="Q169" t="n">
-        <v>478212</v>
+        <v>478139</v>
       </c>
       <c r="R169" t="n">
-        <v>6827573</v>
+        <v>6827554</v>
       </c>
       <c r="S169" t="n">
         <v>10</v>
@@ -17835,10 +17825,10 @@
     </row>
     <row r="170">
       <c r="A170" t="n">
-        <v>120075165</v>
+        <v>120074942</v>
       </c>
       <c r="B170" t="n">
-        <v>78526</v>
+        <v>79144</v>
       </c>
       <c r="C170" t="inlineStr">
         <is>
@@ -17851,21 +17841,21 @@
         </is>
       </c>
       <c r="E170" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G170" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H170" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I170" t="inlineStr"/>
@@ -17875,10 +17865,10 @@
         </is>
       </c>
       <c r="Q170" t="n">
-        <v>478078</v>
+        <v>478065</v>
       </c>
       <c r="R170" t="n">
-        <v>6827834</v>
+        <v>6827842</v>
       </c>
       <c r="S170" t="n">
         <v>10</v>
@@ -17937,10 +17927,10 @@
     </row>
     <row r="171">
       <c r="A171" t="n">
-        <v>120075142</v>
+        <v>120074956</v>
       </c>
       <c r="B171" t="n">
-        <v>78526</v>
+        <v>57310</v>
       </c>
       <c r="C171" t="inlineStr">
         <is>
@@ -17953,34 +17943,39 @@
         </is>
       </c>
       <c r="E171" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G171" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H171" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I171" t="inlineStr"/>
+      <c r="M171" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P171" t="inlineStr">
         <is>
           <t>Hevoslamm, Dlr</t>
         </is>
       </c>
       <c r="Q171" t="n">
-        <v>478313</v>
+        <v>478278</v>
       </c>
       <c r="R171" t="n">
-        <v>6827798</v>
+        <v>6827832</v>
       </c>
       <c r="S171" t="n">
         <v>10</v>
@@ -18013,6 +18008,11 @@
       <c r="AA171" t="inlineStr">
         <is>
           <t>2024-09-27</t>
+        </is>
+      </c>
+      <c r="AC171" t="inlineStr">
+        <is>
+          <t>Färska ringhack (tall)</t>
         </is>
       </c>
       <c r="AD171" t="b">
@@ -18039,10 +18039,10 @@
     </row>
     <row r="172">
       <c r="A172" t="n">
-        <v>120075074</v>
+        <v>120074999</v>
       </c>
       <c r="B172" t="n">
-        <v>78526</v>
+        <v>78263</v>
       </c>
       <c r="C172" t="inlineStr">
         <is>
@@ -18055,21 +18055,21 @@
         </is>
       </c>
       <c r="E172" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G172" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H172" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I172" t="inlineStr"/>
@@ -18079,10 +18079,10 @@
         </is>
       </c>
       <c r="Q172" t="n">
-        <v>478138</v>
+        <v>478161</v>
       </c>
       <c r="R172" t="n">
-        <v>6827599</v>
+        <v>6827592</v>
       </c>
       <c r="S172" t="n">
         <v>10</v>
@@ -18141,10 +18141,10 @@
     </row>
     <row r="173">
       <c r="A173" t="n">
-        <v>120075236</v>
+        <v>120075008</v>
       </c>
       <c r="B173" t="n">
-        <v>78171</v>
+        <v>78263</v>
       </c>
       <c r="C173" t="inlineStr">
         <is>
@@ -18157,21 +18157,21 @@
         </is>
       </c>
       <c r="E173" t="n">
-        <v>353</v>
+        <v>228912</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G173" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H173" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I173" t="inlineStr"/>
@@ -18181,10 +18181,10 @@
         </is>
       </c>
       <c r="Q173" t="n">
-        <v>478062</v>
+        <v>478299</v>
       </c>
       <c r="R173" t="n">
-        <v>6827740</v>
+        <v>6827805</v>
       </c>
       <c r="S173" t="n">
         <v>10</v>
@@ -18243,10 +18243,10 @@
     </row>
     <row r="174">
       <c r="A174" t="n">
-        <v>120075203</v>
+        <v>120075163</v>
       </c>
       <c r="B174" t="n">
-        <v>78171</v>
+        <v>78526</v>
       </c>
       <c r="C174" t="inlineStr">
         <is>
@@ -18259,21 +18259,21 @@
         </is>
       </c>
       <c r="E174" t="n">
-        <v>353</v>
+        <v>6425</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G174" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H174" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I174" t="inlineStr"/>
@@ -18283,10 +18283,10 @@
         </is>
       </c>
       <c r="Q174" t="n">
-        <v>478125</v>
+        <v>478102</v>
       </c>
       <c r="R174" t="n">
-        <v>6827631</v>
+        <v>6827800</v>
       </c>
       <c r="S174" t="n">
         <v>10</v>
@@ -18345,10 +18345,10 @@
     </row>
     <row r="175">
       <c r="A175" t="n">
-        <v>120074907</v>
+        <v>120075095</v>
       </c>
       <c r="B175" t="n">
-        <v>79144</v>
+        <v>78526</v>
       </c>
       <c r="C175" t="inlineStr">
         <is>
@@ -18361,21 +18361,21 @@
         </is>
       </c>
       <c r="E175" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G175" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H175" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I175" t="inlineStr"/>
@@ -18385,10 +18385,10 @@
         </is>
       </c>
       <c r="Q175" t="n">
-        <v>478263</v>
+        <v>478219</v>
       </c>
       <c r="R175" t="n">
-        <v>6827838</v>
+        <v>6827572</v>
       </c>
       <c r="S175" t="n">
         <v>10</v>
@@ -18447,10 +18447,10 @@
     </row>
     <row r="176">
       <c r="A176" t="n">
-        <v>120074932</v>
+        <v>120075084</v>
       </c>
       <c r="B176" t="n">
-        <v>79144</v>
+        <v>78526</v>
       </c>
       <c r="C176" t="inlineStr">
         <is>
@@ -18463,21 +18463,21 @@
         </is>
       </c>
       <c r="E176" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G176" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H176" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I176" t="inlineStr"/>
@@ -18487,10 +18487,10 @@
         </is>
       </c>
       <c r="Q176" t="n">
-        <v>478250</v>
+        <v>478098</v>
       </c>
       <c r="R176" t="n">
-        <v>6827802</v>
+        <v>6827520</v>
       </c>
       <c r="S176" t="n">
         <v>10</v>
@@ -18549,10 +18549,10 @@
     </row>
     <row r="177">
       <c r="A177" t="n">
-        <v>120075232</v>
+        <v>120074907</v>
       </c>
       <c r="B177" t="n">
-        <v>78171</v>
+        <v>79144</v>
       </c>
       <c r="C177" t="inlineStr">
         <is>
@@ -18565,21 +18565,21 @@
         </is>
       </c>
       <c r="E177" t="n">
-        <v>353</v>
+        <v>6453</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G177" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H177" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I177" t="inlineStr"/>
@@ -18589,10 +18589,10 @@
         </is>
       </c>
       <c r="Q177" t="n">
-        <v>478051</v>
+        <v>478263</v>
       </c>
       <c r="R177" t="n">
-        <v>6827739</v>
+        <v>6827838</v>
       </c>
       <c r="S177" t="n">
         <v>10</v>
@@ -18651,10 +18651,10 @@
     </row>
     <row r="178">
       <c r="A178" t="n">
-        <v>120075234</v>
+        <v>120074927</v>
       </c>
       <c r="B178" t="n">
-        <v>78171</v>
+        <v>78560</v>
       </c>
       <c r="C178" t="inlineStr">
         <is>
@@ -18667,21 +18667,21 @@
         </is>
       </c>
       <c r="E178" t="n">
-        <v>353</v>
+        <v>185</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G178" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H178" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I178" t="inlineStr"/>
@@ -18691,10 +18691,10 @@
         </is>
       </c>
       <c r="Q178" t="n">
-        <v>478069</v>
+        <v>478073</v>
       </c>
       <c r="R178" t="n">
-        <v>6827741</v>
+        <v>6827836</v>
       </c>
       <c r="S178" t="n">
         <v>10</v>
@@ -18753,10 +18753,10 @@
     </row>
     <row r="179">
       <c r="A179" t="n">
-        <v>120075242</v>
+        <v>120075201</v>
       </c>
       <c r="B179" t="n">
-        <v>77910</v>
+        <v>78171</v>
       </c>
       <c r="C179" t="inlineStr">
         <is>
@@ -18769,21 +18769,21 @@
         </is>
       </c>
       <c r="E179" t="n">
-        <v>6437</v>
+        <v>353</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G179" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H179" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I179" t="inlineStr"/>
@@ -18793,10 +18793,10 @@
         </is>
       </c>
       <c r="Q179" t="n">
-        <v>478136</v>
+        <v>478182</v>
       </c>
       <c r="R179" t="n">
-        <v>6827556</v>
+        <v>6827728</v>
       </c>
       <c r="S179" t="n">
         <v>10</v>
@@ -18855,10 +18855,10 @@
     </row>
     <row r="180">
       <c r="A180" t="n">
-        <v>120075172</v>
+        <v>120074915</v>
       </c>
       <c r="B180" t="n">
-        <v>78526</v>
+        <v>78560</v>
       </c>
       <c r="C180" t="inlineStr">
         <is>
@@ -18871,21 +18871,21 @@
         </is>
       </c>
       <c r="E180" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G180" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H180" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I180" t="inlineStr"/>
@@ -18895,10 +18895,10 @@
         </is>
       </c>
       <c r="Q180" t="n">
-        <v>478055</v>
+        <v>478102</v>
       </c>
       <c r="R180" t="n">
-        <v>6827768</v>
+        <v>6827555</v>
       </c>
       <c r="S180" t="n">
         <v>10</v>
@@ -18957,10 +18957,10 @@
     </row>
     <row r="181">
       <c r="A181" t="n">
-        <v>120074931</v>
+        <v>120075207</v>
       </c>
       <c r="B181" t="n">
-        <v>79144</v>
+        <v>78171</v>
       </c>
       <c r="C181" t="inlineStr">
         <is>
@@ -18973,21 +18973,21 @@
         </is>
       </c>
       <c r="E181" t="n">
-        <v>6453</v>
+        <v>353</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G181" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H181" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I181" t="inlineStr"/>
@@ -18997,10 +18997,10 @@
         </is>
       </c>
       <c r="Q181" t="n">
-        <v>478261</v>
+        <v>478157</v>
       </c>
       <c r="R181" t="n">
-        <v>6827822</v>
+        <v>6827509</v>
       </c>
       <c r="S181" t="n">
         <v>10</v>

--- a/artfynd/A 32983-2023 artfynd.xlsx
+++ b/artfynd/A 32983-2023 artfynd.xlsx
@@ -2103,10 +2103,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>120075009</v>
+        <v>120075039</v>
       </c>
       <c r="B16" t="n">
-        <v>78263</v>
+        <v>78262</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2119,21 +2119,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>228912</v>
+        <v>6446</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2143,10 +2143,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>478151</v>
+        <v>478238</v>
       </c>
       <c r="R16" t="n">
-        <v>6827745</v>
+        <v>6827752</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2205,10 +2205,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>120075004</v>
+        <v>120075038</v>
       </c>
       <c r="B17" t="n">
-        <v>78263</v>
+        <v>78262</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2221,21 +2221,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>228912</v>
+        <v>6446</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2245,10 +2245,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>478212</v>
+        <v>478261</v>
       </c>
       <c r="R17" t="n">
-        <v>6827573</v>
+        <v>6827731</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2307,10 +2307,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>120075226</v>
+        <v>120075019</v>
       </c>
       <c r="B18" t="n">
-        <v>78171</v>
+        <v>79607</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2323,21 +2323,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>353</v>
+        <v>6458</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2347,10 +2347,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>478098</v>
+        <v>478227</v>
       </c>
       <c r="R18" t="n">
-        <v>6827815</v>
+        <v>6827655</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2409,10 +2409,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>120074928</v>
+        <v>120075009</v>
       </c>
       <c r="B19" t="n">
-        <v>78560</v>
+        <v>78263</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2425,21 +2425,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>185</v>
+        <v>228912</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2449,10 +2449,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>478059</v>
+        <v>478151</v>
       </c>
       <c r="R19" t="n">
-        <v>6827740</v>
+        <v>6827745</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2511,10 +2511,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>120074914</v>
+        <v>120075004</v>
       </c>
       <c r="B20" t="n">
-        <v>78560</v>
+        <v>78263</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2527,21 +2527,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>185</v>
+        <v>228912</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2551,10 +2551,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>478169</v>
+        <v>478212</v>
       </c>
       <c r="R20" t="n">
-        <v>6827680</v>
+        <v>6827573</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2613,10 +2613,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>120075085</v>
+        <v>120075226</v>
       </c>
       <c r="B21" t="n">
-        <v>78526</v>
+        <v>78171</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2629,21 +2629,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6425</v>
+        <v>353</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2653,10 +2653,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>478094</v>
+        <v>478098</v>
       </c>
       <c r="R21" t="n">
-        <v>6827504</v>
+        <v>6827815</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2715,10 +2715,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>120075161</v>
+        <v>120074928</v>
       </c>
       <c r="B22" t="n">
-        <v>78526</v>
+        <v>78560</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2731,21 +2731,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2755,10 +2755,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>478082</v>
+        <v>478059</v>
       </c>
       <c r="R22" t="n">
-        <v>6827766</v>
+        <v>6827740</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2817,10 +2817,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>120075039</v>
+        <v>120074914</v>
       </c>
       <c r="B23" t="n">
-        <v>78262</v>
+        <v>78560</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -2833,21 +2833,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6446</v>
+        <v>185</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2857,10 +2857,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>478238</v>
+        <v>478169</v>
       </c>
       <c r="R23" t="n">
-        <v>6827752</v>
+        <v>6827680</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2919,10 +2919,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>120075038</v>
+        <v>120075085</v>
       </c>
       <c r="B24" t="n">
-        <v>78262</v>
+        <v>78526</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -2935,21 +2935,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -2959,10 +2959,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>478261</v>
+        <v>478094</v>
       </c>
       <c r="R24" t="n">
-        <v>6827731</v>
+        <v>6827504</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3021,10 +3021,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>120075019</v>
+        <v>120075161</v>
       </c>
       <c r="B25" t="n">
-        <v>79607</v>
+        <v>78526</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3037,21 +3037,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3061,10 +3061,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>478227</v>
+        <v>478082</v>
       </c>
       <c r="R25" t="n">
-        <v>6827655</v>
+        <v>6827766</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3123,10 +3123,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>120075197</v>
+        <v>120074929</v>
       </c>
       <c r="B26" t="n">
-        <v>91840</v>
+        <v>78560</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3135,47 +3135,38 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>4364</v>
+        <v>185</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J26" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
           <t>Hevoslamm, Dlr</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>478077</v>
+        <v>478045</v>
       </c>
       <c r="R26" t="n">
-        <v>6827805</v>
+        <v>6827724</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3234,10 +3225,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>120075087</v>
+        <v>120075227</v>
       </c>
       <c r="B27" t="n">
-        <v>78526</v>
+        <v>78171</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3250,21 +3241,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6425</v>
+        <v>353</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3274,10 +3265,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>478145</v>
+        <v>478088</v>
       </c>
       <c r="R27" t="n">
-        <v>6827485</v>
+        <v>6827834</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3336,10 +3327,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>120075134</v>
+        <v>120075202</v>
       </c>
       <c r="B28" t="n">
-        <v>78526</v>
+        <v>78171</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3352,21 +3343,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6425</v>
+        <v>353</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3376,10 +3367,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>478266</v>
+        <v>478218</v>
       </c>
       <c r="R28" t="n">
-        <v>6827765</v>
+        <v>6827721</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3438,10 +3429,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>120074905</v>
+        <v>120075197</v>
       </c>
       <c r="B29" t="n">
-        <v>79144</v>
+        <v>91840</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3450,38 +3441,47 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6453</v>
+        <v>4364</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
-        </is>
-      </c>
-      <c r="I29" t="inlineStr"/>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="P29" t="inlineStr">
         <is>
           <t>Hevoslamm, Dlr</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>478285</v>
+        <v>478077</v>
       </c>
       <c r="R29" t="n">
-        <v>6827770</v>
+        <v>6827805</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3540,7 +3540,7 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>120074891</v>
+        <v>120074905</v>
       </c>
       <c r="B30" t="n">
         <v>79144</v>
@@ -3580,10 +3580,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>478212</v>
+        <v>478285</v>
       </c>
       <c r="R30" t="n">
-        <v>6827573</v>
+        <v>6827770</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3642,10 +3642,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>120075000</v>
+        <v>120074891</v>
       </c>
       <c r="B31" t="n">
-        <v>78263</v>
+        <v>79144</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3658,21 +3658,21 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>228912</v>
+        <v>6453</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3682,10 +3682,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>478121</v>
+        <v>478212</v>
       </c>
       <c r="R31" t="n">
-        <v>6827607</v>
+        <v>6827573</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3744,10 +3744,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>120074929</v>
+        <v>120075000</v>
       </c>
       <c r="B32" t="n">
-        <v>78560</v>
+        <v>78263</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -3760,21 +3760,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>185</v>
+        <v>228912</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3784,10 +3784,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>478045</v>
+        <v>478121</v>
       </c>
       <c r="R32" t="n">
-        <v>6827724</v>
+        <v>6827607</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3846,10 +3846,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>120075227</v>
+        <v>120075087</v>
       </c>
       <c r="B33" t="n">
-        <v>78171</v>
+        <v>78526</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -3862,21 +3862,21 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>353</v>
+        <v>6425</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -3886,10 +3886,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>478088</v>
+        <v>478145</v>
       </c>
       <c r="R33" t="n">
-        <v>6827834</v>
+        <v>6827485</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -3948,10 +3948,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>120075202</v>
+        <v>120075134</v>
       </c>
       <c r="B34" t="n">
-        <v>78171</v>
+        <v>78526</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -3964,21 +3964,21 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>353</v>
+        <v>6425</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -3988,10 +3988,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>478218</v>
+        <v>478266</v>
       </c>
       <c r="R34" t="n">
-        <v>6827721</v>
+        <v>6827765</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4050,10 +4050,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>120075162</v>
+        <v>120074952</v>
       </c>
       <c r="B35" t="n">
-        <v>78526</v>
+        <v>79115</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4066,21 +4066,21 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6425</v>
+        <v>229821</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4090,10 +4090,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>478080</v>
+        <v>478120</v>
       </c>
       <c r="R35" t="n">
-        <v>6827808</v>
+        <v>6827605</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4152,10 +4152,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>120075239</v>
+        <v>120075162</v>
       </c>
       <c r="B36" t="n">
-        <v>77458</v>
+        <v>78526</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4168,21 +4168,21 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6487</v>
+        <v>6425</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Blågrå svartspik</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Chaenothecopsis fennica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Laurila) Tibell</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4192,10 +4192,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>478137</v>
+        <v>478080</v>
       </c>
       <c r="R36" t="n">
-        <v>6827554</v>
+        <v>6827808</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4254,10 +4254,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>120075048</v>
+        <v>120075239</v>
       </c>
       <c r="B37" t="n">
-        <v>56514</v>
+        <v>77458</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4270,39 +4270,34 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>102612</v>
+        <v>6487</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Blågrå svartspik</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Chaenothecopsis fennica</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Laurila) Tibell</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
-      <c r="M37" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
       <c r="P37" t="inlineStr">
         <is>
           <t>Hevoslamm, Dlr</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>478070</v>
+        <v>478137</v>
       </c>
       <c r="R37" t="n">
-        <v>6827723</v>
+        <v>6827554</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4361,10 +4356,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>120074952</v>
+        <v>120075048</v>
       </c>
       <c r="B38" t="n">
-        <v>79115</v>
+        <v>56514</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4377,34 +4372,39 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>229821</v>
+        <v>102612</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
+      <c r="M38" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="P38" t="inlineStr">
         <is>
           <t>Hevoslamm, Dlr</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>478120</v>
+        <v>478070</v>
       </c>
       <c r="R38" t="n">
-        <v>6827605</v>
+        <v>6827723</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -8135,10 +8135,10 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>120075176</v>
+        <v>120075027</v>
       </c>
       <c r="B75" t="n">
-        <v>78526</v>
+        <v>78262</v>
       </c>
       <c r="C75" t="inlineStr">
         <is>
@@ -8151,21 +8151,21 @@
         </is>
       </c>
       <c r="E75" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
@@ -8175,10 +8175,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>478066</v>
+        <v>478144</v>
       </c>
       <c r="R75" t="n">
-        <v>6827732</v>
+        <v>6827593</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -8237,7 +8237,7 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>120075089</v>
+        <v>120075176</v>
       </c>
       <c r="B76" t="n">
         <v>78526</v>
@@ -8277,10 +8277,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>478153</v>
+        <v>478066</v>
       </c>
       <c r="R76" t="n">
-        <v>6827517</v>
+        <v>6827732</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -8339,7 +8339,7 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>120075138</v>
+        <v>120075089</v>
       </c>
       <c r="B77" t="n">
         <v>78526</v>
@@ -8379,10 +8379,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>478294</v>
+        <v>478153</v>
       </c>
       <c r="R77" t="n">
-        <v>6827781</v>
+        <v>6827517</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -8441,7 +8441,7 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>120075120</v>
+        <v>120075138</v>
       </c>
       <c r="B78" t="n">
         <v>78526</v>
@@ -8481,10 +8481,10 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>478223</v>
+        <v>478294</v>
       </c>
       <c r="R78" t="n">
-        <v>6827657</v>
+        <v>6827781</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -8543,7 +8543,7 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>120075140</v>
+        <v>120075120</v>
       </c>
       <c r="B79" t="n">
         <v>78526</v>
@@ -8583,10 +8583,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>478310</v>
+        <v>478223</v>
       </c>
       <c r="R79" t="n">
-        <v>6827797</v>
+        <v>6827657</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -8645,7 +8645,7 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>120075073</v>
+        <v>120075140</v>
       </c>
       <c r="B80" t="n">
         <v>78526</v>
@@ -8685,10 +8685,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>478116</v>
+        <v>478310</v>
       </c>
       <c r="R80" t="n">
-        <v>6827617</v>
+        <v>6827797</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -8747,7 +8747,7 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>120075097</v>
+        <v>120075073</v>
       </c>
       <c r="B81" t="n">
         <v>78526</v>
@@ -8787,10 +8787,10 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>478248</v>
+        <v>478116</v>
       </c>
       <c r="R81" t="n">
-        <v>6827593</v>
+        <v>6827617</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -8849,7 +8849,7 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>120075129</v>
+        <v>120075097</v>
       </c>
       <c r="B82" t="n">
         <v>78526</v>
@@ -8889,10 +8889,10 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>478265</v>
+        <v>478248</v>
       </c>
       <c r="R82" t="n">
-        <v>6827707</v>
+        <v>6827593</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -8951,7 +8951,7 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>120075062</v>
+        <v>120075129</v>
       </c>
       <c r="B83" t="n">
         <v>78526</v>
@@ -8991,10 +8991,10 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>478221</v>
+        <v>478265</v>
       </c>
       <c r="R83" t="n">
-        <v>6827719</v>
+        <v>6827707</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -9053,10 +9053,10 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>120075027</v>
+        <v>120075062</v>
       </c>
       <c r="B84" t="n">
-        <v>78262</v>
+        <v>78526</v>
       </c>
       <c r="C84" t="inlineStr">
         <is>
@@ -9069,21 +9069,21 @@
         </is>
       </c>
       <c r="E84" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
@@ -9093,10 +9093,10 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>478144</v>
+        <v>478221</v>
       </c>
       <c r="R84" t="n">
-        <v>6827593</v>
+        <v>6827719</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -11501,10 +11501,10 @@
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>120075216</v>
+        <v>120074885</v>
       </c>
       <c r="B108" t="n">
-        <v>78171</v>
+        <v>79144</v>
       </c>
       <c r="C108" t="inlineStr">
         <is>
@@ -11517,21 +11517,21 @@
         </is>
       </c>
       <c r="E108" t="n">
-        <v>353</v>
+        <v>6453</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I108" t="inlineStr"/>
@@ -11541,10 +11541,10 @@
         </is>
       </c>
       <c r="Q108" t="n">
-        <v>478294</v>
+        <v>478115</v>
       </c>
       <c r="R108" t="n">
-        <v>6827790</v>
+        <v>6827614</v>
       </c>
       <c r="S108" t="n">
         <v>10</v>
@@ -11603,10 +11603,10 @@
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>120074922</v>
+        <v>120075035</v>
       </c>
       <c r="B109" t="n">
-        <v>78560</v>
+        <v>78262</v>
       </c>
       <c r="C109" t="inlineStr">
         <is>
@@ -11619,21 +11619,21 @@
         </is>
       </c>
       <c r="E109" t="n">
-        <v>185</v>
+        <v>6446</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I109" t="inlineStr"/>
@@ -11643,10 +11643,10 @@
         </is>
       </c>
       <c r="Q109" t="n">
-        <v>478103</v>
+        <v>478273</v>
       </c>
       <c r="R109" t="n">
-        <v>6827718</v>
+        <v>6827711</v>
       </c>
       <c r="S109" t="n">
         <v>10</v>
@@ -11705,10 +11705,10 @@
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>120075196</v>
+        <v>120075040</v>
       </c>
       <c r="B110" t="n">
-        <v>78526</v>
+        <v>78262</v>
       </c>
       <c r="C110" t="inlineStr">
         <is>
@@ -11721,21 +11721,21 @@
         </is>
       </c>
       <c r="E110" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I110" t="inlineStr"/>
@@ -11745,10 +11745,10 @@
         </is>
       </c>
       <c r="Q110" t="n">
-        <v>478288</v>
+        <v>478250</v>
       </c>
       <c r="R110" t="n">
-        <v>6827682</v>
+        <v>6827802</v>
       </c>
       <c r="S110" t="n">
         <v>10</v>
@@ -11807,10 +11807,10 @@
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>120075132</v>
+        <v>120074932</v>
       </c>
       <c r="B111" t="n">
-        <v>78526</v>
+        <v>79144</v>
       </c>
       <c r="C111" t="inlineStr">
         <is>
@@ -11823,21 +11823,21 @@
         </is>
       </c>
       <c r="E111" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I111" t="inlineStr"/>
@@ -11847,10 +11847,10 @@
         </is>
       </c>
       <c r="Q111" t="n">
-        <v>478240</v>
+        <v>478250</v>
       </c>
       <c r="R111" t="n">
-        <v>6827754</v>
+        <v>6827802</v>
       </c>
       <c r="S111" t="n">
         <v>10</v>
@@ -11909,10 +11909,10 @@
     </row>
     <row r="112">
       <c r="A112" t="n">
-        <v>120075173</v>
+        <v>120074943</v>
       </c>
       <c r="B112" t="n">
-        <v>78526</v>
+        <v>79144</v>
       </c>
       <c r="C112" t="inlineStr">
         <is>
@@ -11925,21 +11925,21 @@
         </is>
       </c>
       <c r="E112" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I112" t="inlineStr"/>
@@ -11949,10 +11949,10 @@
         </is>
       </c>
       <c r="Q112" t="n">
-        <v>478052</v>
+        <v>478073</v>
       </c>
       <c r="R112" t="n">
-        <v>6827754</v>
+        <v>6827827</v>
       </c>
       <c r="S112" t="n">
         <v>10</v>
@@ -12011,10 +12011,10 @@
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>120075065</v>
+        <v>120074998</v>
       </c>
       <c r="B113" t="n">
-        <v>78526</v>
+        <v>78263</v>
       </c>
       <c r="C113" t="inlineStr">
         <is>
@@ -12027,21 +12027,21 @@
         </is>
       </c>
       <c r="E113" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I113" t="inlineStr"/>
@@ -12051,10 +12051,10 @@
         </is>
       </c>
       <c r="Q113" t="n">
-        <v>478169</v>
+        <v>478172</v>
       </c>
       <c r="R113" t="n">
-        <v>6827679</v>
+        <v>6827640</v>
       </c>
       <c r="S113" t="n">
         <v>10</v>
@@ -12113,7 +12113,7 @@
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>120075094</v>
+        <v>120075196</v>
       </c>
       <c r="B114" t="n">
         <v>78526</v>
@@ -12153,10 +12153,10 @@
         </is>
       </c>
       <c r="Q114" t="n">
-        <v>478205</v>
+        <v>478288</v>
       </c>
       <c r="R114" t="n">
-        <v>6827556</v>
+        <v>6827682</v>
       </c>
       <c r="S114" t="n">
         <v>10</v>
@@ -12215,7 +12215,7 @@
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>120075177</v>
+        <v>120075132</v>
       </c>
       <c r="B115" t="n">
         <v>78526</v>
@@ -12255,10 +12255,10 @@
         </is>
       </c>
       <c r="Q115" t="n">
-        <v>478075</v>
+        <v>478240</v>
       </c>
       <c r="R115" t="n">
-        <v>6827717</v>
+        <v>6827754</v>
       </c>
       <c r="S115" t="n">
         <v>10</v>
@@ -12317,7 +12317,7 @@
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>120075083</v>
+        <v>120075173</v>
       </c>
       <c r="B116" t="n">
         <v>78526</v>
@@ -12357,10 +12357,10 @@
         </is>
       </c>
       <c r="Q116" t="n">
-        <v>478097</v>
+        <v>478052</v>
       </c>
       <c r="R116" t="n">
-        <v>6827527</v>
+        <v>6827754</v>
       </c>
       <c r="S116" t="n">
         <v>10</v>
@@ -12419,7 +12419,7 @@
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>120075144</v>
+        <v>120075065</v>
       </c>
       <c r="B117" t="n">
         <v>78526</v>
@@ -12459,10 +12459,10 @@
         </is>
       </c>
       <c r="Q117" t="n">
-        <v>478261</v>
+        <v>478169</v>
       </c>
       <c r="R117" t="n">
-        <v>6827822</v>
+        <v>6827679</v>
       </c>
       <c r="S117" t="n">
         <v>10</v>
@@ -12521,7 +12521,7 @@
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>120075068</v>
+        <v>120075094</v>
       </c>
       <c r="B118" t="n">
         <v>78526</v>
@@ -12561,10 +12561,10 @@
         </is>
       </c>
       <c r="Q118" t="n">
-        <v>478174</v>
+        <v>478205</v>
       </c>
       <c r="R118" t="n">
-        <v>6827656</v>
+        <v>6827556</v>
       </c>
       <c r="S118" t="n">
         <v>10</v>
@@ -12623,10 +12623,10 @@
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>120074885</v>
+        <v>120075177</v>
       </c>
       <c r="B119" t="n">
-        <v>79144</v>
+        <v>78526</v>
       </c>
       <c r="C119" t="inlineStr">
         <is>
@@ -12639,21 +12639,21 @@
         </is>
       </c>
       <c r="E119" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I119" t="inlineStr"/>
@@ -12663,10 +12663,10 @@
         </is>
       </c>
       <c r="Q119" t="n">
-        <v>478115</v>
+        <v>478075</v>
       </c>
       <c r="R119" t="n">
-        <v>6827614</v>
+        <v>6827717</v>
       </c>
       <c r="S119" t="n">
         <v>10</v>
@@ -12725,10 +12725,10 @@
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>120075040</v>
+        <v>120075083</v>
       </c>
       <c r="B120" t="n">
-        <v>78262</v>
+        <v>78526</v>
       </c>
       <c r="C120" t="inlineStr">
         <is>
@@ -12741,21 +12741,21 @@
         </is>
       </c>
       <c r="E120" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I120" t="inlineStr"/>
@@ -12765,10 +12765,10 @@
         </is>
       </c>
       <c r="Q120" t="n">
-        <v>478250</v>
+        <v>478097</v>
       </c>
       <c r="R120" t="n">
-        <v>6827802</v>
+        <v>6827527</v>
       </c>
       <c r="S120" t="n">
         <v>10</v>
@@ -12827,10 +12827,10 @@
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>120075035</v>
+        <v>120075144</v>
       </c>
       <c r="B121" t="n">
-        <v>78262</v>
+        <v>78526</v>
       </c>
       <c r="C121" t="inlineStr">
         <is>
@@ -12843,21 +12843,21 @@
         </is>
       </c>
       <c r="E121" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I121" t="inlineStr"/>
@@ -12867,10 +12867,10 @@
         </is>
       </c>
       <c r="Q121" t="n">
-        <v>478273</v>
+        <v>478261</v>
       </c>
       <c r="R121" t="n">
-        <v>6827711</v>
+        <v>6827822</v>
       </c>
       <c r="S121" t="n">
         <v>10</v>
@@ -12929,10 +12929,10 @@
     </row>
     <row r="122">
       <c r="A122" t="n">
-        <v>120074932</v>
+        <v>120075068</v>
       </c>
       <c r="B122" t="n">
-        <v>79144</v>
+        <v>78526</v>
       </c>
       <c r="C122" t="inlineStr">
         <is>
@@ -12945,21 +12945,21 @@
         </is>
       </c>
       <c r="E122" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I122" t="inlineStr"/>
@@ -12969,10 +12969,10 @@
         </is>
       </c>
       <c r="Q122" t="n">
-        <v>478250</v>
+        <v>478174</v>
       </c>
       <c r="R122" t="n">
-        <v>6827802</v>
+        <v>6827656</v>
       </c>
       <c r="S122" t="n">
         <v>10</v>
@@ -13031,10 +13031,10 @@
     </row>
     <row r="123">
       <c r="A123" t="n">
-        <v>120074943</v>
+        <v>120075216</v>
       </c>
       <c r="B123" t="n">
-        <v>79144</v>
+        <v>78171</v>
       </c>
       <c r="C123" t="inlineStr">
         <is>
@@ -13047,21 +13047,21 @@
         </is>
       </c>
       <c r="E123" t="n">
-        <v>6453</v>
+        <v>353</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I123" t="inlineStr"/>
@@ -13071,10 +13071,10 @@
         </is>
       </c>
       <c r="Q123" t="n">
-        <v>478073</v>
+        <v>478294</v>
       </c>
       <c r="R123" t="n">
-        <v>6827827</v>
+        <v>6827790</v>
       </c>
       <c r="S123" t="n">
         <v>10</v>
@@ -13133,10 +13133,10 @@
     </row>
     <row r="124">
       <c r="A124" t="n">
-        <v>120074998</v>
+        <v>120074922</v>
       </c>
       <c r="B124" t="n">
-        <v>78263</v>
+        <v>78560</v>
       </c>
       <c r="C124" t="inlineStr">
         <is>
@@ -13149,21 +13149,21 @@
         </is>
       </c>
       <c r="E124" t="n">
-        <v>228912</v>
+        <v>185</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I124" t="inlineStr"/>
@@ -13173,10 +13173,10 @@
         </is>
       </c>
       <c r="Q124" t="n">
-        <v>478172</v>
+        <v>478103</v>
       </c>
       <c r="R124" t="n">
-        <v>6827640</v>
+        <v>6827718</v>
       </c>
       <c r="S124" t="n">
         <v>10</v>
@@ -13541,10 +13541,10 @@
     </row>
     <row r="128">
       <c r="A128" t="n">
-        <v>120075232</v>
+        <v>120075016</v>
       </c>
       <c r="B128" t="n">
-        <v>78171</v>
+        <v>79607</v>
       </c>
       <c r="C128" t="inlineStr">
         <is>
@@ -13557,21 +13557,21 @@
         </is>
       </c>
       <c r="E128" t="n">
-        <v>353</v>
+        <v>6458</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H128" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I128" t="inlineStr"/>
@@ -13581,10 +13581,10 @@
         </is>
       </c>
       <c r="Q128" t="n">
-        <v>478051</v>
+        <v>478096</v>
       </c>
       <c r="R128" t="n">
-        <v>6827739</v>
+        <v>6827549</v>
       </c>
       <c r="S128" t="n">
         <v>10</v>
@@ -13643,10 +13643,10 @@
     </row>
     <row r="129">
       <c r="A129" t="n">
-        <v>120075225</v>
+        <v>120074948</v>
       </c>
       <c r="B129" t="n">
-        <v>78171</v>
+        <v>79144</v>
       </c>
       <c r="C129" t="inlineStr">
         <is>
@@ -13659,21 +13659,21 @@
         </is>
       </c>
       <c r="E129" t="n">
-        <v>353</v>
+        <v>6453</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H129" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I129" t="inlineStr"/>
@@ -13683,10 +13683,10 @@
         </is>
       </c>
       <c r="Q129" t="n">
-        <v>478075</v>
+        <v>478070</v>
       </c>
       <c r="R129" t="n">
-        <v>6827798</v>
+        <v>6827723</v>
       </c>
       <c r="S129" t="n">
         <v>10</v>
@@ -13745,10 +13745,10 @@
     </row>
     <row r="130">
       <c r="A130" t="n">
-        <v>120075205</v>
+        <v>120074947</v>
       </c>
       <c r="B130" t="n">
-        <v>78171</v>
+        <v>79144</v>
       </c>
       <c r="C130" t="inlineStr">
         <is>
@@ -13761,21 +13761,21 @@
         </is>
       </c>
       <c r="E130" t="n">
-        <v>353</v>
+        <v>6453</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H130" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I130" t="inlineStr"/>
@@ -13785,10 +13785,10 @@
         </is>
       </c>
       <c r="Q130" t="n">
-        <v>478117</v>
+        <v>478061</v>
       </c>
       <c r="R130" t="n">
-        <v>6827612</v>
+        <v>6827751</v>
       </c>
       <c r="S130" t="n">
         <v>10</v>
@@ -13847,10 +13847,10 @@
     </row>
     <row r="131">
       <c r="A131" t="n">
-        <v>120075016</v>
+        <v>120074944</v>
       </c>
       <c r="B131" t="n">
-        <v>79607</v>
+        <v>79144</v>
       </c>
       <c r="C131" t="inlineStr">
         <is>
@@ -13863,21 +13863,21 @@
         </is>
       </c>
       <c r="E131" t="n">
-        <v>6458</v>
+        <v>6453</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H131" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I131" t="inlineStr"/>
@@ -13887,10 +13887,10 @@
         </is>
       </c>
       <c r="Q131" t="n">
-        <v>478096</v>
+        <v>478056</v>
       </c>
       <c r="R131" t="n">
-        <v>6827549</v>
+        <v>6827785</v>
       </c>
       <c r="S131" t="n">
         <v>10</v>
@@ -13949,10 +13949,10 @@
     </row>
     <row r="132">
       <c r="A132" t="n">
-        <v>120074948</v>
+        <v>120075044</v>
       </c>
       <c r="B132" t="n">
-        <v>79144</v>
+        <v>78262</v>
       </c>
       <c r="C132" t="inlineStr">
         <is>
@@ -13965,21 +13965,21 @@
         </is>
       </c>
       <c r="E132" t="n">
-        <v>6453</v>
+        <v>6446</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H132" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I132" t="inlineStr"/>
@@ -13989,10 +13989,10 @@
         </is>
       </c>
       <c r="Q132" t="n">
-        <v>478070</v>
+        <v>478060</v>
       </c>
       <c r="R132" t="n">
-        <v>6827723</v>
+        <v>6827770</v>
       </c>
       <c r="S132" t="n">
         <v>10</v>
@@ -14051,7 +14051,7 @@
     </row>
     <row r="133">
       <c r="A133" t="n">
-        <v>120074947</v>
+        <v>120074941</v>
       </c>
       <c r="B133" t="n">
         <v>79144</v>
@@ -14091,10 +14091,10 @@
         </is>
       </c>
       <c r="Q133" t="n">
-        <v>478061</v>
+        <v>478069</v>
       </c>
       <c r="R133" t="n">
-        <v>6827751</v>
+        <v>6827854</v>
       </c>
       <c r="S133" t="n">
         <v>10</v>
@@ -14153,7 +14153,7 @@
     </row>
     <row r="134">
       <c r="A134" t="n">
-        <v>120074944</v>
+        <v>120074935</v>
       </c>
       <c r="B134" t="n">
         <v>79144</v>
@@ -14193,10 +14193,10 @@
         </is>
       </c>
       <c r="Q134" t="n">
-        <v>478056</v>
+        <v>478150</v>
       </c>
       <c r="R134" t="n">
-        <v>6827785</v>
+        <v>6827745</v>
       </c>
       <c r="S134" t="n">
         <v>10</v>
@@ -14255,10 +14255,10 @@
     </row>
     <row r="135">
       <c r="A135" t="n">
-        <v>120075044</v>
+        <v>120074945</v>
       </c>
       <c r="B135" t="n">
-        <v>78262</v>
+        <v>79144</v>
       </c>
       <c r="C135" t="inlineStr">
         <is>
@@ -14271,21 +14271,21 @@
         </is>
       </c>
       <c r="E135" t="n">
-        <v>6446</v>
+        <v>6453</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H135" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I135" t="inlineStr"/>
@@ -14295,7 +14295,7 @@
         </is>
       </c>
       <c r="Q135" t="n">
-        <v>478060</v>
+        <v>478061</v>
       </c>
       <c r="R135" t="n">
         <v>6827770</v>
@@ -14357,10 +14357,10 @@
     </row>
     <row r="136">
       <c r="A136" t="n">
-        <v>120074941</v>
+        <v>120075047</v>
       </c>
       <c r="B136" t="n">
-        <v>79144</v>
+        <v>78262</v>
       </c>
       <c r="C136" t="inlineStr">
         <is>
@@ -14373,21 +14373,21 @@
         </is>
       </c>
       <c r="E136" t="n">
-        <v>6453</v>
+        <v>6446</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H136" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I136" t="inlineStr"/>
@@ -14397,10 +14397,10 @@
         </is>
       </c>
       <c r="Q136" t="n">
-        <v>478069</v>
+        <v>478212</v>
       </c>
       <c r="R136" t="n">
-        <v>6827854</v>
+        <v>6827573</v>
       </c>
       <c r="S136" t="n">
         <v>10</v>
@@ -14459,10 +14459,10 @@
     </row>
     <row r="137">
       <c r="A137" t="n">
-        <v>120074935</v>
+        <v>120075232</v>
       </c>
       <c r="B137" t="n">
-        <v>79144</v>
+        <v>78171</v>
       </c>
       <c r="C137" t="inlineStr">
         <is>
@@ -14475,21 +14475,21 @@
         </is>
       </c>
       <c r="E137" t="n">
-        <v>6453</v>
+        <v>353</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H137" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I137" t="inlineStr"/>
@@ -14499,10 +14499,10 @@
         </is>
       </c>
       <c r="Q137" t="n">
-        <v>478150</v>
+        <v>478051</v>
       </c>
       <c r="R137" t="n">
-        <v>6827745</v>
+        <v>6827739</v>
       </c>
       <c r="S137" t="n">
         <v>10</v>
@@ -14561,10 +14561,10 @@
     </row>
     <row r="138">
       <c r="A138" t="n">
-        <v>120074945</v>
+        <v>120075225</v>
       </c>
       <c r="B138" t="n">
-        <v>79144</v>
+        <v>78171</v>
       </c>
       <c r="C138" t="inlineStr">
         <is>
@@ -14577,21 +14577,21 @@
         </is>
       </c>
       <c r="E138" t="n">
-        <v>6453</v>
+        <v>353</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H138" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I138" t="inlineStr"/>
@@ -14601,10 +14601,10 @@
         </is>
       </c>
       <c r="Q138" t="n">
-        <v>478061</v>
+        <v>478075</v>
       </c>
       <c r="R138" t="n">
-        <v>6827770</v>
+        <v>6827798</v>
       </c>
       <c r="S138" t="n">
         <v>10</v>
@@ -14663,10 +14663,10 @@
     </row>
     <row r="139">
       <c r="A139" t="n">
-        <v>120075047</v>
+        <v>120075205</v>
       </c>
       <c r="B139" t="n">
-        <v>78262</v>
+        <v>78171</v>
       </c>
       <c r="C139" t="inlineStr">
         <is>
@@ -14679,21 +14679,21 @@
         </is>
       </c>
       <c r="E139" t="n">
-        <v>6446</v>
+        <v>353</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H139" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I139" t="inlineStr"/>
@@ -14703,10 +14703,10 @@
         </is>
       </c>
       <c r="Q139" t="n">
-        <v>478212</v>
+        <v>478117</v>
       </c>
       <c r="R139" t="n">
-        <v>6827573</v>
+        <v>6827612</v>
       </c>
       <c r="S139" t="n">
         <v>10</v>
@@ -16907,10 +16907,10 @@
     </row>
     <row r="161">
       <c r="A161" t="n">
-        <v>120075215</v>
+        <v>120074999</v>
       </c>
       <c r="B161" t="n">
-        <v>78171</v>
+        <v>78263</v>
       </c>
       <c r="C161" t="inlineStr">
         <is>
@@ -16923,21 +16923,21 @@
         </is>
       </c>
       <c r="E161" t="n">
-        <v>353</v>
+        <v>228912</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G161" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H161" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I161" t="inlineStr"/>
@@ -16947,10 +16947,10 @@
         </is>
       </c>
       <c r="Q161" t="n">
-        <v>478239</v>
+        <v>478161</v>
       </c>
       <c r="R161" t="n">
-        <v>6827752</v>
+        <v>6827592</v>
       </c>
       <c r="S161" t="n">
         <v>10</v>
@@ -17009,10 +17009,10 @@
     </row>
     <row r="162">
       <c r="A162" t="n">
-        <v>120075206</v>
+        <v>120075008</v>
       </c>
       <c r="B162" t="n">
-        <v>78171</v>
+        <v>78263</v>
       </c>
       <c r="C162" t="inlineStr">
         <is>
@@ -17025,21 +17025,21 @@
         </is>
       </c>
       <c r="E162" t="n">
-        <v>353</v>
+        <v>228912</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G162" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H162" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I162" t="inlineStr"/>
@@ -17049,10 +17049,10 @@
         </is>
       </c>
       <c r="Q162" t="n">
-        <v>478125</v>
+        <v>478299</v>
       </c>
       <c r="R162" t="n">
-        <v>6827604</v>
+        <v>6827805</v>
       </c>
       <c r="S162" t="n">
         <v>10</v>
@@ -17111,10 +17111,10 @@
     </row>
     <row r="163">
       <c r="A163" t="n">
-        <v>120075090</v>
+        <v>120075215</v>
       </c>
       <c r="B163" t="n">
-        <v>78526</v>
+        <v>78171</v>
       </c>
       <c r="C163" t="inlineStr">
         <is>
@@ -17127,21 +17127,21 @@
         </is>
       </c>
       <c r="E163" t="n">
-        <v>6425</v>
+        <v>353</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G163" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H163" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I163" t="inlineStr"/>
@@ -17151,10 +17151,10 @@
         </is>
       </c>
       <c r="Q163" t="n">
-        <v>478161</v>
+        <v>478239</v>
       </c>
       <c r="R163" t="n">
-        <v>6827528</v>
+        <v>6827752</v>
       </c>
       <c r="S163" t="n">
         <v>10</v>
@@ -17213,10 +17213,10 @@
     </row>
     <row r="164">
       <c r="A164" t="n">
-        <v>120075160</v>
+        <v>120075223</v>
       </c>
       <c r="B164" t="n">
-        <v>78526</v>
+        <v>78171</v>
       </c>
       <c r="C164" t="inlineStr">
         <is>
@@ -17229,21 +17229,21 @@
         </is>
       </c>
       <c r="E164" t="n">
-        <v>6425</v>
+        <v>353</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G164" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H164" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I164" t="inlineStr"/>
@@ -17253,10 +17253,10 @@
         </is>
       </c>
       <c r="Q164" t="n">
-        <v>478097</v>
+        <v>478076</v>
       </c>
       <c r="R164" t="n">
-        <v>6827744</v>
+        <v>6827777</v>
       </c>
       <c r="S164" t="n">
         <v>10</v>
@@ -17315,10 +17315,10 @@
     </row>
     <row r="165">
       <c r="A165" t="n">
-        <v>120075121</v>
+        <v>120075206</v>
       </c>
       <c r="B165" t="n">
-        <v>78526</v>
+        <v>78171</v>
       </c>
       <c r="C165" t="inlineStr">
         <is>
@@ -17331,21 +17331,21 @@
         </is>
       </c>
       <c r="E165" t="n">
-        <v>6425</v>
+        <v>353</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G165" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H165" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I165" t="inlineStr"/>
@@ -17355,10 +17355,10 @@
         </is>
       </c>
       <c r="Q165" t="n">
-        <v>478232</v>
+        <v>478125</v>
       </c>
       <c r="R165" t="n">
-        <v>6827659</v>
+        <v>6827604</v>
       </c>
       <c r="S165" t="n">
         <v>10</v>
@@ -17417,7 +17417,7 @@
     </row>
     <row r="166">
       <c r="A166" t="n">
-        <v>120075067</v>
+        <v>120075090</v>
       </c>
       <c r="B166" t="n">
         <v>78526</v>
@@ -17457,10 +17457,10 @@
         </is>
       </c>
       <c r="Q166" t="n">
-        <v>478164</v>
+        <v>478161</v>
       </c>
       <c r="R166" t="n">
-        <v>6827661</v>
+        <v>6827528</v>
       </c>
       <c r="S166" t="n">
         <v>10</v>
@@ -17519,10 +17519,10 @@
     </row>
     <row r="167">
       <c r="A167" t="n">
-        <v>120075223</v>
+        <v>120075160</v>
       </c>
       <c r="B167" t="n">
-        <v>78171</v>
+        <v>78526</v>
       </c>
       <c r="C167" t="inlineStr">
         <is>
@@ -17535,21 +17535,21 @@
         </is>
       </c>
       <c r="E167" t="n">
-        <v>353</v>
+        <v>6425</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G167" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H167" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I167" t="inlineStr"/>
@@ -17559,10 +17559,10 @@
         </is>
       </c>
       <c r="Q167" t="n">
-        <v>478076</v>
+        <v>478097</v>
       </c>
       <c r="R167" t="n">
-        <v>6827777</v>
+        <v>6827744</v>
       </c>
       <c r="S167" t="n">
         <v>10</v>
@@ -17621,10 +17621,10 @@
     </row>
     <row r="168">
       <c r="A168" t="n">
-        <v>120075042</v>
+        <v>120075121</v>
       </c>
       <c r="B168" t="n">
-        <v>78262</v>
+        <v>78526</v>
       </c>
       <c r="C168" t="inlineStr">
         <is>
@@ -17637,21 +17637,21 @@
         </is>
       </c>
       <c r="E168" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G168" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H168" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I168" t="inlineStr"/>
@@ -17661,10 +17661,10 @@
         </is>
       </c>
       <c r="Q168" t="n">
-        <v>478074</v>
+        <v>478232</v>
       </c>
       <c r="R168" t="n">
-        <v>6827775</v>
+        <v>6827659</v>
       </c>
       <c r="S168" t="n">
         <v>10</v>
@@ -17723,10 +17723,10 @@
     </row>
     <row r="169">
       <c r="A169" t="n">
-        <v>120074888</v>
+        <v>120075067</v>
       </c>
       <c r="B169" t="n">
-        <v>79144</v>
+        <v>78526</v>
       </c>
       <c r="C169" t="inlineStr">
         <is>
@@ -17739,21 +17739,21 @@
         </is>
       </c>
       <c r="E169" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G169" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H169" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I169" t="inlineStr"/>
@@ -17763,10 +17763,10 @@
         </is>
       </c>
       <c r="Q169" t="n">
-        <v>478139</v>
+        <v>478164</v>
       </c>
       <c r="R169" t="n">
-        <v>6827554</v>
+        <v>6827661</v>
       </c>
       <c r="S169" t="n">
         <v>10</v>
@@ -17825,10 +17825,10 @@
     </row>
     <row r="170">
       <c r="A170" t="n">
-        <v>120074942</v>
+        <v>120075042</v>
       </c>
       <c r="B170" t="n">
-        <v>79144</v>
+        <v>78262</v>
       </c>
       <c r="C170" t="inlineStr">
         <is>
@@ -17841,21 +17841,21 @@
         </is>
       </c>
       <c r="E170" t="n">
-        <v>6453</v>
+        <v>6446</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G170" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H170" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I170" t="inlineStr"/>
@@ -17865,10 +17865,10 @@
         </is>
       </c>
       <c r="Q170" t="n">
-        <v>478065</v>
+        <v>478074</v>
       </c>
       <c r="R170" t="n">
-        <v>6827842</v>
+        <v>6827775</v>
       </c>
       <c r="S170" t="n">
         <v>10</v>
@@ -17927,10 +17927,10 @@
     </row>
     <row r="171">
       <c r="A171" t="n">
-        <v>120074956</v>
+        <v>120074888</v>
       </c>
       <c r="B171" t="n">
-        <v>57310</v>
+        <v>79144</v>
       </c>
       <c r="C171" t="inlineStr">
         <is>
@@ -17943,39 +17943,34 @@
         </is>
       </c>
       <c r="E171" t="n">
-        <v>100109</v>
+        <v>6453</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G171" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H171" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I171" t="inlineStr"/>
-      <c r="M171" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P171" t="inlineStr">
         <is>
           <t>Hevoslamm, Dlr</t>
         </is>
       </c>
       <c r="Q171" t="n">
-        <v>478278</v>
+        <v>478139</v>
       </c>
       <c r="R171" t="n">
-        <v>6827832</v>
+        <v>6827554</v>
       </c>
       <c r="S171" t="n">
         <v>10</v>
@@ -18008,11 +18003,6 @@
       <c r="AA171" t="inlineStr">
         <is>
           <t>2024-09-27</t>
-        </is>
-      </c>
-      <c r="AC171" t="inlineStr">
-        <is>
-          <t>Färska ringhack (tall)</t>
         </is>
       </c>
       <c r="AD171" t="b">
@@ -18039,10 +18029,10 @@
     </row>
     <row r="172">
       <c r="A172" t="n">
-        <v>120074999</v>
+        <v>120074942</v>
       </c>
       <c r="B172" t="n">
-        <v>78263</v>
+        <v>79144</v>
       </c>
       <c r="C172" t="inlineStr">
         <is>
@@ -18055,21 +18045,21 @@
         </is>
       </c>
       <c r="E172" t="n">
-        <v>228912</v>
+        <v>6453</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G172" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H172" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I172" t="inlineStr"/>
@@ -18079,10 +18069,10 @@
         </is>
       </c>
       <c r="Q172" t="n">
-        <v>478161</v>
+        <v>478065</v>
       </c>
       <c r="R172" t="n">
-        <v>6827592</v>
+        <v>6827842</v>
       </c>
       <c r="S172" t="n">
         <v>10</v>
@@ -18141,10 +18131,10 @@
     </row>
     <row r="173">
       <c r="A173" t="n">
-        <v>120075008</v>
+        <v>120074956</v>
       </c>
       <c r="B173" t="n">
-        <v>78263</v>
+        <v>57310</v>
       </c>
       <c r="C173" t="inlineStr">
         <is>
@@ -18157,34 +18147,39 @@
         </is>
       </c>
       <c r="E173" t="n">
-        <v>228912</v>
+        <v>100109</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G173" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H173" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I173" t="inlineStr"/>
+      <c r="M173" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P173" t="inlineStr">
         <is>
           <t>Hevoslamm, Dlr</t>
         </is>
       </c>
       <c r="Q173" t="n">
-        <v>478299</v>
+        <v>478278</v>
       </c>
       <c r="R173" t="n">
-        <v>6827805</v>
+        <v>6827832</v>
       </c>
       <c r="S173" t="n">
         <v>10</v>
@@ -18217,6 +18212,11 @@
       <c r="AA173" t="inlineStr">
         <is>
           <t>2024-09-27</t>
+        </is>
+      </c>
+      <c r="AC173" t="inlineStr">
+        <is>
+          <t>Färska ringhack (tall)</t>
         </is>
       </c>
       <c r="AD173" t="b">

--- a/artfynd/A 32983-2023 artfynd.xlsx
+++ b/artfynd/A 32983-2023 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>120075208</v>
+        <v>120075067</v>
       </c>
       <c r="B2" t="n">
-        <v>78171</v>
+        <v>78526</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>353</v>
+        <v>6425</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>478158</v>
+        <v>478164</v>
       </c>
       <c r="R2" t="n">
-        <v>6827519</v>
+        <v>6827661</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -777,7 +777,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>120075203</v>
+        <v>120075207</v>
       </c>
       <c r="B3" t="n">
         <v>78171</v>
@@ -817,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>478125</v>
+        <v>478157</v>
       </c>
       <c r="R3" t="n">
-        <v>6827631</v>
+        <v>6827509</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -879,10 +879,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>120075011</v>
+        <v>120074932</v>
       </c>
       <c r="B4" t="n">
-        <v>78263</v>
+        <v>79144</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -895,21 +895,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>228912</v>
+        <v>6453</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -919,10 +919,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>478103</v>
+        <v>478250</v>
       </c>
       <c r="R4" t="n">
-        <v>6827803</v>
+        <v>6827802</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -981,10 +981,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>120075013</v>
+        <v>120075197</v>
       </c>
       <c r="B5" t="n">
-        <v>78263</v>
+        <v>91840</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -993,38 +993,47 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>228912</v>
+        <v>4364</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr"/>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Hevoslamm, Dlr</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>478239</v>
+        <v>478077</v>
       </c>
       <c r="R5" t="n">
-        <v>6827752</v>
+        <v>6827805</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1083,7 +1092,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>120075192</v>
+        <v>120075127</v>
       </c>
       <c r="B6" t="n">
         <v>78526</v>
@@ -1123,10 +1132,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>478282</v>
+        <v>478292</v>
       </c>
       <c r="R6" t="n">
-        <v>6827683</v>
+        <v>6827708</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1185,7 +1194,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>120075159</v>
+        <v>120075070</v>
       </c>
       <c r="B7" t="n">
         <v>78526</v>
@@ -1225,10 +1234,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>478100</v>
+        <v>478135</v>
       </c>
       <c r="R7" t="n">
-        <v>6827729</v>
+        <v>6827625</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1287,10 +1296,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>120075069</v>
+        <v>120074999</v>
       </c>
       <c r="B8" t="n">
-        <v>78526</v>
+        <v>78263</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1303,21 +1312,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1327,10 +1336,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>478157</v>
+        <v>478161</v>
       </c>
       <c r="R8" t="n">
-        <v>6827611</v>
+        <v>6827592</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1389,10 +1398,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>120074892</v>
+        <v>120075011</v>
       </c>
       <c r="B9" t="n">
-        <v>79144</v>
+        <v>78263</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1405,21 +1414,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6453</v>
+        <v>228912</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1429,10 +1438,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>478243</v>
+        <v>478103</v>
       </c>
       <c r="R9" t="n">
-        <v>6827585</v>
+        <v>6827803</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1491,10 +1500,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>120074933</v>
+        <v>120075013</v>
       </c>
       <c r="B10" t="n">
-        <v>79144</v>
+        <v>78263</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1507,21 +1516,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6453</v>
+        <v>228912</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1531,10 +1540,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>478189</v>
+        <v>478239</v>
       </c>
       <c r="R10" t="n">
-        <v>6827761</v>
+        <v>6827752</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1593,10 +1602,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>120075164</v>
+        <v>120074925</v>
       </c>
       <c r="B11" t="n">
-        <v>78526</v>
+        <v>78560</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1609,21 +1618,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1633,10 +1642,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>478092</v>
+        <v>478088</v>
       </c>
       <c r="R11" t="n">
-        <v>6827810</v>
+        <v>6827834</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1695,10 +1704,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>120075078</v>
+        <v>120074912</v>
       </c>
       <c r="B12" t="n">
-        <v>78526</v>
+        <v>78560</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1711,21 +1720,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1735,10 +1744,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>478116</v>
+        <v>478149</v>
       </c>
       <c r="R12" t="n">
-        <v>6827567</v>
+        <v>6827714</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1797,10 +1806,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>120074934</v>
+        <v>120075019</v>
       </c>
       <c r="B13" t="n">
-        <v>79144</v>
+        <v>79607</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1813,21 +1822,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6453</v>
+        <v>6458</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1837,10 +1846,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>478169</v>
+        <v>478227</v>
       </c>
       <c r="R13" t="n">
-        <v>6827760</v>
+        <v>6827655</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1899,10 +1908,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>120075024</v>
+        <v>120074914</v>
       </c>
       <c r="B14" t="n">
-        <v>78262</v>
+        <v>78560</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1915,21 +1924,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6446</v>
+        <v>185</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1939,10 +1948,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>478165</v>
+        <v>478169</v>
       </c>
       <c r="R14" t="n">
-        <v>6827712</v>
+        <v>6827680</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2001,7 +2010,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>120075236</v>
+        <v>120075227</v>
       </c>
       <c r="B15" t="n">
         <v>78171</v>
@@ -2041,10 +2050,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>478062</v>
+        <v>478088</v>
       </c>
       <c r="R15" t="n">
-        <v>6827740</v>
+        <v>6827834</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2103,10 +2112,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>120075039</v>
+        <v>120075217</v>
       </c>
       <c r="B16" t="n">
-        <v>78262</v>
+        <v>78171</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2119,21 +2128,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6446</v>
+        <v>353</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2143,10 +2152,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>478238</v>
+        <v>478264</v>
       </c>
       <c r="R16" t="n">
-        <v>6827752</v>
+        <v>6827839</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2205,10 +2214,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>120075038</v>
+        <v>120075133</v>
       </c>
       <c r="B17" t="n">
-        <v>78262</v>
+        <v>78526</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2221,21 +2230,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2245,10 +2254,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>478261</v>
+        <v>478258</v>
       </c>
       <c r="R17" t="n">
-        <v>6827731</v>
+        <v>6827753</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2307,10 +2316,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>120075019</v>
+        <v>120075069</v>
       </c>
       <c r="B18" t="n">
-        <v>79607</v>
+        <v>78526</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2323,21 +2332,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2347,10 +2356,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>478227</v>
+        <v>478157</v>
       </c>
       <c r="R18" t="n">
-        <v>6827655</v>
+        <v>6827611</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2409,10 +2418,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>120075009</v>
+        <v>120075157</v>
       </c>
       <c r="B19" t="n">
-        <v>78263</v>
+        <v>78526</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2425,21 +2434,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2449,10 +2458,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>478151</v>
+        <v>478103</v>
       </c>
       <c r="R19" t="n">
-        <v>6827745</v>
+        <v>6827718</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2511,10 +2520,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>120075004</v>
+        <v>120075138</v>
       </c>
       <c r="B20" t="n">
-        <v>78263</v>
+        <v>78526</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2527,21 +2536,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2551,10 +2560,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>478212</v>
+        <v>478294</v>
       </c>
       <c r="R20" t="n">
-        <v>6827573</v>
+        <v>6827781</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2613,10 +2622,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>120075226</v>
+        <v>120074935</v>
       </c>
       <c r="B21" t="n">
-        <v>78171</v>
+        <v>79144</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2629,21 +2638,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>353</v>
+        <v>6453</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2653,10 +2662,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>478098</v>
+        <v>478150</v>
       </c>
       <c r="R21" t="n">
-        <v>6827815</v>
+        <v>6827745</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2715,10 +2724,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>120074928</v>
+        <v>120075205</v>
       </c>
       <c r="B22" t="n">
-        <v>78560</v>
+        <v>78171</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2731,21 +2740,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>185</v>
+        <v>353</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2755,10 +2764,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>478059</v>
+        <v>478117</v>
       </c>
       <c r="R22" t="n">
-        <v>6827740</v>
+        <v>6827612</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2817,10 +2826,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>120074914</v>
+        <v>120075231</v>
       </c>
       <c r="B23" t="n">
-        <v>78560</v>
+        <v>78171</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -2833,21 +2842,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>185</v>
+        <v>353</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2857,10 +2866,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>478169</v>
+        <v>478067</v>
       </c>
       <c r="R23" t="n">
-        <v>6827680</v>
+        <v>6827863</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2919,10 +2928,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>120075085</v>
+        <v>120075208</v>
       </c>
       <c r="B24" t="n">
-        <v>78526</v>
+        <v>78171</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -2935,21 +2944,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6425</v>
+        <v>353</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -2959,10 +2968,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>478094</v>
+        <v>478158</v>
       </c>
       <c r="R24" t="n">
-        <v>6827504</v>
+        <v>6827519</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3021,7 +3030,7 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>120075161</v>
+        <v>120075196</v>
       </c>
       <c r="B25" t="n">
         <v>78526</v>
@@ -3061,10 +3070,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>478082</v>
+        <v>478288</v>
       </c>
       <c r="R25" t="n">
-        <v>6827766</v>
+        <v>6827682</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3123,10 +3132,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>120074929</v>
+        <v>120075144</v>
       </c>
       <c r="B26" t="n">
-        <v>78560</v>
+        <v>78526</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3139,21 +3148,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3163,10 +3172,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>478045</v>
+        <v>478261</v>
       </c>
       <c r="R26" t="n">
-        <v>6827724</v>
+        <v>6827822</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3225,10 +3234,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>120075227</v>
+        <v>120074986</v>
       </c>
       <c r="B27" t="n">
-        <v>78171</v>
+        <v>79608</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3241,21 +3250,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>353</v>
+        <v>2081</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3265,10 +3274,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>478088</v>
+        <v>478096</v>
       </c>
       <c r="R27" t="n">
-        <v>6827834</v>
+        <v>6827549</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3327,10 +3336,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>120075202</v>
+        <v>120075016</v>
       </c>
       <c r="B28" t="n">
-        <v>78171</v>
+        <v>79607</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3343,21 +3352,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>353</v>
+        <v>6458</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3367,10 +3376,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>478218</v>
+        <v>478096</v>
       </c>
       <c r="R28" t="n">
-        <v>6827721</v>
+        <v>6827549</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3429,10 +3438,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>120075197</v>
+        <v>120074947</v>
       </c>
       <c r="B29" t="n">
-        <v>91840</v>
+        <v>79144</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3441,47 +3450,38 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>4364</v>
+        <v>6453</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I29" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J29" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
           <t>Hevoslamm, Dlr</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>478077</v>
+        <v>478061</v>
       </c>
       <c r="R29" t="n">
-        <v>6827805</v>
+        <v>6827751</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3540,10 +3540,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>120074905</v>
+        <v>120075015</v>
       </c>
       <c r="B30" t="n">
-        <v>79144</v>
+        <v>79607</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3556,21 +3556,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6453</v>
+        <v>6458</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3580,10 +3580,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>478285</v>
+        <v>478114</v>
       </c>
       <c r="R30" t="n">
-        <v>6827770</v>
+        <v>6827633</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3642,10 +3642,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>120074891</v>
+        <v>120075219</v>
       </c>
       <c r="B31" t="n">
-        <v>79144</v>
+        <v>78171</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3658,21 +3658,21 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6453</v>
+        <v>353</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3682,10 +3682,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>478212</v>
+        <v>478169</v>
       </c>
       <c r="R31" t="n">
-        <v>6827573</v>
+        <v>6827760</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3744,10 +3744,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>120075000</v>
+        <v>120074915</v>
       </c>
       <c r="B32" t="n">
-        <v>78263</v>
+        <v>78560</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -3760,21 +3760,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>228912</v>
+        <v>185</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3784,10 +3784,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>478121</v>
+        <v>478102</v>
       </c>
       <c r="R32" t="n">
-        <v>6827607</v>
+        <v>6827555</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3846,10 +3846,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>120075087</v>
+        <v>120074881</v>
       </c>
       <c r="B33" t="n">
-        <v>78526</v>
+        <v>79144</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -3862,21 +3862,21 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -3886,10 +3886,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>478145</v>
+        <v>478184</v>
       </c>
       <c r="R33" t="n">
-        <v>6827485</v>
+        <v>6827728</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -3948,10 +3948,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>120075134</v>
+        <v>120075047</v>
       </c>
       <c r="B34" t="n">
-        <v>78526</v>
+        <v>78262</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -3964,21 +3964,21 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -3988,10 +3988,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>478266</v>
+        <v>478212</v>
       </c>
       <c r="R34" t="n">
-        <v>6827765</v>
+        <v>6827573</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4050,10 +4050,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>120074952</v>
+        <v>120074996</v>
       </c>
       <c r="B35" t="n">
-        <v>79115</v>
+        <v>78263</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4066,21 +4066,21 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>229821</v>
+        <v>228912</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4090,10 +4090,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>478120</v>
+        <v>478165</v>
       </c>
       <c r="R35" t="n">
-        <v>6827605</v>
+        <v>6827712</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4152,10 +4152,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>120075162</v>
+        <v>120075039</v>
       </c>
       <c r="B36" t="n">
-        <v>78526</v>
+        <v>78262</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4168,21 +4168,21 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4192,10 +4192,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>478080</v>
+        <v>478238</v>
       </c>
       <c r="R36" t="n">
-        <v>6827808</v>
+        <v>6827752</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4356,10 +4356,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>120075048</v>
+        <v>120075147</v>
       </c>
       <c r="B38" t="n">
-        <v>56514</v>
+        <v>78526</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4372,39 +4372,34 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>102612</v>
+        <v>6425</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
-      <c r="M38" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
       <c r="P38" t="inlineStr">
         <is>
           <t>Hevoslamm, Dlr</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>478070</v>
+        <v>478153</v>
       </c>
       <c r="R38" t="n">
-        <v>6827723</v>
+        <v>6827728</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4463,10 +4458,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>120074931</v>
+        <v>120075173</v>
       </c>
       <c r="B39" t="n">
-        <v>79144</v>
+        <v>78526</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4479,21 +4474,21 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4503,10 +4498,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>478261</v>
+        <v>478052</v>
       </c>
       <c r="R39" t="n">
-        <v>6827822</v>
+        <v>6827754</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4565,10 +4560,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>120075015</v>
+        <v>120075074</v>
       </c>
       <c r="B40" t="n">
-        <v>79607</v>
+        <v>78526</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -4581,21 +4576,21 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4605,10 +4600,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>478114</v>
+        <v>478138</v>
       </c>
       <c r="R40" t="n">
-        <v>6827633</v>
+        <v>6827599</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4667,7 +4662,7 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>120075131</v>
+        <v>120075063</v>
       </c>
       <c r="B41" t="n">
         <v>78526</v>
@@ -4707,10 +4702,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>478258</v>
+        <v>478201</v>
       </c>
       <c r="R41" t="n">
-        <v>6827731</v>
+        <v>6827693</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4769,7 +4764,7 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>120075128</v>
+        <v>120075145</v>
       </c>
       <c r="B42" t="n">
         <v>78526</v>
@@ -4809,10 +4804,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>478275</v>
+        <v>478226</v>
       </c>
       <c r="R42" t="n">
-        <v>6827710</v>
+        <v>6827777</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4871,10 +4866,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>120075043</v>
+        <v>120075174</v>
       </c>
       <c r="B43" t="n">
-        <v>78262</v>
+        <v>78526</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -4887,21 +4882,21 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -4911,10 +4906,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>478103</v>
+        <v>478057</v>
       </c>
       <c r="R43" t="n">
-        <v>6827803</v>
+        <v>6827749</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -4973,10 +4968,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>120074889</v>
+        <v>120075054</v>
       </c>
       <c r="B44" t="n">
-        <v>79144</v>
+        <v>90580</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -4989,21 +4984,21 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>6453</v>
+        <v>5432</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -5013,10 +5008,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>478163</v>
+        <v>478126</v>
       </c>
       <c r="R44" t="n">
-        <v>6827536</v>
+        <v>6827477</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5075,10 +5070,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>120075012</v>
+        <v>120074907</v>
       </c>
       <c r="B45" t="n">
-        <v>78263</v>
+        <v>79144</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5091,21 +5086,21 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>228912</v>
+        <v>6453</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5115,10 +5110,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>478055</v>
+        <v>478263</v>
       </c>
       <c r="R45" t="n">
-        <v>6827786</v>
+        <v>6827838</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5177,10 +5172,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>120075003</v>
+        <v>120075081</v>
       </c>
       <c r="B46" t="n">
-        <v>78263</v>
+        <v>78526</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -5193,21 +5188,21 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5217,10 +5212,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>478137</v>
+        <v>478096</v>
       </c>
       <c r="R46" t="n">
-        <v>6827553</v>
+        <v>6827550</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5279,10 +5274,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>120075168</v>
+        <v>120075242</v>
       </c>
       <c r="B47" t="n">
-        <v>78526</v>
+        <v>77910</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -5295,21 +5290,21 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>6425</v>
+        <v>6437</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5319,10 +5314,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>478086</v>
+        <v>478136</v>
       </c>
       <c r="R47" t="n">
-        <v>6827868</v>
+        <v>6827556</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5381,10 +5376,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>120075224</v>
+        <v>120075094</v>
       </c>
       <c r="B48" t="n">
-        <v>78171</v>
+        <v>78526</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -5397,21 +5392,21 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>353</v>
+        <v>6425</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5421,10 +5416,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>478081</v>
+        <v>478205</v>
       </c>
       <c r="R48" t="n">
-        <v>6827789</v>
+        <v>6827556</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5483,10 +5478,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>120075219</v>
+        <v>120075064</v>
       </c>
       <c r="B49" t="n">
-        <v>78171</v>
+        <v>78526</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -5499,21 +5494,21 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>353</v>
+        <v>6425</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5523,10 +5518,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>478169</v>
+        <v>478192</v>
       </c>
       <c r="R49" t="n">
-        <v>6827760</v>
+        <v>6827690</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5585,10 +5580,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>120075139</v>
+        <v>120075198</v>
       </c>
       <c r="B50" t="n">
-        <v>78526</v>
+        <v>91840</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -5597,25 +5592,25 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -5625,10 +5620,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>478294</v>
+        <v>478163</v>
       </c>
       <c r="R50" t="n">
-        <v>6827803</v>
+        <v>6827530</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5687,10 +5682,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>120075082</v>
+        <v>120075037</v>
       </c>
       <c r="B51" t="n">
-        <v>78526</v>
+        <v>78262</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -5703,21 +5698,21 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -5727,10 +5722,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>478097</v>
+        <v>478265</v>
       </c>
       <c r="R51" t="n">
-        <v>6827544</v>
+        <v>6827716</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5789,10 +5784,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>120075175</v>
+        <v>120075204</v>
       </c>
       <c r="B52" t="n">
-        <v>78526</v>
+        <v>78171</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -5805,21 +5800,21 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>6425</v>
+        <v>353</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -5829,10 +5824,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>478059</v>
+        <v>478115</v>
       </c>
       <c r="R52" t="n">
-        <v>6827739</v>
+        <v>6827614</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -5891,10 +5886,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>120075172</v>
+        <v>120074922</v>
       </c>
       <c r="B53" t="n">
-        <v>78526</v>
+        <v>78560</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -5907,21 +5902,21 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -5931,10 +5926,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>478055</v>
+        <v>478103</v>
       </c>
       <c r="R53" t="n">
-        <v>6827768</v>
+        <v>6827718</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -5993,10 +5988,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>120075234</v>
+        <v>120075165</v>
       </c>
       <c r="B54" t="n">
-        <v>78171</v>
+        <v>78526</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
@@ -6009,21 +6004,21 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>353</v>
+        <v>6425</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -6033,10 +6028,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>478069</v>
+        <v>478078</v>
       </c>
       <c r="R54" t="n">
-        <v>6827741</v>
+        <v>6827834</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6095,10 +6090,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>120075230</v>
+        <v>120075177</v>
       </c>
       <c r="B55" t="n">
-        <v>78171</v>
+        <v>78526</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
@@ -6111,21 +6106,21 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>353</v>
+        <v>6425</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -6135,10 +6130,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>478064</v>
+        <v>478075</v>
       </c>
       <c r="R55" t="n">
-        <v>6827866</v>
+        <v>6827717</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6197,10 +6192,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>120074881</v>
+        <v>120075060</v>
       </c>
       <c r="B56" t="n">
-        <v>79144</v>
+        <v>78526</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
@@ -6213,21 +6208,21 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -6237,10 +6232,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>478184</v>
+        <v>478087</v>
       </c>
       <c r="R56" t="n">
-        <v>6827728</v>
+        <v>6827718</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6299,10 +6294,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>120075029</v>
+        <v>120074883</v>
       </c>
       <c r="B57" t="n">
-        <v>78262</v>
+        <v>79144</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
@@ -6315,21 +6310,21 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>6446</v>
+        <v>6453</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -6339,10 +6334,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>478115</v>
+        <v>478142</v>
       </c>
       <c r="R57" t="n">
-        <v>6827564</v>
+        <v>6827623</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6401,10 +6396,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>120074887</v>
+        <v>120075038</v>
       </c>
       <c r="B58" t="n">
-        <v>79144</v>
+        <v>78262</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
@@ -6417,21 +6412,21 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>6453</v>
+        <v>6446</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
@@ -6441,10 +6436,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>478144</v>
+        <v>478261</v>
       </c>
       <c r="R58" t="n">
-        <v>6827593</v>
+        <v>6827731</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6503,10 +6498,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>120075001</v>
+        <v>120075027</v>
       </c>
       <c r="B59" t="n">
-        <v>78263</v>
+        <v>78262</v>
       </c>
       <c r="C59" t="inlineStr">
         <is>
@@ -6519,21 +6514,21 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>228912</v>
+        <v>6446</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
@@ -6543,10 +6538,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>478125</v>
+        <v>478144</v>
       </c>
       <c r="R59" t="n">
-        <v>6827604</v>
+        <v>6827593</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6605,10 +6600,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>120074986</v>
+        <v>120074943</v>
       </c>
       <c r="B60" t="n">
-        <v>79608</v>
+        <v>79144</v>
       </c>
       <c r="C60" t="inlineStr">
         <is>
@@ -6621,21 +6616,21 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>2081</v>
+        <v>6453</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
@@ -6645,10 +6640,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>478096</v>
+        <v>478073</v>
       </c>
       <c r="R60" t="n">
-        <v>6827549</v>
+        <v>6827827</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -6707,10 +6702,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>120075242</v>
+        <v>120074938</v>
       </c>
       <c r="B61" t="n">
-        <v>77910</v>
+        <v>79144</v>
       </c>
       <c r="C61" t="inlineStr">
         <is>
@@ -6723,21 +6718,21 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>6437</v>
+        <v>6453</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
@@ -6747,10 +6742,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>478136</v>
+        <v>478097</v>
       </c>
       <c r="R61" t="n">
-        <v>6827556</v>
+        <v>6827756</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -6809,10 +6804,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>120075071</v>
+        <v>120075000</v>
       </c>
       <c r="B62" t="n">
-        <v>78526</v>
+        <v>78263</v>
       </c>
       <c r="C62" t="inlineStr">
         <is>
@@ -6825,21 +6820,21 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
@@ -6849,10 +6844,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>478116</v>
+        <v>478121</v>
       </c>
       <c r="R62" t="n">
-        <v>6827633</v>
+        <v>6827607</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -6911,7 +6906,7 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>120075130</v>
+        <v>120075146</v>
       </c>
       <c r="B63" t="n">
         <v>78526</v>
@@ -6951,10 +6946,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>478264</v>
+        <v>478154</v>
       </c>
       <c r="R63" t="n">
-        <v>6827733</v>
+        <v>6827747</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -7013,7 +7008,7 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>120075070</v>
+        <v>120075061</v>
       </c>
       <c r="B64" t="n">
         <v>78526</v>
@@ -7053,10 +7048,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>478135</v>
+        <v>478160</v>
       </c>
       <c r="R64" t="n">
-        <v>6827625</v>
+        <v>6827710</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -7115,7 +7110,7 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>120075074</v>
+        <v>120075084</v>
       </c>
       <c r="B65" t="n">
         <v>78526</v>
@@ -7155,10 +7150,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>478138</v>
+        <v>478098</v>
       </c>
       <c r="R65" t="n">
-        <v>6827599</v>
+        <v>6827520</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7217,7 +7212,7 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>120075092</v>
+        <v>120075066</v>
       </c>
       <c r="B66" t="n">
         <v>78526</v>
@@ -7257,10 +7252,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>478167</v>
+        <v>478160</v>
       </c>
       <c r="R66" t="n">
-        <v>6827561</v>
+        <v>6827680</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7319,7 +7314,7 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>120075171</v>
+        <v>120075166</v>
       </c>
       <c r="B67" t="n">
         <v>78526</v>
@@ -7359,10 +7354,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>478073</v>
+        <v>478092</v>
       </c>
       <c r="R67" t="n">
-        <v>6827831</v>
+        <v>6827839</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7421,10 +7416,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>120075046</v>
+        <v>120075130</v>
       </c>
       <c r="B68" t="n">
-        <v>78262</v>
+        <v>78526</v>
       </c>
       <c r="C68" t="inlineStr">
         <is>
@@ -7437,21 +7432,21 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
@@ -7461,10 +7456,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>478285</v>
+        <v>478264</v>
       </c>
       <c r="R68" t="n">
-        <v>6827770</v>
+        <v>6827733</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7523,10 +7518,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>120075054</v>
+        <v>120075134</v>
       </c>
       <c r="B69" t="n">
-        <v>90580</v>
+        <v>78526</v>
       </c>
       <c r="C69" t="inlineStr">
         <is>
@@ -7539,21 +7534,21 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
@@ -7563,10 +7558,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>478126</v>
+        <v>478266</v>
       </c>
       <c r="R69" t="n">
-        <v>6827477</v>
+        <v>6827765</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -7625,10 +7620,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>120075010</v>
+        <v>120075082</v>
       </c>
       <c r="B70" t="n">
-        <v>78263</v>
+        <v>78526</v>
       </c>
       <c r="C70" t="inlineStr">
         <is>
@@ -7641,21 +7636,21 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
@@ -7665,10 +7660,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>478074</v>
+        <v>478097</v>
       </c>
       <c r="R70" t="n">
-        <v>6827772</v>
+        <v>6827544</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -7727,7 +7722,7 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>120075127</v>
+        <v>120075131</v>
       </c>
       <c r="B71" t="n">
         <v>78526</v>
@@ -7767,10 +7762,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>478292</v>
+        <v>478258</v>
       </c>
       <c r="R71" t="n">
-        <v>6827708</v>
+        <v>6827731</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -7829,7 +7824,7 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>120075157</v>
+        <v>120075120</v>
       </c>
       <c r="B72" t="n">
         <v>78526</v>
@@ -7869,10 +7864,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>478103</v>
+        <v>478223</v>
       </c>
       <c r="R72" t="n">
-        <v>6827718</v>
+        <v>6827657</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -7931,7 +7926,7 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>120074938</v>
+        <v>120074939</v>
       </c>
       <c r="B73" t="n">
         <v>79144</v>
@@ -7971,10 +7966,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>478097</v>
+        <v>478091</v>
       </c>
       <c r="R73" t="n">
-        <v>6827756</v>
+        <v>6827838</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -8033,10 +8028,10 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>120075045</v>
+        <v>120075003</v>
       </c>
       <c r="B74" t="n">
-        <v>78262</v>
+        <v>78263</v>
       </c>
       <c r="C74" t="inlineStr">
         <is>
@@ -8049,21 +8044,21 @@
         </is>
       </c>
       <c r="E74" t="n">
-        <v>6446</v>
+        <v>228912</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
@@ -8073,10 +8068,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>478070</v>
+        <v>478137</v>
       </c>
       <c r="R74" t="n">
-        <v>6827723</v>
+        <v>6827553</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -8135,10 +8130,10 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>120075027</v>
+        <v>120075236</v>
       </c>
       <c r="B75" t="n">
-        <v>78262</v>
+        <v>78171</v>
       </c>
       <c r="C75" t="inlineStr">
         <is>
@@ -8151,21 +8146,21 @@
         </is>
       </c>
       <c r="E75" t="n">
-        <v>6446</v>
+        <v>353</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
@@ -8175,10 +8170,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>478144</v>
+        <v>478062</v>
       </c>
       <c r="R75" t="n">
-        <v>6827593</v>
+        <v>6827740</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -8237,10 +8232,10 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>120075176</v>
+        <v>120074930</v>
       </c>
       <c r="B76" t="n">
-        <v>78526</v>
+        <v>79144</v>
       </c>
       <c r="C76" t="inlineStr">
         <is>
@@ -8253,21 +8248,21 @@
         </is>
       </c>
       <c r="E76" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
@@ -8277,10 +8272,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>478066</v>
+        <v>478299</v>
       </c>
       <c r="R76" t="n">
-        <v>6827732</v>
+        <v>6827805</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -8339,10 +8334,10 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>120075089</v>
+        <v>120074944</v>
       </c>
       <c r="B77" t="n">
-        <v>78526</v>
+        <v>79144</v>
       </c>
       <c r="C77" t="inlineStr">
         <is>
@@ -8355,21 +8350,21 @@
         </is>
       </c>
       <c r="E77" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
@@ -8379,10 +8374,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>478153</v>
+        <v>478056</v>
       </c>
       <c r="R77" t="n">
-        <v>6827517</v>
+        <v>6827785</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -8441,10 +8436,10 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>120075138</v>
+        <v>120074904</v>
       </c>
       <c r="B78" t="n">
-        <v>78526</v>
+        <v>79144</v>
       </c>
       <c r="C78" t="inlineStr">
         <is>
@@ -8457,21 +8452,21 @@
         </is>
       </c>
       <c r="E78" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
@@ -8481,10 +8476,10 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>478294</v>
+        <v>478262</v>
       </c>
       <c r="R78" t="n">
-        <v>6827781</v>
+        <v>6827730</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -8543,10 +8538,10 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>120075120</v>
+        <v>120074889</v>
       </c>
       <c r="B79" t="n">
-        <v>78526</v>
+        <v>79144</v>
       </c>
       <c r="C79" t="inlineStr">
         <is>
@@ -8559,21 +8554,21 @@
         </is>
       </c>
       <c r="E79" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
@@ -8583,10 +8578,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>478223</v>
+        <v>478163</v>
       </c>
       <c r="R79" t="n">
-        <v>6827657</v>
+        <v>6827536</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -8645,10 +8640,10 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>120075140</v>
+        <v>120074946</v>
       </c>
       <c r="B80" t="n">
-        <v>78526</v>
+        <v>79144</v>
       </c>
       <c r="C80" t="inlineStr">
         <is>
@@ -8661,21 +8656,21 @@
         </is>
       </c>
       <c r="E80" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
@@ -8685,10 +8680,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>478310</v>
+        <v>478056</v>
       </c>
       <c r="R80" t="n">
-        <v>6827797</v>
+        <v>6827754</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -8747,7 +8742,7 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>120075073</v>
+        <v>120075161</v>
       </c>
       <c r="B81" t="n">
         <v>78526</v>
@@ -8787,10 +8782,10 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>478116</v>
+        <v>478082</v>
       </c>
       <c r="R81" t="n">
-        <v>6827617</v>
+        <v>6827766</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -8849,7 +8844,7 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>120075097</v>
+        <v>120075121</v>
       </c>
       <c r="B82" t="n">
         <v>78526</v>
@@ -8889,10 +8884,10 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>478248</v>
+        <v>478232</v>
       </c>
       <c r="R82" t="n">
-        <v>6827593</v>
+        <v>6827659</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -8951,7 +8946,7 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>120075129</v>
+        <v>120075077</v>
       </c>
       <c r="B83" t="n">
         <v>78526</v>
@@ -8991,10 +8986,10 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>478265</v>
+        <v>478124</v>
       </c>
       <c r="R83" t="n">
-        <v>6827707</v>
+        <v>6827560</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -9053,7 +9048,7 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>120075062</v>
+        <v>120075175</v>
       </c>
       <c r="B84" t="n">
         <v>78526</v>
@@ -9093,10 +9088,10 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>478221</v>
+        <v>478059</v>
       </c>
       <c r="R84" t="n">
-        <v>6827719</v>
+        <v>6827739</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -9155,10 +9150,10 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>120075136</v>
+        <v>120075232</v>
       </c>
       <c r="B85" t="n">
-        <v>78526</v>
+        <v>78171</v>
       </c>
       <c r="C85" t="inlineStr">
         <is>
@@ -9171,21 +9166,21 @@
         </is>
       </c>
       <c r="E85" t="n">
-        <v>6425</v>
+        <v>353</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
@@ -9195,10 +9190,10 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>478290</v>
+        <v>478051</v>
       </c>
       <c r="R85" t="n">
-        <v>6827758</v>
+        <v>6827739</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -9257,10 +9252,10 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>120075133</v>
+        <v>120075226</v>
       </c>
       <c r="B86" t="n">
-        <v>78526</v>
+        <v>78171</v>
       </c>
       <c r="C86" t="inlineStr">
         <is>
@@ -9273,21 +9268,21 @@
         </is>
       </c>
       <c r="E86" t="n">
-        <v>6425</v>
+        <v>353</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I86" t="inlineStr"/>
@@ -9297,10 +9292,10 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>478258</v>
+        <v>478098</v>
       </c>
       <c r="R86" t="n">
-        <v>6827753</v>
+        <v>6827815</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>
@@ -9359,10 +9354,10 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>120075204</v>
+        <v>120074917</v>
       </c>
       <c r="B87" t="n">
-        <v>78171</v>
+        <v>78560</v>
       </c>
       <c r="C87" t="inlineStr">
         <is>
@@ -9375,21 +9370,21 @@
         </is>
       </c>
       <c r="E87" t="n">
-        <v>353</v>
+        <v>185</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I87" t="inlineStr"/>
@@ -9399,10 +9394,10 @@
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>478115</v>
+        <v>478095</v>
       </c>
       <c r="R87" t="n">
-        <v>6827614</v>
+        <v>6827533</v>
       </c>
       <c r="S87" t="n">
         <v>10</v>
@@ -9461,10 +9456,10 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>120075075</v>
+        <v>120074928</v>
       </c>
       <c r="B88" t="n">
-        <v>78526</v>
+        <v>78560</v>
       </c>
       <c r="C88" t="inlineStr">
         <is>
@@ -9477,21 +9472,21 @@
         </is>
       </c>
       <c r="E88" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I88" t="inlineStr"/>
@@ -9501,10 +9496,10 @@
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>478139</v>
+        <v>478059</v>
       </c>
       <c r="R88" t="n">
-        <v>6827554</v>
+        <v>6827740</v>
       </c>
       <c r="S88" t="n">
         <v>10</v>
@@ -9563,7 +9558,7 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>120075064</v>
+        <v>120075162</v>
       </c>
       <c r="B89" t="n">
         <v>78526</v>
@@ -9603,10 +9598,10 @@
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>478192</v>
+        <v>478080</v>
       </c>
       <c r="R89" t="n">
-        <v>6827690</v>
+        <v>6827808</v>
       </c>
       <c r="S89" t="n">
         <v>10</v>
@@ -9665,7 +9660,7 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>120075145</v>
+        <v>120075159</v>
       </c>
       <c r="B90" t="n">
         <v>78526</v>
@@ -9705,10 +9700,10 @@
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>478226</v>
+        <v>478100</v>
       </c>
       <c r="R90" t="n">
-        <v>6827777</v>
+        <v>6827729</v>
       </c>
       <c r="S90" t="n">
         <v>10</v>
@@ -9767,10 +9762,10 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>120074961</v>
+        <v>120075163</v>
       </c>
       <c r="B91" t="n">
-        <v>90582</v>
+        <v>78526</v>
       </c>
       <c r="C91" t="inlineStr">
         <is>
@@ -9783,21 +9778,21 @@
         </is>
       </c>
       <c r="E91" t="n">
-        <v>5442</v>
+        <v>6425</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I91" t="inlineStr"/>
@@ -9807,10 +9802,10 @@
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>478230</v>
+        <v>478102</v>
       </c>
       <c r="R91" t="n">
-        <v>6827780</v>
+        <v>6827800</v>
       </c>
       <c r="S91" t="n">
         <v>10</v>
@@ -9869,10 +9864,10 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>120074883</v>
+        <v>120075071</v>
       </c>
       <c r="B92" t="n">
-        <v>79144</v>
+        <v>78526</v>
       </c>
       <c r="C92" t="inlineStr">
         <is>
@@ -9885,21 +9880,21 @@
         </is>
       </c>
       <c r="E92" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I92" t="inlineStr"/>
@@ -9909,10 +9904,10 @@
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>478142</v>
+        <v>478116</v>
       </c>
       <c r="R92" t="n">
-        <v>6827623</v>
+        <v>6827633</v>
       </c>
       <c r="S92" t="n">
         <v>10</v>
@@ -9971,10 +9966,10 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>120074904</v>
+        <v>120075167</v>
       </c>
       <c r="B93" t="n">
-        <v>79144</v>
+        <v>78526</v>
       </c>
       <c r="C93" t="inlineStr">
         <is>
@@ -9987,21 +9982,21 @@
         </is>
       </c>
       <c r="E93" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I93" t="inlineStr"/>
@@ -10011,10 +10006,10 @@
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>478262</v>
+        <v>478105</v>
       </c>
       <c r="R93" t="n">
-        <v>6827730</v>
+        <v>6827851</v>
       </c>
       <c r="S93" t="n">
         <v>10</v>
@@ -10073,10 +10068,10 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>120074886</v>
+        <v>120075160</v>
       </c>
       <c r="B94" t="n">
-        <v>79144</v>
+        <v>78526</v>
       </c>
       <c r="C94" t="inlineStr">
         <is>
@@ -10089,21 +10084,21 @@
         </is>
       </c>
       <c r="E94" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I94" t="inlineStr"/>
@@ -10113,10 +10108,10 @@
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>478125</v>
+        <v>478097</v>
       </c>
       <c r="R94" t="n">
-        <v>6827604</v>
+        <v>6827744</v>
       </c>
       <c r="S94" t="n">
         <v>10</v>
@@ -10175,10 +10170,10 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>120075037</v>
+        <v>120075073</v>
       </c>
       <c r="B95" t="n">
-        <v>78262</v>
+        <v>78526</v>
       </c>
       <c r="C95" t="inlineStr">
         <is>
@@ -10191,21 +10186,21 @@
         </is>
       </c>
       <c r="E95" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I95" t="inlineStr"/>
@@ -10215,10 +10210,10 @@
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>478265</v>
+        <v>478116</v>
       </c>
       <c r="R95" t="n">
-        <v>6827716</v>
+        <v>6827617</v>
       </c>
       <c r="S95" t="n">
         <v>10</v>
@@ -10277,10 +10272,10 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>120074997</v>
+        <v>120074934</v>
       </c>
       <c r="B96" t="n">
-        <v>78263</v>
+        <v>79144</v>
       </c>
       <c r="C96" t="inlineStr">
         <is>
@@ -10293,21 +10288,21 @@
         </is>
       </c>
       <c r="E96" t="n">
-        <v>228912</v>
+        <v>6453</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I96" t="inlineStr"/>
@@ -10317,10 +10312,10 @@
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>478218</v>
+        <v>478169</v>
       </c>
       <c r="R96" t="n">
-        <v>6827733</v>
+        <v>6827760</v>
       </c>
       <c r="S96" t="n">
         <v>10</v>
@@ -10379,10 +10374,10 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>120075214</v>
+        <v>120075028</v>
       </c>
       <c r="B97" t="n">
-        <v>78171</v>
+        <v>78262</v>
       </c>
       <c r="C97" t="inlineStr">
         <is>
@@ -10395,21 +10390,21 @@
         </is>
       </c>
       <c r="E97" t="n">
-        <v>353</v>
+        <v>6446</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I97" t="inlineStr"/>
@@ -10419,10 +10414,10 @@
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>478266</v>
+        <v>478137</v>
       </c>
       <c r="R97" t="n">
-        <v>6827724</v>
+        <v>6827553</v>
       </c>
       <c r="S97" t="n">
         <v>10</v>
@@ -10481,10 +10476,10 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>120075025</v>
+        <v>120074956</v>
       </c>
       <c r="B98" t="n">
-        <v>78262</v>
+        <v>57310</v>
       </c>
       <c r="C98" t="inlineStr">
         <is>
@@ -10497,34 +10492,39 @@
         </is>
       </c>
       <c r="E98" t="n">
-        <v>6446</v>
+        <v>100109</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I98" t="inlineStr"/>
+      <c r="M98" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P98" t="inlineStr">
         <is>
           <t>Hevoslamm, Dlr</t>
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>478171</v>
+        <v>478278</v>
       </c>
       <c r="R98" t="n">
-        <v>6827642</v>
+        <v>6827832</v>
       </c>
       <c r="S98" t="n">
         <v>10</v>
@@ -10557,6 +10557,11 @@
       <c r="AA98" t="inlineStr">
         <is>
           <t>2024-09-27</t>
+        </is>
+      </c>
+      <c r="AC98" t="inlineStr">
+        <is>
+          <t>Färska ringhack (tall)</t>
         </is>
       </c>
       <c r="AD98" t="b">
@@ -10583,10 +10588,10 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>120074930</v>
+        <v>120075025</v>
       </c>
       <c r="B99" t="n">
-        <v>79144</v>
+        <v>78262</v>
       </c>
       <c r="C99" t="inlineStr">
         <is>
@@ -10599,21 +10604,21 @@
         </is>
       </c>
       <c r="E99" t="n">
-        <v>6453</v>
+        <v>6446</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I99" t="inlineStr"/>
@@ -10623,10 +10628,10 @@
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>478299</v>
+        <v>478171</v>
       </c>
       <c r="R99" t="n">
-        <v>6827805</v>
+        <v>6827642</v>
       </c>
       <c r="S99" t="n">
         <v>10</v>
@@ -10685,10 +10690,10 @@
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>120075198</v>
+        <v>120075024</v>
       </c>
       <c r="B100" t="n">
-        <v>91840</v>
+        <v>78262</v>
       </c>
       <c r="C100" t="inlineStr">
         <is>
@@ -10697,25 +10702,25 @@
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E100" t="n">
-        <v>4364</v>
+        <v>6446</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I100" t="inlineStr"/>
@@ -10725,10 +10730,10 @@
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>478163</v>
+        <v>478165</v>
       </c>
       <c r="R100" t="n">
-        <v>6827530</v>
+        <v>6827712</v>
       </c>
       <c r="S100" t="n">
         <v>10</v>
@@ -10787,10 +10792,10 @@
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>120075061</v>
+        <v>120074882</v>
       </c>
       <c r="B101" t="n">
-        <v>78526</v>
+        <v>79144</v>
       </c>
       <c r="C101" t="inlineStr">
         <is>
@@ -10803,21 +10808,21 @@
         </is>
       </c>
       <c r="E101" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I101" t="inlineStr"/>
@@ -10827,10 +10832,10 @@
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>478160</v>
+        <v>478162</v>
       </c>
       <c r="R101" t="n">
-        <v>6827710</v>
+        <v>6827593</v>
       </c>
       <c r="S101" t="n">
         <v>10</v>
@@ -10889,10 +10894,10 @@
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>120075167</v>
+        <v>120075216</v>
       </c>
       <c r="B102" t="n">
-        <v>78526</v>
+        <v>78171</v>
       </c>
       <c r="C102" t="inlineStr">
         <is>
@@ -10905,21 +10910,21 @@
         </is>
       </c>
       <c r="E102" t="n">
-        <v>6425</v>
+        <v>353</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I102" t="inlineStr"/>
@@ -10929,10 +10934,10 @@
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>478105</v>
+        <v>478294</v>
       </c>
       <c r="R102" t="n">
-        <v>6827851</v>
+        <v>6827790</v>
       </c>
       <c r="S102" t="n">
         <v>10</v>
@@ -10991,10 +10996,10 @@
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>120075088</v>
+        <v>120075215</v>
       </c>
       <c r="B103" t="n">
-        <v>78526</v>
+        <v>78171</v>
       </c>
       <c r="C103" t="inlineStr">
         <is>
@@ -11007,21 +11012,21 @@
         </is>
       </c>
       <c r="E103" t="n">
-        <v>6425</v>
+        <v>353</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I103" t="inlineStr"/>
@@ -11031,10 +11036,10 @@
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>478151</v>
+        <v>478239</v>
       </c>
       <c r="R103" t="n">
-        <v>6827509</v>
+        <v>6827752</v>
       </c>
       <c r="S103" t="n">
         <v>10</v>
@@ -11093,10 +11098,10 @@
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>120075063</v>
+        <v>120074929</v>
       </c>
       <c r="B104" t="n">
-        <v>78526</v>
+        <v>78560</v>
       </c>
       <c r="C104" t="inlineStr">
         <is>
@@ -11109,21 +11114,21 @@
         </is>
       </c>
       <c r="E104" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I104" t="inlineStr"/>
@@ -11133,10 +11138,10 @@
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>478201</v>
+        <v>478045</v>
       </c>
       <c r="R104" t="n">
-        <v>6827693</v>
+        <v>6827724</v>
       </c>
       <c r="S104" t="n">
         <v>10</v>
@@ -11195,10 +11200,10 @@
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>120075066</v>
+        <v>120075224</v>
       </c>
       <c r="B105" t="n">
-        <v>78526</v>
+        <v>78171</v>
       </c>
       <c r="C105" t="inlineStr">
         <is>
@@ -11211,21 +11216,21 @@
         </is>
       </c>
       <c r="E105" t="n">
-        <v>6425</v>
+        <v>353</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I105" t="inlineStr"/>
@@ -11235,10 +11240,10 @@
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>478160</v>
+        <v>478081</v>
       </c>
       <c r="R105" t="n">
-        <v>6827680</v>
+        <v>6827789</v>
       </c>
       <c r="S105" t="n">
         <v>10</v>
@@ -11297,10 +11302,10 @@
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>120074906</v>
+        <v>120075234</v>
       </c>
       <c r="B106" t="n">
-        <v>79144</v>
+        <v>78171</v>
       </c>
       <c r="C106" t="inlineStr">
         <is>
@@ -11313,21 +11318,21 @@
         </is>
       </c>
       <c r="E106" t="n">
-        <v>6453</v>
+        <v>353</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I106" t="inlineStr"/>
@@ -11337,10 +11342,10 @@
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>478294</v>
+        <v>478069</v>
       </c>
       <c r="R106" t="n">
-        <v>6827790</v>
+        <v>6827741</v>
       </c>
       <c r="S106" t="n">
         <v>10</v>
@@ -11399,10 +11404,10 @@
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>120074996</v>
+        <v>120075088</v>
       </c>
       <c r="B107" t="n">
-        <v>78263</v>
+        <v>78526</v>
       </c>
       <c r="C107" t="inlineStr">
         <is>
@@ -11415,21 +11420,21 @@
         </is>
       </c>
       <c r="E107" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I107" t="inlineStr"/>
@@ -11439,10 +11444,10 @@
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>478165</v>
+        <v>478151</v>
       </c>
       <c r="R107" t="n">
-        <v>6827712</v>
+        <v>6827509</v>
       </c>
       <c r="S107" t="n">
         <v>10</v>
@@ -11501,10 +11506,10 @@
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>120074885</v>
+        <v>120075140</v>
       </c>
       <c r="B108" t="n">
-        <v>79144</v>
+        <v>78526</v>
       </c>
       <c r="C108" t="inlineStr">
         <is>
@@ -11517,21 +11522,21 @@
         </is>
       </c>
       <c r="E108" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I108" t="inlineStr"/>
@@ -11541,10 +11546,10 @@
         </is>
       </c>
       <c r="Q108" t="n">
-        <v>478115</v>
+        <v>478310</v>
       </c>
       <c r="R108" t="n">
-        <v>6827614</v>
+        <v>6827797</v>
       </c>
       <c r="S108" t="n">
         <v>10</v>
@@ -11603,10 +11608,10 @@
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>120075035</v>
+        <v>120075128</v>
       </c>
       <c r="B109" t="n">
-        <v>78262</v>
+        <v>78526</v>
       </c>
       <c r="C109" t="inlineStr">
         <is>
@@ -11619,21 +11624,21 @@
         </is>
       </c>
       <c r="E109" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I109" t="inlineStr"/>
@@ -11643,10 +11648,10 @@
         </is>
       </c>
       <c r="Q109" t="n">
-        <v>478273</v>
+        <v>478275</v>
       </c>
       <c r="R109" t="n">
-        <v>6827711</v>
+        <v>6827710</v>
       </c>
       <c r="S109" t="n">
         <v>10</v>
@@ -11705,10 +11710,10 @@
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>120075040</v>
+        <v>120075171</v>
       </c>
       <c r="B110" t="n">
-        <v>78262</v>
+        <v>78526</v>
       </c>
       <c r="C110" t="inlineStr">
         <is>
@@ -11721,21 +11726,21 @@
         </is>
       </c>
       <c r="E110" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I110" t="inlineStr"/>
@@ -11745,10 +11750,10 @@
         </is>
       </c>
       <c r="Q110" t="n">
-        <v>478250</v>
+        <v>478073</v>
       </c>
       <c r="R110" t="n">
-        <v>6827802</v>
+        <v>6827831</v>
       </c>
       <c r="S110" t="n">
         <v>10</v>
@@ -11807,10 +11812,10 @@
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>120074932</v>
+        <v>120074952</v>
       </c>
       <c r="B111" t="n">
-        <v>79144</v>
+        <v>79115</v>
       </c>
       <c r="C111" t="inlineStr">
         <is>
@@ -11823,21 +11828,21 @@
         </is>
       </c>
       <c r="E111" t="n">
-        <v>6453</v>
+        <v>229821</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I111" t="inlineStr"/>
@@ -11847,10 +11852,10 @@
         </is>
       </c>
       <c r="Q111" t="n">
-        <v>478250</v>
+        <v>478120</v>
       </c>
       <c r="R111" t="n">
-        <v>6827802</v>
+        <v>6827605</v>
       </c>
       <c r="S111" t="n">
         <v>10</v>
@@ -11909,10 +11914,10 @@
     </row>
     <row r="112">
       <c r="A112" t="n">
-        <v>120074943</v>
+        <v>120075176</v>
       </c>
       <c r="B112" t="n">
-        <v>79144</v>
+        <v>78526</v>
       </c>
       <c r="C112" t="inlineStr">
         <is>
@@ -11925,21 +11930,21 @@
         </is>
       </c>
       <c r="E112" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I112" t="inlineStr"/>
@@ -11949,10 +11954,10 @@
         </is>
       </c>
       <c r="Q112" t="n">
-        <v>478073</v>
+        <v>478066</v>
       </c>
       <c r="R112" t="n">
-        <v>6827827</v>
+        <v>6827732</v>
       </c>
       <c r="S112" t="n">
         <v>10</v>
@@ -12011,10 +12016,10 @@
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>120074998</v>
+        <v>120075136</v>
       </c>
       <c r="B113" t="n">
-        <v>78263</v>
+        <v>78526</v>
       </c>
       <c r="C113" t="inlineStr">
         <is>
@@ -12027,21 +12032,21 @@
         </is>
       </c>
       <c r="E113" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I113" t="inlineStr"/>
@@ -12051,10 +12056,10 @@
         </is>
       </c>
       <c r="Q113" t="n">
-        <v>478172</v>
+        <v>478290</v>
       </c>
       <c r="R113" t="n">
-        <v>6827640</v>
+        <v>6827758</v>
       </c>
       <c r="S113" t="n">
         <v>10</v>
@@ -12113,7 +12118,7 @@
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>120075196</v>
+        <v>120075137</v>
       </c>
       <c r="B114" t="n">
         <v>78526</v>
@@ -12156,7 +12161,7 @@
         <v>478288</v>
       </c>
       <c r="R114" t="n">
-        <v>6827682</v>
+        <v>6827763</v>
       </c>
       <c r="S114" t="n">
         <v>10</v>
@@ -12215,7 +12220,7 @@
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>120075132</v>
+        <v>120075075</v>
       </c>
       <c r="B115" t="n">
         <v>78526</v>
@@ -12255,10 +12260,10 @@
         </is>
       </c>
       <c r="Q115" t="n">
-        <v>478240</v>
+        <v>478139</v>
       </c>
       <c r="R115" t="n">
-        <v>6827754</v>
+        <v>6827554</v>
       </c>
       <c r="S115" t="n">
         <v>10</v>
@@ -12317,7 +12322,7 @@
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>120075173</v>
+        <v>120075129</v>
       </c>
       <c r="B116" t="n">
         <v>78526</v>
@@ -12357,10 +12362,10 @@
         </is>
       </c>
       <c r="Q116" t="n">
-        <v>478052</v>
+        <v>478265</v>
       </c>
       <c r="R116" t="n">
-        <v>6827754</v>
+        <v>6827707</v>
       </c>
       <c r="S116" t="n">
         <v>10</v>
@@ -12419,10 +12424,10 @@
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>120075065</v>
+        <v>120075042</v>
       </c>
       <c r="B117" t="n">
-        <v>78526</v>
+        <v>78262</v>
       </c>
       <c r="C117" t="inlineStr">
         <is>
@@ -12435,21 +12440,21 @@
         </is>
       </c>
       <c r="E117" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I117" t="inlineStr"/>
@@ -12459,10 +12464,10 @@
         </is>
       </c>
       <c r="Q117" t="n">
-        <v>478169</v>
+        <v>478074</v>
       </c>
       <c r="R117" t="n">
-        <v>6827679</v>
+        <v>6827775</v>
       </c>
       <c r="S117" t="n">
         <v>10</v>
@@ -12521,10 +12526,10 @@
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>120075094</v>
+        <v>120074931</v>
       </c>
       <c r="B118" t="n">
-        <v>78526</v>
+        <v>79144</v>
       </c>
       <c r="C118" t="inlineStr">
         <is>
@@ -12537,21 +12542,21 @@
         </is>
       </c>
       <c r="E118" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I118" t="inlineStr"/>
@@ -12561,10 +12566,10 @@
         </is>
       </c>
       <c r="Q118" t="n">
-        <v>478205</v>
+        <v>478261</v>
       </c>
       <c r="R118" t="n">
-        <v>6827556</v>
+        <v>6827822</v>
       </c>
       <c r="S118" t="n">
         <v>10</v>
@@ -12623,10 +12628,10 @@
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>120075177</v>
+        <v>120075201</v>
       </c>
       <c r="B119" t="n">
-        <v>78526</v>
+        <v>78171</v>
       </c>
       <c r="C119" t="inlineStr">
         <is>
@@ -12639,21 +12644,21 @@
         </is>
       </c>
       <c r="E119" t="n">
-        <v>6425</v>
+        <v>353</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I119" t="inlineStr"/>
@@ -12663,10 +12668,10 @@
         </is>
       </c>
       <c r="Q119" t="n">
-        <v>478075</v>
+        <v>478182</v>
       </c>
       <c r="R119" t="n">
-        <v>6827717</v>
+        <v>6827728</v>
       </c>
       <c r="S119" t="n">
         <v>10</v>
@@ -12725,10 +12730,10 @@
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>120075083</v>
+        <v>120075230</v>
       </c>
       <c r="B120" t="n">
-        <v>78526</v>
+        <v>78171</v>
       </c>
       <c r="C120" t="inlineStr">
         <is>
@@ -12741,21 +12746,21 @@
         </is>
       </c>
       <c r="E120" t="n">
-        <v>6425</v>
+        <v>353</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I120" t="inlineStr"/>
@@ -12765,10 +12770,10 @@
         </is>
       </c>
       <c r="Q120" t="n">
-        <v>478097</v>
+        <v>478064</v>
       </c>
       <c r="R120" t="n">
-        <v>6827527</v>
+        <v>6827866</v>
       </c>
       <c r="S120" t="n">
         <v>10</v>
@@ -12827,10 +12832,10 @@
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>120075144</v>
+        <v>120074997</v>
       </c>
       <c r="B121" t="n">
-        <v>78526</v>
+        <v>78263</v>
       </c>
       <c r="C121" t="inlineStr">
         <is>
@@ -12843,21 +12848,21 @@
         </is>
       </c>
       <c r="E121" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I121" t="inlineStr"/>
@@ -12867,10 +12872,10 @@
         </is>
       </c>
       <c r="Q121" t="n">
-        <v>478261</v>
+        <v>478218</v>
       </c>
       <c r="R121" t="n">
-        <v>6827822</v>
+        <v>6827733</v>
       </c>
       <c r="S121" t="n">
         <v>10</v>
@@ -12929,10 +12934,10 @@
     </row>
     <row r="122">
       <c r="A122" t="n">
-        <v>120075068</v>
+        <v>120075004</v>
       </c>
       <c r="B122" t="n">
-        <v>78526</v>
+        <v>78263</v>
       </c>
       <c r="C122" t="inlineStr">
         <is>
@@ -12945,21 +12950,21 @@
         </is>
       </c>
       <c r="E122" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I122" t="inlineStr"/>
@@ -12969,10 +12974,10 @@
         </is>
       </c>
       <c r="Q122" t="n">
-        <v>478174</v>
+        <v>478212</v>
       </c>
       <c r="R122" t="n">
-        <v>6827656</v>
+        <v>6827573</v>
       </c>
       <c r="S122" t="n">
         <v>10</v>
@@ -13031,10 +13036,10 @@
     </row>
     <row r="123">
       <c r="A123" t="n">
-        <v>120075216</v>
+        <v>120075008</v>
       </c>
       <c r="B123" t="n">
-        <v>78171</v>
+        <v>78263</v>
       </c>
       <c r="C123" t="inlineStr">
         <is>
@@ -13047,21 +13052,21 @@
         </is>
       </c>
       <c r="E123" t="n">
-        <v>353</v>
+        <v>228912</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I123" t="inlineStr"/>
@@ -13071,10 +13076,10 @@
         </is>
       </c>
       <c r="Q123" t="n">
-        <v>478294</v>
+        <v>478299</v>
       </c>
       <c r="R123" t="n">
-        <v>6827790</v>
+        <v>6827805</v>
       </c>
       <c r="S123" t="n">
         <v>10</v>
@@ -13133,10 +13138,10 @@
     </row>
     <row r="124">
       <c r="A124" t="n">
-        <v>120074922</v>
+        <v>120075192</v>
       </c>
       <c r="B124" t="n">
-        <v>78560</v>
+        <v>78526</v>
       </c>
       <c r="C124" t="inlineStr">
         <is>
@@ -13149,21 +13154,21 @@
         </is>
       </c>
       <c r="E124" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I124" t="inlineStr"/>
@@ -13173,10 +13178,10 @@
         </is>
       </c>
       <c r="Q124" t="n">
-        <v>478103</v>
+        <v>478282</v>
       </c>
       <c r="R124" t="n">
-        <v>6827718</v>
+        <v>6827683</v>
       </c>
       <c r="S124" t="n">
         <v>10</v>
@@ -13235,7 +13240,7 @@
     </row>
     <row r="125">
       <c r="A125" t="n">
-        <v>120075165</v>
+        <v>120075135</v>
       </c>
       <c r="B125" t="n">
         <v>78526</v>
@@ -13275,10 +13280,10 @@
         </is>
       </c>
       <c r="Q125" t="n">
-        <v>478078</v>
+        <v>478291</v>
       </c>
       <c r="R125" t="n">
-        <v>6827834</v>
+        <v>6827744</v>
       </c>
       <c r="S125" t="n">
         <v>10</v>
@@ -13337,7 +13342,7 @@
     </row>
     <row r="126">
       <c r="A126" t="n">
-        <v>120075166</v>
+        <v>120075085</v>
       </c>
       <c r="B126" t="n">
         <v>78526</v>
@@ -13377,10 +13382,10 @@
         </is>
       </c>
       <c r="Q126" t="n">
-        <v>478092</v>
+        <v>478094</v>
       </c>
       <c r="R126" t="n">
-        <v>6827839</v>
+        <v>6827504</v>
       </c>
       <c r="S126" t="n">
         <v>10</v>
@@ -13439,7 +13444,7 @@
     </row>
     <row r="127">
       <c r="A127" t="n">
-        <v>120075146</v>
+        <v>120075065</v>
       </c>
       <c r="B127" t="n">
         <v>78526</v>
@@ -13479,10 +13484,10 @@
         </is>
       </c>
       <c r="Q127" t="n">
-        <v>478154</v>
+        <v>478169</v>
       </c>
       <c r="R127" t="n">
-        <v>6827747</v>
+        <v>6827679</v>
       </c>
       <c r="S127" t="n">
         <v>10</v>
@@ -13541,10 +13546,10 @@
     </row>
     <row r="128">
       <c r="A128" t="n">
-        <v>120075016</v>
+        <v>120075164</v>
       </c>
       <c r="B128" t="n">
-        <v>79607</v>
+        <v>78526</v>
       </c>
       <c r="C128" t="inlineStr">
         <is>
@@ -13557,21 +13562,21 @@
         </is>
       </c>
       <c r="E128" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H128" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I128" t="inlineStr"/>
@@ -13581,10 +13586,10 @@
         </is>
       </c>
       <c r="Q128" t="n">
-        <v>478096</v>
+        <v>478092</v>
       </c>
       <c r="R128" t="n">
-        <v>6827549</v>
+        <v>6827810</v>
       </c>
       <c r="S128" t="n">
         <v>10</v>
@@ -13643,10 +13648,10 @@
     </row>
     <row r="129">
       <c r="A129" t="n">
-        <v>120074948</v>
+        <v>120075078</v>
       </c>
       <c r="B129" t="n">
-        <v>79144</v>
+        <v>78526</v>
       </c>
       <c r="C129" t="inlineStr">
         <is>
@@ -13659,21 +13664,21 @@
         </is>
       </c>
       <c r="E129" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H129" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I129" t="inlineStr"/>
@@ -13683,10 +13688,10 @@
         </is>
       </c>
       <c r="Q129" t="n">
-        <v>478070</v>
+        <v>478116</v>
       </c>
       <c r="R129" t="n">
-        <v>6827723</v>
+        <v>6827567</v>
       </c>
       <c r="S129" t="n">
         <v>10</v>
@@ -13745,10 +13750,10 @@
     </row>
     <row r="130">
       <c r="A130" t="n">
-        <v>120074947</v>
+        <v>120075068</v>
       </c>
       <c r="B130" t="n">
-        <v>79144</v>
+        <v>78526</v>
       </c>
       <c r="C130" t="inlineStr">
         <is>
@@ -13761,21 +13766,21 @@
         </is>
       </c>
       <c r="E130" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H130" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I130" t="inlineStr"/>
@@ -13785,10 +13790,10 @@
         </is>
       </c>
       <c r="Q130" t="n">
-        <v>478061</v>
+        <v>478174</v>
       </c>
       <c r="R130" t="n">
-        <v>6827751</v>
+        <v>6827656</v>
       </c>
       <c r="S130" t="n">
         <v>10</v>
@@ -13847,10 +13852,10 @@
     </row>
     <row r="131">
       <c r="A131" t="n">
-        <v>120074944</v>
+        <v>120075035</v>
       </c>
       <c r="B131" t="n">
-        <v>79144</v>
+        <v>78262</v>
       </c>
       <c r="C131" t="inlineStr">
         <is>
@@ -13863,21 +13868,21 @@
         </is>
       </c>
       <c r="E131" t="n">
-        <v>6453</v>
+        <v>6446</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H131" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I131" t="inlineStr"/>
@@ -13887,10 +13892,10 @@
         </is>
       </c>
       <c r="Q131" t="n">
-        <v>478056</v>
+        <v>478273</v>
       </c>
       <c r="R131" t="n">
-        <v>6827785</v>
+        <v>6827711</v>
       </c>
       <c r="S131" t="n">
         <v>10</v>
@@ -13949,10 +13954,10 @@
     </row>
     <row r="132">
       <c r="A132" t="n">
-        <v>120075044</v>
+        <v>120074941</v>
       </c>
       <c r="B132" t="n">
-        <v>78262</v>
+        <v>79144</v>
       </c>
       <c r="C132" t="inlineStr">
         <is>
@@ -13965,21 +13970,21 @@
         </is>
       </c>
       <c r="E132" t="n">
-        <v>6446</v>
+        <v>6453</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H132" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I132" t="inlineStr"/>
@@ -13989,10 +13994,10 @@
         </is>
       </c>
       <c r="Q132" t="n">
-        <v>478060</v>
+        <v>478069</v>
       </c>
       <c r="R132" t="n">
-        <v>6827770</v>
+        <v>6827854</v>
       </c>
       <c r="S132" t="n">
         <v>10</v>
@@ -14051,10 +14056,10 @@
     </row>
     <row r="133">
       <c r="A133" t="n">
-        <v>120074941</v>
+        <v>120075095</v>
       </c>
       <c r="B133" t="n">
-        <v>79144</v>
+        <v>78526</v>
       </c>
       <c r="C133" t="inlineStr">
         <is>
@@ -14067,21 +14072,21 @@
         </is>
       </c>
       <c r="E133" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H133" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I133" t="inlineStr"/>
@@ -14091,10 +14096,10 @@
         </is>
       </c>
       <c r="Q133" t="n">
-        <v>478069</v>
+        <v>478219</v>
       </c>
       <c r="R133" t="n">
-        <v>6827854</v>
+        <v>6827572</v>
       </c>
       <c r="S133" t="n">
         <v>10</v>
@@ -14153,10 +14158,10 @@
     </row>
     <row r="134">
       <c r="A134" t="n">
-        <v>120074935</v>
+        <v>120075044</v>
       </c>
       <c r="B134" t="n">
-        <v>79144</v>
+        <v>78262</v>
       </c>
       <c r="C134" t="inlineStr">
         <is>
@@ -14169,21 +14174,21 @@
         </is>
       </c>
       <c r="E134" t="n">
-        <v>6453</v>
+        <v>6446</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H134" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I134" t="inlineStr"/>
@@ -14193,10 +14198,10 @@
         </is>
       </c>
       <c r="Q134" t="n">
-        <v>478150</v>
+        <v>478060</v>
       </c>
       <c r="R134" t="n">
-        <v>6827745</v>
+        <v>6827770</v>
       </c>
       <c r="S134" t="n">
         <v>10</v>
@@ -14255,10 +14260,10 @@
     </row>
     <row r="135">
       <c r="A135" t="n">
-        <v>120074945</v>
+        <v>120074927</v>
       </c>
       <c r="B135" t="n">
-        <v>79144</v>
+        <v>78560</v>
       </c>
       <c r="C135" t="inlineStr">
         <is>
@@ -14271,21 +14276,21 @@
         </is>
       </c>
       <c r="E135" t="n">
-        <v>6453</v>
+        <v>185</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H135" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I135" t="inlineStr"/>
@@ -14295,10 +14300,10 @@
         </is>
       </c>
       <c r="Q135" t="n">
-        <v>478061</v>
+        <v>478073</v>
       </c>
       <c r="R135" t="n">
-        <v>6827770</v>
+        <v>6827836</v>
       </c>
       <c r="S135" t="n">
         <v>10</v>
@@ -14357,10 +14362,10 @@
     </row>
     <row r="136">
       <c r="A136" t="n">
-        <v>120075047</v>
+        <v>120075225</v>
       </c>
       <c r="B136" t="n">
-        <v>78262</v>
+        <v>78171</v>
       </c>
       <c r="C136" t="inlineStr">
         <is>
@@ -14373,21 +14378,21 @@
         </is>
       </c>
       <c r="E136" t="n">
-        <v>6446</v>
+        <v>353</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H136" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I136" t="inlineStr"/>
@@ -14397,10 +14402,10 @@
         </is>
       </c>
       <c r="Q136" t="n">
-        <v>478212</v>
+        <v>478075</v>
       </c>
       <c r="R136" t="n">
-        <v>6827573</v>
+        <v>6827798</v>
       </c>
       <c r="S136" t="n">
         <v>10</v>
@@ -14459,7 +14464,7 @@
     </row>
     <row r="137">
       <c r="A137" t="n">
-        <v>120075232</v>
+        <v>120075223</v>
       </c>
       <c r="B137" t="n">
         <v>78171</v>
@@ -14499,10 +14504,10 @@
         </is>
       </c>
       <c r="Q137" t="n">
-        <v>478051</v>
+        <v>478076</v>
       </c>
       <c r="R137" t="n">
-        <v>6827739</v>
+        <v>6827777</v>
       </c>
       <c r="S137" t="n">
         <v>10</v>
@@ -14561,10 +14566,10 @@
     </row>
     <row r="138">
       <c r="A138" t="n">
-        <v>120075225</v>
+        <v>120075142</v>
       </c>
       <c r="B138" t="n">
-        <v>78171</v>
+        <v>78526</v>
       </c>
       <c r="C138" t="inlineStr">
         <is>
@@ -14577,21 +14582,21 @@
         </is>
       </c>
       <c r="E138" t="n">
-        <v>353</v>
+        <v>6425</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H138" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I138" t="inlineStr"/>
@@ -14601,7 +14606,7 @@
         </is>
       </c>
       <c r="Q138" t="n">
-        <v>478075</v>
+        <v>478313</v>
       </c>
       <c r="R138" t="n">
         <v>6827798</v>
@@ -14663,10 +14668,10 @@
     </row>
     <row r="139">
       <c r="A139" t="n">
-        <v>120075205</v>
+        <v>120075083</v>
       </c>
       <c r="B139" t="n">
-        <v>78171</v>
+        <v>78526</v>
       </c>
       <c r="C139" t="inlineStr">
         <is>
@@ -14679,21 +14684,21 @@
         </is>
       </c>
       <c r="E139" t="n">
-        <v>353</v>
+        <v>6425</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H139" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I139" t="inlineStr"/>
@@ -14703,10 +14708,10 @@
         </is>
       </c>
       <c r="Q139" t="n">
-        <v>478117</v>
+        <v>478097</v>
       </c>
       <c r="R139" t="n">
-        <v>6827612</v>
+        <v>6827527</v>
       </c>
       <c r="S139" t="n">
         <v>10</v>
@@ -14765,10 +14770,10 @@
     </row>
     <row r="140">
       <c r="A140" t="n">
-        <v>120075135</v>
+        <v>120075202</v>
       </c>
       <c r="B140" t="n">
-        <v>78526</v>
+        <v>78171</v>
       </c>
       <c r="C140" t="inlineStr">
         <is>
@@ -14781,21 +14786,21 @@
         </is>
       </c>
       <c r="E140" t="n">
-        <v>6425</v>
+        <v>353</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H140" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I140" t="inlineStr"/>
@@ -14805,10 +14810,10 @@
         </is>
       </c>
       <c r="Q140" t="n">
-        <v>478291</v>
+        <v>478218</v>
       </c>
       <c r="R140" t="n">
-        <v>6827744</v>
+        <v>6827721</v>
       </c>
       <c r="S140" t="n">
         <v>10</v>
@@ -14867,10 +14872,10 @@
     </row>
     <row r="141">
       <c r="A141" t="n">
-        <v>120075081</v>
+        <v>120074888</v>
       </c>
       <c r="B141" t="n">
-        <v>78526</v>
+        <v>79144</v>
       </c>
       <c r="C141" t="inlineStr">
         <is>
@@ -14883,21 +14888,21 @@
         </is>
       </c>
       <c r="E141" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H141" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I141" t="inlineStr"/>
@@ -14907,10 +14912,10 @@
         </is>
       </c>
       <c r="Q141" t="n">
-        <v>478096</v>
+        <v>478139</v>
       </c>
       <c r="R141" t="n">
-        <v>6827550</v>
+        <v>6827554</v>
       </c>
       <c r="S141" t="n">
         <v>10</v>
@@ -14969,10 +14974,10 @@
     </row>
     <row r="142">
       <c r="A142" t="n">
-        <v>120075137</v>
+        <v>120074948</v>
       </c>
       <c r="B142" t="n">
-        <v>78526</v>
+        <v>79144</v>
       </c>
       <c r="C142" t="inlineStr">
         <is>
@@ -14985,21 +14990,21 @@
         </is>
       </c>
       <c r="E142" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H142" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I142" t="inlineStr"/>
@@ -15009,10 +15014,10 @@
         </is>
       </c>
       <c r="Q142" t="n">
-        <v>478288</v>
+        <v>478070</v>
       </c>
       <c r="R142" t="n">
-        <v>6827763</v>
+        <v>6827723</v>
       </c>
       <c r="S142" t="n">
         <v>10</v>
@@ -15071,10 +15076,10 @@
     </row>
     <row r="143">
       <c r="A143" t="n">
-        <v>120075143</v>
+        <v>120074892</v>
       </c>
       <c r="B143" t="n">
-        <v>78526</v>
+        <v>79144</v>
       </c>
       <c r="C143" t="inlineStr">
         <is>
@@ -15087,21 +15092,21 @@
         </is>
       </c>
       <c r="E143" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H143" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I143" t="inlineStr"/>
@@ -15111,10 +15116,10 @@
         </is>
       </c>
       <c r="Q143" t="n">
-        <v>478301</v>
+        <v>478243</v>
       </c>
       <c r="R143" t="n">
-        <v>6827814</v>
+        <v>6827585</v>
       </c>
       <c r="S143" t="n">
         <v>10</v>
@@ -15173,10 +15178,10 @@
     </row>
     <row r="144">
       <c r="A144" t="n">
-        <v>120075086</v>
+        <v>120074905</v>
       </c>
       <c r="B144" t="n">
-        <v>78526</v>
+        <v>79144</v>
       </c>
       <c r="C144" t="inlineStr">
         <is>
@@ -15189,21 +15194,21 @@
         </is>
       </c>
       <c r="E144" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H144" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I144" t="inlineStr"/>
@@ -15213,10 +15218,10 @@
         </is>
       </c>
       <c r="Q144" t="n">
-        <v>478104</v>
+        <v>478285</v>
       </c>
       <c r="R144" t="n">
-        <v>6827495</v>
+        <v>6827770</v>
       </c>
       <c r="S144" t="n">
         <v>10</v>
@@ -15275,10 +15280,10 @@
     </row>
     <row r="145">
       <c r="A145" t="n">
-        <v>120075028</v>
+        <v>120074886</v>
       </c>
       <c r="B145" t="n">
-        <v>78262</v>
+        <v>79144</v>
       </c>
       <c r="C145" t="inlineStr">
         <is>
@@ -15291,21 +15296,21 @@
         </is>
       </c>
       <c r="E145" t="n">
-        <v>6446</v>
+        <v>6453</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H145" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I145" t="inlineStr"/>
@@ -15315,10 +15320,10 @@
         </is>
       </c>
       <c r="Q145" t="n">
-        <v>478137</v>
+        <v>478125</v>
       </c>
       <c r="R145" t="n">
-        <v>6827553</v>
+        <v>6827604</v>
       </c>
       <c r="S145" t="n">
         <v>10</v>
@@ -15377,7 +15382,7 @@
     </row>
     <row r="146">
       <c r="A146" t="n">
-        <v>120074882</v>
+        <v>120074945</v>
       </c>
       <c r="B146" t="n">
         <v>79144</v>
@@ -15417,10 +15422,10 @@
         </is>
       </c>
       <c r="Q146" t="n">
-        <v>478162</v>
+        <v>478061</v>
       </c>
       <c r="R146" t="n">
-        <v>6827593</v>
+        <v>6827770</v>
       </c>
       <c r="S146" t="n">
         <v>10</v>
@@ -15479,7 +15484,7 @@
     </row>
     <row r="147">
       <c r="A147" t="n">
-        <v>120074946</v>
+        <v>120074891</v>
       </c>
       <c r="B147" t="n">
         <v>79144</v>
@@ -15519,10 +15524,10 @@
         </is>
       </c>
       <c r="Q147" t="n">
-        <v>478056</v>
+        <v>478212</v>
       </c>
       <c r="R147" t="n">
-        <v>6827754</v>
+        <v>6827573</v>
       </c>
       <c r="S147" t="n">
         <v>10</v>
@@ -15581,10 +15586,10 @@
     </row>
     <row r="148">
       <c r="A148" t="n">
-        <v>120074917</v>
+        <v>120074933</v>
       </c>
       <c r="B148" t="n">
-        <v>78560</v>
+        <v>79144</v>
       </c>
       <c r="C148" t="inlineStr">
         <is>
@@ -15597,21 +15602,21 @@
         </is>
       </c>
       <c r="E148" t="n">
-        <v>185</v>
+        <v>6453</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G148" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H148" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I148" t="inlineStr"/>
@@ -15621,10 +15626,10 @@
         </is>
       </c>
       <c r="Q148" t="n">
-        <v>478095</v>
+        <v>478189</v>
       </c>
       <c r="R148" t="n">
-        <v>6827533</v>
+        <v>6827761</v>
       </c>
       <c r="S148" t="n">
         <v>10</v>
@@ -15683,10 +15688,10 @@
     </row>
     <row r="149">
       <c r="A149" t="n">
-        <v>120074912</v>
+        <v>120074906</v>
       </c>
       <c r="B149" t="n">
-        <v>78560</v>
+        <v>79144</v>
       </c>
       <c r="C149" t="inlineStr">
         <is>
@@ -15699,21 +15704,21 @@
         </is>
       </c>
       <c r="E149" t="n">
-        <v>185</v>
+        <v>6453</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G149" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H149" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I149" t="inlineStr"/>
@@ -15723,10 +15728,10 @@
         </is>
       </c>
       <c r="Q149" t="n">
-        <v>478149</v>
+        <v>478294</v>
       </c>
       <c r="R149" t="n">
-        <v>6827714</v>
+        <v>6827790</v>
       </c>
       <c r="S149" t="n">
         <v>10</v>
@@ -15785,10 +15790,10 @@
     </row>
     <row r="150">
       <c r="A150" t="n">
-        <v>120075026</v>
+        <v>120074961</v>
       </c>
       <c r="B150" t="n">
-        <v>78262</v>
+        <v>90582</v>
       </c>
       <c r="C150" t="inlineStr">
         <is>
@@ -15801,21 +15806,21 @@
         </is>
       </c>
       <c r="E150" t="n">
-        <v>6446</v>
+        <v>5442</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G150" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H150" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I150" t="inlineStr"/>
@@ -15825,10 +15830,10 @@
         </is>
       </c>
       <c r="Q150" t="n">
-        <v>478161</v>
+        <v>478230</v>
       </c>
       <c r="R150" t="n">
-        <v>6827592</v>
+        <v>6827780</v>
       </c>
       <c r="S150" t="n">
         <v>10</v>
@@ -15887,10 +15892,10 @@
     </row>
     <row r="151">
       <c r="A151" t="n">
-        <v>120074939</v>
+        <v>120075007</v>
       </c>
       <c r="B151" t="n">
-        <v>79144</v>
+        <v>78263</v>
       </c>
       <c r="C151" t="inlineStr">
         <is>
@@ -15903,21 +15908,21 @@
         </is>
       </c>
       <c r="E151" t="n">
-        <v>6453</v>
+        <v>228912</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G151" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H151" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I151" t="inlineStr"/>
@@ -15927,10 +15932,10 @@
         </is>
       </c>
       <c r="Q151" t="n">
-        <v>478091</v>
+        <v>478285</v>
       </c>
       <c r="R151" t="n">
-        <v>6827838</v>
+        <v>6827770</v>
       </c>
       <c r="S151" t="n">
         <v>10</v>
@@ -15989,10 +15994,10 @@
     </row>
     <row r="152">
       <c r="A152" t="n">
-        <v>120075007</v>
+        <v>120075139</v>
       </c>
       <c r="B152" t="n">
-        <v>78263</v>
+        <v>78526</v>
       </c>
       <c r="C152" t="inlineStr">
         <is>
@@ -16005,21 +16010,21 @@
         </is>
       </c>
       <c r="E152" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G152" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H152" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I152" t="inlineStr"/>
@@ -16029,10 +16034,10 @@
         </is>
       </c>
       <c r="Q152" t="n">
-        <v>478285</v>
+        <v>478294</v>
       </c>
       <c r="R152" t="n">
-        <v>6827770</v>
+        <v>6827803</v>
       </c>
       <c r="S152" t="n">
         <v>10</v>
@@ -16091,10 +16096,10 @@
     </row>
     <row r="153">
       <c r="A153" t="n">
-        <v>120075231</v>
+        <v>120075089</v>
       </c>
       <c r="B153" t="n">
-        <v>78171</v>
+        <v>78526</v>
       </c>
       <c r="C153" t="inlineStr">
         <is>
@@ -16107,21 +16112,21 @@
         </is>
       </c>
       <c r="E153" t="n">
-        <v>353</v>
+        <v>6425</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G153" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H153" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I153" t="inlineStr"/>
@@ -16131,10 +16136,10 @@
         </is>
       </c>
       <c r="Q153" t="n">
-        <v>478067</v>
+        <v>478153</v>
       </c>
       <c r="R153" t="n">
-        <v>6827863</v>
+        <v>6827517</v>
       </c>
       <c r="S153" t="n">
         <v>10</v>
@@ -16193,10 +16198,10 @@
     </row>
     <row r="154">
       <c r="A154" t="n">
-        <v>120074925</v>
+        <v>120075090</v>
       </c>
       <c r="B154" t="n">
-        <v>78560</v>
+        <v>78526</v>
       </c>
       <c r="C154" t="inlineStr">
         <is>
@@ -16209,21 +16214,21 @@
         </is>
       </c>
       <c r="E154" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G154" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H154" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I154" t="inlineStr"/>
@@ -16233,10 +16238,10 @@
         </is>
       </c>
       <c r="Q154" t="n">
-        <v>478088</v>
+        <v>478161</v>
       </c>
       <c r="R154" t="n">
-        <v>6827834</v>
+        <v>6827528</v>
       </c>
       <c r="S154" t="n">
         <v>10</v>
@@ -16295,10 +16300,10 @@
     </row>
     <row r="155">
       <c r="A155" t="n">
-        <v>120075217</v>
+        <v>120075092</v>
       </c>
       <c r="B155" t="n">
-        <v>78171</v>
+        <v>78526</v>
       </c>
       <c r="C155" t="inlineStr">
         <is>
@@ -16311,21 +16316,21 @@
         </is>
       </c>
       <c r="E155" t="n">
-        <v>353</v>
+        <v>6425</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G155" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H155" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I155" t="inlineStr"/>
@@ -16335,10 +16340,10 @@
         </is>
       </c>
       <c r="Q155" t="n">
-        <v>478264</v>
+        <v>478167</v>
       </c>
       <c r="R155" t="n">
-        <v>6827839</v>
+        <v>6827561</v>
       </c>
       <c r="S155" t="n">
         <v>10</v>
@@ -16397,7 +16402,7 @@
     </row>
     <row r="156">
       <c r="A156" t="n">
-        <v>120075142</v>
+        <v>120075172</v>
       </c>
       <c r="B156" t="n">
         <v>78526</v>
@@ -16437,10 +16442,10 @@
         </is>
       </c>
       <c r="Q156" t="n">
-        <v>478313</v>
+        <v>478055</v>
       </c>
       <c r="R156" t="n">
-        <v>6827798</v>
+        <v>6827768</v>
       </c>
       <c r="S156" t="n">
         <v>10</v>
@@ -16499,7 +16504,7 @@
     </row>
     <row r="157">
       <c r="A157" t="n">
-        <v>120075147</v>
+        <v>120075086</v>
       </c>
       <c r="B157" t="n">
         <v>78526</v>
@@ -16539,10 +16544,10 @@
         </is>
       </c>
       <c r="Q157" t="n">
-        <v>478153</v>
+        <v>478104</v>
       </c>
       <c r="R157" t="n">
-        <v>6827728</v>
+        <v>6827495</v>
       </c>
       <c r="S157" t="n">
         <v>10</v>
@@ -16601,7 +16606,7 @@
     </row>
     <row r="158">
       <c r="A158" t="n">
-        <v>120075060</v>
+        <v>120075132</v>
       </c>
       <c r="B158" t="n">
         <v>78526</v>
@@ -16641,10 +16646,10 @@
         </is>
       </c>
       <c r="Q158" t="n">
-        <v>478087</v>
+        <v>478240</v>
       </c>
       <c r="R158" t="n">
-        <v>6827718</v>
+        <v>6827754</v>
       </c>
       <c r="S158" t="n">
         <v>10</v>
@@ -16703,7 +16708,7 @@
     </row>
     <row r="159">
       <c r="A159" t="n">
-        <v>120075077</v>
+        <v>120075143</v>
       </c>
       <c r="B159" t="n">
         <v>78526</v>
@@ -16743,10 +16748,10 @@
         </is>
       </c>
       <c r="Q159" t="n">
-        <v>478124</v>
+        <v>478301</v>
       </c>
       <c r="R159" t="n">
-        <v>6827560</v>
+        <v>6827814</v>
       </c>
       <c r="S159" t="n">
         <v>10</v>
@@ -16805,7 +16810,7 @@
     </row>
     <row r="160">
       <c r="A160" t="n">
-        <v>120075174</v>
+        <v>120075097</v>
       </c>
       <c r="B160" t="n">
         <v>78526</v>
@@ -16845,10 +16850,10 @@
         </is>
       </c>
       <c r="Q160" t="n">
-        <v>478057</v>
+        <v>478248</v>
       </c>
       <c r="R160" t="n">
-        <v>6827749</v>
+        <v>6827593</v>
       </c>
       <c r="S160" t="n">
         <v>10</v>
@@ -16907,10 +16912,10 @@
     </row>
     <row r="161">
       <c r="A161" t="n">
-        <v>120074999</v>
+        <v>120075062</v>
       </c>
       <c r="B161" t="n">
-        <v>78263</v>
+        <v>78526</v>
       </c>
       <c r="C161" t="inlineStr">
         <is>
@@ -16923,21 +16928,21 @@
         </is>
       </c>
       <c r="E161" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G161" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H161" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I161" t="inlineStr"/>
@@ -16947,10 +16952,10 @@
         </is>
       </c>
       <c r="Q161" t="n">
-        <v>478161</v>
+        <v>478221</v>
       </c>
       <c r="R161" t="n">
-        <v>6827592</v>
+        <v>6827719</v>
       </c>
       <c r="S161" t="n">
         <v>10</v>
@@ -17009,10 +17014,10 @@
     </row>
     <row r="162">
       <c r="A162" t="n">
-        <v>120075008</v>
+        <v>120075026</v>
       </c>
       <c r="B162" t="n">
-        <v>78263</v>
+        <v>78262</v>
       </c>
       <c r="C162" t="inlineStr">
         <is>
@@ -17025,21 +17030,21 @@
         </is>
       </c>
       <c r="E162" t="n">
-        <v>228912</v>
+        <v>6446</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G162" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H162" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I162" t="inlineStr"/>
@@ -17049,10 +17054,10 @@
         </is>
       </c>
       <c r="Q162" t="n">
-        <v>478299</v>
+        <v>478161</v>
       </c>
       <c r="R162" t="n">
-        <v>6827805</v>
+        <v>6827592</v>
       </c>
       <c r="S162" t="n">
         <v>10</v>
@@ -17111,10 +17116,10 @@
     </row>
     <row r="163">
       <c r="A163" t="n">
-        <v>120075215</v>
+        <v>120075046</v>
       </c>
       <c r="B163" t="n">
-        <v>78171</v>
+        <v>78262</v>
       </c>
       <c r="C163" t="inlineStr">
         <is>
@@ -17127,21 +17132,21 @@
         </is>
       </c>
       <c r="E163" t="n">
-        <v>353</v>
+        <v>6446</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G163" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H163" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I163" t="inlineStr"/>
@@ -17151,10 +17156,10 @@
         </is>
       </c>
       <c r="Q163" t="n">
-        <v>478239</v>
+        <v>478285</v>
       </c>
       <c r="R163" t="n">
-        <v>6827752</v>
+        <v>6827770</v>
       </c>
       <c r="S163" t="n">
         <v>10</v>
@@ -17213,10 +17218,10 @@
     </row>
     <row r="164">
       <c r="A164" t="n">
-        <v>120075223</v>
+        <v>120075043</v>
       </c>
       <c r="B164" t="n">
-        <v>78171</v>
+        <v>78262</v>
       </c>
       <c r="C164" t="inlineStr">
         <is>
@@ -17229,21 +17234,21 @@
         </is>
       </c>
       <c r="E164" t="n">
-        <v>353</v>
+        <v>6446</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G164" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H164" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I164" t="inlineStr"/>
@@ -17253,10 +17258,10 @@
         </is>
       </c>
       <c r="Q164" t="n">
-        <v>478076</v>
+        <v>478103</v>
       </c>
       <c r="R164" t="n">
-        <v>6827777</v>
+        <v>6827803</v>
       </c>
       <c r="S164" t="n">
         <v>10</v>
@@ -17315,10 +17320,10 @@
     </row>
     <row r="165">
       <c r="A165" t="n">
-        <v>120075206</v>
+        <v>120075048</v>
       </c>
       <c r="B165" t="n">
-        <v>78171</v>
+        <v>56514</v>
       </c>
       <c r="C165" t="inlineStr">
         <is>
@@ -17331,34 +17336,39 @@
         </is>
       </c>
       <c r="E165" t="n">
-        <v>353</v>
+        <v>102612</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G165" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H165" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I165" t="inlineStr"/>
+      <c r="M165" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="P165" t="inlineStr">
         <is>
           <t>Hevoslamm, Dlr</t>
         </is>
       </c>
       <c r="Q165" t="n">
-        <v>478125</v>
+        <v>478070</v>
       </c>
       <c r="R165" t="n">
-        <v>6827604</v>
+        <v>6827723</v>
       </c>
       <c r="S165" t="n">
         <v>10</v>
@@ -17417,10 +17427,10 @@
     </row>
     <row r="166">
       <c r="A166" t="n">
-        <v>120075090</v>
+        <v>120075012</v>
       </c>
       <c r="B166" t="n">
-        <v>78526</v>
+        <v>78263</v>
       </c>
       <c r="C166" t="inlineStr">
         <is>
@@ -17433,21 +17443,21 @@
         </is>
       </c>
       <c r="E166" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G166" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H166" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I166" t="inlineStr"/>
@@ -17457,10 +17467,10 @@
         </is>
       </c>
       <c r="Q166" t="n">
-        <v>478161</v>
+        <v>478055</v>
       </c>
       <c r="R166" t="n">
-        <v>6827528</v>
+        <v>6827786</v>
       </c>
       <c r="S166" t="n">
         <v>10</v>
@@ -17519,10 +17529,10 @@
     </row>
     <row r="167">
       <c r="A167" t="n">
-        <v>120075160</v>
+        <v>120075001</v>
       </c>
       <c r="B167" t="n">
-        <v>78526</v>
+        <v>78263</v>
       </c>
       <c r="C167" t="inlineStr">
         <is>
@@ -17535,21 +17545,21 @@
         </is>
       </c>
       <c r="E167" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G167" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H167" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I167" t="inlineStr"/>
@@ -17559,10 +17569,10 @@
         </is>
       </c>
       <c r="Q167" t="n">
-        <v>478097</v>
+        <v>478125</v>
       </c>
       <c r="R167" t="n">
-        <v>6827744</v>
+        <v>6827604</v>
       </c>
       <c r="S167" t="n">
         <v>10</v>
@@ -17621,10 +17631,10 @@
     </row>
     <row r="168">
       <c r="A168" t="n">
-        <v>120075121</v>
+        <v>120075010</v>
       </c>
       <c r="B168" t="n">
-        <v>78526</v>
+        <v>78263</v>
       </c>
       <c r="C168" t="inlineStr">
         <is>
@@ -17637,21 +17647,21 @@
         </is>
       </c>
       <c r="E168" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G168" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H168" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I168" t="inlineStr"/>
@@ -17661,10 +17671,10 @@
         </is>
       </c>
       <c r="Q168" t="n">
-        <v>478232</v>
+        <v>478074</v>
       </c>
       <c r="R168" t="n">
-        <v>6827659</v>
+        <v>6827772</v>
       </c>
       <c r="S168" t="n">
         <v>10</v>
@@ -17723,10 +17733,10 @@
     </row>
     <row r="169">
       <c r="A169" t="n">
-        <v>120075067</v>
+        <v>120075214</v>
       </c>
       <c r="B169" t="n">
-        <v>78526</v>
+        <v>78171</v>
       </c>
       <c r="C169" t="inlineStr">
         <is>
@@ -17739,21 +17749,21 @@
         </is>
       </c>
       <c r="E169" t="n">
-        <v>6425</v>
+        <v>353</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G169" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H169" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I169" t="inlineStr"/>
@@ -17763,10 +17773,10 @@
         </is>
       </c>
       <c r="Q169" t="n">
-        <v>478164</v>
+        <v>478266</v>
       </c>
       <c r="R169" t="n">
-        <v>6827661</v>
+        <v>6827724</v>
       </c>
       <c r="S169" t="n">
         <v>10</v>
@@ -17825,10 +17835,10 @@
     </row>
     <row r="170">
       <c r="A170" t="n">
-        <v>120075042</v>
+        <v>120075203</v>
       </c>
       <c r="B170" t="n">
-        <v>78262</v>
+        <v>78171</v>
       </c>
       <c r="C170" t="inlineStr">
         <is>
@@ -17841,21 +17851,21 @@
         </is>
       </c>
       <c r="E170" t="n">
-        <v>6446</v>
+        <v>353</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G170" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H170" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I170" t="inlineStr"/>
@@ -17865,10 +17875,10 @@
         </is>
       </c>
       <c r="Q170" t="n">
-        <v>478074</v>
+        <v>478125</v>
       </c>
       <c r="R170" t="n">
-        <v>6827775</v>
+        <v>6827631</v>
       </c>
       <c r="S170" t="n">
         <v>10</v>
@@ -17927,10 +17937,10 @@
     </row>
     <row r="171">
       <c r="A171" t="n">
-        <v>120074888</v>
+        <v>120075206</v>
       </c>
       <c r="B171" t="n">
-        <v>79144</v>
+        <v>78171</v>
       </c>
       <c r="C171" t="inlineStr">
         <is>
@@ -17943,21 +17953,21 @@
         </is>
       </c>
       <c r="E171" t="n">
-        <v>6453</v>
+        <v>353</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G171" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H171" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I171" t="inlineStr"/>
@@ -17967,10 +17977,10 @@
         </is>
       </c>
       <c r="Q171" t="n">
-        <v>478139</v>
+        <v>478125</v>
       </c>
       <c r="R171" t="n">
-        <v>6827554</v>
+        <v>6827604</v>
       </c>
       <c r="S171" t="n">
         <v>10</v>
@@ -18029,10 +18039,10 @@
     </row>
     <row r="172">
       <c r="A172" t="n">
-        <v>120074942</v>
+        <v>120075168</v>
       </c>
       <c r="B172" t="n">
-        <v>79144</v>
+        <v>78526</v>
       </c>
       <c r="C172" t="inlineStr">
         <is>
@@ -18045,21 +18055,21 @@
         </is>
       </c>
       <c r="E172" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G172" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H172" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I172" t="inlineStr"/>
@@ -18069,10 +18079,10 @@
         </is>
       </c>
       <c r="Q172" t="n">
-        <v>478065</v>
+        <v>478086</v>
       </c>
       <c r="R172" t="n">
-        <v>6827842</v>
+        <v>6827868</v>
       </c>
       <c r="S172" t="n">
         <v>10</v>
@@ -18131,10 +18141,10 @@
     </row>
     <row r="173">
       <c r="A173" t="n">
-        <v>120074956</v>
+        <v>120075029</v>
       </c>
       <c r="B173" t="n">
-        <v>57310</v>
+        <v>78262</v>
       </c>
       <c r="C173" t="inlineStr">
         <is>
@@ -18147,39 +18157,34 @@
         </is>
       </c>
       <c r="E173" t="n">
-        <v>100109</v>
+        <v>6446</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G173" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H173" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I173" t="inlineStr"/>
-      <c r="M173" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P173" t="inlineStr">
         <is>
           <t>Hevoslamm, Dlr</t>
         </is>
       </c>
       <c r="Q173" t="n">
-        <v>478278</v>
+        <v>478115</v>
       </c>
       <c r="R173" t="n">
-        <v>6827832</v>
+        <v>6827564</v>
       </c>
       <c r="S173" t="n">
         <v>10</v>
@@ -18212,11 +18217,6 @@
       <c r="AA173" t="inlineStr">
         <is>
           <t>2024-09-27</t>
-        </is>
-      </c>
-      <c r="AC173" t="inlineStr">
-        <is>
-          <t>Färska ringhack (tall)</t>
         </is>
       </c>
       <c r="AD173" t="b">
@@ -18243,10 +18243,10 @@
     </row>
     <row r="174">
       <c r="A174" t="n">
-        <v>120075163</v>
+        <v>120075045</v>
       </c>
       <c r="B174" t="n">
-        <v>78526</v>
+        <v>78262</v>
       </c>
       <c r="C174" t="inlineStr">
         <is>
@@ -18259,21 +18259,21 @@
         </is>
       </c>
       <c r="E174" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G174" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H174" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I174" t="inlineStr"/>
@@ -18283,10 +18283,10 @@
         </is>
       </c>
       <c r="Q174" t="n">
-        <v>478102</v>
+        <v>478070</v>
       </c>
       <c r="R174" t="n">
-        <v>6827800</v>
+        <v>6827723</v>
       </c>
       <c r="S174" t="n">
         <v>10</v>
@@ -18345,10 +18345,10 @@
     </row>
     <row r="175">
       <c r="A175" t="n">
-        <v>120075095</v>
+        <v>120075040</v>
       </c>
       <c r="B175" t="n">
-        <v>78526</v>
+        <v>78262</v>
       </c>
       <c r="C175" t="inlineStr">
         <is>
@@ -18361,21 +18361,21 @@
         </is>
       </c>
       <c r="E175" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G175" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H175" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I175" t="inlineStr"/>
@@ -18385,10 +18385,10 @@
         </is>
       </c>
       <c r="Q175" t="n">
-        <v>478219</v>
+        <v>478250</v>
       </c>
       <c r="R175" t="n">
-        <v>6827572</v>
+        <v>6827802</v>
       </c>
       <c r="S175" t="n">
         <v>10</v>
@@ -18447,10 +18447,10 @@
     </row>
     <row r="176">
       <c r="A176" t="n">
-        <v>120075084</v>
+        <v>120074942</v>
       </c>
       <c r="B176" t="n">
-        <v>78526</v>
+        <v>79144</v>
       </c>
       <c r="C176" t="inlineStr">
         <is>
@@ -18463,21 +18463,21 @@
         </is>
       </c>
       <c r="E176" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G176" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H176" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I176" t="inlineStr"/>
@@ -18487,10 +18487,10 @@
         </is>
       </c>
       <c r="Q176" t="n">
-        <v>478098</v>
+        <v>478065</v>
       </c>
       <c r="R176" t="n">
-        <v>6827520</v>
+        <v>6827842</v>
       </c>
       <c r="S176" t="n">
         <v>10</v>
@@ -18549,10 +18549,10 @@
     </row>
     <row r="177">
       <c r="A177" t="n">
-        <v>120074907</v>
+        <v>120074998</v>
       </c>
       <c r="B177" t="n">
-        <v>79144</v>
+        <v>78263</v>
       </c>
       <c r="C177" t="inlineStr">
         <is>
@@ -18565,21 +18565,21 @@
         </is>
       </c>
       <c r="E177" t="n">
-        <v>6453</v>
+        <v>228912</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G177" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H177" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I177" t="inlineStr"/>
@@ -18589,10 +18589,10 @@
         </is>
       </c>
       <c r="Q177" t="n">
-        <v>478263</v>
+        <v>478172</v>
       </c>
       <c r="R177" t="n">
-        <v>6827838</v>
+        <v>6827640</v>
       </c>
       <c r="S177" t="n">
         <v>10</v>
@@ -18651,10 +18651,10 @@
     </row>
     <row r="178">
       <c r="A178" t="n">
-        <v>120074927</v>
+        <v>120075009</v>
       </c>
       <c r="B178" t="n">
-        <v>78560</v>
+        <v>78263</v>
       </c>
       <c r="C178" t="inlineStr">
         <is>
@@ -18667,21 +18667,21 @@
         </is>
       </c>
       <c r="E178" t="n">
-        <v>185</v>
+        <v>228912</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G178" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H178" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I178" t="inlineStr"/>
@@ -18691,10 +18691,10 @@
         </is>
       </c>
       <c r="Q178" t="n">
-        <v>478073</v>
+        <v>478151</v>
       </c>
       <c r="R178" t="n">
-        <v>6827836</v>
+        <v>6827745</v>
       </c>
       <c r="S178" t="n">
         <v>10</v>
@@ -18753,10 +18753,10 @@
     </row>
     <row r="179">
       <c r="A179" t="n">
-        <v>120075201</v>
+        <v>120074885</v>
       </c>
       <c r="B179" t="n">
-        <v>78171</v>
+        <v>79144</v>
       </c>
       <c r="C179" t="inlineStr">
         <is>
@@ -18769,21 +18769,21 @@
         </is>
       </c>
       <c r="E179" t="n">
-        <v>353</v>
+        <v>6453</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G179" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H179" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I179" t="inlineStr"/>
@@ -18793,10 +18793,10 @@
         </is>
       </c>
       <c r="Q179" t="n">
-        <v>478182</v>
+        <v>478115</v>
       </c>
       <c r="R179" t="n">
-        <v>6827728</v>
+        <v>6827614</v>
       </c>
       <c r="S179" t="n">
         <v>10</v>
@@ -18855,10 +18855,10 @@
     </row>
     <row r="180">
       <c r="A180" t="n">
-        <v>120074915</v>
+        <v>120074887</v>
       </c>
       <c r="B180" t="n">
-        <v>78560</v>
+        <v>79144</v>
       </c>
       <c r="C180" t="inlineStr">
         <is>
@@ -18871,21 +18871,21 @@
         </is>
       </c>
       <c r="E180" t="n">
-        <v>185</v>
+        <v>6453</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G180" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H180" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I180" t="inlineStr"/>
@@ -18895,10 +18895,10 @@
         </is>
       </c>
       <c r="Q180" t="n">
-        <v>478102</v>
+        <v>478144</v>
       </c>
       <c r="R180" t="n">
-        <v>6827555</v>
+        <v>6827593</v>
       </c>
       <c r="S180" t="n">
         <v>10</v>
@@ -18957,10 +18957,10 @@
     </row>
     <row r="181">
       <c r="A181" t="n">
-        <v>120075207</v>
+        <v>120075087</v>
       </c>
       <c r="B181" t="n">
-        <v>78171</v>
+        <v>78526</v>
       </c>
       <c r="C181" t="inlineStr">
         <is>
@@ -18973,21 +18973,21 @@
         </is>
       </c>
       <c r="E181" t="n">
-        <v>353</v>
+        <v>6425</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G181" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H181" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I181" t="inlineStr"/>
@@ -18997,10 +18997,10 @@
         </is>
       </c>
       <c r="Q181" t="n">
-        <v>478157</v>
+        <v>478145</v>
       </c>
       <c r="R181" t="n">
-        <v>6827509</v>
+        <v>6827485</v>
       </c>
       <c r="S181" t="n">
         <v>10</v>

--- a/artfynd/A 32983-2023 artfynd.xlsx
+++ b/artfynd/A 32983-2023 artfynd.xlsx
@@ -777,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>120075207</v>
+        <v>120074932</v>
       </c>
       <c r="B3" t="n">
-        <v>78171</v>
+        <v>79144</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -793,21 +793,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>353</v>
+        <v>6453</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -817,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>478157</v>
+        <v>478250</v>
       </c>
       <c r="R3" t="n">
-        <v>6827509</v>
+        <v>6827802</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -879,10 +879,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>120074932</v>
+        <v>120075207</v>
       </c>
       <c r="B4" t="n">
-        <v>79144</v>
+        <v>78171</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -895,21 +895,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6453</v>
+        <v>353</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -919,10 +919,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>478250</v>
+        <v>478157</v>
       </c>
       <c r="R4" t="n">
-        <v>6827802</v>
+        <v>6827509</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -981,10 +981,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>120075197</v>
+        <v>120074999</v>
       </c>
       <c r="B5" t="n">
-        <v>91840</v>
+        <v>78263</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -993,47 +993,38 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>4364</v>
+        <v>228912</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
           <t>Hevoslamm, Dlr</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>478077</v>
+        <v>478161</v>
       </c>
       <c r="R5" t="n">
-        <v>6827805</v>
+        <v>6827592</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1092,10 +1083,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>120075127</v>
+        <v>120075011</v>
       </c>
       <c r="B6" t="n">
-        <v>78526</v>
+        <v>78263</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1108,21 +1099,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1132,10 +1123,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>478292</v>
+        <v>478103</v>
       </c>
       <c r="R6" t="n">
-        <v>6827708</v>
+        <v>6827803</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1194,10 +1185,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>120075070</v>
+        <v>120075013</v>
       </c>
       <c r="B7" t="n">
-        <v>78526</v>
+        <v>78263</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1210,21 +1201,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1234,10 +1225,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>478135</v>
+        <v>478239</v>
       </c>
       <c r="R7" t="n">
-        <v>6827625</v>
+        <v>6827752</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1296,10 +1287,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>120074999</v>
+        <v>120075197</v>
       </c>
       <c r="B8" t="n">
-        <v>78263</v>
+        <v>91840</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1308,38 +1299,47 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>228912</v>
+        <v>4364</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr"/>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="P8" t="inlineStr">
         <is>
           <t>Hevoslamm, Dlr</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>478161</v>
+        <v>478077</v>
       </c>
       <c r="R8" t="n">
-        <v>6827592</v>
+        <v>6827805</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1398,10 +1398,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>120075011</v>
+        <v>120075019</v>
       </c>
       <c r="B9" t="n">
-        <v>78263</v>
+        <v>79607</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1414,21 +1414,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>228912</v>
+        <v>6458</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1438,10 +1438,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>478103</v>
+        <v>478227</v>
       </c>
       <c r="R9" t="n">
-        <v>6827803</v>
+        <v>6827655</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1500,10 +1500,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>120075013</v>
+        <v>120074925</v>
       </c>
       <c r="B10" t="n">
-        <v>78263</v>
+        <v>78560</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1516,21 +1516,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>228912</v>
+        <v>185</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1540,10 +1540,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>478239</v>
+        <v>478088</v>
       </c>
       <c r="R10" t="n">
-        <v>6827752</v>
+        <v>6827834</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1602,7 +1602,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>120074925</v>
+        <v>120074912</v>
       </c>
       <c r="B11" t="n">
         <v>78560</v>
@@ -1642,10 +1642,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>478088</v>
+        <v>478149</v>
       </c>
       <c r="R11" t="n">
-        <v>6827834</v>
+        <v>6827714</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1704,10 +1704,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>120074912</v>
+        <v>120075127</v>
       </c>
       <c r="B12" t="n">
-        <v>78560</v>
+        <v>78526</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1720,21 +1720,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1744,10 +1744,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>478149</v>
+        <v>478292</v>
       </c>
       <c r="R12" t="n">
-        <v>6827714</v>
+        <v>6827708</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1806,10 +1806,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>120075019</v>
+        <v>120075070</v>
       </c>
       <c r="B13" t="n">
-        <v>79607</v>
+        <v>78526</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1822,21 +1822,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1846,10 +1846,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>478227</v>
+        <v>478135</v>
       </c>
       <c r="R13" t="n">
-        <v>6827655</v>
+        <v>6827625</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -4152,10 +4152,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>120075039</v>
+        <v>120075054</v>
       </c>
       <c r="B36" t="n">
-        <v>78262</v>
+        <v>90580</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4168,21 +4168,21 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6446</v>
+        <v>5432</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4192,10 +4192,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>478238</v>
+        <v>478126</v>
       </c>
       <c r="R36" t="n">
-        <v>6827752</v>
+        <v>6827477</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4254,10 +4254,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>120075239</v>
+        <v>120075147</v>
       </c>
       <c r="B37" t="n">
-        <v>77458</v>
+        <v>78526</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4270,21 +4270,21 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6487</v>
+        <v>6425</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Blågrå svartspik</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Chaenothecopsis fennica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Laurila) Tibell</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4294,10 +4294,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>478137</v>
+        <v>478153</v>
       </c>
       <c r="R37" t="n">
-        <v>6827554</v>
+        <v>6827728</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4356,7 +4356,7 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>120075147</v>
+        <v>120075173</v>
       </c>
       <c r="B38" t="n">
         <v>78526</v>
@@ -4396,10 +4396,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>478153</v>
+        <v>478052</v>
       </c>
       <c r="R38" t="n">
-        <v>6827728</v>
+        <v>6827754</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4458,7 +4458,7 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>120075173</v>
+        <v>120075074</v>
       </c>
       <c r="B39" t="n">
         <v>78526</v>
@@ -4498,10 +4498,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>478052</v>
+        <v>478138</v>
       </c>
       <c r="R39" t="n">
-        <v>6827754</v>
+        <v>6827599</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4560,7 +4560,7 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>120075074</v>
+        <v>120075063</v>
       </c>
       <c r="B40" t="n">
         <v>78526</v>
@@ -4600,10 +4600,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>478138</v>
+        <v>478201</v>
       </c>
       <c r="R40" t="n">
-        <v>6827599</v>
+        <v>6827693</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4662,7 +4662,7 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>120075063</v>
+        <v>120075145</v>
       </c>
       <c r="B41" t="n">
         <v>78526</v>
@@ -4702,10 +4702,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>478201</v>
+        <v>478226</v>
       </c>
       <c r="R41" t="n">
-        <v>6827693</v>
+        <v>6827777</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4764,7 +4764,7 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>120075145</v>
+        <v>120075174</v>
       </c>
       <c r="B42" t="n">
         <v>78526</v>
@@ -4804,10 +4804,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>478226</v>
+        <v>478057</v>
       </c>
       <c r="R42" t="n">
-        <v>6827777</v>
+        <v>6827749</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4866,10 +4866,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>120075174</v>
+        <v>120075039</v>
       </c>
       <c r="B43" t="n">
-        <v>78526</v>
+        <v>78262</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -4882,21 +4882,21 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -4906,10 +4906,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>478057</v>
+        <v>478238</v>
       </c>
       <c r="R43" t="n">
-        <v>6827749</v>
+        <v>6827752</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -4968,10 +4968,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>120075054</v>
+        <v>120075239</v>
       </c>
       <c r="B44" t="n">
-        <v>90580</v>
+        <v>77458</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -4984,21 +4984,21 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>5432</v>
+        <v>6487</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Blågrå svartspik</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Chaenothecopsis fennica</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Laurila) Tibell</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -5008,10 +5008,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>478126</v>
+        <v>478137</v>
       </c>
       <c r="R44" t="n">
-        <v>6827477</v>
+        <v>6827554</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5988,10 +5988,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>120075165</v>
+        <v>120074943</v>
       </c>
       <c r="B54" t="n">
-        <v>78526</v>
+        <v>79144</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
@@ -6004,21 +6004,21 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -6028,10 +6028,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>478078</v>
+        <v>478073</v>
       </c>
       <c r="R54" t="n">
-        <v>6827834</v>
+        <v>6827827</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6090,10 +6090,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>120075177</v>
+        <v>120074883</v>
       </c>
       <c r="B55" t="n">
-        <v>78526</v>
+        <v>79144</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
@@ -6106,21 +6106,21 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -6130,10 +6130,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>478075</v>
+        <v>478142</v>
       </c>
       <c r="R55" t="n">
-        <v>6827717</v>
+        <v>6827623</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6192,10 +6192,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>120075060</v>
+        <v>120075038</v>
       </c>
       <c r="B56" t="n">
-        <v>78526</v>
+        <v>78262</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
@@ -6208,21 +6208,21 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -6232,10 +6232,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>478087</v>
+        <v>478261</v>
       </c>
       <c r="R56" t="n">
-        <v>6827718</v>
+        <v>6827731</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6294,10 +6294,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>120074883</v>
+        <v>120075027</v>
       </c>
       <c r="B57" t="n">
-        <v>79144</v>
+        <v>78262</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
@@ -6310,21 +6310,21 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>6453</v>
+        <v>6446</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -6334,10 +6334,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>478142</v>
+        <v>478144</v>
       </c>
       <c r="R57" t="n">
-        <v>6827623</v>
+        <v>6827593</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6396,10 +6396,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>120075038</v>
+        <v>120075165</v>
       </c>
       <c r="B58" t="n">
-        <v>78262</v>
+        <v>78526</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
@@ -6412,21 +6412,21 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
@@ -6436,10 +6436,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>478261</v>
+        <v>478078</v>
       </c>
       <c r="R58" t="n">
-        <v>6827731</v>
+        <v>6827834</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6498,10 +6498,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>120075027</v>
+        <v>120075177</v>
       </c>
       <c r="B59" t="n">
-        <v>78262</v>
+        <v>78526</v>
       </c>
       <c r="C59" t="inlineStr">
         <is>
@@ -6514,21 +6514,21 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
@@ -6538,10 +6538,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>478144</v>
+        <v>478075</v>
       </c>
       <c r="R59" t="n">
-        <v>6827593</v>
+        <v>6827717</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6600,10 +6600,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>120074943</v>
+        <v>120075060</v>
       </c>
       <c r="B60" t="n">
-        <v>79144</v>
+        <v>78526</v>
       </c>
       <c r="C60" t="inlineStr">
         <is>
@@ -6616,21 +6616,21 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
@@ -6640,10 +6640,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>478073</v>
+        <v>478087</v>
       </c>
       <c r="R60" t="n">
-        <v>6827827</v>
+        <v>6827718</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -10272,10 +10272,10 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>120074934</v>
+        <v>120074956</v>
       </c>
       <c r="B96" t="n">
-        <v>79144</v>
+        <v>57310</v>
       </c>
       <c r="C96" t="inlineStr">
         <is>
@@ -10288,34 +10288,39 @@
         </is>
       </c>
       <c r="E96" t="n">
-        <v>6453</v>
+        <v>100109</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I96" t="inlineStr"/>
+      <c r="M96" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P96" t="inlineStr">
         <is>
           <t>Hevoslamm, Dlr</t>
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>478169</v>
+        <v>478278</v>
       </c>
       <c r="R96" t="n">
-        <v>6827760</v>
+        <v>6827832</v>
       </c>
       <c r="S96" t="n">
         <v>10</v>
@@ -10348,6 +10353,11 @@
       <c r="AA96" t="inlineStr">
         <is>
           <t>2024-09-27</t>
+        </is>
+      </c>
+      <c r="AC96" t="inlineStr">
+        <is>
+          <t>Färska ringhack (tall)</t>
         </is>
       </c>
       <c r="AD96" t="b">
@@ -10374,10 +10384,10 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>120075028</v>
+        <v>120074934</v>
       </c>
       <c r="B97" t="n">
-        <v>78262</v>
+        <v>79144</v>
       </c>
       <c r="C97" t="inlineStr">
         <is>
@@ -10390,21 +10400,21 @@
         </is>
       </c>
       <c r="E97" t="n">
-        <v>6446</v>
+        <v>6453</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I97" t="inlineStr"/>
@@ -10414,10 +10424,10 @@
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>478137</v>
+        <v>478169</v>
       </c>
       <c r="R97" t="n">
-        <v>6827553</v>
+        <v>6827760</v>
       </c>
       <c r="S97" t="n">
         <v>10</v>
@@ -10476,10 +10486,10 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>120074956</v>
+        <v>120075028</v>
       </c>
       <c r="B98" t="n">
-        <v>57310</v>
+        <v>78262</v>
       </c>
       <c r="C98" t="inlineStr">
         <is>
@@ -10492,39 +10502,34 @@
         </is>
       </c>
       <c r="E98" t="n">
-        <v>100109</v>
+        <v>6446</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I98" t="inlineStr"/>
-      <c r="M98" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P98" t="inlineStr">
         <is>
           <t>Hevoslamm, Dlr</t>
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>478278</v>
+        <v>478137</v>
       </c>
       <c r="R98" t="n">
-        <v>6827832</v>
+        <v>6827553</v>
       </c>
       <c r="S98" t="n">
         <v>10</v>
@@ -10557,11 +10562,6 @@
       <c r="AA98" t="inlineStr">
         <is>
           <t>2024-09-27</t>
-        </is>
-      </c>
-      <c r="AC98" t="inlineStr">
-        <is>
-          <t>Färska ringhack (tall)</t>
         </is>
       </c>
       <c r="AD98" t="b">
@@ -13036,10 +13036,10 @@
     </row>
     <row r="123">
       <c r="A123" t="n">
-        <v>120075008</v>
+        <v>120075035</v>
       </c>
       <c r="B123" t="n">
-        <v>78263</v>
+        <v>78262</v>
       </c>
       <c r="C123" t="inlineStr">
         <is>
@@ -13052,21 +13052,21 @@
         </is>
       </c>
       <c r="E123" t="n">
-        <v>228912</v>
+        <v>6446</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I123" t="inlineStr"/>
@@ -13076,10 +13076,10 @@
         </is>
       </c>
       <c r="Q123" t="n">
-        <v>478299</v>
+        <v>478273</v>
       </c>
       <c r="R123" t="n">
-        <v>6827805</v>
+        <v>6827711</v>
       </c>
       <c r="S123" t="n">
         <v>10</v>
@@ -13138,10 +13138,10 @@
     </row>
     <row r="124">
       <c r="A124" t="n">
-        <v>120075192</v>
+        <v>120074941</v>
       </c>
       <c r="B124" t="n">
-        <v>78526</v>
+        <v>79144</v>
       </c>
       <c r="C124" t="inlineStr">
         <is>
@@ -13154,21 +13154,21 @@
         </is>
       </c>
       <c r="E124" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I124" t="inlineStr"/>
@@ -13178,10 +13178,10 @@
         </is>
       </c>
       <c r="Q124" t="n">
-        <v>478282</v>
+        <v>478069</v>
       </c>
       <c r="R124" t="n">
-        <v>6827683</v>
+        <v>6827854</v>
       </c>
       <c r="S124" t="n">
         <v>10</v>
@@ -13240,10 +13240,10 @@
     </row>
     <row r="125">
       <c r="A125" t="n">
-        <v>120075135</v>
+        <v>120075008</v>
       </c>
       <c r="B125" t="n">
-        <v>78526</v>
+        <v>78263</v>
       </c>
       <c r="C125" t="inlineStr">
         <is>
@@ -13256,21 +13256,21 @@
         </is>
       </c>
       <c r="E125" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I125" t="inlineStr"/>
@@ -13280,10 +13280,10 @@
         </is>
       </c>
       <c r="Q125" t="n">
-        <v>478291</v>
+        <v>478299</v>
       </c>
       <c r="R125" t="n">
-        <v>6827744</v>
+        <v>6827805</v>
       </c>
       <c r="S125" t="n">
         <v>10</v>
@@ -13342,7 +13342,7 @@
     </row>
     <row r="126">
       <c r="A126" t="n">
-        <v>120075085</v>
+        <v>120075192</v>
       </c>
       <c r="B126" t="n">
         <v>78526</v>
@@ -13382,10 +13382,10 @@
         </is>
       </c>
       <c r="Q126" t="n">
-        <v>478094</v>
+        <v>478282</v>
       </c>
       <c r="R126" t="n">
-        <v>6827504</v>
+        <v>6827683</v>
       </c>
       <c r="S126" t="n">
         <v>10</v>
@@ -13444,7 +13444,7 @@
     </row>
     <row r="127">
       <c r="A127" t="n">
-        <v>120075065</v>
+        <v>120075135</v>
       </c>
       <c r="B127" t="n">
         <v>78526</v>
@@ -13484,10 +13484,10 @@
         </is>
       </c>
       <c r="Q127" t="n">
-        <v>478169</v>
+        <v>478291</v>
       </c>
       <c r="R127" t="n">
-        <v>6827679</v>
+        <v>6827744</v>
       </c>
       <c r="S127" t="n">
         <v>10</v>
@@ -13546,7 +13546,7 @@
     </row>
     <row r="128">
       <c r="A128" t="n">
-        <v>120075164</v>
+        <v>120075085</v>
       </c>
       <c r="B128" t="n">
         <v>78526</v>
@@ -13586,10 +13586,10 @@
         </is>
       </c>
       <c r="Q128" t="n">
-        <v>478092</v>
+        <v>478094</v>
       </c>
       <c r="R128" t="n">
-        <v>6827810</v>
+        <v>6827504</v>
       </c>
       <c r="S128" t="n">
         <v>10</v>
@@ -13648,7 +13648,7 @@
     </row>
     <row r="129">
       <c r="A129" t="n">
-        <v>120075078</v>
+        <v>120075095</v>
       </c>
       <c r="B129" t="n">
         <v>78526</v>
@@ -13688,10 +13688,10 @@
         </is>
       </c>
       <c r="Q129" t="n">
-        <v>478116</v>
+        <v>478219</v>
       </c>
       <c r="R129" t="n">
-        <v>6827567</v>
+        <v>6827572</v>
       </c>
       <c r="S129" t="n">
         <v>10</v>
@@ -13750,7 +13750,7 @@
     </row>
     <row r="130">
       <c r="A130" t="n">
-        <v>120075068</v>
+        <v>120075065</v>
       </c>
       <c r="B130" t="n">
         <v>78526</v>
@@ -13790,10 +13790,10 @@
         </is>
       </c>
       <c r="Q130" t="n">
-        <v>478174</v>
+        <v>478169</v>
       </c>
       <c r="R130" t="n">
-        <v>6827656</v>
+        <v>6827679</v>
       </c>
       <c r="S130" t="n">
         <v>10</v>
@@ -13852,10 +13852,10 @@
     </row>
     <row r="131">
       <c r="A131" t="n">
-        <v>120075035</v>
+        <v>120075164</v>
       </c>
       <c r="B131" t="n">
-        <v>78262</v>
+        <v>78526</v>
       </c>
       <c r="C131" t="inlineStr">
         <is>
@@ -13868,21 +13868,21 @@
         </is>
       </c>
       <c r="E131" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H131" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I131" t="inlineStr"/>
@@ -13892,10 +13892,10 @@
         </is>
       </c>
       <c r="Q131" t="n">
-        <v>478273</v>
+        <v>478092</v>
       </c>
       <c r="R131" t="n">
-        <v>6827711</v>
+        <v>6827810</v>
       </c>
       <c r="S131" t="n">
         <v>10</v>
@@ -13954,10 +13954,10 @@
     </row>
     <row r="132">
       <c r="A132" t="n">
-        <v>120074941</v>
+        <v>120075078</v>
       </c>
       <c r="B132" t="n">
-        <v>79144</v>
+        <v>78526</v>
       </c>
       <c r="C132" t="inlineStr">
         <is>
@@ -13970,21 +13970,21 @@
         </is>
       </c>
       <c r="E132" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H132" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I132" t="inlineStr"/>
@@ -13994,10 +13994,10 @@
         </is>
       </c>
       <c r="Q132" t="n">
-        <v>478069</v>
+        <v>478116</v>
       </c>
       <c r="R132" t="n">
-        <v>6827854</v>
+        <v>6827567</v>
       </c>
       <c r="S132" t="n">
         <v>10</v>
@@ -14056,7 +14056,7 @@
     </row>
     <row r="133">
       <c r="A133" t="n">
-        <v>120075095</v>
+        <v>120075068</v>
       </c>
       <c r="B133" t="n">
         <v>78526</v>
@@ -14096,10 +14096,10 @@
         </is>
       </c>
       <c r="Q133" t="n">
-        <v>478219</v>
+        <v>478174</v>
       </c>
       <c r="R133" t="n">
-        <v>6827572</v>
+        <v>6827656</v>
       </c>
       <c r="S133" t="n">
         <v>10</v>
@@ -17014,7 +17014,7 @@
     </row>
     <row r="162">
       <c r="A162" t="n">
-        <v>120075026</v>
+        <v>120075043</v>
       </c>
       <c r="B162" t="n">
         <v>78262</v>
@@ -17054,10 +17054,10 @@
         </is>
       </c>
       <c r="Q162" t="n">
-        <v>478161</v>
+        <v>478103</v>
       </c>
       <c r="R162" t="n">
-        <v>6827592</v>
+        <v>6827803</v>
       </c>
       <c r="S162" t="n">
         <v>10</v>
@@ -17116,10 +17116,10 @@
     </row>
     <row r="163">
       <c r="A163" t="n">
-        <v>120075046</v>
+        <v>120075048</v>
       </c>
       <c r="B163" t="n">
-        <v>78262</v>
+        <v>56514</v>
       </c>
       <c r="C163" t="inlineStr">
         <is>
@@ -17132,34 +17132,39 @@
         </is>
       </c>
       <c r="E163" t="n">
-        <v>6446</v>
+        <v>102612</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G163" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H163" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I163" t="inlineStr"/>
+      <c r="M163" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="P163" t="inlineStr">
         <is>
           <t>Hevoslamm, Dlr</t>
         </is>
       </c>
       <c r="Q163" t="n">
-        <v>478285</v>
+        <v>478070</v>
       </c>
       <c r="R163" t="n">
-        <v>6827770</v>
+        <v>6827723</v>
       </c>
       <c r="S163" t="n">
         <v>10</v>
@@ -17218,10 +17223,10 @@
     </row>
     <row r="164">
       <c r="A164" t="n">
-        <v>120075043</v>
+        <v>120075214</v>
       </c>
       <c r="B164" t="n">
-        <v>78262</v>
+        <v>78171</v>
       </c>
       <c r="C164" t="inlineStr">
         <is>
@@ -17234,21 +17239,21 @@
         </is>
       </c>
       <c r="E164" t="n">
-        <v>6446</v>
+        <v>353</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G164" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H164" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I164" t="inlineStr"/>
@@ -17258,10 +17263,10 @@
         </is>
       </c>
       <c r="Q164" t="n">
-        <v>478103</v>
+        <v>478266</v>
       </c>
       <c r="R164" t="n">
-        <v>6827803</v>
+        <v>6827724</v>
       </c>
       <c r="S164" t="n">
         <v>10</v>
@@ -17320,10 +17325,10 @@
     </row>
     <row r="165">
       <c r="A165" t="n">
-        <v>120075048</v>
+        <v>120075203</v>
       </c>
       <c r="B165" t="n">
-        <v>56514</v>
+        <v>78171</v>
       </c>
       <c r="C165" t="inlineStr">
         <is>
@@ -17336,39 +17341,34 @@
         </is>
       </c>
       <c r="E165" t="n">
-        <v>102612</v>
+        <v>353</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G165" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H165" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I165" t="inlineStr"/>
-      <c r="M165" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
       <c r="P165" t="inlineStr">
         <is>
           <t>Hevoslamm, Dlr</t>
         </is>
       </c>
       <c r="Q165" t="n">
-        <v>478070</v>
+        <v>478125</v>
       </c>
       <c r="R165" t="n">
-        <v>6827723</v>
+        <v>6827631</v>
       </c>
       <c r="S165" t="n">
         <v>10</v>
@@ -17427,10 +17427,10 @@
     </row>
     <row r="166">
       <c r="A166" t="n">
-        <v>120075012</v>
+        <v>120075026</v>
       </c>
       <c r="B166" t="n">
-        <v>78263</v>
+        <v>78262</v>
       </c>
       <c r="C166" t="inlineStr">
         <is>
@@ -17443,21 +17443,21 @@
         </is>
       </c>
       <c r="E166" t="n">
-        <v>228912</v>
+        <v>6446</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G166" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H166" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I166" t="inlineStr"/>
@@ -17467,10 +17467,10 @@
         </is>
       </c>
       <c r="Q166" t="n">
-        <v>478055</v>
+        <v>478161</v>
       </c>
       <c r="R166" t="n">
-        <v>6827786</v>
+        <v>6827592</v>
       </c>
       <c r="S166" t="n">
         <v>10</v>
@@ -17529,10 +17529,10 @@
     </row>
     <row r="167">
       <c r="A167" t="n">
-        <v>120075001</v>
+        <v>120075046</v>
       </c>
       <c r="B167" t="n">
-        <v>78263</v>
+        <v>78262</v>
       </c>
       <c r="C167" t="inlineStr">
         <is>
@@ -17545,21 +17545,21 @@
         </is>
       </c>
       <c r="E167" t="n">
-        <v>228912</v>
+        <v>6446</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G167" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H167" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I167" t="inlineStr"/>
@@ -17569,10 +17569,10 @@
         </is>
       </c>
       <c r="Q167" t="n">
-        <v>478125</v>
+        <v>478285</v>
       </c>
       <c r="R167" t="n">
-        <v>6827604</v>
+        <v>6827770</v>
       </c>
       <c r="S167" t="n">
         <v>10</v>
@@ -17631,7 +17631,7 @@
     </row>
     <row r="168">
       <c r="A168" t="n">
-        <v>120075010</v>
+        <v>120075012</v>
       </c>
       <c r="B168" t="n">
         <v>78263</v>
@@ -17671,10 +17671,10 @@
         </is>
       </c>
       <c r="Q168" t="n">
-        <v>478074</v>
+        <v>478055</v>
       </c>
       <c r="R168" t="n">
-        <v>6827772</v>
+        <v>6827786</v>
       </c>
       <c r="S168" t="n">
         <v>10</v>
@@ -17733,10 +17733,10 @@
     </row>
     <row r="169">
       <c r="A169" t="n">
-        <v>120075214</v>
+        <v>120075001</v>
       </c>
       <c r="B169" t="n">
-        <v>78171</v>
+        <v>78263</v>
       </c>
       <c r="C169" t="inlineStr">
         <is>
@@ -17749,21 +17749,21 @@
         </is>
       </c>
       <c r="E169" t="n">
-        <v>353</v>
+        <v>228912</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G169" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H169" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I169" t="inlineStr"/>
@@ -17773,10 +17773,10 @@
         </is>
       </c>
       <c r="Q169" t="n">
-        <v>478266</v>
+        <v>478125</v>
       </c>
       <c r="R169" t="n">
-        <v>6827724</v>
+        <v>6827604</v>
       </c>
       <c r="S169" t="n">
         <v>10</v>
@@ -17835,10 +17835,10 @@
     </row>
     <row r="170">
       <c r="A170" t="n">
-        <v>120075203</v>
+        <v>120075010</v>
       </c>
       <c r="B170" t="n">
-        <v>78171</v>
+        <v>78263</v>
       </c>
       <c r="C170" t="inlineStr">
         <is>
@@ -17851,21 +17851,21 @@
         </is>
       </c>
       <c r="E170" t="n">
-        <v>353</v>
+        <v>228912</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G170" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H170" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I170" t="inlineStr"/>
@@ -17875,10 +17875,10 @@
         </is>
       </c>
       <c r="Q170" t="n">
-        <v>478125</v>
+        <v>478074</v>
       </c>
       <c r="R170" t="n">
-        <v>6827631</v>
+        <v>6827772</v>
       </c>
       <c r="S170" t="n">
         <v>10</v>
@@ -18753,7 +18753,7 @@
     </row>
     <row r="179">
       <c r="A179" t="n">
-        <v>120074885</v>
+        <v>120074887</v>
       </c>
       <c r="B179" t="n">
         <v>79144</v>
@@ -18793,10 +18793,10 @@
         </is>
       </c>
       <c r="Q179" t="n">
-        <v>478115</v>
+        <v>478144</v>
       </c>
       <c r="R179" t="n">
-        <v>6827614</v>
+        <v>6827593</v>
       </c>
       <c r="S179" t="n">
         <v>10</v>
@@ -18855,10 +18855,10 @@
     </row>
     <row r="180">
       <c r="A180" t="n">
-        <v>120074887</v>
+        <v>120075087</v>
       </c>
       <c r="B180" t="n">
-        <v>79144</v>
+        <v>78526</v>
       </c>
       <c r="C180" t="inlineStr">
         <is>
@@ -18871,21 +18871,21 @@
         </is>
       </c>
       <c r="E180" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G180" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H180" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I180" t="inlineStr"/>
@@ -18895,10 +18895,10 @@
         </is>
       </c>
       <c r="Q180" t="n">
-        <v>478144</v>
+        <v>478145</v>
       </c>
       <c r="R180" t="n">
-        <v>6827593</v>
+        <v>6827485</v>
       </c>
       <c r="S180" t="n">
         <v>10</v>
@@ -18957,10 +18957,10 @@
     </row>
     <row r="181">
       <c r="A181" t="n">
-        <v>120075087</v>
+        <v>120074885</v>
       </c>
       <c r="B181" t="n">
-        <v>78526</v>
+        <v>79144</v>
       </c>
       <c r="C181" t="inlineStr">
         <is>
@@ -18973,21 +18973,21 @@
         </is>
       </c>
       <c r="E181" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G181" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H181" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I181" t="inlineStr"/>
@@ -18997,10 +18997,10 @@
         </is>
       </c>
       <c r="Q181" t="n">
-        <v>478145</v>
+        <v>478115</v>
       </c>
       <c r="R181" t="n">
-        <v>6827485</v>
+        <v>6827614</v>
       </c>
       <c r="S181" t="n">
         <v>10</v>

--- a/artfynd/A 32983-2023 artfynd.xlsx
+++ b/artfynd/A 32983-2023 artfynd.xlsx
@@ -777,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>120074932</v>
+        <v>120075207</v>
       </c>
       <c r="B3" t="n">
-        <v>79144</v>
+        <v>78171</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -793,21 +793,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6453</v>
+        <v>353</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -817,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>478250</v>
+        <v>478157</v>
       </c>
       <c r="R3" t="n">
-        <v>6827802</v>
+        <v>6827509</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -879,10 +879,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>120075207</v>
+        <v>120074932</v>
       </c>
       <c r="B4" t="n">
-        <v>78171</v>
+        <v>79144</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -895,21 +895,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>353</v>
+        <v>6453</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -919,10 +919,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>478157</v>
+        <v>478250</v>
       </c>
       <c r="R4" t="n">
-        <v>6827509</v>
+        <v>6827802</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -981,10 +981,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>120074999</v>
+        <v>120075197</v>
       </c>
       <c r="B5" t="n">
-        <v>78263</v>
+        <v>91840</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -993,38 +993,47 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>228912</v>
+        <v>4364</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr"/>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Hevoslamm, Dlr</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>478161</v>
+        <v>478077</v>
       </c>
       <c r="R5" t="n">
-        <v>6827592</v>
+        <v>6827805</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1083,10 +1092,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>120075011</v>
+        <v>120075127</v>
       </c>
       <c r="B6" t="n">
-        <v>78263</v>
+        <v>78526</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1099,21 +1108,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1123,10 +1132,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>478103</v>
+        <v>478292</v>
       </c>
       <c r="R6" t="n">
-        <v>6827803</v>
+        <v>6827708</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1185,10 +1194,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>120075013</v>
+        <v>120075070</v>
       </c>
       <c r="B7" t="n">
-        <v>78263</v>
+        <v>78526</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1201,21 +1210,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1225,10 +1234,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>478239</v>
+        <v>478135</v>
       </c>
       <c r="R7" t="n">
-        <v>6827752</v>
+        <v>6827625</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1287,10 +1296,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>120075197</v>
+        <v>120074999</v>
       </c>
       <c r="B8" t="n">
-        <v>91840</v>
+        <v>78263</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1299,47 +1308,38 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>4364</v>
+        <v>228912</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
           <t>Hevoslamm, Dlr</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>478077</v>
+        <v>478161</v>
       </c>
       <c r="R8" t="n">
-        <v>6827805</v>
+        <v>6827592</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1398,10 +1398,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>120075019</v>
+        <v>120075011</v>
       </c>
       <c r="B9" t="n">
-        <v>79607</v>
+        <v>78263</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1414,21 +1414,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6458</v>
+        <v>228912</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1438,10 +1438,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>478227</v>
+        <v>478103</v>
       </c>
       <c r="R9" t="n">
-        <v>6827655</v>
+        <v>6827803</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1500,10 +1500,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>120074925</v>
+        <v>120075013</v>
       </c>
       <c r="B10" t="n">
-        <v>78560</v>
+        <v>78263</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1516,21 +1516,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>185</v>
+        <v>228912</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1540,10 +1540,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>478088</v>
+        <v>478239</v>
       </c>
       <c r="R10" t="n">
-        <v>6827834</v>
+        <v>6827752</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1602,7 +1602,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>120074912</v>
+        <v>120074925</v>
       </c>
       <c r="B11" t="n">
         <v>78560</v>
@@ -1642,10 +1642,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>478149</v>
+        <v>478088</v>
       </c>
       <c r="R11" t="n">
-        <v>6827714</v>
+        <v>6827834</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1704,10 +1704,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>120075127</v>
+        <v>120074912</v>
       </c>
       <c r="B12" t="n">
-        <v>78526</v>
+        <v>78560</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1720,21 +1720,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1744,10 +1744,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>478292</v>
+        <v>478149</v>
       </c>
       <c r="R12" t="n">
-        <v>6827708</v>
+        <v>6827714</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1806,10 +1806,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>120075070</v>
+        <v>120075019</v>
       </c>
       <c r="B13" t="n">
-        <v>78526</v>
+        <v>79607</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1822,21 +1822,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1846,10 +1846,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>478135</v>
+        <v>478227</v>
       </c>
       <c r="R13" t="n">
-        <v>6827625</v>
+        <v>6827655</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -3642,10 +3642,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>120075219</v>
+        <v>120074996</v>
       </c>
       <c r="B31" t="n">
-        <v>78171</v>
+        <v>78263</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3658,21 +3658,21 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>353</v>
+        <v>228912</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3682,10 +3682,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>478169</v>
+        <v>478165</v>
       </c>
       <c r="R31" t="n">
-        <v>6827760</v>
+        <v>6827712</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3744,10 +3744,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>120074915</v>
+        <v>120075219</v>
       </c>
       <c r="B32" t="n">
-        <v>78560</v>
+        <v>78171</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -3760,21 +3760,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>185</v>
+        <v>353</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3784,10 +3784,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>478102</v>
+        <v>478169</v>
       </c>
       <c r="R32" t="n">
-        <v>6827555</v>
+        <v>6827760</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3846,10 +3846,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>120074881</v>
+        <v>120074915</v>
       </c>
       <c r="B33" t="n">
-        <v>79144</v>
+        <v>78560</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -3862,21 +3862,21 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6453</v>
+        <v>185</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -3886,10 +3886,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>478184</v>
+        <v>478102</v>
       </c>
       <c r="R33" t="n">
-        <v>6827728</v>
+        <v>6827555</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -3948,10 +3948,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>120075047</v>
+        <v>120074881</v>
       </c>
       <c r="B34" t="n">
-        <v>78262</v>
+        <v>79144</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -3964,21 +3964,21 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6446</v>
+        <v>6453</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -3988,10 +3988,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>478212</v>
+        <v>478184</v>
       </c>
       <c r="R34" t="n">
-        <v>6827573</v>
+        <v>6827728</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4050,10 +4050,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>120074996</v>
+        <v>120075047</v>
       </c>
       <c r="B35" t="n">
-        <v>78263</v>
+        <v>78262</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4066,21 +4066,21 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>228912</v>
+        <v>6446</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4090,10 +4090,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>478165</v>
+        <v>478212</v>
       </c>
       <c r="R35" t="n">
-        <v>6827712</v>
+        <v>6827573</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4152,10 +4152,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>120075054</v>
+        <v>120075039</v>
       </c>
       <c r="B36" t="n">
-        <v>90580</v>
+        <v>78262</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4168,21 +4168,21 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>5432</v>
+        <v>6446</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4192,10 +4192,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>478126</v>
+        <v>478238</v>
       </c>
       <c r="R36" t="n">
-        <v>6827477</v>
+        <v>6827752</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4254,10 +4254,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>120075147</v>
+        <v>120075239</v>
       </c>
       <c r="B37" t="n">
-        <v>78526</v>
+        <v>77458</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4270,21 +4270,21 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6425</v>
+        <v>6487</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Blågrå svartspik</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenothecopsis fennica</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Laurila) Tibell</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4294,10 +4294,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>478153</v>
+        <v>478137</v>
       </c>
       <c r="R37" t="n">
-        <v>6827728</v>
+        <v>6827554</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4356,7 +4356,7 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>120075173</v>
+        <v>120075147</v>
       </c>
       <c r="B38" t="n">
         <v>78526</v>
@@ -4396,10 +4396,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>478052</v>
+        <v>478153</v>
       </c>
       <c r="R38" t="n">
-        <v>6827754</v>
+        <v>6827728</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4458,7 +4458,7 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>120075074</v>
+        <v>120075173</v>
       </c>
       <c r="B39" t="n">
         <v>78526</v>
@@ -4498,10 +4498,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>478138</v>
+        <v>478052</v>
       </c>
       <c r="R39" t="n">
-        <v>6827599</v>
+        <v>6827754</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4560,7 +4560,7 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>120075063</v>
+        <v>120075074</v>
       </c>
       <c r="B40" t="n">
         <v>78526</v>
@@ -4600,10 +4600,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>478201</v>
+        <v>478138</v>
       </c>
       <c r="R40" t="n">
-        <v>6827693</v>
+        <v>6827599</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4662,7 +4662,7 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>120075145</v>
+        <v>120075063</v>
       </c>
       <c r="B41" t="n">
         <v>78526</v>
@@ -4702,10 +4702,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>478226</v>
+        <v>478201</v>
       </c>
       <c r="R41" t="n">
-        <v>6827777</v>
+        <v>6827693</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4764,7 +4764,7 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>120075174</v>
+        <v>120075145</v>
       </c>
       <c r="B42" t="n">
         <v>78526</v>
@@ -4804,10 +4804,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>478057</v>
+        <v>478226</v>
       </c>
       <c r="R42" t="n">
-        <v>6827749</v>
+        <v>6827777</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4866,10 +4866,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>120075039</v>
+        <v>120075174</v>
       </c>
       <c r="B43" t="n">
-        <v>78262</v>
+        <v>78526</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -4882,21 +4882,21 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -4906,10 +4906,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>478238</v>
+        <v>478057</v>
       </c>
       <c r="R43" t="n">
-        <v>6827752</v>
+        <v>6827749</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -4968,10 +4968,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>120075239</v>
+        <v>120075054</v>
       </c>
       <c r="B44" t="n">
-        <v>77458</v>
+        <v>90580</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -4984,21 +4984,21 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>6487</v>
+        <v>5432</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Blågrå svartspik</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Chaenothecopsis fennica</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Laurila) Tibell</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -5008,10 +5008,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>478137</v>
+        <v>478126</v>
       </c>
       <c r="R44" t="n">
-        <v>6827554</v>
+        <v>6827477</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5070,10 +5070,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>120074907</v>
+        <v>120075198</v>
       </c>
       <c r="B45" t="n">
-        <v>79144</v>
+        <v>91840</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5082,25 +5082,25 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>6453</v>
+        <v>4364</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5110,10 +5110,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>478263</v>
+        <v>478163</v>
       </c>
       <c r="R45" t="n">
-        <v>6827838</v>
+        <v>6827530</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5580,10 +5580,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>120075198</v>
+        <v>120074907</v>
       </c>
       <c r="B50" t="n">
-        <v>91840</v>
+        <v>79144</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -5592,25 +5592,25 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>4364</v>
+        <v>6453</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -5620,10 +5620,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>478163</v>
+        <v>478263</v>
       </c>
       <c r="R50" t="n">
-        <v>6827530</v>
+        <v>6827838</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5988,10 +5988,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>120074943</v>
+        <v>120075165</v>
       </c>
       <c r="B54" t="n">
-        <v>79144</v>
+        <v>78526</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
@@ -6004,21 +6004,21 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -6028,10 +6028,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>478073</v>
+        <v>478078</v>
       </c>
       <c r="R54" t="n">
-        <v>6827827</v>
+        <v>6827834</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6090,10 +6090,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>120074883</v>
+        <v>120075177</v>
       </c>
       <c r="B55" t="n">
-        <v>79144</v>
+        <v>78526</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
@@ -6106,21 +6106,21 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -6130,10 +6130,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>478142</v>
+        <v>478075</v>
       </c>
       <c r="R55" t="n">
-        <v>6827623</v>
+        <v>6827717</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6192,10 +6192,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>120075038</v>
+        <v>120075060</v>
       </c>
       <c r="B56" t="n">
-        <v>78262</v>
+        <v>78526</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
@@ -6208,21 +6208,21 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -6232,10 +6232,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>478261</v>
+        <v>478087</v>
       </c>
       <c r="R56" t="n">
-        <v>6827731</v>
+        <v>6827718</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6294,10 +6294,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>120075027</v>
+        <v>120074883</v>
       </c>
       <c r="B57" t="n">
-        <v>78262</v>
+        <v>79144</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
@@ -6310,21 +6310,21 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>6446</v>
+        <v>6453</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -6334,10 +6334,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>478144</v>
+        <v>478142</v>
       </c>
       <c r="R57" t="n">
-        <v>6827593</v>
+        <v>6827623</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6396,10 +6396,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>120075165</v>
+        <v>120075038</v>
       </c>
       <c r="B58" t="n">
-        <v>78526</v>
+        <v>78262</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
@@ -6412,21 +6412,21 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
@@ -6436,10 +6436,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>478078</v>
+        <v>478261</v>
       </c>
       <c r="R58" t="n">
-        <v>6827834</v>
+        <v>6827731</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6498,10 +6498,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>120075177</v>
+        <v>120075027</v>
       </c>
       <c r="B59" t="n">
-        <v>78526</v>
+        <v>78262</v>
       </c>
       <c r="C59" t="inlineStr">
         <is>
@@ -6514,21 +6514,21 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
@@ -6538,10 +6538,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>478075</v>
+        <v>478144</v>
       </c>
       <c r="R59" t="n">
-        <v>6827717</v>
+        <v>6827593</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6600,10 +6600,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>120075060</v>
+        <v>120074943</v>
       </c>
       <c r="B60" t="n">
-        <v>78526</v>
+        <v>79144</v>
       </c>
       <c r="C60" t="inlineStr">
         <is>
@@ -6616,21 +6616,21 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
@@ -6640,10 +6640,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>478087</v>
+        <v>478073</v>
       </c>
       <c r="R60" t="n">
-        <v>6827718</v>
+        <v>6827827</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -7314,10 +7314,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>120075166</v>
+        <v>120074939</v>
       </c>
       <c r="B67" t="n">
-        <v>78526</v>
+        <v>79144</v>
       </c>
       <c r="C67" t="inlineStr">
         <is>
@@ -7330,21 +7330,21 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
@@ -7354,10 +7354,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>478092</v>
+        <v>478091</v>
       </c>
       <c r="R67" t="n">
-        <v>6827839</v>
+        <v>6827838</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7416,7 +7416,7 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>120075130</v>
+        <v>120075166</v>
       </c>
       <c r="B68" t="n">
         <v>78526</v>
@@ -7456,10 +7456,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>478264</v>
+        <v>478092</v>
       </c>
       <c r="R68" t="n">
-        <v>6827733</v>
+        <v>6827839</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7518,7 +7518,7 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>120075134</v>
+        <v>120075130</v>
       </c>
       <c r="B69" t="n">
         <v>78526</v>
@@ -7558,10 +7558,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>478266</v>
+        <v>478264</v>
       </c>
       <c r="R69" t="n">
-        <v>6827765</v>
+        <v>6827733</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -7620,7 +7620,7 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>120075082</v>
+        <v>120075134</v>
       </c>
       <c r="B70" t="n">
         <v>78526</v>
@@ -7660,10 +7660,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>478097</v>
+        <v>478266</v>
       </c>
       <c r="R70" t="n">
-        <v>6827544</v>
+        <v>6827765</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -7722,7 +7722,7 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>120075131</v>
+        <v>120075082</v>
       </c>
       <c r="B71" t="n">
         <v>78526</v>
@@ -7762,10 +7762,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>478258</v>
+        <v>478097</v>
       </c>
       <c r="R71" t="n">
-        <v>6827731</v>
+        <v>6827544</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -7824,7 +7824,7 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>120075120</v>
+        <v>120075131</v>
       </c>
       <c r="B72" t="n">
         <v>78526</v>
@@ -7864,10 +7864,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>478223</v>
+        <v>478258</v>
       </c>
       <c r="R72" t="n">
-        <v>6827657</v>
+        <v>6827731</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -7926,10 +7926,10 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>120074939</v>
+        <v>120075120</v>
       </c>
       <c r="B73" t="n">
-        <v>79144</v>
+        <v>78526</v>
       </c>
       <c r="C73" t="inlineStr">
         <is>
@@ -7942,21 +7942,21 @@
         </is>
       </c>
       <c r="E73" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
@@ -7966,10 +7966,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>478091</v>
+        <v>478223</v>
       </c>
       <c r="R73" t="n">
-        <v>6827838</v>
+        <v>6827657</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -10272,10 +10272,10 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>120074956</v>
+        <v>120074934</v>
       </c>
       <c r="B96" t="n">
-        <v>57310</v>
+        <v>79144</v>
       </c>
       <c r="C96" t="inlineStr">
         <is>
@@ -10288,39 +10288,34 @@
         </is>
       </c>
       <c r="E96" t="n">
-        <v>100109</v>
+        <v>6453</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I96" t="inlineStr"/>
-      <c r="M96" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P96" t="inlineStr">
         <is>
           <t>Hevoslamm, Dlr</t>
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>478278</v>
+        <v>478169</v>
       </c>
       <c r="R96" t="n">
-        <v>6827832</v>
+        <v>6827760</v>
       </c>
       <c r="S96" t="n">
         <v>10</v>
@@ -10353,11 +10348,6 @@
       <c r="AA96" t="inlineStr">
         <is>
           <t>2024-09-27</t>
-        </is>
-      </c>
-      <c r="AC96" t="inlineStr">
-        <is>
-          <t>Färska ringhack (tall)</t>
         </is>
       </c>
       <c r="AD96" t="b">
@@ -10384,10 +10374,10 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>120074934</v>
+        <v>120075028</v>
       </c>
       <c r="B97" t="n">
-        <v>79144</v>
+        <v>78262</v>
       </c>
       <c r="C97" t="inlineStr">
         <is>
@@ -10400,21 +10390,21 @@
         </is>
       </c>
       <c r="E97" t="n">
-        <v>6453</v>
+        <v>6446</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I97" t="inlineStr"/>
@@ -10424,10 +10414,10 @@
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>478169</v>
+        <v>478137</v>
       </c>
       <c r="R97" t="n">
-        <v>6827760</v>
+        <v>6827553</v>
       </c>
       <c r="S97" t="n">
         <v>10</v>
@@ -10486,10 +10476,10 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>120075028</v>
+        <v>120074956</v>
       </c>
       <c r="B98" t="n">
-        <v>78262</v>
+        <v>57310</v>
       </c>
       <c r="C98" t="inlineStr">
         <is>
@@ -10502,34 +10492,39 @@
         </is>
       </c>
       <c r="E98" t="n">
-        <v>6446</v>
+        <v>100109</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I98" t="inlineStr"/>
+      <c r="M98" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P98" t="inlineStr">
         <is>
           <t>Hevoslamm, Dlr</t>
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>478137</v>
+        <v>478278</v>
       </c>
       <c r="R98" t="n">
-        <v>6827553</v>
+        <v>6827832</v>
       </c>
       <c r="S98" t="n">
         <v>10</v>
@@ -10562,6 +10557,11 @@
       <c r="AA98" t="inlineStr">
         <is>
           <t>2024-09-27</t>
+        </is>
+      </c>
+      <c r="AC98" t="inlineStr">
+        <is>
+          <t>Färska ringhack (tall)</t>
         </is>
       </c>
       <c r="AD98" t="b">
@@ -11914,10 +11914,10 @@
     </row>
     <row r="112">
       <c r="A112" t="n">
-        <v>120075176</v>
+        <v>120075201</v>
       </c>
       <c r="B112" t="n">
-        <v>78526</v>
+        <v>78171</v>
       </c>
       <c r="C112" t="inlineStr">
         <is>
@@ -11930,21 +11930,21 @@
         </is>
       </c>
       <c r="E112" t="n">
-        <v>6425</v>
+        <v>353</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I112" t="inlineStr"/>
@@ -11954,10 +11954,10 @@
         </is>
       </c>
       <c r="Q112" t="n">
-        <v>478066</v>
+        <v>478182</v>
       </c>
       <c r="R112" t="n">
-        <v>6827732</v>
+        <v>6827728</v>
       </c>
       <c r="S112" t="n">
         <v>10</v>
@@ -12016,10 +12016,10 @@
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>120075136</v>
+        <v>120075230</v>
       </c>
       <c r="B113" t="n">
-        <v>78526</v>
+        <v>78171</v>
       </c>
       <c r="C113" t="inlineStr">
         <is>
@@ -12032,21 +12032,21 @@
         </is>
       </c>
       <c r="E113" t="n">
-        <v>6425</v>
+        <v>353</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I113" t="inlineStr"/>
@@ -12056,10 +12056,10 @@
         </is>
       </c>
       <c r="Q113" t="n">
-        <v>478290</v>
+        <v>478064</v>
       </c>
       <c r="R113" t="n">
-        <v>6827758</v>
+        <v>6827866</v>
       </c>
       <c r="S113" t="n">
         <v>10</v>
@@ -12118,7 +12118,7 @@
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>120075137</v>
+        <v>120075176</v>
       </c>
       <c r="B114" t="n">
         <v>78526</v>
@@ -12158,10 +12158,10 @@
         </is>
       </c>
       <c r="Q114" t="n">
-        <v>478288</v>
+        <v>478066</v>
       </c>
       <c r="R114" t="n">
-        <v>6827763</v>
+        <v>6827732</v>
       </c>
       <c r="S114" t="n">
         <v>10</v>
@@ -12220,7 +12220,7 @@
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>120075075</v>
+        <v>120075136</v>
       </c>
       <c r="B115" t="n">
         <v>78526</v>
@@ -12260,10 +12260,10 @@
         </is>
       </c>
       <c r="Q115" t="n">
-        <v>478139</v>
+        <v>478290</v>
       </c>
       <c r="R115" t="n">
-        <v>6827554</v>
+        <v>6827758</v>
       </c>
       <c r="S115" t="n">
         <v>10</v>
@@ -12322,7 +12322,7 @@
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>120075129</v>
+        <v>120075137</v>
       </c>
       <c r="B116" t="n">
         <v>78526</v>
@@ -12362,10 +12362,10 @@
         </is>
       </c>
       <c r="Q116" t="n">
-        <v>478265</v>
+        <v>478288</v>
       </c>
       <c r="R116" t="n">
-        <v>6827707</v>
+        <v>6827763</v>
       </c>
       <c r="S116" t="n">
         <v>10</v>
@@ -12424,10 +12424,10 @@
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>120075042</v>
+        <v>120075075</v>
       </c>
       <c r="B117" t="n">
-        <v>78262</v>
+        <v>78526</v>
       </c>
       <c r="C117" t="inlineStr">
         <is>
@@ -12440,21 +12440,21 @@
         </is>
       </c>
       <c r="E117" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I117" t="inlineStr"/>
@@ -12464,10 +12464,10 @@
         </is>
       </c>
       <c r="Q117" t="n">
-        <v>478074</v>
+        <v>478139</v>
       </c>
       <c r="R117" t="n">
-        <v>6827775</v>
+        <v>6827554</v>
       </c>
       <c r="S117" t="n">
         <v>10</v>
@@ -12526,10 +12526,10 @@
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>120074931</v>
+        <v>120075129</v>
       </c>
       <c r="B118" t="n">
-        <v>79144</v>
+        <v>78526</v>
       </c>
       <c r="C118" t="inlineStr">
         <is>
@@ -12542,21 +12542,21 @@
         </is>
       </c>
       <c r="E118" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I118" t="inlineStr"/>
@@ -12566,10 +12566,10 @@
         </is>
       </c>
       <c r="Q118" t="n">
-        <v>478261</v>
+        <v>478265</v>
       </c>
       <c r="R118" t="n">
-        <v>6827822</v>
+        <v>6827707</v>
       </c>
       <c r="S118" t="n">
         <v>10</v>
@@ -12628,10 +12628,10 @@
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>120075201</v>
+        <v>120075042</v>
       </c>
       <c r="B119" t="n">
-        <v>78171</v>
+        <v>78262</v>
       </c>
       <c r="C119" t="inlineStr">
         <is>
@@ -12644,21 +12644,21 @@
         </is>
       </c>
       <c r="E119" t="n">
-        <v>353</v>
+        <v>6446</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I119" t="inlineStr"/>
@@ -12668,10 +12668,10 @@
         </is>
       </c>
       <c r="Q119" t="n">
-        <v>478182</v>
+        <v>478074</v>
       </c>
       <c r="R119" t="n">
-        <v>6827728</v>
+        <v>6827775</v>
       </c>
       <c r="S119" t="n">
         <v>10</v>
@@ -12730,10 +12730,10 @@
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>120075230</v>
+        <v>120074931</v>
       </c>
       <c r="B120" t="n">
-        <v>78171</v>
+        <v>79144</v>
       </c>
       <c r="C120" t="inlineStr">
         <is>
@@ -12746,21 +12746,21 @@
         </is>
       </c>
       <c r="E120" t="n">
-        <v>353</v>
+        <v>6453</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I120" t="inlineStr"/>
@@ -12770,10 +12770,10 @@
         </is>
       </c>
       <c r="Q120" t="n">
-        <v>478064</v>
+        <v>478261</v>
       </c>
       <c r="R120" t="n">
-        <v>6827866</v>
+        <v>6827822</v>
       </c>
       <c r="S120" t="n">
         <v>10</v>
@@ -18753,7 +18753,7 @@
     </row>
     <row r="179">
       <c r="A179" t="n">
-        <v>120074887</v>
+        <v>120074885</v>
       </c>
       <c r="B179" t="n">
         <v>79144</v>
@@ -18793,10 +18793,10 @@
         </is>
       </c>
       <c r="Q179" t="n">
-        <v>478144</v>
+        <v>478115</v>
       </c>
       <c r="R179" t="n">
-        <v>6827593</v>
+        <v>6827614</v>
       </c>
       <c r="S179" t="n">
         <v>10</v>
@@ -18855,10 +18855,10 @@
     </row>
     <row r="180">
       <c r="A180" t="n">
-        <v>120075087</v>
+        <v>120074887</v>
       </c>
       <c r="B180" t="n">
-        <v>78526</v>
+        <v>79144</v>
       </c>
       <c r="C180" t="inlineStr">
         <is>
@@ -18871,21 +18871,21 @@
         </is>
       </c>
       <c r="E180" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G180" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H180" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I180" t="inlineStr"/>
@@ -18895,10 +18895,10 @@
         </is>
       </c>
       <c r="Q180" t="n">
-        <v>478145</v>
+        <v>478144</v>
       </c>
       <c r="R180" t="n">
-        <v>6827485</v>
+        <v>6827593</v>
       </c>
       <c r="S180" t="n">
         <v>10</v>
@@ -18957,10 +18957,10 @@
     </row>
     <row r="181">
       <c r="A181" t="n">
-        <v>120074885</v>
+        <v>120075087</v>
       </c>
       <c r="B181" t="n">
-        <v>79144</v>
+        <v>78526</v>
       </c>
       <c r="C181" t="inlineStr">
         <is>
@@ -18973,21 +18973,21 @@
         </is>
       </c>
       <c r="E181" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G181" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H181" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I181" t="inlineStr"/>
@@ -18997,10 +18997,10 @@
         </is>
       </c>
       <c r="Q181" t="n">
-        <v>478115</v>
+        <v>478145</v>
       </c>
       <c r="R181" t="n">
-        <v>6827614</v>
+        <v>6827485</v>
       </c>
       <c r="S181" t="n">
         <v>10</v>

--- a/artfynd/A 32983-2023 artfynd.xlsx
+++ b/artfynd/A 32983-2023 artfynd.xlsx
@@ -5070,10 +5070,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>120075198</v>
+        <v>120074907</v>
       </c>
       <c r="B45" t="n">
-        <v>91840</v>
+        <v>79144</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5082,25 +5082,25 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>4364</v>
+        <v>6453</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5110,10 +5110,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>478163</v>
+        <v>478263</v>
       </c>
       <c r="R45" t="n">
-        <v>6827530</v>
+        <v>6827838</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5580,10 +5580,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>120074907</v>
+        <v>120075198</v>
       </c>
       <c r="B50" t="n">
-        <v>79144</v>
+        <v>91840</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -5592,25 +5592,25 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>6453</v>
+        <v>4364</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -5620,10 +5620,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>478263</v>
+        <v>478163</v>
       </c>
       <c r="R50" t="n">
-        <v>6827838</v>
+        <v>6827530</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -8232,10 +8232,10 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>120074930</v>
+        <v>120075161</v>
       </c>
       <c r="B76" t="n">
-        <v>79144</v>
+        <v>78526</v>
       </c>
       <c r="C76" t="inlineStr">
         <is>
@@ -8248,21 +8248,21 @@
         </is>
       </c>
       <c r="E76" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
@@ -8272,10 +8272,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>478299</v>
+        <v>478082</v>
       </c>
       <c r="R76" t="n">
-        <v>6827805</v>
+        <v>6827766</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -8334,10 +8334,10 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>120074944</v>
+        <v>120075121</v>
       </c>
       <c r="B77" t="n">
-        <v>79144</v>
+        <v>78526</v>
       </c>
       <c r="C77" t="inlineStr">
         <is>
@@ -8350,21 +8350,21 @@
         </is>
       </c>
       <c r="E77" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
@@ -8374,10 +8374,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>478056</v>
+        <v>478232</v>
       </c>
       <c r="R77" t="n">
-        <v>6827785</v>
+        <v>6827659</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -8436,10 +8436,10 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>120074904</v>
+        <v>120075077</v>
       </c>
       <c r="B78" t="n">
-        <v>79144</v>
+        <v>78526</v>
       </c>
       <c r="C78" t="inlineStr">
         <is>
@@ -8452,21 +8452,21 @@
         </is>
       </c>
       <c r="E78" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
@@ -8476,10 +8476,10 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>478262</v>
+        <v>478124</v>
       </c>
       <c r="R78" t="n">
-        <v>6827730</v>
+        <v>6827560</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -8538,10 +8538,10 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>120074889</v>
+        <v>120075175</v>
       </c>
       <c r="B79" t="n">
-        <v>79144</v>
+        <v>78526</v>
       </c>
       <c r="C79" t="inlineStr">
         <is>
@@ -8554,21 +8554,21 @@
         </is>
       </c>
       <c r="E79" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
@@ -8578,10 +8578,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>478163</v>
+        <v>478059</v>
       </c>
       <c r="R79" t="n">
-        <v>6827536</v>
+        <v>6827739</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -8640,7 +8640,7 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>120074946</v>
+        <v>120074930</v>
       </c>
       <c r="B80" t="n">
         <v>79144</v>
@@ -8680,10 +8680,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>478056</v>
+        <v>478299</v>
       </c>
       <c r="R80" t="n">
-        <v>6827754</v>
+        <v>6827805</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -8742,10 +8742,10 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>120075161</v>
+        <v>120074944</v>
       </c>
       <c r="B81" t="n">
-        <v>78526</v>
+        <v>79144</v>
       </c>
       <c r="C81" t="inlineStr">
         <is>
@@ -8758,21 +8758,21 @@
         </is>
       </c>
       <c r="E81" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
@@ -8782,10 +8782,10 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>478082</v>
+        <v>478056</v>
       </c>
       <c r="R81" t="n">
-        <v>6827766</v>
+        <v>6827785</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -8844,10 +8844,10 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>120075121</v>
+        <v>120074904</v>
       </c>
       <c r="B82" t="n">
-        <v>78526</v>
+        <v>79144</v>
       </c>
       <c r="C82" t="inlineStr">
         <is>
@@ -8860,21 +8860,21 @@
         </is>
       </c>
       <c r="E82" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
@@ -8884,10 +8884,10 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>478232</v>
+        <v>478262</v>
       </c>
       <c r="R82" t="n">
-        <v>6827659</v>
+        <v>6827730</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -8946,10 +8946,10 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>120075077</v>
+        <v>120074889</v>
       </c>
       <c r="B83" t="n">
-        <v>78526</v>
+        <v>79144</v>
       </c>
       <c r="C83" t="inlineStr">
         <is>
@@ -8962,21 +8962,21 @@
         </is>
       </c>
       <c r="E83" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
@@ -8986,10 +8986,10 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>478124</v>
+        <v>478163</v>
       </c>
       <c r="R83" t="n">
-        <v>6827560</v>
+        <v>6827536</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -9048,10 +9048,10 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>120075175</v>
+        <v>120074946</v>
       </c>
       <c r="B84" t="n">
-        <v>78526</v>
+        <v>79144</v>
       </c>
       <c r="C84" t="inlineStr">
         <is>
@@ -9064,21 +9064,21 @@
         </is>
       </c>
       <c r="E84" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
@@ -9088,10 +9088,10 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>478059</v>
+        <v>478056</v>
       </c>
       <c r="R84" t="n">
-        <v>6827739</v>
+        <v>6827754</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -10272,10 +10272,10 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>120074934</v>
+        <v>120074956</v>
       </c>
       <c r="B96" t="n">
-        <v>79144</v>
+        <v>57310</v>
       </c>
       <c r="C96" t="inlineStr">
         <is>
@@ -10288,34 +10288,39 @@
         </is>
       </c>
       <c r="E96" t="n">
-        <v>6453</v>
+        <v>100109</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I96" t="inlineStr"/>
+      <c r="M96" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P96" t="inlineStr">
         <is>
           <t>Hevoslamm, Dlr</t>
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>478169</v>
+        <v>478278</v>
       </c>
       <c r="R96" t="n">
-        <v>6827760</v>
+        <v>6827832</v>
       </c>
       <c r="S96" t="n">
         <v>10</v>
@@ -10348,6 +10353,11 @@
       <c r="AA96" t="inlineStr">
         <is>
           <t>2024-09-27</t>
+        </is>
+      </c>
+      <c r="AC96" t="inlineStr">
+        <is>
+          <t>Färska ringhack (tall)</t>
         </is>
       </c>
       <c r="AD96" t="b">
@@ -10374,10 +10384,10 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>120075028</v>
+        <v>120074934</v>
       </c>
       <c r="B97" t="n">
-        <v>78262</v>
+        <v>79144</v>
       </c>
       <c r="C97" t="inlineStr">
         <is>
@@ -10390,21 +10400,21 @@
         </is>
       </c>
       <c r="E97" t="n">
-        <v>6446</v>
+        <v>6453</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I97" t="inlineStr"/>
@@ -10414,10 +10424,10 @@
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>478137</v>
+        <v>478169</v>
       </c>
       <c r="R97" t="n">
-        <v>6827553</v>
+        <v>6827760</v>
       </c>
       <c r="S97" t="n">
         <v>10</v>
@@ -10476,10 +10486,10 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>120074956</v>
+        <v>120075028</v>
       </c>
       <c r="B98" t="n">
-        <v>57310</v>
+        <v>78262</v>
       </c>
       <c r="C98" t="inlineStr">
         <is>
@@ -10492,39 +10502,34 @@
         </is>
       </c>
       <c r="E98" t="n">
-        <v>100109</v>
+        <v>6446</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I98" t="inlineStr"/>
-      <c r="M98" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P98" t="inlineStr">
         <is>
           <t>Hevoslamm, Dlr</t>
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>478278</v>
+        <v>478137</v>
       </c>
       <c r="R98" t="n">
-        <v>6827832</v>
+        <v>6827553</v>
       </c>
       <c r="S98" t="n">
         <v>10</v>
@@ -10557,11 +10562,6 @@
       <c r="AA98" t="inlineStr">
         <is>
           <t>2024-09-27</t>
-        </is>
-      </c>
-      <c r="AC98" t="inlineStr">
-        <is>
-          <t>Färska ringhack (tall)</t>
         </is>
       </c>
       <c r="AD98" t="b">
@@ -10894,10 +10894,10 @@
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>120075216</v>
+        <v>120074952</v>
       </c>
       <c r="B102" t="n">
-        <v>78171</v>
+        <v>79115</v>
       </c>
       <c r="C102" t="inlineStr">
         <is>
@@ -10910,21 +10910,21 @@
         </is>
       </c>
       <c r="E102" t="n">
-        <v>353</v>
+        <v>229821</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I102" t="inlineStr"/>
@@ -10934,10 +10934,10 @@
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>478294</v>
+        <v>478120</v>
       </c>
       <c r="R102" t="n">
-        <v>6827790</v>
+        <v>6827605</v>
       </c>
       <c r="S102" t="n">
         <v>10</v>
@@ -10996,7 +10996,7 @@
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>120075215</v>
+        <v>120075216</v>
       </c>
       <c r="B103" t="n">
         <v>78171</v>
@@ -11036,10 +11036,10 @@
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>478239</v>
+        <v>478294</v>
       </c>
       <c r="R103" t="n">
-        <v>6827752</v>
+        <v>6827790</v>
       </c>
       <c r="S103" t="n">
         <v>10</v>
@@ -11098,10 +11098,10 @@
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>120074929</v>
+        <v>120075215</v>
       </c>
       <c r="B104" t="n">
-        <v>78560</v>
+        <v>78171</v>
       </c>
       <c r="C104" t="inlineStr">
         <is>
@@ -11114,21 +11114,21 @@
         </is>
       </c>
       <c r="E104" t="n">
-        <v>185</v>
+        <v>353</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I104" t="inlineStr"/>
@@ -11138,10 +11138,10 @@
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>478045</v>
+        <v>478239</v>
       </c>
       <c r="R104" t="n">
-        <v>6827724</v>
+        <v>6827752</v>
       </c>
       <c r="S104" t="n">
         <v>10</v>
@@ -11200,10 +11200,10 @@
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>120075224</v>
+        <v>120074929</v>
       </c>
       <c r="B105" t="n">
-        <v>78171</v>
+        <v>78560</v>
       </c>
       <c r="C105" t="inlineStr">
         <is>
@@ -11216,21 +11216,21 @@
         </is>
       </c>
       <c r="E105" t="n">
-        <v>353</v>
+        <v>185</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I105" t="inlineStr"/>
@@ -11240,10 +11240,10 @@
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>478081</v>
+        <v>478045</v>
       </c>
       <c r="R105" t="n">
-        <v>6827789</v>
+        <v>6827724</v>
       </c>
       <c r="S105" t="n">
         <v>10</v>
@@ -11302,7 +11302,7 @@
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>120075234</v>
+        <v>120075224</v>
       </c>
       <c r="B106" t="n">
         <v>78171</v>
@@ -11342,10 +11342,10 @@
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>478069</v>
+        <v>478081</v>
       </c>
       <c r="R106" t="n">
-        <v>6827741</v>
+        <v>6827789</v>
       </c>
       <c r="S106" t="n">
         <v>10</v>
@@ -11404,10 +11404,10 @@
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>120075088</v>
+        <v>120075234</v>
       </c>
       <c r="B107" t="n">
-        <v>78526</v>
+        <v>78171</v>
       </c>
       <c r="C107" t="inlineStr">
         <is>
@@ -11420,21 +11420,21 @@
         </is>
       </c>
       <c r="E107" t="n">
-        <v>6425</v>
+        <v>353</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I107" t="inlineStr"/>
@@ -11444,10 +11444,10 @@
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>478151</v>
+        <v>478069</v>
       </c>
       <c r="R107" t="n">
-        <v>6827509</v>
+        <v>6827741</v>
       </c>
       <c r="S107" t="n">
         <v>10</v>
@@ -11506,7 +11506,7 @@
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>120075140</v>
+        <v>120075088</v>
       </c>
       <c r="B108" t="n">
         <v>78526</v>
@@ -11546,10 +11546,10 @@
         </is>
       </c>
       <c r="Q108" t="n">
-        <v>478310</v>
+        <v>478151</v>
       </c>
       <c r="R108" t="n">
-        <v>6827797</v>
+        <v>6827509</v>
       </c>
       <c r="S108" t="n">
         <v>10</v>
@@ -11608,7 +11608,7 @@
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>120075128</v>
+        <v>120075140</v>
       </c>
       <c r="B109" t="n">
         <v>78526</v>
@@ -11648,10 +11648,10 @@
         </is>
       </c>
       <c r="Q109" t="n">
-        <v>478275</v>
+        <v>478310</v>
       </c>
       <c r="R109" t="n">
-        <v>6827710</v>
+        <v>6827797</v>
       </c>
       <c r="S109" t="n">
         <v>10</v>
@@ -11710,7 +11710,7 @@
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>120075171</v>
+        <v>120075128</v>
       </c>
       <c r="B110" t="n">
         <v>78526</v>
@@ -11750,10 +11750,10 @@
         </is>
       </c>
       <c r="Q110" t="n">
-        <v>478073</v>
+        <v>478275</v>
       </c>
       <c r="R110" t="n">
-        <v>6827831</v>
+        <v>6827710</v>
       </c>
       <c r="S110" t="n">
         <v>10</v>
@@ -11812,10 +11812,10 @@
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>120074952</v>
+        <v>120075171</v>
       </c>
       <c r="B111" t="n">
-        <v>79115</v>
+        <v>78526</v>
       </c>
       <c r="C111" t="inlineStr">
         <is>
@@ -11828,21 +11828,21 @@
         </is>
       </c>
       <c r="E111" t="n">
-        <v>229821</v>
+        <v>6425</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I111" t="inlineStr"/>
@@ -11852,10 +11852,10 @@
         </is>
       </c>
       <c r="Q111" t="n">
-        <v>478120</v>
+        <v>478073</v>
       </c>
       <c r="R111" t="n">
-        <v>6827605</v>
+        <v>6827831</v>
       </c>
       <c r="S111" t="n">
         <v>10</v>
@@ -13036,10 +13036,10 @@
     </row>
     <row r="123">
       <c r="A123" t="n">
-        <v>120075035</v>
+        <v>120075008</v>
       </c>
       <c r="B123" t="n">
-        <v>78262</v>
+        <v>78263</v>
       </c>
       <c r="C123" t="inlineStr">
         <is>
@@ -13052,21 +13052,21 @@
         </is>
       </c>
       <c r="E123" t="n">
-        <v>6446</v>
+        <v>228912</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I123" t="inlineStr"/>
@@ -13076,10 +13076,10 @@
         </is>
       </c>
       <c r="Q123" t="n">
-        <v>478273</v>
+        <v>478299</v>
       </c>
       <c r="R123" t="n">
-        <v>6827711</v>
+        <v>6827805</v>
       </c>
       <c r="S123" t="n">
         <v>10</v>
@@ -13138,10 +13138,10 @@
     </row>
     <row r="124">
       <c r="A124" t="n">
-        <v>120074941</v>
+        <v>120075192</v>
       </c>
       <c r="B124" t="n">
-        <v>79144</v>
+        <v>78526</v>
       </c>
       <c r="C124" t="inlineStr">
         <is>
@@ -13154,21 +13154,21 @@
         </is>
       </c>
       <c r="E124" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I124" t="inlineStr"/>
@@ -13178,10 +13178,10 @@
         </is>
       </c>
       <c r="Q124" t="n">
-        <v>478069</v>
+        <v>478282</v>
       </c>
       <c r="R124" t="n">
-        <v>6827854</v>
+        <v>6827683</v>
       </c>
       <c r="S124" t="n">
         <v>10</v>
@@ -13240,10 +13240,10 @@
     </row>
     <row r="125">
       <c r="A125" t="n">
-        <v>120075008</v>
+        <v>120075135</v>
       </c>
       <c r="B125" t="n">
-        <v>78263</v>
+        <v>78526</v>
       </c>
       <c r="C125" t="inlineStr">
         <is>
@@ -13256,21 +13256,21 @@
         </is>
       </c>
       <c r="E125" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I125" t="inlineStr"/>
@@ -13280,10 +13280,10 @@
         </is>
       </c>
       <c r="Q125" t="n">
-        <v>478299</v>
+        <v>478291</v>
       </c>
       <c r="R125" t="n">
-        <v>6827805</v>
+        <v>6827744</v>
       </c>
       <c r="S125" t="n">
         <v>10</v>
@@ -13342,7 +13342,7 @@
     </row>
     <row r="126">
       <c r="A126" t="n">
-        <v>120075192</v>
+        <v>120075085</v>
       </c>
       <c r="B126" t="n">
         <v>78526</v>
@@ -13382,10 +13382,10 @@
         </is>
       </c>
       <c r="Q126" t="n">
-        <v>478282</v>
+        <v>478094</v>
       </c>
       <c r="R126" t="n">
-        <v>6827683</v>
+        <v>6827504</v>
       </c>
       <c r="S126" t="n">
         <v>10</v>
@@ -13444,7 +13444,7 @@
     </row>
     <row r="127">
       <c r="A127" t="n">
-        <v>120075135</v>
+        <v>120075065</v>
       </c>
       <c r="B127" t="n">
         <v>78526</v>
@@ -13484,10 +13484,10 @@
         </is>
       </c>
       <c r="Q127" t="n">
-        <v>478291</v>
+        <v>478169</v>
       </c>
       <c r="R127" t="n">
-        <v>6827744</v>
+        <v>6827679</v>
       </c>
       <c r="S127" t="n">
         <v>10</v>
@@ -13546,7 +13546,7 @@
     </row>
     <row r="128">
       <c r="A128" t="n">
-        <v>120075085</v>
+        <v>120075164</v>
       </c>
       <c r="B128" t="n">
         <v>78526</v>
@@ -13586,10 +13586,10 @@
         </is>
       </c>
       <c r="Q128" t="n">
-        <v>478094</v>
+        <v>478092</v>
       </c>
       <c r="R128" t="n">
-        <v>6827504</v>
+        <v>6827810</v>
       </c>
       <c r="S128" t="n">
         <v>10</v>
@@ -13648,7 +13648,7 @@
     </row>
     <row r="129">
       <c r="A129" t="n">
-        <v>120075095</v>
+        <v>120075078</v>
       </c>
       <c r="B129" t="n">
         <v>78526</v>
@@ -13688,10 +13688,10 @@
         </is>
       </c>
       <c r="Q129" t="n">
-        <v>478219</v>
+        <v>478116</v>
       </c>
       <c r="R129" t="n">
-        <v>6827572</v>
+        <v>6827567</v>
       </c>
       <c r="S129" t="n">
         <v>10</v>
@@ -13750,7 +13750,7 @@
     </row>
     <row r="130">
       <c r="A130" t="n">
-        <v>120075065</v>
+        <v>120075068</v>
       </c>
       <c r="B130" t="n">
         <v>78526</v>
@@ -13790,10 +13790,10 @@
         </is>
       </c>
       <c r="Q130" t="n">
-        <v>478169</v>
+        <v>478174</v>
       </c>
       <c r="R130" t="n">
-        <v>6827679</v>
+        <v>6827656</v>
       </c>
       <c r="S130" t="n">
         <v>10</v>
@@ -13852,10 +13852,10 @@
     </row>
     <row r="131">
       <c r="A131" t="n">
-        <v>120075164</v>
+        <v>120075035</v>
       </c>
       <c r="B131" t="n">
-        <v>78526</v>
+        <v>78262</v>
       </c>
       <c r="C131" t="inlineStr">
         <is>
@@ -13868,21 +13868,21 @@
         </is>
       </c>
       <c r="E131" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H131" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I131" t="inlineStr"/>
@@ -13892,10 +13892,10 @@
         </is>
       </c>
       <c r="Q131" t="n">
-        <v>478092</v>
+        <v>478273</v>
       </c>
       <c r="R131" t="n">
-        <v>6827810</v>
+        <v>6827711</v>
       </c>
       <c r="S131" t="n">
         <v>10</v>
@@ -13954,10 +13954,10 @@
     </row>
     <row r="132">
       <c r="A132" t="n">
-        <v>120075078</v>
+        <v>120074941</v>
       </c>
       <c r="B132" t="n">
-        <v>78526</v>
+        <v>79144</v>
       </c>
       <c r="C132" t="inlineStr">
         <is>
@@ -13970,21 +13970,21 @@
         </is>
       </c>
       <c r="E132" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H132" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I132" t="inlineStr"/>
@@ -13994,10 +13994,10 @@
         </is>
       </c>
       <c r="Q132" t="n">
-        <v>478116</v>
+        <v>478069</v>
       </c>
       <c r="R132" t="n">
-        <v>6827567</v>
+        <v>6827854</v>
       </c>
       <c r="S132" t="n">
         <v>10</v>
@@ -14056,7 +14056,7 @@
     </row>
     <row r="133">
       <c r="A133" t="n">
-        <v>120075068</v>
+        <v>120075095</v>
       </c>
       <c r="B133" t="n">
         <v>78526</v>
@@ -14096,10 +14096,10 @@
         </is>
       </c>
       <c r="Q133" t="n">
-        <v>478174</v>
+        <v>478219</v>
       </c>
       <c r="R133" t="n">
-        <v>6827656</v>
+        <v>6827572</v>
       </c>
       <c r="S133" t="n">
         <v>10</v>
@@ -14158,10 +14158,10 @@
     </row>
     <row r="134">
       <c r="A134" t="n">
-        <v>120075044</v>
+        <v>120074927</v>
       </c>
       <c r="B134" t="n">
-        <v>78262</v>
+        <v>78560</v>
       </c>
       <c r="C134" t="inlineStr">
         <is>
@@ -14174,21 +14174,21 @@
         </is>
       </c>
       <c r="E134" t="n">
-        <v>6446</v>
+        <v>185</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H134" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I134" t="inlineStr"/>
@@ -14198,10 +14198,10 @@
         </is>
       </c>
       <c r="Q134" t="n">
-        <v>478060</v>
+        <v>478073</v>
       </c>
       <c r="R134" t="n">
-        <v>6827770</v>
+        <v>6827836</v>
       </c>
       <c r="S134" t="n">
         <v>10</v>
@@ -14260,10 +14260,10 @@
     </row>
     <row r="135">
       <c r="A135" t="n">
-        <v>120074927</v>
+        <v>120075225</v>
       </c>
       <c r="B135" t="n">
-        <v>78560</v>
+        <v>78171</v>
       </c>
       <c r="C135" t="inlineStr">
         <is>
@@ -14276,21 +14276,21 @@
         </is>
       </c>
       <c r="E135" t="n">
-        <v>185</v>
+        <v>353</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H135" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I135" t="inlineStr"/>
@@ -14300,10 +14300,10 @@
         </is>
       </c>
       <c r="Q135" t="n">
-        <v>478073</v>
+        <v>478075</v>
       </c>
       <c r="R135" t="n">
-        <v>6827836</v>
+        <v>6827798</v>
       </c>
       <c r="S135" t="n">
         <v>10</v>
@@ -14362,7 +14362,7 @@
     </row>
     <row r="136">
       <c r="A136" t="n">
-        <v>120075225</v>
+        <v>120075223</v>
       </c>
       <c r="B136" t="n">
         <v>78171</v>
@@ -14402,10 +14402,10 @@
         </is>
       </c>
       <c r="Q136" t="n">
-        <v>478075</v>
+        <v>478076</v>
       </c>
       <c r="R136" t="n">
-        <v>6827798</v>
+        <v>6827777</v>
       </c>
       <c r="S136" t="n">
         <v>10</v>
@@ -14464,10 +14464,10 @@
     </row>
     <row r="137">
       <c r="A137" t="n">
-        <v>120075223</v>
+        <v>120075142</v>
       </c>
       <c r="B137" t="n">
-        <v>78171</v>
+        <v>78526</v>
       </c>
       <c r="C137" t="inlineStr">
         <is>
@@ -14480,21 +14480,21 @@
         </is>
       </c>
       <c r="E137" t="n">
-        <v>353</v>
+        <v>6425</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H137" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I137" t="inlineStr"/>
@@ -14504,10 +14504,10 @@
         </is>
       </c>
       <c r="Q137" t="n">
-        <v>478076</v>
+        <v>478313</v>
       </c>
       <c r="R137" t="n">
-        <v>6827777</v>
+        <v>6827798</v>
       </c>
       <c r="S137" t="n">
         <v>10</v>
@@ -14566,7 +14566,7 @@
     </row>
     <row r="138">
       <c r="A138" t="n">
-        <v>120075142</v>
+        <v>120075083</v>
       </c>
       <c r="B138" t="n">
         <v>78526</v>
@@ -14606,10 +14606,10 @@
         </is>
       </c>
       <c r="Q138" t="n">
-        <v>478313</v>
+        <v>478097</v>
       </c>
       <c r="R138" t="n">
-        <v>6827798</v>
+        <v>6827527</v>
       </c>
       <c r="S138" t="n">
         <v>10</v>
@@ -14668,10 +14668,10 @@
     </row>
     <row r="139">
       <c r="A139" t="n">
-        <v>120075083</v>
+        <v>120075044</v>
       </c>
       <c r="B139" t="n">
-        <v>78526</v>
+        <v>78262</v>
       </c>
       <c r="C139" t="inlineStr">
         <is>
@@ -14684,21 +14684,21 @@
         </is>
       </c>
       <c r="E139" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H139" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I139" t="inlineStr"/>
@@ -14708,10 +14708,10 @@
         </is>
       </c>
       <c r="Q139" t="n">
-        <v>478097</v>
+        <v>478060</v>
       </c>
       <c r="R139" t="n">
-        <v>6827527</v>
+        <v>6827770</v>
       </c>
       <c r="S139" t="n">
         <v>10</v>
@@ -14872,10 +14872,10 @@
     </row>
     <row r="141">
       <c r="A141" t="n">
-        <v>120074888</v>
+        <v>120075139</v>
       </c>
       <c r="B141" t="n">
-        <v>79144</v>
+        <v>78526</v>
       </c>
       <c r="C141" t="inlineStr">
         <is>
@@ -14888,21 +14888,21 @@
         </is>
       </c>
       <c r="E141" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H141" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I141" t="inlineStr"/>
@@ -14912,10 +14912,10 @@
         </is>
       </c>
       <c r="Q141" t="n">
-        <v>478139</v>
+        <v>478294</v>
       </c>
       <c r="R141" t="n">
-        <v>6827554</v>
+        <v>6827803</v>
       </c>
       <c r="S141" t="n">
         <v>10</v>
@@ -14974,10 +14974,10 @@
     </row>
     <row r="142">
       <c r="A142" t="n">
-        <v>120074948</v>
+        <v>120075089</v>
       </c>
       <c r="B142" t="n">
-        <v>79144</v>
+        <v>78526</v>
       </c>
       <c r="C142" t="inlineStr">
         <is>
@@ -14990,21 +14990,21 @@
         </is>
       </c>
       <c r="E142" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H142" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I142" t="inlineStr"/>
@@ -15014,10 +15014,10 @@
         </is>
       </c>
       <c r="Q142" t="n">
-        <v>478070</v>
+        <v>478153</v>
       </c>
       <c r="R142" t="n">
-        <v>6827723</v>
+        <v>6827517</v>
       </c>
       <c r="S142" t="n">
         <v>10</v>
@@ -15076,10 +15076,10 @@
     </row>
     <row r="143">
       <c r="A143" t="n">
-        <v>120074892</v>
+        <v>120075090</v>
       </c>
       <c r="B143" t="n">
-        <v>79144</v>
+        <v>78526</v>
       </c>
       <c r="C143" t="inlineStr">
         <is>
@@ -15092,21 +15092,21 @@
         </is>
       </c>
       <c r="E143" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H143" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I143" t="inlineStr"/>
@@ -15116,10 +15116,10 @@
         </is>
       </c>
       <c r="Q143" t="n">
-        <v>478243</v>
+        <v>478161</v>
       </c>
       <c r="R143" t="n">
-        <v>6827585</v>
+        <v>6827528</v>
       </c>
       <c r="S143" t="n">
         <v>10</v>
@@ -15178,10 +15178,10 @@
     </row>
     <row r="144">
       <c r="A144" t="n">
-        <v>120074905</v>
+        <v>120075092</v>
       </c>
       <c r="B144" t="n">
-        <v>79144</v>
+        <v>78526</v>
       </c>
       <c r="C144" t="inlineStr">
         <is>
@@ -15194,21 +15194,21 @@
         </is>
       </c>
       <c r="E144" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H144" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I144" t="inlineStr"/>
@@ -15218,10 +15218,10 @@
         </is>
       </c>
       <c r="Q144" t="n">
-        <v>478285</v>
+        <v>478167</v>
       </c>
       <c r="R144" t="n">
-        <v>6827770</v>
+        <v>6827561</v>
       </c>
       <c r="S144" t="n">
         <v>10</v>
@@ -15280,10 +15280,10 @@
     </row>
     <row r="145">
       <c r="A145" t="n">
-        <v>120074886</v>
+        <v>120075172</v>
       </c>
       <c r="B145" t="n">
-        <v>79144</v>
+        <v>78526</v>
       </c>
       <c r="C145" t="inlineStr">
         <is>
@@ -15296,21 +15296,21 @@
         </is>
       </c>
       <c r="E145" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H145" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I145" t="inlineStr"/>
@@ -15320,10 +15320,10 @@
         </is>
       </c>
       <c r="Q145" t="n">
-        <v>478125</v>
+        <v>478055</v>
       </c>
       <c r="R145" t="n">
-        <v>6827604</v>
+        <v>6827768</v>
       </c>
       <c r="S145" t="n">
         <v>10</v>
@@ -15382,10 +15382,10 @@
     </row>
     <row r="146">
       <c r="A146" t="n">
-        <v>120074945</v>
+        <v>120075086</v>
       </c>
       <c r="B146" t="n">
-        <v>79144</v>
+        <v>78526</v>
       </c>
       <c r="C146" t="inlineStr">
         <is>
@@ -15398,21 +15398,21 @@
         </is>
       </c>
       <c r="E146" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H146" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I146" t="inlineStr"/>
@@ -15422,10 +15422,10 @@
         </is>
       </c>
       <c r="Q146" t="n">
-        <v>478061</v>
+        <v>478104</v>
       </c>
       <c r="R146" t="n">
-        <v>6827770</v>
+        <v>6827495</v>
       </c>
       <c r="S146" t="n">
         <v>10</v>
@@ -15484,10 +15484,10 @@
     </row>
     <row r="147">
       <c r="A147" t="n">
-        <v>120074891</v>
+        <v>120074961</v>
       </c>
       <c r="B147" t="n">
-        <v>79144</v>
+        <v>90582</v>
       </c>
       <c r="C147" t="inlineStr">
         <is>
@@ -15500,21 +15500,21 @@
         </is>
       </c>
       <c r="E147" t="n">
-        <v>6453</v>
+        <v>5442</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G147" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H147" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I147" t="inlineStr"/>
@@ -15524,10 +15524,10 @@
         </is>
       </c>
       <c r="Q147" t="n">
-        <v>478212</v>
+        <v>478230</v>
       </c>
       <c r="R147" t="n">
-        <v>6827573</v>
+        <v>6827780</v>
       </c>
       <c r="S147" t="n">
         <v>10</v>
@@ -15586,10 +15586,10 @@
     </row>
     <row r="148">
       <c r="A148" t="n">
-        <v>120074933</v>
+        <v>120075007</v>
       </c>
       <c r="B148" t="n">
-        <v>79144</v>
+        <v>78263</v>
       </c>
       <c r="C148" t="inlineStr">
         <is>
@@ -15602,21 +15602,21 @@
         </is>
       </c>
       <c r="E148" t="n">
-        <v>6453</v>
+        <v>228912</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G148" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H148" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I148" t="inlineStr"/>
@@ -15626,10 +15626,10 @@
         </is>
       </c>
       <c r="Q148" t="n">
-        <v>478189</v>
+        <v>478285</v>
       </c>
       <c r="R148" t="n">
-        <v>6827761</v>
+        <v>6827770</v>
       </c>
       <c r="S148" t="n">
         <v>10</v>
@@ -15688,7 +15688,7 @@
     </row>
     <row r="149">
       <c r="A149" t="n">
-        <v>120074906</v>
+        <v>120074888</v>
       </c>
       <c r="B149" t="n">
         <v>79144</v>
@@ -15728,10 +15728,10 @@
         </is>
       </c>
       <c r="Q149" t="n">
-        <v>478294</v>
+        <v>478139</v>
       </c>
       <c r="R149" t="n">
-        <v>6827790</v>
+        <v>6827554</v>
       </c>
       <c r="S149" t="n">
         <v>10</v>
@@ -15790,10 +15790,10 @@
     </row>
     <row r="150">
       <c r="A150" t="n">
-        <v>120074961</v>
+        <v>120074948</v>
       </c>
       <c r="B150" t="n">
-        <v>90582</v>
+        <v>79144</v>
       </c>
       <c r="C150" t="inlineStr">
         <is>
@@ -15806,21 +15806,21 @@
         </is>
       </c>
       <c r="E150" t="n">
-        <v>5442</v>
+        <v>6453</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G150" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H150" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I150" t="inlineStr"/>
@@ -15830,10 +15830,10 @@
         </is>
       </c>
       <c r="Q150" t="n">
-        <v>478230</v>
+        <v>478070</v>
       </c>
       <c r="R150" t="n">
-        <v>6827780</v>
+        <v>6827723</v>
       </c>
       <c r="S150" t="n">
         <v>10</v>
@@ -15892,10 +15892,10 @@
     </row>
     <row r="151">
       <c r="A151" t="n">
-        <v>120075007</v>
+        <v>120074892</v>
       </c>
       <c r="B151" t="n">
-        <v>78263</v>
+        <v>79144</v>
       </c>
       <c r="C151" t="inlineStr">
         <is>
@@ -15908,21 +15908,21 @@
         </is>
       </c>
       <c r="E151" t="n">
-        <v>228912</v>
+        <v>6453</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G151" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H151" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I151" t="inlineStr"/>
@@ -15932,10 +15932,10 @@
         </is>
       </c>
       <c r="Q151" t="n">
-        <v>478285</v>
+        <v>478243</v>
       </c>
       <c r="R151" t="n">
-        <v>6827770</v>
+        <v>6827585</v>
       </c>
       <c r="S151" t="n">
         <v>10</v>
@@ -15994,10 +15994,10 @@
     </row>
     <row r="152">
       <c r="A152" t="n">
-        <v>120075139</v>
+        <v>120074905</v>
       </c>
       <c r="B152" t="n">
-        <v>78526</v>
+        <v>79144</v>
       </c>
       <c r="C152" t="inlineStr">
         <is>
@@ -16010,21 +16010,21 @@
         </is>
       </c>
       <c r="E152" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G152" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H152" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I152" t="inlineStr"/>
@@ -16034,10 +16034,10 @@
         </is>
       </c>
       <c r="Q152" t="n">
-        <v>478294</v>
+        <v>478285</v>
       </c>
       <c r="R152" t="n">
-        <v>6827803</v>
+        <v>6827770</v>
       </c>
       <c r="S152" t="n">
         <v>10</v>
@@ -16096,10 +16096,10 @@
     </row>
     <row r="153">
       <c r="A153" t="n">
-        <v>120075089</v>
+        <v>120074886</v>
       </c>
       <c r="B153" t="n">
-        <v>78526</v>
+        <v>79144</v>
       </c>
       <c r="C153" t="inlineStr">
         <is>
@@ -16112,21 +16112,21 @@
         </is>
       </c>
       <c r="E153" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G153" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H153" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I153" t="inlineStr"/>
@@ -16136,10 +16136,10 @@
         </is>
       </c>
       <c r="Q153" t="n">
-        <v>478153</v>
+        <v>478125</v>
       </c>
       <c r="R153" t="n">
-        <v>6827517</v>
+        <v>6827604</v>
       </c>
       <c r="S153" t="n">
         <v>10</v>
@@ -16198,10 +16198,10 @@
     </row>
     <row r="154">
       <c r="A154" t="n">
-        <v>120075090</v>
+        <v>120074945</v>
       </c>
       <c r="B154" t="n">
-        <v>78526</v>
+        <v>79144</v>
       </c>
       <c r="C154" t="inlineStr">
         <is>
@@ -16214,21 +16214,21 @@
         </is>
       </c>
       <c r="E154" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G154" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H154" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I154" t="inlineStr"/>
@@ -16238,10 +16238,10 @@
         </is>
       </c>
       <c r="Q154" t="n">
-        <v>478161</v>
+        <v>478061</v>
       </c>
       <c r="R154" t="n">
-        <v>6827528</v>
+        <v>6827770</v>
       </c>
       <c r="S154" t="n">
         <v>10</v>
@@ -16300,10 +16300,10 @@
     </row>
     <row r="155">
       <c r="A155" t="n">
-        <v>120075092</v>
+        <v>120074891</v>
       </c>
       <c r="B155" t="n">
-        <v>78526</v>
+        <v>79144</v>
       </c>
       <c r="C155" t="inlineStr">
         <is>
@@ -16316,21 +16316,21 @@
         </is>
       </c>
       <c r="E155" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G155" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H155" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I155" t="inlineStr"/>
@@ -16340,10 +16340,10 @@
         </is>
       </c>
       <c r="Q155" t="n">
-        <v>478167</v>
+        <v>478212</v>
       </c>
       <c r="R155" t="n">
-        <v>6827561</v>
+        <v>6827573</v>
       </c>
       <c r="S155" t="n">
         <v>10</v>
@@ -16402,10 +16402,10 @@
     </row>
     <row r="156">
       <c r="A156" t="n">
-        <v>120075172</v>
+        <v>120074933</v>
       </c>
       <c r="B156" t="n">
-        <v>78526</v>
+        <v>79144</v>
       </c>
       <c r="C156" t="inlineStr">
         <is>
@@ -16418,21 +16418,21 @@
         </is>
       </c>
       <c r="E156" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G156" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H156" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I156" t="inlineStr"/>
@@ -16442,10 +16442,10 @@
         </is>
       </c>
       <c r="Q156" t="n">
-        <v>478055</v>
+        <v>478189</v>
       </c>
       <c r="R156" t="n">
-        <v>6827768</v>
+        <v>6827761</v>
       </c>
       <c r="S156" t="n">
         <v>10</v>
@@ -16504,10 +16504,10 @@
     </row>
     <row r="157">
       <c r="A157" t="n">
-        <v>120075086</v>
+        <v>120074906</v>
       </c>
       <c r="B157" t="n">
-        <v>78526</v>
+        <v>79144</v>
       </c>
       <c r="C157" t="inlineStr">
         <is>
@@ -16520,21 +16520,21 @@
         </is>
       </c>
       <c r="E157" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G157" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H157" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I157" t="inlineStr"/>
@@ -16544,10 +16544,10 @@
         </is>
       </c>
       <c r="Q157" t="n">
-        <v>478104</v>
+        <v>478294</v>
       </c>
       <c r="R157" t="n">
-        <v>6827495</v>
+        <v>6827790</v>
       </c>
       <c r="S157" t="n">
         <v>10</v>

--- a/artfynd/A 32983-2023 artfynd.xlsx
+++ b/artfynd/A 32983-2023 artfynd.xlsx
@@ -777,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>120075207</v>
+        <v>120074932</v>
       </c>
       <c r="B3" t="n">
-        <v>78171</v>
+        <v>79144</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -793,21 +793,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>353</v>
+        <v>6453</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -817,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>478157</v>
+        <v>478250</v>
       </c>
       <c r="R3" t="n">
-        <v>6827509</v>
+        <v>6827802</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -879,10 +879,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>120074932</v>
+        <v>120075207</v>
       </c>
       <c r="B4" t="n">
-        <v>79144</v>
+        <v>78171</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -895,21 +895,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6453</v>
+        <v>353</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -919,10 +919,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>478250</v>
+        <v>478157</v>
       </c>
       <c r="R4" t="n">
-        <v>6827802</v>
+        <v>6827509</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -3234,10 +3234,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>120074986</v>
+        <v>120075016</v>
       </c>
       <c r="B27" t="n">
-        <v>79608</v>
+        <v>79607</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3250,21 +3250,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>2081</v>
+        <v>6458</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3336,10 +3336,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>120075016</v>
+        <v>120074947</v>
       </c>
       <c r="B28" t="n">
-        <v>79607</v>
+        <v>79144</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3352,21 +3352,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6458</v>
+        <v>6453</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3376,10 +3376,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>478096</v>
+        <v>478061</v>
       </c>
       <c r="R28" t="n">
-        <v>6827549</v>
+        <v>6827751</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3438,10 +3438,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>120074947</v>
+        <v>120075015</v>
       </c>
       <c r="B29" t="n">
-        <v>79144</v>
+        <v>79607</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3454,21 +3454,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6453</v>
+        <v>6458</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3478,10 +3478,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>478061</v>
+        <v>478114</v>
       </c>
       <c r="R29" t="n">
-        <v>6827751</v>
+        <v>6827633</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3540,10 +3540,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>120075015</v>
+        <v>120074986</v>
       </c>
       <c r="B30" t="n">
-        <v>79607</v>
+        <v>79608</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3556,21 +3556,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6458</v>
+        <v>2081</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3580,10 +3580,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>478114</v>
+        <v>478096</v>
       </c>
       <c r="R30" t="n">
-        <v>6827633</v>
+        <v>6827549</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -5070,10 +5070,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>120074907</v>
+        <v>120075198</v>
       </c>
       <c r="B45" t="n">
-        <v>79144</v>
+        <v>91840</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5082,25 +5082,25 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>6453</v>
+        <v>4364</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5110,10 +5110,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>478263</v>
+        <v>478163</v>
       </c>
       <c r="R45" t="n">
-        <v>6827838</v>
+        <v>6827530</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5580,10 +5580,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>120075198</v>
+        <v>120074907</v>
       </c>
       <c r="B50" t="n">
-        <v>91840</v>
+        <v>79144</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -5592,25 +5592,25 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>4364</v>
+        <v>6453</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -5620,10 +5620,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>478163</v>
+        <v>478263</v>
       </c>
       <c r="R50" t="n">
-        <v>6827530</v>
+        <v>6827838</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -6702,10 +6702,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>120074938</v>
+        <v>120075146</v>
       </c>
       <c r="B61" t="n">
-        <v>79144</v>
+        <v>78526</v>
       </c>
       <c r="C61" t="inlineStr">
         <is>
@@ -6718,21 +6718,21 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
@@ -6742,10 +6742,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>478097</v>
+        <v>478154</v>
       </c>
       <c r="R61" t="n">
-        <v>6827756</v>
+        <v>6827747</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -6804,10 +6804,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>120075000</v>
+        <v>120075061</v>
       </c>
       <c r="B62" t="n">
-        <v>78263</v>
+        <v>78526</v>
       </c>
       <c r="C62" t="inlineStr">
         <is>
@@ -6820,21 +6820,21 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
@@ -6844,10 +6844,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>478121</v>
+        <v>478160</v>
       </c>
       <c r="R62" t="n">
-        <v>6827607</v>
+        <v>6827710</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -6906,7 +6906,7 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>120075146</v>
+        <v>120075084</v>
       </c>
       <c r="B63" t="n">
         <v>78526</v>
@@ -6946,10 +6946,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>478154</v>
+        <v>478098</v>
       </c>
       <c r="R63" t="n">
-        <v>6827747</v>
+        <v>6827520</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -7008,7 +7008,7 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>120075061</v>
+        <v>120075066</v>
       </c>
       <c r="B64" t="n">
         <v>78526</v>
@@ -7051,7 +7051,7 @@
         <v>478160</v>
       </c>
       <c r="R64" t="n">
-        <v>6827710</v>
+        <v>6827680</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -7110,10 +7110,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>120075084</v>
+        <v>120074938</v>
       </c>
       <c r="B65" t="n">
-        <v>78526</v>
+        <v>79144</v>
       </c>
       <c r="C65" t="inlineStr">
         <is>
@@ -7126,21 +7126,21 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
@@ -7150,10 +7150,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>478098</v>
+        <v>478097</v>
       </c>
       <c r="R65" t="n">
-        <v>6827520</v>
+        <v>6827756</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7212,10 +7212,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>120075066</v>
+        <v>120075000</v>
       </c>
       <c r="B66" t="n">
-        <v>78526</v>
+        <v>78263</v>
       </c>
       <c r="C66" t="inlineStr">
         <is>
@@ -7228,21 +7228,21 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
@@ -7252,10 +7252,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>478160</v>
+        <v>478121</v>
       </c>
       <c r="R66" t="n">
-        <v>6827680</v>
+        <v>6827607</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7314,10 +7314,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>120074939</v>
+        <v>120075166</v>
       </c>
       <c r="B67" t="n">
-        <v>79144</v>
+        <v>78526</v>
       </c>
       <c r="C67" t="inlineStr">
         <is>
@@ -7330,21 +7330,21 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
@@ -7354,10 +7354,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>478091</v>
+        <v>478092</v>
       </c>
       <c r="R67" t="n">
-        <v>6827838</v>
+        <v>6827839</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7416,7 +7416,7 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>120075166</v>
+        <v>120075130</v>
       </c>
       <c r="B68" t="n">
         <v>78526</v>
@@ -7456,10 +7456,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>478092</v>
+        <v>478264</v>
       </c>
       <c r="R68" t="n">
-        <v>6827839</v>
+        <v>6827733</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7518,7 +7518,7 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>120075130</v>
+        <v>120075134</v>
       </c>
       <c r="B69" t="n">
         <v>78526</v>
@@ -7558,10 +7558,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>478264</v>
+        <v>478266</v>
       </c>
       <c r="R69" t="n">
-        <v>6827733</v>
+        <v>6827765</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -7620,7 +7620,7 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>120075134</v>
+        <v>120075082</v>
       </c>
       <c r="B70" t="n">
         <v>78526</v>
@@ -7660,10 +7660,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>478266</v>
+        <v>478097</v>
       </c>
       <c r="R70" t="n">
-        <v>6827765</v>
+        <v>6827544</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -7722,7 +7722,7 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>120075082</v>
+        <v>120075131</v>
       </c>
       <c r="B71" t="n">
         <v>78526</v>
@@ -7762,10 +7762,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>478097</v>
+        <v>478258</v>
       </c>
       <c r="R71" t="n">
-        <v>6827544</v>
+        <v>6827731</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -7824,7 +7824,7 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>120075131</v>
+        <v>120075120</v>
       </c>
       <c r="B72" t="n">
         <v>78526</v>
@@ -7864,10 +7864,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>478258</v>
+        <v>478223</v>
       </c>
       <c r="R72" t="n">
-        <v>6827731</v>
+        <v>6827657</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -7926,10 +7926,10 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>120075120</v>
+        <v>120074939</v>
       </c>
       <c r="B73" t="n">
-        <v>78526</v>
+        <v>79144</v>
       </c>
       <c r="C73" t="inlineStr">
         <is>
@@ -7942,21 +7942,21 @@
         </is>
       </c>
       <c r="E73" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
@@ -7966,10 +7966,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>478223</v>
+        <v>478091</v>
       </c>
       <c r="R73" t="n">
-        <v>6827657</v>
+        <v>6827838</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -8130,10 +8130,10 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>120075236</v>
+        <v>120075161</v>
       </c>
       <c r="B75" t="n">
-        <v>78171</v>
+        <v>78526</v>
       </c>
       <c r="C75" t="inlineStr">
         <is>
@@ -8146,21 +8146,21 @@
         </is>
       </c>
       <c r="E75" t="n">
-        <v>353</v>
+        <v>6425</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
@@ -8170,10 +8170,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>478062</v>
+        <v>478082</v>
       </c>
       <c r="R75" t="n">
-        <v>6827740</v>
+        <v>6827766</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -8232,7 +8232,7 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>120075161</v>
+        <v>120075121</v>
       </c>
       <c r="B76" t="n">
         <v>78526</v>
@@ -8272,10 +8272,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>478082</v>
+        <v>478232</v>
       </c>
       <c r="R76" t="n">
-        <v>6827766</v>
+        <v>6827659</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -8334,7 +8334,7 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>120075121</v>
+        <v>120075077</v>
       </c>
       <c r="B77" t="n">
         <v>78526</v>
@@ -8374,10 +8374,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>478232</v>
+        <v>478124</v>
       </c>
       <c r="R77" t="n">
-        <v>6827659</v>
+        <v>6827560</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -8436,7 +8436,7 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>120075077</v>
+        <v>120075175</v>
       </c>
       <c r="B78" t="n">
         <v>78526</v>
@@ -8476,10 +8476,10 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>478124</v>
+        <v>478059</v>
       </c>
       <c r="R78" t="n">
-        <v>6827560</v>
+        <v>6827739</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -8538,10 +8538,10 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>120075175</v>
+        <v>120075236</v>
       </c>
       <c r="B79" t="n">
-        <v>78526</v>
+        <v>78171</v>
       </c>
       <c r="C79" t="inlineStr">
         <is>
@@ -8554,21 +8554,21 @@
         </is>
       </c>
       <c r="E79" t="n">
-        <v>6425</v>
+        <v>353</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
@@ -8578,10 +8578,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>478059</v>
+        <v>478062</v>
       </c>
       <c r="R79" t="n">
-        <v>6827739</v>
+        <v>6827740</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -10272,10 +10272,10 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>120074956</v>
+        <v>120074934</v>
       </c>
       <c r="B96" t="n">
-        <v>57310</v>
+        <v>79144</v>
       </c>
       <c r="C96" t="inlineStr">
         <is>
@@ -10288,39 +10288,34 @@
         </is>
       </c>
       <c r="E96" t="n">
-        <v>100109</v>
+        <v>6453</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I96" t="inlineStr"/>
-      <c r="M96" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P96" t="inlineStr">
         <is>
           <t>Hevoslamm, Dlr</t>
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>478278</v>
+        <v>478169</v>
       </c>
       <c r="R96" t="n">
-        <v>6827832</v>
+        <v>6827760</v>
       </c>
       <c r="S96" t="n">
         <v>10</v>
@@ -10353,11 +10348,6 @@
       <c r="AA96" t="inlineStr">
         <is>
           <t>2024-09-27</t>
-        </is>
-      </c>
-      <c r="AC96" t="inlineStr">
-        <is>
-          <t>Färska ringhack (tall)</t>
         </is>
       </c>
       <c r="AD96" t="b">
@@ -10384,10 +10374,10 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>120074934</v>
+        <v>120075028</v>
       </c>
       <c r="B97" t="n">
-        <v>79144</v>
+        <v>78262</v>
       </c>
       <c r="C97" t="inlineStr">
         <is>
@@ -10400,21 +10390,21 @@
         </is>
       </c>
       <c r="E97" t="n">
-        <v>6453</v>
+        <v>6446</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I97" t="inlineStr"/>
@@ -10424,10 +10414,10 @@
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>478169</v>
+        <v>478137</v>
       </c>
       <c r="R97" t="n">
-        <v>6827760</v>
+        <v>6827553</v>
       </c>
       <c r="S97" t="n">
         <v>10</v>
@@ -10486,10 +10476,10 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>120075028</v>
+        <v>120074956</v>
       </c>
       <c r="B98" t="n">
-        <v>78262</v>
+        <v>57310</v>
       </c>
       <c r="C98" t="inlineStr">
         <is>
@@ -10502,34 +10492,39 @@
         </is>
       </c>
       <c r="E98" t="n">
-        <v>6446</v>
+        <v>100109</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I98" t="inlineStr"/>
+      <c r="M98" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P98" t="inlineStr">
         <is>
           <t>Hevoslamm, Dlr</t>
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>478137</v>
+        <v>478278</v>
       </c>
       <c r="R98" t="n">
-        <v>6827553</v>
+        <v>6827832</v>
       </c>
       <c r="S98" t="n">
         <v>10</v>
@@ -10562,6 +10557,11 @@
       <c r="AA98" t="inlineStr">
         <is>
           <t>2024-09-27</t>
+        </is>
+      </c>
+      <c r="AC98" t="inlineStr">
+        <is>
+          <t>Färska ringhack (tall)</t>
         </is>
       </c>
       <c r="AD98" t="b">
@@ -10894,10 +10894,10 @@
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>120074952</v>
+        <v>120075216</v>
       </c>
       <c r="B102" t="n">
-        <v>79115</v>
+        <v>78171</v>
       </c>
       <c r="C102" t="inlineStr">
         <is>
@@ -10910,21 +10910,21 @@
         </is>
       </c>
       <c r="E102" t="n">
-        <v>229821</v>
+        <v>353</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I102" t="inlineStr"/>
@@ -10934,10 +10934,10 @@
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>478120</v>
+        <v>478294</v>
       </c>
       <c r="R102" t="n">
-        <v>6827605</v>
+        <v>6827790</v>
       </c>
       <c r="S102" t="n">
         <v>10</v>
@@ -10996,7 +10996,7 @@
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>120075216</v>
+        <v>120075215</v>
       </c>
       <c r="B103" t="n">
         <v>78171</v>
@@ -11036,10 +11036,10 @@
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>478294</v>
+        <v>478239</v>
       </c>
       <c r="R103" t="n">
-        <v>6827790</v>
+        <v>6827752</v>
       </c>
       <c r="S103" t="n">
         <v>10</v>
@@ -11098,10 +11098,10 @@
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>120075215</v>
+        <v>120074929</v>
       </c>
       <c r="B104" t="n">
-        <v>78171</v>
+        <v>78560</v>
       </c>
       <c r="C104" t="inlineStr">
         <is>
@@ -11114,21 +11114,21 @@
         </is>
       </c>
       <c r="E104" t="n">
-        <v>353</v>
+        <v>185</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I104" t="inlineStr"/>
@@ -11138,10 +11138,10 @@
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>478239</v>
+        <v>478045</v>
       </c>
       <c r="R104" t="n">
-        <v>6827752</v>
+        <v>6827724</v>
       </c>
       <c r="S104" t="n">
         <v>10</v>
@@ -11200,10 +11200,10 @@
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>120074929</v>
+        <v>120075224</v>
       </c>
       <c r="B105" t="n">
-        <v>78560</v>
+        <v>78171</v>
       </c>
       <c r="C105" t="inlineStr">
         <is>
@@ -11216,21 +11216,21 @@
         </is>
       </c>
       <c r="E105" t="n">
-        <v>185</v>
+        <v>353</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I105" t="inlineStr"/>
@@ -11240,10 +11240,10 @@
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>478045</v>
+        <v>478081</v>
       </c>
       <c r="R105" t="n">
-        <v>6827724</v>
+        <v>6827789</v>
       </c>
       <c r="S105" t="n">
         <v>10</v>
@@ -11302,7 +11302,7 @@
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>120075224</v>
+        <v>120075234</v>
       </c>
       <c r="B106" t="n">
         <v>78171</v>
@@ -11342,10 +11342,10 @@
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>478081</v>
+        <v>478069</v>
       </c>
       <c r="R106" t="n">
-        <v>6827789</v>
+        <v>6827741</v>
       </c>
       <c r="S106" t="n">
         <v>10</v>
@@ -11404,10 +11404,10 @@
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>120075234</v>
+        <v>120075088</v>
       </c>
       <c r="B107" t="n">
-        <v>78171</v>
+        <v>78526</v>
       </c>
       <c r="C107" t="inlineStr">
         <is>
@@ -11420,21 +11420,21 @@
         </is>
       </c>
       <c r="E107" t="n">
-        <v>353</v>
+        <v>6425</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I107" t="inlineStr"/>
@@ -11444,10 +11444,10 @@
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>478069</v>
+        <v>478151</v>
       </c>
       <c r="R107" t="n">
-        <v>6827741</v>
+        <v>6827509</v>
       </c>
       <c r="S107" t="n">
         <v>10</v>
@@ -11506,7 +11506,7 @@
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>120075088</v>
+        <v>120075140</v>
       </c>
       <c r="B108" t="n">
         <v>78526</v>
@@ -11546,10 +11546,10 @@
         </is>
       </c>
       <c r="Q108" t="n">
-        <v>478151</v>
+        <v>478310</v>
       </c>
       <c r="R108" t="n">
-        <v>6827509</v>
+        <v>6827797</v>
       </c>
       <c r="S108" t="n">
         <v>10</v>
@@ -11608,7 +11608,7 @@
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>120075140</v>
+        <v>120075128</v>
       </c>
       <c r="B109" t="n">
         <v>78526</v>
@@ -11648,10 +11648,10 @@
         </is>
       </c>
       <c r="Q109" t="n">
-        <v>478310</v>
+        <v>478275</v>
       </c>
       <c r="R109" t="n">
-        <v>6827797</v>
+        <v>6827710</v>
       </c>
       <c r="S109" t="n">
         <v>10</v>
@@ -11710,7 +11710,7 @@
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>120075128</v>
+        <v>120075171</v>
       </c>
       <c r="B110" t="n">
         <v>78526</v>
@@ -11750,10 +11750,10 @@
         </is>
       </c>
       <c r="Q110" t="n">
-        <v>478275</v>
+        <v>478073</v>
       </c>
       <c r="R110" t="n">
-        <v>6827710</v>
+        <v>6827831</v>
       </c>
       <c r="S110" t="n">
         <v>10</v>
@@ -11812,10 +11812,10 @@
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>120075171</v>
+        <v>120074952</v>
       </c>
       <c r="B111" t="n">
-        <v>78526</v>
+        <v>79115</v>
       </c>
       <c r="C111" t="inlineStr">
         <is>
@@ -11828,21 +11828,21 @@
         </is>
       </c>
       <c r="E111" t="n">
-        <v>6425</v>
+        <v>229821</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I111" t="inlineStr"/>
@@ -11852,10 +11852,10 @@
         </is>
       </c>
       <c r="Q111" t="n">
-        <v>478073</v>
+        <v>478120</v>
       </c>
       <c r="R111" t="n">
-        <v>6827831</v>
+        <v>6827605</v>
       </c>
       <c r="S111" t="n">
         <v>10</v>
@@ -11914,10 +11914,10 @@
     </row>
     <row r="112">
       <c r="A112" t="n">
-        <v>120075201</v>
+        <v>120075176</v>
       </c>
       <c r="B112" t="n">
-        <v>78171</v>
+        <v>78526</v>
       </c>
       <c r="C112" t="inlineStr">
         <is>
@@ -11930,21 +11930,21 @@
         </is>
       </c>
       <c r="E112" t="n">
-        <v>353</v>
+        <v>6425</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I112" t="inlineStr"/>
@@ -11954,10 +11954,10 @@
         </is>
       </c>
       <c r="Q112" t="n">
-        <v>478182</v>
+        <v>478066</v>
       </c>
       <c r="R112" t="n">
-        <v>6827728</v>
+        <v>6827732</v>
       </c>
       <c r="S112" t="n">
         <v>10</v>
@@ -12016,10 +12016,10 @@
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>120075230</v>
+        <v>120075136</v>
       </c>
       <c r="B113" t="n">
-        <v>78171</v>
+        <v>78526</v>
       </c>
       <c r="C113" t="inlineStr">
         <is>
@@ -12032,21 +12032,21 @@
         </is>
       </c>
       <c r="E113" t="n">
-        <v>353</v>
+        <v>6425</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I113" t="inlineStr"/>
@@ -12056,10 +12056,10 @@
         </is>
       </c>
       <c r="Q113" t="n">
-        <v>478064</v>
+        <v>478290</v>
       </c>
       <c r="R113" t="n">
-        <v>6827866</v>
+        <v>6827758</v>
       </c>
       <c r="S113" t="n">
         <v>10</v>
@@ -12118,7 +12118,7 @@
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>120075176</v>
+        <v>120075137</v>
       </c>
       <c r="B114" t="n">
         <v>78526</v>
@@ -12158,10 +12158,10 @@
         </is>
       </c>
       <c r="Q114" t="n">
-        <v>478066</v>
+        <v>478288</v>
       </c>
       <c r="R114" t="n">
-        <v>6827732</v>
+        <v>6827763</v>
       </c>
       <c r="S114" t="n">
         <v>10</v>
@@ -12220,7 +12220,7 @@
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>120075136</v>
+        <v>120075075</v>
       </c>
       <c r="B115" t="n">
         <v>78526</v>
@@ -12260,10 +12260,10 @@
         </is>
       </c>
       <c r="Q115" t="n">
-        <v>478290</v>
+        <v>478139</v>
       </c>
       <c r="R115" t="n">
-        <v>6827758</v>
+        <v>6827554</v>
       </c>
       <c r="S115" t="n">
         <v>10</v>
@@ -12322,7 +12322,7 @@
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>120075137</v>
+        <v>120075129</v>
       </c>
       <c r="B116" t="n">
         <v>78526</v>
@@ -12362,10 +12362,10 @@
         </is>
       </c>
       <c r="Q116" t="n">
-        <v>478288</v>
+        <v>478265</v>
       </c>
       <c r="R116" t="n">
-        <v>6827763</v>
+        <v>6827707</v>
       </c>
       <c r="S116" t="n">
         <v>10</v>
@@ -12424,10 +12424,10 @@
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>120075075</v>
+        <v>120075042</v>
       </c>
       <c r="B117" t="n">
-        <v>78526</v>
+        <v>78262</v>
       </c>
       <c r="C117" t="inlineStr">
         <is>
@@ -12440,21 +12440,21 @@
         </is>
       </c>
       <c r="E117" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I117" t="inlineStr"/>
@@ -12464,10 +12464,10 @@
         </is>
       </c>
       <c r="Q117" t="n">
-        <v>478139</v>
+        <v>478074</v>
       </c>
       <c r="R117" t="n">
-        <v>6827554</v>
+        <v>6827775</v>
       </c>
       <c r="S117" t="n">
         <v>10</v>
@@ -12526,10 +12526,10 @@
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>120075129</v>
+        <v>120074931</v>
       </c>
       <c r="B118" t="n">
-        <v>78526</v>
+        <v>79144</v>
       </c>
       <c r="C118" t="inlineStr">
         <is>
@@ -12542,21 +12542,21 @@
         </is>
       </c>
       <c r="E118" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I118" t="inlineStr"/>
@@ -12566,10 +12566,10 @@
         </is>
       </c>
       <c r="Q118" t="n">
-        <v>478265</v>
+        <v>478261</v>
       </c>
       <c r="R118" t="n">
-        <v>6827707</v>
+        <v>6827822</v>
       </c>
       <c r="S118" t="n">
         <v>10</v>
@@ -12628,10 +12628,10 @@
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>120075042</v>
+        <v>120075201</v>
       </c>
       <c r="B119" t="n">
-        <v>78262</v>
+        <v>78171</v>
       </c>
       <c r="C119" t="inlineStr">
         <is>
@@ -12644,21 +12644,21 @@
         </is>
       </c>
       <c r="E119" t="n">
-        <v>6446</v>
+        <v>353</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I119" t="inlineStr"/>
@@ -12668,10 +12668,10 @@
         </is>
       </c>
       <c r="Q119" t="n">
-        <v>478074</v>
+        <v>478182</v>
       </c>
       <c r="R119" t="n">
-        <v>6827775</v>
+        <v>6827728</v>
       </c>
       <c r="S119" t="n">
         <v>10</v>
@@ -12730,10 +12730,10 @@
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>120074931</v>
+        <v>120075230</v>
       </c>
       <c r="B120" t="n">
-        <v>79144</v>
+        <v>78171</v>
       </c>
       <c r="C120" t="inlineStr">
         <is>
@@ -12746,21 +12746,21 @@
         </is>
       </c>
       <c r="E120" t="n">
-        <v>6453</v>
+        <v>353</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I120" t="inlineStr"/>
@@ -12770,10 +12770,10 @@
         </is>
       </c>
       <c r="Q120" t="n">
-        <v>478261</v>
+        <v>478064</v>
       </c>
       <c r="R120" t="n">
-        <v>6827822</v>
+        <v>6827866</v>
       </c>
       <c r="S120" t="n">
         <v>10</v>
@@ -14872,10 +14872,10 @@
     </row>
     <row r="141">
       <c r="A141" t="n">
-        <v>120075139</v>
+        <v>120074888</v>
       </c>
       <c r="B141" t="n">
-        <v>78526</v>
+        <v>79144</v>
       </c>
       <c r="C141" t="inlineStr">
         <is>
@@ -14888,21 +14888,21 @@
         </is>
       </c>
       <c r="E141" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H141" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I141" t="inlineStr"/>
@@ -14912,10 +14912,10 @@
         </is>
       </c>
       <c r="Q141" t="n">
-        <v>478294</v>
+        <v>478139</v>
       </c>
       <c r="R141" t="n">
-        <v>6827803</v>
+        <v>6827554</v>
       </c>
       <c r="S141" t="n">
         <v>10</v>
@@ -14974,10 +14974,10 @@
     </row>
     <row r="142">
       <c r="A142" t="n">
-        <v>120075089</v>
+        <v>120074948</v>
       </c>
       <c r="B142" t="n">
-        <v>78526</v>
+        <v>79144</v>
       </c>
       <c r="C142" t="inlineStr">
         <is>
@@ -14990,21 +14990,21 @@
         </is>
       </c>
       <c r="E142" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H142" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I142" t="inlineStr"/>
@@ -15014,10 +15014,10 @@
         </is>
       </c>
       <c r="Q142" t="n">
-        <v>478153</v>
+        <v>478070</v>
       </c>
       <c r="R142" t="n">
-        <v>6827517</v>
+        <v>6827723</v>
       </c>
       <c r="S142" t="n">
         <v>10</v>
@@ -15076,10 +15076,10 @@
     </row>
     <row r="143">
       <c r="A143" t="n">
-        <v>120075090</v>
+        <v>120074892</v>
       </c>
       <c r="B143" t="n">
-        <v>78526</v>
+        <v>79144</v>
       </c>
       <c r="C143" t="inlineStr">
         <is>
@@ -15092,21 +15092,21 @@
         </is>
       </c>
       <c r="E143" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H143" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I143" t="inlineStr"/>
@@ -15116,10 +15116,10 @@
         </is>
       </c>
       <c r="Q143" t="n">
-        <v>478161</v>
+        <v>478243</v>
       </c>
       <c r="R143" t="n">
-        <v>6827528</v>
+        <v>6827585</v>
       </c>
       <c r="S143" t="n">
         <v>10</v>
@@ -15178,10 +15178,10 @@
     </row>
     <row r="144">
       <c r="A144" t="n">
-        <v>120075092</v>
+        <v>120074905</v>
       </c>
       <c r="B144" t="n">
-        <v>78526</v>
+        <v>79144</v>
       </c>
       <c r="C144" t="inlineStr">
         <is>
@@ -15194,21 +15194,21 @@
         </is>
       </c>
       <c r="E144" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H144" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I144" t="inlineStr"/>
@@ -15218,10 +15218,10 @@
         </is>
       </c>
       <c r="Q144" t="n">
-        <v>478167</v>
+        <v>478285</v>
       </c>
       <c r="R144" t="n">
-        <v>6827561</v>
+        <v>6827770</v>
       </c>
       <c r="S144" t="n">
         <v>10</v>
@@ -15280,10 +15280,10 @@
     </row>
     <row r="145">
       <c r="A145" t="n">
-        <v>120075172</v>
+        <v>120074886</v>
       </c>
       <c r="B145" t="n">
-        <v>78526</v>
+        <v>79144</v>
       </c>
       <c r="C145" t="inlineStr">
         <is>
@@ -15296,21 +15296,21 @@
         </is>
       </c>
       <c r="E145" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H145" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I145" t="inlineStr"/>
@@ -15320,10 +15320,10 @@
         </is>
       </c>
       <c r="Q145" t="n">
-        <v>478055</v>
+        <v>478125</v>
       </c>
       <c r="R145" t="n">
-        <v>6827768</v>
+        <v>6827604</v>
       </c>
       <c r="S145" t="n">
         <v>10</v>
@@ -15382,10 +15382,10 @@
     </row>
     <row r="146">
       <c r="A146" t="n">
-        <v>120075086</v>
+        <v>120074945</v>
       </c>
       <c r="B146" t="n">
-        <v>78526</v>
+        <v>79144</v>
       </c>
       <c r="C146" t="inlineStr">
         <is>
@@ -15398,21 +15398,21 @@
         </is>
       </c>
       <c r="E146" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H146" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I146" t="inlineStr"/>
@@ -15422,10 +15422,10 @@
         </is>
       </c>
       <c r="Q146" t="n">
-        <v>478104</v>
+        <v>478061</v>
       </c>
       <c r="R146" t="n">
-        <v>6827495</v>
+        <v>6827770</v>
       </c>
       <c r="S146" t="n">
         <v>10</v>
@@ -15484,10 +15484,10 @@
     </row>
     <row r="147">
       <c r="A147" t="n">
-        <v>120074961</v>
+        <v>120074891</v>
       </c>
       <c r="B147" t="n">
-        <v>90582</v>
+        <v>79144</v>
       </c>
       <c r="C147" t="inlineStr">
         <is>
@@ -15500,21 +15500,21 @@
         </is>
       </c>
       <c r="E147" t="n">
-        <v>5442</v>
+        <v>6453</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G147" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H147" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I147" t="inlineStr"/>
@@ -15524,10 +15524,10 @@
         </is>
       </c>
       <c r="Q147" t="n">
-        <v>478230</v>
+        <v>478212</v>
       </c>
       <c r="R147" t="n">
-        <v>6827780</v>
+        <v>6827573</v>
       </c>
       <c r="S147" t="n">
         <v>10</v>
@@ -15586,10 +15586,10 @@
     </row>
     <row r="148">
       <c r="A148" t="n">
-        <v>120075007</v>
+        <v>120074933</v>
       </c>
       <c r="B148" t="n">
-        <v>78263</v>
+        <v>79144</v>
       </c>
       <c r="C148" t="inlineStr">
         <is>
@@ -15602,21 +15602,21 @@
         </is>
       </c>
       <c r="E148" t="n">
-        <v>228912</v>
+        <v>6453</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G148" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H148" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I148" t="inlineStr"/>
@@ -15626,10 +15626,10 @@
         </is>
       </c>
       <c r="Q148" t="n">
-        <v>478285</v>
+        <v>478189</v>
       </c>
       <c r="R148" t="n">
-        <v>6827770</v>
+        <v>6827761</v>
       </c>
       <c r="S148" t="n">
         <v>10</v>
@@ -15688,7 +15688,7 @@
     </row>
     <row r="149">
       <c r="A149" t="n">
-        <v>120074888</v>
+        <v>120074906</v>
       </c>
       <c r="B149" t="n">
         <v>79144</v>
@@ -15728,10 +15728,10 @@
         </is>
       </c>
       <c r="Q149" t="n">
-        <v>478139</v>
+        <v>478294</v>
       </c>
       <c r="R149" t="n">
-        <v>6827554</v>
+        <v>6827790</v>
       </c>
       <c r="S149" t="n">
         <v>10</v>
@@ -15790,10 +15790,10 @@
     </row>
     <row r="150">
       <c r="A150" t="n">
-        <v>120074948</v>
+        <v>120074961</v>
       </c>
       <c r="B150" t="n">
-        <v>79144</v>
+        <v>90582</v>
       </c>
       <c r="C150" t="inlineStr">
         <is>
@@ -15806,21 +15806,21 @@
         </is>
       </c>
       <c r="E150" t="n">
-        <v>6453</v>
+        <v>5442</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G150" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H150" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I150" t="inlineStr"/>
@@ -15830,10 +15830,10 @@
         </is>
       </c>
       <c r="Q150" t="n">
-        <v>478070</v>
+        <v>478230</v>
       </c>
       <c r="R150" t="n">
-        <v>6827723</v>
+        <v>6827780</v>
       </c>
       <c r="S150" t="n">
         <v>10</v>
@@ -15892,10 +15892,10 @@
     </row>
     <row r="151">
       <c r="A151" t="n">
-        <v>120074892</v>
+        <v>120075007</v>
       </c>
       <c r="B151" t="n">
-        <v>79144</v>
+        <v>78263</v>
       </c>
       <c r="C151" t="inlineStr">
         <is>
@@ -15908,21 +15908,21 @@
         </is>
       </c>
       <c r="E151" t="n">
-        <v>6453</v>
+        <v>228912</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G151" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H151" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I151" t="inlineStr"/>
@@ -15932,10 +15932,10 @@
         </is>
       </c>
       <c r="Q151" t="n">
-        <v>478243</v>
+        <v>478285</v>
       </c>
       <c r="R151" t="n">
-        <v>6827585</v>
+        <v>6827770</v>
       </c>
       <c r="S151" t="n">
         <v>10</v>
@@ -15994,10 +15994,10 @@
     </row>
     <row r="152">
       <c r="A152" t="n">
-        <v>120074905</v>
+        <v>120075139</v>
       </c>
       <c r="B152" t="n">
-        <v>79144</v>
+        <v>78526</v>
       </c>
       <c r="C152" t="inlineStr">
         <is>
@@ -16010,21 +16010,21 @@
         </is>
       </c>
       <c r="E152" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G152" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H152" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I152" t="inlineStr"/>
@@ -16034,10 +16034,10 @@
         </is>
       </c>
       <c r="Q152" t="n">
-        <v>478285</v>
+        <v>478294</v>
       </c>
       <c r="R152" t="n">
-        <v>6827770</v>
+        <v>6827803</v>
       </c>
       <c r="S152" t="n">
         <v>10</v>
@@ -16096,10 +16096,10 @@
     </row>
     <row r="153">
       <c r="A153" t="n">
-        <v>120074886</v>
+        <v>120075089</v>
       </c>
       <c r="B153" t="n">
-        <v>79144</v>
+        <v>78526</v>
       </c>
       <c r="C153" t="inlineStr">
         <is>
@@ -16112,21 +16112,21 @@
         </is>
       </c>
       <c r="E153" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G153" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H153" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I153" t="inlineStr"/>
@@ -16136,10 +16136,10 @@
         </is>
       </c>
       <c r="Q153" t="n">
-        <v>478125</v>
+        <v>478153</v>
       </c>
       <c r="R153" t="n">
-        <v>6827604</v>
+        <v>6827517</v>
       </c>
       <c r="S153" t="n">
         <v>10</v>
@@ -16198,10 +16198,10 @@
     </row>
     <row r="154">
       <c r="A154" t="n">
-        <v>120074945</v>
+        <v>120075090</v>
       </c>
       <c r="B154" t="n">
-        <v>79144</v>
+        <v>78526</v>
       </c>
       <c r="C154" t="inlineStr">
         <is>
@@ -16214,21 +16214,21 @@
         </is>
       </c>
       <c r="E154" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G154" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H154" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I154" t="inlineStr"/>
@@ -16238,10 +16238,10 @@
         </is>
       </c>
       <c r="Q154" t="n">
-        <v>478061</v>
+        <v>478161</v>
       </c>
       <c r="R154" t="n">
-        <v>6827770</v>
+        <v>6827528</v>
       </c>
       <c r="S154" t="n">
         <v>10</v>
@@ -16300,10 +16300,10 @@
     </row>
     <row r="155">
       <c r="A155" t="n">
-        <v>120074891</v>
+        <v>120075092</v>
       </c>
       <c r="B155" t="n">
-        <v>79144</v>
+        <v>78526</v>
       </c>
       <c r="C155" t="inlineStr">
         <is>
@@ -16316,21 +16316,21 @@
         </is>
       </c>
       <c r="E155" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G155" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H155" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I155" t="inlineStr"/>
@@ -16340,10 +16340,10 @@
         </is>
       </c>
       <c r="Q155" t="n">
-        <v>478212</v>
+        <v>478167</v>
       </c>
       <c r="R155" t="n">
-        <v>6827573</v>
+        <v>6827561</v>
       </c>
       <c r="S155" t="n">
         <v>10</v>
@@ -16402,10 +16402,10 @@
     </row>
     <row r="156">
       <c r="A156" t="n">
-        <v>120074933</v>
+        <v>120075172</v>
       </c>
       <c r="B156" t="n">
-        <v>79144</v>
+        <v>78526</v>
       </c>
       <c r="C156" t="inlineStr">
         <is>
@@ -16418,21 +16418,21 @@
         </is>
       </c>
       <c r="E156" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G156" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H156" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I156" t="inlineStr"/>
@@ -16442,10 +16442,10 @@
         </is>
       </c>
       <c r="Q156" t="n">
-        <v>478189</v>
+        <v>478055</v>
       </c>
       <c r="R156" t="n">
-        <v>6827761</v>
+        <v>6827768</v>
       </c>
       <c r="S156" t="n">
         <v>10</v>
@@ -16504,10 +16504,10 @@
     </row>
     <row r="157">
       <c r="A157" t="n">
-        <v>120074906</v>
+        <v>120075086</v>
       </c>
       <c r="B157" t="n">
-        <v>79144</v>
+        <v>78526</v>
       </c>
       <c r="C157" t="inlineStr">
         <is>
@@ -16520,21 +16520,21 @@
         </is>
       </c>
       <c r="E157" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G157" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H157" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I157" t="inlineStr"/>
@@ -16544,10 +16544,10 @@
         </is>
       </c>
       <c r="Q157" t="n">
-        <v>478294</v>
+        <v>478104</v>
       </c>
       <c r="R157" t="n">
-        <v>6827790</v>
+        <v>6827495</v>
       </c>
       <c r="S157" t="n">
         <v>10</v>

--- a/artfynd/A 32983-2023 artfynd.xlsx
+++ b/artfynd/A 32983-2023 artfynd.xlsx
@@ -777,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>120074932</v>
+        <v>120075207</v>
       </c>
       <c r="B3" t="n">
-        <v>79144</v>
+        <v>78171</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -793,21 +793,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6453</v>
+        <v>353</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -817,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>478250</v>
+        <v>478157</v>
       </c>
       <c r="R3" t="n">
-        <v>6827802</v>
+        <v>6827509</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -879,10 +879,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>120075207</v>
+        <v>120074932</v>
       </c>
       <c r="B4" t="n">
-        <v>78171</v>
+        <v>79144</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -895,21 +895,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>353</v>
+        <v>6453</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -919,10 +919,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>478157</v>
+        <v>478250</v>
       </c>
       <c r="R4" t="n">
-        <v>6827509</v>
+        <v>6827802</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -3234,10 +3234,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>120075016</v>
+        <v>120074986</v>
       </c>
       <c r="B27" t="n">
-        <v>79607</v>
+        <v>79608</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3250,21 +3250,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6458</v>
+        <v>2081</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3336,10 +3336,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>120074947</v>
+        <v>120075016</v>
       </c>
       <c r="B28" t="n">
-        <v>79144</v>
+        <v>79607</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3352,21 +3352,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6453</v>
+        <v>6458</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3376,10 +3376,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>478061</v>
+        <v>478096</v>
       </c>
       <c r="R28" t="n">
-        <v>6827751</v>
+        <v>6827549</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3438,10 +3438,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>120075015</v>
+        <v>120074947</v>
       </c>
       <c r="B29" t="n">
-        <v>79607</v>
+        <v>79144</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3454,21 +3454,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6458</v>
+        <v>6453</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3478,10 +3478,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>478114</v>
+        <v>478061</v>
       </c>
       <c r="R29" t="n">
-        <v>6827633</v>
+        <v>6827751</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3540,10 +3540,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>120074986</v>
+        <v>120075015</v>
       </c>
       <c r="B30" t="n">
-        <v>79608</v>
+        <v>79607</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3556,21 +3556,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>2081</v>
+        <v>6458</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3580,10 +3580,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>478096</v>
+        <v>478114</v>
       </c>
       <c r="R30" t="n">
-        <v>6827549</v>
+        <v>6827633</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3642,10 +3642,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>120074996</v>
+        <v>120075219</v>
       </c>
       <c r="B31" t="n">
-        <v>78263</v>
+        <v>78171</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3658,21 +3658,21 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>228912</v>
+        <v>353</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3682,10 +3682,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>478165</v>
+        <v>478169</v>
       </c>
       <c r="R31" t="n">
-        <v>6827712</v>
+        <v>6827760</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3744,10 +3744,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>120075219</v>
+        <v>120074915</v>
       </c>
       <c r="B32" t="n">
-        <v>78171</v>
+        <v>78560</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -3760,21 +3760,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>353</v>
+        <v>185</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3784,10 +3784,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>478169</v>
+        <v>478102</v>
       </c>
       <c r="R32" t="n">
-        <v>6827760</v>
+        <v>6827555</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3846,10 +3846,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>120074915</v>
+        <v>120074881</v>
       </c>
       <c r="B33" t="n">
-        <v>78560</v>
+        <v>79144</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -3862,21 +3862,21 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>185</v>
+        <v>6453</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -3886,10 +3886,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>478102</v>
+        <v>478184</v>
       </c>
       <c r="R33" t="n">
-        <v>6827555</v>
+        <v>6827728</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -3948,10 +3948,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>120074881</v>
+        <v>120075047</v>
       </c>
       <c r="B34" t="n">
-        <v>79144</v>
+        <v>78262</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -3964,21 +3964,21 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6453</v>
+        <v>6446</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -3988,10 +3988,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>478184</v>
+        <v>478212</v>
       </c>
       <c r="R34" t="n">
-        <v>6827728</v>
+        <v>6827573</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4050,10 +4050,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>120075047</v>
+        <v>120074996</v>
       </c>
       <c r="B35" t="n">
-        <v>78262</v>
+        <v>78263</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4066,21 +4066,21 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6446</v>
+        <v>228912</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4090,10 +4090,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>478212</v>
+        <v>478165</v>
       </c>
       <c r="R35" t="n">
-        <v>6827573</v>
+        <v>6827712</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -6702,10 +6702,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>120075146</v>
+        <v>120074938</v>
       </c>
       <c r="B61" t="n">
-        <v>78526</v>
+        <v>79144</v>
       </c>
       <c r="C61" t="inlineStr">
         <is>
@@ -6718,21 +6718,21 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
@@ -6742,10 +6742,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>478154</v>
+        <v>478097</v>
       </c>
       <c r="R61" t="n">
-        <v>6827747</v>
+        <v>6827756</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -6804,10 +6804,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>120075061</v>
+        <v>120075000</v>
       </c>
       <c r="B62" t="n">
-        <v>78526</v>
+        <v>78263</v>
       </c>
       <c r="C62" t="inlineStr">
         <is>
@@ -6820,21 +6820,21 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
@@ -6844,10 +6844,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>478160</v>
+        <v>478121</v>
       </c>
       <c r="R62" t="n">
-        <v>6827710</v>
+        <v>6827607</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -6906,7 +6906,7 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>120075084</v>
+        <v>120075146</v>
       </c>
       <c r="B63" t="n">
         <v>78526</v>
@@ -6946,10 +6946,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>478098</v>
+        <v>478154</v>
       </c>
       <c r="R63" t="n">
-        <v>6827520</v>
+        <v>6827747</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -7008,7 +7008,7 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>120075066</v>
+        <v>120075061</v>
       </c>
       <c r="B64" t="n">
         <v>78526</v>
@@ -7051,7 +7051,7 @@
         <v>478160</v>
       </c>
       <c r="R64" t="n">
-        <v>6827680</v>
+        <v>6827710</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -7110,10 +7110,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>120074938</v>
+        <v>120075084</v>
       </c>
       <c r="B65" t="n">
-        <v>79144</v>
+        <v>78526</v>
       </c>
       <c r="C65" t="inlineStr">
         <is>
@@ -7126,21 +7126,21 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
@@ -7150,10 +7150,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>478097</v>
+        <v>478098</v>
       </c>
       <c r="R65" t="n">
-        <v>6827756</v>
+        <v>6827520</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7212,10 +7212,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>120075000</v>
+        <v>120075066</v>
       </c>
       <c r="B66" t="n">
-        <v>78263</v>
+        <v>78526</v>
       </c>
       <c r="C66" t="inlineStr">
         <is>
@@ -7228,21 +7228,21 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
@@ -7252,10 +7252,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>478121</v>
+        <v>478160</v>
       </c>
       <c r="R66" t="n">
-        <v>6827607</v>
+        <v>6827680</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -13036,10 +13036,10 @@
     </row>
     <row r="123">
       <c r="A123" t="n">
-        <v>120075008</v>
+        <v>120075035</v>
       </c>
       <c r="B123" t="n">
-        <v>78263</v>
+        <v>78262</v>
       </c>
       <c r="C123" t="inlineStr">
         <is>
@@ -13052,21 +13052,21 @@
         </is>
       </c>
       <c r="E123" t="n">
-        <v>228912</v>
+        <v>6446</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I123" t="inlineStr"/>
@@ -13076,10 +13076,10 @@
         </is>
       </c>
       <c r="Q123" t="n">
-        <v>478299</v>
+        <v>478273</v>
       </c>
       <c r="R123" t="n">
-        <v>6827805</v>
+        <v>6827711</v>
       </c>
       <c r="S123" t="n">
         <v>10</v>
@@ -13138,10 +13138,10 @@
     </row>
     <row r="124">
       <c r="A124" t="n">
-        <v>120075192</v>
+        <v>120074941</v>
       </c>
       <c r="B124" t="n">
-        <v>78526</v>
+        <v>79144</v>
       </c>
       <c r="C124" t="inlineStr">
         <is>
@@ -13154,21 +13154,21 @@
         </is>
       </c>
       <c r="E124" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I124" t="inlineStr"/>
@@ -13178,10 +13178,10 @@
         </is>
       </c>
       <c r="Q124" t="n">
-        <v>478282</v>
+        <v>478069</v>
       </c>
       <c r="R124" t="n">
-        <v>6827683</v>
+        <v>6827854</v>
       </c>
       <c r="S124" t="n">
         <v>10</v>
@@ -13240,10 +13240,10 @@
     </row>
     <row r="125">
       <c r="A125" t="n">
-        <v>120075135</v>
+        <v>120075008</v>
       </c>
       <c r="B125" t="n">
-        <v>78526</v>
+        <v>78263</v>
       </c>
       <c r="C125" t="inlineStr">
         <is>
@@ -13256,21 +13256,21 @@
         </is>
       </c>
       <c r="E125" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I125" t="inlineStr"/>
@@ -13280,10 +13280,10 @@
         </is>
       </c>
       <c r="Q125" t="n">
-        <v>478291</v>
+        <v>478299</v>
       </c>
       <c r="R125" t="n">
-        <v>6827744</v>
+        <v>6827805</v>
       </c>
       <c r="S125" t="n">
         <v>10</v>
@@ -13342,7 +13342,7 @@
     </row>
     <row r="126">
       <c r="A126" t="n">
-        <v>120075085</v>
+        <v>120075192</v>
       </c>
       <c r="B126" t="n">
         <v>78526</v>
@@ -13382,10 +13382,10 @@
         </is>
       </c>
       <c r="Q126" t="n">
-        <v>478094</v>
+        <v>478282</v>
       </c>
       <c r="R126" t="n">
-        <v>6827504</v>
+        <v>6827683</v>
       </c>
       <c r="S126" t="n">
         <v>10</v>
@@ -13444,7 +13444,7 @@
     </row>
     <row r="127">
       <c r="A127" t="n">
-        <v>120075065</v>
+        <v>120075135</v>
       </c>
       <c r="B127" t="n">
         <v>78526</v>
@@ -13484,10 +13484,10 @@
         </is>
       </c>
       <c r="Q127" t="n">
-        <v>478169</v>
+        <v>478291</v>
       </c>
       <c r="R127" t="n">
-        <v>6827679</v>
+        <v>6827744</v>
       </c>
       <c r="S127" t="n">
         <v>10</v>
@@ -13546,7 +13546,7 @@
     </row>
     <row r="128">
       <c r="A128" t="n">
-        <v>120075164</v>
+        <v>120075085</v>
       </c>
       <c r="B128" t="n">
         <v>78526</v>
@@ -13586,10 +13586,10 @@
         </is>
       </c>
       <c r="Q128" t="n">
-        <v>478092</v>
+        <v>478094</v>
       </c>
       <c r="R128" t="n">
-        <v>6827810</v>
+        <v>6827504</v>
       </c>
       <c r="S128" t="n">
         <v>10</v>
@@ -13648,7 +13648,7 @@
     </row>
     <row r="129">
       <c r="A129" t="n">
-        <v>120075078</v>
+        <v>120075095</v>
       </c>
       <c r="B129" t="n">
         <v>78526</v>
@@ -13688,10 +13688,10 @@
         </is>
       </c>
       <c r="Q129" t="n">
-        <v>478116</v>
+        <v>478219</v>
       </c>
       <c r="R129" t="n">
-        <v>6827567</v>
+        <v>6827572</v>
       </c>
       <c r="S129" t="n">
         <v>10</v>
@@ -13750,7 +13750,7 @@
     </row>
     <row r="130">
       <c r="A130" t="n">
-        <v>120075068</v>
+        <v>120075065</v>
       </c>
       <c r="B130" t="n">
         <v>78526</v>
@@ -13790,10 +13790,10 @@
         </is>
       </c>
       <c r="Q130" t="n">
-        <v>478174</v>
+        <v>478169</v>
       </c>
       <c r="R130" t="n">
-        <v>6827656</v>
+        <v>6827679</v>
       </c>
       <c r="S130" t="n">
         <v>10</v>
@@ -13852,10 +13852,10 @@
     </row>
     <row r="131">
       <c r="A131" t="n">
-        <v>120075035</v>
+        <v>120075164</v>
       </c>
       <c r="B131" t="n">
-        <v>78262</v>
+        <v>78526</v>
       </c>
       <c r="C131" t="inlineStr">
         <is>
@@ -13868,21 +13868,21 @@
         </is>
       </c>
       <c r="E131" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H131" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I131" t="inlineStr"/>
@@ -13892,10 +13892,10 @@
         </is>
       </c>
       <c r="Q131" t="n">
-        <v>478273</v>
+        <v>478092</v>
       </c>
       <c r="R131" t="n">
-        <v>6827711</v>
+        <v>6827810</v>
       </c>
       <c r="S131" t="n">
         <v>10</v>
@@ -13954,10 +13954,10 @@
     </row>
     <row r="132">
       <c r="A132" t="n">
-        <v>120074941</v>
+        <v>120075078</v>
       </c>
       <c r="B132" t="n">
-        <v>79144</v>
+        <v>78526</v>
       </c>
       <c r="C132" t="inlineStr">
         <is>
@@ -13970,21 +13970,21 @@
         </is>
       </c>
       <c r="E132" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H132" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I132" t="inlineStr"/>
@@ -13994,10 +13994,10 @@
         </is>
       </c>
       <c r="Q132" t="n">
-        <v>478069</v>
+        <v>478116</v>
       </c>
       <c r="R132" t="n">
-        <v>6827854</v>
+        <v>6827567</v>
       </c>
       <c r="S132" t="n">
         <v>10</v>
@@ -14056,7 +14056,7 @@
     </row>
     <row r="133">
       <c r="A133" t="n">
-        <v>120075095</v>
+        <v>120075068</v>
       </c>
       <c r="B133" t="n">
         <v>78526</v>
@@ -14096,10 +14096,10 @@
         </is>
       </c>
       <c r="Q133" t="n">
-        <v>478219</v>
+        <v>478174</v>
       </c>
       <c r="R133" t="n">
-        <v>6827572</v>
+        <v>6827656</v>
       </c>
       <c r="S133" t="n">
         <v>10</v>
@@ -17014,7 +17014,7 @@
     </row>
     <row r="162">
       <c r="A162" t="n">
-        <v>120075043</v>
+        <v>120075026</v>
       </c>
       <c r="B162" t="n">
         <v>78262</v>
@@ -17054,10 +17054,10 @@
         </is>
       </c>
       <c r="Q162" t="n">
-        <v>478103</v>
+        <v>478161</v>
       </c>
       <c r="R162" t="n">
-        <v>6827803</v>
+        <v>6827592</v>
       </c>
       <c r="S162" t="n">
         <v>10</v>
@@ -17116,10 +17116,10 @@
     </row>
     <row r="163">
       <c r="A163" t="n">
-        <v>120075048</v>
+        <v>120075046</v>
       </c>
       <c r="B163" t="n">
-        <v>56514</v>
+        <v>78262</v>
       </c>
       <c r="C163" t="inlineStr">
         <is>
@@ -17132,39 +17132,34 @@
         </is>
       </c>
       <c r="E163" t="n">
-        <v>102612</v>
+        <v>6446</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G163" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H163" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I163" t="inlineStr"/>
-      <c r="M163" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
       <c r="P163" t="inlineStr">
         <is>
           <t>Hevoslamm, Dlr</t>
         </is>
       </c>
       <c r="Q163" t="n">
-        <v>478070</v>
+        <v>478285</v>
       </c>
       <c r="R163" t="n">
-        <v>6827723</v>
+        <v>6827770</v>
       </c>
       <c r="S163" t="n">
         <v>10</v>
@@ -17223,10 +17218,10 @@
     </row>
     <row r="164">
       <c r="A164" t="n">
-        <v>120075214</v>
+        <v>120075043</v>
       </c>
       <c r="B164" t="n">
-        <v>78171</v>
+        <v>78262</v>
       </c>
       <c r="C164" t="inlineStr">
         <is>
@@ -17239,21 +17234,21 @@
         </is>
       </c>
       <c r="E164" t="n">
-        <v>353</v>
+        <v>6446</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G164" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H164" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I164" t="inlineStr"/>
@@ -17263,10 +17258,10 @@
         </is>
       </c>
       <c r="Q164" t="n">
-        <v>478266</v>
+        <v>478103</v>
       </c>
       <c r="R164" t="n">
-        <v>6827724</v>
+        <v>6827803</v>
       </c>
       <c r="S164" t="n">
         <v>10</v>
@@ -17325,10 +17320,10 @@
     </row>
     <row r="165">
       <c r="A165" t="n">
-        <v>120075203</v>
+        <v>120075048</v>
       </c>
       <c r="B165" t="n">
-        <v>78171</v>
+        <v>56514</v>
       </c>
       <c r="C165" t="inlineStr">
         <is>
@@ -17341,34 +17336,39 @@
         </is>
       </c>
       <c r="E165" t="n">
-        <v>353</v>
+        <v>102612</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G165" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H165" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I165" t="inlineStr"/>
+      <c r="M165" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="P165" t="inlineStr">
         <is>
           <t>Hevoslamm, Dlr</t>
         </is>
       </c>
       <c r="Q165" t="n">
-        <v>478125</v>
+        <v>478070</v>
       </c>
       <c r="R165" t="n">
-        <v>6827631</v>
+        <v>6827723</v>
       </c>
       <c r="S165" t="n">
         <v>10</v>
@@ -17427,10 +17427,10 @@
     </row>
     <row r="166">
       <c r="A166" t="n">
-        <v>120075026</v>
+        <v>120075012</v>
       </c>
       <c r="B166" t="n">
-        <v>78262</v>
+        <v>78263</v>
       </c>
       <c r="C166" t="inlineStr">
         <is>
@@ -17443,21 +17443,21 @@
         </is>
       </c>
       <c r="E166" t="n">
-        <v>6446</v>
+        <v>228912</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G166" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H166" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I166" t="inlineStr"/>
@@ -17467,10 +17467,10 @@
         </is>
       </c>
       <c r="Q166" t="n">
-        <v>478161</v>
+        <v>478055</v>
       </c>
       <c r="R166" t="n">
-        <v>6827592</v>
+        <v>6827786</v>
       </c>
       <c r="S166" t="n">
         <v>10</v>
@@ -17529,10 +17529,10 @@
     </row>
     <row r="167">
       <c r="A167" t="n">
-        <v>120075046</v>
+        <v>120075001</v>
       </c>
       <c r="B167" t="n">
-        <v>78262</v>
+        <v>78263</v>
       </c>
       <c r="C167" t="inlineStr">
         <is>
@@ -17545,21 +17545,21 @@
         </is>
       </c>
       <c r="E167" t="n">
-        <v>6446</v>
+        <v>228912</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G167" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H167" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I167" t="inlineStr"/>
@@ -17569,10 +17569,10 @@
         </is>
       </c>
       <c r="Q167" t="n">
-        <v>478285</v>
+        <v>478125</v>
       </c>
       <c r="R167" t="n">
-        <v>6827770</v>
+        <v>6827604</v>
       </c>
       <c r="S167" t="n">
         <v>10</v>
@@ -17631,7 +17631,7 @@
     </row>
     <row r="168">
       <c r="A168" t="n">
-        <v>120075012</v>
+        <v>120075010</v>
       </c>
       <c r="B168" t="n">
         <v>78263</v>
@@ -17671,10 +17671,10 @@
         </is>
       </c>
       <c r="Q168" t="n">
-        <v>478055</v>
+        <v>478074</v>
       </c>
       <c r="R168" t="n">
-        <v>6827786</v>
+        <v>6827772</v>
       </c>
       <c r="S168" t="n">
         <v>10</v>
@@ -17733,10 +17733,10 @@
     </row>
     <row r="169">
       <c r="A169" t="n">
-        <v>120075001</v>
+        <v>120075214</v>
       </c>
       <c r="B169" t="n">
-        <v>78263</v>
+        <v>78171</v>
       </c>
       <c r="C169" t="inlineStr">
         <is>
@@ -17749,21 +17749,21 @@
         </is>
       </c>
       <c r="E169" t="n">
-        <v>228912</v>
+        <v>353</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G169" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H169" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I169" t="inlineStr"/>
@@ -17773,10 +17773,10 @@
         </is>
       </c>
       <c r="Q169" t="n">
-        <v>478125</v>
+        <v>478266</v>
       </c>
       <c r="R169" t="n">
-        <v>6827604</v>
+        <v>6827724</v>
       </c>
       <c r="S169" t="n">
         <v>10</v>
@@ -17835,10 +17835,10 @@
     </row>
     <row r="170">
       <c r="A170" t="n">
-        <v>120075010</v>
+        <v>120075203</v>
       </c>
       <c r="B170" t="n">
-        <v>78263</v>
+        <v>78171</v>
       </c>
       <c r="C170" t="inlineStr">
         <is>
@@ -17851,21 +17851,21 @@
         </is>
       </c>
       <c r="E170" t="n">
-        <v>228912</v>
+        <v>353</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G170" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H170" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I170" t="inlineStr"/>
@@ -17875,10 +17875,10 @@
         </is>
       </c>
       <c r="Q170" t="n">
-        <v>478074</v>
+        <v>478125</v>
       </c>
       <c r="R170" t="n">
-        <v>6827772</v>
+        <v>6827631</v>
       </c>
       <c r="S170" t="n">
         <v>10</v>

--- a/artfynd/A 32983-2023 artfynd.xlsx
+++ b/artfynd/A 32983-2023 artfynd.xlsx
@@ -4152,10 +4152,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>120075039</v>
+        <v>120075054</v>
       </c>
       <c r="B36" t="n">
-        <v>78262</v>
+        <v>90580</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4168,21 +4168,21 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6446</v>
+        <v>5432</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4192,10 +4192,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>478238</v>
+        <v>478126</v>
       </c>
       <c r="R36" t="n">
-        <v>6827752</v>
+        <v>6827477</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4254,10 +4254,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>120075239</v>
+        <v>120075147</v>
       </c>
       <c r="B37" t="n">
-        <v>77458</v>
+        <v>78526</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4270,21 +4270,21 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6487</v>
+        <v>6425</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Blågrå svartspik</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Chaenothecopsis fennica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Laurila) Tibell</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4294,10 +4294,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>478137</v>
+        <v>478153</v>
       </c>
       <c r="R37" t="n">
-        <v>6827554</v>
+        <v>6827728</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4356,7 +4356,7 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>120075147</v>
+        <v>120075173</v>
       </c>
       <c r="B38" t="n">
         <v>78526</v>
@@ -4396,10 +4396,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>478153</v>
+        <v>478052</v>
       </c>
       <c r="R38" t="n">
-        <v>6827728</v>
+        <v>6827754</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4458,7 +4458,7 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>120075173</v>
+        <v>120075074</v>
       </c>
       <c r="B39" t="n">
         <v>78526</v>
@@ -4498,10 +4498,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>478052</v>
+        <v>478138</v>
       </c>
       <c r="R39" t="n">
-        <v>6827754</v>
+        <v>6827599</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4560,7 +4560,7 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>120075074</v>
+        <v>120075063</v>
       </c>
       <c r="B40" t="n">
         <v>78526</v>
@@ -4600,10 +4600,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>478138</v>
+        <v>478201</v>
       </c>
       <c r="R40" t="n">
-        <v>6827599</v>
+        <v>6827693</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4662,7 +4662,7 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>120075063</v>
+        <v>120075145</v>
       </c>
       <c r="B41" t="n">
         <v>78526</v>
@@ -4702,10 +4702,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>478201</v>
+        <v>478226</v>
       </c>
       <c r="R41" t="n">
-        <v>6827693</v>
+        <v>6827777</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4764,7 +4764,7 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>120075145</v>
+        <v>120075174</v>
       </c>
       <c r="B42" t="n">
         <v>78526</v>
@@ -4804,10 +4804,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>478226</v>
+        <v>478057</v>
       </c>
       <c r="R42" t="n">
-        <v>6827777</v>
+        <v>6827749</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4866,10 +4866,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>120075174</v>
+        <v>120075039</v>
       </c>
       <c r="B43" t="n">
-        <v>78526</v>
+        <v>78262</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -4882,21 +4882,21 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -4906,10 +4906,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>478057</v>
+        <v>478238</v>
       </c>
       <c r="R43" t="n">
-        <v>6827749</v>
+        <v>6827752</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -4968,10 +4968,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>120075054</v>
+        <v>120075239</v>
       </c>
       <c r="B44" t="n">
-        <v>90580</v>
+        <v>77458</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -4984,21 +4984,21 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>5432</v>
+        <v>6487</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Blågrå svartspik</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Chaenothecopsis fennica</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Laurila) Tibell</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -5008,10 +5008,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>478126</v>
+        <v>478137</v>
       </c>
       <c r="R44" t="n">
-        <v>6827477</v>
+        <v>6827554</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5784,10 +5784,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>120075204</v>
+        <v>120074883</v>
       </c>
       <c r="B52" t="n">
-        <v>78171</v>
+        <v>79144</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -5800,21 +5800,21 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>353</v>
+        <v>6453</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -5824,10 +5824,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>478115</v>
+        <v>478142</v>
       </c>
       <c r="R52" t="n">
-        <v>6827614</v>
+        <v>6827623</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -5886,10 +5886,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>120074922</v>
+        <v>120075038</v>
       </c>
       <c r="B53" t="n">
-        <v>78560</v>
+        <v>78262</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -5902,21 +5902,21 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>185</v>
+        <v>6446</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -5926,10 +5926,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>478103</v>
+        <v>478261</v>
       </c>
       <c r="R53" t="n">
-        <v>6827718</v>
+        <v>6827731</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -5988,10 +5988,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>120075165</v>
+        <v>120075027</v>
       </c>
       <c r="B54" t="n">
-        <v>78526</v>
+        <v>78262</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
@@ -6004,21 +6004,21 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -6028,10 +6028,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>478078</v>
+        <v>478144</v>
       </c>
       <c r="R54" t="n">
-        <v>6827834</v>
+        <v>6827593</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6090,7 +6090,7 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>120075177</v>
+        <v>120075165</v>
       </c>
       <c r="B55" t="n">
         <v>78526</v>
@@ -6130,10 +6130,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>478075</v>
+        <v>478078</v>
       </c>
       <c r="R55" t="n">
-        <v>6827717</v>
+        <v>6827834</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6192,7 +6192,7 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>120075060</v>
+        <v>120075177</v>
       </c>
       <c r="B56" t="n">
         <v>78526</v>
@@ -6232,10 +6232,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>478087</v>
+        <v>478075</v>
       </c>
       <c r="R56" t="n">
-        <v>6827718</v>
+        <v>6827717</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6294,10 +6294,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>120074883</v>
+        <v>120075060</v>
       </c>
       <c r="B57" t="n">
-        <v>79144</v>
+        <v>78526</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
@@ -6310,21 +6310,21 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -6334,10 +6334,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>478142</v>
+        <v>478087</v>
       </c>
       <c r="R57" t="n">
-        <v>6827623</v>
+        <v>6827718</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6396,10 +6396,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>120075038</v>
+        <v>120075204</v>
       </c>
       <c r="B58" t="n">
-        <v>78262</v>
+        <v>78171</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
@@ -6412,21 +6412,21 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>6446</v>
+        <v>353</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
@@ -6436,10 +6436,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>478261</v>
+        <v>478115</v>
       </c>
       <c r="R58" t="n">
-        <v>6827731</v>
+        <v>6827614</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6498,10 +6498,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>120075027</v>
+        <v>120074922</v>
       </c>
       <c r="B59" t="n">
-        <v>78262</v>
+        <v>78560</v>
       </c>
       <c r="C59" t="inlineStr">
         <is>
@@ -6514,21 +6514,21 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>6446</v>
+        <v>185</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
@@ -6538,10 +6538,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>478144</v>
+        <v>478103</v>
       </c>
       <c r="R59" t="n">
-        <v>6827593</v>
+        <v>6827718</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6702,10 +6702,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>120074938</v>
+        <v>120075146</v>
       </c>
       <c r="B61" t="n">
-        <v>79144</v>
+        <v>78526</v>
       </c>
       <c r="C61" t="inlineStr">
         <is>
@@ -6718,21 +6718,21 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
@@ -6742,10 +6742,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>478097</v>
+        <v>478154</v>
       </c>
       <c r="R61" t="n">
-        <v>6827756</v>
+        <v>6827747</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -6804,10 +6804,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>120075000</v>
+        <v>120075061</v>
       </c>
       <c r="B62" t="n">
-        <v>78263</v>
+        <v>78526</v>
       </c>
       <c r="C62" t="inlineStr">
         <is>
@@ -6820,21 +6820,21 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
@@ -6844,10 +6844,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>478121</v>
+        <v>478160</v>
       </c>
       <c r="R62" t="n">
-        <v>6827607</v>
+        <v>6827710</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -6906,7 +6906,7 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>120075146</v>
+        <v>120075084</v>
       </c>
       <c r="B63" t="n">
         <v>78526</v>
@@ -6946,10 +6946,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>478154</v>
+        <v>478098</v>
       </c>
       <c r="R63" t="n">
-        <v>6827747</v>
+        <v>6827520</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -7008,7 +7008,7 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>120075061</v>
+        <v>120075066</v>
       </c>
       <c r="B64" t="n">
         <v>78526</v>
@@ -7051,7 +7051,7 @@
         <v>478160</v>
       </c>
       <c r="R64" t="n">
-        <v>6827710</v>
+        <v>6827680</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -7110,10 +7110,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>120075084</v>
+        <v>120074938</v>
       </c>
       <c r="B65" t="n">
-        <v>78526</v>
+        <v>79144</v>
       </c>
       <c r="C65" t="inlineStr">
         <is>
@@ -7126,21 +7126,21 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
@@ -7150,10 +7150,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>478098</v>
+        <v>478097</v>
       </c>
       <c r="R65" t="n">
-        <v>6827520</v>
+        <v>6827756</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7212,10 +7212,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>120075066</v>
+        <v>120075000</v>
       </c>
       <c r="B66" t="n">
-        <v>78526</v>
+        <v>78263</v>
       </c>
       <c r="C66" t="inlineStr">
         <is>
@@ -7228,21 +7228,21 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
@@ -7252,10 +7252,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>478160</v>
+        <v>478121</v>
       </c>
       <c r="R66" t="n">
-        <v>6827680</v>
+        <v>6827607</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -13036,10 +13036,10 @@
     </row>
     <row r="123">
       <c r="A123" t="n">
-        <v>120075035</v>
+        <v>120075008</v>
       </c>
       <c r="B123" t="n">
-        <v>78262</v>
+        <v>78263</v>
       </c>
       <c r="C123" t="inlineStr">
         <is>
@@ -13052,21 +13052,21 @@
         </is>
       </c>
       <c r="E123" t="n">
-        <v>6446</v>
+        <v>228912</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I123" t="inlineStr"/>
@@ -13076,10 +13076,10 @@
         </is>
       </c>
       <c r="Q123" t="n">
-        <v>478273</v>
+        <v>478299</v>
       </c>
       <c r="R123" t="n">
-        <v>6827711</v>
+        <v>6827805</v>
       </c>
       <c r="S123" t="n">
         <v>10</v>
@@ -13138,10 +13138,10 @@
     </row>
     <row r="124">
       <c r="A124" t="n">
-        <v>120074941</v>
+        <v>120075192</v>
       </c>
       <c r="B124" t="n">
-        <v>79144</v>
+        <v>78526</v>
       </c>
       <c r="C124" t="inlineStr">
         <is>
@@ -13154,21 +13154,21 @@
         </is>
       </c>
       <c r="E124" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I124" t="inlineStr"/>
@@ -13178,10 +13178,10 @@
         </is>
       </c>
       <c r="Q124" t="n">
-        <v>478069</v>
+        <v>478282</v>
       </c>
       <c r="R124" t="n">
-        <v>6827854</v>
+        <v>6827683</v>
       </c>
       <c r="S124" t="n">
         <v>10</v>
@@ -13240,10 +13240,10 @@
     </row>
     <row r="125">
       <c r="A125" t="n">
-        <v>120075008</v>
+        <v>120075135</v>
       </c>
       <c r="B125" t="n">
-        <v>78263</v>
+        <v>78526</v>
       </c>
       <c r="C125" t="inlineStr">
         <is>
@@ -13256,21 +13256,21 @@
         </is>
       </c>
       <c r="E125" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I125" t="inlineStr"/>
@@ -13280,10 +13280,10 @@
         </is>
       </c>
       <c r="Q125" t="n">
-        <v>478299</v>
+        <v>478291</v>
       </c>
       <c r="R125" t="n">
-        <v>6827805</v>
+        <v>6827744</v>
       </c>
       <c r="S125" t="n">
         <v>10</v>
@@ -13342,7 +13342,7 @@
     </row>
     <row r="126">
       <c r="A126" t="n">
-        <v>120075192</v>
+        <v>120075085</v>
       </c>
       <c r="B126" t="n">
         <v>78526</v>
@@ -13382,10 +13382,10 @@
         </is>
       </c>
       <c r="Q126" t="n">
-        <v>478282</v>
+        <v>478094</v>
       </c>
       <c r="R126" t="n">
-        <v>6827683</v>
+        <v>6827504</v>
       </c>
       <c r="S126" t="n">
         <v>10</v>
@@ -13444,7 +13444,7 @@
     </row>
     <row r="127">
       <c r="A127" t="n">
-        <v>120075135</v>
+        <v>120075065</v>
       </c>
       <c r="B127" t="n">
         <v>78526</v>
@@ -13484,10 +13484,10 @@
         </is>
       </c>
       <c r="Q127" t="n">
-        <v>478291</v>
+        <v>478169</v>
       </c>
       <c r="R127" t="n">
-        <v>6827744</v>
+        <v>6827679</v>
       </c>
       <c r="S127" t="n">
         <v>10</v>
@@ -13546,7 +13546,7 @@
     </row>
     <row r="128">
       <c r="A128" t="n">
-        <v>120075085</v>
+        <v>120075164</v>
       </c>
       <c r="B128" t="n">
         <v>78526</v>
@@ -13586,10 +13586,10 @@
         </is>
       </c>
       <c r="Q128" t="n">
-        <v>478094</v>
+        <v>478092</v>
       </c>
       <c r="R128" t="n">
-        <v>6827504</v>
+        <v>6827810</v>
       </c>
       <c r="S128" t="n">
         <v>10</v>
@@ -13648,7 +13648,7 @@
     </row>
     <row r="129">
       <c r="A129" t="n">
-        <v>120075095</v>
+        <v>120075078</v>
       </c>
       <c r="B129" t="n">
         <v>78526</v>
@@ -13688,10 +13688,10 @@
         </is>
       </c>
       <c r="Q129" t="n">
-        <v>478219</v>
+        <v>478116</v>
       </c>
       <c r="R129" t="n">
-        <v>6827572</v>
+        <v>6827567</v>
       </c>
       <c r="S129" t="n">
         <v>10</v>
@@ -13750,7 +13750,7 @@
     </row>
     <row r="130">
       <c r="A130" t="n">
-        <v>120075065</v>
+        <v>120075068</v>
       </c>
       <c r="B130" t="n">
         <v>78526</v>
@@ -13790,10 +13790,10 @@
         </is>
       </c>
       <c r="Q130" t="n">
-        <v>478169</v>
+        <v>478174</v>
       </c>
       <c r="R130" t="n">
-        <v>6827679</v>
+        <v>6827656</v>
       </c>
       <c r="S130" t="n">
         <v>10</v>
@@ -13852,10 +13852,10 @@
     </row>
     <row r="131">
       <c r="A131" t="n">
-        <v>120075164</v>
+        <v>120075035</v>
       </c>
       <c r="B131" t="n">
-        <v>78526</v>
+        <v>78262</v>
       </c>
       <c r="C131" t="inlineStr">
         <is>
@@ -13868,21 +13868,21 @@
         </is>
       </c>
       <c r="E131" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H131" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I131" t="inlineStr"/>
@@ -13892,10 +13892,10 @@
         </is>
       </c>
       <c r="Q131" t="n">
-        <v>478092</v>
+        <v>478273</v>
       </c>
       <c r="R131" t="n">
-        <v>6827810</v>
+        <v>6827711</v>
       </c>
       <c r="S131" t="n">
         <v>10</v>
@@ -13954,10 +13954,10 @@
     </row>
     <row r="132">
       <c r="A132" t="n">
-        <v>120075078</v>
+        <v>120074941</v>
       </c>
       <c r="B132" t="n">
-        <v>78526</v>
+        <v>79144</v>
       </c>
       <c r="C132" t="inlineStr">
         <is>
@@ -13970,21 +13970,21 @@
         </is>
       </c>
       <c r="E132" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H132" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I132" t="inlineStr"/>
@@ -13994,10 +13994,10 @@
         </is>
       </c>
       <c r="Q132" t="n">
-        <v>478116</v>
+        <v>478069</v>
       </c>
       <c r="R132" t="n">
-        <v>6827567</v>
+        <v>6827854</v>
       </c>
       <c r="S132" t="n">
         <v>10</v>
@@ -14056,7 +14056,7 @@
     </row>
     <row r="133">
       <c r="A133" t="n">
-        <v>120075068</v>
+        <v>120075095</v>
       </c>
       <c r="B133" t="n">
         <v>78526</v>
@@ -14096,10 +14096,10 @@
         </is>
       </c>
       <c r="Q133" t="n">
-        <v>478174</v>
+        <v>478219</v>
       </c>
       <c r="R133" t="n">
-        <v>6827656</v>
+        <v>6827572</v>
       </c>
       <c r="S133" t="n">
         <v>10</v>
@@ -14872,10 +14872,10 @@
     </row>
     <row r="141">
       <c r="A141" t="n">
-        <v>120074888</v>
+        <v>120075139</v>
       </c>
       <c r="B141" t="n">
-        <v>79144</v>
+        <v>78526</v>
       </c>
       <c r="C141" t="inlineStr">
         <is>
@@ -14888,21 +14888,21 @@
         </is>
       </c>
       <c r="E141" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H141" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I141" t="inlineStr"/>
@@ -14912,10 +14912,10 @@
         </is>
       </c>
       <c r="Q141" t="n">
-        <v>478139</v>
+        <v>478294</v>
       </c>
       <c r="R141" t="n">
-        <v>6827554</v>
+        <v>6827803</v>
       </c>
       <c r="S141" t="n">
         <v>10</v>
@@ -14974,10 +14974,10 @@
     </row>
     <row r="142">
       <c r="A142" t="n">
-        <v>120074948</v>
+        <v>120075089</v>
       </c>
       <c r="B142" t="n">
-        <v>79144</v>
+        <v>78526</v>
       </c>
       <c r="C142" t="inlineStr">
         <is>
@@ -14990,21 +14990,21 @@
         </is>
       </c>
       <c r="E142" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H142" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I142" t="inlineStr"/>
@@ -15014,10 +15014,10 @@
         </is>
       </c>
       <c r="Q142" t="n">
-        <v>478070</v>
+        <v>478153</v>
       </c>
       <c r="R142" t="n">
-        <v>6827723</v>
+        <v>6827517</v>
       </c>
       <c r="S142" t="n">
         <v>10</v>
@@ -15076,10 +15076,10 @@
     </row>
     <row r="143">
       <c r="A143" t="n">
-        <v>120074892</v>
+        <v>120075090</v>
       </c>
       <c r="B143" t="n">
-        <v>79144</v>
+        <v>78526</v>
       </c>
       <c r="C143" t="inlineStr">
         <is>
@@ -15092,21 +15092,21 @@
         </is>
       </c>
       <c r="E143" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H143" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I143" t="inlineStr"/>
@@ -15116,10 +15116,10 @@
         </is>
       </c>
       <c r="Q143" t="n">
-        <v>478243</v>
+        <v>478161</v>
       </c>
       <c r="R143" t="n">
-        <v>6827585</v>
+        <v>6827528</v>
       </c>
       <c r="S143" t="n">
         <v>10</v>
@@ -15178,10 +15178,10 @@
     </row>
     <row r="144">
       <c r="A144" t="n">
-        <v>120074905</v>
+        <v>120075092</v>
       </c>
       <c r="B144" t="n">
-        <v>79144</v>
+        <v>78526</v>
       </c>
       <c r="C144" t="inlineStr">
         <is>
@@ -15194,21 +15194,21 @@
         </is>
       </c>
       <c r="E144" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H144" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I144" t="inlineStr"/>
@@ -15218,10 +15218,10 @@
         </is>
       </c>
       <c r="Q144" t="n">
-        <v>478285</v>
+        <v>478167</v>
       </c>
       <c r="R144" t="n">
-        <v>6827770</v>
+        <v>6827561</v>
       </c>
       <c r="S144" t="n">
         <v>10</v>
@@ -15280,10 +15280,10 @@
     </row>
     <row r="145">
       <c r="A145" t="n">
-        <v>120074886</v>
+        <v>120075172</v>
       </c>
       <c r="B145" t="n">
-        <v>79144</v>
+        <v>78526</v>
       </c>
       <c r="C145" t="inlineStr">
         <is>
@@ -15296,21 +15296,21 @@
         </is>
       </c>
       <c r="E145" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H145" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I145" t="inlineStr"/>
@@ -15320,10 +15320,10 @@
         </is>
       </c>
       <c r="Q145" t="n">
-        <v>478125</v>
+        <v>478055</v>
       </c>
       <c r="R145" t="n">
-        <v>6827604</v>
+        <v>6827768</v>
       </c>
       <c r="S145" t="n">
         <v>10</v>
@@ -15382,10 +15382,10 @@
     </row>
     <row r="146">
       <c r="A146" t="n">
-        <v>120074945</v>
+        <v>120075086</v>
       </c>
       <c r="B146" t="n">
-        <v>79144</v>
+        <v>78526</v>
       </c>
       <c r="C146" t="inlineStr">
         <is>
@@ -15398,21 +15398,21 @@
         </is>
       </c>
       <c r="E146" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H146" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I146" t="inlineStr"/>
@@ -15422,10 +15422,10 @@
         </is>
       </c>
       <c r="Q146" t="n">
-        <v>478061</v>
+        <v>478104</v>
       </c>
       <c r="R146" t="n">
-        <v>6827770</v>
+        <v>6827495</v>
       </c>
       <c r="S146" t="n">
         <v>10</v>
@@ -15484,10 +15484,10 @@
     </row>
     <row r="147">
       <c r="A147" t="n">
-        <v>120074891</v>
+        <v>120074961</v>
       </c>
       <c r="B147" t="n">
-        <v>79144</v>
+        <v>90582</v>
       </c>
       <c r="C147" t="inlineStr">
         <is>
@@ -15500,21 +15500,21 @@
         </is>
       </c>
       <c r="E147" t="n">
-        <v>6453</v>
+        <v>5442</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G147" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H147" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I147" t="inlineStr"/>
@@ -15524,10 +15524,10 @@
         </is>
       </c>
       <c r="Q147" t="n">
-        <v>478212</v>
+        <v>478230</v>
       </c>
       <c r="R147" t="n">
-        <v>6827573</v>
+        <v>6827780</v>
       </c>
       <c r="S147" t="n">
         <v>10</v>
@@ -15586,10 +15586,10 @@
     </row>
     <row r="148">
       <c r="A148" t="n">
-        <v>120074933</v>
+        <v>120075007</v>
       </c>
       <c r="B148" t="n">
-        <v>79144</v>
+        <v>78263</v>
       </c>
       <c r="C148" t="inlineStr">
         <is>
@@ -15602,21 +15602,21 @@
         </is>
       </c>
       <c r="E148" t="n">
-        <v>6453</v>
+        <v>228912</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G148" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H148" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I148" t="inlineStr"/>
@@ -15626,10 +15626,10 @@
         </is>
       </c>
       <c r="Q148" t="n">
-        <v>478189</v>
+        <v>478285</v>
       </c>
       <c r="R148" t="n">
-        <v>6827761</v>
+        <v>6827770</v>
       </c>
       <c r="S148" t="n">
         <v>10</v>
@@ -15688,7 +15688,7 @@
     </row>
     <row r="149">
       <c r="A149" t="n">
-        <v>120074906</v>
+        <v>120074888</v>
       </c>
       <c r="B149" t="n">
         <v>79144</v>
@@ -15728,10 +15728,10 @@
         </is>
       </c>
       <c r="Q149" t="n">
-        <v>478294</v>
+        <v>478139</v>
       </c>
       <c r="R149" t="n">
-        <v>6827790</v>
+        <v>6827554</v>
       </c>
       <c r="S149" t="n">
         <v>10</v>
@@ -15790,10 +15790,10 @@
     </row>
     <row r="150">
       <c r="A150" t="n">
-        <v>120074961</v>
+        <v>120074948</v>
       </c>
       <c r="B150" t="n">
-        <v>90582</v>
+        <v>79144</v>
       </c>
       <c r="C150" t="inlineStr">
         <is>
@@ -15806,21 +15806,21 @@
         </is>
       </c>
       <c r="E150" t="n">
-        <v>5442</v>
+        <v>6453</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G150" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H150" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I150" t="inlineStr"/>
@@ -15830,10 +15830,10 @@
         </is>
       </c>
       <c r="Q150" t="n">
-        <v>478230</v>
+        <v>478070</v>
       </c>
       <c r="R150" t="n">
-        <v>6827780</v>
+        <v>6827723</v>
       </c>
       <c r="S150" t="n">
         <v>10</v>
@@ -15892,10 +15892,10 @@
     </row>
     <row r="151">
       <c r="A151" t="n">
-        <v>120075007</v>
+        <v>120074892</v>
       </c>
       <c r="B151" t="n">
-        <v>78263</v>
+        <v>79144</v>
       </c>
       <c r="C151" t="inlineStr">
         <is>
@@ -15908,21 +15908,21 @@
         </is>
       </c>
       <c r="E151" t="n">
-        <v>228912</v>
+        <v>6453</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G151" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H151" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I151" t="inlineStr"/>
@@ -15932,10 +15932,10 @@
         </is>
       </c>
       <c r="Q151" t="n">
-        <v>478285</v>
+        <v>478243</v>
       </c>
       <c r="R151" t="n">
-        <v>6827770</v>
+        <v>6827585</v>
       </c>
       <c r="S151" t="n">
         <v>10</v>
@@ -15994,10 +15994,10 @@
     </row>
     <row r="152">
       <c r="A152" t="n">
-        <v>120075139</v>
+        <v>120074905</v>
       </c>
       <c r="B152" t="n">
-        <v>78526</v>
+        <v>79144</v>
       </c>
       <c r="C152" t="inlineStr">
         <is>
@@ -16010,21 +16010,21 @@
         </is>
       </c>
       <c r="E152" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G152" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H152" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I152" t="inlineStr"/>
@@ -16034,10 +16034,10 @@
         </is>
       </c>
       <c r="Q152" t="n">
-        <v>478294</v>
+        <v>478285</v>
       </c>
       <c r="R152" t="n">
-        <v>6827803</v>
+        <v>6827770</v>
       </c>
       <c r="S152" t="n">
         <v>10</v>
@@ -16096,10 +16096,10 @@
     </row>
     <row r="153">
       <c r="A153" t="n">
-        <v>120075089</v>
+        <v>120074886</v>
       </c>
       <c r="B153" t="n">
-        <v>78526</v>
+        <v>79144</v>
       </c>
       <c r="C153" t="inlineStr">
         <is>
@@ -16112,21 +16112,21 @@
         </is>
       </c>
       <c r="E153" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G153" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H153" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I153" t="inlineStr"/>
@@ -16136,10 +16136,10 @@
         </is>
       </c>
       <c r="Q153" t="n">
-        <v>478153</v>
+        <v>478125</v>
       </c>
       <c r="R153" t="n">
-        <v>6827517</v>
+        <v>6827604</v>
       </c>
       <c r="S153" t="n">
         <v>10</v>
@@ -16198,10 +16198,10 @@
     </row>
     <row r="154">
       <c r="A154" t="n">
-        <v>120075090</v>
+        <v>120074945</v>
       </c>
       <c r="B154" t="n">
-        <v>78526</v>
+        <v>79144</v>
       </c>
       <c r="C154" t="inlineStr">
         <is>
@@ -16214,21 +16214,21 @@
         </is>
       </c>
       <c r="E154" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G154" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H154" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I154" t="inlineStr"/>
@@ -16238,10 +16238,10 @@
         </is>
       </c>
       <c r="Q154" t="n">
-        <v>478161</v>
+        <v>478061</v>
       </c>
       <c r="R154" t="n">
-        <v>6827528</v>
+        <v>6827770</v>
       </c>
       <c r="S154" t="n">
         <v>10</v>
@@ -16300,10 +16300,10 @@
     </row>
     <row r="155">
       <c r="A155" t="n">
-        <v>120075092</v>
+        <v>120074891</v>
       </c>
       <c r="B155" t="n">
-        <v>78526</v>
+        <v>79144</v>
       </c>
       <c r="C155" t="inlineStr">
         <is>
@@ -16316,21 +16316,21 @@
         </is>
       </c>
       <c r="E155" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G155" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H155" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I155" t="inlineStr"/>
@@ -16340,10 +16340,10 @@
         </is>
       </c>
       <c r="Q155" t="n">
-        <v>478167</v>
+        <v>478212</v>
       </c>
       <c r="R155" t="n">
-        <v>6827561</v>
+        <v>6827573</v>
       </c>
       <c r="S155" t="n">
         <v>10</v>
@@ -16402,10 +16402,10 @@
     </row>
     <row r="156">
       <c r="A156" t="n">
-        <v>120075172</v>
+        <v>120074933</v>
       </c>
       <c r="B156" t="n">
-        <v>78526</v>
+        <v>79144</v>
       </c>
       <c r="C156" t="inlineStr">
         <is>
@@ -16418,21 +16418,21 @@
         </is>
       </c>
       <c r="E156" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G156" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H156" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I156" t="inlineStr"/>
@@ -16442,10 +16442,10 @@
         </is>
       </c>
       <c r="Q156" t="n">
-        <v>478055</v>
+        <v>478189</v>
       </c>
       <c r="R156" t="n">
-        <v>6827768</v>
+        <v>6827761</v>
       </c>
       <c r="S156" t="n">
         <v>10</v>
@@ -16504,10 +16504,10 @@
     </row>
     <row r="157">
       <c r="A157" t="n">
-        <v>120075086</v>
+        <v>120074906</v>
       </c>
       <c r="B157" t="n">
-        <v>78526</v>
+        <v>79144</v>
       </c>
       <c r="C157" t="inlineStr">
         <is>
@@ -16520,21 +16520,21 @@
         </is>
       </c>
       <c r="E157" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G157" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H157" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I157" t="inlineStr"/>
@@ -16544,10 +16544,10 @@
         </is>
       </c>
       <c r="Q157" t="n">
-        <v>478104</v>
+        <v>478294</v>
       </c>
       <c r="R157" t="n">
-        <v>6827495</v>
+        <v>6827790</v>
       </c>
       <c r="S157" t="n">
         <v>10</v>
@@ -17014,7 +17014,7 @@
     </row>
     <row r="162">
       <c r="A162" t="n">
-        <v>120075026</v>
+        <v>120075043</v>
       </c>
       <c r="B162" t="n">
         <v>78262</v>
@@ -17054,10 +17054,10 @@
         </is>
       </c>
       <c r="Q162" t="n">
-        <v>478161</v>
+        <v>478103</v>
       </c>
       <c r="R162" t="n">
-        <v>6827592</v>
+        <v>6827803</v>
       </c>
       <c r="S162" t="n">
         <v>10</v>
@@ -17116,10 +17116,10 @@
     </row>
     <row r="163">
       <c r="A163" t="n">
-        <v>120075046</v>
+        <v>120075048</v>
       </c>
       <c r="B163" t="n">
-        <v>78262</v>
+        <v>56514</v>
       </c>
       <c r="C163" t="inlineStr">
         <is>
@@ -17132,34 +17132,39 @@
         </is>
       </c>
       <c r="E163" t="n">
-        <v>6446</v>
+        <v>102612</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G163" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H163" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I163" t="inlineStr"/>
+      <c r="M163" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="P163" t="inlineStr">
         <is>
           <t>Hevoslamm, Dlr</t>
         </is>
       </c>
       <c r="Q163" t="n">
-        <v>478285</v>
+        <v>478070</v>
       </c>
       <c r="R163" t="n">
-        <v>6827770</v>
+        <v>6827723</v>
       </c>
       <c r="S163" t="n">
         <v>10</v>
@@ -17218,10 +17223,10 @@
     </row>
     <row r="164">
       <c r="A164" t="n">
-        <v>120075043</v>
+        <v>120075214</v>
       </c>
       <c r="B164" t="n">
-        <v>78262</v>
+        <v>78171</v>
       </c>
       <c r="C164" t="inlineStr">
         <is>
@@ -17234,21 +17239,21 @@
         </is>
       </c>
       <c r="E164" t="n">
-        <v>6446</v>
+        <v>353</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G164" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H164" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I164" t="inlineStr"/>
@@ -17258,10 +17263,10 @@
         </is>
       </c>
       <c r="Q164" t="n">
-        <v>478103</v>
+        <v>478266</v>
       </c>
       <c r="R164" t="n">
-        <v>6827803</v>
+        <v>6827724</v>
       </c>
       <c r="S164" t="n">
         <v>10</v>
@@ -17320,10 +17325,10 @@
     </row>
     <row r="165">
       <c r="A165" t="n">
-        <v>120075048</v>
+        <v>120075203</v>
       </c>
       <c r="B165" t="n">
-        <v>56514</v>
+        <v>78171</v>
       </c>
       <c r="C165" t="inlineStr">
         <is>
@@ -17336,39 +17341,34 @@
         </is>
       </c>
       <c r="E165" t="n">
-        <v>102612</v>
+        <v>353</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G165" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H165" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I165" t="inlineStr"/>
-      <c r="M165" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
       <c r="P165" t="inlineStr">
         <is>
           <t>Hevoslamm, Dlr</t>
         </is>
       </c>
       <c r="Q165" t="n">
-        <v>478070</v>
+        <v>478125</v>
       </c>
       <c r="R165" t="n">
-        <v>6827723</v>
+        <v>6827631</v>
       </c>
       <c r="S165" t="n">
         <v>10</v>
@@ -17427,10 +17427,10 @@
     </row>
     <row r="166">
       <c r="A166" t="n">
-        <v>120075012</v>
+        <v>120075026</v>
       </c>
       <c r="B166" t="n">
-        <v>78263</v>
+        <v>78262</v>
       </c>
       <c r="C166" t="inlineStr">
         <is>
@@ -17443,21 +17443,21 @@
         </is>
       </c>
       <c r="E166" t="n">
-        <v>228912</v>
+        <v>6446</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G166" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H166" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I166" t="inlineStr"/>
@@ -17467,10 +17467,10 @@
         </is>
       </c>
       <c r="Q166" t="n">
-        <v>478055</v>
+        <v>478161</v>
       </c>
       <c r="R166" t="n">
-        <v>6827786</v>
+        <v>6827592</v>
       </c>
       <c r="S166" t="n">
         <v>10</v>
@@ -17529,10 +17529,10 @@
     </row>
     <row r="167">
       <c r="A167" t="n">
-        <v>120075001</v>
+        <v>120075046</v>
       </c>
       <c r="B167" t="n">
-        <v>78263</v>
+        <v>78262</v>
       </c>
       <c r="C167" t="inlineStr">
         <is>
@@ -17545,21 +17545,21 @@
         </is>
       </c>
       <c r="E167" t="n">
-        <v>228912</v>
+        <v>6446</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G167" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H167" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I167" t="inlineStr"/>
@@ -17569,10 +17569,10 @@
         </is>
       </c>
       <c r="Q167" t="n">
-        <v>478125</v>
+        <v>478285</v>
       </c>
       <c r="R167" t="n">
-        <v>6827604</v>
+        <v>6827770</v>
       </c>
       <c r="S167" t="n">
         <v>10</v>
@@ -17631,7 +17631,7 @@
     </row>
     <row r="168">
       <c r="A168" t="n">
-        <v>120075010</v>
+        <v>120075012</v>
       </c>
       <c r="B168" t="n">
         <v>78263</v>
@@ -17671,10 +17671,10 @@
         </is>
       </c>
       <c r="Q168" t="n">
-        <v>478074</v>
+        <v>478055</v>
       </c>
       <c r="R168" t="n">
-        <v>6827772</v>
+        <v>6827786</v>
       </c>
       <c r="S168" t="n">
         <v>10</v>
@@ -17733,10 +17733,10 @@
     </row>
     <row r="169">
       <c r="A169" t="n">
-        <v>120075214</v>
+        <v>120075001</v>
       </c>
       <c r="B169" t="n">
-        <v>78171</v>
+        <v>78263</v>
       </c>
       <c r="C169" t="inlineStr">
         <is>
@@ -17749,21 +17749,21 @@
         </is>
       </c>
       <c r="E169" t="n">
-        <v>353</v>
+        <v>228912</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G169" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H169" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I169" t="inlineStr"/>
@@ -17773,10 +17773,10 @@
         </is>
       </c>
       <c r="Q169" t="n">
-        <v>478266</v>
+        <v>478125</v>
       </c>
       <c r="R169" t="n">
-        <v>6827724</v>
+        <v>6827604</v>
       </c>
       <c r="S169" t="n">
         <v>10</v>
@@ -17835,10 +17835,10 @@
     </row>
     <row r="170">
       <c r="A170" t="n">
-        <v>120075203</v>
+        <v>120075010</v>
       </c>
       <c r="B170" t="n">
-        <v>78171</v>
+        <v>78263</v>
       </c>
       <c r="C170" t="inlineStr">
         <is>
@@ -17851,21 +17851,21 @@
         </is>
       </c>
       <c r="E170" t="n">
-        <v>353</v>
+        <v>228912</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G170" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H170" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I170" t="inlineStr"/>
@@ -17875,10 +17875,10 @@
         </is>
       </c>
       <c r="Q170" t="n">
-        <v>478125</v>
+        <v>478074</v>
       </c>
       <c r="R170" t="n">
-        <v>6827631</v>
+        <v>6827772</v>
       </c>
       <c r="S170" t="n">
         <v>10</v>

--- a/artfynd/A 32983-2023 artfynd.xlsx
+++ b/artfynd/A 32983-2023 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>120075067</v>
+        <v>120074999</v>
       </c>
       <c r="B2" t="n">
-        <v>78526</v>
+        <v>78279</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>478164</v>
+        <v>478161</v>
       </c>
       <c r="R2" t="n">
-        <v>6827661</v>
+        <v>6827592</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -777,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>120075207</v>
+        <v>120075007</v>
       </c>
       <c r="B3" t="n">
-        <v>78171</v>
+        <v>78279</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -793,21 +793,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>353</v>
+        <v>228912</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -817,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>478157</v>
+        <v>478285</v>
       </c>
       <c r="R3" t="n">
-        <v>6827509</v>
+        <v>6827770</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -879,10 +879,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>120074932</v>
+        <v>120075159</v>
       </c>
       <c r="B4" t="n">
-        <v>79144</v>
+        <v>78542</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -895,21 +895,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -919,10 +919,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>478250</v>
+        <v>478100</v>
       </c>
       <c r="R4" t="n">
-        <v>6827802</v>
+        <v>6827729</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -981,10 +981,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>120075197</v>
+        <v>120075083</v>
       </c>
       <c r="B5" t="n">
-        <v>91840</v>
+        <v>78542</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -993,47 +993,38 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
           <t>Hevoslamm, Dlr</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>478077</v>
+        <v>478097</v>
       </c>
       <c r="R5" t="n">
-        <v>6827805</v>
+        <v>6827527</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1092,10 +1083,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>120075127</v>
+        <v>120074905</v>
       </c>
       <c r="B6" t="n">
-        <v>78526</v>
+        <v>79160</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1108,21 +1099,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1132,10 +1123,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>478292</v>
+        <v>478285</v>
       </c>
       <c r="R6" t="n">
-        <v>6827708</v>
+        <v>6827770</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1194,10 +1185,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>120075070</v>
+        <v>120075134</v>
       </c>
       <c r="B7" t="n">
-        <v>78526</v>
+        <v>78542</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1234,10 +1225,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>478135</v>
+        <v>478266</v>
       </c>
       <c r="R7" t="n">
-        <v>6827625</v>
+        <v>6827765</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1296,10 +1287,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>120074999</v>
+        <v>120075171</v>
       </c>
       <c r="B8" t="n">
-        <v>78263</v>
+        <v>78542</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1312,21 +1303,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1336,10 +1327,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>478161</v>
+        <v>478073</v>
       </c>
       <c r="R8" t="n">
-        <v>6827592</v>
+        <v>6827831</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1398,10 +1389,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>120075011</v>
+        <v>120074927</v>
       </c>
       <c r="B9" t="n">
-        <v>78263</v>
+        <v>78576</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1414,21 +1405,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>228912</v>
+        <v>185</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1438,10 +1429,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>478103</v>
+        <v>478073</v>
       </c>
       <c r="R9" t="n">
-        <v>6827803</v>
+        <v>6827836</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1500,10 +1491,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>120075013</v>
+        <v>120075231</v>
       </c>
       <c r="B10" t="n">
-        <v>78263</v>
+        <v>78187</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1516,21 +1507,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>228912</v>
+        <v>353</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1540,10 +1531,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>478239</v>
+        <v>478067</v>
       </c>
       <c r="R10" t="n">
-        <v>6827752</v>
+        <v>6827863</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1602,10 +1593,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>120074925</v>
+        <v>120075230</v>
       </c>
       <c r="B11" t="n">
-        <v>78560</v>
+        <v>78187</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1618,21 +1609,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>185</v>
+        <v>353</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1642,10 +1633,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>478088</v>
+        <v>478064</v>
       </c>
       <c r="R11" t="n">
-        <v>6827834</v>
+        <v>6827866</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1704,10 +1695,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>120074912</v>
+        <v>120075196</v>
       </c>
       <c r="B12" t="n">
-        <v>78560</v>
+        <v>78542</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1720,21 +1711,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1744,10 +1735,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>478149</v>
+        <v>478288</v>
       </c>
       <c r="R12" t="n">
-        <v>6827714</v>
+        <v>6827682</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1806,10 +1797,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>120075019</v>
+        <v>120075139</v>
       </c>
       <c r="B13" t="n">
-        <v>79607</v>
+        <v>78542</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1822,21 +1813,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1846,10 +1837,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>478227</v>
+        <v>478294</v>
       </c>
       <c r="R13" t="n">
-        <v>6827655</v>
+        <v>6827803</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1908,10 +1899,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>120074914</v>
+        <v>120075162</v>
       </c>
       <c r="B14" t="n">
-        <v>78560</v>
+        <v>78542</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1924,21 +1915,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1948,10 +1939,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>478169</v>
+        <v>478080</v>
       </c>
       <c r="R14" t="n">
-        <v>6827680</v>
+        <v>6827808</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2010,10 +2001,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>120075227</v>
+        <v>120075085</v>
       </c>
       <c r="B15" t="n">
-        <v>78171</v>
+        <v>78542</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2026,21 +2017,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>353</v>
+        <v>6425</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2050,10 +2041,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>478088</v>
+        <v>478094</v>
       </c>
       <c r="R15" t="n">
-        <v>6827834</v>
+        <v>6827504</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2112,10 +2103,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>120075217</v>
+        <v>120075173</v>
       </c>
       <c r="B16" t="n">
-        <v>78171</v>
+        <v>78542</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2128,21 +2119,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>353</v>
+        <v>6425</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2152,10 +2143,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>478264</v>
+        <v>478052</v>
       </c>
       <c r="R16" t="n">
-        <v>6827839</v>
+        <v>6827754</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2214,10 +2205,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>120075133</v>
+        <v>120075043</v>
       </c>
       <c r="B17" t="n">
-        <v>78526</v>
+        <v>78278</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2230,21 +2221,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2254,10 +2245,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>478258</v>
+        <v>478103</v>
       </c>
       <c r="R17" t="n">
-        <v>6827753</v>
+        <v>6827803</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2316,10 +2307,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>120075069</v>
+        <v>120075145</v>
       </c>
       <c r="B18" t="n">
-        <v>78526</v>
+        <v>78542</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2356,10 +2347,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>478157</v>
+        <v>478226</v>
       </c>
       <c r="R18" t="n">
-        <v>6827611</v>
+        <v>6827777</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2418,10 +2409,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>120075157</v>
+        <v>120075008</v>
       </c>
       <c r="B19" t="n">
-        <v>78526</v>
+        <v>78279</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2434,21 +2425,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2458,10 +2449,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>478103</v>
+        <v>478299</v>
       </c>
       <c r="R19" t="n">
-        <v>6827718</v>
+        <v>6827805</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2520,10 +2511,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>120075138</v>
+        <v>120074907</v>
       </c>
       <c r="B20" t="n">
-        <v>78526</v>
+        <v>79160</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2536,21 +2527,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2560,10 +2551,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>478294</v>
+        <v>478263</v>
       </c>
       <c r="R20" t="n">
-        <v>6827781</v>
+        <v>6827838</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2622,10 +2613,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>120074935</v>
+        <v>120074883</v>
       </c>
       <c r="B21" t="n">
-        <v>79144</v>
+        <v>79160</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2662,10 +2653,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>478150</v>
+        <v>478142</v>
       </c>
       <c r="R21" t="n">
-        <v>6827745</v>
+        <v>6827623</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2724,10 +2715,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>120075205</v>
+        <v>120074938</v>
       </c>
       <c r="B22" t="n">
-        <v>78171</v>
+        <v>79160</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2740,21 +2731,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>353</v>
+        <v>6453</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2764,10 +2755,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>478117</v>
+        <v>478097</v>
       </c>
       <c r="R22" t="n">
-        <v>6827612</v>
+        <v>6827756</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2826,10 +2817,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>120075231</v>
+        <v>120074930</v>
       </c>
       <c r="B23" t="n">
-        <v>78171</v>
+        <v>79160</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -2842,21 +2833,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>353</v>
+        <v>6453</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2866,10 +2857,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>478067</v>
+        <v>478299</v>
       </c>
       <c r="R23" t="n">
-        <v>6827863</v>
+        <v>6827805</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2928,10 +2919,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>120075208</v>
+        <v>120075044</v>
       </c>
       <c r="B24" t="n">
-        <v>78171</v>
+        <v>78278</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -2944,21 +2935,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>353</v>
+        <v>6446</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -2968,10 +2959,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>478158</v>
+        <v>478060</v>
       </c>
       <c r="R24" t="n">
-        <v>6827519</v>
+        <v>6827770</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3030,10 +3021,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>120075196</v>
+        <v>120075074</v>
       </c>
       <c r="B25" t="n">
-        <v>78526</v>
+        <v>78542</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3070,10 +3061,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>478288</v>
+        <v>478138</v>
       </c>
       <c r="R25" t="n">
-        <v>6827682</v>
+        <v>6827599</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3132,10 +3123,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>120075144</v>
+        <v>120075077</v>
       </c>
       <c r="B26" t="n">
-        <v>78526</v>
+        <v>78542</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3172,10 +3163,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>478261</v>
+        <v>478124</v>
       </c>
       <c r="R26" t="n">
-        <v>6827822</v>
+        <v>6827560</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3234,10 +3225,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>120074986</v>
+        <v>120075174</v>
       </c>
       <c r="B27" t="n">
-        <v>79608</v>
+        <v>78542</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3250,21 +3241,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>2081</v>
+        <v>6425</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3274,10 +3265,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>478096</v>
+        <v>478057</v>
       </c>
       <c r="R27" t="n">
-        <v>6827549</v>
+        <v>6827749</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3336,10 +3327,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>120075016</v>
+        <v>120075062</v>
       </c>
       <c r="B28" t="n">
-        <v>79607</v>
+        <v>78542</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3352,21 +3343,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3376,10 +3367,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>478096</v>
+        <v>478221</v>
       </c>
       <c r="R28" t="n">
-        <v>6827549</v>
+        <v>6827719</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3438,10 +3429,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>120074947</v>
+        <v>120074943</v>
       </c>
       <c r="B29" t="n">
-        <v>79144</v>
+        <v>79160</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3478,10 +3469,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>478061</v>
+        <v>478073</v>
       </c>
       <c r="R29" t="n">
-        <v>6827751</v>
+        <v>6827827</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3540,10 +3531,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>120075015</v>
+        <v>120075001</v>
       </c>
       <c r="B30" t="n">
-        <v>79607</v>
+        <v>78279</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3556,21 +3547,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6458</v>
+        <v>228912</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3580,10 +3571,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>478114</v>
+        <v>478125</v>
       </c>
       <c r="R30" t="n">
-        <v>6827633</v>
+        <v>6827604</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3642,10 +3633,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>120075219</v>
+        <v>120074929</v>
       </c>
       <c r="B31" t="n">
-        <v>78171</v>
+        <v>78576</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3658,21 +3649,21 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>353</v>
+        <v>185</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3682,10 +3673,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>478169</v>
+        <v>478045</v>
       </c>
       <c r="R31" t="n">
-        <v>6827760</v>
+        <v>6827724</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3744,10 +3735,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>120074915</v>
+        <v>120074914</v>
       </c>
       <c r="B32" t="n">
-        <v>78560</v>
+        <v>78576</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -3784,10 +3775,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>478102</v>
+        <v>478169</v>
       </c>
       <c r="R32" t="n">
-        <v>6827555</v>
+        <v>6827680</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3846,10 +3837,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>120074881</v>
+        <v>120075204</v>
       </c>
       <c r="B33" t="n">
-        <v>79144</v>
+        <v>78187</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -3862,21 +3853,21 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6453</v>
+        <v>353</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -3886,10 +3877,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>478184</v>
+        <v>478115</v>
       </c>
       <c r="R33" t="n">
-        <v>6827728</v>
+        <v>6827614</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -3948,10 +3939,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>120075047</v>
+        <v>120075214</v>
       </c>
       <c r="B34" t="n">
-        <v>78262</v>
+        <v>78187</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -3964,21 +3955,21 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6446</v>
+        <v>353</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -3988,10 +3979,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>478212</v>
+        <v>478266</v>
       </c>
       <c r="R34" t="n">
-        <v>6827573</v>
+        <v>6827724</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4050,10 +4041,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>120074996</v>
+        <v>120075206</v>
       </c>
       <c r="B35" t="n">
-        <v>78263</v>
+        <v>78187</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4066,21 +4057,21 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>228912</v>
+        <v>353</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4090,10 +4081,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>478165</v>
+        <v>478125</v>
       </c>
       <c r="R35" t="n">
-        <v>6827712</v>
+        <v>6827604</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4152,10 +4143,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>120075054</v>
+        <v>120074956</v>
       </c>
       <c r="B36" t="n">
-        <v>90580</v>
+        <v>57320</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4168,34 +4159,39 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
+      <c r="M36" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P36" t="inlineStr">
         <is>
           <t>Hevoslamm, Dlr</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>478126</v>
+        <v>478278</v>
       </c>
       <c r="R36" t="n">
-        <v>6827477</v>
+        <v>6827832</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4228,6 +4224,11 @@
       <c r="AA36" t="inlineStr">
         <is>
           <t>2024-09-27</t>
+        </is>
+      </c>
+      <c r="AC36" t="inlineStr">
+        <is>
+          <t>Färska ringhack (tall)</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4254,10 +4255,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>120075147</v>
+        <v>120075015</v>
       </c>
       <c r="B37" t="n">
-        <v>78526</v>
+        <v>79623</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4270,21 +4271,21 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4294,10 +4295,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>478153</v>
+        <v>478114</v>
       </c>
       <c r="R37" t="n">
-        <v>6827728</v>
+        <v>6827633</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4356,10 +4357,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>120075173</v>
+        <v>120075120</v>
       </c>
       <c r="B38" t="n">
-        <v>78526</v>
+        <v>78542</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4396,10 +4397,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>478052</v>
+        <v>478223</v>
       </c>
       <c r="R38" t="n">
-        <v>6827754</v>
+        <v>6827657</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4458,10 +4459,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>120075074</v>
+        <v>120075215</v>
       </c>
       <c r="B39" t="n">
-        <v>78526</v>
+        <v>78187</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4474,21 +4475,21 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6425</v>
+        <v>353</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4498,10 +4499,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>478138</v>
+        <v>478239</v>
       </c>
       <c r="R39" t="n">
-        <v>6827599</v>
+        <v>6827752</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4560,10 +4561,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>120075063</v>
+        <v>120075003</v>
       </c>
       <c r="B40" t="n">
-        <v>78526</v>
+        <v>78279</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -4576,21 +4577,21 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4600,10 +4601,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>478201</v>
+        <v>478137</v>
       </c>
       <c r="R40" t="n">
-        <v>6827693</v>
+        <v>6827553</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4662,10 +4663,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>120075145</v>
+        <v>120075202</v>
       </c>
       <c r="B41" t="n">
-        <v>78526</v>
+        <v>78187</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -4678,21 +4679,21 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6425</v>
+        <v>353</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4702,10 +4703,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>478226</v>
+        <v>478218</v>
       </c>
       <c r="R41" t="n">
-        <v>6827777</v>
+        <v>6827721</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4764,10 +4765,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>120075174</v>
+        <v>120075143</v>
       </c>
       <c r="B42" t="n">
-        <v>78526</v>
+        <v>78542</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -4804,10 +4805,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>478057</v>
+        <v>478301</v>
       </c>
       <c r="R42" t="n">
-        <v>6827749</v>
+        <v>6827814</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4866,10 +4867,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>120075039</v>
+        <v>120074939</v>
       </c>
       <c r="B43" t="n">
-        <v>78262</v>
+        <v>79160</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -4882,21 +4883,21 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>6446</v>
+        <v>6453</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -4906,10 +4907,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>478238</v>
+        <v>478091</v>
       </c>
       <c r="R43" t="n">
-        <v>6827752</v>
+        <v>6827838</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -4968,10 +4969,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>120075239</v>
+        <v>120075157</v>
       </c>
       <c r="B44" t="n">
-        <v>77458</v>
+        <v>78542</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -4984,21 +4985,21 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>6487</v>
+        <v>6425</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Blågrå svartspik</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Chaenothecopsis fennica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Laurila) Tibell</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -5008,10 +5009,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>478137</v>
+        <v>478103</v>
       </c>
       <c r="R44" t="n">
-        <v>6827554</v>
+        <v>6827718</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5070,10 +5071,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>120075198</v>
+        <v>120074886</v>
       </c>
       <c r="B45" t="n">
-        <v>91840</v>
+        <v>79160</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5082,25 +5083,25 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>4364</v>
+        <v>6453</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5110,10 +5111,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>478163</v>
+        <v>478125</v>
       </c>
       <c r="R45" t="n">
-        <v>6827530</v>
+        <v>6827604</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5172,10 +5173,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>120075081</v>
+        <v>120074881</v>
       </c>
       <c r="B46" t="n">
-        <v>78526</v>
+        <v>79160</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -5188,21 +5189,21 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5212,10 +5213,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>478096</v>
+        <v>478184</v>
       </c>
       <c r="R46" t="n">
-        <v>6827550</v>
+        <v>6827728</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5274,10 +5275,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>120075242</v>
+        <v>120074941</v>
       </c>
       <c r="B47" t="n">
-        <v>77910</v>
+        <v>79160</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -5290,21 +5291,21 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>6437</v>
+        <v>6453</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5314,10 +5315,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>478136</v>
+        <v>478069</v>
       </c>
       <c r="R47" t="n">
-        <v>6827556</v>
+        <v>6827854</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5376,10 +5377,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>120075094</v>
+        <v>120075234</v>
       </c>
       <c r="B48" t="n">
-        <v>78526</v>
+        <v>78187</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -5392,21 +5393,21 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>6425</v>
+        <v>353</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5416,10 +5417,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>478205</v>
+        <v>478069</v>
       </c>
       <c r="R48" t="n">
-        <v>6827556</v>
+        <v>6827741</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5478,10 +5479,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>120075064</v>
+        <v>120075165</v>
       </c>
       <c r="B49" t="n">
-        <v>78526</v>
+        <v>78542</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -5518,10 +5519,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>478192</v>
+        <v>478078</v>
       </c>
       <c r="R49" t="n">
-        <v>6827690</v>
+        <v>6827834</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5580,10 +5581,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>120074907</v>
+        <v>120075142</v>
       </c>
       <c r="B50" t="n">
-        <v>79144</v>
+        <v>78542</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -5596,21 +5597,21 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -5620,10 +5621,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>478263</v>
+        <v>478313</v>
       </c>
       <c r="R50" t="n">
-        <v>6827838</v>
+        <v>6827798</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5682,10 +5683,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>120075037</v>
+        <v>120075146</v>
       </c>
       <c r="B51" t="n">
-        <v>78262</v>
+        <v>78542</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -5698,21 +5699,21 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -5722,10 +5723,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>478265</v>
+        <v>478154</v>
       </c>
       <c r="R51" t="n">
-        <v>6827716</v>
+        <v>6827747</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5784,10 +5785,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>120074883</v>
+        <v>120075039</v>
       </c>
       <c r="B52" t="n">
-        <v>79144</v>
+        <v>78278</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -5800,21 +5801,21 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>6453</v>
+        <v>6446</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -5824,10 +5825,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>478142</v>
+        <v>478238</v>
       </c>
       <c r="R52" t="n">
-        <v>6827623</v>
+        <v>6827752</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -5886,10 +5887,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>120075038</v>
+        <v>120075040</v>
       </c>
       <c r="B53" t="n">
-        <v>78262</v>
+        <v>78278</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -5926,10 +5927,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>478261</v>
+        <v>478250</v>
       </c>
       <c r="R53" t="n">
-        <v>6827731</v>
+        <v>6827802</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -5988,10 +5989,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>120075027</v>
+        <v>120075082</v>
       </c>
       <c r="B54" t="n">
-        <v>78262</v>
+        <v>78542</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
@@ -6004,21 +6005,21 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -6028,10 +6029,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>478144</v>
+        <v>478097</v>
       </c>
       <c r="R54" t="n">
-        <v>6827593</v>
+        <v>6827544</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6090,10 +6091,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>120075165</v>
+        <v>120074906</v>
       </c>
       <c r="B55" t="n">
-        <v>78526</v>
+        <v>79160</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
@@ -6106,21 +6107,21 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -6130,10 +6131,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>478078</v>
+        <v>478294</v>
       </c>
       <c r="R55" t="n">
-        <v>6827834</v>
+        <v>6827790</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6192,10 +6193,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>120075177</v>
+        <v>120074952</v>
       </c>
       <c r="B56" t="n">
-        <v>78526</v>
+        <v>79131</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
@@ -6208,21 +6209,21 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>6425</v>
+        <v>229821</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -6232,10 +6233,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>478075</v>
+        <v>478120</v>
       </c>
       <c r="R56" t="n">
-        <v>6827717</v>
+        <v>6827605</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6294,10 +6295,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>120075060</v>
+        <v>120075225</v>
       </c>
       <c r="B57" t="n">
-        <v>78526</v>
+        <v>78187</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
@@ -6310,21 +6311,21 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>6425</v>
+        <v>353</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -6334,10 +6335,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>478087</v>
+        <v>478075</v>
       </c>
       <c r="R57" t="n">
-        <v>6827718</v>
+        <v>6827798</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6396,10 +6397,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>120075204</v>
+        <v>120075207</v>
       </c>
       <c r="B58" t="n">
-        <v>78171</v>
+        <v>78187</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
@@ -6436,10 +6437,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>478115</v>
+        <v>478157</v>
       </c>
       <c r="R58" t="n">
-        <v>6827614</v>
+        <v>6827509</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6498,10 +6499,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>120074922</v>
+        <v>120075226</v>
       </c>
       <c r="B59" t="n">
-        <v>78560</v>
+        <v>78187</v>
       </c>
       <c r="C59" t="inlineStr">
         <is>
@@ -6514,21 +6515,21 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>185</v>
+        <v>353</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
@@ -6538,10 +6539,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>478103</v>
+        <v>478098</v>
       </c>
       <c r="R59" t="n">
-        <v>6827718</v>
+        <v>6827815</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6600,10 +6601,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>120074943</v>
+        <v>120075217</v>
       </c>
       <c r="B60" t="n">
-        <v>79144</v>
+        <v>78187</v>
       </c>
       <c r="C60" t="inlineStr">
         <is>
@@ -6616,21 +6617,21 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>6453</v>
+        <v>353</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
@@ -6640,10 +6641,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>478073</v>
+        <v>478264</v>
       </c>
       <c r="R60" t="n">
-        <v>6827827</v>
+        <v>6827839</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -6702,10 +6703,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>120075146</v>
+        <v>120074986</v>
       </c>
       <c r="B61" t="n">
-        <v>78526</v>
+        <v>79624</v>
       </c>
       <c r="C61" t="inlineStr">
         <is>
@@ -6718,21 +6719,21 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>6425</v>
+        <v>2081</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
@@ -6742,10 +6743,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>478154</v>
+        <v>478096</v>
       </c>
       <c r="R61" t="n">
-        <v>6827747</v>
+        <v>6827549</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -6804,10 +6805,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>120075061</v>
+        <v>120075133</v>
       </c>
       <c r="B62" t="n">
-        <v>78526</v>
+        <v>78542</v>
       </c>
       <c r="C62" t="inlineStr">
         <is>
@@ -6844,10 +6845,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>478160</v>
+        <v>478258</v>
       </c>
       <c r="R62" t="n">
-        <v>6827710</v>
+        <v>6827753</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -6906,10 +6907,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>120075084</v>
+        <v>120075168</v>
       </c>
       <c r="B63" t="n">
-        <v>78526</v>
+        <v>78542</v>
       </c>
       <c r="C63" t="inlineStr">
         <is>
@@ -6946,10 +6947,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>478098</v>
+        <v>478086</v>
       </c>
       <c r="R63" t="n">
-        <v>6827520</v>
+        <v>6827868</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -7008,10 +7009,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>120075066</v>
+        <v>120075067</v>
       </c>
       <c r="B64" t="n">
-        <v>78526</v>
+        <v>78542</v>
       </c>
       <c r="C64" t="inlineStr">
         <is>
@@ -7048,10 +7049,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>478160</v>
+        <v>478164</v>
       </c>
       <c r="R64" t="n">
-        <v>6827680</v>
+        <v>6827661</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -7110,10 +7111,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>120074938</v>
+        <v>120075086</v>
       </c>
       <c r="B65" t="n">
-        <v>79144</v>
+        <v>78542</v>
       </c>
       <c r="C65" t="inlineStr">
         <is>
@@ -7126,21 +7127,21 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
@@ -7150,10 +7151,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>478097</v>
+        <v>478104</v>
       </c>
       <c r="R65" t="n">
-        <v>6827756</v>
+        <v>6827495</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7212,10 +7213,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>120075000</v>
+        <v>120075192</v>
       </c>
       <c r="B66" t="n">
-        <v>78263</v>
+        <v>78542</v>
       </c>
       <c r="C66" t="inlineStr">
         <is>
@@ -7228,21 +7229,21 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
@@ -7252,10 +7253,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>478121</v>
+        <v>478282</v>
       </c>
       <c r="R66" t="n">
-        <v>6827607</v>
+        <v>6827683</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7314,10 +7315,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>120075166</v>
+        <v>120074904</v>
       </c>
       <c r="B67" t="n">
-        <v>78526</v>
+        <v>79160</v>
       </c>
       <c r="C67" t="inlineStr">
         <is>
@@ -7330,21 +7331,21 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
@@ -7354,10 +7355,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>478092</v>
+        <v>478262</v>
       </c>
       <c r="R67" t="n">
-        <v>6827839</v>
+        <v>6827730</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7416,10 +7417,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>120075130</v>
+        <v>120075084</v>
       </c>
       <c r="B68" t="n">
-        <v>78526</v>
+        <v>78542</v>
       </c>
       <c r="C68" t="inlineStr">
         <is>
@@ -7456,10 +7457,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>478264</v>
+        <v>478098</v>
       </c>
       <c r="R68" t="n">
-        <v>6827733</v>
+        <v>6827520</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7518,10 +7519,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>120075134</v>
+        <v>120075037</v>
       </c>
       <c r="B69" t="n">
-        <v>78526</v>
+        <v>78278</v>
       </c>
       <c r="C69" t="inlineStr">
         <is>
@@ -7534,21 +7535,21 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
@@ -7558,10 +7559,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>478266</v>
+        <v>478265</v>
       </c>
       <c r="R69" t="n">
-        <v>6827765</v>
+        <v>6827716</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -7620,10 +7621,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>120075082</v>
+        <v>120075012</v>
       </c>
       <c r="B70" t="n">
-        <v>78526</v>
+        <v>78279</v>
       </c>
       <c r="C70" t="inlineStr">
         <is>
@@ -7636,21 +7637,21 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
@@ -7660,10 +7661,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>478097</v>
+        <v>478055</v>
       </c>
       <c r="R70" t="n">
-        <v>6827544</v>
+        <v>6827786</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -7722,10 +7723,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>120075131</v>
+        <v>120075013</v>
       </c>
       <c r="B71" t="n">
-        <v>78526</v>
+        <v>78279</v>
       </c>
       <c r="C71" t="inlineStr">
         <is>
@@ -7738,21 +7739,21 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
@@ -7762,10 +7763,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>478258</v>
+        <v>478239</v>
       </c>
       <c r="R71" t="n">
-        <v>6827731</v>
+        <v>6827752</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -7824,10 +7825,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>120075120</v>
+        <v>120075216</v>
       </c>
       <c r="B72" t="n">
-        <v>78526</v>
+        <v>78187</v>
       </c>
       <c r="C72" t="inlineStr">
         <is>
@@ -7840,21 +7841,21 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>6425</v>
+        <v>353</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
@@ -7864,10 +7865,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>478223</v>
+        <v>478294</v>
       </c>
       <c r="R72" t="n">
-        <v>6827657</v>
+        <v>6827790</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -7926,10 +7927,10 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>120074939</v>
+        <v>120075069</v>
       </c>
       <c r="B73" t="n">
-        <v>79144</v>
+        <v>78542</v>
       </c>
       <c r="C73" t="inlineStr">
         <is>
@@ -7942,21 +7943,21 @@
         </is>
       </c>
       <c r="E73" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
@@ -7966,10 +7967,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>478091</v>
+        <v>478157</v>
       </c>
       <c r="R73" t="n">
-        <v>6827838</v>
+        <v>6827611</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -8028,10 +8029,10 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>120075003</v>
+        <v>120074891</v>
       </c>
       <c r="B74" t="n">
-        <v>78263</v>
+        <v>79160</v>
       </c>
       <c r="C74" t="inlineStr">
         <is>
@@ -8044,21 +8045,21 @@
         </is>
       </c>
       <c r="E74" t="n">
-        <v>228912</v>
+        <v>6453</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
@@ -8068,10 +8069,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>478137</v>
+        <v>478212</v>
       </c>
       <c r="R74" t="n">
-        <v>6827553</v>
+        <v>6827573</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -8130,10 +8131,10 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>120075161</v>
+        <v>120075092</v>
       </c>
       <c r="B75" t="n">
-        <v>78526</v>
+        <v>78542</v>
       </c>
       <c r="C75" t="inlineStr">
         <is>
@@ -8170,10 +8171,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>478082</v>
+        <v>478167</v>
       </c>
       <c r="R75" t="n">
-        <v>6827766</v>
+        <v>6827561</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -8232,10 +8233,10 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>120075121</v>
+        <v>120075172</v>
       </c>
       <c r="B76" t="n">
-        <v>78526</v>
+        <v>78542</v>
       </c>
       <c r="C76" t="inlineStr">
         <is>
@@ -8272,10 +8273,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>478232</v>
+        <v>478055</v>
       </c>
       <c r="R76" t="n">
-        <v>6827659</v>
+        <v>6827768</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -8334,10 +8335,10 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>120075077</v>
+        <v>120075047</v>
       </c>
       <c r="B77" t="n">
-        <v>78526</v>
+        <v>78278</v>
       </c>
       <c r="C77" t="inlineStr">
         <is>
@@ -8350,21 +8351,21 @@
         </is>
       </c>
       <c r="E77" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
@@ -8374,10 +8375,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>478124</v>
+        <v>478212</v>
       </c>
       <c r="R77" t="n">
-        <v>6827560</v>
+        <v>6827573</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -8436,10 +8437,10 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>120075175</v>
+        <v>120075197</v>
       </c>
       <c r="B78" t="n">
-        <v>78526</v>
+        <v>91858</v>
       </c>
       <c r="C78" t="inlineStr">
         <is>
@@ -8448,38 +8449,47 @@
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E78" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I78" t="inlineStr"/>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I78" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J78" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="P78" t="inlineStr">
         <is>
           <t>Hevoslamm, Dlr</t>
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>478059</v>
+        <v>478077</v>
       </c>
       <c r="R78" t="n">
-        <v>6827739</v>
+        <v>6827805</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -8538,10 +8548,10 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>120075236</v>
+        <v>120075135</v>
       </c>
       <c r="B79" t="n">
-        <v>78171</v>
+        <v>78542</v>
       </c>
       <c r="C79" t="inlineStr">
         <is>
@@ -8554,21 +8564,21 @@
         </is>
       </c>
       <c r="E79" t="n">
-        <v>353</v>
+        <v>6425</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
@@ -8578,10 +8588,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>478062</v>
+        <v>478291</v>
       </c>
       <c r="R79" t="n">
-        <v>6827740</v>
+        <v>6827744</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -8640,10 +8650,10 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>120074930</v>
+        <v>120075177</v>
       </c>
       <c r="B80" t="n">
-        <v>79144</v>
+        <v>78542</v>
       </c>
       <c r="C80" t="inlineStr">
         <is>
@@ -8656,21 +8666,21 @@
         </is>
       </c>
       <c r="E80" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
@@ -8680,10 +8690,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>478299</v>
+        <v>478075</v>
       </c>
       <c r="R80" t="n">
-        <v>6827805</v>
+        <v>6827717</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -8742,10 +8752,10 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>120074944</v>
+        <v>120075131</v>
       </c>
       <c r="B81" t="n">
-        <v>79144</v>
+        <v>78542</v>
       </c>
       <c r="C81" t="inlineStr">
         <is>
@@ -8758,21 +8768,21 @@
         </is>
       </c>
       <c r="E81" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
@@ -8782,10 +8792,10 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>478056</v>
+        <v>478258</v>
       </c>
       <c r="R81" t="n">
-        <v>6827785</v>
+        <v>6827731</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -8844,10 +8854,10 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>120074904</v>
+        <v>120075097</v>
       </c>
       <c r="B82" t="n">
-        <v>79144</v>
+        <v>78542</v>
       </c>
       <c r="C82" t="inlineStr">
         <is>
@@ -8860,21 +8870,21 @@
         </is>
       </c>
       <c r="E82" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
@@ -8884,10 +8894,10 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>478262</v>
+        <v>478248</v>
       </c>
       <c r="R82" t="n">
-        <v>6827730</v>
+        <v>6827593</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -8946,10 +8956,10 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>120074889</v>
+        <v>120075068</v>
       </c>
       <c r="B83" t="n">
-        <v>79144</v>
+        <v>78542</v>
       </c>
       <c r="C83" t="inlineStr">
         <is>
@@ -8962,21 +8972,21 @@
         </is>
       </c>
       <c r="E83" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
@@ -8986,10 +8996,10 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>478163</v>
+        <v>478174</v>
       </c>
       <c r="R83" t="n">
-        <v>6827536</v>
+        <v>6827656</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -9048,10 +9058,10 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>120074946</v>
+        <v>120075066</v>
       </c>
       <c r="B84" t="n">
-        <v>79144</v>
+        <v>78542</v>
       </c>
       <c r="C84" t="inlineStr">
         <is>
@@ -9064,21 +9074,21 @@
         </is>
       </c>
       <c r="E84" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
@@ -9088,10 +9098,10 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>478056</v>
+        <v>478160</v>
       </c>
       <c r="R84" t="n">
-        <v>6827754</v>
+        <v>6827680</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -9150,10 +9160,10 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>120075232</v>
+        <v>120075000</v>
       </c>
       <c r="B85" t="n">
-        <v>78171</v>
+        <v>78279</v>
       </c>
       <c r="C85" t="inlineStr">
         <is>
@@ -9166,21 +9176,21 @@
         </is>
       </c>
       <c r="E85" t="n">
-        <v>353</v>
+        <v>228912</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
@@ -9190,10 +9200,10 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>478051</v>
+        <v>478121</v>
       </c>
       <c r="R85" t="n">
-        <v>6827739</v>
+        <v>6827607</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -9252,10 +9262,10 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>120075226</v>
+        <v>120074917</v>
       </c>
       <c r="B86" t="n">
-        <v>78171</v>
+        <v>78576</v>
       </c>
       <c r="C86" t="inlineStr">
         <is>
@@ -9268,21 +9278,21 @@
         </is>
       </c>
       <c r="E86" t="n">
-        <v>353</v>
+        <v>185</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I86" t="inlineStr"/>
@@ -9292,10 +9302,10 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>478098</v>
+        <v>478095</v>
       </c>
       <c r="R86" t="n">
-        <v>6827815</v>
+        <v>6827533</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>
@@ -9354,10 +9364,10 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>120074917</v>
+        <v>120075224</v>
       </c>
       <c r="B87" t="n">
-        <v>78560</v>
+        <v>78187</v>
       </c>
       <c r="C87" t="inlineStr">
         <is>
@@ -9370,21 +9380,21 @@
         </is>
       </c>
       <c r="E87" t="n">
-        <v>185</v>
+        <v>353</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I87" t="inlineStr"/>
@@ -9394,10 +9404,10 @@
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>478095</v>
+        <v>478081</v>
       </c>
       <c r="R87" t="n">
-        <v>6827533</v>
+        <v>6827789</v>
       </c>
       <c r="S87" t="n">
         <v>10</v>
@@ -9456,10 +9466,10 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>120074928</v>
+        <v>120075201</v>
       </c>
       <c r="B88" t="n">
-        <v>78560</v>
+        <v>78187</v>
       </c>
       <c r="C88" t="inlineStr">
         <is>
@@ -9472,21 +9482,21 @@
         </is>
       </c>
       <c r="E88" t="n">
-        <v>185</v>
+        <v>353</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I88" t="inlineStr"/>
@@ -9496,10 +9506,10 @@
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>478059</v>
+        <v>478182</v>
       </c>
       <c r="R88" t="n">
-        <v>6827740</v>
+        <v>6827728</v>
       </c>
       <c r="S88" t="n">
         <v>10</v>
@@ -9558,10 +9568,10 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>120075162</v>
+        <v>120075081</v>
       </c>
       <c r="B89" t="n">
-        <v>78526</v>
+        <v>78542</v>
       </c>
       <c r="C89" t="inlineStr">
         <is>
@@ -9598,10 +9608,10 @@
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>478080</v>
+        <v>478096</v>
       </c>
       <c r="R89" t="n">
-        <v>6827808</v>
+        <v>6827550</v>
       </c>
       <c r="S89" t="n">
         <v>10</v>
@@ -9660,10 +9670,10 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>120075159</v>
+        <v>120075046</v>
       </c>
       <c r="B90" t="n">
-        <v>78526</v>
+        <v>78278</v>
       </c>
       <c r="C90" t="inlineStr">
         <is>
@@ -9676,21 +9686,21 @@
         </is>
       </c>
       <c r="E90" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I90" t="inlineStr"/>
@@ -9700,10 +9710,10 @@
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>478100</v>
+        <v>478285</v>
       </c>
       <c r="R90" t="n">
-        <v>6827729</v>
+        <v>6827770</v>
       </c>
       <c r="S90" t="n">
         <v>10</v>
@@ -9762,10 +9772,10 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>120075163</v>
+        <v>120075095</v>
       </c>
       <c r="B91" t="n">
-        <v>78526</v>
+        <v>78542</v>
       </c>
       <c r="C91" t="inlineStr">
         <is>
@@ -9802,10 +9812,10 @@
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>478102</v>
+        <v>478219</v>
       </c>
       <c r="R91" t="n">
-        <v>6827800</v>
+        <v>6827572</v>
       </c>
       <c r="S91" t="n">
         <v>10</v>
@@ -9864,10 +9874,10 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>120075071</v>
+        <v>120075035</v>
       </c>
       <c r="B92" t="n">
-        <v>78526</v>
+        <v>78278</v>
       </c>
       <c r="C92" t="inlineStr">
         <is>
@@ -9880,21 +9890,21 @@
         </is>
       </c>
       <c r="E92" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I92" t="inlineStr"/>
@@ -9904,10 +9914,10 @@
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>478116</v>
+        <v>478273</v>
       </c>
       <c r="R92" t="n">
-        <v>6827633</v>
+        <v>6827711</v>
       </c>
       <c r="S92" t="n">
         <v>10</v>
@@ -9966,10 +9976,10 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>120075167</v>
+        <v>120074892</v>
       </c>
       <c r="B93" t="n">
-        <v>78526</v>
+        <v>79160</v>
       </c>
       <c r="C93" t="inlineStr">
         <is>
@@ -9982,21 +9992,21 @@
         </is>
       </c>
       <c r="E93" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I93" t="inlineStr"/>
@@ -10006,10 +10016,10 @@
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>478105</v>
+        <v>478243</v>
       </c>
       <c r="R93" t="n">
-        <v>6827851</v>
+        <v>6827585</v>
       </c>
       <c r="S93" t="n">
         <v>10</v>
@@ -10068,10 +10078,10 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>120075160</v>
+        <v>120075045</v>
       </c>
       <c r="B94" t="n">
-        <v>78526</v>
+        <v>78278</v>
       </c>
       <c r="C94" t="inlineStr">
         <is>
@@ -10084,21 +10094,21 @@
         </is>
       </c>
       <c r="E94" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I94" t="inlineStr"/>
@@ -10108,10 +10118,10 @@
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>478097</v>
+        <v>478070</v>
       </c>
       <c r="R94" t="n">
-        <v>6827744</v>
+        <v>6827723</v>
       </c>
       <c r="S94" t="n">
         <v>10</v>
@@ -10170,10 +10180,10 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>120075073</v>
+        <v>120075087</v>
       </c>
       <c r="B95" t="n">
-        <v>78526</v>
+        <v>78542</v>
       </c>
       <c r="C95" t="inlineStr">
         <is>
@@ -10210,10 +10220,10 @@
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>478116</v>
+        <v>478145</v>
       </c>
       <c r="R95" t="n">
-        <v>6827617</v>
+        <v>6827485</v>
       </c>
       <c r="S95" t="n">
         <v>10</v>
@@ -10272,10 +10282,10 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>120074934</v>
+        <v>120075028</v>
       </c>
       <c r="B96" t="n">
-        <v>79144</v>
+        <v>78278</v>
       </c>
       <c r="C96" t="inlineStr">
         <is>
@@ -10288,21 +10298,21 @@
         </is>
       </c>
       <c r="E96" t="n">
-        <v>6453</v>
+        <v>6446</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I96" t="inlineStr"/>
@@ -10312,10 +10322,10 @@
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>478169</v>
+        <v>478137</v>
       </c>
       <c r="R96" t="n">
-        <v>6827760</v>
+        <v>6827553</v>
       </c>
       <c r="S96" t="n">
         <v>10</v>
@@ -10374,10 +10384,10 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>120075028</v>
+        <v>120075138</v>
       </c>
       <c r="B97" t="n">
-        <v>78262</v>
+        <v>78542</v>
       </c>
       <c r="C97" t="inlineStr">
         <is>
@@ -10390,21 +10400,21 @@
         </is>
       </c>
       <c r="E97" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I97" t="inlineStr"/>
@@ -10414,10 +10424,10 @@
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>478137</v>
+        <v>478294</v>
       </c>
       <c r="R97" t="n">
-        <v>6827553</v>
+        <v>6827781</v>
       </c>
       <c r="S97" t="n">
         <v>10</v>
@@ -10476,10 +10486,10 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>120074956</v>
+        <v>120075129</v>
       </c>
       <c r="B98" t="n">
-        <v>57310</v>
+        <v>78542</v>
       </c>
       <c r="C98" t="inlineStr">
         <is>
@@ -10492,39 +10502,34 @@
         </is>
       </c>
       <c r="E98" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I98" t="inlineStr"/>
-      <c r="M98" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P98" t="inlineStr">
         <is>
           <t>Hevoslamm, Dlr</t>
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>478278</v>
+        <v>478265</v>
       </c>
       <c r="R98" t="n">
-        <v>6827832</v>
+        <v>6827707</v>
       </c>
       <c r="S98" t="n">
         <v>10</v>
@@ -10557,11 +10562,6 @@
       <c r="AA98" t="inlineStr">
         <is>
           <t>2024-09-27</t>
-        </is>
-      </c>
-      <c r="AC98" t="inlineStr">
-        <is>
-          <t>Färska ringhack (tall)</t>
         </is>
       </c>
       <c r="AD98" t="b">
@@ -10588,10 +10588,10 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>120075025</v>
+        <v>120074942</v>
       </c>
       <c r="B99" t="n">
-        <v>78262</v>
+        <v>79160</v>
       </c>
       <c r="C99" t="inlineStr">
         <is>
@@ -10604,21 +10604,21 @@
         </is>
       </c>
       <c r="E99" t="n">
-        <v>6446</v>
+        <v>6453</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I99" t="inlineStr"/>
@@ -10628,10 +10628,10 @@
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>478171</v>
+        <v>478065</v>
       </c>
       <c r="R99" t="n">
-        <v>6827642</v>
+        <v>6827842</v>
       </c>
       <c r="S99" t="n">
         <v>10</v>
@@ -10690,10 +10690,10 @@
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>120075024</v>
+        <v>120074922</v>
       </c>
       <c r="B100" t="n">
-        <v>78262</v>
+        <v>78576</v>
       </c>
       <c r="C100" t="inlineStr">
         <is>
@@ -10706,21 +10706,21 @@
         </is>
       </c>
       <c r="E100" t="n">
-        <v>6446</v>
+        <v>185</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I100" t="inlineStr"/>
@@ -10730,10 +10730,10 @@
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>478165</v>
+        <v>478103</v>
       </c>
       <c r="R100" t="n">
-        <v>6827712</v>
+        <v>6827718</v>
       </c>
       <c r="S100" t="n">
         <v>10</v>
@@ -10792,10 +10792,10 @@
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>120074882</v>
+        <v>120075208</v>
       </c>
       <c r="B101" t="n">
-        <v>79144</v>
+        <v>78187</v>
       </c>
       <c r="C101" t="inlineStr">
         <is>
@@ -10808,21 +10808,21 @@
         </is>
       </c>
       <c r="E101" t="n">
-        <v>6453</v>
+        <v>353</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I101" t="inlineStr"/>
@@ -10832,10 +10832,10 @@
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>478162</v>
+        <v>478158</v>
       </c>
       <c r="R101" t="n">
-        <v>6827593</v>
+        <v>6827519</v>
       </c>
       <c r="S101" t="n">
         <v>10</v>
@@ -10894,10 +10894,10 @@
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>120075216</v>
+        <v>120074947</v>
       </c>
       <c r="B102" t="n">
-        <v>78171</v>
+        <v>79160</v>
       </c>
       <c r="C102" t="inlineStr">
         <is>
@@ -10910,21 +10910,21 @@
         </is>
       </c>
       <c r="E102" t="n">
-        <v>353</v>
+        <v>6453</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I102" t="inlineStr"/>
@@ -10934,10 +10934,10 @@
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>478294</v>
+        <v>478061</v>
       </c>
       <c r="R102" t="n">
-        <v>6827790</v>
+        <v>6827751</v>
       </c>
       <c r="S102" t="n">
         <v>10</v>
@@ -10996,10 +10996,10 @@
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>120075215</v>
+        <v>120075094</v>
       </c>
       <c r="B103" t="n">
-        <v>78171</v>
+        <v>78542</v>
       </c>
       <c r="C103" t="inlineStr">
         <is>
@@ -11012,21 +11012,21 @@
         </is>
       </c>
       <c r="E103" t="n">
-        <v>353</v>
+        <v>6425</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I103" t="inlineStr"/>
@@ -11036,10 +11036,10 @@
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>478239</v>
+        <v>478205</v>
       </c>
       <c r="R103" t="n">
-        <v>6827752</v>
+        <v>6827556</v>
       </c>
       <c r="S103" t="n">
         <v>10</v>
@@ -11098,10 +11098,10 @@
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>120074929</v>
+        <v>120075088</v>
       </c>
       <c r="B104" t="n">
-        <v>78560</v>
+        <v>78542</v>
       </c>
       <c r="C104" t="inlineStr">
         <is>
@@ -11114,21 +11114,21 @@
         </is>
       </c>
       <c r="E104" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I104" t="inlineStr"/>
@@ -11138,10 +11138,10 @@
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>478045</v>
+        <v>478151</v>
       </c>
       <c r="R104" t="n">
-        <v>6827724</v>
+        <v>6827509</v>
       </c>
       <c r="S104" t="n">
         <v>10</v>
@@ -11200,10 +11200,10 @@
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>120075224</v>
+        <v>120075027</v>
       </c>
       <c r="B105" t="n">
-        <v>78171</v>
+        <v>78278</v>
       </c>
       <c r="C105" t="inlineStr">
         <is>
@@ -11216,21 +11216,21 @@
         </is>
       </c>
       <c r="E105" t="n">
-        <v>353</v>
+        <v>6446</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I105" t="inlineStr"/>
@@ -11240,10 +11240,10 @@
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>478081</v>
+        <v>478144</v>
       </c>
       <c r="R105" t="n">
-        <v>6827789</v>
+        <v>6827593</v>
       </c>
       <c r="S105" t="n">
         <v>10</v>
@@ -11302,10 +11302,10 @@
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>120075234</v>
+        <v>120075161</v>
       </c>
       <c r="B106" t="n">
-        <v>78171</v>
+        <v>78542</v>
       </c>
       <c r="C106" t="inlineStr">
         <is>
@@ -11318,21 +11318,21 @@
         </is>
       </c>
       <c r="E106" t="n">
-        <v>353</v>
+        <v>6425</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I106" t="inlineStr"/>
@@ -11342,10 +11342,10 @@
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>478069</v>
+        <v>478082</v>
       </c>
       <c r="R106" t="n">
-        <v>6827741</v>
+        <v>6827766</v>
       </c>
       <c r="S106" t="n">
         <v>10</v>
@@ -11404,10 +11404,10 @@
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>120075088</v>
+        <v>120074932</v>
       </c>
       <c r="B107" t="n">
-        <v>78526</v>
+        <v>79160</v>
       </c>
       <c r="C107" t="inlineStr">
         <is>
@@ -11420,21 +11420,21 @@
         </is>
       </c>
       <c r="E107" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I107" t="inlineStr"/>
@@ -11444,10 +11444,10 @@
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>478151</v>
+        <v>478250</v>
       </c>
       <c r="R107" t="n">
-        <v>6827509</v>
+        <v>6827802</v>
       </c>
       <c r="S107" t="n">
         <v>10</v>
@@ -11506,10 +11506,10 @@
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>120075140</v>
+        <v>120075236</v>
       </c>
       <c r="B108" t="n">
-        <v>78526</v>
+        <v>78187</v>
       </c>
       <c r="C108" t="inlineStr">
         <is>
@@ -11522,21 +11522,21 @@
         </is>
       </c>
       <c r="E108" t="n">
-        <v>6425</v>
+        <v>353</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I108" t="inlineStr"/>
@@ -11546,10 +11546,10 @@
         </is>
       </c>
       <c r="Q108" t="n">
-        <v>478310</v>
+        <v>478062</v>
       </c>
       <c r="R108" t="n">
-        <v>6827797</v>
+        <v>6827740</v>
       </c>
       <c r="S108" t="n">
         <v>10</v>
@@ -11608,10 +11608,10 @@
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>120075128</v>
+        <v>120074912</v>
       </c>
       <c r="B109" t="n">
-        <v>78526</v>
+        <v>78576</v>
       </c>
       <c r="C109" t="inlineStr">
         <is>
@@ -11624,21 +11624,21 @@
         </is>
       </c>
       <c r="E109" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I109" t="inlineStr"/>
@@ -11648,10 +11648,10 @@
         </is>
       </c>
       <c r="Q109" t="n">
-        <v>478275</v>
+        <v>478149</v>
       </c>
       <c r="R109" t="n">
-        <v>6827710</v>
+        <v>6827714</v>
       </c>
       <c r="S109" t="n">
         <v>10</v>
@@ -11710,10 +11710,10 @@
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>120075171</v>
+        <v>120075042</v>
       </c>
       <c r="B110" t="n">
-        <v>78526</v>
+        <v>78278</v>
       </c>
       <c r="C110" t="inlineStr">
         <is>
@@ -11726,21 +11726,21 @@
         </is>
       </c>
       <c r="E110" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I110" t="inlineStr"/>
@@ -11750,10 +11750,10 @@
         </is>
       </c>
       <c r="Q110" t="n">
-        <v>478073</v>
+        <v>478074</v>
       </c>
       <c r="R110" t="n">
-        <v>6827831</v>
+        <v>6827775</v>
       </c>
       <c r="S110" t="n">
         <v>10</v>
@@ -11812,10 +11812,10 @@
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>120074952</v>
+        <v>120075136</v>
       </c>
       <c r="B111" t="n">
-        <v>79115</v>
+        <v>78542</v>
       </c>
       <c r="C111" t="inlineStr">
         <is>
@@ -11828,21 +11828,21 @@
         </is>
       </c>
       <c r="E111" t="n">
-        <v>229821</v>
+        <v>6425</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I111" t="inlineStr"/>
@@ -11852,10 +11852,10 @@
         </is>
       </c>
       <c r="Q111" t="n">
-        <v>478120</v>
+        <v>478290</v>
       </c>
       <c r="R111" t="n">
-        <v>6827605</v>
+        <v>6827758</v>
       </c>
       <c r="S111" t="n">
         <v>10</v>
@@ -11914,10 +11914,10 @@
     </row>
     <row r="112">
       <c r="A112" t="n">
-        <v>120075176</v>
+        <v>120074885</v>
       </c>
       <c r="B112" t="n">
-        <v>78526</v>
+        <v>79160</v>
       </c>
       <c r="C112" t="inlineStr">
         <is>
@@ -11930,21 +11930,21 @@
         </is>
       </c>
       <c r="E112" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I112" t="inlineStr"/>
@@ -11954,10 +11954,10 @@
         </is>
       </c>
       <c r="Q112" t="n">
-        <v>478066</v>
+        <v>478115</v>
       </c>
       <c r="R112" t="n">
-        <v>6827732</v>
+        <v>6827614</v>
       </c>
       <c r="S112" t="n">
         <v>10</v>
@@ -12016,10 +12016,10 @@
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>120075136</v>
+        <v>120074934</v>
       </c>
       <c r="B113" t="n">
-        <v>78526</v>
+        <v>79160</v>
       </c>
       <c r="C113" t="inlineStr">
         <is>
@@ -12032,21 +12032,21 @@
         </is>
       </c>
       <c r="E113" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I113" t="inlineStr"/>
@@ -12056,10 +12056,10 @@
         </is>
       </c>
       <c r="Q113" t="n">
-        <v>478290</v>
+        <v>478169</v>
       </c>
       <c r="R113" t="n">
-        <v>6827758</v>
+        <v>6827760</v>
       </c>
       <c r="S113" t="n">
         <v>10</v>
@@ -12118,10 +12118,10 @@
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>120075137</v>
+        <v>120074944</v>
       </c>
       <c r="B114" t="n">
-        <v>78526</v>
+        <v>79160</v>
       </c>
       <c r="C114" t="inlineStr">
         <is>
@@ -12134,21 +12134,21 @@
         </is>
       </c>
       <c r="E114" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I114" t="inlineStr"/>
@@ -12158,10 +12158,10 @@
         </is>
       </c>
       <c r="Q114" t="n">
-        <v>478288</v>
+        <v>478056</v>
       </c>
       <c r="R114" t="n">
-        <v>6827763</v>
+        <v>6827785</v>
       </c>
       <c r="S114" t="n">
         <v>10</v>
@@ -12220,10 +12220,10 @@
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>120075075</v>
+        <v>120075029</v>
       </c>
       <c r="B115" t="n">
-        <v>78526</v>
+        <v>78278</v>
       </c>
       <c r="C115" t="inlineStr">
         <is>
@@ -12236,21 +12236,21 @@
         </is>
       </c>
       <c r="E115" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I115" t="inlineStr"/>
@@ -12260,10 +12260,10 @@
         </is>
       </c>
       <c r="Q115" t="n">
-        <v>478139</v>
+        <v>478115</v>
       </c>
       <c r="R115" t="n">
-        <v>6827554</v>
+        <v>6827564</v>
       </c>
       <c r="S115" t="n">
         <v>10</v>
@@ -12322,10 +12322,10 @@
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>120075129</v>
+        <v>120075144</v>
       </c>
       <c r="B116" t="n">
-        <v>78526</v>
+        <v>78542</v>
       </c>
       <c r="C116" t="inlineStr">
         <is>
@@ -12362,10 +12362,10 @@
         </is>
       </c>
       <c r="Q116" t="n">
-        <v>478265</v>
+        <v>478261</v>
       </c>
       <c r="R116" t="n">
-        <v>6827707</v>
+        <v>6827822</v>
       </c>
       <c r="S116" t="n">
         <v>10</v>
@@ -12424,10 +12424,10 @@
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>120075042</v>
+        <v>120075239</v>
       </c>
       <c r="B117" t="n">
-        <v>78262</v>
+        <v>77474</v>
       </c>
       <c r="C117" t="inlineStr">
         <is>
@@ -12440,21 +12440,21 @@
         </is>
       </c>
       <c r="E117" t="n">
-        <v>6446</v>
+        <v>6487</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Blågrå svartspik</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Chaenothecopsis fennica</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Laurila) Tibell</t>
         </is>
       </c>
       <c r="I117" t="inlineStr"/>
@@ -12464,10 +12464,10 @@
         </is>
       </c>
       <c r="Q117" t="n">
-        <v>478074</v>
+        <v>478137</v>
       </c>
       <c r="R117" t="n">
-        <v>6827775</v>
+        <v>6827554</v>
       </c>
       <c r="S117" t="n">
         <v>10</v>
@@ -12526,10 +12526,10 @@
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>120074931</v>
+        <v>120075203</v>
       </c>
       <c r="B118" t="n">
-        <v>79144</v>
+        <v>78187</v>
       </c>
       <c r="C118" t="inlineStr">
         <is>
@@ -12542,21 +12542,21 @@
         </is>
       </c>
       <c r="E118" t="n">
-        <v>6453</v>
+        <v>353</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I118" t="inlineStr"/>
@@ -12566,10 +12566,10 @@
         </is>
       </c>
       <c r="Q118" t="n">
-        <v>478261</v>
+        <v>478125</v>
       </c>
       <c r="R118" t="n">
-        <v>6827822</v>
+        <v>6827631</v>
       </c>
       <c r="S118" t="n">
         <v>10</v>
@@ -12628,10 +12628,10 @@
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>120075201</v>
+        <v>120075176</v>
       </c>
       <c r="B119" t="n">
-        <v>78171</v>
+        <v>78542</v>
       </c>
       <c r="C119" t="inlineStr">
         <is>
@@ -12644,21 +12644,21 @@
         </is>
       </c>
       <c r="E119" t="n">
-        <v>353</v>
+        <v>6425</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I119" t="inlineStr"/>
@@ -12668,10 +12668,10 @@
         </is>
       </c>
       <c r="Q119" t="n">
-        <v>478182</v>
+        <v>478066</v>
       </c>
       <c r="R119" t="n">
-        <v>6827728</v>
+        <v>6827732</v>
       </c>
       <c r="S119" t="n">
         <v>10</v>
@@ -12730,10 +12730,10 @@
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>120075230</v>
+        <v>120075061</v>
       </c>
       <c r="B120" t="n">
-        <v>78171</v>
+        <v>78542</v>
       </c>
       <c r="C120" t="inlineStr">
         <is>
@@ -12746,21 +12746,21 @@
         </is>
       </c>
       <c r="E120" t="n">
-        <v>353</v>
+        <v>6425</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I120" t="inlineStr"/>
@@ -12770,10 +12770,10 @@
         </is>
       </c>
       <c r="Q120" t="n">
-        <v>478064</v>
+        <v>478160</v>
       </c>
       <c r="R120" t="n">
-        <v>6827866</v>
+        <v>6827710</v>
       </c>
       <c r="S120" t="n">
         <v>10</v>
@@ -12832,10 +12832,10 @@
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>120074997</v>
+        <v>120075064</v>
       </c>
       <c r="B121" t="n">
-        <v>78263</v>
+        <v>78542</v>
       </c>
       <c r="C121" t="inlineStr">
         <is>
@@ -12848,21 +12848,21 @@
         </is>
       </c>
       <c r="E121" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I121" t="inlineStr"/>
@@ -12872,10 +12872,10 @@
         </is>
       </c>
       <c r="Q121" t="n">
-        <v>478218</v>
+        <v>478192</v>
       </c>
       <c r="R121" t="n">
-        <v>6827733</v>
+        <v>6827690</v>
       </c>
       <c r="S121" t="n">
         <v>10</v>
@@ -12934,10 +12934,10 @@
     </row>
     <row r="122">
       <c r="A122" t="n">
-        <v>120075004</v>
+        <v>120074889</v>
       </c>
       <c r="B122" t="n">
-        <v>78263</v>
+        <v>79160</v>
       </c>
       <c r="C122" t="inlineStr">
         <is>
@@ -12950,21 +12950,21 @@
         </is>
       </c>
       <c r="E122" t="n">
-        <v>228912</v>
+        <v>6453</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I122" t="inlineStr"/>
@@ -12974,10 +12974,10 @@
         </is>
       </c>
       <c r="Q122" t="n">
-        <v>478212</v>
+        <v>478163</v>
       </c>
       <c r="R122" t="n">
-        <v>6827573</v>
+        <v>6827536</v>
       </c>
       <c r="S122" t="n">
         <v>10</v>
@@ -13036,10 +13036,10 @@
     </row>
     <row r="123">
       <c r="A123" t="n">
-        <v>120075008</v>
+        <v>120074935</v>
       </c>
       <c r="B123" t="n">
-        <v>78263</v>
+        <v>79160</v>
       </c>
       <c r="C123" t="inlineStr">
         <is>
@@ -13052,21 +13052,21 @@
         </is>
       </c>
       <c r="E123" t="n">
-        <v>228912</v>
+        <v>6453</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I123" t="inlineStr"/>
@@ -13076,10 +13076,10 @@
         </is>
       </c>
       <c r="Q123" t="n">
-        <v>478299</v>
+        <v>478150</v>
       </c>
       <c r="R123" t="n">
-        <v>6827805</v>
+        <v>6827745</v>
       </c>
       <c r="S123" t="n">
         <v>10</v>
@@ -13138,10 +13138,10 @@
     </row>
     <row r="124">
       <c r="A124" t="n">
-        <v>120075192</v>
+        <v>120074945</v>
       </c>
       <c r="B124" t="n">
-        <v>78526</v>
+        <v>79160</v>
       </c>
       <c r="C124" t="inlineStr">
         <is>
@@ -13154,21 +13154,21 @@
         </is>
       </c>
       <c r="E124" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I124" t="inlineStr"/>
@@ -13178,10 +13178,10 @@
         </is>
       </c>
       <c r="Q124" t="n">
-        <v>478282</v>
+        <v>478061</v>
       </c>
       <c r="R124" t="n">
-        <v>6827683</v>
+        <v>6827770</v>
       </c>
       <c r="S124" t="n">
         <v>10</v>
@@ -13240,10 +13240,10 @@
     </row>
     <row r="125">
       <c r="A125" t="n">
-        <v>120075135</v>
+        <v>120075063</v>
       </c>
       <c r="B125" t="n">
-        <v>78526</v>
+        <v>78542</v>
       </c>
       <c r="C125" t="inlineStr">
         <is>
@@ -13280,10 +13280,10 @@
         </is>
       </c>
       <c r="Q125" t="n">
-        <v>478291</v>
+        <v>478201</v>
       </c>
       <c r="R125" t="n">
-        <v>6827744</v>
+        <v>6827693</v>
       </c>
       <c r="S125" t="n">
         <v>10</v>
@@ -13342,10 +13342,10 @@
     </row>
     <row r="126">
       <c r="A126" t="n">
-        <v>120075085</v>
+        <v>120075009</v>
       </c>
       <c r="B126" t="n">
-        <v>78526</v>
+        <v>78279</v>
       </c>
       <c r="C126" t="inlineStr">
         <is>
@@ -13358,21 +13358,21 @@
         </is>
       </c>
       <c r="E126" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H126" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I126" t="inlineStr"/>
@@ -13382,10 +13382,10 @@
         </is>
       </c>
       <c r="Q126" t="n">
-        <v>478094</v>
+        <v>478151</v>
       </c>
       <c r="R126" t="n">
-        <v>6827504</v>
+        <v>6827745</v>
       </c>
       <c r="S126" t="n">
         <v>10</v>
@@ -13444,10 +13444,10 @@
     </row>
     <row r="127">
       <c r="A127" t="n">
-        <v>120075065</v>
+        <v>120075016</v>
       </c>
       <c r="B127" t="n">
-        <v>78526</v>
+        <v>79623</v>
       </c>
       <c r="C127" t="inlineStr">
         <is>
@@ -13460,21 +13460,21 @@
         </is>
       </c>
       <c r="E127" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H127" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I127" t="inlineStr"/>
@@ -13484,10 +13484,10 @@
         </is>
       </c>
       <c r="Q127" t="n">
-        <v>478169</v>
+        <v>478096</v>
       </c>
       <c r="R127" t="n">
-        <v>6827679</v>
+        <v>6827549</v>
       </c>
       <c r="S127" t="n">
         <v>10</v>
@@ -13546,10 +13546,10 @@
     </row>
     <row r="128">
       <c r="A128" t="n">
-        <v>120075164</v>
+        <v>120075019</v>
       </c>
       <c r="B128" t="n">
-        <v>78526</v>
+        <v>79623</v>
       </c>
       <c r="C128" t="inlineStr">
         <is>
@@ -13562,21 +13562,21 @@
         </is>
       </c>
       <c r="E128" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H128" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I128" t="inlineStr"/>
@@ -13586,10 +13586,10 @@
         </is>
       </c>
       <c r="Q128" t="n">
-        <v>478092</v>
+        <v>478227</v>
       </c>
       <c r="R128" t="n">
-        <v>6827810</v>
+        <v>6827655</v>
       </c>
       <c r="S128" t="n">
         <v>10</v>
@@ -13648,10 +13648,10 @@
     </row>
     <row r="129">
       <c r="A129" t="n">
-        <v>120075078</v>
+        <v>120075163</v>
       </c>
       <c r="B129" t="n">
-        <v>78526</v>
+        <v>78542</v>
       </c>
       <c r="C129" t="inlineStr">
         <is>
@@ -13688,10 +13688,10 @@
         </is>
       </c>
       <c r="Q129" t="n">
-        <v>478116</v>
+        <v>478102</v>
       </c>
       <c r="R129" t="n">
-        <v>6827567</v>
+        <v>6827800</v>
       </c>
       <c r="S129" t="n">
         <v>10</v>
@@ -13750,10 +13750,10 @@
     </row>
     <row r="130">
       <c r="A130" t="n">
-        <v>120075068</v>
+        <v>120074948</v>
       </c>
       <c r="B130" t="n">
-        <v>78526</v>
+        <v>79160</v>
       </c>
       <c r="C130" t="inlineStr">
         <is>
@@ -13766,21 +13766,21 @@
         </is>
       </c>
       <c r="E130" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H130" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I130" t="inlineStr"/>
@@ -13790,10 +13790,10 @@
         </is>
       </c>
       <c r="Q130" t="n">
-        <v>478174</v>
+        <v>478070</v>
       </c>
       <c r="R130" t="n">
-        <v>6827656</v>
+        <v>6827723</v>
       </c>
       <c r="S130" t="n">
         <v>10</v>
@@ -13852,10 +13852,10 @@
     </row>
     <row r="131">
       <c r="A131" t="n">
-        <v>120075035</v>
+        <v>120075121</v>
       </c>
       <c r="B131" t="n">
-        <v>78262</v>
+        <v>78542</v>
       </c>
       <c r="C131" t="inlineStr">
         <is>
@@ -13868,21 +13868,21 @@
         </is>
       </c>
       <c r="E131" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H131" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I131" t="inlineStr"/>
@@ -13892,10 +13892,10 @@
         </is>
       </c>
       <c r="Q131" t="n">
-        <v>478273</v>
+        <v>478232</v>
       </c>
       <c r="R131" t="n">
-        <v>6827711</v>
+        <v>6827659</v>
       </c>
       <c r="S131" t="n">
         <v>10</v>
@@ -13954,10 +13954,10 @@
     </row>
     <row r="132">
       <c r="A132" t="n">
-        <v>120074941</v>
+        <v>120074946</v>
       </c>
       <c r="B132" t="n">
-        <v>79144</v>
+        <v>79160</v>
       </c>
       <c r="C132" t="inlineStr">
         <is>
@@ -13994,10 +13994,10 @@
         </is>
       </c>
       <c r="Q132" t="n">
-        <v>478069</v>
+        <v>478056</v>
       </c>
       <c r="R132" t="n">
-        <v>6827854</v>
+        <v>6827754</v>
       </c>
       <c r="S132" t="n">
         <v>10</v>
@@ -14056,10 +14056,10 @@
     </row>
     <row r="133">
       <c r="A133" t="n">
-        <v>120075095</v>
+        <v>120074996</v>
       </c>
       <c r="B133" t="n">
-        <v>78526</v>
+        <v>78279</v>
       </c>
       <c r="C133" t="inlineStr">
         <is>
@@ -14072,21 +14072,21 @@
         </is>
       </c>
       <c r="E133" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H133" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I133" t="inlineStr"/>
@@ -14096,10 +14096,10 @@
         </is>
       </c>
       <c r="Q133" t="n">
-        <v>478219</v>
+        <v>478165</v>
       </c>
       <c r="R133" t="n">
-        <v>6827572</v>
+        <v>6827712</v>
       </c>
       <c r="S133" t="n">
         <v>10</v>
@@ -14158,10 +14158,10 @@
     </row>
     <row r="134">
       <c r="A134" t="n">
-        <v>120074927</v>
+        <v>120075004</v>
       </c>
       <c r="B134" t="n">
-        <v>78560</v>
+        <v>78279</v>
       </c>
       <c r="C134" t="inlineStr">
         <is>
@@ -14174,21 +14174,21 @@
         </is>
       </c>
       <c r="E134" t="n">
-        <v>185</v>
+        <v>228912</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H134" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I134" t="inlineStr"/>
@@ -14198,10 +14198,10 @@
         </is>
       </c>
       <c r="Q134" t="n">
-        <v>478073</v>
+        <v>478212</v>
       </c>
       <c r="R134" t="n">
-        <v>6827836</v>
+        <v>6827573</v>
       </c>
       <c r="S134" t="n">
         <v>10</v>
@@ -14260,10 +14260,10 @@
     </row>
     <row r="135">
       <c r="A135" t="n">
-        <v>120075225</v>
+        <v>120075011</v>
       </c>
       <c r="B135" t="n">
-        <v>78171</v>
+        <v>78279</v>
       </c>
       <c r="C135" t="inlineStr">
         <is>
@@ -14276,21 +14276,21 @@
         </is>
       </c>
       <c r="E135" t="n">
-        <v>353</v>
+        <v>228912</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H135" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I135" t="inlineStr"/>
@@ -14300,10 +14300,10 @@
         </is>
       </c>
       <c r="Q135" t="n">
-        <v>478075</v>
+        <v>478103</v>
       </c>
       <c r="R135" t="n">
-        <v>6827798</v>
+        <v>6827803</v>
       </c>
       <c r="S135" t="n">
         <v>10</v>
@@ -14362,10 +14362,10 @@
     </row>
     <row r="136">
       <c r="A136" t="n">
-        <v>120075223</v>
+        <v>120074888</v>
       </c>
       <c r="B136" t="n">
-        <v>78171</v>
+        <v>79160</v>
       </c>
       <c r="C136" t="inlineStr">
         <is>
@@ -14378,21 +14378,21 @@
         </is>
       </c>
       <c r="E136" t="n">
-        <v>353</v>
+        <v>6453</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H136" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I136" t="inlineStr"/>
@@ -14402,10 +14402,10 @@
         </is>
       </c>
       <c r="Q136" t="n">
-        <v>478076</v>
+        <v>478139</v>
       </c>
       <c r="R136" t="n">
-        <v>6827777</v>
+        <v>6827554</v>
       </c>
       <c r="S136" t="n">
         <v>10</v>
@@ -14464,10 +14464,10 @@
     </row>
     <row r="137">
       <c r="A137" t="n">
-        <v>120075142</v>
+        <v>120075132</v>
       </c>
       <c r="B137" t="n">
-        <v>78526</v>
+        <v>78542</v>
       </c>
       <c r="C137" t="inlineStr">
         <is>
@@ -14504,10 +14504,10 @@
         </is>
       </c>
       <c r="Q137" t="n">
-        <v>478313</v>
+        <v>478240</v>
       </c>
       <c r="R137" t="n">
-        <v>6827798</v>
+        <v>6827754</v>
       </c>
       <c r="S137" t="n">
         <v>10</v>
@@ -14566,10 +14566,10 @@
     </row>
     <row r="138">
       <c r="A138" t="n">
-        <v>120075083</v>
+        <v>120075038</v>
       </c>
       <c r="B138" t="n">
-        <v>78526</v>
+        <v>78278</v>
       </c>
       <c r="C138" t="inlineStr">
         <is>
@@ -14582,21 +14582,21 @@
         </is>
       </c>
       <c r="E138" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H138" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I138" t="inlineStr"/>
@@ -14606,10 +14606,10 @@
         </is>
       </c>
       <c r="Q138" t="n">
-        <v>478097</v>
+        <v>478261</v>
       </c>
       <c r="R138" t="n">
-        <v>6827527</v>
+        <v>6827731</v>
       </c>
       <c r="S138" t="n">
         <v>10</v>
@@ -14668,10 +14668,10 @@
     </row>
     <row r="139">
       <c r="A139" t="n">
-        <v>120075044</v>
+        <v>120074887</v>
       </c>
       <c r="B139" t="n">
-        <v>78262</v>
+        <v>79160</v>
       </c>
       <c r="C139" t="inlineStr">
         <is>
@@ -14684,21 +14684,21 @@
         </is>
       </c>
       <c r="E139" t="n">
-        <v>6446</v>
+        <v>6453</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H139" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I139" t="inlineStr"/>
@@ -14708,10 +14708,10 @@
         </is>
       </c>
       <c r="Q139" t="n">
-        <v>478060</v>
+        <v>478144</v>
       </c>
       <c r="R139" t="n">
-        <v>6827770</v>
+        <v>6827593</v>
       </c>
       <c r="S139" t="n">
         <v>10</v>
@@ -14770,10 +14770,10 @@
     </row>
     <row r="140">
       <c r="A140" t="n">
-        <v>120075202</v>
+        <v>120075164</v>
       </c>
       <c r="B140" t="n">
-        <v>78171</v>
+        <v>78542</v>
       </c>
       <c r="C140" t="inlineStr">
         <is>
@@ -14786,21 +14786,21 @@
         </is>
       </c>
       <c r="E140" t="n">
-        <v>353</v>
+        <v>6425</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H140" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I140" t="inlineStr"/>
@@ -14810,10 +14810,10 @@
         </is>
       </c>
       <c r="Q140" t="n">
-        <v>478218</v>
+        <v>478092</v>
       </c>
       <c r="R140" t="n">
-        <v>6827721</v>
+        <v>6827810</v>
       </c>
       <c r="S140" t="n">
         <v>10</v>
@@ -14872,10 +14872,10 @@
     </row>
     <row r="141">
       <c r="A141" t="n">
-        <v>120075139</v>
+        <v>120075140</v>
       </c>
       <c r="B141" t="n">
-        <v>78526</v>
+        <v>78542</v>
       </c>
       <c r="C141" t="inlineStr">
         <is>
@@ -14912,10 +14912,10 @@
         </is>
       </c>
       <c r="Q141" t="n">
-        <v>478294</v>
+        <v>478310</v>
       </c>
       <c r="R141" t="n">
-        <v>6827803</v>
+        <v>6827797</v>
       </c>
       <c r="S141" t="n">
         <v>10</v>
@@ -14974,10 +14974,10 @@
     </row>
     <row r="142">
       <c r="A142" t="n">
-        <v>120075089</v>
+        <v>120075048</v>
       </c>
       <c r="B142" t="n">
-        <v>78526</v>
+        <v>56524</v>
       </c>
       <c r="C142" t="inlineStr">
         <is>
@@ -14990,34 +14990,39 @@
         </is>
       </c>
       <c r="E142" t="n">
-        <v>6425</v>
+        <v>102612</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H142" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I142" t="inlineStr"/>
+      <c r="M142" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="P142" t="inlineStr">
         <is>
           <t>Hevoslamm, Dlr</t>
         </is>
       </c>
       <c r="Q142" t="n">
-        <v>478153</v>
+        <v>478070</v>
       </c>
       <c r="R142" t="n">
-        <v>6827517</v>
+        <v>6827723</v>
       </c>
       <c r="S142" t="n">
         <v>10</v>
@@ -15076,10 +15081,10 @@
     </row>
     <row r="143">
       <c r="A143" t="n">
-        <v>120075090</v>
+        <v>120075198</v>
       </c>
       <c r="B143" t="n">
-        <v>78526</v>
+        <v>91858</v>
       </c>
       <c r="C143" t="inlineStr">
         <is>
@@ -15088,25 +15093,25 @@
       </c>
       <c r="D143" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E143" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H143" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I143" t="inlineStr"/>
@@ -15116,10 +15121,10 @@
         </is>
       </c>
       <c r="Q143" t="n">
-        <v>478161</v>
+        <v>478163</v>
       </c>
       <c r="R143" t="n">
-        <v>6827528</v>
+        <v>6827530</v>
       </c>
       <c r="S143" t="n">
         <v>10</v>
@@ -15178,10 +15183,10 @@
     </row>
     <row r="144">
       <c r="A144" t="n">
-        <v>120075092</v>
+        <v>120075219</v>
       </c>
       <c r="B144" t="n">
-        <v>78526</v>
+        <v>78187</v>
       </c>
       <c r="C144" t="inlineStr">
         <is>
@@ -15194,21 +15199,21 @@
         </is>
       </c>
       <c r="E144" t="n">
-        <v>6425</v>
+        <v>353</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H144" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I144" t="inlineStr"/>
@@ -15218,10 +15223,10 @@
         </is>
       </c>
       <c r="Q144" t="n">
-        <v>478167</v>
+        <v>478169</v>
       </c>
       <c r="R144" t="n">
-        <v>6827561</v>
+        <v>6827760</v>
       </c>
       <c r="S144" t="n">
         <v>10</v>
@@ -15280,10 +15285,10 @@
     </row>
     <row r="145">
       <c r="A145" t="n">
-        <v>120075172</v>
+        <v>120074915</v>
       </c>
       <c r="B145" t="n">
-        <v>78526</v>
+        <v>78576</v>
       </c>
       <c r="C145" t="inlineStr">
         <is>
@@ -15296,21 +15301,21 @@
         </is>
       </c>
       <c r="E145" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H145" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I145" t="inlineStr"/>
@@ -15320,10 +15325,10 @@
         </is>
       </c>
       <c r="Q145" t="n">
-        <v>478055</v>
+        <v>478102</v>
       </c>
       <c r="R145" t="n">
-        <v>6827768</v>
+        <v>6827555</v>
       </c>
       <c r="S145" t="n">
         <v>10</v>
@@ -15382,10 +15387,10 @@
     </row>
     <row r="146">
       <c r="A146" t="n">
-        <v>120075086</v>
+        <v>120074998</v>
       </c>
       <c r="B146" t="n">
-        <v>78526</v>
+        <v>78279</v>
       </c>
       <c r="C146" t="inlineStr">
         <is>
@@ -15398,21 +15403,21 @@
         </is>
       </c>
       <c r="E146" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H146" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I146" t="inlineStr"/>
@@ -15422,10 +15427,10 @@
         </is>
       </c>
       <c r="Q146" t="n">
-        <v>478104</v>
+        <v>478172</v>
       </c>
       <c r="R146" t="n">
-        <v>6827495</v>
+        <v>6827640</v>
       </c>
       <c r="S146" t="n">
         <v>10</v>
@@ -15484,10 +15489,10 @@
     </row>
     <row r="147">
       <c r="A147" t="n">
-        <v>120074961</v>
+        <v>120074997</v>
       </c>
       <c r="B147" t="n">
-        <v>90582</v>
+        <v>78279</v>
       </c>
       <c r="C147" t="inlineStr">
         <is>
@@ -15500,21 +15505,21 @@
         </is>
       </c>
       <c r="E147" t="n">
-        <v>5442</v>
+        <v>228912</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G147" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H147" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I147" t="inlineStr"/>
@@ -15524,10 +15529,10 @@
         </is>
       </c>
       <c r="Q147" t="n">
-        <v>478230</v>
+        <v>478218</v>
       </c>
       <c r="R147" t="n">
-        <v>6827780</v>
+        <v>6827733</v>
       </c>
       <c r="S147" t="n">
         <v>10</v>
@@ -15586,10 +15591,10 @@
     </row>
     <row r="148">
       <c r="A148" t="n">
-        <v>120075007</v>
+        <v>120075010</v>
       </c>
       <c r="B148" t="n">
-        <v>78263</v>
+        <v>78279</v>
       </c>
       <c r="C148" t="inlineStr">
         <is>
@@ -15626,10 +15631,10 @@
         </is>
       </c>
       <c r="Q148" t="n">
-        <v>478285</v>
+        <v>478074</v>
       </c>
       <c r="R148" t="n">
-        <v>6827770</v>
+        <v>6827772</v>
       </c>
       <c r="S148" t="n">
         <v>10</v>
@@ -15688,10 +15693,10 @@
     </row>
     <row r="149">
       <c r="A149" t="n">
-        <v>120074888</v>
+        <v>120074928</v>
       </c>
       <c r="B149" t="n">
-        <v>79144</v>
+        <v>78576</v>
       </c>
       <c r="C149" t="inlineStr">
         <is>
@@ -15704,21 +15709,21 @@
         </is>
       </c>
       <c r="E149" t="n">
-        <v>6453</v>
+        <v>185</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G149" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H149" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I149" t="inlineStr"/>
@@ -15728,10 +15733,10 @@
         </is>
       </c>
       <c r="Q149" t="n">
-        <v>478139</v>
+        <v>478059</v>
       </c>
       <c r="R149" t="n">
-        <v>6827554</v>
+        <v>6827740</v>
       </c>
       <c r="S149" t="n">
         <v>10</v>
@@ -15790,10 +15795,10 @@
     </row>
     <row r="150">
       <c r="A150" t="n">
-        <v>120074948</v>
+        <v>120074925</v>
       </c>
       <c r="B150" t="n">
-        <v>79144</v>
+        <v>78576</v>
       </c>
       <c r="C150" t="inlineStr">
         <is>
@@ -15806,21 +15811,21 @@
         </is>
       </c>
       <c r="E150" t="n">
-        <v>6453</v>
+        <v>185</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G150" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H150" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I150" t="inlineStr"/>
@@ -15830,10 +15835,10 @@
         </is>
       </c>
       <c r="Q150" t="n">
-        <v>478070</v>
+        <v>478088</v>
       </c>
       <c r="R150" t="n">
-        <v>6827723</v>
+        <v>6827834</v>
       </c>
       <c r="S150" t="n">
         <v>10</v>
@@ -15892,10 +15897,10 @@
     </row>
     <row r="151">
       <c r="A151" t="n">
-        <v>120074892</v>
+        <v>120074961</v>
       </c>
       <c r="B151" t="n">
-        <v>79144</v>
+        <v>90600</v>
       </c>
       <c r="C151" t="inlineStr">
         <is>
@@ -15908,21 +15913,21 @@
         </is>
       </c>
       <c r="E151" t="n">
-        <v>6453</v>
+        <v>5442</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G151" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H151" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I151" t="inlineStr"/>
@@ -15932,10 +15937,10 @@
         </is>
       </c>
       <c r="Q151" t="n">
-        <v>478243</v>
+        <v>478230</v>
       </c>
       <c r="R151" t="n">
-        <v>6827585</v>
+        <v>6827780</v>
       </c>
       <c r="S151" t="n">
         <v>10</v>
@@ -15994,10 +15999,10 @@
     </row>
     <row r="152">
       <c r="A152" t="n">
-        <v>120074905</v>
+        <v>120075026</v>
       </c>
       <c r="B152" t="n">
-        <v>79144</v>
+        <v>78278</v>
       </c>
       <c r="C152" t="inlineStr">
         <is>
@@ -16010,21 +16015,21 @@
         </is>
       </c>
       <c r="E152" t="n">
-        <v>6453</v>
+        <v>6446</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G152" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H152" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I152" t="inlineStr"/>
@@ -16034,10 +16039,10 @@
         </is>
       </c>
       <c r="Q152" t="n">
-        <v>478285</v>
+        <v>478161</v>
       </c>
       <c r="R152" t="n">
-        <v>6827770</v>
+        <v>6827592</v>
       </c>
       <c r="S152" t="n">
         <v>10</v>
@@ -16096,10 +16101,10 @@
     </row>
     <row r="153">
       <c r="A153" t="n">
-        <v>120074886</v>
+        <v>120075075</v>
       </c>
       <c r="B153" t="n">
-        <v>79144</v>
+        <v>78542</v>
       </c>
       <c r="C153" t="inlineStr">
         <is>
@@ -16112,21 +16117,21 @@
         </is>
       </c>
       <c r="E153" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G153" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H153" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I153" t="inlineStr"/>
@@ -16136,10 +16141,10 @@
         </is>
       </c>
       <c r="Q153" t="n">
-        <v>478125</v>
+        <v>478139</v>
       </c>
       <c r="R153" t="n">
-        <v>6827604</v>
+        <v>6827554</v>
       </c>
       <c r="S153" t="n">
         <v>10</v>
@@ -16198,10 +16203,10 @@
     </row>
     <row r="154">
       <c r="A154" t="n">
-        <v>120074945</v>
+        <v>120075065</v>
       </c>
       <c r="B154" t="n">
-        <v>79144</v>
+        <v>78542</v>
       </c>
       <c r="C154" t="inlineStr">
         <is>
@@ -16214,21 +16219,21 @@
         </is>
       </c>
       <c r="E154" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G154" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H154" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I154" t="inlineStr"/>
@@ -16238,10 +16243,10 @@
         </is>
       </c>
       <c r="Q154" t="n">
-        <v>478061</v>
+        <v>478169</v>
       </c>
       <c r="R154" t="n">
-        <v>6827770</v>
+        <v>6827679</v>
       </c>
       <c r="S154" t="n">
         <v>10</v>
@@ -16300,10 +16305,10 @@
     </row>
     <row r="155">
       <c r="A155" t="n">
-        <v>120074891</v>
+        <v>120075167</v>
       </c>
       <c r="B155" t="n">
-        <v>79144</v>
+        <v>78542</v>
       </c>
       <c r="C155" t="inlineStr">
         <is>
@@ -16316,21 +16321,21 @@
         </is>
       </c>
       <c r="E155" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G155" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H155" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I155" t="inlineStr"/>
@@ -16340,10 +16345,10 @@
         </is>
       </c>
       <c r="Q155" t="n">
-        <v>478212</v>
+        <v>478105</v>
       </c>
       <c r="R155" t="n">
-        <v>6827573</v>
+        <v>6827851</v>
       </c>
       <c r="S155" t="n">
         <v>10</v>
@@ -16402,10 +16407,10 @@
     </row>
     <row r="156">
       <c r="A156" t="n">
-        <v>120074933</v>
+        <v>120075160</v>
       </c>
       <c r="B156" t="n">
-        <v>79144</v>
+        <v>78542</v>
       </c>
       <c r="C156" t="inlineStr">
         <is>
@@ -16418,21 +16423,21 @@
         </is>
       </c>
       <c r="E156" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G156" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H156" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I156" t="inlineStr"/>
@@ -16442,10 +16447,10 @@
         </is>
       </c>
       <c r="Q156" t="n">
-        <v>478189</v>
+        <v>478097</v>
       </c>
       <c r="R156" t="n">
-        <v>6827761</v>
+        <v>6827744</v>
       </c>
       <c r="S156" t="n">
         <v>10</v>
@@ -16504,10 +16509,10 @@
     </row>
     <row r="157">
       <c r="A157" t="n">
-        <v>120074906</v>
+        <v>120075070</v>
       </c>
       <c r="B157" t="n">
-        <v>79144</v>
+        <v>78542</v>
       </c>
       <c r="C157" t="inlineStr">
         <is>
@@ -16520,21 +16525,21 @@
         </is>
       </c>
       <c r="E157" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G157" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H157" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I157" t="inlineStr"/>
@@ -16544,10 +16549,10 @@
         </is>
       </c>
       <c r="Q157" t="n">
-        <v>478294</v>
+        <v>478135</v>
       </c>
       <c r="R157" t="n">
-        <v>6827790</v>
+        <v>6827625</v>
       </c>
       <c r="S157" t="n">
         <v>10</v>
@@ -16606,10 +16611,10 @@
     </row>
     <row r="158">
       <c r="A158" t="n">
-        <v>120075132</v>
+        <v>120075175</v>
       </c>
       <c r="B158" t="n">
-        <v>78526</v>
+        <v>78542</v>
       </c>
       <c r="C158" t="inlineStr">
         <is>
@@ -16646,10 +16651,10 @@
         </is>
       </c>
       <c r="Q158" t="n">
-        <v>478240</v>
+        <v>478059</v>
       </c>
       <c r="R158" t="n">
-        <v>6827754</v>
+        <v>6827739</v>
       </c>
       <c r="S158" t="n">
         <v>10</v>
@@ -16708,10 +16713,10 @@
     </row>
     <row r="159">
       <c r="A159" t="n">
-        <v>120075143</v>
+        <v>120075232</v>
       </c>
       <c r="B159" t="n">
-        <v>78526</v>
+        <v>78187</v>
       </c>
       <c r="C159" t="inlineStr">
         <is>
@@ -16724,21 +16729,21 @@
         </is>
       </c>
       <c r="E159" t="n">
-        <v>6425</v>
+        <v>353</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G159" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H159" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I159" t="inlineStr"/>
@@ -16748,10 +16753,10 @@
         </is>
       </c>
       <c r="Q159" t="n">
-        <v>478301</v>
+        <v>478051</v>
       </c>
       <c r="R159" t="n">
-        <v>6827814</v>
+        <v>6827739</v>
       </c>
       <c r="S159" t="n">
         <v>10</v>
@@ -16810,10 +16815,10 @@
     </row>
     <row r="160">
       <c r="A160" t="n">
-        <v>120075097</v>
+        <v>120075090</v>
       </c>
       <c r="B160" t="n">
-        <v>78526</v>
+        <v>78542</v>
       </c>
       <c r="C160" t="inlineStr">
         <is>
@@ -16850,10 +16855,10 @@
         </is>
       </c>
       <c r="Q160" t="n">
-        <v>478248</v>
+        <v>478161</v>
       </c>
       <c r="R160" t="n">
-        <v>6827593</v>
+        <v>6827528</v>
       </c>
       <c r="S160" t="n">
         <v>10</v>
@@ -16912,10 +16917,10 @@
     </row>
     <row r="161">
       <c r="A161" t="n">
-        <v>120075062</v>
+        <v>120075060</v>
       </c>
       <c r="B161" t="n">
-        <v>78526</v>
+        <v>78542</v>
       </c>
       <c r="C161" t="inlineStr">
         <is>
@@ -16952,10 +16957,10 @@
         </is>
       </c>
       <c r="Q161" t="n">
-        <v>478221</v>
+        <v>478087</v>
       </c>
       <c r="R161" t="n">
-        <v>6827719</v>
+        <v>6827718</v>
       </c>
       <c r="S161" t="n">
         <v>10</v>
@@ -17014,10 +17019,10 @@
     </row>
     <row r="162">
       <c r="A162" t="n">
-        <v>120075043</v>
+        <v>120074931</v>
       </c>
       <c r="B162" t="n">
-        <v>78262</v>
+        <v>79160</v>
       </c>
       <c r="C162" t="inlineStr">
         <is>
@@ -17030,21 +17035,21 @@
         </is>
       </c>
       <c r="E162" t="n">
-        <v>6446</v>
+        <v>6453</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G162" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H162" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I162" t="inlineStr"/>
@@ -17054,10 +17059,10 @@
         </is>
       </c>
       <c r="Q162" t="n">
-        <v>478103</v>
+        <v>478261</v>
       </c>
       <c r="R162" t="n">
-        <v>6827803</v>
+        <v>6827822</v>
       </c>
       <c r="S162" t="n">
         <v>10</v>
@@ -17116,10 +17121,10 @@
     </row>
     <row r="163">
       <c r="A163" t="n">
-        <v>120075048</v>
+        <v>120075054</v>
       </c>
       <c r="B163" t="n">
-        <v>56514</v>
+        <v>90598</v>
       </c>
       <c r="C163" t="inlineStr">
         <is>
@@ -17132,39 +17137,34 @@
         </is>
       </c>
       <c r="E163" t="n">
-        <v>102612</v>
+        <v>5432</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G163" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H163" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I163" t="inlineStr"/>
-      <c r="M163" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
       <c r="P163" t="inlineStr">
         <is>
           <t>Hevoslamm, Dlr</t>
         </is>
       </c>
       <c r="Q163" t="n">
-        <v>478070</v>
+        <v>478126</v>
       </c>
       <c r="R163" t="n">
-        <v>6827723</v>
+        <v>6827477</v>
       </c>
       <c r="S163" t="n">
         <v>10</v>
@@ -17223,10 +17223,10 @@
     </row>
     <row r="164">
       <c r="A164" t="n">
-        <v>120075214</v>
+        <v>120075223</v>
       </c>
       <c r="B164" t="n">
-        <v>78171</v>
+        <v>78187</v>
       </c>
       <c r="C164" t="inlineStr">
         <is>
@@ -17263,10 +17263,10 @@
         </is>
       </c>
       <c r="Q164" t="n">
-        <v>478266</v>
+        <v>478076</v>
       </c>
       <c r="R164" t="n">
-        <v>6827724</v>
+        <v>6827777</v>
       </c>
       <c r="S164" t="n">
         <v>10</v>
@@ -17325,10 +17325,10 @@
     </row>
     <row r="165">
       <c r="A165" t="n">
-        <v>120075203</v>
+        <v>120075089</v>
       </c>
       <c r="B165" t="n">
-        <v>78171</v>
+        <v>78542</v>
       </c>
       <c r="C165" t="inlineStr">
         <is>
@@ -17341,21 +17341,21 @@
         </is>
       </c>
       <c r="E165" t="n">
-        <v>353</v>
+        <v>6425</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G165" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H165" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I165" t="inlineStr"/>
@@ -17365,10 +17365,10 @@
         </is>
       </c>
       <c r="Q165" t="n">
-        <v>478125</v>
+        <v>478153</v>
       </c>
       <c r="R165" t="n">
-        <v>6827631</v>
+        <v>6827517</v>
       </c>
       <c r="S165" t="n">
         <v>10</v>
@@ -17427,10 +17427,10 @@
     </row>
     <row r="166">
       <c r="A166" t="n">
-        <v>120075026</v>
+        <v>120075025</v>
       </c>
       <c r="B166" t="n">
-        <v>78262</v>
+        <v>78278</v>
       </c>
       <c r="C166" t="inlineStr">
         <is>
@@ -17467,10 +17467,10 @@
         </is>
       </c>
       <c r="Q166" t="n">
-        <v>478161</v>
+        <v>478171</v>
       </c>
       <c r="R166" t="n">
-        <v>6827592</v>
+        <v>6827642</v>
       </c>
       <c r="S166" t="n">
         <v>10</v>
@@ -17529,10 +17529,10 @@
     </row>
     <row r="167">
       <c r="A167" t="n">
-        <v>120075046</v>
+        <v>120075137</v>
       </c>
       <c r="B167" t="n">
-        <v>78262</v>
+        <v>78542</v>
       </c>
       <c r="C167" t="inlineStr">
         <is>
@@ -17545,21 +17545,21 @@
         </is>
       </c>
       <c r="E167" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G167" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H167" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I167" t="inlineStr"/>
@@ -17569,10 +17569,10 @@
         </is>
       </c>
       <c r="Q167" t="n">
-        <v>478285</v>
+        <v>478288</v>
       </c>
       <c r="R167" t="n">
-        <v>6827770</v>
+        <v>6827763</v>
       </c>
       <c r="S167" t="n">
         <v>10</v>
@@ -17631,10 +17631,10 @@
     </row>
     <row r="168">
       <c r="A168" t="n">
-        <v>120075012</v>
+        <v>120075242</v>
       </c>
       <c r="B168" t="n">
-        <v>78263</v>
+        <v>77926</v>
       </c>
       <c r="C168" t="inlineStr">
         <is>
@@ -17647,21 +17647,21 @@
         </is>
       </c>
       <c r="E168" t="n">
-        <v>228912</v>
+        <v>6437</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G168" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H168" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I168" t="inlineStr"/>
@@ -17671,10 +17671,10 @@
         </is>
       </c>
       <c r="Q168" t="n">
-        <v>478055</v>
+        <v>478136</v>
       </c>
       <c r="R168" t="n">
-        <v>6827786</v>
+        <v>6827556</v>
       </c>
       <c r="S168" t="n">
         <v>10</v>
@@ -17733,10 +17733,10 @@
     </row>
     <row r="169">
       <c r="A169" t="n">
-        <v>120075001</v>
+        <v>120075147</v>
       </c>
       <c r="B169" t="n">
-        <v>78263</v>
+        <v>78542</v>
       </c>
       <c r="C169" t="inlineStr">
         <is>
@@ -17749,21 +17749,21 @@
         </is>
       </c>
       <c r="E169" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G169" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H169" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I169" t="inlineStr"/>
@@ -17773,10 +17773,10 @@
         </is>
       </c>
       <c r="Q169" t="n">
-        <v>478125</v>
+        <v>478153</v>
       </c>
       <c r="R169" t="n">
-        <v>6827604</v>
+        <v>6827728</v>
       </c>
       <c r="S169" t="n">
         <v>10</v>
@@ -17835,10 +17835,10 @@
     </row>
     <row r="170">
       <c r="A170" t="n">
-        <v>120075010</v>
+        <v>120075024</v>
       </c>
       <c r="B170" t="n">
-        <v>78263</v>
+        <v>78278</v>
       </c>
       <c r="C170" t="inlineStr">
         <is>
@@ -17851,21 +17851,21 @@
         </is>
       </c>
       <c r="E170" t="n">
-        <v>228912</v>
+        <v>6446</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G170" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H170" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I170" t="inlineStr"/>
@@ -17875,10 +17875,10 @@
         </is>
       </c>
       <c r="Q170" t="n">
-        <v>478074</v>
+        <v>478165</v>
       </c>
       <c r="R170" t="n">
-        <v>6827772</v>
+        <v>6827712</v>
       </c>
       <c r="S170" t="n">
         <v>10</v>
@@ -17937,10 +17937,10 @@
     </row>
     <row r="171">
       <c r="A171" t="n">
-        <v>120075206</v>
+        <v>120075130</v>
       </c>
       <c r="B171" t="n">
-        <v>78171</v>
+        <v>78542</v>
       </c>
       <c r="C171" t="inlineStr">
         <is>
@@ -17953,21 +17953,21 @@
         </is>
       </c>
       <c r="E171" t="n">
-        <v>353</v>
+        <v>6425</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G171" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H171" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I171" t="inlineStr"/>
@@ -17977,10 +17977,10 @@
         </is>
       </c>
       <c r="Q171" t="n">
-        <v>478125</v>
+        <v>478264</v>
       </c>
       <c r="R171" t="n">
-        <v>6827604</v>
+        <v>6827733</v>
       </c>
       <c r="S171" t="n">
         <v>10</v>
@@ -18039,10 +18039,10 @@
     </row>
     <row r="172">
       <c r="A172" t="n">
-        <v>120075168</v>
+        <v>120074882</v>
       </c>
       <c r="B172" t="n">
-        <v>78526</v>
+        <v>79160</v>
       </c>
       <c r="C172" t="inlineStr">
         <is>
@@ -18055,21 +18055,21 @@
         </is>
       </c>
       <c r="E172" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G172" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H172" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I172" t="inlineStr"/>
@@ -18079,10 +18079,10 @@
         </is>
       </c>
       <c r="Q172" t="n">
-        <v>478086</v>
+        <v>478162</v>
       </c>
       <c r="R172" t="n">
-        <v>6827868</v>
+        <v>6827593</v>
       </c>
       <c r="S172" t="n">
         <v>10</v>
@@ -18141,10 +18141,10 @@
     </row>
     <row r="173">
       <c r="A173" t="n">
-        <v>120075029</v>
+        <v>120075205</v>
       </c>
       <c r="B173" t="n">
-        <v>78262</v>
+        <v>78187</v>
       </c>
       <c r="C173" t="inlineStr">
         <is>
@@ -18157,21 +18157,21 @@
         </is>
       </c>
       <c r="E173" t="n">
-        <v>6446</v>
+        <v>353</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G173" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H173" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I173" t="inlineStr"/>
@@ -18181,10 +18181,10 @@
         </is>
       </c>
       <c r="Q173" t="n">
-        <v>478115</v>
+        <v>478117</v>
       </c>
       <c r="R173" t="n">
-        <v>6827564</v>
+        <v>6827612</v>
       </c>
       <c r="S173" t="n">
         <v>10</v>
@@ -18243,10 +18243,10 @@
     </row>
     <row r="174">
       <c r="A174" t="n">
-        <v>120075045</v>
+        <v>120075227</v>
       </c>
       <c r="B174" t="n">
-        <v>78262</v>
+        <v>78187</v>
       </c>
       <c r="C174" t="inlineStr">
         <is>
@@ -18259,21 +18259,21 @@
         </is>
       </c>
       <c r="E174" t="n">
-        <v>6446</v>
+        <v>353</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G174" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H174" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I174" t="inlineStr"/>
@@ -18283,10 +18283,10 @@
         </is>
       </c>
       <c r="Q174" t="n">
-        <v>478070</v>
+        <v>478088</v>
       </c>
       <c r="R174" t="n">
-        <v>6827723</v>
+        <v>6827834</v>
       </c>
       <c r="S174" t="n">
         <v>10</v>
@@ -18345,10 +18345,10 @@
     </row>
     <row r="175">
       <c r="A175" t="n">
-        <v>120075040</v>
+        <v>120075166</v>
       </c>
       <c r="B175" t="n">
-        <v>78262</v>
+        <v>78542</v>
       </c>
       <c r="C175" t="inlineStr">
         <is>
@@ -18361,21 +18361,21 @@
         </is>
       </c>
       <c r="E175" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G175" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H175" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I175" t="inlineStr"/>
@@ -18385,10 +18385,10 @@
         </is>
       </c>
       <c r="Q175" t="n">
-        <v>478250</v>
+        <v>478092</v>
       </c>
       <c r="R175" t="n">
-        <v>6827802</v>
+        <v>6827839</v>
       </c>
       <c r="S175" t="n">
         <v>10</v>
@@ -18447,10 +18447,10 @@
     </row>
     <row r="176">
       <c r="A176" t="n">
-        <v>120074942</v>
+        <v>120075071</v>
       </c>
       <c r="B176" t="n">
-        <v>79144</v>
+        <v>78542</v>
       </c>
       <c r="C176" t="inlineStr">
         <is>
@@ -18463,21 +18463,21 @@
         </is>
       </c>
       <c r="E176" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G176" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H176" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I176" t="inlineStr"/>
@@ -18487,10 +18487,10 @@
         </is>
       </c>
       <c r="Q176" t="n">
-        <v>478065</v>
+        <v>478116</v>
       </c>
       <c r="R176" t="n">
-        <v>6827842</v>
+        <v>6827633</v>
       </c>
       <c r="S176" t="n">
         <v>10</v>
@@ -18549,10 +18549,10 @@
     </row>
     <row r="177">
       <c r="A177" t="n">
-        <v>120074998</v>
+        <v>120075127</v>
       </c>
       <c r="B177" t="n">
-        <v>78263</v>
+        <v>78542</v>
       </c>
       <c r="C177" t="inlineStr">
         <is>
@@ -18565,21 +18565,21 @@
         </is>
       </c>
       <c r="E177" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G177" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H177" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I177" t="inlineStr"/>
@@ -18589,10 +18589,10 @@
         </is>
       </c>
       <c r="Q177" t="n">
-        <v>478172</v>
+        <v>478292</v>
       </c>
       <c r="R177" t="n">
-        <v>6827640</v>
+        <v>6827708</v>
       </c>
       <c r="S177" t="n">
         <v>10</v>
@@ -18651,10 +18651,10 @@
     </row>
     <row r="178">
       <c r="A178" t="n">
-        <v>120075009</v>
+        <v>120075073</v>
       </c>
       <c r="B178" t="n">
-        <v>78263</v>
+        <v>78542</v>
       </c>
       <c r="C178" t="inlineStr">
         <is>
@@ -18667,21 +18667,21 @@
         </is>
       </c>
       <c r="E178" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G178" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H178" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I178" t="inlineStr"/>
@@ -18691,10 +18691,10 @@
         </is>
       </c>
       <c r="Q178" t="n">
-        <v>478151</v>
+        <v>478116</v>
       </c>
       <c r="R178" t="n">
-        <v>6827745</v>
+        <v>6827617</v>
       </c>
       <c r="S178" t="n">
         <v>10</v>
@@ -18753,10 +18753,10 @@
     </row>
     <row r="179">
       <c r="A179" t="n">
-        <v>120074885</v>
+        <v>120075078</v>
       </c>
       <c r="B179" t="n">
-        <v>79144</v>
+        <v>78542</v>
       </c>
       <c r="C179" t="inlineStr">
         <is>
@@ -18769,21 +18769,21 @@
         </is>
       </c>
       <c r="E179" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G179" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H179" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I179" t="inlineStr"/>
@@ -18793,10 +18793,10 @@
         </is>
       </c>
       <c r="Q179" t="n">
-        <v>478115</v>
+        <v>478116</v>
       </c>
       <c r="R179" t="n">
-        <v>6827614</v>
+        <v>6827567</v>
       </c>
       <c r="S179" t="n">
         <v>10</v>
@@ -18855,10 +18855,10 @@
     </row>
     <row r="180">
       <c r="A180" t="n">
-        <v>120074887</v>
+        <v>120075128</v>
       </c>
       <c r="B180" t="n">
-        <v>79144</v>
+        <v>78542</v>
       </c>
       <c r="C180" t="inlineStr">
         <is>
@@ -18871,21 +18871,21 @@
         </is>
       </c>
       <c r="E180" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G180" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H180" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I180" t="inlineStr"/>
@@ -18895,10 +18895,10 @@
         </is>
       </c>
       <c r="Q180" t="n">
-        <v>478144</v>
+        <v>478275</v>
       </c>
       <c r="R180" t="n">
-        <v>6827593</v>
+        <v>6827710</v>
       </c>
       <c r="S180" t="n">
         <v>10</v>
@@ -18957,10 +18957,10 @@
     </row>
     <row r="181">
       <c r="A181" t="n">
-        <v>120075087</v>
+        <v>120074933</v>
       </c>
       <c r="B181" t="n">
-        <v>78526</v>
+        <v>79160</v>
       </c>
       <c r="C181" t="inlineStr">
         <is>
@@ -18973,21 +18973,21 @@
         </is>
       </c>
       <c r="E181" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G181" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H181" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I181" t="inlineStr"/>
@@ -18997,10 +18997,10 @@
         </is>
       </c>
       <c r="Q181" t="n">
-        <v>478145</v>
+        <v>478189</v>
       </c>
       <c r="R181" t="n">
-        <v>6827485</v>
+        <v>6827761</v>
       </c>
       <c r="S181" t="n">
         <v>10</v>

--- a/artfynd/A 32983-2023 artfynd.xlsx
+++ b/artfynd/A 32983-2023 artfynd.xlsx
@@ -4255,10 +4255,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>120075015</v>
+        <v>120075215</v>
       </c>
       <c r="B37" t="n">
-        <v>79623</v>
+        <v>78187</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4271,21 +4271,21 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6458</v>
+        <v>353</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4295,10 +4295,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>478114</v>
+        <v>478239</v>
       </c>
       <c r="R37" t="n">
-        <v>6827633</v>
+        <v>6827752</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4459,10 +4459,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>120075215</v>
+        <v>120075015</v>
       </c>
       <c r="B39" t="n">
-        <v>78187</v>
+        <v>79623</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4475,21 +4475,21 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>353</v>
+        <v>6458</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4499,10 +4499,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>478239</v>
+        <v>478114</v>
       </c>
       <c r="R39" t="n">
-        <v>6827752</v>
+        <v>6827633</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4561,10 +4561,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>120075003</v>
+        <v>120075202</v>
       </c>
       <c r="B40" t="n">
-        <v>78279</v>
+        <v>78187</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -4577,21 +4577,21 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>228912</v>
+        <v>353</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4601,10 +4601,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>478137</v>
+        <v>478218</v>
       </c>
       <c r="R40" t="n">
-        <v>6827553</v>
+        <v>6827721</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4663,10 +4663,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>120075202</v>
+        <v>120075003</v>
       </c>
       <c r="B41" t="n">
-        <v>78187</v>
+        <v>78279</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -4679,21 +4679,21 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>353</v>
+        <v>228912</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4703,10 +4703,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>478218</v>
+        <v>478137</v>
       </c>
       <c r="R41" t="n">
-        <v>6827721</v>
+        <v>6827553</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -6499,10 +6499,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>120075226</v>
+        <v>120075133</v>
       </c>
       <c r="B59" t="n">
-        <v>78187</v>
+        <v>78542</v>
       </c>
       <c r="C59" t="inlineStr">
         <is>
@@ -6515,21 +6515,21 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>353</v>
+        <v>6425</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
@@ -6539,10 +6539,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>478098</v>
+        <v>478258</v>
       </c>
       <c r="R59" t="n">
-        <v>6827815</v>
+        <v>6827753</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6601,10 +6601,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>120075217</v>
+        <v>120075168</v>
       </c>
       <c r="B60" t="n">
-        <v>78187</v>
+        <v>78542</v>
       </c>
       <c r="C60" t="inlineStr">
         <is>
@@ -6617,21 +6617,21 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>353</v>
+        <v>6425</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
@@ -6641,10 +6641,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>478264</v>
+        <v>478086</v>
       </c>
       <c r="R60" t="n">
-        <v>6827839</v>
+        <v>6827868</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -6703,10 +6703,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>120074986</v>
+        <v>120075067</v>
       </c>
       <c r="B61" t="n">
-        <v>79624</v>
+        <v>78542</v>
       </c>
       <c r="C61" t="inlineStr">
         <is>
@@ -6719,21 +6719,21 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>2081</v>
+        <v>6425</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
@@ -6743,10 +6743,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>478096</v>
+        <v>478164</v>
       </c>
       <c r="R61" t="n">
-        <v>6827549</v>
+        <v>6827661</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -6805,7 +6805,7 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>120075133</v>
+        <v>120075086</v>
       </c>
       <c r="B62" t="n">
         <v>78542</v>
@@ -6845,10 +6845,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>478258</v>
+        <v>478104</v>
       </c>
       <c r="R62" t="n">
-        <v>6827753</v>
+        <v>6827495</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -6907,10 +6907,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>120075168</v>
+        <v>120075226</v>
       </c>
       <c r="B63" t="n">
-        <v>78542</v>
+        <v>78187</v>
       </c>
       <c r="C63" t="inlineStr">
         <is>
@@ -6923,21 +6923,21 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>6425</v>
+        <v>353</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
@@ -6947,10 +6947,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>478086</v>
+        <v>478098</v>
       </c>
       <c r="R63" t="n">
-        <v>6827868</v>
+        <v>6827815</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -7009,10 +7009,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>120075067</v>
+        <v>120075217</v>
       </c>
       <c r="B64" t="n">
-        <v>78542</v>
+        <v>78187</v>
       </c>
       <c r="C64" t="inlineStr">
         <is>
@@ -7025,21 +7025,21 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>6425</v>
+        <v>353</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
@@ -7049,10 +7049,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>478164</v>
+        <v>478264</v>
       </c>
       <c r="R64" t="n">
-        <v>6827661</v>
+        <v>6827839</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -7111,10 +7111,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>120075086</v>
+        <v>120074986</v>
       </c>
       <c r="B65" t="n">
-        <v>78542</v>
+        <v>79624</v>
       </c>
       <c r="C65" t="inlineStr">
         <is>
@@ -7127,21 +7127,21 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>6425</v>
+        <v>2081</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
@@ -7151,10 +7151,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>478104</v>
+        <v>478096</v>
       </c>
       <c r="R65" t="n">
-        <v>6827495</v>
+        <v>6827549</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -8548,7 +8548,7 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>120075135</v>
+        <v>120075131</v>
       </c>
       <c r="B79" t="n">
         <v>78542</v>
@@ -8588,10 +8588,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>478291</v>
+        <v>478258</v>
       </c>
       <c r="R79" t="n">
-        <v>6827744</v>
+        <v>6827731</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -8650,7 +8650,7 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>120075177</v>
+        <v>120075097</v>
       </c>
       <c r="B80" t="n">
         <v>78542</v>
@@ -8690,10 +8690,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>478075</v>
+        <v>478248</v>
       </c>
       <c r="R80" t="n">
-        <v>6827717</v>
+        <v>6827593</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -8752,7 +8752,7 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>120075131</v>
+        <v>120075068</v>
       </c>
       <c r="B81" t="n">
         <v>78542</v>
@@ -8792,10 +8792,10 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>478258</v>
+        <v>478174</v>
       </c>
       <c r="R81" t="n">
-        <v>6827731</v>
+        <v>6827656</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -8854,7 +8854,7 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>120075097</v>
+        <v>120075066</v>
       </c>
       <c r="B82" t="n">
         <v>78542</v>
@@ -8894,10 +8894,10 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>478248</v>
+        <v>478160</v>
       </c>
       <c r="R82" t="n">
-        <v>6827593</v>
+        <v>6827680</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -8956,7 +8956,7 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>120075068</v>
+        <v>120075135</v>
       </c>
       <c r="B83" t="n">
         <v>78542</v>
@@ -8996,10 +8996,10 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>478174</v>
+        <v>478291</v>
       </c>
       <c r="R83" t="n">
-        <v>6827656</v>
+        <v>6827744</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -9058,7 +9058,7 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>120075066</v>
+        <v>120075177</v>
       </c>
       <c r="B84" t="n">
         <v>78542</v>
@@ -9098,10 +9098,10 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>478160</v>
+        <v>478075</v>
       </c>
       <c r="R84" t="n">
-        <v>6827680</v>
+        <v>6827717</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -9160,10 +9160,10 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>120075000</v>
+        <v>120074917</v>
       </c>
       <c r="B85" t="n">
-        <v>78279</v>
+        <v>78576</v>
       </c>
       <c r="C85" t="inlineStr">
         <is>
@@ -9176,21 +9176,21 @@
         </is>
       </c>
       <c r="E85" t="n">
-        <v>228912</v>
+        <v>185</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
@@ -9200,10 +9200,10 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>478121</v>
+        <v>478095</v>
       </c>
       <c r="R85" t="n">
-        <v>6827607</v>
+        <v>6827533</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -9262,10 +9262,10 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>120074917</v>
+        <v>120075224</v>
       </c>
       <c r="B86" t="n">
-        <v>78576</v>
+        <v>78187</v>
       </c>
       <c r="C86" t="inlineStr">
         <is>
@@ -9278,21 +9278,21 @@
         </is>
       </c>
       <c r="E86" t="n">
-        <v>185</v>
+        <v>353</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I86" t="inlineStr"/>
@@ -9302,10 +9302,10 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>478095</v>
+        <v>478081</v>
       </c>
       <c r="R86" t="n">
-        <v>6827533</v>
+        <v>6827789</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>
@@ -9364,7 +9364,7 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>120075224</v>
+        <v>120075201</v>
       </c>
       <c r="B87" t="n">
         <v>78187</v>
@@ -9404,10 +9404,10 @@
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>478081</v>
+        <v>478182</v>
       </c>
       <c r="R87" t="n">
-        <v>6827789</v>
+        <v>6827728</v>
       </c>
       <c r="S87" t="n">
         <v>10</v>
@@ -9466,10 +9466,10 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>120075201</v>
+        <v>120075081</v>
       </c>
       <c r="B88" t="n">
-        <v>78187</v>
+        <v>78542</v>
       </c>
       <c r="C88" t="inlineStr">
         <is>
@@ -9482,21 +9482,21 @@
         </is>
       </c>
       <c r="E88" t="n">
-        <v>353</v>
+        <v>6425</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I88" t="inlineStr"/>
@@ -9506,10 +9506,10 @@
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>478182</v>
+        <v>478096</v>
       </c>
       <c r="R88" t="n">
-        <v>6827728</v>
+        <v>6827550</v>
       </c>
       <c r="S88" t="n">
         <v>10</v>
@@ -9568,10 +9568,10 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>120075081</v>
+        <v>120075046</v>
       </c>
       <c r="B89" t="n">
-        <v>78542</v>
+        <v>78278</v>
       </c>
       <c r="C89" t="inlineStr">
         <is>
@@ -9584,21 +9584,21 @@
         </is>
       </c>
       <c r="E89" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I89" t="inlineStr"/>
@@ -9608,10 +9608,10 @@
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>478096</v>
+        <v>478285</v>
       </c>
       <c r="R89" t="n">
-        <v>6827550</v>
+        <v>6827770</v>
       </c>
       <c r="S89" t="n">
         <v>10</v>
@@ -9670,10 +9670,10 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>120075046</v>
+        <v>120075095</v>
       </c>
       <c r="B90" t="n">
-        <v>78278</v>
+        <v>78542</v>
       </c>
       <c r="C90" t="inlineStr">
         <is>
@@ -9686,21 +9686,21 @@
         </is>
       </c>
       <c r="E90" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I90" t="inlineStr"/>
@@ -9710,10 +9710,10 @@
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>478285</v>
+        <v>478219</v>
       </c>
       <c r="R90" t="n">
-        <v>6827770</v>
+        <v>6827572</v>
       </c>
       <c r="S90" t="n">
         <v>10</v>
@@ -9772,10 +9772,10 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>120075095</v>
+        <v>120075035</v>
       </c>
       <c r="B91" t="n">
-        <v>78542</v>
+        <v>78278</v>
       </c>
       <c r="C91" t="inlineStr">
         <is>
@@ -9788,21 +9788,21 @@
         </is>
       </c>
       <c r="E91" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I91" t="inlineStr"/>
@@ -9812,10 +9812,10 @@
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>478219</v>
+        <v>478273</v>
       </c>
       <c r="R91" t="n">
-        <v>6827572</v>
+        <v>6827711</v>
       </c>
       <c r="S91" t="n">
         <v>10</v>
@@ -9874,10 +9874,10 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>120075035</v>
+        <v>120074892</v>
       </c>
       <c r="B92" t="n">
-        <v>78278</v>
+        <v>79160</v>
       </c>
       <c r="C92" t="inlineStr">
         <is>
@@ -9890,21 +9890,21 @@
         </is>
       </c>
       <c r="E92" t="n">
-        <v>6446</v>
+        <v>6453</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I92" t="inlineStr"/>
@@ -9914,10 +9914,10 @@
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>478273</v>
+        <v>478243</v>
       </c>
       <c r="R92" t="n">
-        <v>6827711</v>
+        <v>6827585</v>
       </c>
       <c r="S92" t="n">
         <v>10</v>
@@ -9976,10 +9976,10 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>120074892</v>
+        <v>120075045</v>
       </c>
       <c r="B93" t="n">
-        <v>79160</v>
+        <v>78278</v>
       </c>
       <c r="C93" t="inlineStr">
         <is>
@@ -9992,21 +9992,21 @@
         </is>
       </c>
       <c r="E93" t="n">
-        <v>6453</v>
+        <v>6446</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I93" t="inlineStr"/>
@@ -10016,10 +10016,10 @@
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>478243</v>
+        <v>478070</v>
       </c>
       <c r="R93" t="n">
-        <v>6827585</v>
+        <v>6827723</v>
       </c>
       <c r="S93" t="n">
         <v>10</v>
@@ -10078,10 +10078,10 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>120075045</v>
+        <v>120075087</v>
       </c>
       <c r="B94" t="n">
-        <v>78278</v>
+        <v>78542</v>
       </c>
       <c r="C94" t="inlineStr">
         <is>
@@ -10094,21 +10094,21 @@
         </is>
       </c>
       <c r="E94" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I94" t="inlineStr"/>
@@ -10118,10 +10118,10 @@
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>478070</v>
+        <v>478145</v>
       </c>
       <c r="R94" t="n">
-        <v>6827723</v>
+        <v>6827485</v>
       </c>
       <c r="S94" t="n">
         <v>10</v>
@@ -10180,10 +10180,10 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>120075087</v>
+        <v>120075028</v>
       </c>
       <c r="B95" t="n">
-        <v>78542</v>
+        <v>78278</v>
       </c>
       <c r="C95" t="inlineStr">
         <is>
@@ -10196,21 +10196,21 @@
         </is>
       </c>
       <c r="E95" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I95" t="inlineStr"/>
@@ -10220,10 +10220,10 @@
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>478145</v>
+        <v>478137</v>
       </c>
       <c r="R95" t="n">
-        <v>6827485</v>
+        <v>6827553</v>
       </c>
       <c r="S95" t="n">
         <v>10</v>
@@ -10282,10 +10282,10 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>120075028</v>
+        <v>120075138</v>
       </c>
       <c r="B96" t="n">
-        <v>78278</v>
+        <v>78542</v>
       </c>
       <c r="C96" t="inlineStr">
         <is>
@@ -10298,21 +10298,21 @@
         </is>
       </c>
       <c r="E96" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I96" t="inlineStr"/>
@@ -10322,10 +10322,10 @@
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>478137</v>
+        <v>478294</v>
       </c>
       <c r="R96" t="n">
-        <v>6827553</v>
+        <v>6827781</v>
       </c>
       <c r="S96" t="n">
         <v>10</v>
@@ -10384,7 +10384,7 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>120075138</v>
+        <v>120075129</v>
       </c>
       <c r="B97" t="n">
         <v>78542</v>
@@ -10424,10 +10424,10 @@
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>478294</v>
+        <v>478265</v>
       </c>
       <c r="R97" t="n">
-        <v>6827781</v>
+        <v>6827707</v>
       </c>
       <c r="S97" t="n">
         <v>10</v>
@@ -10486,10 +10486,10 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>120075129</v>
+        <v>120074942</v>
       </c>
       <c r="B98" t="n">
-        <v>78542</v>
+        <v>79160</v>
       </c>
       <c r="C98" t="inlineStr">
         <is>
@@ -10502,21 +10502,21 @@
         </is>
       </c>
       <c r="E98" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I98" t="inlineStr"/>
@@ -10526,10 +10526,10 @@
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>478265</v>
+        <v>478065</v>
       </c>
       <c r="R98" t="n">
-        <v>6827707</v>
+        <v>6827842</v>
       </c>
       <c r="S98" t="n">
         <v>10</v>
@@ -10588,10 +10588,10 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>120074942</v>
+        <v>120075000</v>
       </c>
       <c r="B99" t="n">
-        <v>79160</v>
+        <v>78279</v>
       </c>
       <c r="C99" t="inlineStr">
         <is>
@@ -10604,21 +10604,21 @@
         </is>
       </c>
       <c r="E99" t="n">
-        <v>6453</v>
+        <v>228912</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I99" t="inlineStr"/>
@@ -10628,10 +10628,10 @@
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>478065</v>
+        <v>478121</v>
       </c>
       <c r="R99" t="n">
-        <v>6827842</v>
+        <v>6827607</v>
       </c>
       <c r="S99" t="n">
         <v>10</v>
@@ -16815,10 +16815,10 @@
     </row>
     <row r="160">
       <c r="A160" t="n">
-        <v>120075090</v>
+        <v>120075054</v>
       </c>
       <c r="B160" t="n">
-        <v>78542</v>
+        <v>90598</v>
       </c>
       <c r="C160" t="inlineStr">
         <is>
@@ -16831,21 +16831,21 @@
         </is>
       </c>
       <c r="E160" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G160" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H160" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I160" t="inlineStr"/>
@@ -16855,10 +16855,10 @@
         </is>
       </c>
       <c r="Q160" t="n">
-        <v>478161</v>
+        <v>478126</v>
       </c>
       <c r="R160" t="n">
-        <v>6827528</v>
+        <v>6827477</v>
       </c>
       <c r="S160" t="n">
         <v>10</v>
@@ -16917,7 +16917,7 @@
     </row>
     <row r="161">
       <c r="A161" t="n">
-        <v>120075060</v>
+        <v>120075090</v>
       </c>
       <c r="B161" t="n">
         <v>78542</v>
@@ -16957,10 +16957,10 @@
         </is>
       </c>
       <c r="Q161" t="n">
-        <v>478087</v>
+        <v>478161</v>
       </c>
       <c r="R161" t="n">
-        <v>6827718</v>
+        <v>6827528</v>
       </c>
       <c r="S161" t="n">
         <v>10</v>
@@ -17019,10 +17019,10 @@
     </row>
     <row r="162">
       <c r="A162" t="n">
-        <v>120074931</v>
+        <v>120075060</v>
       </c>
       <c r="B162" t="n">
-        <v>79160</v>
+        <v>78542</v>
       </c>
       <c r="C162" t="inlineStr">
         <is>
@@ -17035,21 +17035,21 @@
         </is>
       </c>
       <c r="E162" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G162" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H162" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I162" t="inlineStr"/>
@@ -17059,10 +17059,10 @@
         </is>
       </c>
       <c r="Q162" t="n">
-        <v>478261</v>
+        <v>478087</v>
       </c>
       <c r="R162" t="n">
-        <v>6827822</v>
+        <v>6827718</v>
       </c>
       <c r="S162" t="n">
         <v>10</v>
@@ -17121,10 +17121,10 @@
     </row>
     <row r="163">
       <c r="A163" t="n">
-        <v>120075054</v>
+        <v>120074931</v>
       </c>
       <c r="B163" t="n">
-        <v>90598</v>
+        <v>79160</v>
       </c>
       <c r="C163" t="inlineStr">
         <is>
@@ -17137,21 +17137,21 @@
         </is>
       </c>
       <c r="E163" t="n">
-        <v>5432</v>
+        <v>6453</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G163" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H163" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I163" t="inlineStr"/>
@@ -17161,10 +17161,10 @@
         </is>
       </c>
       <c r="Q163" t="n">
-        <v>478126</v>
+        <v>478261</v>
       </c>
       <c r="R163" t="n">
-        <v>6827477</v>
+        <v>6827822</v>
       </c>
       <c r="S163" t="n">
         <v>10</v>
@@ -18345,7 +18345,7 @@
     </row>
     <row r="175">
       <c r="A175" t="n">
-        <v>120075166</v>
+        <v>120075071</v>
       </c>
       <c r="B175" t="n">
         <v>78542</v>
@@ -18385,10 +18385,10 @@
         </is>
       </c>
       <c r="Q175" t="n">
-        <v>478092</v>
+        <v>478116</v>
       </c>
       <c r="R175" t="n">
-        <v>6827839</v>
+        <v>6827633</v>
       </c>
       <c r="S175" t="n">
         <v>10</v>
@@ -18447,7 +18447,7 @@
     </row>
     <row r="176">
       <c r="A176" t="n">
-        <v>120075071</v>
+        <v>120075127</v>
       </c>
       <c r="B176" t="n">
         <v>78542</v>
@@ -18487,10 +18487,10 @@
         </is>
       </c>
       <c r="Q176" t="n">
-        <v>478116</v>
+        <v>478292</v>
       </c>
       <c r="R176" t="n">
-        <v>6827633</v>
+        <v>6827708</v>
       </c>
       <c r="S176" t="n">
         <v>10</v>
@@ -18549,7 +18549,7 @@
     </row>
     <row r="177">
       <c r="A177" t="n">
-        <v>120075127</v>
+        <v>120075073</v>
       </c>
       <c r="B177" t="n">
         <v>78542</v>
@@ -18589,10 +18589,10 @@
         </is>
       </c>
       <c r="Q177" t="n">
-        <v>478292</v>
+        <v>478116</v>
       </c>
       <c r="R177" t="n">
-        <v>6827708</v>
+        <v>6827617</v>
       </c>
       <c r="S177" t="n">
         <v>10</v>
@@ -18651,7 +18651,7 @@
     </row>
     <row r="178">
       <c r="A178" t="n">
-        <v>120075073</v>
+        <v>120075078</v>
       </c>
       <c r="B178" t="n">
         <v>78542</v>
@@ -18694,7 +18694,7 @@
         <v>478116</v>
       </c>
       <c r="R178" t="n">
-        <v>6827617</v>
+        <v>6827567</v>
       </c>
       <c r="S178" t="n">
         <v>10</v>
@@ -18753,7 +18753,7 @@
     </row>
     <row r="179">
       <c r="A179" t="n">
-        <v>120075078</v>
+        <v>120075128</v>
       </c>
       <c r="B179" t="n">
         <v>78542</v>
@@ -18793,10 +18793,10 @@
         </is>
       </c>
       <c r="Q179" t="n">
-        <v>478116</v>
+        <v>478275</v>
       </c>
       <c r="R179" t="n">
-        <v>6827567</v>
+        <v>6827710</v>
       </c>
       <c r="S179" t="n">
         <v>10</v>
@@ -18855,10 +18855,10 @@
     </row>
     <row r="180">
       <c r="A180" t="n">
-        <v>120075128</v>
+        <v>120074933</v>
       </c>
       <c r="B180" t="n">
-        <v>78542</v>
+        <v>79160</v>
       </c>
       <c r="C180" t="inlineStr">
         <is>
@@ -18871,21 +18871,21 @@
         </is>
       </c>
       <c r="E180" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G180" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H180" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I180" t="inlineStr"/>
@@ -18895,10 +18895,10 @@
         </is>
       </c>
       <c r="Q180" t="n">
-        <v>478275</v>
+        <v>478189</v>
       </c>
       <c r="R180" t="n">
-        <v>6827710</v>
+        <v>6827761</v>
       </c>
       <c r="S180" t="n">
         <v>10</v>
@@ -18957,10 +18957,10 @@
     </row>
     <row r="181">
       <c r="A181" t="n">
-        <v>120074933</v>
+        <v>120075166</v>
       </c>
       <c r="B181" t="n">
-        <v>79160</v>
+        <v>78542</v>
       </c>
       <c r="C181" t="inlineStr">
         <is>
@@ -18973,21 +18973,21 @@
         </is>
       </c>
       <c r="E181" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G181" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H181" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I181" t="inlineStr"/>
@@ -18997,10 +18997,10 @@
         </is>
       </c>
       <c r="Q181" t="n">
-        <v>478189</v>
+        <v>478092</v>
       </c>
       <c r="R181" t="n">
-        <v>6827761</v>
+        <v>6827839</v>
       </c>
       <c r="S181" t="n">
         <v>10</v>

--- a/artfynd/A 32983-2023 artfynd.xlsx
+++ b/artfynd/A 32983-2023 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>120074999</v>
+        <v>120074986</v>
       </c>
       <c r="B2" t="n">
-        <v>78279</v>
+        <v>79624</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>228912</v>
+        <v>2081</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>478161</v>
+        <v>478096</v>
       </c>
       <c r="R2" t="n">
-        <v>6827592</v>
+        <v>6827549</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -777,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>120075007</v>
+        <v>120074930</v>
       </c>
       <c r="B3" t="n">
-        <v>78279</v>
+        <v>79160</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -793,21 +793,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>228912</v>
+        <v>6453</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -817,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>478285</v>
+        <v>478299</v>
       </c>
       <c r="R3" t="n">
-        <v>6827770</v>
+        <v>6827805</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -879,7 +879,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>120075159</v>
+        <v>120075085</v>
       </c>
       <c r="B4" t="n">
         <v>78542</v>
@@ -919,10 +919,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>478100</v>
+        <v>478094</v>
       </c>
       <c r="R4" t="n">
-        <v>6827729</v>
+        <v>6827504</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -981,7 +981,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>120075083</v>
+        <v>120075157</v>
       </c>
       <c r="B5" t="n">
         <v>78542</v>
@@ -1021,10 +1021,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>478097</v>
+        <v>478103</v>
       </c>
       <c r="R5" t="n">
-        <v>6827527</v>
+        <v>6827718</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1083,10 +1083,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>120074905</v>
+        <v>120075216</v>
       </c>
       <c r="B6" t="n">
-        <v>79160</v>
+        <v>78187</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1099,21 +1099,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6453</v>
+        <v>353</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1123,10 +1123,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>478285</v>
+        <v>478294</v>
       </c>
       <c r="R6" t="n">
-        <v>6827770</v>
+        <v>6827790</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1185,10 +1185,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>120075134</v>
+        <v>120074928</v>
       </c>
       <c r="B7" t="n">
-        <v>78542</v>
+        <v>78576</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1201,21 +1201,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1225,10 +1225,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>478266</v>
+        <v>478059</v>
       </c>
       <c r="R7" t="n">
-        <v>6827765</v>
+        <v>6827740</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1287,10 +1287,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>120075171</v>
+        <v>120074882</v>
       </c>
       <c r="B8" t="n">
-        <v>78542</v>
+        <v>79160</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1303,21 +1303,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1327,10 +1327,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>478073</v>
+        <v>478162</v>
       </c>
       <c r="R8" t="n">
-        <v>6827831</v>
+        <v>6827593</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1389,10 +1389,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>120074927</v>
+        <v>120075097</v>
       </c>
       <c r="B9" t="n">
-        <v>78576</v>
+        <v>78542</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1405,21 +1405,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1429,10 +1429,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>478073</v>
+        <v>478248</v>
       </c>
       <c r="R9" t="n">
-        <v>6827836</v>
+        <v>6827593</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1491,10 +1491,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>120075231</v>
+        <v>120075140</v>
       </c>
       <c r="B10" t="n">
-        <v>78187</v>
+        <v>78542</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1507,21 +1507,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>353</v>
+        <v>6425</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1531,10 +1531,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>478067</v>
+        <v>478310</v>
       </c>
       <c r="R10" t="n">
-        <v>6827863</v>
+        <v>6827797</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1593,7 +1593,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>120075230</v>
+        <v>120075226</v>
       </c>
       <c r="B11" t="n">
         <v>78187</v>
@@ -1633,10 +1633,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>478064</v>
+        <v>478098</v>
       </c>
       <c r="R11" t="n">
-        <v>6827866</v>
+        <v>6827815</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1695,10 +1695,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>120075196</v>
+        <v>120074922</v>
       </c>
       <c r="B12" t="n">
-        <v>78542</v>
+        <v>78576</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1711,21 +1711,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1735,10 +1735,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>478288</v>
+        <v>478103</v>
       </c>
       <c r="R12" t="n">
-        <v>6827682</v>
+        <v>6827718</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1797,7 +1797,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>120075139</v>
+        <v>120075131</v>
       </c>
       <c r="B13" t="n">
         <v>78542</v>
@@ -1837,10 +1837,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>478294</v>
+        <v>478258</v>
       </c>
       <c r="R13" t="n">
-        <v>6827803</v>
+        <v>6827731</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1899,7 +1899,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>120075162</v>
+        <v>120075077</v>
       </c>
       <c r="B14" t="n">
         <v>78542</v>
@@ -1939,10 +1939,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>478080</v>
+        <v>478124</v>
       </c>
       <c r="R14" t="n">
-        <v>6827808</v>
+        <v>6827560</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2001,7 +2001,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>120075085</v>
+        <v>120075174</v>
       </c>
       <c r="B15" t="n">
         <v>78542</v>
@@ -2041,10 +2041,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>478094</v>
+        <v>478057</v>
       </c>
       <c r="R15" t="n">
-        <v>6827504</v>
+        <v>6827749</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2103,7 +2103,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>120075173</v>
+        <v>120075129</v>
       </c>
       <c r="B16" t="n">
         <v>78542</v>
@@ -2143,10 +2143,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>478052</v>
+        <v>478265</v>
       </c>
       <c r="R16" t="n">
-        <v>6827754</v>
+        <v>6827707</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2205,10 +2205,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>120075043</v>
+        <v>120075120</v>
       </c>
       <c r="B17" t="n">
-        <v>78278</v>
+        <v>78542</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2221,21 +2221,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2245,10 +2245,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>478103</v>
+        <v>478223</v>
       </c>
       <c r="R17" t="n">
-        <v>6827803</v>
+        <v>6827657</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2307,7 +2307,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>120075145</v>
+        <v>120075075</v>
       </c>
       <c r="B18" t="n">
         <v>78542</v>
@@ -2347,10 +2347,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>478226</v>
+        <v>478139</v>
       </c>
       <c r="R18" t="n">
-        <v>6827777</v>
+        <v>6827554</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2409,10 +2409,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>120075008</v>
+        <v>120075063</v>
       </c>
       <c r="B19" t="n">
-        <v>78279</v>
+        <v>78542</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2425,21 +2425,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2449,10 +2449,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>478299</v>
+        <v>478201</v>
       </c>
       <c r="R19" t="n">
-        <v>6827805</v>
+        <v>6827693</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2511,10 +2511,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>120074907</v>
+        <v>120075146</v>
       </c>
       <c r="B20" t="n">
-        <v>79160</v>
+        <v>78542</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2527,21 +2527,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2551,10 +2551,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>478263</v>
+        <v>478154</v>
       </c>
       <c r="R20" t="n">
-        <v>6827838</v>
+        <v>6827747</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2613,10 +2613,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>120074883</v>
+        <v>120075001</v>
       </c>
       <c r="B21" t="n">
-        <v>79160</v>
+        <v>78279</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2629,21 +2629,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6453</v>
+        <v>228912</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2653,10 +2653,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>478142</v>
+        <v>478125</v>
       </c>
       <c r="R21" t="n">
-        <v>6827623</v>
+        <v>6827604</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2715,10 +2715,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>120074938</v>
+        <v>120075009</v>
       </c>
       <c r="B22" t="n">
-        <v>79160</v>
+        <v>78279</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2731,21 +2731,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6453</v>
+        <v>228912</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2755,10 +2755,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>478097</v>
+        <v>478151</v>
       </c>
       <c r="R22" t="n">
-        <v>6827756</v>
+        <v>6827745</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2817,10 +2817,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>120074930</v>
+        <v>120075004</v>
       </c>
       <c r="B23" t="n">
-        <v>79160</v>
+        <v>78279</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -2833,21 +2833,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6453</v>
+        <v>228912</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2857,10 +2857,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>478299</v>
+        <v>478212</v>
       </c>
       <c r="R23" t="n">
-        <v>6827805</v>
+        <v>6827573</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2919,10 +2919,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>120075044</v>
+        <v>120075003</v>
       </c>
       <c r="B24" t="n">
-        <v>78278</v>
+        <v>78279</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -2935,21 +2935,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6446</v>
+        <v>228912</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -2959,10 +2959,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>478060</v>
+        <v>478137</v>
       </c>
       <c r="R24" t="n">
-        <v>6827770</v>
+        <v>6827553</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3021,7 +3021,7 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>120075074</v>
+        <v>120075132</v>
       </c>
       <c r="B25" t="n">
         <v>78542</v>
@@ -3061,10 +3061,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>478138</v>
+        <v>478240</v>
       </c>
       <c r="R25" t="n">
-        <v>6827599</v>
+        <v>6827754</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3123,7 +3123,7 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>120075077</v>
+        <v>120075062</v>
       </c>
       <c r="B26" t="n">
         <v>78542</v>
@@ -3163,10 +3163,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>478124</v>
+        <v>478221</v>
       </c>
       <c r="R26" t="n">
-        <v>6827560</v>
+        <v>6827719</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3225,10 +3225,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>120075174</v>
+        <v>120074932</v>
       </c>
       <c r="B27" t="n">
-        <v>78542</v>
+        <v>79160</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3241,21 +3241,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3265,10 +3265,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>478057</v>
+        <v>478250</v>
       </c>
       <c r="R27" t="n">
-        <v>6827749</v>
+        <v>6827802</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3327,10 +3327,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>120075062</v>
+        <v>120075224</v>
       </c>
       <c r="B28" t="n">
-        <v>78542</v>
+        <v>78187</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3343,21 +3343,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6425</v>
+        <v>353</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3367,10 +3367,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>478221</v>
+        <v>478081</v>
       </c>
       <c r="R28" t="n">
-        <v>6827719</v>
+        <v>6827789</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3429,10 +3429,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>120074943</v>
+        <v>120075092</v>
       </c>
       <c r="B29" t="n">
-        <v>79160</v>
+        <v>78542</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3445,21 +3445,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3469,10 +3469,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>478073</v>
+        <v>478167</v>
       </c>
       <c r="R29" t="n">
-        <v>6827827</v>
+        <v>6827561</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3531,10 +3531,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>120075001</v>
+        <v>120075069</v>
       </c>
       <c r="B30" t="n">
-        <v>78279</v>
+        <v>78542</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3547,21 +3547,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3571,10 +3571,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>478125</v>
+        <v>478157</v>
       </c>
       <c r="R30" t="n">
-        <v>6827604</v>
+        <v>6827611</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3633,10 +3633,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>120074929</v>
+        <v>120074945</v>
       </c>
       <c r="B31" t="n">
-        <v>78576</v>
+        <v>79160</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3649,21 +3649,21 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>185</v>
+        <v>6453</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3673,10 +3673,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>478045</v>
+        <v>478061</v>
       </c>
       <c r="R31" t="n">
-        <v>6827724</v>
+        <v>6827770</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3735,10 +3735,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>120074914</v>
+        <v>120075090</v>
       </c>
       <c r="B32" t="n">
-        <v>78576</v>
+        <v>78542</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -3751,21 +3751,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3775,10 +3775,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>478169</v>
+        <v>478161</v>
       </c>
       <c r="R32" t="n">
-        <v>6827680</v>
+        <v>6827528</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3837,10 +3837,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>120075204</v>
+        <v>120075046</v>
       </c>
       <c r="B33" t="n">
-        <v>78187</v>
+        <v>78278</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -3853,21 +3853,21 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>353</v>
+        <v>6446</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -3877,10 +3877,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>478115</v>
+        <v>478285</v>
       </c>
       <c r="R33" t="n">
-        <v>6827614</v>
+        <v>6827770</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -3939,10 +3939,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>120075214</v>
+        <v>120075073</v>
       </c>
       <c r="B34" t="n">
-        <v>78187</v>
+        <v>78542</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -3955,21 +3955,21 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>353</v>
+        <v>6425</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -3979,10 +3979,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>478266</v>
+        <v>478116</v>
       </c>
       <c r="R34" t="n">
-        <v>6827724</v>
+        <v>6827617</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4041,10 +4041,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>120075206</v>
+        <v>120075133</v>
       </c>
       <c r="B35" t="n">
-        <v>78187</v>
+        <v>78542</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4057,21 +4057,21 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>353</v>
+        <v>6425</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4081,10 +4081,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>478125</v>
+        <v>478258</v>
       </c>
       <c r="R35" t="n">
-        <v>6827604</v>
+        <v>6827753</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4143,10 +4143,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>120074956</v>
+        <v>120075176</v>
       </c>
       <c r="B36" t="n">
-        <v>57320</v>
+        <v>78542</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4159,39 +4159,34 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
-      <c r="M36" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P36" t="inlineStr">
         <is>
           <t>Hevoslamm, Dlr</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>478278</v>
+        <v>478066</v>
       </c>
       <c r="R36" t="n">
-        <v>6827832</v>
+        <v>6827732</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4224,11 +4219,6 @@
       <c r="AA36" t="inlineStr">
         <is>
           <t>2024-09-27</t>
-        </is>
-      </c>
-      <c r="AC36" t="inlineStr">
-        <is>
-          <t>Färska ringhack (tall)</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4255,10 +4245,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>120075215</v>
+        <v>120075139</v>
       </c>
       <c r="B37" t="n">
-        <v>78187</v>
+        <v>78542</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4271,21 +4261,21 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>353</v>
+        <v>6425</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4295,10 +4285,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>478239</v>
+        <v>478294</v>
       </c>
       <c r="R37" t="n">
-        <v>6827752</v>
+        <v>6827803</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4357,10 +4347,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>120075120</v>
+        <v>120074952</v>
       </c>
       <c r="B38" t="n">
-        <v>78542</v>
+        <v>79131</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4373,21 +4363,21 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6425</v>
+        <v>229821</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4397,10 +4387,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>478223</v>
+        <v>478120</v>
       </c>
       <c r="R38" t="n">
-        <v>6827657</v>
+        <v>6827605</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4459,10 +4449,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>120075015</v>
+        <v>120075166</v>
       </c>
       <c r="B39" t="n">
-        <v>79623</v>
+        <v>78542</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4475,21 +4465,21 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4499,10 +4489,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>478114</v>
+        <v>478092</v>
       </c>
       <c r="R39" t="n">
-        <v>6827633</v>
+        <v>6827839</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4561,7 +4551,7 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>120075202</v>
+        <v>120075223</v>
       </c>
       <c r="B40" t="n">
         <v>78187</v>
@@ -4601,10 +4591,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>478218</v>
+        <v>478076</v>
       </c>
       <c r="R40" t="n">
-        <v>6827721</v>
+        <v>6827777</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4663,10 +4653,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>120075003</v>
+        <v>120074948</v>
       </c>
       <c r="B41" t="n">
-        <v>78279</v>
+        <v>79160</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -4679,21 +4669,21 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>228912</v>
+        <v>6453</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4703,10 +4693,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>478137</v>
+        <v>478070</v>
       </c>
       <c r="R41" t="n">
-        <v>6827553</v>
+        <v>6827723</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4765,10 +4755,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>120075143</v>
+        <v>120074885</v>
       </c>
       <c r="B42" t="n">
-        <v>78542</v>
+        <v>79160</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -4781,21 +4771,21 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -4805,10 +4795,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>478301</v>
+        <v>478115</v>
       </c>
       <c r="R42" t="n">
-        <v>6827814</v>
+        <v>6827614</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4867,10 +4857,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>120074939</v>
+        <v>120075171</v>
       </c>
       <c r="B43" t="n">
-        <v>79160</v>
+        <v>78542</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -4883,21 +4873,21 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -4907,10 +4897,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>478091</v>
+        <v>478073</v>
       </c>
       <c r="R43" t="n">
-        <v>6827838</v>
+        <v>6827831</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -4969,7 +4959,7 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>120075157</v>
+        <v>120075175</v>
       </c>
       <c r="B44" t="n">
         <v>78542</v>
@@ -5009,10 +4999,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>478103</v>
+        <v>478059</v>
       </c>
       <c r="R44" t="n">
-        <v>6827718</v>
+        <v>6827739</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5071,10 +5061,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>120074886</v>
+        <v>120074956</v>
       </c>
       <c r="B45" t="n">
-        <v>79160</v>
+        <v>57320</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5087,34 +5077,39 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>6453</v>
+        <v>100109</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
+      <c r="M45" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P45" t="inlineStr">
         <is>
           <t>Hevoslamm, Dlr</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>478125</v>
+        <v>478278</v>
       </c>
       <c r="R45" t="n">
-        <v>6827604</v>
+        <v>6827832</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5147,6 +5142,11 @@
       <c r="AA45" t="inlineStr">
         <is>
           <t>2024-09-27</t>
+        </is>
+      </c>
+      <c r="AC45" t="inlineStr">
+        <is>
+          <t>Färska ringhack (tall)</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5173,10 +5173,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>120074881</v>
+        <v>120075201</v>
       </c>
       <c r="B46" t="n">
-        <v>79160</v>
+        <v>78187</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -5189,21 +5189,21 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>6453</v>
+        <v>353</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5213,7 +5213,7 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>478184</v>
+        <v>478182</v>
       </c>
       <c r="R46" t="n">
         <v>6827728</v>
@@ -5275,7 +5275,7 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>120074941</v>
+        <v>120074907</v>
       </c>
       <c r="B47" t="n">
         <v>79160</v>
@@ -5315,10 +5315,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>478069</v>
+        <v>478263</v>
       </c>
       <c r="R47" t="n">
-        <v>6827854</v>
+        <v>6827838</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5377,10 +5377,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>120075234</v>
+        <v>120075081</v>
       </c>
       <c r="B48" t="n">
-        <v>78187</v>
+        <v>78542</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -5393,21 +5393,21 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>353</v>
+        <v>6425</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5417,10 +5417,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>478069</v>
+        <v>478096</v>
       </c>
       <c r="R48" t="n">
-        <v>6827741</v>
+        <v>6827550</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5479,7 +5479,7 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>120075165</v>
+        <v>120075095</v>
       </c>
       <c r="B49" t="n">
         <v>78542</v>
@@ -5519,10 +5519,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>478078</v>
+        <v>478219</v>
       </c>
       <c r="R49" t="n">
-        <v>6827834</v>
+        <v>6827572</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5581,7 +5581,7 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>120075142</v>
+        <v>120075065</v>
       </c>
       <c r="B50" t="n">
         <v>78542</v>
@@ -5621,10 +5621,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>478313</v>
+        <v>478169</v>
       </c>
       <c r="R50" t="n">
-        <v>6827798</v>
+        <v>6827679</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5683,7 +5683,7 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>120075146</v>
+        <v>120075172</v>
       </c>
       <c r="B51" t="n">
         <v>78542</v>
@@ -5723,10 +5723,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>478154</v>
+        <v>478055</v>
       </c>
       <c r="R51" t="n">
-        <v>6827747</v>
+        <v>6827768</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5785,10 +5785,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>120075039</v>
+        <v>120075137</v>
       </c>
       <c r="B52" t="n">
-        <v>78278</v>
+        <v>78542</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -5801,21 +5801,21 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -5825,10 +5825,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>478238</v>
+        <v>478288</v>
       </c>
       <c r="R52" t="n">
-        <v>6827752</v>
+        <v>6827763</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -5887,10 +5887,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>120075040</v>
+        <v>120074931</v>
       </c>
       <c r="B53" t="n">
-        <v>78278</v>
+        <v>79160</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -5903,21 +5903,21 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>6446</v>
+        <v>6453</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -5927,10 +5927,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>478250</v>
+        <v>478261</v>
       </c>
       <c r="R53" t="n">
-        <v>6827802</v>
+        <v>6827822</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -5989,10 +5989,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>120075082</v>
+        <v>120074998</v>
       </c>
       <c r="B54" t="n">
-        <v>78542</v>
+        <v>78279</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
@@ -6005,21 +6005,21 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -6029,10 +6029,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>478097</v>
+        <v>478172</v>
       </c>
       <c r="R54" t="n">
-        <v>6827544</v>
+        <v>6827640</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6091,10 +6091,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>120074906</v>
+        <v>120074999</v>
       </c>
       <c r="B55" t="n">
-        <v>79160</v>
+        <v>78279</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
@@ -6107,21 +6107,21 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>6453</v>
+        <v>228912</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -6131,10 +6131,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>478294</v>
+        <v>478161</v>
       </c>
       <c r="R55" t="n">
-        <v>6827790</v>
+        <v>6827592</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6193,10 +6193,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>120074952</v>
+        <v>120075164</v>
       </c>
       <c r="B56" t="n">
-        <v>79131</v>
+        <v>78542</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
@@ -6209,21 +6209,21 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>229821</v>
+        <v>6425</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -6233,10 +6233,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>478120</v>
+        <v>478092</v>
       </c>
       <c r="R56" t="n">
-        <v>6827605</v>
+        <v>6827810</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6295,10 +6295,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>120075225</v>
+        <v>120075037</v>
       </c>
       <c r="B57" t="n">
-        <v>78187</v>
+        <v>78278</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
@@ -6311,21 +6311,21 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>353</v>
+        <v>6446</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -6335,10 +6335,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>478075</v>
+        <v>478265</v>
       </c>
       <c r="R57" t="n">
-        <v>6827798</v>
+        <v>6827716</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6397,10 +6397,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>120075207</v>
+        <v>120074887</v>
       </c>
       <c r="B58" t="n">
-        <v>78187</v>
+        <v>79160</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
@@ -6413,21 +6413,21 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>353</v>
+        <v>6453</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
@@ -6437,10 +6437,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>478157</v>
+        <v>478144</v>
       </c>
       <c r="R58" t="n">
-        <v>6827509</v>
+        <v>6827593</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6499,10 +6499,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>120075133</v>
+        <v>120075024</v>
       </c>
       <c r="B59" t="n">
-        <v>78542</v>
+        <v>78278</v>
       </c>
       <c r="C59" t="inlineStr">
         <is>
@@ -6515,21 +6515,21 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
@@ -6539,10 +6539,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>478258</v>
+        <v>478165</v>
       </c>
       <c r="R59" t="n">
-        <v>6827753</v>
+        <v>6827712</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6601,10 +6601,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>120075168</v>
+        <v>120074947</v>
       </c>
       <c r="B60" t="n">
-        <v>78542</v>
+        <v>79160</v>
       </c>
       <c r="C60" t="inlineStr">
         <is>
@@ -6617,21 +6617,21 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
@@ -6641,10 +6641,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>478086</v>
+        <v>478061</v>
       </c>
       <c r="R60" t="n">
-        <v>6827868</v>
+        <v>6827751</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -6703,10 +6703,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>120075067</v>
+        <v>120075026</v>
       </c>
       <c r="B61" t="n">
-        <v>78542</v>
+        <v>78278</v>
       </c>
       <c r="C61" t="inlineStr">
         <is>
@@ -6719,21 +6719,21 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
@@ -6743,10 +6743,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>478164</v>
+        <v>478161</v>
       </c>
       <c r="R61" t="n">
-        <v>6827661</v>
+        <v>6827592</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -6805,7 +6805,7 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>120075086</v>
+        <v>120075162</v>
       </c>
       <c r="B62" t="n">
         <v>78542</v>
@@ -6845,10 +6845,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>478104</v>
+        <v>478080</v>
       </c>
       <c r="R62" t="n">
-        <v>6827495</v>
+        <v>6827808</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -6907,10 +6907,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>120075226</v>
+        <v>120075163</v>
       </c>
       <c r="B63" t="n">
-        <v>78187</v>
+        <v>78542</v>
       </c>
       <c r="C63" t="inlineStr">
         <is>
@@ -6923,21 +6923,21 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>353</v>
+        <v>6425</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
@@ -6947,10 +6947,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>478098</v>
+        <v>478102</v>
       </c>
       <c r="R63" t="n">
-        <v>6827815</v>
+        <v>6827800</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -7009,10 +7009,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>120075217</v>
+        <v>120075000</v>
       </c>
       <c r="B64" t="n">
-        <v>78187</v>
+        <v>78279</v>
       </c>
       <c r="C64" t="inlineStr">
         <is>
@@ -7025,21 +7025,21 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>353</v>
+        <v>228912</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
@@ -7049,10 +7049,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>478264</v>
+        <v>478121</v>
       </c>
       <c r="R64" t="n">
-        <v>6827839</v>
+        <v>6827607</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -7111,10 +7111,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>120074986</v>
+        <v>120075007</v>
       </c>
       <c r="B65" t="n">
-        <v>79624</v>
+        <v>78279</v>
       </c>
       <c r="C65" t="inlineStr">
         <is>
@@ -7127,21 +7127,21 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>2081</v>
+        <v>228912</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
@@ -7151,10 +7151,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>478096</v>
+        <v>478285</v>
       </c>
       <c r="R65" t="n">
-        <v>6827549</v>
+        <v>6827770</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7213,10 +7213,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>120075192</v>
+        <v>120075206</v>
       </c>
       <c r="B66" t="n">
-        <v>78542</v>
+        <v>78187</v>
       </c>
       <c r="C66" t="inlineStr">
         <is>
@@ -7229,21 +7229,21 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>6425</v>
+        <v>353</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
@@ -7253,10 +7253,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>478282</v>
+        <v>478125</v>
       </c>
       <c r="R66" t="n">
-        <v>6827683</v>
+        <v>6827604</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7315,10 +7315,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>120074904</v>
+        <v>120075066</v>
       </c>
       <c r="B67" t="n">
-        <v>79160</v>
+        <v>78542</v>
       </c>
       <c r="C67" t="inlineStr">
         <is>
@@ -7331,21 +7331,21 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
@@ -7355,10 +7355,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>478262</v>
+        <v>478160</v>
       </c>
       <c r="R67" t="n">
-        <v>6827730</v>
+        <v>6827680</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7417,7 +7417,7 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>120075084</v>
+        <v>120075138</v>
       </c>
       <c r="B68" t="n">
         <v>78542</v>
@@ -7457,10 +7457,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>478098</v>
+        <v>478294</v>
       </c>
       <c r="R68" t="n">
-        <v>6827520</v>
+        <v>6827781</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7519,10 +7519,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>120075037</v>
+        <v>120075134</v>
       </c>
       <c r="B69" t="n">
-        <v>78278</v>
+        <v>78542</v>
       </c>
       <c r="C69" t="inlineStr">
         <is>
@@ -7535,21 +7535,21 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
@@ -7559,10 +7559,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>478265</v>
+        <v>478266</v>
       </c>
       <c r="R69" t="n">
-        <v>6827716</v>
+        <v>6827765</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -7621,10 +7621,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>120075012</v>
+        <v>120074904</v>
       </c>
       <c r="B70" t="n">
-        <v>78279</v>
+        <v>79160</v>
       </c>
       <c r="C70" t="inlineStr">
         <is>
@@ -7637,21 +7637,21 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>228912</v>
+        <v>6453</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
@@ -7661,10 +7661,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>478055</v>
+        <v>478262</v>
       </c>
       <c r="R70" t="n">
-        <v>6827786</v>
+        <v>6827730</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -7723,10 +7723,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>120075013</v>
+        <v>120074927</v>
       </c>
       <c r="B71" t="n">
-        <v>78279</v>
+        <v>78576</v>
       </c>
       <c r="C71" t="inlineStr">
         <is>
@@ -7739,21 +7739,21 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>228912</v>
+        <v>185</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
@@ -7763,10 +7763,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>478239</v>
+        <v>478073</v>
       </c>
       <c r="R71" t="n">
-        <v>6827752</v>
+        <v>6827836</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -7825,7 +7825,7 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>120075216</v>
+        <v>120075231</v>
       </c>
       <c r="B72" t="n">
         <v>78187</v>
@@ -7865,10 +7865,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>478294</v>
+        <v>478067</v>
       </c>
       <c r="R72" t="n">
-        <v>6827790</v>
+        <v>6827863</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -7927,7 +7927,7 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>120075069</v>
+        <v>120075168</v>
       </c>
       <c r="B73" t="n">
         <v>78542</v>
@@ -7967,10 +7967,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>478157</v>
+        <v>478086</v>
       </c>
       <c r="R73" t="n">
-        <v>6827611</v>
+        <v>6827868</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -8029,10 +8029,10 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>120074891</v>
+        <v>120075048</v>
       </c>
       <c r="B74" t="n">
-        <v>79160</v>
+        <v>56524</v>
       </c>
       <c r="C74" t="inlineStr">
         <is>
@@ -8045,34 +8045,39 @@
         </is>
       </c>
       <c r="E74" t="n">
-        <v>6453</v>
+        <v>102612</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
+      <c r="M74" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="P74" t="inlineStr">
         <is>
           <t>Hevoslamm, Dlr</t>
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>478212</v>
+        <v>478070</v>
       </c>
       <c r="R74" t="n">
-        <v>6827573</v>
+        <v>6827723</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -8131,7 +8136,7 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>120075092</v>
+        <v>120075130</v>
       </c>
       <c r="B75" t="n">
         <v>78542</v>
@@ -8171,10 +8176,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>478167</v>
+        <v>478264</v>
       </c>
       <c r="R75" t="n">
-        <v>6827561</v>
+        <v>6827733</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -8233,10 +8238,10 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>120075172</v>
+        <v>120075236</v>
       </c>
       <c r="B76" t="n">
-        <v>78542</v>
+        <v>78187</v>
       </c>
       <c r="C76" t="inlineStr">
         <is>
@@ -8249,21 +8254,21 @@
         </is>
       </c>
       <c r="E76" t="n">
-        <v>6425</v>
+        <v>353</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
@@ -8273,10 +8278,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>478055</v>
+        <v>478062</v>
       </c>
       <c r="R76" t="n">
-        <v>6827768</v>
+        <v>6827740</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -8335,10 +8340,10 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>120075047</v>
+        <v>120074917</v>
       </c>
       <c r="B77" t="n">
-        <v>78278</v>
+        <v>78576</v>
       </c>
       <c r="C77" t="inlineStr">
         <is>
@@ -8351,21 +8356,21 @@
         </is>
       </c>
       <c r="E77" t="n">
-        <v>6446</v>
+        <v>185</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
@@ -8375,10 +8380,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>478212</v>
+        <v>478095</v>
       </c>
       <c r="R77" t="n">
-        <v>6827573</v>
+        <v>6827533</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -8437,10 +8442,10 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>120075197</v>
+        <v>120075217</v>
       </c>
       <c r="B78" t="n">
-        <v>91858</v>
+        <v>78187</v>
       </c>
       <c r="C78" t="inlineStr">
         <is>
@@ -8449,47 +8454,38 @@
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E78" t="n">
-        <v>4364</v>
+        <v>353</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I78" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J78" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(Hoffm.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I78" t="inlineStr"/>
       <c r="P78" t="inlineStr">
         <is>
           <t>Hevoslamm, Dlr</t>
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>478077</v>
+        <v>478264</v>
       </c>
       <c r="R78" t="n">
-        <v>6827805</v>
+        <v>6827839</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -8548,7 +8544,7 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>120075131</v>
+        <v>120075074</v>
       </c>
       <c r="B79" t="n">
         <v>78542</v>
@@ -8588,10 +8584,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>478258</v>
+        <v>478138</v>
       </c>
       <c r="R79" t="n">
-        <v>6827731</v>
+        <v>6827599</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -8650,10 +8646,10 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>120075097</v>
+        <v>120074938</v>
       </c>
       <c r="B80" t="n">
-        <v>78542</v>
+        <v>79160</v>
       </c>
       <c r="C80" t="inlineStr">
         <is>
@@ -8666,21 +8662,21 @@
         </is>
       </c>
       <c r="E80" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
@@ -8690,10 +8686,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>478248</v>
+        <v>478097</v>
       </c>
       <c r="R80" t="n">
-        <v>6827593</v>
+        <v>6827756</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -8752,10 +8748,10 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>120075068</v>
+        <v>120074943</v>
       </c>
       <c r="B81" t="n">
-        <v>78542</v>
+        <v>79160</v>
       </c>
       <c r="C81" t="inlineStr">
         <is>
@@ -8768,21 +8764,21 @@
         </is>
       </c>
       <c r="E81" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
@@ -8792,10 +8788,10 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>478174</v>
+        <v>478073</v>
       </c>
       <c r="R81" t="n">
-        <v>6827656</v>
+        <v>6827827</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -8854,7 +8850,7 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>120075066</v>
+        <v>120075192</v>
       </c>
       <c r="B82" t="n">
         <v>78542</v>
@@ -8894,10 +8890,10 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>478160</v>
+        <v>478282</v>
       </c>
       <c r="R82" t="n">
-        <v>6827680</v>
+        <v>6827683</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -8956,7 +8952,7 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>120075135</v>
+        <v>120075070</v>
       </c>
       <c r="B83" t="n">
         <v>78542</v>
@@ -8996,10 +8992,10 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>478291</v>
+        <v>478135</v>
       </c>
       <c r="R83" t="n">
-        <v>6827744</v>
+        <v>6827625</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -9058,7 +9054,7 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>120075177</v>
+        <v>120075145</v>
       </c>
       <c r="B84" t="n">
         <v>78542</v>
@@ -9098,10 +9094,10 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>478075</v>
+        <v>478226</v>
       </c>
       <c r="R84" t="n">
-        <v>6827717</v>
+        <v>6827777</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -9160,10 +9156,10 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>120074917</v>
+        <v>120075067</v>
       </c>
       <c r="B85" t="n">
-        <v>78576</v>
+        <v>78542</v>
       </c>
       <c r="C85" t="inlineStr">
         <is>
@@ -9176,21 +9172,21 @@
         </is>
       </c>
       <c r="E85" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
@@ -9200,10 +9196,10 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>478095</v>
+        <v>478164</v>
       </c>
       <c r="R85" t="n">
-        <v>6827533</v>
+        <v>6827661</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -9262,10 +9258,10 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>120075224</v>
+        <v>120074997</v>
       </c>
       <c r="B86" t="n">
-        <v>78187</v>
+        <v>78279</v>
       </c>
       <c r="C86" t="inlineStr">
         <is>
@@ -9278,21 +9274,21 @@
         </is>
       </c>
       <c r="E86" t="n">
-        <v>353</v>
+        <v>228912</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I86" t="inlineStr"/>
@@ -9302,10 +9298,10 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>478081</v>
+        <v>478218</v>
       </c>
       <c r="R86" t="n">
-        <v>6827789</v>
+        <v>6827733</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>
@@ -9364,7 +9360,7 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>120075201</v>
+        <v>120075203</v>
       </c>
       <c r="B87" t="n">
         <v>78187</v>
@@ -9404,10 +9400,10 @@
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>478182</v>
+        <v>478125</v>
       </c>
       <c r="R87" t="n">
-        <v>6827728</v>
+        <v>6827631</v>
       </c>
       <c r="S87" t="n">
         <v>10</v>
@@ -9466,7 +9462,7 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>120075081</v>
+        <v>120075060</v>
       </c>
       <c r="B88" t="n">
         <v>78542</v>
@@ -9506,10 +9502,10 @@
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>478096</v>
+        <v>478087</v>
       </c>
       <c r="R88" t="n">
-        <v>6827550</v>
+        <v>6827718</v>
       </c>
       <c r="S88" t="n">
         <v>10</v>
@@ -9568,10 +9564,10 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>120075046</v>
+        <v>120074888</v>
       </c>
       <c r="B89" t="n">
-        <v>78278</v>
+        <v>79160</v>
       </c>
       <c r="C89" t="inlineStr">
         <is>
@@ -9584,21 +9580,21 @@
         </is>
       </c>
       <c r="E89" t="n">
-        <v>6446</v>
+        <v>6453</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I89" t="inlineStr"/>
@@ -9608,10 +9604,10 @@
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>478285</v>
+        <v>478139</v>
       </c>
       <c r="R89" t="n">
-        <v>6827770</v>
+        <v>6827554</v>
       </c>
       <c r="S89" t="n">
         <v>10</v>
@@ -9670,7 +9666,7 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>120075095</v>
+        <v>120075089</v>
       </c>
       <c r="B90" t="n">
         <v>78542</v>
@@ -9710,10 +9706,10 @@
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>478219</v>
+        <v>478153</v>
       </c>
       <c r="R90" t="n">
-        <v>6827572</v>
+        <v>6827517</v>
       </c>
       <c r="S90" t="n">
         <v>10</v>
@@ -9772,10 +9768,10 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>120075035</v>
+        <v>120075143</v>
       </c>
       <c r="B91" t="n">
-        <v>78278</v>
+        <v>78542</v>
       </c>
       <c r="C91" t="inlineStr">
         <is>
@@ -9788,21 +9784,21 @@
         </is>
       </c>
       <c r="E91" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I91" t="inlineStr"/>
@@ -9812,10 +9808,10 @@
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>478273</v>
+        <v>478301</v>
       </c>
       <c r="R91" t="n">
-        <v>6827711</v>
+        <v>6827814</v>
       </c>
       <c r="S91" t="n">
         <v>10</v>
@@ -9874,10 +9870,10 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>120074892</v>
+        <v>120075012</v>
       </c>
       <c r="B92" t="n">
-        <v>79160</v>
+        <v>78279</v>
       </c>
       <c r="C92" t="inlineStr">
         <is>
@@ -9890,21 +9886,21 @@
         </is>
       </c>
       <c r="E92" t="n">
-        <v>6453</v>
+        <v>228912</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I92" t="inlineStr"/>
@@ -9914,10 +9910,10 @@
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>478243</v>
+        <v>478055</v>
       </c>
       <c r="R92" t="n">
-        <v>6827585</v>
+        <v>6827786</v>
       </c>
       <c r="S92" t="n">
         <v>10</v>
@@ -9976,10 +9972,10 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>120075045</v>
+        <v>120075011</v>
       </c>
       <c r="B93" t="n">
-        <v>78278</v>
+        <v>78279</v>
       </c>
       <c r="C93" t="inlineStr">
         <is>
@@ -9992,21 +9988,21 @@
         </is>
       </c>
       <c r="E93" t="n">
-        <v>6446</v>
+        <v>228912</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I93" t="inlineStr"/>
@@ -10016,10 +10012,10 @@
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>478070</v>
+        <v>478103</v>
       </c>
       <c r="R93" t="n">
-        <v>6827723</v>
+        <v>6827803</v>
       </c>
       <c r="S93" t="n">
         <v>10</v>
@@ -10078,7 +10074,7 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>120075087</v>
+        <v>120075144</v>
       </c>
       <c r="B94" t="n">
         <v>78542</v>
@@ -10118,10 +10114,10 @@
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>478145</v>
+        <v>478261</v>
       </c>
       <c r="R94" t="n">
-        <v>6827485</v>
+        <v>6827822</v>
       </c>
       <c r="S94" t="n">
         <v>10</v>
@@ -10180,10 +10176,10 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>120075028</v>
+        <v>120075019</v>
       </c>
       <c r="B95" t="n">
-        <v>78278</v>
+        <v>79623</v>
       </c>
       <c r="C95" t="inlineStr">
         <is>
@@ -10196,21 +10192,21 @@
         </is>
       </c>
       <c r="E95" t="n">
-        <v>6446</v>
+        <v>6458</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I95" t="inlineStr"/>
@@ -10220,10 +10216,10 @@
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>478137</v>
+        <v>478227</v>
       </c>
       <c r="R95" t="n">
-        <v>6827553</v>
+        <v>6827655</v>
       </c>
       <c r="S95" t="n">
         <v>10</v>
@@ -10282,7 +10278,7 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>120075138</v>
+        <v>120075083</v>
       </c>
       <c r="B96" t="n">
         <v>78542</v>
@@ -10322,10 +10318,10 @@
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>478294</v>
+        <v>478097</v>
       </c>
       <c r="R96" t="n">
-        <v>6827781</v>
+        <v>6827527</v>
       </c>
       <c r="S96" t="n">
         <v>10</v>
@@ -10384,7 +10380,7 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>120075129</v>
+        <v>120075087</v>
       </c>
       <c r="B97" t="n">
         <v>78542</v>
@@ -10424,10 +10420,10 @@
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>478265</v>
+        <v>478145</v>
       </c>
       <c r="R97" t="n">
-        <v>6827707</v>
+        <v>6827485</v>
       </c>
       <c r="S97" t="n">
         <v>10</v>
@@ -10486,10 +10482,10 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>120074942</v>
+        <v>120074929</v>
       </c>
       <c r="B98" t="n">
-        <v>79160</v>
+        <v>78576</v>
       </c>
       <c r="C98" t="inlineStr">
         <is>
@@ -10502,21 +10498,21 @@
         </is>
       </c>
       <c r="E98" t="n">
-        <v>6453</v>
+        <v>185</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I98" t="inlineStr"/>
@@ -10526,10 +10522,10 @@
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>478065</v>
+        <v>478045</v>
       </c>
       <c r="R98" t="n">
-        <v>6827842</v>
+        <v>6827724</v>
       </c>
       <c r="S98" t="n">
         <v>10</v>
@@ -10588,10 +10584,10 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>120075000</v>
+        <v>120075208</v>
       </c>
       <c r="B99" t="n">
-        <v>78279</v>
+        <v>78187</v>
       </c>
       <c r="C99" t="inlineStr">
         <is>
@@ -10604,21 +10600,21 @@
         </is>
       </c>
       <c r="E99" t="n">
-        <v>228912</v>
+        <v>353</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I99" t="inlineStr"/>
@@ -10628,10 +10624,10 @@
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>478121</v>
+        <v>478158</v>
       </c>
       <c r="R99" t="n">
-        <v>6827607</v>
+        <v>6827519</v>
       </c>
       <c r="S99" t="n">
         <v>10</v>
@@ -10690,10 +10686,10 @@
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>120074922</v>
+        <v>120075196</v>
       </c>
       <c r="B100" t="n">
-        <v>78576</v>
+        <v>78542</v>
       </c>
       <c r="C100" t="inlineStr">
         <is>
@@ -10706,21 +10702,21 @@
         </is>
       </c>
       <c r="E100" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I100" t="inlineStr"/>
@@ -10730,10 +10726,10 @@
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>478103</v>
+        <v>478288</v>
       </c>
       <c r="R100" t="n">
-        <v>6827718</v>
+        <v>6827682</v>
       </c>
       <c r="S100" t="n">
         <v>10</v>
@@ -10792,10 +10788,10 @@
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>120075208</v>
+        <v>120074946</v>
       </c>
       <c r="B101" t="n">
-        <v>78187</v>
+        <v>79160</v>
       </c>
       <c r="C101" t="inlineStr">
         <is>
@@ -10808,21 +10804,21 @@
         </is>
       </c>
       <c r="E101" t="n">
-        <v>353</v>
+        <v>6453</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I101" t="inlineStr"/>
@@ -10832,10 +10828,10 @@
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>478158</v>
+        <v>478056</v>
       </c>
       <c r="R101" t="n">
-        <v>6827519</v>
+        <v>6827754</v>
       </c>
       <c r="S101" t="n">
         <v>10</v>
@@ -10894,10 +10890,10 @@
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>120074947</v>
+        <v>120074996</v>
       </c>
       <c r="B102" t="n">
-        <v>79160</v>
+        <v>78279</v>
       </c>
       <c r="C102" t="inlineStr">
         <is>
@@ -10910,21 +10906,21 @@
         </is>
       </c>
       <c r="E102" t="n">
-        <v>6453</v>
+        <v>228912</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I102" t="inlineStr"/>
@@ -10934,10 +10930,10 @@
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>478061</v>
+        <v>478165</v>
       </c>
       <c r="R102" t="n">
-        <v>6827751</v>
+        <v>6827712</v>
       </c>
       <c r="S102" t="n">
         <v>10</v>
@@ -10996,7 +10992,7 @@
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>120075094</v>
+        <v>120075084</v>
       </c>
       <c r="B103" t="n">
         <v>78542</v>
@@ -11036,10 +11032,10 @@
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>478205</v>
+        <v>478098</v>
       </c>
       <c r="R103" t="n">
-        <v>6827556</v>
+        <v>6827520</v>
       </c>
       <c r="S103" t="n">
         <v>10</v>
@@ -11098,10 +11094,10 @@
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>120075088</v>
+        <v>120074883</v>
       </c>
       <c r="B104" t="n">
-        <v>78542</v>
+        <v>79160</v>
       </c>
       <c r="C104" t="inlineStr">
         <is>
@@ -11114,21 +11110,21 @@
         </is>
       </c>
       <c r="E104" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I104" t="inlineStr"/>
@@ -11138,10 +11134,10 @@
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>478151</v>
+        <v>478142</v>
       </c>
       <c r="R104" t="n">
-        <v>6827509</v>
+        <v>6827623</v>
       </c>
       <c r="S104" t="n">
         <v>10</v>
@@ -11200,10 +11196,10 @@
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>120075027</v>
+        <v>120074912</v>
       </c>
       <c r="B105" t="n">
-        <v>78278</v>
+        <v>78576</v>
       </c>
       <c r="C105" t="inlineStr">
         <is>
@@ -11216,21 +11212,21 @@
         </is>
       </c>
       <c r="E105" t="n">
-        <v>6446</v>
+        <v>185</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I105" t="inlineStr"/>
@@ -11240,10 +11236,10 @@
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>478144</v>
+        <v>478149</v>
       </c>
       <c r="R105" t="n">
-        <v>6827593</v>
+        <v>6827714</v>
       </c>
       <c r="S105" t="n">
         <v>10</v>
@@ -11302,10 +11298,10 @@
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>120075161</v>
+        <v>120075054</v>
       </c>
       <c r="B106" t="n">
-        <v>78542</v>
+        <v>90598</v>
       </c>
       <c r="C106" t="inlineStr">
         <is>
@@ -11318,21 +11314,21 @@
         </is>
       </c>
       <c r="E106" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I106" t="inlineStr"/>
@@ -11342,10 +11338,10 @@
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>478082</v>
+        <v>478126</v>
       </c>
       <c r="R106" t="n">
-        <v>6827766</v>
+        <v>6827477</v>
       </c>
       <c r="S106" t="n">
         <v>10</v>
@@ -11404,10 +11400,10 @@
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>120074932</v>
+        <v>120075086</v>
       </c>
       <c r="B107" t="n">
-        <v>79160</v>
+        <v>78542</v>
       </c>
       <c r="C107" t="inlineStr">
         <is>
@@ -11420,21 +11416,21 @@
         </is>
       </c>
       <c r="E107" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I107" t="inlineStr"/>
@@ -11444,10 +11440,10 @@
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>478250</v>
+        <v>478104</v>
       </c>
       <c r="R107" t="n">
-        <v>6827802</v>
+        <v>6827495</v>
       </c>
       <c r="S107" t="n">
         <v>10</v>
@@ -11506,10 +11502,10 @@
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>120075236</v>
+        <v>120075028</v>
       </c>
       <c r="B108" t="n">
-        <v>78187</v>
+        <v>78278</v>
       </c>
       <c r="C108" t="inlineStr">
         <is>
@@ -11522,21 +11518,21 @@
         </is>
       </c>
       <c r="E108" t="n">
-        <v>353</v>
+        <v>6446</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I108" t="inlineStr"/>
@@ -11546,10 +11542,10 @@
         </is>
       </c>
       <c r="Q108" t="n">
-        <v>478062</v>
+        <v>478137</v>
       </c>
       <c r="R108" t="n">
-        <v>6827740</v>
+        <v>6827553</v>
       </c>
       <c r="S108" t="n">
         <v>10</v>
@@ -11608,10 +11604,10 @@
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>120074912</v>
+        <v>120075173</v>
       </c>
       <c r="B109" t="n">
-        <v>78576</v>
+        <v>78542</v>
       </c>
       <c r="C109" t="inlineStr">
         <is>
@@ -11624,21 +11620,21 @@
         </is>
       </c>
       <c r="E109" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I109" t="inlineStr"/>
@@ -11648,10 +11644,10 @@
         </is>
       </c>
       <c r="Q109" t="n">
-        <v>478149</v>
+        <v>478052</v>
       </c>
       <c r="R109" t="n">
-        <v>6827714</v>
+        <v>6827754</v>
       </c>
       <c r="S109" t="n">
         <v>10</v>
@@ -11710,10 +11706,10 @@
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>120075042</v>
+        <v>120075242</v>
       </c>
       <c r="B110" t="n">
-        <v>78278</v>
+        <v>77926</v>
       </c>
       <c r="C110" t="inlineStr">
         <is>
@@ -11726,21 +11722,21 @@
         </is>
       </c>
       <c r="E110" t="n">
-        <v>6446</v>
+        <v>6437</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I110" t="inlineStr"/>
@@ -11750,10 +11746,10 @@
         </is>
       </c>
       <c r="Q110" t="n">
-        <v>478074</v>
+        <v>478136</v>
       </c>
       <c r="R110" t="n">
-        <v>6827775</v>
+        <v>6827556</v>
       </c>
       <c r="S110" t="n">
         <v>10</v>
@@ -11812,7 +11808,7 @@
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>120075136</v>
+        <v>120075094</v>
       </c>
       <c r="B111" t="n">
         <v>78542</v>
@@ -11852,10 +11848,10 @@
         </is>
       </c>
       <c r="Q111" t="n">
-        <v>478290</v>
+        <v>478205</v>
       </c>
       <c r="R111" t="n">
-        <v>6827758</v>
+        <v>6827556</v>
       </c>
       <c r="S111" t="n">
         <v>10</v>
@@ -11914,7 +11910,7 @@
     </row>
     <row r="112">
       <c r="A112" t="n">
-        <v>120074885</v>
+        <v>120074905</v>
       </c>
       <c r="B112" t="n">
         <v>79160</v>
@@ -11954,10 +11950,10 @@
         </is>
       </c>
       <c r="Q112" t="n">
-        <v>478115</v>
+        <v>478285</v>
       </c>
       <c r="R112" t="n">
-        <v>6827614</v>
+        <v>6827770</v>
       </c>
       <c r="S112" t="n">
         <v>10</v>
@@ -12016,10 +12012,10 @@
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>120074934</v>
+        <v>120075042</v>
       </c>
       <c r="B113" t="n">
-        <v>79160</v>
+        <v>78278</v>
       </c>
       <c r="C113" t="inlineStr">
         <is>
@@ -12032,21 +12028,21 @@
         </is>
       </c>
       <c r="E113" t="n">
-        <v>6453</v>
+        <v>6446</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I113" t="inlineStr"/>
@@ -12056,10 +12052,10 @@
         </is>
       </c>
       <c r="Q113" t="n">
-        <v>478169</v>
+        <v>478074</v>
       </c>
       <c r="R113" t="n">
-        <v>6827760</v>
+        <v>6827775</v>
       </c>
       <c r="S113" t="n">
         <v>10</v>
@@ -12118,10 +12114,10 @@
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>120074944</v>
+        <v>120075047</v>
       </c>
       <c r="B114" t="n">
-        <v>79160</v>
+        <v>78278</v>
       </c>
       <c r="C114" t="inlineStr">
         <is>
@@ -12134,21 +12130,21 @@
         </is>
       </c>
       <c r="E114" t="n">
-        <v>6453</v>
+        <v>6446</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I114" t="inlineStr"/>
@@ -12158,10 +12154,10 @@
         </is>
       </c>
       <c r="Q114" t="n">
-        <v>478056</v>
+        <v>478212</v>
       </c>
       <c r="R114" t="n">
-        <v>6827785</v>
+        <v>6827573</v>
       </c>
       <c r="S114" t="n">
         <v>10</v>
@@ -12220,10 +12216,10 @@
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>120075029</v>
+        <v>120075167</v>
       </c>
       <c r="B115" t="n">
-        <v>78278</v>
+        <v>78542</v>
       </c>
       <c r="C115" t="inlineStr">
         <is>
@@ -12236,21 +12232,21 @@
         </is>
       </c>
       <c r="E115" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I115" t="inlineStr"/>
@@ -12260,10 +12256,10 @@
         </is>
       </c>
       <c r="Q115" t="n">
-        <v>478115</v>
+        <v>478105</v>
       </c>
       <c r="R115" t="n">
-        <v>6827564</v>
+        <v>6827851</v>
       </c>
       <c r="S115" t="n">
         <v>10</v>
@@ -12322,10 +12318,10 @@
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>120075144</v>
+        <v>120075215</v>
       </c>
       <c r="B116" t="n">
-        <v>78542</v>
+        <v>78187</v>
       </c>
       <c r="C116" t="inlineStr">
         <is>
@@ -12338,21 +12334,21 @@
         </is>
       </c>
       <c r="E116" t="n">
-        <v>6425</v>
+        <v>353</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I116" t="inlineStr"/>
@@ -12362,10 +12358,10 @@
         </is>
       </c>
       <c r="Q116" t="n">
-        <v>478261</v>
+        <v>478239</v>
       </c>
       <c r="R116" t="n">
-        <v>6827822</v>
+        <v>6827752</v>
       </c>
       <c r="S116" t="n">
         <v>10</v>
@@ -12424,10 +12420,10 @@
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>120075239</v>
+        <v>120074914</v>
       </c>
       <c r="B117" t="n">
-        <v>77474</v>
+        <v>78576</v>
       </c>
       <c r="C117" t="inlineStr">
         <is>
@@ -12440,21 +12436,21 @@
         </is>
       </c>
       <c r="E117" t="n">
-        <v>6487</v>
+        <v>185</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Blågrå svartspik</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>Chaenothecopsis fennica</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>(Laurila) Tibell</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I117" t="inlineStr"/>
@@ -12464,10 +12460,10 @@
         </is>
       </c>
       <c r="Q117" t="n">
-        <v>478137</v>
+        <v>478169</v>
       </c>
       <c r="R117" t="n">
-        <v>6827554</v>
+        <v>6827680</v>
       </c>
       <c r="S117" t="n">
         <v>10</v>
@@ -12526,7 +12522,7 @@
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>120075203</v>
+        <v>120075234</v>
       </c>
       <c r="B118" t="n">
         <v>78187</v>
@@ -12566,10 +12562,10 @@
         </is>
       </c>
       <c r="Q118" t="n">
-        <v>478125</v>
+        <v>478069</v>
       </c>
       <c r="R118" t="n">
-        <v>6827631</v>
+        <v>6827741</v>
       </c>
       <c r="S118" t="n">
         <v>10</v>
@@ -12628,10 +12624,10 @@
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>120075176</v>
+        <v>120074961</v>
       </c>
       <c r="B119" t="n">
-        <v>78542</v>
+        <v>90600</v>
       </c>
       <c r="C119" t="inlineStr">
         <is>
@@ -12644,21 +12640,21 @@
         </is>
       </c>
       <c r="E119" t="n">
-        <v>6425</v>
+        <v>5442</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I119" t="inlineStr"/>
@@ -12668,10 +12664,10 @@
         </is>
       </c>
       <c r="Q119" t="n">
-        <v>478066</v>
+        <v>478230</v>
       </c>
       <c r="R119" t="n">
-        <v>6827732</v>
+        <v>6827780</v>
       </c>
       <c r="S119" t="n">
         <v>10</v>
@@ -12730,7 +12726,7 @@
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>120075061</v>
+        <v>120075071</v>
       </c>
       <c r="B120" t="n">
         <v>78542</v>
@@ -12770,10 +12766,10 @@
         </is>
       </c>
       <c r="Q120" t="n">
-        <v>478160</v>
+        <v>478116</v>
       </c>
       <c r="R120" t="n">
-        <v>6827710</v>
+        <v>6827633</v>
       </c>
       <c r="S120" t="n">
         <v>10</v>
@@ -12832,7 +12828,7 @@
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>120075064</v>
+        <v>120075078</v>
       </c>
       <c r="B121" t="n">
         <v>78542</v>
@@ -12872,10 +12868,10 @@
         </is>
       </c>
       <c r="Q121" t="n">
-        <v>478192</v>
+        <v>478116</v>
       </c>
       <c r="R121" t="n">
-        <v>6827690</v>
+        <v>6827567</v>
       </c>
       <c r="S121" t="n">
         <v>10</v>
@@ -12934,10 +12930,10 @@
     </row>
     <row r="122">
       <c r="A122" t="n">
-        <v>120074889</v>
+        <v>120075232</v>
       </c>
       <c r="B122" t="n">
-        <v>79160</v>
+        <v>78187</v>
       </c>
       <c r="C122" t="inlineStr">
         <is>
@@ -12950,21 +12946,21 @@
         </is>
       </c>
       <c r="E122" t="n">
-        <v>6453</v>
+        <v>353</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I122" t="inlineStr"/>
@@ -12974,10 +12970,10 @@
         </is>
       </c>
       <c r="Q122" t="n">
-        <v>478163</v>
+        <v>478051</v>
       </c>
       <c r="R122" t="n">
-        <v>6827536</v>
+        <v>6827739</v>
       </c>
       <c r="S122" t="n">
         <v>10</v>
@@ -13036,10 +13032,10 @@
     </row>
     <row r="123">
       <c r="A123" t="n">
-        <v>120074935</v>
+        <v>120075230</v>
       </c>
       <c r="B123" t="n">
-        <v>79160</v>
+        <v>78187</v>
       </c>
       <c r="C123" t="inlineStr">
         <is>
@@ -13052,21 +13048,21 @@
         </is>
       </c>
       <c r="E123" t="n">
-        <v>6453</v>
+        <v>353</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I123" t="inlineStr"/>
@@ -13076,10 +13072,10 @@
         </is>
       </c>
       <c r="Q123" t="n">
-        <v>478150</v>
+        <v>478064</v>
       </c>
       <c r="R123" t="n">
-        <v>6827745</v>
+        <v>6827866</v>
       </c>
       <c r="S123" t="n">
         <v>10</v>
@@ -13138,10 +13134,10 @@
     </row>
     <row r="124">
       <c r="A124" t="n">
-        <v>120074945</v>
+        <v>120075214</v>
       </c>
       <c r="B124" t="n">
-        <v>79160</v>
+        <v>78187</v>
       </c>
       <c r="C124" t="inlineStr">
         <is>
@@ -13154,21 +13150,21 @@
         </is>
       </c>
       <c r="E124" t="n">
-        <v>6453</v>
+        <v>353</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I124" t="inlineStr"/>
@@ -13178,10 +13174,10 @@
         </is>
       </c>
       <c r="Q124" t="n">
-        <v>478061</v>
+        <v>478266</v>
       </c>
       <c r="R124" t="n">
-        <v>6827770</v>
+        <v>6827724</v>
       </c>
       <c r="S124" t="n">
         <v>10</v>
@@ -13240,10 +13236,10 @@
     </row>
     <row r="125">
       <c r="A125" t="n">
-        <v>120075063</v>
+        <v>120075207</v>
       </c>
       <c r="B125" t="n">
-        <v>78542</v>
+        <v>78187</v>
       </c>
       <c r="C125" t="inlineStr">
         <is>
@@ -13256,21 +13252,21 @@
         </is>
       </c>
       <c r="E125" t="n">
-        <v>6425</v>
+        <v>353</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I125" t="inlineStr"/>
@@ -13280,10 +13276,10 @@
         </is>
       </c>
       <c r="Q125" t="n">
-        <v>478201</v>
+        <v>478157</v>
       </c>
       <c r="R125" t="n">
-        <v>6827693</v>
+        <v>6827509</v>
       </c>
       <c r="S125" t="n">
         <v>10</v>
@@ -13342,10 +13338,10 @@
     </row>
     <row r="126">
       <c r="A126" t="n">
-        <v>120075009</v>
+        <v>120074892</v>
       </c>
       <c r="B126" t="n">
-        <v>78279</v>
+        <v>79160</v>
       </c>
       <c r="C126" t="inlineStr">
         <is>
@@ -13358,21 +13354,21 @@
         </is>
       </c>
       <c r="E126" t="n">
-        <v>228912</v>
+        <v>6453</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H126" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I126" t="inlineStr"/>
@@ -13382,10 +13378,10 @@
         </is>
       </c>
       <c r="Q126" t="n">
-        <v>478151</v>
+        <v>478243</v>
       </c>
       <c r="R126" t="n">
-        <v>6827745</v>
+        <v>6827585</v>
       </c>
       <c r="S126" t="n">
         <v>10</v>
@@ -13444,10 +13440,10 @@
     </row>
     <row r="127">
       <c r="A127" t="n">
-        <v>120075016</v>
+        <v>120075135</v>
       </c>
       <c r="B127" t="n">
-        <v>79623</v>
+        <v>78542</v>
       </c>
       <c r="C127" t="inlineStr">
         <is>
@@ -13460,21 +13456,21 @@
         </is>
       </c>
       <c r="E127" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H127" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I127" t="inlineStr"/>
@@ -13484,10 +13480,10 @@
         </is>
       </c>
       <c r="Q127" t="n">
-        <v>478096</v>
+        <v>478291</v>
       </c>
       <c r="R127" t="n">
-        <v>6827549</v>
+        <v>6827744</v>
       </c>
       <c r="S127" t="n">
         <v>10</v>
@@ -13546,10 +13542,10 @@
     </row>
     <row r="128">
       <c r="A128" t="n">
-        <v>120075019</v>
+        <v>120075147</v>
       </c>
       <c r="B128" t="n">
-        <v>79623</v>
+        <v>78542</v>
       </c>
       <c r="C128" t="inlineStr">
         <is>
@@ -13562,21 +13558,21 @@
         </is>
       </c>
       <c r="E128" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H128" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I128" t="inlineStr"/>
@@ -13586,10 +13582,10 @@
         </is>
       </c>
       <c r="Q128" t="n">
-        <v>478227</v>
+        <v>478153</v>
       </c>
       <c r="R128" t="n">
-        <v>6827655</v>
+        <v>6827728</v>
       </c>
       <c r="S128" t="n">
         <v>10</v>
@@ -13648,10 +13644,10 @@
     </row>
     <row r="129">
       <c r="A129" t="n">
-        <v>120075163</v>
+        <v>120074935</v>
       </c>
       <c r="B129" t="n">
-        <v>78542</v>
+        <v>79160</v>
       </c>
       <c r="C129" t="inlineStr">
         <is>
@@ -13664,21 +13660,21 @@
         </is>
       </c>
       <c r="E129" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H129" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I129" t="inlineStr"/>
@@ -13688,10 +13684,10 @@
         </is>
       </c>
       <c r="Q129" t="n">
-        <v>478102</v>
+        <v>478150</v>
       </c>
       <c r="R129" t="n">
-        <v>6827800</v>
+        <v>6827745</v>
       </c>
       <c r="S129" t="n">
         <v>10</v>
@@ -13750,10 +13746,10 @@
     </row>
     <row r="130">
       <c r="A130" t="n">
-        <v>120074948</v>
+        <v>120075198</v>
       </c>
       <c r="B130" t="n">
-        <v>79160</v>
+        <v>91858</v>
       </c>
       <c r="C130" t="inlineStr">
         <is>
@@ -13762,25 +13758,25 @@
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E130" t="n">
-        <v>6453</v>
+        <v>4364</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H130" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I130" t="inlineStr"/>
@@ -13790,10 +13786,10 @@
         </is>
       </c>
       <c r="Q130" t="n">
-        <v>478070</v>
+        <v>478163</v>
       </c>
       <c r="R130" t="n">
-        <v>6827723</v>
+        <v>6827530</v>
       </c>
       <c r="S130" t="n">
         <v>10</v>
@@ -13852,7 +13848,7 @@
     </row>
     <row r="131">
       <c r="A131" t="n">
-        <v>120075121</v>
+        <v>120075160</v>
       </c>
       <c r="B131" t="n">
         <v>78542</v>
@@ -13892,10 +13888,10 @@
         </is>
       </c>
       <c r="Q131" t="n">
-        <v>478232</v>
+        <v>478097</v>
       </c>
       <c r="R131" t="n">
-        <v>6827659</v>
+        <v>6827744</v>
       </c>
       <c r="S131" t="n">
         <v>10</v>
@@ -13954,7 +13950,7 @@
     </row>
     <row r="132">
       <c r="A132" t="n">
-        <v>120074946</v>
+        <v>120074934</v>
       </c>
       <c r="B132" t="n">
         <v>79160</v>
@@ -13994,10 +13990,10 @@
         </is>
       </c>
       <c r="Q132" t="n">
-        <v>478056</v>
+        <v>478169</v>
       </c>
       <c r="R132" t="n">
-        <v>6827754</v>
+        <v>6827760</v>
       </c>
       <c r="S132" t="n">
         <v>10</v>
@@ -14056,10 +14052,10 @@
     </row>
     <row r="133">
       <c r="A133" t="n">
-        <v>120074996</v>
+        <v>120074942</v>
       </c>
       <c r="B133" t="n">
-        <v>78279</v>
+        <v>79160</v>
       </c>
       <c r="C133" t="inlineStr">
         <is>
@@ -14072,21 +14068,21 @@
         </is>
       </c>
       <c r="E133" t="n">
-        <v>228912</v>
+        <v>6453</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H133" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I133" t="inlineStr"/>
@@ -14096,10 +14092,10 @@
         </is>
       </c>
       <c r="Q133" t="n">
-        <v>478165</v>
+        <v>478065</v>
       </c>
       <c r="R133" t="n">
-        <v>6827712</v>
+        <v>6827842</v>
       </c>
       <c r="S133" t="n">
         <v>10</v>
@@ -14158,10 +14154,10 @@
     </row>
     <row r="134">
       <c r="A134" t="n">
-        <v>120075004</v>
+        <v>120075043</v>
       </c>
       <c r="B134" t="n">
-        <v>78279</v>
+        <v>78278</v>
       </c>
       <c r="C134" t="inlineStr">
         <is>
@@ -14174,21 +14170,21 @@
         </is>
       </c>
       <c r="E134" t="n">
-        <v>228912</v>
+        <v>6446</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H134" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I134" t="inlineStr"/>
@@ -14198,10 +14194,10 @@
         </is>
       </c>
       <c r="Q134" t="n">
-        <v>478212</v>
+        <v>478103</v>
       </c>
       <c r="R134" t="n">
-        <v>6827573</v>
+        <v>6827803</v>
       </c>
       <c r="S134" t="n">
         <v>10</v>
@@ -14260,10 +14256,10 @@
     </row>
     <row r="135">
       <c r="A135" t="n">
-        <v>120075011</v>
+        <v>120075044</v>
       </c>
       <c r="B135" t="n">
-        <v>78279</v>
+        <v>78278</v>
       </c>
       <c r="C135" t="inlineStr">
         <is>
@@ -14276,21 +14272,21 @@
         </is>
       </c>
       <c r="E135" t="n">
-        <v>228912</v>
+        <v>6446</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H135" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I135" t="inlineStr"/>
@@ -14300,10 +14296,10 @@
         </is>
       </c>
       <c r="Q135" t="n">
-        <v>478103</v>
+        <v>478060</v>
       </c>
       <c r="R135" t="n">
-        <v>6827803</v>
+        <v>6827770</v>
       </c>
       <c r="S135" t="n">
         <v>10</v>
@@ -14362,7 +14358,7 @@
     </row>
     <row r="136">
       <c r="A136" t="n">
-        <v>120074888</v>
+        <v>120074906</v>
       </c>
       <c r="B136" t="n">
         <v>79160</v>
@@ -14402,10 +14398,10 @@
         </is>
       </c>
       <c r="Q136" t="n">
-        <v>478139</v>
+        <v>478294</v>
       </c>
       <c r="R136" t="n">
-        <v>6827554</v>
+        <v>6827790</v>
       </c>
       <c r="S136" t="n">
         <v>10</v>
@@ -14464,10 +14460,10 @@
     </row>
     <row r="137">
       <c r="A137" t="n">
-        <v>120075132</v>
+        <v>120075029</v>
       </c>
       <c r="B137" t="n">
-        <v>78542</v>
+        <v>78278</v>
       </c>
       <c r="C137" t="inlineStr">
         <is>
@@ -14480,21 +14476,21 @@
         </is>
       </c>
       <c r="E137" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H137" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I137" t="inlineStr"/>
@@ -14504,10 +14500,10 @@
         </is>
       </c>
       <c r="Q137" t="n">
-        <v>478240</v>
+        <v>478115</v>
       </c>
       <c r="R137" t="n">
-        <v>6827754</v>
+        <v>6827564</v>
       </c>
       <c r="S137" t="n">
         <v>10</v>
@@ -14566,10 +14562,10 @@
     </row>
     <row r="138">
       <c r="A138" t="n">
-        <v>120075038</v>
+        <v>120074933</v>
       </c>
       <c r="B138" t="n">
-        <v>78278</v>
+        <v>79160</v>
       </c>
       <c r="C138" t="inlineStr">
         <is>
@@ -14582,21 +14578,21 @@
         </is>
       </c>
       <c r="E138" t="n">
-        <v>6446</v>
+        <v>6453</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H138" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I138" t="inlineStr"/>
@@ -14606,10 +14602,10 @@
         </is>
       </c>
       <c r="Q138" t="n">
-        <v>478261</v>
+        <v>478189</v>
       </c>
       <c r="R138" t="n">
-        <v>6827731</v>
+        <v>6827761</v>
       </c>
       <c r="S138" t="n">
         <v>10</v>
@@ -14668,10 +14664,10 @@
     </row>
     <row r="139">
       <c r="A139" t="n">
-        <v>120074887</v>
+        <v>120075142</v>
       </c>
       <c r="B139" t="n">
-        <v>79160</v>
+        <v>78542</v>
       </c>
       <c r="C139" t="inlineStr">
         <is>
@@ -14684,21 +14680,21 @@
         </is>
       </c>
       <c r="E139" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H139" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I139" t="inlineStr"/>
@@ -14708,10 +14704,10 @@
         </is>
       </c>
       <c r="Q139" t="n">
-        <v>478144</v>
+        <v>478313</v>
       </c>
       <c r="R139" t="n">
-        <v>6827593</v>
+        <v>6827798</v>
       </c>
       <c r="S139" t="n">
         <v>10</v>
@@ -14770,10 +14766,10 @@
     </row>
     <row r="140">
       <c r="A140" t="n">
-        <v>120075164</v>
+        <v>120074881</v>
       </c>
       <c r="B140" t="n">
-        <v>78542</v>
+        <v>79160</v>
       </c>
       <c r="C140" t="inlineStr">
         <is>
@@ -14786,21 +14782,21 @@
         </is>
       </c>
       <c r="E140" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H140" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I140" t="inlineStr"/>
@@ -14810,10 +14806,10 @@
         </is>
       </c>
       <c r="Q140" t="n">
-        <v>478092</v>
+        <v>478184</v>
       </c>
       <c r="R140" t="n">
-        <v>6827810</v>
+        <v>6827728</v>
       </c>
       <c r="S140" t="n">
         <v>10</v>
@@ -14872,7 +14868,7 @@
     </row>
     <row r="141">
       <c r="A141" t="n">
-        <v>120075140</v>
+        <v>120075082</v>
       </c>
       <c r="B141" t="n">
         <v>78542</v>
@@ -14912,10 +14908,10 @@
         </is>
       </c>
       <c r="Q141" t="n">
-        <v>478310</v>
+        <v>478097</v>
       </c>
       <c r="R141" t="n">
-        <v>6827797</v>
+        <v>6827544</v>
       </c>
       <c r="S141" t="n">
         <v>10</v>
@@ -14974,10 +14970,10 @@
     </row>
     <row r="142">
       <c r="A142" t="n">
-        <v>120075048</v>
+        <v>120075013</v>
       </c>
       <c r="B142" t="n">
-        <v>56524</v>
+        <v>78279</v>
       </c>
       <c r="C142" t="inlineStr">
         <is>
@@ -14990,39 +14986,34 @@
         </is>
       </c>
       <c r="E142" t="n">
-        <v>102612</v>
+        <v>228912</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H142" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I142" t="inlineStr"/>
-      <c r="M142" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
       <c r="P142" t="inlineStr">
         <is>
           <t>Hevoslamm, Dlr</t>
         </is>
       </c>
       <c r="Q142" t="n">
-        <v>478070</v>
+        <v>478239</v>
       </c>
       <c r="R142" t="n">
-        <v>6827723</v>
+        <v>6827752</v>
       </c>
       <c r="S142" t="n">
         <v>10</v>
@@ -15081,10 +15072,10 @@
     </row>
     <row r="143">
       <c r="A143" t="n">
-        <v>120075198</v>
+        <v>120075136</v>
       </c>
       <c r="B143" t="n">
-        <v>91858</v>
+        <v>78542</v>
       </c>
       <c r="C143" t="inlineStr">
         <is>
@@ -15093,25 +15084,25 @@
       </c>
       <c r="D143" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E143" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H143" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I143" t="inlineStr"/>
@@ -15121,10 +15112,10 @@
         </is>
       </c>
       <c r="Q143" t="n">
-        <v>478163</v>
+        <v>478290</v>
       </c>
       <c r="R143" t="n">
-        <v>6827530</v>
+        <v>6827758</v>
       </c>
       <c r="S143" t="n">
         <v>10</v>
@@ -15183,10 +15174,10 @@
     </row>
     <row r="144">
       <c r="A144" t="n">
-        <v>120075219</v>
+        <v>120075016</v>
       </c>
       <c r="B144" t="n">
-        <v>78187</v>
+        <v>79623</v>
       </c>
       <c r="C144" t="inlineStr">
         <is>
@@ -15199,21 +15190,21 @@
         </is>
       </c>
       <c r="E144" t="n">
-        <v>353</v>
+        <v>6458</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H144" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I144" t="inlineStr"/>
@@ -15223,10 +15214,10 @@
         </is>
       </c>
       <c r="Q144" t="n">
-        <v>478169</v>
+        <v>478096</v>
       </c>
       <c r="R144" t="n">
-        <v>6827760</v>
+        <v>6827549</v>
       </c>
       <c r="S144" t="n">
         <v>10</v>
@@ -15285,10 +15276,10 @@
     </row>
     <row r="145">
       <c r="A145" t="n">
-        <v>120074915</v>
+        <v>120075128</v>
       </c>
       <c r="B145" t="n">
-        <v>78576</v>
+        <v>78542</v>
       </c>
       <c r="C145" t="inlineStr">
         <is>
@@ -15301,21 +15292,21 @@
         </is>
       </c>
       <c r="E145" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H145" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I145" t="inlineStr"/>
@@ -15325,10 +15316,10 @@
         </is>
       </c>
       <c r="Q145" t="n">
-        <v>478102</v>
+        <v>478275</v>
       </c>
       <c r="R145" t="n">
-        <v>6827555</v>
+        <v>6827710</v>
       </c>
       <c r="S145" t="n">
         <v>10</v>
@@ -15387,10 +15378,10 @@
     </row>
     <row r="146">
       <c r="A146" t="n">
-        <v>120074998</v>
+        <v>120075045</v>
       </c>
       <c r="B146" t="n">
-        <v>78279</v>
+        <v>78278</v>
       </c>
       <c r="C146" t="inlineStr">
         <is>
@@ -15403,21 +15394,21 @@
         </is>
       </c>
       <c r="E146" t="n">
-        <v>228912</v>
+        <v>6446</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H146" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I146" t="inlineStr"/>
@@ -15427,10 +15418,10 @@
         </is>
       </c>
       <c r="Q146" t="n">
-        <v>478172</v>
+        <v>478070</v>
       </c>
       <c r="R146" t="n">
-        <v>6827640</v>
+        <v>6827723</v>
       </c>
       <c r="S146" t="n">
         <v>10</v>
@@ -15489,10 +15480,10 @@
     </row>
     <row r="147">
       <c r="A147" t="n">
-        <v>120074997</v>
+        <v>120075177</v>
       </c>
       <c r="B147" t="n">
-        <v>78279</v>
+        <v>78542</v>
       </c>
       <c r="C147" t="inlineStr">
         <is>
@@ -15505,21 +15496,21 @@
         </is>
       </c>
       <c r="E147" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G147" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H147" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I147" t="inlineStr"/>
@@ -15529,10 +15520,10 @@
         </is>
       </c>
       <c r="Q147" t="n">
-        <v>478218</v>
+        <v>478075</v>
       </c>
       <c r="R147" t="n">
-        <v>6827733</v>
+        <v>6827717</v>
       </c>
       <c r="S147" t="n">
         <v>10</v>
@@ -15591,10 +15582,10 @@
     </row>
     <row r="148">
       <c r="A148" t="n">
-        <v>120075010</v>
+        <v>120075038</v>
       </c>
       <c r="B148" t="n">
-        <v>78279</v>
+        <v>78278</v>
       </c>
       <c r="C148" t="inlineStr">
         <is>
@@ -15607,21 +15598,21 @@
         </is>
       </c>
       <c r="E148" t="n">
-        <v>228912</v>
+        <v>6446</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G148" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H148" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I148" t="inlineStr"/>
@@ -15631,10 +15622,10 @@
         </is>
       </c>
       <c r="Q148" t="n">
-        <v>478074</v>
+        <v>478261</v>
       </c>
       <c r="R148" t="n">
-        <v>6827772</v>
+        <v>6827731</v>
       </c>
       <c r="S148" t="n">
         <v>10</v>
@@ -15693,10 +15684,10 @@
     </row>
     <row r="149">
       <c r="A149" t="n">
-        <v>120074928</v>
+        <v>120075068</v>
       </c>
       <c r="B149" t="n">
-        <v>78576</v>
+        <v>78542</v>
       </c>
       <c r="C149" t="inlineStr">
         <is>
@@ -15709,21 +15700,21 @@
         </is>
       </c>
       <c r="E149" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G149" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H149" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I149" t="inlineStr"/>
@@ -15733,10 +15724,10 @@
         </is>
       </c>
       <c r="Q149" t="n">
-        <v>478059</v>
+        <v>478174</v>
       </c>
       <c r="R149" t="n">
-        <v>6827740</v>
+        <v>6827656</v>
       </c>
       <c r="S149" t="n">
         <v>10</v>
@@ -15795,10 +15786,10 @@
     </row>
     <row r="150">
       <c r="A150" t="n">
-        <v>120074925</v>
+        <v>120075008</v>
       </c>
       <c r="B150" t="n">
-        <v>78576</v>
+        <v>78279</v>
       </c>
       <c r="C150" t="inlineStr">
         <is>
@@ -15811,21 +15802,21 @@
         </is>
       </c>
       <c r="E150" t="n">
-        <v>185</v>
+        <v>228912</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G150" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H150" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I150" t="inlineStr"/>
@@ -15835,10 +15826,10 @@
         </is>
       </c>
       <c r="Q150" t="n">
-        <v>478088</v>
+        <v>478299</v>
       </c>
       <c r="R150" t="n">
-        <v>6827834</v>
+        <v>6827805</v>
       </c>
       <c r="S150" t="n">
         <v>10</v>
@@ -15897,10 +15888,10 @@
     </row>
     <row r="151">
       <c r="A151" t="n">
-        <v>120074961</v>
+        <v>120075225</v>
       </c>
       <c r="B151" t="n">
-        <v>90600</v>
+        <v>78187</v>
       </c>
       <c r="C151" t="inlineStr">
         <is>
@@ -15913,21 +15904,21 @@
         </is>
       </c>
       <c r="E151" t="n">
-        <v>5442</v>
+        <v>353</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G151" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H151" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I151" t="inlineStr"/>
@@ -15937,10 +15928,10 @@
         </is>
       </c>
       <c r="Q151" t="n">
-        <v>478230</v>
+        <v>478075</v>
       </c>
       <c r="R151" t="n">
-        <v>6827780</v>
+        <v>6827798</v>
       </c>
       <c r="S151" t="n">
         <v>10</v>
@@ -15999,10 +15990,10 @@
     </row>
     <row r="152">
       <c r="A152" t="n">
-        <v>120075026</v>
+        <v>120075205</v>
       </c>
       <c r="B152" t="n">
-        <v>78278</v>
+        <v>78187</v>
       </c>
       <c r="C152" t="inlineStr">
         <is>
@@ -16015,21 +16006,21 @@
         </is>
       </c>
       <c r="E152" t="n">
-        <v>6446</v>
+        <v>353</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G152" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H152" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I152" t="inlineStr"/>
@@ -16039,10 +16030,10 @@
         </is>
       </c>
       <c r="Q152" t="n">
-        <v>478161</v>
+        <v>478117</v>
       </c>
       <c r="R152" t="n">
-        <v>6827592</v>
+        <v>6827612</v>
       </c>
       <c r="S152" t="n">
         <v>10</v>
@@ -16101,10 +16092,10 @@
     </row>
     <row r="153">
       <c r="A153" t="n">
-        <v>120075075</v>
+        <v>120075204</v>
       </c>
       <c r="B153" t="n">
-        <v>78542</v>
+        <v>78187</v>
       </c>
       <c r="C153" t="inlineStr">
         <is>
@@ -16117,21 +16108,21 @@
         </is>
       </c>
       <c r="E153" t="n">
-        <v>6425</v>
+        <v>353</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G153" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H153" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I153" t="inlineStr"/>
@@ -16141,10 +16132,10 @@
         </is>
       </c>
       <c r="Q153" t="n">
-        <v>478139</v>
+        <v>478115</v>
       </c>
       <c r="R153" t="n">
-        <v>6827554</v>
+        <v>6827614</v>
       </c>
       <c r="S153" t="n">
         <v>10</v>
@@ -16203,10 +16194,10 @@
     </row>
     <row r="154">
       <c r="A154" t="n">
-        <v>120075065</v>
+        <v>120075010</v>
       </c>
       <c r="B154" t="n">
-        <v>78542</v>
+        <v>78279</v>
       </c>
       <c r="C154" t="inlineStr">
         <is>
@@ -16219,21 +16210,21 @@
         </is>
       </c>
       <c r="E154" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G154" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H154" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I154" t="inlineStr"/>
@@ -16243,10 +16234,10 @@
         </is>
       </c>
       <c r="Q154" t="n">
-        <v>478169</v>
+        <v>478074</v>
       </c>
       <c r="R154" t="n">
-        <v>6827679</v>
+        <v>6827772</v>
       </c>
       <c r="S154" t="n">
         <v>10</v>
@@ -16305,10 +16296,10 @@
     </row>
     <row r="155">
       <c r="A155" t="n">
-        <v>120075167</v>
+        <v>120075219</v>
       </c>
       <c r="B155" t="n">
-        <v>78542</v>
+        <v>78187</v>
       </c>
       <c r="C155" t="inlineStr">
         <is>
@@ -16321,21 +16312,21 @@
         </is>
       </c>
       <c r="E155" t="n">
-        <v>6425</v>
+        <v>353</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G155" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H155" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I155" t="inlineStr"/>
@@ -16345,10 +16336,10 @@
         </is>
       </c>
       <c r="Q155" t="n">
-        <v>478105</v>
+        <v>478169</v>
       </c>
       <c r="R155" t="n">
-        <v>6827851</v>
+        <v>6827760</v>
       </c>
       <c r="S155" t="n">
         <v>10</v>
@@ -16407,10 +16398,10 @@
     </row>
     <row r="156">
       <c r="A156" t="n">
-        <v>120075160</v>
+        <v>120075015</v>
       </c>
       <c r="B156" t="n">
-        <v>78542</v>
+        <v>79623</v>
       </c>
       <c r="C156" t="inlineStr">
         <is>
@@ -16423,21 +16414,21 @@
         </is>
       </c>
       <c r="E156" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G156" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H156" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I156" t="inlineStr"/>
@@ -16447,10 +16438,10 @@
         </is>
       </c>
       <c r="Q156" t="n">
-        <v>478097</v>
+        <v>478114</v>
       </c>
       <c r="R156" t="n">
-        <v>6827744</v>
+        <v>6827633</v>
       </c>
       <c r="S156" t="n">
         <v>10</v>
@@ -16509,10 +16500,10 @@
     </row>
     <row r="157">
       <c r="A157" t="n">
-        <v>120075070</v>
+        <v>120075239</v>
       </c>
       <c r="B157" t="n">
-        <v>78542</v>
+        <v>77474</v>
       </c>
       <c r="C157" t="inlineStr">
         <is>
@@ -16525,21 +16516,21 @@
         </is>
       </c>
       <c r="E157" t="n">
-        <v>6425</v>
+        <v>6487</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Blågrå svartspik</t>
         </is>
       </c>
       <c r="G157" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenothecopsis fennica</t>
         </is>
       </c>
       <c r="H157" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Laurila) Tibell</t>
         </is>
       </c>
       <c r="I157" t="inlineStr"/>
@@ -16549,10 +16540,10 @@
         </is>
       </c>
       <c r="Q157" t="n">
-        <v>478135</v>
+        <v>478137</v>
       </c>
       <c r="R157" t="n">
-        <v>6827625</v>
+        <v>6827554</v>
       </c>
       <c r="S157" t="n">
         <v>10</v>
@@ -16611,7 +16602,7 @@
     </row>
     <row r="158">
       <c r="A158" t="n">
-        <v>120075175</v>
+        <v>120075064</v>
       </c>
       <c r="B158" t="n">
         <v>78542</v>
@@ -16651,10 +16642,10 @@
         </is>
       </c>
       <c r="Q158" t="n">
-        <v>478059</v>
+        <v>478192</v>
       </c>
       <c r="R158" t="n">
-        <v>6827739</v>
+        <v>6827690</v>
       </c>
       <c r="S158" t="n">
         <v>10</v>
@@ -16713,10 +16704,10 @@
     </row>
     <row r="159">
       <c r="A159" t="n">
-        <v>120075232</v>
+        <v>120074886</v>
       </c>
       <c r="B159" t="n">
-        <v>78187</v>
+        <v>79160</v>
       </c>
       <c r="C159" t="inlineStr">
         <is>
@@ -16729,21 +16720,21 @@
         </is>
       </c>
       <c r="E159" t="n">
-        <v>353</v>
+        <v>6453</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G159" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H159" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I159" t="inlineStr"/>
@@ -16753,10 +16744,10 @@
         </is>
       </c>
       <c r="Q159" t="n">
-        <v>478051</v>
+        <v>478125</v>
       </c>
       <c r="R159" t="n">
-        <v>6827739</v>
+        <v>6827604</v>
       </c>
       <c r="S159" t="n">
         <v>10</v>
@@ -16815,10 +16806,10 @@
     </row>
     <row r="160">
       <c r="A160" t="n">
-        <v>120075054</v>
+        <v>120075159</v>
       </c>
       <c r="B160" t="n">
-        <v>90598</v>
+        <v>78542</v>
       </c>
       <c r="C160" t="inlineStr">
         <is>
@@ -16831,21 +16822,21 @@
         </is>
       </c>
       <c r="E160" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G160" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H160" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I160" t="inlineStr"/>
@@ -16855,10 +16846,10 @@
         </is>
       </c>
       <c r="Q160" t="n">
-        <v>478126</v>
+        <v>478100</v>
       </c>
       <c r="R160" t="n">
-        <v>6827477</v>
+        <v>6827729</v>
       </c>
       <c r="S160" t="n">
         <v>10</v>
@@ -16917,10 +16908,10 @@
     </row>
     <row r="161">
       <c r="A161" t="n">
-        <v>120075090</v>
+        <v>120075040</v>
       </c>
       <c r="B161" t="n">
-        <v>78542</v>
+        <v>78278</v>
       </c>
       <c r="C161" t="inlineStr">
         <is>
@@ -16933,21 +16924,21 @@
         </is>
       </c>
       <c r="E161" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G161" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H161" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I161" t="inlineStr"/>
@@ -16957,10 +16948,10 @@
         </is>
       </c>
       <c r="Q161" t="n">
-        <v>478161</v>
+        <v>478250</v>
       </c>
       <c r="R161" t="n">
-        <v>6827528</v>
+        <v>6827802</v>
       </c>
       <c r="S161" t="n">
         <v>10</v>
@@ -17019,10 +17010,10 @@
     </row>
     <row r="162">
       <c r="A162" t="n">
-        <v>120075060</v>
+        <v>120074944</v>
       </c>
       <c r="B162" t="n">
-        <v>78542</v>
+        <v>79160</v>
       </c>
       <c r="C162" t="inlineStr">
         <is>
@@ -17035,21 +17026,21 @@
         </is>
       </c>
       <c r="E162" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G162" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H162" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I162" t="inlineStr"/>
@@ -17059,10 +17050,10 @@
         </is>
       </c>
       <c r="Q162" t="n">
-        <v>478087</v>
+        <v>478056</v>
       </c>
       <c r="R162" t="n">
-        <v>6827718</v>
+        <v>6827785</v>
       </c>
       <c r="S162" t="n">
         <v>10</v>
@@ -17121,10 +17112,10 @@
     </row>
     <row r="163">
       <c r="A163" t="n">
-        <v>120074931</v>
+        <v>120075025</v>
       </c>
       <c r="B163" t="n">
-        <v>79160</v>
+        <v>78278</v>
       </c>
       <c r="C163" t="inlineStr">
         <is>
@@ -17137,21 +17128,21 @@
         </is>
       </c>
       <c r="E163" t="n">
-        <v>6453</v>
+        <v>6446</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G163" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H163" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I163" t="inlineStr"/>
@@ -17161,10 +17152,10 @@
         </is>
       </c>
       <c r="Q163" t="n">
-        <v>478261</v>
+        <v>478171</v>
       </c>
       <c r="R163" t="n">
-        <v>6827822</v>
+        <v>6827642</v>
       </c>
       <c r="S163" t="n">
         <v>10</v>
@@ -17223,10 +17214,10 @@
     </row>
     <row r="164">
       <c r="A164" t="n">
-        <v>120075223</v>
+        <v>120075039</v>
       </c>
       <c r="B164" t="n">
-        <v>78187</v>
+        <v>78278</v>
       </c>
       <c r="C164" t="inlineStr">
         <is>
@@ -17239,21 +17230,21 @@
         </is>
       </c>
       <c r="E164" t="n">
-        <v>353</v>
+        <v>6446</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G164" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H164" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I164" t="inlineStr"/>
@@ -17263,10 +17254,10 @@
         </is>
       </c>
       <c r="Q164" t="n">
-        <v>478076</v>
+        <v>478238</v>
       </c>
       <c r="R164" t="n">
-        <v>6827777</v>
+        <v>6827752</v>
       </c>
       <c r="S164" t="n">
         <v>10</v>
@@ -17325,10 +17316,10 @@
     </row>
     <row r="165">
       <c r="A165" t="n">
-        <v>120075089</v>
+        <v>120075035</v>
       </c>
       <c r="B165" t="n">
-        <v>78542</v>
+        <v>78278</v>
       </c>
       <c r="C165" t="inlineStr">
         <is>
@@ -17341,21 +17332,21 @@
         </is>
       </c>
       <c r="E165" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G165" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H165" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I165" t="inlineStr"/>
@@ -17365,10 +17356,10 @@
         </is>
       </c>
       <c r="Q165" t="n">
-        <v>478153</v>
+        <v>478273</v>
       </c>
       <c r="R165" t="n">
-        <v>6827517</v>
+        <v>6827711</v>
       </c>
       <c r="S165" t="n">
         <v>10</v>
@@ -17427,10 +17418,10 @@
     </row>
     <row r="166">
       <c r="A166" t="n">
-        <v>120075025</v>
+        <v>120075127</v>
       </c>
       <c r="B166" t="n">
-        <v>78278</v>
+        <v>78542</v>
       </c>
       <c r="C166" t="inlineStr">
         <is>
@@ -17443,21 +17434,21 @@
         </is>
       </c>
       <c r="E166" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G166" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H166" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I166" t="inlineStr"/>
@@ -17467,10 +17458,10 @@
         </is>
       </c>
       <c r="Q166" t="n">
-        <v>478171</v>
+        <v>478292</v>
       </c>
       <c r="R166" t="n">
-        <v>6827642</v>
+        <v>6827708</v>
       </c>
       <c r="S166" t="n">
         <v>10</v>
@@ -17529,10 +17520,10 @@
     </row>
     <row r="167">
       <c r="A167" t="n">
-        <v>120075137</v>
+        <v>120074889</v>
       </c>
       <c r="B167" t="n">
-        <v>78542</v>
+        <v>79160</v>
       </c>
       <c r="C167" t="inlineStr">
         <is>
@@ -17545,21 +17536,21 @@
         </is>
       </c>
       <c r="E167" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G167" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H167" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I167" t="inlineStr"/>
@@ -17569,10 +17560,10 @@
         </is>
       </c>
       <c r="Q167" t="n">
-        <v>478288</v>
+        <v>478163</v>
       </c>
       <c r="R167" t="n">
-        <v>6827763</v>
+        <v>6827536</v>
       </c>
       <c r="S167" t="n">
         <v>10</v>
@@ -17631,10 +17622,10 @@
     </row>
     <row r="168">
       <c r="A168" t="n">
-        <v>120075242</v>
+        <v>120075061</v>
       </c>
       <c r="B168" t="n">
-        <v>77926</v>
+        <v>78542</v>
       </c>
       <c r="C168" t="inlineStr">
         <is>
@@ -17647,21 +17638,21 @@
         </is>
       </c>
       <c r="E168" t="n">
-        <v>6437</v>
+        <v>6425</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G168" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H168" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I168" t="inlineStr"/>
@@ -17671,10 +17662,10 @@
         </is>
       </c>
       <c r="Q168" t="n">
-        <v>478136</v>
+        <v>478160</v>
       </c>
       <c r="R168" t="n">
-        <v>6827556</v>
+        <v>6827710</v>
       </c>
       <c r="S168" t="n">
         <v>10</v>
@@ -17733,7 +17724,7 @@
     </row>
     <row r="169">
       <c r="A169" t="n">
-        <v>120075147</v>
+        <v>120075161</v>
       </c>
       <c r="B169" t="n">
         <v>78542</v>
@@ -17773,10 +17764,10 @@
         </is>
       </c>
       <c r="Q169" t="n">
-        <v>478153</v>
+        <v>478082</v>
       </c>
       <c r="R169" t="n">
-        <v>6827728</v>
+        <v>6827766</v>
       </c>
       <c r="S169" t="n">
         <v>10</v>
@@ -17835,10 +17826,10 @@
     </row>
     <row r="170">
       <c r="A170" t="n">
-        <v>120075024</v>
+        <v>120075121</v>
       </c>
       <c r="B170" t="n">
-        <v>78278</v>
+        <v>78542</v>
       </c>
       <c r="C170" t="inlineStr">
         <is>
@@ -17851,21 +17842,21 @@
         </is>
       </c>
       <c r="E170" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G170" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H170" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I170" t="inlineStr"/>
@@ -17875,10 +17866,10 @@
         </is>
       </c>
       <c r="Q170" t="n">
-        <v>478165</v>
+        <v>478232</v>
       </c>
       <c r="R170" t="n">
-        <v>6827712</v>
+        <v>6827659</v>
       </c>
       <c r="S170" t="n">
         <v>10</v>
@@ -17937,10 +17928,10 @@
     </row>
     <row r="171">
       <c r="A171" t="n">
-        <v>120075130</v>
+        <v>120074939</v>
       </c>
       <c r="B171" t="n">
-        <v>78542</v>
+        <v>79160</v>
       </c>
       <c r="C171" t="inlineStr">
         <is>
@@ -17953,21 +17944,21 @@
         </is>
       </c>
       <c r="E171" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G171" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H171" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I171" t="inlineStr"/>
@@ -17977,10 +17968,10 @@
         </is>
       </c>
       <c r="Q171" t="n">
-        <v>478264</v>
+        <v>478091</v>
       </c>
       <c r="R171" t="n">
-        <v>6827733</v>
+        <v>6827838</v>
       </c>
       <c r="S171" t="n">
         <v>10</v>
@@ -18039,10 +18030,10 @@
     </row>
     <row r="172">
       <c r="A172" t="n">
-        <v>120074882</v>
+        <v>120075027</v>
       </c>
       <c r="B172" t="n">
-        <v>79160</v>
+        <v>78278</v>
       </c>
       <c r="C172" t="inlineStr">
         <is>
@@ -18055,21 +18046,21 @@
         </is>
       </c>
       <c r="E172" t="n">
-        <v>6453</v>
+        <v>6446</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G172" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H172" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I172" t="inlineStr"/>
@@ -18079,7 +18070,7 @@
         </is>
       </c>
       <c r="Q172" t="n">
-        <v>478162</v>
+        <v>478144</v>
       </c>
       <c r="R172" t="n">
         <v>6827593</v>
@@ -18141,10 +18132,10 @@
     </row>
     <row r="173">
       <c r="A173" t="n">
-        <v>120075205</v>
+        <v>120074941</v>
       </c>
       <c r="B173" t="n">
-        <v>78187</v>
+        <v>79160</v>
       </c>
       <c r="C173" t="inlineStr">
         <is>
@@ -18157,21 +18148,21 @@
         </is>
       </c>
       <c r="E173" t="n">
-        <v>353</v>
+        <v>6453</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G173" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H173" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I173" t="inlineStr"/>
@@ -18181,10 +18172,10 @@
         </is>
       </c>
       <c r="Q173" t="n">
-        <v>478117</v>
+        <v>478069</v>
       </c>
       <c r="R173" t="n">
-        <v>6827612</v>
+        <v>6827854</v>
       </c>
       <c r="S173" t="n">
         <v>10</v>
@@ -18243,10 +18234,10 @@
     </row>
     <row r="174">
       <c r="A174" t="n">
-        <v>120075227</v>
+        <v>120075088</v>
       </c>
       <c r="B174" t="n">
-        <v>78187</v>
+        <v>78542</v>
       </c>
       <c r="C174" t="inlineStr">
         <is>
@@ -18259,21 +18250,21 @@
         </is>
       </c>
       <c r="E174" t="n">
-        <v>353</v>
+        <v>6425</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G174" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H174" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I174" t="inlineStr"/>
@@ -18283,10 +18274,10 @@
         </is>
       </c>
       <c r="Q174" t="n">
-        <v>478088</v>
+        <v>478151</v>
       </c>
       <c r="R174" t="n">
-        <v>6827834</v>
+        <v>6827509</v>
       </c>
       <c r="S174" t="n">
         <v>10</v>
@@ -18345,10 +18336,10 @@
     </row>
     <row r="175">
       <c r="A175" t="n">
-        <v>120075071</v>
+        <v>120074891</v>
       </c>
       <c r="B175" t="n">
-        <v>78542</v>
+        <v>79160</v>
       </c>
       <c r="C175" t="inlineStr">
         <is>
@@ -18361,21 +18352,21 @@
         </is>
       </c>
       <c r="E175" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G175" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H175" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I175" t="inlineStr"/>
@@ -18385,10 +18376,10 @@
         </is>
       </c>
       <c r="Q175" t="n">
-        <v>478116</v>
+        <v>478212</v>
       </c>
       <c r="R175" t="n">
-        <v>6827633</v>
+        <v>6827573</v>
       </c>
       <c r="S175" t="n">
         <v>10</v>
@@ -18447,7 +18438,7 @@
     </row>
     <row r="176">
       <c r="A176" t="n">
-        <v>120075127</v>
+        <v>120075165</v>
       </c>
       <c r="B176" t="n">
         <v>78542</v>
@@ -18487,10 +18478,10 @@
         </is>
       </c>
       <c r="Q176" t="n">
-        <v>478292</v>
+        <v>478078</v>
       </c>
       <c r="R176" t="n">
-        <v>6827708</v>
+        <v>6827834</v>
       </c>
       <c r="S176" t="n">
         <v>10</v>
@@ -18549,10 +18540,10 @@
     </row>
     <row r="177">
       <c r="A177" t="n">
-        <v>120075073</v>
+        <v>120074915</v>
       </c>
       <c r="B177" t="n">
-        <v>78542</v>
+        <v>78576</v>
       </c>
       <c r="C177" t="inlineStr">
         <is>
@@ -18565,21 +18556,21 @@
         </is>
       </c>
       <c r="E177" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G177" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H177" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I177" t="inlineStr"/>
@@ -18589,10 +18580,10 @@
         </is>
       </c>
       <c r="Q177" t="n">
-        <v>478116</v>
+        <v>478102</v>
       </c>
       <c r="R177" t="n">
-        <v>6827617</v>
+        <v>6827555</v>
       </c>
       <c r="S177" t="n">
         <v>10</v>
@@ -18651,10 +18642,10 @@
     </row>
     <row r="178">
       <c r="A178" t="n">
-        <v>120075078</v>
+        <v>120074925</v>
       </c>
       <c r="B178" t="n">
-        <v>78542</v>
+        <v>78576</v>
       </c>
       <c r="C178" t="inlineStr">
         <is>
@@ -18667,21 +18658,21 @@
         </is>
       </c>
       <c r="E178" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G178" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H178" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I178" t="inlineStr"/>
@@ -18691,10 +18682,10 @@
         </is>
       </c>
       <c r="Q178" t="n">
-        <v>478116</v>
+        <v>478088</v>
       </c>
       <c r="R178" t="n">
-        <v>6827567</v>
+        <v>6827834</v>
       </c>
       <c r="S178" t="n">
         <v>10</v>
@@ -18753,10 +18744,10 @@
     </row>
     <row r="179">
       <c r="A179" t="n">
-        <v>120075128</v>
+        <v>120075227</v>
       </c>
       <c r="B179" t="n">
-        <v>78542</v>
+        <v>78187</v>
       </c>
       <c r="C179" t="inlineStr">
         <is>
@@ -18769,21 +18760,21 @@
         </is>
       </c>
       <c r="E179" t="n">
-        <v>6425</v>
+        <v>353</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G179" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H179" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I179" t="inlineStr"/>
@@ -18793,10 +18784,10 @@
         </is>
       </c>
       <c r="Q179" t="n">
-        <v>478275</v>
+        <v>478088</v>
       </c>
       <c r="R179" t="n">
-        <v>6827710</v>
+        <v>6827834</v>
       </c>
       <c r="S179" t="n">
         <v>10</v>
@@ -18855,10 +18846,10 @@
     </row>
     <row r="180">
       <c r="A180" t="n">
-        <v>120074933</v>
+        <v>120075202</v>
       </c>
       <c r="B180" t="n">
-        <v>79160</v>
+        <v>78187</v>
       </c>
       <c r="C180" t="inlineStr">
         <is>
@@ -18871,21 +18862,21 @@
         </is>
       </c>
       <c r="E180" t="n">
-        <v>6453</v>
+        <v>353</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G180" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H180" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I180" t="inlineStr"/>
@@ -18895,10 +18886,10 @@
         </is>
       </c>
       <c r="Q180" t="n">
-        <v>478189</v>
+        <v>478218</v>
       </c>
       <c r="R180" t="n">
-        <v>6827761</v>
+        <v>6827721</v>
       </c>
       <c r="S180" t="n">
         <v>10</v>
@@ -18957,10 +18948,10 @@
     </row>
     <row r="181">
       <c r="A181" t="n">
-        <v>120075166</v>
+        <v>120075197</v>
       </c>
       <c r="B181" t="n">
-        <v>78542</v>
+        <v>91858</v>
       </c>
       <c r="C181" t="inlineStr">
         <is>
@@ -18969,38 +18960,47 @@
       </c>
       <c r="D181" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E181" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G181" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H181" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I181" t="inlineStr"/>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I181" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J181" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="P181" t="inlineStr">
         <is>
           <t>Hevoslamm, Dlr</t>
         </is>
       </c>
       <c r="Q181" t="n">
-        <v>478092</v>
+        <v>478077</v>
       </c>
       <c r="R181" t="n">
-        <v>6827839</v>
+        <v>6827805</v>
       </c>
       <c r="S181" t="n">
         <v>10</v>

--- a/artfynd/A 32983-2023 artfynd.xlsx
+++ b/artfynd/A 32983-2023 artfynd.xlsx
@@ -1797,7 +1797,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>120075131</v>
+        <v>120075129</v>
       </c>
       <c r="B13" t="n">
         <v>78542</v>
@@ -1837,10 +1837,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>478258</v>
+        <v>478265</v>
       </c>
       <c r="R13" t="n">
-        <v>6827731</v>
+        <v>6827707</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1899,7 +1899,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>120075077</v>
+        <v>120075120</v>
       </c>
       <c r="B14" t="n">
         <v>78542</v>
@@ -1939,10 +1939,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>478124</v>
+        <v>478223</v>
       </c>
       <c r="R14" t="n">
-        <v>6827560</v>
+        <v>6827657</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2001,7 +2001,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>120075174</v>
+        <v>120075075</v>
       </c>
       <c r="B15" t="n">
         <v>78542</v>
@@ -2041,10 +2041,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>478057</v>
+        <v>478139</v>
       </c>
       <c r="R15" t="n">
-        <v>6827749</v>
+        <v>6827554</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2103,7 +2103,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>120075129</v>
+        <v>120075063</v>
       </c>
       <c r="B16" t="n">
         <v>78542</v>
@@ -2143,10 +2143,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>478265</v>
+        <v>478201</v>
       </c>
       <c r="R16" t="n">
-        <v>6827707</v>
+        <v>6827693</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2205,7 +2205,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>120075120</v>
+        <v>120075146</v>
       </c>
       <c r="B17" t="n">
         <v>78542</v>
@@ -2245,10 +2245,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>478223</v>
+        <v>478154</v>
       </c>
       <c r="R17" t="n">
-        <v>6827657</v>
+        <v>6827747</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2307,7 +2307,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>120075075</v>
+        <v>120075131</v>
       </c>
       <c r="B18" t="n">
         <v>78542</v>
@@ -2347,10 +2347,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>478139</v>
+        <v>478258</v>
       </c>
       <c r="R18" t="n">
-        <v>6827554</v>
+        <v>6827731</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2409,7 +2409,7 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>120075063</v>
+        <v>120075077</v>
       </c>
       <c r="B19" t="n">
         <v>78542</v>
@@ -2449,10 +2449,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>478201</v>
+        <v>478124</v>
       </c>
       <c r="R19" t="n">
-        <v>6827693</v>
+        <v>6827560</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2511,7 +2511,7 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>120075146</v>
+        <v>120075174</v>
       </c>
       <c r="B20" t="n">
         <v>78542</v>
@@ -2551,10 +2551,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>478154</v>
+        <v>478057</v>
       </c>
       <c r="R20" t="n">
-        <v>6827747</v>
+        <v>6827749</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -4347,10 +4347,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>120074952</v>
+        <v>120075166</v>
       </c>
       <c r="B38" t="n">
-        <v>79131</v>
+        <v>78542</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4363,21 +4363,21 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>229821</v>
+        <v>6425</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4387,10 +4387,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>478120</v>
+        <v>478092</v>
       </c>
       <c r="R38" t="n">
-        <v>6827605</v>
+        <v>6827839</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4449,10 +4449,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>120075166</v>
+        <v>120074952</v>
       </c>
       <c r="B39" t="n">
-        <v>78542</v>
+        <v>79131</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4465,21 +4465,21 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6425</v>
+        <v>229821</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4489,10 +4489,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>478092</v>
+        <v>478120</v>
       </c>
       <c r="R39" t="n">
-        <v>6827839</v>
+        <v>6827605</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -5061,10 +5061,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>120074956</v>
+        <v>120074907</v>
       </c>
       <c r="B45" t="n">
-        <v>57320</v>
+        <v>79160</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5077,39 +5077,34 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>100109</v>
+        <v>6453</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
-      <c r="M45" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P45" t="inlineStr">
         <is>
           <t>Hevoslamm, Dlr</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>478278</v>
+        <v>478263</v>
       </c>
       <c r="R45" t="n">
-        <v>6827832</v>
+        <v>6827838</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5142,11 +5137,6 @@
       <c r="AA45" t="inlineStr">
         <is>
           <t>2024-09-27</t>
-        </is>
-      </c>
-      <c r="AC45" t="inlineStr">
-        <is>
-          <t>Färska ringhack (tall)</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5173,10 +5163,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>120075201</v>
+        <v>120075081</v>
       </c>
       <c r="B46" t="n">
-        <v>78187</v>
+        <v>78542</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -5189,21 +5179,21 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>353</v>
+        <v>6425</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5213,10 +5203,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>478182</v>
+        <v>478096</v>
       </c>
       <c r="R46" t="n">
-        <v>6827728</v>
+        <v>6827550</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5275,10 +5265,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>120074907</v>
+        <v>120075095</v>
       </c>
       <c r="B47" t="n">
-        <v>79160</v>
+        <v>78542</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -5291,21 +5281,21 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5315,10 +5305,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>478263</v>
+        <v>478219</v>
       </c>
       <c r="R47" t="n">
-        <v>6827838</v>
+        <v>6827572</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5377,7 +5367,7 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>120075081</v>
+        <v>120075172</v>
       </c>
       <c r="B48" t="n">
         <v>78542</v>
@@ -5417,10 +5407,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>478096</v>
+        <v>478055</v>
       </c>
       <c r="R48" t="n">
-        <v>6827550</v>
+        <v>6827768</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5479,7 +5469,7 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>120075095</v>
+        <v>120075137</v>
       </c>
       <c r="B49" t="n">
         <v>78542</v>
@@ -5519,10 +5509,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>478219</v>
+        <v>478288</v>
       </c>
       <c r="R49" t="n">
-        <v>6827572</v>
+        <v>6827763</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5581,10 +5571,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>120075065</v>
+        <v>120074931</v>
       </c>
       <c r="B50" t="n">
-        <v>78542</v>
+        <v>79160</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -5597,21 +5587,21 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -5621,10 +5611,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>478169</v>
+        <v>478261</v>
       </c>
       <c r="R50" t="n">
-        <v>6827679</v>
+        <v>6827822</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5683,10 +5673,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>120075172</v>
+        <v>120075201</v>
       </c>
       <c r="B51" t="n">
-        <v>78542</v>
+        <v>78187</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -5699,21 +5689,21 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>6425</v>
+        <v>353</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -5723,10 +5713,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>478055</v>
+        <v>478182</v>
       </c>
       <c r="R51" t="n">
-        <v>6827768</v>
+        <v>6827728</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5785,7 +5775,7 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>120075137</v>
+        <v>120075065</v>
       </c>
       <c r="B52" t="n">
         <v>78542</v>
@@ -5825,10 +5815,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>478288</v>
+        <v>478169</v>
       </c>
       <c r="R52" t="n">
-        <v>6827763</v>
+        <v>6827679</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -5887,10 +5877,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>120074931</v>
+        <v>120074956</v>
       </c>
       <c r="B53" t="n">
-        <v>79160</v>
+        <v>57320</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -5903,34 +5893,39 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>6453</v>
+        <v>100109</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
+      <c r="M53" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P53" t="inlineStr">
         <is>
           <t>Hevoslamm, Dlr</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>478261</v>
+        <v>478278</v>
       </c>
       <c r="R53" t="n">
-        <v>6827822</v>
+        <v>6827832</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -5963,6 +5958,11 @@
       <c r="AA53" t="inlineStr">
         <is>
           <t>2024-09-27</t>
+        </is>
+      </c>
+      <c r="AC53" t="inlineStr">
+        <is>
+          <t>Färska ringhack (tall)</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6193,7 +6193,7 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>120075164</v>
+        <v>120075162</v>
       </c>
       <c r="B56" t="n">
         <v>78542</v>
@@ -6233,10 +6233,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>478092</v>
+        <v>478080</v>
       </c>
       <c r="R56" t="n">
-        <v>6827810</v>
+        <v>6827808</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6295,10 +6295,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>120075037</v>
+        <v>120075163</v>
       </c>
       <c r="B57" t="n">
-        <v>78278</v>
+        <v>78542</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
@@ -6311,21 +6311,21 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -6335,10 +6335,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>478265</v>
+        <v>478102</v>
       </c>
       <c r="R57" t="n">
-        <v>6827716</v>
+        <v>6827800</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6397,10 +6397,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>120074887</v>
+        <v>120075000</v>
       </c>
       <c r="B58" t="n">
-        <v>79160</v>
+        <v>78279</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
@@ -6413,21 +6413,21 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>6453</v>
+        <v>228912</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
@@ -6437,10 +6437,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>478144</v>
+        <v>478121</v>
       </c>
       <c r="R58" t="n">
-        <v>6827593</v>
+        <v>6827607</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6499,10 +6499,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>120075024</v>
+        <v>120075007</v>
       </c>
       <c r="B59" t="n">
-        <v>78278</v>
+        <v>78279</v>
       </c>
       <c r="C59" t="inlineStr">
         <is>
@@ -6515,21 +6515,21 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>6446</v>
+        <v>228912</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
@@ -6539,10 +6539,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>478165</v>
+        <v>478285</v>
       </c>
       <c r="R59" t="n">
-        <v>6827712</v>
+        <v>6827770</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6601,10 +6601,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>120074947</v>
+        <v>120075206</v>
       </c>
       <c r="B60" t="n">
-        <v>79160</v>
+        <v>78187</v>
       </c>
       <c r="C60" t="inlineStr">
         <is>
@@ -6617,21 +6617,21 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>6453</v>
+        <v>353</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
@@ -6641,10 +6641,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>478061</v>
+        <v>478125</v>
       </c>
       <c r="R60" t="n">
-        <v>6827751</v>
+        <v>6827604</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -6703,10 +6703,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>120075026</v>
+        <v>120075164</v>
       </c>
       <c r="B61" t="n">
-        <v>78278</v>
+        <v>78542</v>
       </c>
       <c r="C61" t="inlineStr">
         <is>
@@ -6719,21 +6719,21 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
@@ -6743,10 +6743,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>478161</v>
+        <v>478092</v>
       </c>
       <c r="R61" t="n">
-        <v>6827592</v>
+        <v>6827810</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -6805,10 +6805,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>120075162</v>
+        <v>120075037</v>
       </c>
       <c r="B62" t="n">
-        <v>78542</v>
+        <v>78278</v>
       </c>
       <c r="C62" t="inlineStr">
         <is>
@@ -6821,21 +6821,21 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
@@ -6845,10 +6845,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>478080</v>
+        <v>478265</v>
       </c>
       <c r="R62" t="n">
-        <v>6827808</v>
+        <v>6827716</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -6907,10 +6907,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>120075163</v>
+        <v>120074887</v>
       </c>
       <c r="B63" t="n">
-        <v>78542</v>
+        <v>79160</v>
       </c>
       <c r="C63" t="inlineStr">
         <is>
@@ -6923,21 +6923,21 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
@@ -6947,10 +6947,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>478102</v>
+        <v>478144</v>
       </c>
       <c r="R63" t="n">
-        <v>6827800</v>
+        <v>6827593</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -7009,10 +7009,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>120075000</v>
+        <v>120075024</v>
       </c>
       <c r="B64" t="n">
-        <v>78279</v>
+        <v>78278</v>
       </c>
       <c r="C64" t="inlineStr">
         <is>
@@ -7025,21 +7025,21 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>228912</v>
+        <v>6446</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
@@ -7049,10 +7049,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>478121</v>
+        <v>478165</v>
       </c>
       <c r="R64" t="n">
-        <v>6827607</v>
+        <v>6827712</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -7111,10 +7111,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>120075007</v>
+        <v>120074947</v>
       </c>
       <c r="B65" t="n">
-        <v>78279</v>
+        <v>79160</v>
       </c>
       <c r="C65" t="inlineStr">
         <is>
@@ -7127,21 +7127,21 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>228912</v>
+        <v>6453</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
@@ -7151,10 +7151,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>478285</v>
+        <v>478061</v>
       </c>
       <c r="R65" t="n">
-        <v>6827770</v>
+        <v>6827751</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7213,10 +7213,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>120075206</v>
+        <v>120075026</v>
       </c>
       <c r="B66" t="n">
-        <v>78187</v>
+        <v>78278</v>
       </c>
       <c r="C66" t="inlineStr">
         <is>
@@ -7229,21 +7229,21 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>353</v>
+        <v>6446</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
@@ -7253,10 +7253,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>478125</v>
+        <v>478161</v>
       </c>
       <c r="R66" t="n">
-        <v>6827604</v>
+        <v>6827592</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7315,10 +7315,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>120075066</v>
+        <v>120074927</v>
       </c>
       <c r="B67" t="n">
-        <v>78542</v>
+        <v>78576</v>
       </c>
       <c r="C67" t="inlineStr">
         <is>
@@ -7331,21 +7331,21 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
@@ -7355,10 +7355,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>478160</v>
+        <v>478073</v>
       </c>
       <c r="R67" t="n">
-        <v>6827680</v>
+        <v>6827836</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7417,10 +7417,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>120075138</v>
+        <v>120075231</v>
       </c>
       <c r="B68" t="n">
-        <v>78542</v>
+        <v>78187</v>
       </c>
       <c r="C68" t="inlineStr">
         <is>
@@ -7433,21 +7433,21 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>6425</v>
+        <v>353</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
@@ -7457,10 +7457,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>478294</v>
+        <v>478067</v>
       </c>
       <c r="R68" t="n">
-        <v>6827781</v>
+        <v>6827863</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7519,7 +7519,7 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>120075134</v>
+        <v>120075066</v>
       </c>
       <c r="B69" t="n">
         <v>78542</v>
@@ -7559,10 +7559,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>478266</v>
+        <v>478160</v>
       </c>
       <c r="R69" t="n">
-        <v>6827765</v>
+        <v>6827680</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -7621,10 +7621,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>120074904</v>
+        <v>120075138</v>
       </c>
       <c r="B70" t="n">
-        <v>79160</v>
+        <v>78542</v>
       </c>
       <c r="C70" t="inlineStr">
         <is>
@@ -7637,21 +7637,21 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
@@ -7661,10 +7661,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>478262</v>
+        <v>478294</v>
       </c>
       <c r="R70" t="n">
-        <v>6827730</v>
+        <v>6827781</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -7723,10 +7723,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>120074927</v>
+        <v>120075134</v>
       </c>
       <c r="B71" t="n">
-        <v>78576</v>
+        <v>78542</v>
       </c>
       <c r="C71" t="inlineStr">
         <is>
@@ -7739,21 +7739,21 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
@@ -7763,10 +7763,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>478073</v>
+        <v>478266</v>
       </c>
       <c r="R71" t="n">
-        <v>6827836</v>
+        <v>6827765</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -7825,10 +7825,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>120075231</v>
+        <v>120074904</v>
       </c>
       <c r="B72" t="n">
-        <v>78187</v>
+        <v>79160</v>
       </c>
       <c r="C72" t="inlineStr">
         <is>
@@ -7841,21 +7841,21 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>353</v>
+        <v>6453</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
@@ -7865,10 +7865,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>478067</v>
+        <v>478262</v>
       </c>
       <c r="R72" t="n">
-        <v>6827863</v>
+        <v>6827730</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -8029,10 +8029,10 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>120075048</v>
+        <v>120075130</v>
       </c>
       <c r="B74" t="n">
-        <v>56524</v>
+        <v>78542</v>
       </c>
       <c r="C74" t="inlineStr">
         <is>
@@ -8045,39 +8045,34 @@
         </is>
       </c>
       <c r="E74" t="n">
-        <v>102612</v>
+        <v>6425</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
-      <c r="M74" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
       <c r="P74" t="inlineStr">
         <is>
           <t>Hevoslamm, Dlr</t>
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>478070</v>
+        <v>478264</v>
       </c>
       <c r="R74" t="n">
-        <v>6827723</v>
+        <v>6827733</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -8136,10 +8131,10 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>120075130</v>
+        <v>120075048</v>
       </c>
       <c r="B75" t="n">
-        <v>78542</v>
+        <v>56524</v>
       </c>
       <c r="C75" t="inlineStr">
         <is>
@@ -8152,34 +8147,39 @@
         </is>
       </c>
       <c r="E75" t="n">
-        <v>6425</v>
+        <v>102612</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
+      <c r="M75" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="P75" t="inlineStr">
         <is>
           <t>Hevoslamm, Dlr</t>
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>478264</v>
+        <v>478070</v>
       </c>
       <c r="R75" t="n">
-        <v>6827733</v>
+        <v>6827723</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -10176,10 +10176,10 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>120075019</v>
+        <v>120074996</v>
       </c>
       <c r="B95" t="n">
-        <v>79623</v>
+        <v>78279</v>
       </c>
       <c r="C95" t="inlineStr">
         <is>
@@ -10192,21 +10192,21 @@
         </is>
       </c>
       <c r="E95" t="n">
-        <v>6458</v>
+        <v>228912</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I95" t="inlineStr"/>
@@ -10216,10 +10216,10 @@
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>478227</v>
+        <v>478165</v>
       </c>
       <c r="R95" t="n">
-        <v>6827655</v>
+        <v>6827712</v>
       </c>
       <c r="S95" t="n">
         <v>10</v>
@@ -10278,10 +10278,10 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>120075083</v>
+        <v>120075019</v>
       </c>
       <c r="B96" t="n">
-        <v>78542</v>
+        <v>79623</v>
       </c>
       <c r="C96" t="inlineStr">
         <is>
@@ -10294,21 +10294,21 @@
         </is>
       </c>
       <c r="E96" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I96" t="inlineStr"/>
@@ -10318,10 +10318,10 @@
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>478097</v>
+        <v>478227</v>
       </c>
       <c r="R96" t="n">
-        <v>6827527</v>
+        <v>6827655</v>
       </c>
       <c r="S96" t="n">
         <v>10</v>
@@ -10380,7 +10380,7 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>120075087</v>
+        <v>120075083</v>
       </c>
       <c r="B97" t="n">
         <v>78542</v>
@@ -10420,10 +10420,10 @@
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>478145</v>
+        <v>478097</v>
       </c>
       <c r="R97" t="n">
-        <v>6827485</v>
+        <v>6827527</v>
       </c>
       <c r="S97" t="n">
         <v>10</v>
@@ -10482,10 +10482,10 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>120074929</v>
+        <v>120075087</v>
       </c>
       <c r="B98" t="n">
-        <v>78576</v>
+        <v>78542</v>
       </c>
       <c r="C98" t="inlineStr">
         <is>
@@ -10498,21 +10498,21 @@
         </is>
       </c>
       <c r="E98" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I98" t="inlineStr"/>
@@ -10522,10 +10522,10 @@
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>478045</v>
+        <v>478145</v>
       </c>
       <c r="R98" t="n">
-        <v>6827724</v>
+        <v>6827485</v>
       </c>
       <c r="S98" t="n">
         <v>10</v>
@@ -10584,10 +10584,10 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>120075208</v>
+        <v>120074929</v>
       </c>
       <c r="B99" t="n">
-        <v>78187</v>
+        <v>78576</v>
       </c>
       <c r="C99" t="inlineStr">
         <is>
@@ -10600,21 +10600,21 @@
         </is>
       </c>
       <c r="E99" t="n">
-        <v>353</v>
+        <v>185</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I99" t="inlineStr"/>
@@ -10624,10 +10624,10 @@
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>478158</v>
+        <v>478045</v>
       </c>
       <c r="R99" t="n">
-        <v>6827519</v>
+        <v>6827724</v>
       </c>
       <c r="S99" t="n">
         <v>10</v>
@@ -10686,10 +10686,10 @@
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>120075196</v>
+        <v>120075208</v>
       </c>
       <c r="B100" t="n">
-        <v>78542</v>
+        <v>78187</v>
       </c>
       <c r="C100" t="inlineStr">
         <is>
@@ -10702,21 +10702,21 @@
         </is>
       </c>
       <c r="E100" t="n">
-        <v>6425</v>
+        <v>353</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I100" t="inlineStr"/>
@@ -10726,10 +10726,10 @@
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>478288</v>
+        <v>478158</v>
       </c>
       <c r="R100" t="n">
-        <v>6827682</v>
+        <v>6827519</v>
       </c>
       <c r="S100" t="n">
         <v>10</v>
@@ -10788,10 +10788,10 @@
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>120074946</v>
+        <v>120075196</v>
       </c>
       <c r="B101" t="n">
-        <v>79160</v>
+        <v>78542</v>
       </c>
       <c r="C101" t="inlineStr">
         <is>
@@ -10804,21 +10804,21 @@
         </is>
       </c>
       <c r="E101" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I101" t="inlineStr"/>
@@ -10828,10 +10828,10 @@
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>478056</v>
+        <v>478288</v>
       </c>
       <c r="R101" t="n">
-        <v>6827754</v>
+        <v>6827682</v>
       </c>
       <c r="S101" t="n">
         <v>10</v>
@@ -10890,10 +10890,10 @@
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>120074996</v>
+        <v>120074946</v>
       </c>
       <c r="B102" t="n">
-        <v>78279</v>
+        <v>79160</v>
       </c>
       <c r="C102" t="inlineStr">
         <is>
@@ -10906,21 +10906,21 @@
         </is>
       </c>
       <c r="E102" t="n">
-        <v>228912</v>
+        <v>6453</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I102" t="inlineStr"/>
@@ -10930,10 +10930,10 @@
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>478165</v>
+        <v>478056</v>
       </c>
       <c r="R102" t="n">
-        <v>6827712</v>
+        <v>6827754</v>
       </c>
       <c r="S102" t="n">
         <v>10</v>
@@ -10992,10 +10992,10 @@
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>120075084</v>
+        <v>120074912</v>
       </c>
       <c r="B103" t="n">
-        <v>78542</v>
+        <v>78576</v>
       </c>
       <c r="C103" t="inlineStr">
         <is>
@@ -11008,21 +11008,21 @@
         </is>
       </c>
       <c r="E103" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I103" t="inlineStr"/>
@@ -11032,10 +11032,10 @@
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>478098</v>
+        <v>478149</v>
       </c>
       <c r="R103" t="n">
-        <v>6827520</v>
+        <v>6827714</v>
       </c>
       <c r="S103" t="n">
         <v>10</v>
@@ -11094,10 +11094,10 @@
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>120074883</v>
+        <v>120075084</v>
       </c>
       <c r="B104" t="n">
-        <v>79160</v>
+        <v>78542</v>
       </c>
       <c r="C104" t="inlineStr">
         <is>
@@ -11110,21 +11110,21 @@
         </is>
       </c>
       <c r="E104" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I104" t="inlineStr"/>
@@ -11134,10 +11134,10 @@
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>478142</v>
+        <v>478098</v>
       </c>
       <c r="R104" t="n">
-        <v>6827623</v>
+        <v>6827520</v>
       </c>
       <c r="S104" t="n">
         <v>10</v>
@@ -11196,10 +11196,10 @@
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>120074912</v>
+        <v>120074883</v>
       </c>
       <c r="B105" t="n">
-        <v>78576</v>
+        <v>79160</v>
       </c>
       <c r="C105" t="inlineStr">
         <is>
@@ -11212,21 +11212,21 @@
         </is>
       </c>
       <c r="E105" t="n">
-        <v>185</v>
+        <v>6453</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I105" t="inlineStr"/>
@@ -11236,10 +11236,10 @@
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>478149</v>
+        <v>478142</v>
       </c>
       <c r="R105" t="n">
-        <v>6827714</v>
+        <v>6827623</v>
       </c>
       <c r="S105" t="n">
         <v>10</v>
@@ -12726,10 +12726,10 @@
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>120075071</v>
+        <v>120074892</v>
       </c>
       <c r="B120" t="n">
-        <v>78542</v>
+        <v>79160</v>
       </c>
       <c r="C120" t="inlineStr">
         <is>
@@ -12742,21 +12742,21 @@
         </is>
       </c>
       <c r="E120" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I120" t="inlineStr"/>
@@ -12766,10 +12766,10 @@
         </is>
       </c>
       <c r="Q120" t="n">
-        <v>478116</v>
+        <v>478243</v>
       </c>
       <c r="R120" t="n">
-        <v>6827633</v>
+        <v>6827585</v>
       </c>
       <c r="S120" t="n">
         <v>10</v>
@@ -12828,7 +12828,7 @@
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>120075078</v>
+        <v>120075135</v>
       </c>
       <c r="B121" t="n">
         <v>78542</v>
@@ -12868,10 +12868,10 @@
         </is>
       </c>
       <c r="Q121" t="n">
-        <v>478116</v>
+        <v>478291</v>
       </c>
       <c r="R121" t="n">
-        <v>6827567</v>
+        <v>6827744</v>
       </c>
       <c r="S121" t="n">
         <v>10</v>
@@ -12930,10 +12930,10 @@
     </row>
     <row r="122">
       <c r="A122" t="n">
-        <v>120075232</v>
+        <v>120075147</v>
       </c>
       <c r="B122" t="n">
-        <v>78187</v>
+        <v>78542</v>
       </c>
       <c r="C122" t="inlineStr">
         <is>
@@ -12946,21 +12946,21 @@
         </is>
       </c>
       <c r="E122" t="n">
-        <v>353</v>
+        <v>6425</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I122" t="inlineStr"/>
@@ -12970,10 +12970,10 @@
         </is>
       </c>
       <c r="Q122" t="n">
-        <v>478051</v>
+        <v>478153</v>
       </c>
       <c r="R122" t="n">
-        <v>6827739</v>
+        <v>6827728</v>
       </c>
       <c r="S122" t="n">
         <v>10</v>
@@ -13032,10 +13032,10 @@
     </row>
     <row r="123">
       <c r="A123" t="n">
-        <v>120075230</v>
+        <v>120074935</v>
       </c>
       <c r="B123" t="n">
-        <v>78187</v>
+        <v>79160</v>
       </c>
       <c r="C123" t="inlineStr">
         <is>
@@ -13048,21 +13048,21 @@
         </is>
       </c>
       <c r="E123" t="n">
-        <v>353</v>
+        <v>6453</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I123" t="inlineStr"/>
@@ -13072,10 +13072,10 @@
         </is>
       </c>
       <c r="Q123" t="n">
-        <v>478064</v>
+        <v>478150</v>
       </c>
       <c r="R123" t="n">
-        <v>6827866</v>
+        <v>6827745</v>
       </c>
       <c r="S123" t="n">
         <v>10</v>
@@ -13134,7 +13134,7 @@
     </row>
     <row r="124">
       <c r="A124" t="n">
-        <v>120075214</v>
+        <v>120075232</v>
       </c>
       <c r="B124" t="n">
         <v>78187</v>
@@ -13174,10 +13174,10 @@
         </is>
       </c>
       <c r="Q124" t="n">
-        <v>478266</v>
+        <v>478051</v>
       </c>
       <c r="R124" t="n">
-        <v>6827724</v>
+        <v>6827739</v>
       </c>
       <c r="S124" t="n">
         <v>10</v>
@@ -13236,7 +13236,7 @@
     </row>
     <row r="125">
       <c r="A125" t="n">
-        <v>120075207</v>
+        <v>120075230</v>
       </c>
       <c r="B125" t="n">
         <v>78187</v>
@@ -13276,10 +13276,10 @@
         </is>
       </c>
       <c r="Q125" t="n">
-        <v>478157</v>
+        <v>478064</v>
       </c>
       <c r="R125" t="n">
-        <v>6827509</v>
+        <v>6827866</v>
       </c>
       <c r="S125" t="n">
         <v>10</v>
@@ -13338,10 +13338,10 @@
     </row>
     <row r="126">
       <c r="A126" t="n">
-        <v>120074892</v>
+        <v>120075214</v>
       </c>
       <c r="B126" t="n">
-        <v>79160</v>
+        <v>78187</v>
       </c>
       <c r="C126" t="inlineStr">
         <is>
@@ -13354,21 +13354,21 @@
         </is>
       </c>
       <c r="E126" t="n">
-        <v>6453</v>
+        <v>353</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H126" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I126" t="inlineStr"/>
@@ -13378,10 +13378,10 @@
         </is>
       </c>
       <c r="Q126" t="n">
-        <v>478243</v>
+        <v>478266</v>
       </c>
       <c r="R126" t="n">
-        <v>6827585</v>
+        <v>6827724</v>
       </c>
       <c r="S126" t="n">
         <v>10</v>
@@ -13440,10 +13440,10 @@
     </row>
     <row r="127">
       <c r="A127" t="n">
-        <v>120075135</v>
+        <v>120075207</v>
       </c>
       <c r="B127" t="n">
-        <v>78542</v>
+        <v>78187</v>
       </c>
       <c r="C127" t="inlineStr">
         <is>
@@ -13456,21 +13456,21 @@
         </is>
       </c>
       <c r="E127" t="n">
-        <v>6425</v>
+        <v>353</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H127" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I127" t="inlineStr"/>
@@ -13480,10 +13480,10 @@
         </is>
       </c>
       <c r="Q127" t="n">
-        <v>478291</v>
+        <v>478157</v>
       </c>
       <c r="R127" t="n">
-        <v>6827744</v>
+        <v>6827509</v>
       </c>
       <c r="S127" t="n">
         <v>10</v>
@@ -13542,10 +13542,10 @@
     </row>
     <row r="128">
       <c r="A128" t="n">
-        <v>120075147</v>
+        <v>120075198</v>
       </c>
       <c r="B128" t="n">
-        <v>78542</v>
+        <v>91858</v>
       </c>
       <c r="C128" t="inlineStr">
         <is>
@@ -13554,25 +13554,25 @@
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E128" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H128" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I128" t="inlineStr"/>
@@ -13582,10 +13582,10 @@
         </is>
       </c>
       <c r="Q128" t="n">
-        <v>478153</v>
+        <v>478163</v>
       </c>
       <c r="R128" t="n">
-        <v>6827728</v>
+        <v>6827530</v>
       </c>
       <c r="S128" t="n">
         <v>10</v>
@@ -13644,10 +13644,10 @@
     </row>
     <row r="129">
       <c r="A129" t="n">
-        <v>120074935</v>
+        <v>120075071</v>
       </c>
       <c r="B129" t="n">
-        <v>79160</v>
+        <v>78542</v>
       </c>
       <c r="C129" t="inlineStr">
         <is>
@@ -13660,21 +13660,21 @@
         </is>
       </c>
       <c r="E129" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H129" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I129" t="inlineStr"/>
@@ -13684,10 +13684,10 @@
         </is>
       </c>
       <c r="Q129" t="n">
-        <v>478150</v>
+        <v>478116</v>
       </c>
       <c r="R129" t="n">
-        <v>6827745</v>
+        <v>6827633</v>
       </c>
       <c r="S129" t="n">
         <v>10</v>
@@ -13746,10 +13746,10 @@
     </row>
     <row r="130">
       <c r="A130" t="n">
-        <v>120075198</v>
+        <v>120075078</v>
       </c>
       <c r="B130" t="n">
-        <v>91858</v>
+        <v>78542</v>
       </c>
       <c r="C130" t="inlineStr">
         <is>
@@ -13758,25 +13758,25 @@
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E130" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H130" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I130" t="inlineStr"/>
@@ -13786,10 +13786,10 @@
         </is>
       </c>
       <c r="Q130" t="n">
-        <v>478163</v>
+        <v>478116</v>
       </c>
       <c r="R130" t="n">
-        <v>6827530</v>
+        <v>6827567</v>
       </c>
       <c r="S130" t="n">
         <v>10</v>
@@ -16194,10 +16194,10 @@
     </row>
     <row r="154">
       <c r="A154" t="n">
-        <v>120075010</v>
+        <v>120075219</v>
       </c>
       <c r="B154" t="n">
-        <v>78279</v>
+        <v>78187</v>
       </c>
       <c r="C154" t="inlineStr">
         <is>
@@ -16210,21 +16210,21 @@
         </is>
       </c>
       <c r="E154" t="n">
-        <v>228912</v>
+        <v>353</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G154" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H154" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I154" t="inlineStr"/>
@@ -16234,10 +16234,10 @@
         </is>
       </c>
       <c r="Q154" t="n">
-        <v>478074</v>
+        <v>478169</v>
       </c>
       <c r="R154" t="n">
-        <v>6827772</v>
+        <v>6827760</v>
       </c>
       <c r="S154" t="n">
         <v>10</v>
@@ -16296,10 +16296,10 @@
     </row>
     <row r="155">
       <c r="A155" t="n">
-        <v>120075219</v>
+        <v>120075064</v>
       </c>
       <c r="B155" t="n">
-        <v>78187</v>
+        <v>78542</v>
       </c>
       <c r="C155" t="inlineStr">
         <is>
@@ -16312,21 +16312,21 @@
         </is>
       </c>
       <c r="E155" t="n">
-        <v>353</v>
+        <v>6425</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G155" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H155" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I155" t="inlineStr"/>
@@ -16336,10 +16336,10 @@
         </is>
       </c>
       <c r="Q155" t="n">
-        <v>478169</v>
+        <v>478192</v>
       </c>
       <c r="R155" t="n">
-        <v>6827760</v>
+        <v>6827690</v>
       </c>
       <c r="S155" t="n">
         <v>10</v>
@@ -16398,10 +16398,10 @@
     </row>
     <row r="156">
       <c r="A156" t="n">
-        <v>120075015</v>
+        <v>120074886</v>
       </c>
       <c r="B156" t="n">
-        <v>79623</v>
+        <v>79160</v>
       </c>
       <c r="C156" t="inlineStr">
         <is>
@@ -16414,21 +16414,21 @@
         </is>
       </c>
       <c r="E156" t="n">
-        <v>6458</v>
+        <v>6453</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G156" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H156" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I156" t="inlineStr"/>
@@ -16438,10 +16438,10 @@
         </is>
       </c>
       <c r="Q156" t="n">
-        <v>478114</v>
+        <v>478125</v>
       </c>
       <c r="R156" t="n">
-        <v>6827633</v>
+        <v>6827604</v>
       </c>
       <c r="S156" t="n">
         <v>10</v>
@@ -16500,10 +16500,10 @@
     </row>
     <row r="157">
       <c r="A157" t="n">
-        <v>120075239</v>
+        <v>120075159</v>
       </c>
       <c r="B157" t="n">
-        <v>77474</v>
+        <v>78542</v>
       </c>
       <c r="C157" t="inlineStr">
         <is>
@@ -16516,21 +16516,21 @@
         </is>
       </c>
       <c r="E157" t="n">
-        <v>6487</v>
+        <v>6425</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t>Blågrå svartspik</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G157" t="inlineStr">
         <is>
-          <t>Chaenothecopsis fennica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H157" t="inlineStr">
         <is>
-          <t>(Laurila) Tibell</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I157" t="inlineStr"/>
@@ -16540,10 +16540,10 @@
         </is>
       </c>
       <c r="Q157" t="n">
-        <v>478137</v>
+        <v>478100</v>
       </c>
       <c r="R157" t="n">
-        <v>6827554</v>
+        <v>6827729</v>
       </c>
       <c r="S157" t="n">
         <v>10</v>
@@ -16602,10 +16602,10 @@
     </row>
     <row r="158">
       <c r="A158" t="n">
-        <v>120075064</v>
+        <v>120075040</v>
       </c>
       <c r="B158" t="n">
-        <v>78542</v>
+        <v>78278</v>
       </c>
       <c r="C158" t="inlineStr">
         <is>
@@ -16618,21 +16618,21 @@
         </is>
       </c>
       <c r="E158" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G158" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H158" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I158" t="inlineStr"/>
@@ -16642,10 +16642,10 @@
         </is>
       </c>
       <c r="Q158" t="n">
-        <v>478192</v>
+        <v>478250</v>
       </c>
       <c r="R158" t="n">
-        <v>6827690</v>
+        <v>6827802</v>
       </c>
       <c r="S158" t="n">
         <v>10</v>
@@ -16704,7 +16704,7 @@
     </row>
     <row r="159">
       <c r="A159" t="n">
-        <v>120074886</v>
+        <v>120074944</v>
       </c>
       <c r="B159" t="n">
         <v>79160</v>
@@ -16744,10 +16744,10 @@
         </is>
       </c>
       <c r="Q159" t="n">
-        <v>478125</v>
+        <v>478056</v>
       </c>
       <c r="R159" t="n">
-        <v>6827604</v>
+        <v>6827785</v>
       </c>
       <c r="S159" t="n">
         <v>10</v>
@@ -16806,10 +16806,10 @@
     </row>
     <row r="160">
       <c r="A160" t="n">
-        <v>120075159</v>
+        <v>120075025</v>
       </c>
       <c r="B160" t="n">
-        <v>78542</v>
+        <v>78278</v>
       </c>
       <c r="C160" t="inlineStr">
         <is>
@@ -16822,21 +16822,21 @@
         </is>
       </c>
       <c r="E160" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G160" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H160" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I160" t="inlineStr"/>
@@ -16846,10 +16846,10 @@
         </is>
       </c>
       <c r="Q160" t="n">
-        <v>478100</v>
+        <v>478171</v>
       </c>
       <c r="R160" t="n">
-        <v>6827729</v>
+        <v>6827642</v>
       </c>
       <c r="S160" t="n">
         <v>10</v>
@@ -16908,7 +16908,7 @@
     </row>
     <row r="161">
       <c r="A161" t="n">
-        <v>120075040</v>
+        <v>120075039</v>
       </c>
       <c r="B161" t="n">
         <v>78278</v>
@@ -16948,10 +16948,10 @@
         </is>
       </c>
       <c r="Q161" t="n">
-        <v>478250</v>
+        <v>478238</v>
       </c>
       <c r="R161" t="n">
-        <v>6827802</v>
+        <v>6827752</v>
       </c>
       <c r="S161" t="n">
         <v>10</v>
@@ -17010,10 +17010,10 @@
     </row>
     <row r="162">
       <c r="A162" t="n">
-        <v>120074944</v>
+        <v>120075035</v>
       </c>
       <c r="B162" t="n">
-        <v>79160</v>
+        <v>78278</v>
       </c>
       <c r="C162" t="inlineStr">
         <is>
@@ -17026,21 +17026,21 @@
         </is>
       </c>
       <c r="E162" t="n">
-        <v>6453</v>
+        <v>6446</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G162" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H162" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I162" t="inlineStr"/>
@@ -17050,10 +17050,10 @@
         </is>
       </c>
       <c r="Q162" t="n">
-        <v>478056</v>
+        <v>478273</v>
       </c>
       <c r="R162" t="n">
-        <v>6827785</v>
+        <v>6827711</v>
       </c>
       <c r="S162" t="n">
         <v>10</v>
@@ -17112,10 +17112,10 @@
     </row>
     <row r="163">
       <c r="A163" t="n">
-        <v>120075025</v>
+        <v>120075127</v>
       </c>
       <c r="B163" t="n">
-        <v>78278</v>
+        <v>78542</v>
       </c>
       <c r="C163" t="inlineStr">
         <is>
@@ -17128,21 +17128,21 @@
         </is>
       </c>
       <c r="E163" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G163" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H163" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I163" t="inlineStr"/>
@@ -17152,10 +17152,10 @@
         </is>
       </c>
       <c r="Q163" t="n">
-        <v>478171</v>
+        <v>478292</v>
       </c>
       <c r="R163" t="n">
-        <v>6827642</v>
+        <v>6827708</v>
       </c>
       <c r="S163" t="n">
         <v>10</v>
@@ -17214,10 +17214,10 @@
     </row>
     <row r="164">
       <c r="A164" t="n">
-        <v>120075039</v>
+        <v>120074889</v>
       </c>
       <c r="B164" t="n">
-        <v>78278</v>
+        <v>79160</v>
       </c>
       <c r="C164" t="inlineStr">
         <is>
@@ -17230,21 +17230,21 @@
         </is>
       </c>
       <c r="E164" t="n">
-        <v>6446</v>
+        <v>6453</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G164" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H164" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I164" t="inlineStr"/>
@@ -17254,10 +17254,10 @@
         </is>
       </c>
       <c r="Q164" t="n">
-        <v>478238</v>
+        <v>478163</v>
       </c>
       <c r="R164" t="n">
-        <v>6827752</v>
+        <v>6827536</v>
       </c>
       <c r="S164" t="n">
         <v>10</v>
@@ -17316,10 +17316,10 @@
     </row>
     <row r="165">
       <c r="A165" t="n">
-        <v>120075035</v>
+        <v>120075161</v>
       </c>
       <c r="B165" t="n">
-        <v>78278</v>
+        <v>78542</v>
       </c>
       <c r="C165" t="inlineStr">
         <is>
@@ -17332,21 +17332,21 @@
         </is>
       </c>
       <c r="E165" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G165" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H165" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I165" t="inlineStr"/>
@@ -17356,10 +17356,10 @@
         </is>
       </c>
       <c r="Q165" t="n">
-        <v>478273</v>
+        <v>478082</v>
       </c>
       <c r="R165" t="n">
-        <v>6827711</v>
+        <v>6827766</v>
       </c>
       <c r="S165" t="n">
         <v>10</v>
@@ -17418,7 +17418,7 @@
     </row>
     <row r="166">
       <c r="A166" t="n">
-        <v>120075127</v>
+        <v>120075121</v>
       </c>
       <c r="B166" t="n">
         <v>78542</v>
@@ -17458,10 +17458,10 @@
         </is>
       </c>
       <c r="Q166" t="n">
-        <v>478292</v>
+        <v>478232</v>
       </c>
       <c r="R166" t="n">
-        <v>6827708</v>
+        <v>6827659</v>
       </c>
       <c r="S166" t="n">
         <v>10</v>
@@ -17520,10 +17520,10 @@
     </row>
     <row r="167">
       <c r="A167" t="n">
-        <v>120074889</v>
+        <v>120075015</v>
       </c>
       <c r="B167" t="n">
-        <v>79160</v>
+        <v>79623</v>
       </c>
       <c r="C167" t="inlineStr">
         <is>
@@ -17536,21 +17536,21 @@
         </is>
       </c>
       <c r="E167" t="n">
-        <v>6453</v>
+        <v>6458</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G167" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H167" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I167" t="inlineStr"/>
@@ -17560,10 +17560,10 @@
         </is>
       </c>
       <c r="Q167" t="n">
-        <v>478163</v>
+        <v>478114</v>
       </c>
       <c r="R167" t="n">
-        <v>6827536</v>
+        <v>6827633</v>
       </c>
       <c r="S167" t="n">
         <v>10</v>
@@ -17622,10 +17622,10 @@
     </row>
     <row r="168">
       <c r="A168" t="n">
-        <v>120075061</v>
+        <v>120075239</v>
       </c>
       <c r="B168" t="n">
-        <v>78542</v>
+        <v>77474</v>
       </c>
       <c r="C168" t="inlineStr">
         <is>
@@ -17638,21 +17638,21 @@
         </is>
       </c>
       <c r="E168" t="n">
-        <v>6425</v>
+        <v>6487</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Blågrå svartspik</t>
         </is>
       </c>
       <c r="G168" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenothecopsis fennica</t>
         </is>
       </c>
       <c r="H168" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Laurila) Tibell</t>
         </is>
       </c>
       <c r="I168" t="inlineStr"/>
@@ -17662,10 +17662,10 @@
         </is>
       </c>
       <c r="Q168" t="n">
-        <v>478160</v>
+        <v>478137</v>
       </c>
       <c r="R168" t="n">
-        <v>6827710</v>
+        <v>6827554</v>
       </c>
       <c r="S168" t="n">
         <v>10</v>
@@ -17724,7 +17724,7 @@
     </row>
     <row r="169">
       <c r="A169" t="n">
-        <v>120075161</v>
+        <v>120075061</v>
       </c>
       <c r="B169" t="n">
         <v>78542</v>
@@ -17764,10 +17764,10 @@
         </is>
       </c>
       <c r="Q169" t="n">
-        <v>478082</v>
+        <v>478160</v>
       </c>
       <c r="R169" t="n">
-        <v>6827766</v>
+        <v>6827710</v>
       </c>
       <c r="S169" t="n">
         <v>10</v>
@@ -17826,10 +17826,10 @@
     </row>
     <row r="170">
       <c r="A170" t="n">
-        <v>120075121</v>
+        <v>120075010</v>
       </c>
       <c r="B170" t="n">
-        <v>78542</v>
+        <v>78279</v>
       </c>
       <c r="C170" t="inlineStr">
         <is>
@@ -17842,21 +17842,21 @@
         </is>
       </c>
       <c r="E170" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G170" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H170" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I170" t="inlineStr"/>
@@ -17866,10 +17866,10 @@
         </is>
       </c>
       <c r="Q170" t="n">
-        <v>478232</v>
+        <v>478074</v>
       </c>
       <c r="R170" t="n">
-        <v>6827659</v>
+        <v>6827772</v>
       </c>
       <c r="S170" t="n">
         <v>10</v>
@@ -17928,10 +17928,10 @@
     </row>
     <row r="171">
       <c r="A171" t="n">
-        <v>120074939</v>
+        <v>120075197</v>
       </c>
       <c r="B171" t="n">
-        <v>79160</v>
+        <v>91858</v>
       </c>
       <c r="C171" t="inlineStr">
         <is>
@@ -17940,38 +17940,47 @@
       </c>
       <c r="D171" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E171" t="n">
-        <v>6453</v>
+        <v>4364</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G171" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H171" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
-        </is>
-      </c>
-      <c r="I171" t="inlineStr"/>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I171" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J171" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="P171" t="inlineStr">
         <is>
           <t>Hevoslamm, Dlr</t>
         </is>
       </c>
       <c r="Q171" t="n">
-        <v>478091</v>
+        <v>478077</v>
       </c>
       <c r="R171" t="n">
-        <v>6827838</v>
+        <v>6827805</v>
       </c>
       <c r="S171" t="n">
         <v>10</v>
@@ -18030,10 +18039,10 @@
     </row>
     <row r="172">
       <c r="A172" t="n">
-        <v>120075027</v>
+        <v>120074915</v>
       </c>
       <c r="B172" t="n">
-        <v>78278</v>
+        <v>78576</v>
       </c>
       <c r="C172" t="inlineStr">
         <is>
@@ -18046,21 +18055,21 @@
         </is>
       </c>
       <c r="E172" t="n">
-        <v>6446</v>
+        <v>185</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G172" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H172" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I172" t="inlineStr"/>
@@ -18070,10 +18079,10 @@
         </is>
       </c>
       <c r="Q172" t="n">
-        <v>478144</v>
+        <v>478102</v>
       </c>
       <c r="R172" t="n">
-        <v>6827593</v>
+        <v>6827555</v>
       </c>
       <c r="S172" t="n">
         <v>10</v>
@@ -18132,10 +18141,10 @@
     </row>
     <row r="173">
       <c r="A173" t="n">
-        <v>120074941</v>
+        <v>120074925</v>
       </c>
       <c r="B173" t="n">
-        <v>79160</v>
+        <v>78576</v>
       </c>
       <c r="C173" t="inlineStr">
         <is>
@@ -18148,21 +18157,21 @@
         </is>
       </c>
       <c r="E173" t="n">
-        <v>6453</v>
+        <v>185</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G173" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H173" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I173" t="inlineStr"/>
@@ -18172,10 +18181,10 @@
         </is>
       </c>
       <c r="Q173" t="n">
-        <v>478069</v>
+        <v>478088</v>
       </c>
       <c r="R173" t="n">
-        <v>6827854</v>
+        <v>6827834</v>
       </c>
       <c r="S173" t="n">
         <v>10</v>
@@ -18234,10 +18243,10 @@
     </row>
     <row r="174">
       <c r="A174" t="n">
-        <v>120075088</v>
+        <v>120075227</v>
       </c>
       <c r="B174" t="n">
-        <v>78542</v>
+        <v>78187</v>
       </c>
       <c r="C174" t="inlineStr">
         <is>
@@ -18250,21 +18259,21 @@
         </is>
       </c>
       <c r="E174" t="n">
-        <v>6425</v>
+        <v>353</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G174" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H174" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I174" t="inlineStr"/>
@@ -18274,10 +18283,10 @@
         </is>
       </c>
       <c r="Q174" t="n">
-        <v>478151</v>
+        <v>478088</v>
       </c>
       <c r="R174" t="n">
-        <v>6827509</v>
+        <v>6827834</v>
       </c>
       <c r="S174" t="n">
         <v>10</v>
@@ -18336,10 +18345,10 @@
     </row>
     <row r="175">
       <c r="A175" t="n">
-        <v>120074891</v>
+        <v>120075202</v>
       </c>
       <c r="B175" t="n">
-        <v>79160</v>
+        <v>78187</v>
       </c>
       <c r="C175" t="inlineStr">
         <is>
@@ -18352,21 +18361,21 @@
         </is>
       </c>
       <c r="E175" t="n">
-        <v>6453</v>
+        <v>353</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G175" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H175" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I175" t="inlineStr"/>
@@ -18376,10 +18385,10 @@
         </is>
       </c>
       <c r="Q175" t="n">
-        <v>478212</v>
+        <v>478218</v>
       </c>
       <c r="R175" t="n">
-        <v>6827573</v>
+        <v>6827721</v>
       </c>
       <c r="S175" t="n">
         <v>10</v>
@@ -18438,10 +18447,10 @@
     </row>
     <row r="176">
       <c r="A176" t="n">
-        <v>120075165</v>
+        <v>120074939</v>
       </c>
       <c r="B176" t="n">
-        <v>78542</v>
+        <v>79160</v>
       </c>
       <c r="C176" t="inlineStr">
         <is>
@@ -18454,21 +18463,21 @@
         </is>
       </c>
       <c r="E176" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G176" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H176" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I176" t="inlineStr"/>
@@ -18478,10 +18487,10 @@
         </is>
       </c>
       <c r="Q176" t="n">
-        <v>478078</v>
+        <v>478091</v>
       </c>
       <c r="R176" t="n">
-        <v>6827834</v>
+        <v>6827838</v>
       </c>
       <c r="S176" t="n">
         <v>10</v>
@@ -18540,10 +18549,10 @@
     </row>
     <row r="177">
       <c r="A177" t="n">
-        <v>120074915</v>
+        <v>120075027</v>
       </c>
       <c r="B177" t="n">
-        <v>78576</v>
+        <v>78278</v>
       </c>
       <c r="C177" t="inlineStr">
         <is>
@@ -18556,21 +18565,21 @@
         </is>
       </c>
       <c r="E177" t="n">
-        <v>185</v>
+        <v>6446</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G177" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H177" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I177" t="inlineStr"/>
@@ -18580,10 +18589,10 @@
         </is>
       </c>
       <c r="Q177" t="n">
-        <v>478102</v>
+        <v>478144</v>
       </c>
       <c r="R177" t="n">
-        <v>6827555</v>
+        <v>6827593</v>
       </c>
       <c r="S177" t="n">
         <v>10</v>
@@ -18642,10 +18651,10 @@
     </row>
     <row r="178">
       <c r="A178" t="n">
-        <v>120074925</v>
+        <v>120074941</v>
       </c>
       <c r="B178" t="n">
-        <v>78576</v>
+        <v>79160</v>
       </c>
       <c r="C178" t="inlineStr">
         <is>
@@ -18658,21 +18667,21 @@
         </is>
       </c>
       <c r="E178" t="n">
-        <v>185</v>
+        <v>6453</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G178" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H178" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I178" t="inlineStr"/>
@@ -18682,10 +18691,10 @@
         </is>
       </c>
       <c r="Q178" t="n">
-        <v>478088</v>
+        <v>478069</v>
       </c>
       <c r="R178" t="n">
-        <v>6827834</v>
+        <v>6827854</v>
       </c>
       <c r="S178" t="n">
         <v>10</v>
@@ -18744,10 +18753,10 @@
     </row>
     <row r="179">
       <c r="A179" t="n">
-        <v>120075227</v>
+        <v>120075088</v>
       </c>
       <c r="B179" t="n">
-        <v>78187</v>
+        <v>78542</v>
       </c>
       <c r="C179" t="inlineStr">
         <is>
@@ -18760,21 +18769,21 @@
         </is>
       </c>
       <c r="E179" t="n">
-        <v>353</v>
+        <v>6425</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G179" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H179" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I179" t="inlineStr"/>
@@ -18784,10 +18793,10 @@
         </is>
       </c>
       <c r="Q179" t="n">
-        <v>478088</v>
+        <v>478151</v>
       </c>
       <c r="R179" t="n">
-        <v>6827834</v>
+        <v>6827509</v>
       </c>
       <c r="S179" t="n">
         <v>10</v>
@@ -18846,10 +18855,10 @@
     </row>
     <row r="180">
       <c r="A180" t="n">
-        <v>120075202</v>
+        <v>120074891</v>
       </c>
       <c r="B180" t="n">
-        <v>78187</v>
+        <v>79160</v>
       </c>
       <c r="C180" t="inlineStr">
         <is>
@@ -18862,21 +18871,21 @@
         </is>
       </c>
       <c r="E180" t="n">
-        <v>353</v>
+        <v>6453</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G180" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H180" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I180" t="inlineStr"/>
@@ -18886,10 +18895,10 @@
         </is>
       </c>
       <c r="Q180" t="n">
-        <v>478218</v>
+        <v>478212</v>
       </c>
       <c r="R180" t="n">
-        <v>6827721</v>
+        <v>6827573</v>
       </c>
       <c r="S180" t="n">
         <v>10</v>
@@ -18948,10 +18957,10 @@
     </row>
     <row r="181">
       <c r="A181" t="n">
-        <v>120075197</v>
+        <v>120075165</v>
       </c>
       <c r="B181" t="n">
-        <v>91858</v>
+        <v>78542</v>
       </c>
       <c r="C181" t="inlineStr">
         <is>
@@ -18960,47 +18969,38 @@
       </c>
       <c r="D181" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E181" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G181" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H181" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I181" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J181" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I181" t="inlineStr"/>
       <c r="P181" t="inlineStr">
         <is>
           <t>Hevoslamm, Dlr</t>
         </is>
       </c>
       <c r="Q181" t="n">
-        <v>478077</v>
+        <v>478078</v>
       </c>
       <c r="R181" t="n">
-        <v>6827805</v>
+        <v>6827834</v>
       </c>
       <c r="S181" t="n">
         <v>10</v>

--- a/artfynd/A 32983-2023 artfynd.xlsx
+++ b/artfynd/A 32983-2023 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>120074986</v>
+        <v>120075012</v>
       </c>
       <c r="B2" t="n">
-        <v>79624</v>
+        <v>78279</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>2081</v>
+        <v>228912</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>478096</v>
+        <v>478055</v>
       </c>
       <c r="R2" t="n">
-        <v>6827549</v>
+        <v>6827786</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -777,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>120074930</v>
+        <v>120075159</v>
       </c>
       <c r="B3" t="n">
-        <v>79160</v>
+        <v>78542</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -793,21 +793,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -817,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>478299</v>
+        <v>478100</v>
       </c>
       <c r="R3" t="n">
-        <v>6827805</v>
+        <v>6827729</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -879,7 +879,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>120075085</v>
+        <v>120075146</v>
       </c>
       <c r="B4" t="n">
         <v>78542</v>
@@ -919,10 +919,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>478094</v>
+        <v>478154</v>
       </c>
       <c r="R4" t="n">
-        <v>6827504</v>
+        <v>6827747</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -981,7 +981,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>120075157</v>
+        <v>120075161</v>
       </c>
       <c r="B5" t="n">
         <v>78542</v>
@@ -1021,10 +1021,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>478103</v>
+        <v>478082</v>
       </c>
       <c r="R5" t="n">
-        <v>6827718</v>
+        <v>6827766</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1083,7 +1083,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>120075216</v>
+        <v>120075201</v>
       </c>
       <c r="B6" t="n">
         <v>78187</v>
@@ -1123,10 +1123,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>478294</v>
+        <v>478182</v>
       </c>
       <c r="R6" t="n">
-        <v>6827790</v>
+        <v>6827728</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1185,7 +1185,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>120074928</v>
+        <v>120074922</v>
       </c>
       <c r="B7" t="n">
         <v>78576</v>
@@ -1225,10 +1225,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>478059</v>
+        <v>478103</v>
       </c>
       <c r="R7" t="n">
-        <v>6827740</v>
+        <v>6827718</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1287,10 +1287,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>120074882</v>
+        <v>120075165</v>
       </c>
       <c r="B8" t="n">
-        <v>79160</v>
+        <v>78542</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1303,21 +1303,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1327,10 +1327,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>478162</v>
+        <v>478078</v>
       </c>
       <c r="R8" t="n">
-        <v>6827593</v>
+        <v>6827834</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1389,7 +1389,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>120075097</v>
+        <v>120075166</v>
       </c>
       <c r="B9" t="n">
         <v>78542</v>
@@ -1429,10 +1429,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>478248</v>
+        <v>478092</v>
       </c>
       <c r="R9" t="n">
-        <v>6827593</v>
+        <v>6827839</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1491,7 +1491,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>120075140</v>
+        <v>120075090</v>
       </c>
       <c r="B10" t="n">
         <v>78542</v>
@@ -1531,10 +1531,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>478310</v>
+        <v>478161</v>
       </c>
       <c r="R10" t="n">
-        <v>6827797</v>
+        <v>6827528</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1593,10 +1593,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>120075226</v>
+        <v>120075094</v>
       </c>
       <c r="B11" t="n">
-        <v>78187</v>
+        <v>78542</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1609,21 +1609,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>353</v>
+        <v>6425</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1633,10 +1633,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>478098</v>
+        <v>478205</v>
       </c>
       <c r="R11" t="n">
-        <v>6827815</v>
+        <v>6827556</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1695,10 +1695,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>120074922</v>
+        <v>120075083</v>
       </c>
       <c r="B12" t="n">
-        <v>78576</v>
+        <v>78542</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1711,21 +1711,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1735,10 +1735,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>478103</v>
+        <v>478097</v>
       </c>
       <c r="R12" t="n">
-        <v>6827718</v>
+        <v>6827527</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1797,7 +1797,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>120075129</v>
+        <v>120075171</v>
       </c>
       <c r="B13" t="n">
         <v>78542</v>
@@ -1837,10 +1837,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>478265</v>
+        <v>478073</v>
       </c>
       <c r="R13" t="n">
-        <v>6827707</v>
+        <v>6827831</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1899,10 +1899,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>120075120</v>
+        <v>120074888</v>
       </c>
       <c r="B14" t="n">
-        <v>78542</v>
+        <v>79160</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1915,21 +1915,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1939,10 +1939,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>478223</v>
+        <v>478139</v>
       </c>
       <c r="R14" t="n">
-        <v>6827657</v>
+        <v>6827554</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2001,10 +2001,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>120075075</v>
+        <v>120074885</v>
       </c>
       <c r="B15" t="n">
-        <v>78542</v>
+        <v>79160</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2017,21 +2017,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2041,10 +2041,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>478139</v>
+        <v>478115</v>
       </c>
       <c r="R15" t="n">
-        <v>6827554</v>
+        <v>6827614</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2103,10 +2103,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>120075063</v>
+        <v>120074952</v>
       </c>
       <c r="B16" t="n">
-        <v>78542</v>
+        <v>79131</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2119,21 +2119,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6425</v>
+        <v>229821</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2143,10 +2143,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>478201</v>
+        <v>478120</v>
       </c>
       <c r="R16" t="n">
-        <v>6827693</v>
+        <v>6827605</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2205,10 +2205,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>120075146</v>
+        <v>120074886</v>
       </c>
       <c r="B17" t="n">
-        <v>78542</v>
+        <v>79160</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2221,21 +2221,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2245,10 +2245,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>478154</v>
+        <v>478125</v>
       </c>
       <c r="R17" t="n">
-        <v>6827747</v>
+        <v>6827604</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2307,10 +2307,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>120075131</v>
+        <v>120074943</v>
       </c>
       <c r="B18" t="n">
-        <v>78542</v>
+        <v>79160</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2323,21 +2323,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2347,10 +2347,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>478258</v>
+        <v>478073</v>
       </c>
       <c r="R18" t="n">
-        <v>6827731</v>
+        <v>6827827</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2409,10 +2409,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>120075077</v>
+        <v>120075242</v>
       </c>
       <c r="B19" t="n">
-        <v>78542</v>
+        <v>77926</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2425,21 +2425,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6425</v>
+        <v>6437</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2449,10 +2449,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>478124</v>
+        <v>478136</v>
       </c>
       <c r="R19" t="n">
-        <v>6827560</v>
+        <v>6827556</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2511,7 +2511,7 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>120075174</v>
+        <v>120075065</v>
       </c>
       <c r="B20" t="n">
         <v>78542</v>
@@ -2551,10 +2551,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>478057</v>
+        <v>478169</v>
       </c>
       <c r="R20" t="n">
-        <v>6827749</v>
+        <v>6827679</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2613,10 +2613,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>120075001</v>
+        <v>120075203</v>
       </c>
       <c r="B21" t="n">
-        <v>78279</v>
+        <v>78187</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2629,21 +2629,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>228912</v>
+        <v>353</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2656,7 +2656,7 @@
         <v>478125</v>
       </c>
       <c r="R21" t="n">
-        <v>6827604</v>
+        <v>6827631</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2715,10 +2715,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>120075009</v>
+        <v>120075225</v>
       </c>
       <c r="B22" t="n">
-        <v>78279</v>
+        <v>78187</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2731,21 +2731,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>228912</v>
+        <v>353</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2755,10 +2755,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>478151</v>
+        <v>478075</v>
       </c>
       <c r="R22" t="n">
-        <v>6827745</v>
+        <v>6827798</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2817,10 +2817,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>120075004</v>
+        <v>120075162</v>
       </c>
       <c r="B23" t="n">
-        <v>78279</v>
+        <v>78542</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -2833,21 +2833,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2857,10 +2857,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>478212</v>
+        <v>478080</v>
       </c>
       <c r="R23" t="n">
-        <v>6827573</v>
+        <v>6827808</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2919,10 +2919,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>120075003</v>
+        <v>120075089</v>
       </c>
       <c r="B24" t="n">
-        <v>78279</v>
+        <v>78542</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -2935,21 +2935,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -2959,10 +2959,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>478137</v>
+        <v>478153</v>
       </c>
       <c r="R24" t="n">
-        <v>6827553</v>
+        <v>6827517</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3021,7 +3021,7 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>120075132</v>
+        <v>120075147</v>
       </c>
       <c r="B25" t="n">
         <v>78542</v>
@@ -3061,10 +3061,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>478240</v>
+        <v>478153</v>
       </c>
       <c r="R25" t="n">
-        <v>6827754</v>
+        <v>6827728</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3123,10 +3123,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>120075062</v>
+        <v>120074998</v>
       </c>
       <c r="B26" t="n">
-        <v>78542</v>
+        <v>78279</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3139,21 +3139,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3163,10 +3163,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>478221</v>
+        <v>478172</v>
       </c>
       <c r="R26" t="n">
-        <v>6827719</v>
+        <v>6827640</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3225,10 +3225,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>120074932</v>
+        <v>120075009</v>
       </c>
       <c r="B27" t="n">
-        <v>79160</v>
+        <v>78279</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3241,21 +3241,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6453</v>
+        <v>228912</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3265,10 +3265,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>478250</v>
+        <v>478151</v>
       </c>
       <c r="R27" t="n">
-        <v>6827802</v>
+        <v>6827745</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3327,10 +3327,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>120075224</v>
+        <v>120074907</v>
       </c>
       <c r="B28" t="n">
-        <v>78187</v>
+        <v>79160</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3343,21 +3343,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>353</v>
+        <v>6453</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3367,10 +3367,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>478081</v>
+        <v>478263</v>
       </c>
       <c r="R28" t="n">
-        <v>6827789</v>
+        <v>6827838</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3429,10 +3429,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>120075092</v>
+        <v>120074935</v>
       </c>
       <c r="B29" t="n">
-        <v>78542</v>
+        <v>79160</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3445,21 +3445,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3469,10 +3469,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>478167</v>
+        <v>478150</v>
       </c>
       <c r="R29" t="n">
-        <v>6827561</v>
+        <v>6827745</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3531,7 +3531,7 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>120075069</v>
+        <v>120075095</v>
       </c>
       <c r="B30" t="n">
         <v>78542</v>
@@ -3571,10 +3571,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>478157</v>
+        <v>478219</v>
       </c>
       <c r="R30" t="n">
-        <v>6827611</v>
+        <v>6827572</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3633,10 +3633,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>120074945</v>
+        <v>120075138</v>
       </c>
       <c r="B31" t="n">
-        <v>79160</v>
+        <v>78542</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3649,21 +3649,21 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3673,10 +3673,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>478061</v>
+        <v>478294</v>
       </c>
       <c r="R31" t="n">
-        <v>6827770</v>
+        <v>6827781</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3735,7 +3735,7 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>120075090</v>
+        <v>120075067</v>
       </c>
       <c r="B32" t="n">
         <v>78542</v>
@@ -3775,10 +3775,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>478161</v>
+        <v>478164</v>
       </c>
       <c r="R32" t="n">
-        <v>6827528</v>
+        <v>6827661</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3837,10 +3837,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>120075046</v>
+        <v>120075175</v>
       </c>
       <c r="B33" t="n">
-        <v>78278</v>
+        <v>78542</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -3853,21 +3853,21 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -3877,10 +3877,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>478285</v>
+        <v>478059</v>
       </c>
       <c r="R33" t="n">
-        <v>6827770</v>
+        <v>6827739</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -3939,7 +3939,7 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>120075073</v>
+        <v>120075143</v>
       </c>
       <c r="B34" t="n">
         <v>78542</v>
@@ -3979,10 +3979,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>478116</v>
+        <v>478301</v>
       </c>
       <c r="R34" t="n">
-        <v>6827617</v>
+        <v>6827814</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4041,7 +4041,7 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>120075133</v>
+        <v>120075064</v>
       </c>
       <c r="B35" t="n">
         <v>78542</v>
@@ -4081,10 +4081,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>478258</v>
+        <v>478192</v>
       </c>
       <c r="R35" t="n">
-        <v>6827753</v>
+        <v>6827690</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4143,10 +4143,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>120075176</v>
+        <v>120075040</v>
       </c>
       <c r="B36" t="n">
-        <v>78542</v>
+        <v>78278</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4159,21 +4159,21 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4183,10 +4183,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>478066</v>
+        <v>478250</v>
       </c>
       <c r="R36" t="n">
-        <v>6827732</v>
+        <v>6827802</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4245,10 +4245,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>120075139</v>
+        <v>120075231</v>
       </c>
       <c r="B37" t="n">
-        <v>78542</v>
+        <v>78187</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4261,21 +4261,21 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6425</v>
+        <v>353</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4285,10 +4285,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>478294</v>
+        <v>478067</v>
       </c>
       <c r="R37" t="n">
-        <v>6827803</v>
+        <v>6827863</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4347,10 +4347,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>120075166</v>
+        <v>120075214</v>
       </c>
       <c r="B38" t="n">
-        <v>78542</v>
+        <v>78187</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4363,21 +4363,21 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6425</v>
+        <v>353</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4387,10 +4387,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>478092</v>
+        <v>478266</v>
       </c>
       <c r="R38" t="n">
-        <v>6827839</v>
+        <v>6827724</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4449,10 +4449,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>120074952</v>
+        <v>120075206</v>
       </c>
       <c r="B39" t="n">
-        <v>79131</v>
+        <v>78187</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4465,21 +4465,21 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>229821</v>
+        <v>353</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4489,10 +4489,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>478120</v>
+        <v>478125</v>
       </c>
       <c r="R39" t="n">
-        <v>6827605</v>
+        <v>6827604</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4551,10 +4551,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>120075223</v>
+        <v>120074928</v>
       </c>
       <c r="B40" t="n">
-        <v>78187</v>
+        <v>78576</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -4567,21 +4567,21 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>353</v>
+        <v>185</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4591,10 +4591,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>478076</v>
+        <v>478059</v>
       </c>
       <c r="R40" t="n">
-        <v>6827777</v>
+        <v>6827740</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4653,10 +4653,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>120074948</v>
+        <v>120075019</v>
       </c>
       <c r="B41" t="n">
-        <v>79160</v>
+        <v>79623</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -4669,21 +4669,21 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6453</v>
+        <v>6458</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4693,10 +4693,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>478070</v>
+        <v>478227</v>
       </c>
       <c r="R41" t="n">
-        <v>6827723</v>
+        <v>6827655</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4755,10 +4755,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>120074885</v>
+        <v>120075207</v>
       </c>
       <c r="B42" t="n">
-        <v>79160</v>
+        <v>78187</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -4771,21 +4771,21 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>6453</v>
+        <v>353</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -4795,10 +4795,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>478115</v>
+        <v>478157</v>
       </c>
       <c r="R42" t="n">
-        <v>6827614</v>
+        <v>6827509</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4857,10 +4857,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>120075171</v>
+        <v>120075054</v>
       </c>
       <c r="B43" t="n">
-        <v>78542</v>
+        <v>90598</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -4873,21 +4873,21 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -4897,10 +4897,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>478073</v>
+        <v>478126</v>
       </c>
       <c r="R43" t="n">
-        <v>6827831</v>
+        <v>6827477</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -4959,7 +4959,7 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>120075175</v>
+        <v>120075132</v>
       </c>
       <c r="B44" t="n">
         <v>78542</v>
@@ -4999,10 +4999,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>478059</v>
+        <v>478240</v>
       </c>
       <c r="R44" t="n">
-        <v>6827739</v>
+        <v>6827754</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5061,10 +5061,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>120074907</v>
+        <v>120075061</v>
       </c>
       <c r="B45" t="n">
-        <v>79160</v>
+        <v>78542</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5077,21 +5077,21 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5101,10 +5101,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>478263</v>
+        <v>478160</v>
       </c>
       <c r="R45" t="n">
-        <v>6827838</v>
+        <v>6827710</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5163,7 +5163,7 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>120075081</v>
+        <v>120075130</v>
       </c>
       <c r="B46" t="n">
         <v>78542</v>
@@ -5203,10 +5203,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>478096</v>
+        <v>478264</v>
       </c>
       <c r="R46" t="n">
-        <v>6827550</v>
+        <v>6827733</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5265,7 +5265,7 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>120075095</v>
+        <v>120075082</v>
       </c>
       <c r="B47" t="n">
         <v>78542</v>
@@ -5305,10 +5305,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>478219</v>
+        <v>478097</v>
       </c>
       <c r="R47" t="n">
-        <v>6827572</v>
+        <v>6827544</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5367,7 +5367,7 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>120075172</v>
+        <v>120075120</v>
       </c>
       <c r="B48" t="n">
         <v>78542</v>
@@ -5407,10 +5407,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>478055</v>
+        <v>478223</v>
       </c>
       <c r="R48" t="n">
-        <v>6827768</v>
+        <v>6827657</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5469,10 +5469,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>120075137</v>
+        <v>120075198</v>
       </c>
       <c r="B49" t="n">
-        <v>78542</v>
+        <v>91858</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -5481,25 +5481,25 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5509,10 +5509,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>478288</v>
+        <v>478163</v>
       </c>
       <c r="R49" t="n">
-        <v>6827763</v>
+        <v>6827530</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5571,10 +5571,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>120074931</v>
+        <v>120074915</v>
       </c>
       <c r="B50" t="n">
-        <v>79160</v>
+        <v>78576</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -5587,21 +5587,21 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>6453</v>
+        <v>185</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -5611,10 +5611,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>478261</v>
+        <v>478102</v>
       </c>
       <c r="R50" t="n">
-        <v>6827822</v>
+        <v>6827555</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5673,10 +5673,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>120075201</v>
+        <v>120074947</v>
       </c>
       <c r="B51" t="n">
-        <v>78187</v>
+        <v>79160</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -5689,21 +5689,21 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>353</v>
+        <v>6453</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -5713,10 +5713,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>478182</v>
+        <v>478061</v>
       </c>
       <c r="R51" t="n">
-        <v>6827728</v>
+        <v>6827751</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5775,10 +5775,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>120075065</v>
+        <v>120075038</v>
       </c>
       <c r="B52" t="n">
-        <v>78542</v>
+        <v>78278</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -5791,21 +5791,21 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -5815,10 +5815,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>478169</v>
+        <v>478261</v>
       </c>
       <c r="R52" t="n">
-        <v>6827679</v>
+        <v>6827731</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -5877,10 +5877,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>120074956</v>
+        <v>120075081</v>
       </c>
       <c r="B53" t="n">
-        <v>57320</v>
+        <v>78542</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -5893,39 +5893,34 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
-      <c r="M53" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P53" t="inlineStr">
         <is>
           <t>Hevoslamm, Dlr</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>478278</v>
+        <v>478096</v>
       </c>
       <c r="R53" t="n">
-        <v>6827832</v>
+        <v>6827550</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -5958,11 +5953,6 @@
       <c r="AA53" t="inlineStr">
         <is>
           <t>2024-09-27</t>
-        </is>
-      </c>
-      <c r="AC53" t="inlineStr">
-        <is>
-          <t>Färska ringhack (tall)</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -5989,10 +5979,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>120074998</v>
+        <v>120075173</v>
       </c>
       <c r="B54" t="n">
-        <v>78279</v>
+        <v>78542</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
@@ -6005,21 +5995,21 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -6029,10 +6019,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>478172</v>
+        <v>478052</v>
       </c>
       <c r="R54" t="n">
-        <v>6827640</v>
+        <v>6827754</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6091,10 +6081,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>120074999</v>
+        <v>120075134</v>
       </c>
       <c r="B55" t="n">
-        <v>78279</v>
+        <v>78542</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
@@ -6107,21 +6097,21 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -6131,10 +6121,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>478161</v>
+        <v>478266</v>
       </c>
       <c r="R55" t="n">
-        <v>6827592</v>
+        <v>6827765</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6193,7 +6183,7 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>120075162</v>
+        <v>120075070</v>
       </c>
       <c r="B56" t="n">
         <v>78542</v>
@@ -6233,10 +6223,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>478080</v>
+        <v>478135</v>
       </c>
       <c r="R56" t="n">
-        <v>6827808</v>
+        <v>6827625</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6295,7 +6285,7 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>120075163</v>
+        <v>120075174</v>
       </c>
       <c r="B57" t="n">
         <v>78542</v>
@@ -6335,10 +6325,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>478102</v>
+        <v>478057</v>
       </c>
       <c r="R57" t="n">
-        <v>6827800</v>
+        <v>6827749</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6397,10 +6387,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>120075000</v>
+        <v>120074887</v>
       </c>
       <c r="B58" t="n">
-        <v>78279</v>
+        <v>79160</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
@@ -6413,21 +6403,21 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>228912</v>
+        <v>6453</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
@@ -6437,10 +6427,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>478121</v>
+        <v>478144</v>
       </c>
       <c r="R58" t="n">
-        <v>6827607</v>
+        <v>6827593</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6499,10 +6489,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>120075007</v>
+        <v>120075027</v>
       </c>
       <c r="B59" t="n">
-        <v>78279</v>
+        <v>78278</v>
       </c>
       <c r="C59" t="inlineStr">
         <is>
@@ -6515,21 +6505,21 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>228912</v>
+        <v>6446</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
@@ -6539,10 +6529,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>478285</v>
+        <v>478144</v>
       </c>
       <c r="R59" t="n">
-        <v>6827770</v>
+        <v>6827593</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6601,10 +6591,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>120075206</v>
+        <v>120075074</v>
       </c>
       <c r="B60" t="n">
-        <v>78187</v>
+        <v>78542</v>
       </c>
       <c r="C60" t="inlineStr">
         <is>
@@ -6617,21 +6607,21 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>353</v>
+        <v>6425</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
@@ -6641,10 +6631,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>478125</v>
+        <v>478138</v>
       </c>
       <c r="R60" t="n">
-        <v>6827604</v>
+        <v>6827599</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -6703,10 +6693,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>120075164</v>
+        <v>120074881</v>
       </c>
       <c r="B61" t="n">
-        <v>78542</v>
+        <v>79160</v>
       </c>
       <c r="C61" t="inlineStr">
         <is>
@@ -6719,21 +6709,21 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
@@ -6743,10 +6733,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>478092</v>
+        <v>478184</v>
       </c>
       <c r="R61" t="n">
-        <v>6827810</v>
+        <v>6827728</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -6805,10 +6795,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>120075037</v>
+        <v>120074997</v>
       </c>
       <c r="B62" t="n">
-        <v>78278</v>
+        <v>78279</v>
       </c>
       <c r="C62" t="inlineStr">
         <is>
@@ -6821,21 +6811,21 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>6446</v>
+        <v>228912</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
@@ -6845,10 +6835,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>478265</v>
+        <v>478218</v>
       </c>
       <c r="R62" t="n">
-        <v>6827716</v>
+        <v>6827733</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -6907,10 +6897,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>120074887</v>
+        <v>120075196</v>
       </c>
       <c r="B63" t="n">
-        <v>79160</v>
+        <v>78542</v>
       </c>
       <c r="C63" t="inlineStr">
         <is>
@@ -6923,21 +6913,21 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
@@ -6947,10 +6937,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>478144</v>
+        <v>478288</v>
       </c>
       <c r="R63" t="n">
-        <v>6827593</v>
+        <v>6827682</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -7009,10 +6999,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>120075024</v>
+        <v>120075085</v>
       </c>
       <c r="B64" t="n">
-        <v>78278</v>
+        <v>78542</v>
       </c>
       <c r="C64" t="inlineStr">
         <is>
@@ -7025,21 +7015,21 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
@@ -7049,10 +7039,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>478165</v>
+        <v>478094</v>
       </c>
       <c r="R64" t="n">
-        <v>6827712</v>
+        <v>6827504</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -7111,10 +7101,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>120074947</v>
+        <v>120075142</v>
       </c>
       <c r="B65" t="n">
-        <v>79160</v>
+        <v>78542</v>
       </c>
       <c r="C65" t="inlineStr">
         <is>
@@ -7127,21 +7117,21 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
@@ -7151,10 +7141,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>478061</v>
+        <v>478313</v>
       </c>
       <c r="R65" t="n">
-        <v>6827751</v>
+        <v>6827798</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7213,10 +7203,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>120075026</v>
+        <v>120075069</v>
       </c>
       <c r="B66" t="n">
-        <v>78278</v>
+        <v>78542</v>
       </c>
       <c r="C66" t="inlineStr">
         <is>
@@ -7229,21 +7219,21 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
@@ -7253,10 +7243,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>478161</v>
+        <v>478157</v>
       </c>
       <c r="R66" t="n">
-        <v>6827592</v>
+        <v>6827611</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7315,10 +7305,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>120074927</v>
+        <v>120075167</v>
       </c>
       <c r="B67" t="n">
-        <v>78576</v>
+        <v>78542</v>
       </c>
       <c r="C67" t="inlineStr">
         <is>
@@ -7331,21 +7321,21 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
@@ -7355,10 +7345,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>478073</v>
+        <v>478105</v>
       </c>
       <c r="R67" t="n">
-        <v>6827836</v>
+        <v>6827851</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7417,10 +7407,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>120075231</v>
+        <v>120075073</v>
       </c>
       <c r="B68" t="n">
-        <v>78187</v>
+        <v>78542</v>
       </c>
       <c r="C68" t="inlineStr">
         <is>
@@ -7433,21 +7423,21 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>353</v>
+        <v>6425</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
@@ -7457,10 +7447,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>478067</v>
+        <v>478116</v>
       </c>
       <c r="R68" t="n">
-        <v>6827863</v>
+        <v>6827617</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7519,7 +7509,7 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>120075066</v>
+        <v>120075097</v>
       </c>
       <c r="B69" t="n">
         <v>78542</v>
@@ -7559,10 +7549,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>478160</v>
+        <v>478248</v>
       </c>
       <c r="R69" t="n">
-        <v>6827680</v>
+        <v>6827593</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -7621,10 +7611,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>120075138</v>
+        <v>120075227</v>
       </c>
       <c r="B70" t="n">
-        <v>78542</v>
+        <v>78187</v>
       </c>
       <c r="C70" t="inlineStr">
         <is>
@@ -7637,21 +7627,21 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>6425</v>
+        <v>353</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
@@ -7661,10 +7651,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>478294</v>
+        <v>478088</v>
       </c>
       <c r="R70" t="n">
-        <v>6827781</v>
+        <v>6827834</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -7723,10 +7713,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>120075134</v>
+        <v>120075042</v>
       </c>
       <c r="B71" t="n">
-        <v>78542</v>
+        <v>78278</v>
       </c>
       <c r="C71" t="inlineStr">
         <is>
@@ -7739,21 +7729,21 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
@@ -7763,10 +7753,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>478266</v>
+        <v>478074</v>
       </c>
       <c r="R71" t="n">
-        <v>6827765</v>
+        <v>6827775</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -7825,10 +7815,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>120074904</v>
+        <v>120075226</v>
       </c>
       <c r="B72" t="n">
-        <v>79160</v>
+        <v>78187</v>
       </c>
       <c r="C72" t="inlineStr">
         <is>
@@ -7841,21 +7831,21 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>6453</v>
+        <v>353</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
@@ -7865,10 +7855,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>478262</v>
+        <v>478098</v>
       </c>
       <c r="R72" t="n">
-        <v>6827730</v>
+        <v>6827815</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -7927,7 +7917,7 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>120075168</v>
+        <v>120075088</v>
       </c>
       <c r="B73" t="n">
         <v>78542</v>
@@ -7967,10 +7957,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>478086</v>
+        <v>478151</v>
       </c>
       <c r="R73" t="n">
-        <v>6827868</v>
+        <v>6827509</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -8029,7 +8019,7 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>120075130</v>
+        <v>120075128</v>
       </c>
       <c r="B74" t="n">
         <v>78542</v>
@@ -8069,10 +8059,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>478264</v>
+        <v>478275</v>
       </c>
       <c r="R74" t="n">
-        <v>6827733</v>
+        <v>6827710</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -8131,10 +8121,10 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>120075048</v>
+        <v>120075077</v>
       </c>
       <c r="B75" t="n">
-        <v>56524</v>
+        <v>78542</v>
       </c>
       <c r="C75" t="inlineStr">
         <is>
@@ -8147,39 +8137,34 @@
         </is>
       </c>
       <c r="E75" t="n">
-        <v>102612</v>
+        <v>6425</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
-      <c r="M75" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
       <c r="P75" t="inlineStr">
         <is>
           <t>Hevoslamm, Dlr</t>
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>478070</v>
+        <v>478124</v>
       </c>
       <c r="R75" t="n">
-        <v>6827723</v>
+        <v>6827560</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -8238,10 +8223,10 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>120075236</v>
+        <v>120075145</v>
       </c>
       <c r="B76" t="n">
-        <v>78187</v>
+        <v>78542</v>
       </c>
       <c r="C76" t="inlineStr">
         <is>
@@ -8254,21 +8239,21 @@
         </is>
       </c>
       <c r="E76" t="n">
-        <v>353</v>
+        <v>6425</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
@@ -8278,10 +8263,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>478062</v>
+        <v>478226</v>
       </c>
       <c r="R76" t="n">
-        <v>6827740</v>
+        <v>6827777</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -8340,10 +8325,10 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>120074917</v>
+        <v>120075048</v>
       </c>
       <c r="B77" t="n">
-        <v>78576</v>
+        <v>56524</v>
       </c>
       <c r="C77" t="inlineStr">
         <is>
@@ -8356,34 +8341,39 @@
         </is>
       </c>
       <c r="E77" t="n">
-        <v>185</v>
+        <v>102612</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
+      <c r="M77" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="P77" t="inlineStr">
         <is>
           <t>Hevoslamm, Dlr</t>
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>478095</v>
+        <v>478070</v>
       </c>
       <c r="R77" t="n">
-        <v>6827533</v>
+        <v>6827723</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -8442,7 +8432,7 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>120075217</v>
+        <v>120075232</v>
       </c>
       <c r="B78" t="n">
         <v>78187</v>
@@ -8482,10 +8472,10 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>478264</v>
+        <v>478051</v>
       </c>
       <c r="R78" t="n">
-        <v>6827839</v>
+        <v>6827739</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -8544,10 +8534,10 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>120075074</v>
+        <v>120074912</v>
       </c>
       <c r="B79" t="n">
-        <v>78542</v>
+        <v>78576</v>
       </c>
       <c r="C79" t="inlineStr">
         <is>
@@ -8560,21 +8550,21 @@
         </is>
       </c>
       <c r="E79" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
@@ -8584,10 +8574,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>478138</v>
+        <v>478149</v>
       </c>
       <c r="R79" t="n">
-        <v>6827599</v>
+        <v>6827714</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -8646,7 +8636,7 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>120074938</v>
+        <v>120074904</v>
       </c>
       <c r="B80" t="n">
         <v>79160</v>
@@ -8686,10 +8676,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>478097</v>
+        <v>478262</v>
       </c>
       <c r="R80" t="n">
-        <v>6827756</v>
+        <v>6827730</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -8748,7 +8738,7 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>120074943</v>
+        <v>120074905</v>
       </c>
       <c r="B81" t="n">
         <v>79160</v>
@@ -8788,10 +8778,10 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>478073</v>
+        <v>478285</v>
       </c>
       <c r="R81" t="n">
-        <v>6827827</v>
+        <v>6827770</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -8850,10 +8840,10 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>120075192</v>
+        <v>120075028</v>
       </c>
       <c r="B82" t="n">
-        <v>78542</v>
+        <v>78278</v>
       </c>
       <c r="C82" t="inlineStr">
         <is>
@@ -8866,21 +8856,21 @@
         </is>
       </c>
       <c r="E82" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
@@ -8890,10 +8880,10 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>478282</v>
+        <v>478137</v>
       </c>
       <c r="R82" t="n">
-        <v>6827683</v>
+        <v>6827553</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -8952,10 +8942,10 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>120075070</v>
+        <v>120074945</v>
       </c>
       <c r="B83" t="n">
-        <v>78542</v>
+        <v>79160</v>
       </c>
       <c r="C83" t="inlineStr">
         <is>
@@ -8968,21 +8958,21 @@
         </is>
       </c>
       <c r="E83" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
@@ -8992,10 +8982,10 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>478135</v>
+        <v>478061</v>
       </c>
       <c r="R83" t="n">
-        <v>6827625</v>
+        <v>6827770</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -9054,10 +9044,10 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>120075145</v>
+        <v>120074996</v>
       </c>
       <c r="B84" t="n">
-        <v>78542</v>
+        <v>78279</v>
       </c>
       <c r="C84" t="inlineStr">
         <is>
@@ -9070,21 +9060,21 @@
         </is>
       </c>
       <c r="E84" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
@@ -9094,10 +9084,10 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>478226</v>
+        <v>478165</v>
       </c>
       <c r="R84" t="n">
-        <v>6827777</v>
+        <v>6827712</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -9156,10 +9146,10 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>120075067</v>
+        <v>120075003</v>
       </c>
       <c r="B85" t="n">
-        <v>78542</v>
+        <v>78279</v>
       </c>
       <c r="C85" t="inlineStr">
         <is>
@@ -9172,21 +9162,21 @@
         </is>
       </c>
       <c r="E85" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
@@ -9196,10 +9186,10 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>478164</v>
+        <v>478137</v>
       </c>
       <c r="R85" t="n">
-        <v>6827661</v>
+        <v>6827553</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -9258,10 +9248,10 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>120074997</v>
+        <v>120075215</v>
       </c>
       <c r="B86" t="n">
-        <v>78279</v>
+        <v>78187</v>
       </c>
       <c r="C86" t="inlineStr">
         <is>
@@ -9274,21 +9264,21 @@
         </is>
       </c>
       <c r="E86" t="n">
-        <v>228912</v>
+        <v>353</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I86" t="inlineStr"/>
@@ -9298,10 +9288,10 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>478218</v>
+        <v>478239</v>
       </c>
       <c r="R86" t="n">
-        <v>6827733</v>
+        <v>6827752</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>
@@ -9360,10 +9350,10 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>120075203</v>
+        <v>120074961</v>
       </c>
       <c r="B87" t="n">
-        <v>78187</v>
+        <v>90600</v>
       </c>
       <c r="C87" t="inlineStr">
         <is>
@@ -9376,21 +9366,21 @@
         </is>
       </c>
       <c r="E87" t="n">
-        <v>353</v>
+        <v>5442</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I87" t="inlineStr"/>
@@ -9400,10 +9390,10 @@
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>478125</v>
+        <v>478230</v>
       </c>
       <c r="R87" t="n">
-        <v>6827631</v>
+        <v>6827780</v>
       </c>
       <c r="S87" t="n">
         <v>10</v>
@@ -9462,7 +9452,7 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>120075060</v>
+        <v>120075176</v>
       </c>
       <c r="B88" t="n">
         <v>78542</v>
@@ -9502,10 +9492,10 @@
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>478087</v>
+        <v>478066</v>
       </c>
       <c r="R88" t="n">
-        <v>6827718</v>
+        <v>6827732</v>
       </c>
       <c r="S88" t="n">
         <v>10</v>
@@ -9564,10 +9554,10 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>120074888</v>
+        <v>120075239</v>
       </c>
       <c r="B89" t="n">
-        <v>79160</v>
+        <v>77474</v>
       </c>
       <c r="C89" t="inlineStr">
         <is>
@@ -9580,21 +9570,21 @@
         </is>
       </c>
       <c r="E89" t="n">
-        <v>6453</v>
+        <v>6487</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Blågrå svartspik</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Chaenothecopsis fennica</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Laurila) Tibell</t>
         </is>
       </c>
       <c r="I89" t="inlineStr"/>
@@ -9604,7 +9594,7 @@
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>478139</v>
+        <v>478137</v>
       </c>
       <c r="R89" t="n">
         <v>6827554</v>
@@ -9666,10 +9656,10 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>120075089</v>
+        <v>120074930</v>
       </c>
       <c r="B90" t="n">
-        <v>78542</v>
+        <v>79160</v>
       </c>
       <c r="C90" t="inlineStr">
         <is>
@@ -9682,21 +9672,21 @@
         </is>
       </c>
       <c r="E90" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I90" t="inlineStr"/>
@@ -9706,10 +9696,10 @@
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>478153</v>
+        <v>478299</v>
       </c>
       <c r="R90" t="n">
-        <v>6827517</v>
+        <v>6827805</v>
       </c>
       <c r="S90" t="n">
         <v>10</v>
@@ -9768,10 +9758,10 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>120075143</v>
+        <v>120074999</v>
       </c>
       <c r="B91" t="n">
-        <v>78542</v>
+        <v>78279</v>
       </c>
       <c r="C91" t="inlineStr">
         <is>
@@ -9784,21 +9774,21 @@
         </is>
       </c>
       <c r="E91" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I91" t="inlineStr"/>
@@ -9808,10 +9798,10 @@
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>478301</v>
+        <v>478161</v>
       </c>
       <c r="R91" t="n">
-        <v>6827814</v>
+        <v>6827592</v>
       </c>
       <c r="S91" t="n">
         <v>10</v>
@@ -9870,10 +9860,10 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>120075012</v>
+        <v>120075197</v>
       </c>
       <c r="B92" t="n">
-        <v>78279</v>
+        <v>91858</v>
       </c>
       <c r="C92" t="inlineStr">
         <is>
@@ -9882,38 +9872,47 @@
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E92" t="n">
-        <v>228912</v>
+        <v>4364</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
-        </is>
-      </c>
-      <c r="I92" t="inlineStr"/>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I92" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J92" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="P92" t="inlineStr">
         <is>
           <t>Hevoslamm, Dlr</t>
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>478055</v>
+        <v>478077</v>
       </c>
       <c r="R92" t="n">
-        <v>6827786</v>
+        <v>6827805</v>
       </c>
       <c r="S92" t="n">
         <v>10</v>
@@ -9972,10 +9971,10 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>120075011</v>
+        <v>120075219</v>
       </c>
       <c r="B93" t="n">
-        <v>78279</v>
+        <v>78187</v>
       </c>
       <c r="C93" t="inlineStr">
         <is>
@@ -9988,21 +9987,21 @@
         </is>
       </c>
       <c r="E93" t="n">
-        <v>228912</v>
+        <v>353</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I93" t="inlineStr"/>
@@ -10012,10 +10011,10 @@
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>478103</v>
+        <v>478169</v>
       </c>
       <c r="R93" t="n">
-        <v>6827803</v>
+        <v>6827760</v>
       </c>
       <c r="S93" t="n">
         <v>10</v>
@@ -10074,10 +10073,10 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>120075144</v>
+        <v>120075216</v>
       </c>
       <c r="B94" t="n">
-        <v>78542</v>
+        <v>78187</v>
       </c>
       <c r="C94" t="inlineStr">
         <is>
@@ -10090,21 +10089,21 @@
         </is>
       </c>
       <c r="E94" t="n">
-        <v>6425</v>
+        <v>353</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I94" t="inlineStr"/>
@@ -10114,10 +10113,10 @@
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>478261</v>
+        <v>478294</v>
       </c>
       <c r="R94" t="n">
-        <v>6827822</v>
+        <v>6827790</v>
       </c>
       <c r="S94" t="n">
         <v>10</v>
@@ -10176,10 +10175,10 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>120074996</v>
+        <v>120075137</v>
       </c>
       <c r="B95" t="n">
-        <v>78279</v>
+        <v>78542</v>
       </c>
       <c r="C95" t="inlineStr">
         <is>
@@ -10192,21 +10191,21 @@
         </is>
       </c>
       <c r="E95" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I95" t="inlineStr"/>
@@ -10216,10 +10215,10 @@
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>478165</v>
+        <v>478288</v>
       </c>
       <c r="R95" t="n">
-        <v>6827712</v>
+        <v>6827763</v>
       </c>
       <c r="S95" t="n">
         <v>10</v>
@@ -10278,10 +10277,10 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>120075019</v>
+        <v>120075066</v>
       </c>
       <c r="B96" t="n">
-        <v>79623</v>
+        <v>78542</v>
       </c>
       <c r="C96" t="inlineStr">
         <is>
@@ -10294,21 +10293,21 @@
         </is>
       </c>
       <c r="E96" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I96" t="inlineStr"/>
@@ -10318,10 +10317,10 @@
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>478227</v>
+        <v>478160</v>
       </c>
       <c r="R96" t="n">
-        <v>6827655</v>
+        <v>6827680</v>
       </c>
       <c r="S96" t="n">
         <v>10</v>
@@ -10380,10 +10379,10 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>120075083</v>
+        <v>120074939</v>
       </c>
       <c r="B97" t="n">
-        <v>78542</v>
+        <v>79160</v>
       </c>
       <c r="C97" t="inlineStr">
         <is>
@@ -10396,21 +10395,21 @@
         </is>
       </c>
       <c r="E97" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I97" t="inlineStr"/>
@@ -10420,10 +10419,10 @@
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>478097</v>
+        <v>478091</v>
       </c>
       <c r="R97" t="n">
-        <v>6827527</v>
+        <v>6827838</v>
       </c>
       <c r="S97" t="n">
         <v>10</v>
@@ -10482,10 +10481,10 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>120075087</v>
+        <v>120074932</v>
       </c>
       <c r="B98" t="n">
-        <v>78542</v>
+        <v>79160</v>
       </c>
       <c r="C98" t="inlineStr">
         <is>
@@ -10498,21 +10497,21 @@
         </is>
       </c>
       <c r="E98" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I98" t="inlineStr"/>
@@ -10522,10 +10521,10 @@
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>478145</v>
+        <v>478250</v>
       </c>
       <c r="R98" t="n">
-        <v>6827485</v>
+        <v>6827802</v>
       </c>
       <c r="S98" t="n">
         <v>10</v>
@@ -10584,10 +10583,10 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>120074929</v>
+        <v>120075157</v>
       </c>
       <c r="B99" t="n">
-        <v>78576</v>
+        <v>78542</v>
       </c>
       <c r="C99" t="inlineStr">
         <is>
@@ -10600,21 +10599,21 @@
         </is>
       </c>
       <c r="E99" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I99" t="inlineStr"/>
@@ -10624,10 +10623,10 @@
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>478045</v>
+        <v>478103</v>
       </c>
       <c r="R99" t="n">
-        <v>6827724</v>
+        <v>6827718</v>
       </c>
       <c r="S99" t="n">
         <v>10</v>
@@ -10686,10 +10685,10 @@
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>120075208</v>
+        <v>120074934</v>
       </c>
       <c r="B100" t="n">
-        <v>78187</v>
+        <v>79160</v>
       </c>
       <c r="C100" t="inlineStr">
         <is>
@@ -10702,21 +10701,21 @@
         </is>
       </c>
       <c r="E100" t="n">
-        <v>353</v>
+        <v>6453</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I100" t="inlineStr"/>
@@ -10726,10 +10725,10 @@
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>478158</v>
+        <v>478169</v>
       </c>
       <c r="R100" t="n">
-        <v>6827519</v>
+        <v>6827760</v>
       </c>
       <c r="S100" t="n">
         <v>10</v>
@@ -10788,10 +10787,10 @@
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>120075196</v>
+        <v>120074944</v>
       </c>
       <c r="B101" t="n">
-        <v>78542</v>
+        <v>79160</v>
       </c>
       <c r="C101" t="inlineStr">
         <is>
@@ -10804,21 +10803,21 @@
         </is>
       </c>
       <c r="E101" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I101" t="inlineStr"/>
@@ -10828,10 +10827,10 @@
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>478288</v>
+        <v>478056</v>
       </c>
       <c r="R101" t="n">
-        <v>6827682</v>
+        <v>6827785</v>
       </c>
       <c r="S101" t="n">
         <v>10</v>
@@ -10890,10 +10889,10 @@
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>120074946</v>
+        <v>120075224</v>
       </c>
       <c r="B102" t="n">
-        <v>79160</v>
+        <v>78187</v>
       </c>
       <c r="C102" t="inlineStr">
         <is>
@@ -10906,21 +10905,21 @@
         </is>
       </c>
       <c r="E102" t="n">
-        <v>6453</v>
+        <v>353</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I102" t="inlineStr"/>
@@ -10930,10 +10929,10 @@
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>478056</v>
+        <v>478081</v>
       </c>
       <c r="R102" t="n">
-        <v>6827754</v>
+        <v>6827789</v>
       </c>
       <c r="S102" t="n">
         <v>10</v>
@@ -10992,7 +10991,7 @@
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>120074912</v>
+        <v>120074917</v>
       </c>
       <c r="B103" t="n">
         <v>78576</v>
@@ -11032,10 +11031,10 @@
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>478149</v>
+        <v>478095</v>
       </c>
       <c r="R103" t="n">
-        <v>6827714</v>
+        <v>6827533</v>
       </c>
       <c r="S103" t="n">
         <v>10</v>
@@ -11094,7 +11093,7 @@
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>120075084</v>
+        <v>120075071</v>
       </c>
       <c r="B104" t="n">
         <v>78542</v>
@@ -11134,10 +11133,10 @@
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>478098</v>
+        <v>478116</v>
       </c>
       <c r="R104" t="n">
-        <v>6827520</v>
+        <v>6827633</v>
       </c>
       <c r="S104" t="n">
         <v>10</v>
@@ -11196,10 +11195,10 @@
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>120074883</v>
+        <v>120075015</v>
       </c>
       <c r="B105" t="n">
-        <v>79160</v>
+        <v>79623</v>
       </c>
       <c r="C105" t="inlineStr">
         <is>
@@ -11212,21 +11211,21 @@
         </is>
       </c>
       <c r="E105" t="n">
-        <v>6453</v>
+        <v>6458</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I105" t="inlineStr"/>
@@ -11236,10 +11235,10 @@
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>478142</v>
+        <v>478114</v>
       </c>
       <c r="R105" t="n">
-        <v>6827623</v>
+        <v>6827633</v>
       </c>
       <c r="S105" t="n">
         <v>10</v>
@@ -11298,10 +11297,10 @@
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>120075054</v>
+        <v>120074882</v>
       </c>
       <c r="B106" t="n">
-        <v>90598</v>
+        <v>79160</v>
       </c>
       <c r="C106" t="inlineStr">
         <is>
@@ -11314,21 +11313,21 @@
         </is>
       </c>
       <c r="E106" t="n">
-        <v>5432</v>
+        <v>6453</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I106" t="inlineStr"/>
@@ -11338,10 +11337,10 @@
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>478126</v>
+        <v>478162</v>
       </c>
       <c r="R106" t="n">
-        <v>6827477</v>
+        <v>6827593</v>
       </c>
       <c r="S106" t="n">
         <v>10</v>
@@ -11400,10 +11399,10 @@
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>120075086</v>
+        <v>120075025</v>
       </c>
       <c r="B107" t="n">
-        <v>78542</v>
+        <v>78278</v>
       </c>
       <c r="C107" t="inlineStr">
         <is>
@@ -11416,21 +11415,21 @@
         </is>
       </c>
       <c r="E107" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I107" t="inlineStr"/>
@@ -11440,10 +11439,10 @@
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>478104</v>
+        <v>478171</v>
       </c>
       <c r="R107" t="n">
-        <v>6827495</v>
+        <v>6827642</v>
       </c>
       <c r="S107" t="n">
         <v>10</v>
@@ -11502,10 +11501,10 @@
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>120075028</v>
+        <v>120075087</v>
       </c>
       <c r="B108" t="n">
-        <v>78278</v>
+        <v>78542</v>
       </c>
       <c r="C108" t="inlineStr">
         <is>
@@ -11518,21 +11517,21 @@
         </is>
       </c>
       <c r="E108" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I108" t="inlineStr"/>
@@ -11542,10 +11541,10 @@
         </is>
       </c>
       <c r="Q108" t="n">
-        <v>478137</v>
+        <v>478145</v>
       </c>
       <c r="R108" t="n">
-        <v>6827553</v>
+        <v>6827485</v>
       </c>
       <c r="S108" t="n">
         <v>10</v>
@@ -11604,10 +11603,10 @@
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>120075173</v>
+        <v>120074906</v>
       </c>
       <c r="B109" t="n">
-        <v>78542</v>
+        <v>79160</v>
       </c>
       <c r="C109" t="inlineStr">
         <is>
@@ -11620,21 +11619,21 @@
         </is>
       </c>
       <c r="E109" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I109" t="inlineStr"/>
@@ -11644,10 +11643,10 @@
         </is>
       </c>
       <c r="Q109" t="n">
-        <v>478052</v>
+        <v>478294</v>
       </c>
       <c r="R109" t="n">
-        <v>6827754</v>
+        <v>6827790</v>
       </c>
       <c r="S109" t="n">
         <v>10</v>
@@ -11706,10 +11705,10 @@
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>120075242</v>
+        <v>120075013</v>
       </c>
       <c r="B110" t="n">
-        <v>77926</v>
+        <v>78279</v>
       </c>
       <c r="C110" t="inlineStr">
         <is>
@@ -11722,21 +11721,21 @@
         </is>
       </c>
       <c r="E110" t="n">
-        <v>6437</v>
+        <v>228912</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I110" t="inlineStr"/>
@@ -11746,10 +11745,10 @@
         </is>
       </c>
       <c r="Q110" t="n">
-        <v>478136</v>
+        <v>478239</v>
       </c>
       <c r="R110" t="n">
-        <v>6827556</v>
+        <v>6827752</v>
       </c>
       <c r="S110" t="n">
         <v>10</v>
@@ -11808,10 +11807,10 @@
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>120075094</v>
+        <v>120075208</v>
       </c>
       <c r="B111" t="n">
-        <v>78542</v>
+        <v>78187</v>
       </c>
       <c r="C111" t="inlineStr">
         <is>
@@ -11824,21 +11823,21 @@
         </is>
       </c>
       <c r="E111" t="n">
-        <v>6425</v>
+        <v>353</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I111" t="inlineStr"/>
@@ -11848,10 +11847,10 @@
         </is>
       </c>
       <c r="Q111" t="n">
-        <v>478205</v>
+        <v>478158</v>
       </c>
       <c r="R111" t="n">
-        <v>6827556</v>
+        <v>6827519</v>
       </c>
       <c r="S111" t="n">
         <v>10</v>
@@ -11910,10 +11909,10 @@
     </row>
     <row r="112">
       <c r="A112" t="n">
-        <v>120074905</v>
+        <v>120075236</v>
       </c>
       <c r="B112" t="n">
-        <v>79160</v>
+        <v>78187</v>
       </c>
       <c r="C112" t="inlineStr">
         <is>
@@ -11926,21 +11925,21 @@
         </is>
       </c>
       <c r="E112" t="n">
-        <v>6453</v>
+        <v>353</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I112" t="inlineStr"/>
@@ -11950,10 +11949,10 @@
         </is>
       </c>
       <c r="Q112" t="n">
-        <v>478285</v>
+        <v>478062</v>
       </c>
       <c r="R112" t="n">
-        <v>6827770</v>
+        <v>6827740</v>
       </c>
       <c r="S112" t="n">
         <v>10</v>
@@ -12012,10 +12011,10 @@
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>120075042</v>
+        <v>120075135</v>
       </c>
       <c r="B113" t="n">
-        <v>78278</v>
+        <v>78542</v>
       </c>
       <c r="C113" t="inlineStr">
         <is>
@@ -12028,21 +12027,21 @@
         </is>
       </c>
       <c r="E113" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I113" t="inlineStr"/>
@@ -12052,10 +12051,10 @@
         </is>
       </c>
       <c r="Q113" t="n">
-        <v>478074</v>
+        <v>478291</v>
       </c>
       <c r="R113" t="n">
-        <v>6827775</v>
+        <v>6827744</v>
       </c>
       <c r="S113" t="n">
         <v>10</v>
@@ -12114,10 +12113,10 @@
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>120075047</v>
+        <v>120075133</v>
       </c>
       <c r="B114" t="n">
-        <v>78278</v>
+        <v>78542</v>
       </c>
       <c r="C114" t="inlineStr">
         <is>
@@ -12130,21 +12129,21 @@
         </is>
       </c>
       <c r="E114" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I114" t="inlineStr"/>
@@ -12154,10 +12153,10 @@
         </is>
       </c>
       <c r="Q114" t="n">
-        <v>478212</v>
+        <v>478258</v>
       </c>
       <c r="R114" t="n">
-        <v>6827573</v>
+        <v>6827753</v>
       </c>
       <c r="S114" t="n">
         <v>10</v>
@@ -12216,7 +12215,7 @@
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>120075167</v>
+        <v>120075163</v>
       </c>
       <c r="B115" t="n">
         <v>78542</v>
@@ -12256,10 +12255,10 @@
         </is>
       </c>
       <c r="Q115" t="n">
-        <v>478105</v>
+        <v>478102</v>
       </c>
       <c r="R115" t="n">
-        <v>6827851</v>
+        <v>6827800</v>
       </c>
       <c r="S115" t="n">
         <v>10</v>
@@ -12318,10 +12317,10 @@
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>120075215</v>
+        <v>120075063</v>
       </c>
       <c r="B116" t="n">
-        <v>78187</v>
+        <v>78542</v>
       </c>
       <c r="C116" t="inlineStr">
         <is>
@@ -12334,21 +12333,21 @@
         </is>
       </c>
       <c r="E116" t="n">
-        <v>353</v>
+        <v>6425</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I116" t="inlineStr"/>
@@ -12358,10 +12357,10 @@
         </is>
       </c>
       <c r="Q116" t="n">
-        <v>478239</v>
+        <v>478201</v>
       </c>
       <c r="R116" t="n">
-        <v>6827752</v>
+        <v>6827693</v>
       </c>
       <c r="S116" t="n">
         <v>10</v>
@@ -12420,10 +12419,10 @@
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>120074914</v>
+        <v>120075026</v>
       </c>
       <c r="B117" t="n">
-        <v>78576</v>
+        <v>78278</v>
       </c>
       <c r="C117" t="inlineStr">
         <is>
@@ -12436,21 +12435,21 @@
         </is>
       </c>
       <c r="E117" t="n">
-        <v>185</v>
+        <v>6446</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I117" t="inlineStr"/>
@@ -12460,10 +12459,10 @@
         </is>
       </c>
       <c r="Q117" t="n">
-        <v>478169</v>
+        <v>478161</v>
       </c>
       <c r="R117" t="n">
-        <v>6827680</v>
+        <v>6827592</v>
       </c>
       <c r="S117" t="n">
         <v>10</v>
@@ -12522,10 +12521,10 @@
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>120075234</v>
+        <v>120075044</v>
       </c>
       <c r="B118" t="n">
-        <v>78187</v>
+        <v>78278</v>
       </c>
       <c r="C118" t="inlineStr">
         <is>
@@ -12538,21 +12537,21 @@
         </is>
       </c>
       <c r="E118" t="n">
-        <v>353</v>
+        <v>6446</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I118" t="inlineStr"/>
@@ -12562,10 +12561,10 @@
         </is>
       </c>
       <c r="Q118" t="n">
-        <v>478069</v>
+        <v>478060</v>
       </c>
       <c r="R118" t="n">
-        <v>6827741</v>
+        <v>6827770</v>
       </c>
       <c r="S118" t="n">
         <v>10</v>
@@ -12624,10 +12623,10 @@
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>120074961</v>
+        <v>120075000</v>
       </c>
       <c r="B119" t="n">
-        <v>90600</v>
+        <v>78279</v>
       </c>
       <c r="C119" t="inlineStr">
         <is>
@@ -12640,21 +12639,21 @@
         </is>
       </c>
       <c r="E119" t="n">
-        <v>5442</v>
+        <v>228912</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I119" t="inlineStr"/>
@@ -12664,10 +12663,10 @@
         </is>
       </c>
       <c r="Q119" t="n">
-        <v>478230</v>
+        <v>478121</v>
       </c>
       <c r="R119" t="n">
-        <v>6827780</v>
+        <v>6827607</v>
       </c>
       <c r="S119" t="n">
         <v>10</v>
@@ -12726,10 +12725,10 @@
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>120074892</v>
+        <v>120075008</v>
       </c>
       <c r="B120" t="n">
-        <v>79160</v>
+        <v>78279</v>
       </c>
       <c r="C120" t="inlineStr">
         <is>
@@ -12742,21 +12741,21 @@
         </is>
       </c>
       <c r="E120" t="n">
-        <v>6453</v>
+        <v>228912</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I120" t="inlineStr"/>
@@ -12766,10 +12765,10 @@
         </is>
       </c>
       <c r="Q120" t="n">
-        <v>478243</v>
+        <v>478299</v>
       </c>
       <c r="R120" t="n">
-        <v>6827585</v>
+        <v>6827805</v>
       </c>
       <c r="S120" t="n">
         <v>10</v>
@@ -12828,10 +12827,10 @@
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>120075135</v>
+        <v>120075230</v>
       </c>
       <c r="B121" t="n">
-        <v>78542</v>
+        <v>78187</v>
       </c>
       <c r="C121" t="inlineStr">
         <is>
@@ -12844,21 +12843,21 @@
         </is>
       </c>
       <c r="E121" t="n">
-        <v>6425</v>
+        <v>353</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I121" t="inlineStr"/>
@@ -12868,10 +12867,10 @@
         </is>
       </c>
       <c r="Q121" t="n">
-        <v>478291</v>
+        <v>478064</v>
       </c>
       <c r="R121" t="n">
-        <v>6827744</v>
+        <v>6827866</v>
       </c>
       <c r="S121" t="n">
         <v>10</v>
@@ -12930,10 +12929,10 @@
     </row>
     <row r="122">
       <c r="A122" t="n">
-        <v>120075147</v>
+        <v>120074889</v>
       </c>
       <c r="B122" t="n">
-        <v>78542</v>
+        <v>79160</v>
       </c>
       <c r="C122" t="inlineStr">
         <is>
@@ -12946,21 +12945,21 @@
         </is>
       </c>
       <c r="E122" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I122" t="inlineStr"/>
@@ -12970,10 +12969,10 @@
         </is>
       </c>
       <c r="Q122" t="n">
-        <v>478153</v>
+        <v>478163</v>
       </c>
       <c r="R122" t="n">
-        <v>6827728</v>
+        <v>6827536</v>
       </c>
       <c r="S122" t="n">
         <v>10</v>
@@ -13032,10 +13031,10 @@
     </row>
     <row r="123">
       <c r="A123" t="n">
-        <v>120074935</v>
+        <v>120075060</v>
       </c>
       <c r="B123" t="n">
-        <v>79160</v>
+        <v>78542</v>
       </c>
       <c r="C123" t="inlineStr">
         <is>
@@ -13048,21 +13047,21 @@
         </is>
       </c>
       <c r="E123" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I123" t="inlineStr"/>
@@ -13072,10 +13071,10 @@
         </is>
       </c>
       <c r="Q123" t="n">
-        <v>478150</v>
+        <v>478087</v>
       </c>
       <c r="R123" t="n">
-        <v>6827745</v>
+        <v>6827718</v>
       </c>
       <c r="S123" t="n">
         <v>10</v>
@@ -13134,10 +13133,10 @@
     </row>
     <row r="124">
       <c r="A124" t="n">
-        <v>120075232</v>
+        <v>120075062</v>
       </c>
       <c r="B124" t="n">
-        <v>78187</v>
+        <v>78542</v>
       </c>
       <c r="C124" t="inlineStr">
         <is>
@@ -13150,21 +13149,21 @@
         </is>
       </c>
       <c r="E124" t="n">
-        <v>353</v>
+        <v>6425</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I124" t="inlineStr"/>
@@ -13174,10 +13173,10 @@
         </is>
       </c>
       <c r="Q124" t="n">
-        <v>478051</v>
+        <v>478221</v>
       </c>
       <c r="R124" t="n">
-        <v>6827739</v>
+        <v>6827719</v>
       </c>
       <c r="S124" t="n">
         <v>10</v>
@@ -13236,10 +13235,10 @@
     </row>
     <row r="125">
       <c r="A125" t="n">
-        <v>120075230</v>
+        <v>120074948</v>
       </c>
       <c r="B125" t="n">
-        <v>78187</v>
+        <v>79160</v>
       </c>
       <c r="C125" t="inlineStr">
         <is>
@@ -13252,21 +13251,21 @@
         </is>
       </c>
       <c r="E125" t="n">
-        <v>353</v>
+        <v>6453</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I125" t="inlineStr"/>
@@ -13276,10 +13275,10 @@
         </is>
       </c>
       <c r="Q125" t="n">
-        <v>478064</v>
+        <v>478070</v>
       </c>
       <c r="R125" t="n">
-        <v>6827866</v>
+        <v>6827723</v>
       </c>
       <c r="S125" t="n">
         <v>10</v>
@@ -13338,10 +13337,10 @@
     </row>
     <row r="126">
       <c r="A126" t="n">
-        <v>120075214</v>
+        <v>120075024</v>
       </c>
       <c r="B126" t="n">
-        <v>78187</v>
+        <v>78278</v>
       </c>
       <c r="C126" t="inlineStr">
         <is>
@@ -13354,21 +13353,21 @@
         </is>
       </c>
       <c r="E126" t="n">
-        <v>353</v>
+        <v>6446</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H126" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I126" t="inlineStr"/>
@@ -13378,10 +13377,10 @@
         </is>
       </c>
       <c r="Q126" t="n">
-        <v>478266</v>
+        <v>478165</v>
       </c>
       <c r="R126" t="n">
-        <v>6827724</v>
+        <v>6827712</v>
       </c>
       <c r="S126" t="n">
         <v>10</v>
@@ -13440,10 +13439,10 @@
     </row>
     <row r="127">
       <c r="A127" t="n">
-        <v>120075207</v>
+        <v>120074946</v>
       </c>
       <c r="B127" t="n">
-        <v>78187</v>
+        <v>79160</v>
       </c>
       <c r="C127" t="inlineStr">
         <is>
@@ -13456,21 +13455,21 @@
         </is>
       </c>
       <c r="E127" t="n">
-        <v>353</v>
+        <v>6453</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H127" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I127" t="inlineStr"/>
@@ -13480,10 +13479,10 @@
         </is>
       </c>
       <c r="Q127" t="n">
-        <v>478157</v>
+        <v>478056</v>
       </c>
       <c r="R127" t="n">
-        <v>6827509</v>
+        <v>6827754</v>
       </c>
       <c r="S127" t="n">
         <v>10</v>
@@ -13542,10 +13541,10 @@
     </row>
     <row r="128">
       <c r="A128" t="n">
-        <v>120075198</v>
+        <v>120075010</v>
       </c>
       <c r="B128" t="n">
-        <v>91858</v>
+        <v>78279</v>
       </c>
       <c r="C128" t="inlineStr">
         <is>
@@ -13554,25 +13553,25 @@
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E128" t="n">
-        <v>4364</v>
+        <v>228912</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H128" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I128" t="inlineStr"/>
@@ -13582,10 +13581,10 @@
         </is>
       </c>
       <c r="Q128" t="n">
-        <v>478163</v>
+        <v>478074</v>
       </c>
       <c r="R128" t="n">
-        <v>6827530</v>
+        <v>6827772</v>
       </c>
       <c r="S128" t="n">
         <v>10</v>
@@ -13644,10 +13643,10 @@
     </row>
     <row r="129">
       <c r="A129" t="n">
-        <v>120075071</v>
+        <v>120075004</v>
       </c>
       <c r="B129" t="n">
-        <v>78542</v>
+        <v>78279</v>
       </c>
       <c r="C129" t="inlineStr">
         <is>
@@ -13660,21 +13659,21 @@
         </is>
       </c>
       <c r="E129" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H129" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I129" t="inlineStr"/>
@@ -13684,10 +13683,10 @@
         </is>
       </c>
       <c r="Q129" t="n">
-        <v>478116</v>
+        <v>478212</v>
       </c>
       <c r="R129" t="n">
-        <v>6827633</v>
+        <v>6827573</v>
       </c>
       <c r="S129" t="n">
         <v>10</v>
@@ -13746,10 +13745,10 @@
     </row>
     <row r="130">
       <c r="A130" t="n">
-        <v>120075078</v>
+        <v>120075205</v>
       </c>
       <c r="B130" t="n">
-        <v>78542</v>
+        <v>78187</v>
       </c>
       <c r="C130" t="inlineStr">
         <is>
@@ -13762,21 +13761,21 @@
         </is>
       </c>
       <c r="E130" t="n">
-        <v>6425</v>
+        <v>353</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H130" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I130" t="inlineStr"/>
@@ -13786,10 +13785,10 @@
         </is>
       </c>
       <c r="Q130" t="n">
-        <v>478116</v>
+        <v>478117</v>
       </c>
       <c r="R130" t="n">
-        <v>6827567</v>
+        <v>6827612</v>
       </c>
       <c r="S130" t="n">
         <v>10</v>
@@ -13848,10 +13847,10 @@
     </row>
     <row r="131">
       <c r="A131" t="n">
-        <v>120075160</v>
+        <v>120075202</v>
       </c>
       <c r="B131" t="n">
-        <v>78542</v>
+        <v>78187</v>
       </c>
       <c r="C131" t="inlineStr">
         <is>
@@ -13864,21 +13863,21 @@
         </is>
       </c>
       <c r="E131" t="n">
-        <v>6425</v>
+        <v>353</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H131" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I131" t="inlineStr"/>
@@ -13888,10 +13887,10 @@
         </is>
       </c>
       <c r="Q131" t="n">
-        <v>478097</v>
+        <v>478218</v>
       </c>
       <c r="R131" t="n">
-        <v>6827744</v>
+        <v>6827721</v>
       </c>
       <c r="S131" t="n">
         <v>10</v>
@@ -13950,10 +13949,10 @@
     </row>
     <row r="132">
       <c r="A132" t="n">
-        <v>120074934</v>
+        <v>120074929</v>
       </c>
       <c r="B132" t="n">
-        <v>79160</v>
+        <v>78576</v>
       </c>
       <c r="C132" t="inlineStr">
         <is>
@@ -13966,21 +13965,21 @@
         </is>
       </c>
       <c r="E132" t="n">
-        <v>6453</v>
+        <v>185</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H132" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I132" t="inlineStr"/>
@@ -13990,10 +13989,10 @@
         </is>
       </c>
       <c r="Q132" t="n">
-        <v>478169</v>
+        <v>478045</v>
       </c>
       <c r="R132" t="n">
-        <v>6827760</v>
+        <v>6827724</v>
       </c>
       <c r="S132" t="n">
         <v>10</v>
@@ -14052,10 +14051,10 @@
     </row>
     <row r="133">
       <c r="A133" t="n">
-        <v>120074942</v>
+        <v>120074914</v>
       </c>
       <c r="B133" t="n">
-        <v>79160</v>
+        <v>78576</v>
       </c>
       <c r="C133" t="inlineStr">
         <is>
@@ -14068,21 +14067,21 @@
         </is>
       </c>
       <c r="E133" t="n">
-        <v>6453</v>
+        <v>185</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H133" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I133" t="inlineStr"/>
@@ -14092,10 +14091,10 @@
         </is>
       </c>
       <c r="Q133" t="n">
-        <v>478065</v>
+        <v>478169</v>
       </c>
       <c r="R133" t="n">
-        <v>6827842</v>
+        <v>6827680</v>
       </c>
       <c r="S133" t="n">
         <v>10</v>
@@ -14154,10 +14153,10 @@
     </row>
     <row r="134">
       <c r="A134" t="n">
-        <v>120075043</v>
+        <v>120075144</v>
       </c>
       <c r="B134" t="n">
-        <v>78278</v>
+        <v>78542</v>
       </c>
       <c r="C134" t="inlineStr">
         <is>
@@ -14170,21 +14169,21 @@
         </is>
       </c>
       <c r="E134" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H134" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I134" t="inlineStr"/>
@@ -14194,10 +14193,10 @@
         </is>
       </c>
       <c r="Q134" t="n">
-        <v>478103</v>
+        <v>478261</v>
       </c>
       <c r="R134" t="n">
-        <v>6827803</v>
+        <v>6827822</v>
       </c>
       <c r="S134" t="n">
         <v>10</v>
@@ -14256,10 +14255,10 @@
     </row>
     <row r="135">
       <c r="A135" t="n">
-        <v>120075044</v>
+        <v>120074883</v>
       </c>
       <c r="B135" t="n">
-        <v>78278</v>
+        <v>79160</v>
       </c>
       <c r="C135" t="inlineStr">
         <is>
@@ -14272,21 +14271,21 @@
         </is>
       </c>
       <c r="E135" t="n">
-        <v>6446</v>
+        <v>6453</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H135" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I135" t="inlineStr"/>
@@ -14296,10 +14295,10 @@
         </is>
       </c>
       <c r="Q135" t="n">
-        <v>478060</v>
+        <v>478142</v>
       </c>
       <c r="R135" t="n">
-        <v>6827770</v>
+        <v>6827623</v>
       </c>
       <c r="S135" t="n">
         <v>10</v>
@@ -14358,10 +14357,10 @@
     </row>
     <row r="136">
       <c r="A136" t="n">
-        <v>120074906</v>
+        <v>120075043</v>
       </c>
       <c r="B136" t="n">
-        <v>79160</v>
+        <v>78278</v>
       </c>
       <c r="C136" t="inlineStr">
         <is>
@@ -14374,21 +14373,21 @@
         </is>
       </c>
       <c r="E136" t="n">
-        <v>6453</v>
+        <v>6446</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H136" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I136" t="inlineStr"/>
@@ -14398,10 +14397,10 @@
         </is>
       </c>
       <c r="Q136" t="n">
-        <v>478294</v>
+        <v>478103</v>
       </c>
       <c r="R136" t="n">
-        <v>6827790</v>
+        <v>6827803</v>
       </c>
       <c r="S136" t="n">
         <v>10</v>
@@ -14460,10 +14459,10 @@
     </row>
     <row r="137">
       <c r="A137" t="n">
-        <v>120075029</v>
+        <v>120074891</v>
       </c>
       <c r="B137" t="n">
-        <v>78278</v>
+        <v>79160</v>
       </c>
       <c r="C137" t="inlineStr">
         <is>
@@ -14476,21 +14475,21 @@
         </is>
       </c>
       <c r="E137" t="n">
-        <v>6446</v>
+        <v>6453</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H137" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I137" t="inlineStr"/>
@@ -14500,10 +14499,10 @@
         </is>
       </c>
       <c r="Q137" t="n">
-        <v>478115</v>
+        <v>478212</v>
       </c>
       <c r="R137" t="n">
-        <v>6827564</v>
+        <v>6827573</v>
       </c>
       <c r="S137" t="n">
         <v>10</v>
@@ -14562,10 +14561,10 @@
     </row>
     <row r="138">
       <c r="A138" t="n">
-        <v>120074933</v>
+        <v>120075007</v>
       </c>
       <c r="B138" t="n">
-        <v>79160</v>
+        <v>78279</v>
       </c>
       <c r="C138" t="inlineStr">
         <is>
@@ -14578,21 +14577,21 @@
         </is>
       </c>
       <c r="E138" t="n">
-        <v>6453</v>
+        <v>228912</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H138" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I138" t="inlineStr"/>
@@ -14602,10 +14601,10 @@
         </is>
       </c>
       <c r="Q138" t="n">
-        <v>478189</v>
+        <v>478285</v>
       </c>
       <c r="R138" t="n">
-        <v>6827761</v>
+        <v>6827770</v>
       </c>
       <c r="S138" t="n">
         <v>10</v>
@@ -14664,10 +14663,10 @@
     </row>
     <row r="139">
       <c r="A139" t="n">
-        <v>120075142</v>
+        <v>120075234</v>
       </c>
       <c r="B139" t="n">
-        <v>78542</v>
+        <v>78187</v>
       </c>
       <c r="C139" t="inlineStr">
         <is>
@@ -14680,21 +14679,21 @@
         </is>
       </c>
       <c r="E139" t="n">
-        <v>6425</v>
+        <v>353</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H139" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I139" t="inlineStr"/>
@@ -14704,10 +14703,10 @@
         </is>
       </c>
       <c r="Q139" t="n">
-        <v>478313</v>
+        <v>478069</v>
       </c>
       <c r="R139" t="n">
-        <v>6827798</v>
+        <v>6827741</v>
       </c>
       <c r="S139" t="n">
         <v>10</v>
@@ -14766,10 +14765,10 @@
     </row>
     <row r="140">
       <c r="A140" t="n">
-        <v>120074881</v>
+        <v>120075223</v>
       </c>
       <c r="B140" t="n">
-        <v>79160</v>
+        <v>78187</v>
       </c>
       <c r="C140" t="inlineStr">
         <is>
@@ -14782,21 +14781,21 @@
         </is>
       </c>
       <c r="E140" t="n">
-        <v>6453</v>
+        <v>353</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H140" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I140" t="inlineStr"/>
@@ -14806,10 +14805,10 @@
         </is>
       </c>
       <c r="Q140" t="n">
-        <v>478184</v>
+        <v>478076</v>
       </c>
       <c r="R140" t="n">
-        <v>6827728</v>
+        <v>6827777</v>
       </c>
       <c r="S140" t="n">
         <v>10</v>
@@ -14868,7 +14867,7 @@
     </row>
     <row r="141">
       <c r="A141" t="n">
-        <v>120075082</v>
+        <v>120075084</v>
       </c>
       <c r="B141" t="n">
         <v>78542</v>
@@ -14908,10 +14907,10 @@
         </is>
       </c>
       <c r="Q141" t="n">
-        <v>478097</v>
+        <v>478098</v>
       </c>
       <c r="R141" t="n">
-        <v>6827544</v>
+        <v>6827520</v>
       </c>
       <c r="S141" t="n">
         <v>10</v>
@@ -14970,10 +14969,10 @@
     </row>
     <row r="142">
       <c r="A142" t="n">
-        <v>120075013</v>
+        <v>120075129</v>
       </c>
       <c r="B142" t="n">
-        <v>78279</v>
+        <v>78542</v>
       </c>
       <c r="C142" t="inlineStr">
         <is>
@@ -14986,21 +14985,21 @@
         </is>
       </c>
       <c r="E142" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H142" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I142" t="inlineStr"/>
@@ -15010,10 +15009,10 @@
         </is>
       </c>
       <c r="Q142" t="n">
-        <v>478239</v>
+        <v>478265</v>
       </c>
       <c r="R142" t="n">
-        <v>6827752</v>
+        <v>6827707</v>
       </c>
       <c r="S142" t="n">
         <v>10</v>
@@ -15072,10 +15071,10 @@
     </row>
     <row r="143">
       <c r="A143" t="n">
-        <v>120075136</v>
+        <v>120075016</v>
       </c>
       <c r="B143" t="n">
-        <v>78542</v>
+        <v>79623</v>
       </c>
       <c r="C143" t="inlineStr">
         <is>
@@ -15088,21 +15087,21 @@
         </is>
       </c>
       <c r="E143" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H143" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I143" t="inlineStr"/>
@@ -15112,10 +15111,10 @@
         </is>
       </c>
       <c r="Q143" t="n">
-        <v>478290</v>
+        <v>478096</v>
       </c>
       <c r="R143" t="n">
-        <v>6827758</v>
+        <v>6827549</v>
       </c>
       <c r="S143" t="n">
         <v>10</v>
@@ -15174,10 +15173,10 @@
     </row>
     <row r="144">
       <c r="A144" t="n">
-        <v>120075016</v>
+        <v>120075046</v>
       </c>
       <c r="B144" t="n">
-        <v>79623</v>
+        <v>78278</v>
       </c>
       <c r="C144" t="inlineStr">
         <is>
@@ -15190,21 +15189,21 @@
         </is>
       </c>
       <c r="E144" t="n">
-        <v>6458</v>
+        <v>6446</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H144" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I144" t="inlineStr"/>
@@ -15214,10 +15213,10 @@
         </is>
       </c>
       <c r="Q144" t="n">
-        <v>478096</v>
+        <v>478285</v>
       </c>
       <c r="R144" t="n">
-        <v>6827549</v>
+        <v>6827770</v>
       </c>
       <c r="S144" t="n">
         <v>10</v>
@@ -15276,10 +15275,10 @@
     </row>
     <row r="145">
       <c r="A145" t="n">
-        <v>120075128</v>
+        <v>120074892</v>
       </c>
       <c r="B145" t="n">
-        <v>78542</v>
+        <v>79160</v>
       </c>
       <c r="C145" t="inlineStr">
         <is>
@@ -15292,21 +15291,21 @@
         </is>
       </c>
       <c r="E145" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H145" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I145" t="inlineStr"/>
@@ -15316,10 +15315,10 @@
         </is>
       </c>
       <c r="Q145" t="n">
-        <v>478275</v>
+        <v>478243</v>
       </c>
       <c r="R145" t="n">
-        <v>6827710</v>
+        <v>6827585</v>
       </c>
       <c r="S145" t="n">
         <v>10</v>
@@ -15378,10 +15377,10 @@
     </row>
     <row r="146">
       <c r="A146" t="n">
-        <v>120075045</v>
+        <v>120075121</v>
       </c>
       <c r="B146" t="n">
-        <v>78278</v>
+        <v>78542</v>
       </c>
       <c r="C146" t="inlineStr">
         <is>
@@ -15394,21 +15393,21 @@
         </is>
       </c>
       <c r="E146" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H146" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I146" t="inlineStr"/>
@@ -15418,10 +15417,10 @@
         </is>
       </c>
       <c r="Q146" t="n">
-        <v>478070</v>
+        <v>478232</v>
       </c>
       <c r="R146" t="n">
-        <v>6827723</v>
+        <v>6827659</v>
       </c>
       <c r="S146" t="n">
         <v>10</v>
@@ -15480,10 +15479,10 @@
     </row>
     <row r="147">
       <c r="A147" t="n">
-        <v>120075177</v>
+        <v>120074942</v>
       </c>
       <c r="B147" t="n">
-        <v>78542</v>
+        <v>79160</v>
       </c>
       <c r="C147" t="inlineStr">
         <is>
@@ -15496,21 +15495,21 @@
         </is>
       </c>
       <c r="E147" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G147" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H147" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I147" t="inlineStr"/>
@@ -15520,10 +15519,10 @@
         </is>
       </c>
       <c r="Q147" t="n">
-        <v>478075</v>
+        <v>478065</v>
       </c>
       <c r="R147" t="n">
-        <v>6827717</v>
+        <v>6827842</v>
       </c>
       <c r="S147" t="n">
         <v>10</v>
@@ -15582,10 +15581,10 @@
     </row>
     <row r="148">
       <c r="A148" t="n">
-        <v>120075038</v>
+        <v>120075011</v>
       </c>
       <c r="B148" t="n">
-        <v>78278</v>
+        <v>78279</v>
       </c>
       <c r="C148" t="inlineStr">
         <is>
@@ -15598,21 +15597,21 @@
         </is>
       </c>
       <c r="E148" t="n">
-        <v>6446</v>
+        <v>228912</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G148" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H148" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I148" t="inlineStr"/>
@@ -15622,10 +15621,10 @@
         </is>
       </c>
       <c r="Q148" t="n">
-        <v>478261</v>
+        <v>478103</v>
       </c>
       <c r="R148" t="n">
-        <v>6827731</v>
+        <v>6827803</v>
       </c>
       <c r="S148" t="n">
         <v>10</v>
@@ -15684,10 +15683,10 @@
     </row>
     <row r="149">
       <c r="A149" t="n">
-        <v>120075068</v>
+        <v>120075001</v>
       </c>
       <c r="B149" t="n">
-        <v>78542</v>
+        <v>78279</v>
       </c>
       <c r="C149" t="inlineStr">
         <is>
@@ -15700,21 +15699,21 @@
         </is>
       </c>
       <c r="E149" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G149" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H149" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I149" t="inlineStr"/>
@@ -15724,10 +15723,10 @@
         </is>
       </c>
       <c r="Q149" t="n">
-        <v>478174</v>
+        <v>478125</v>
       </c>
       <c r="R149" t="n">
-        <v>6827656</v>
+        <v>6827604</v>
       </c>
       <c r="S149" t="n">
         <v>10</v>
@@ -15786,10 +15785,10 @@
     </row>
     <row r="150">
       <c r="A150" t="n">
-        <v>120075008</v>
+        <v>120075139</v>
       </c>
       <c r="B150" t="n">
-        <v>78279</v>
+        <v>78542</v>
       </c>
       <c r="C150" t="inlineStr">
         <is>
@@ -15802,21 +15801,21 @@
         </is>
       </c>
       <c r="E150" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G150" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H150" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I150" t="inlineStr"/>
@@ -15826,10 +15825,10 @@
         </is>
       </c>
       <c r="Q150" t="n">
-        <v>478299</v>
+        <v>478294</v>
       </c>
       <c r="R150" t="n">
-        <v>6827805</v>
+        <v>6827803</v>
       </c>
       <c r="S150" t="n">
         <v>10</v>
@@ -15888,10 +15887,10 @@
     </row>
     <row r="151">
       <c r="A151" t="n">
-        <v>120075225</v>
+        <v>120075136</v>
       </c>
       <c r="B151" t="n">
-        <v>78187</v>
+        <v>78542</v>
       </c>
       <c r="C151" t="inlineStr">
         <is>
@@ -15904,21 +15903,21 @@
         </is>
       </c>
       <c r="E151" t="n">
-        <v>353</v>
+        <v>6425</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G151" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H151" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I151" t="inlineStr"/>
@@ -15928,10 +15927,10 @@
         </is>
       </c>
       <c r="Q151" t="n">
-        <v>478075</v>
+        <v>478290</v>
       </c>
       <c r="R151" t="n">
-        <v>6827798</v>
+        <v>6827758</v>
       </c>
       <c r="S151" t="n">
         <v>10</v>
@@ -15990,10 +15989,10 @@
     </row>
     <row r="152">
       <c r="A152" t="n">
-        <v>120075205</v>
+        <v>120075131</v>
       </c>
       <c r="B152" t="n">
-        <v>78187</v>
+        <v>78542</v>
       </c>
       <c r="C152" t="inlineStr">
         <is>
@@ -16006,21 +16005,21 @@
         </is>
       </c>
       <c r="E152" t="n">
-        <v>353</v>
+        <v>6425</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G152" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H152" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I152" t="inlineStr"/>
@@ -16030,10 +16029,10 @@
         </is>
       </c>
       <c r="Q152" t="n">
-        <v>478117</v>
+        <v>478258</v>
       </c>
       <c r="R152" t="n">
-        <v>6827612</v>
+        <v>6827731</v>
       </c>
       <c r="S152" t="n">
         <v>10</v>
@@ -16092,10 +16091,10 @@
     </row>
     <row r="153">
       <c r="A153" t="n">
-        <v>120075204</v>
+        <v>120075068</v>
       </c>
       <c r="B153" t="n">
-        <v>78187</v>
+        <v>78542</v>
       </c>
       <c r="C153" t="inlineStr">
         <is>
@@ -16108,21 +16107,21 @@
         </is>
       </c>
       <c r="E153" t="n">
-        <v>353</v>
+        <v>6425</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G153" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H153" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I153" t="inlineStr"/>
@@ -16132,10 +16131,10 @@
         </is>
       </c>
       <c r="Q153" t="n">
-        <v>478115</v>
+        <v>478174</v>
       </c>
       <c r="R153" t="n">
-        <v>6827614</v>
+        <v>6827656</v>
       </c>
       <c r="S153" t="n">
         <v>10</v>
@@ -16194,10 +16193,10 @@
     </row>
     <row r="154">
       <c r="A154" t="n">
-        <v>120075219</v>
+        <v>120075092</v>
       </c>
       <c r="B154" t="n">
-        <v>78187</v>
+        <v>78542</v>
       </c>
       <c r="C154" t="inlineStr">
         <is>
@@ -16210,21 +16209,21 @@
         </is>
       </c>
       <c r="E154" t="n">
-        <v>353</v>
+        <v>6425</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G154" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H154" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I154" t="inlineStr"/>
@@ -16234,10 +16233,10 @@
         </is>
       </c>
       <c r="Q154" t="n">
-        <v>478169</v>
+        <v>478167</v>
       </c>
       <c r="R154" t="n">
-        <v>6827760</v>
+        <v>6827561</v>
       </c>
       <c r="S154" t="n">
         <v>10</v>
@@ -16296,7 +16295,7 @@
     </row>
     <row r="155">
       <c r="A155" t="n">
-        <v>120075064</v>
+        <v>120075086</v>
       </c>
       <c r="B155" t="n">
         <v>78542</v>
@@ -16336,10 +16335,10 @@
         </is>
       </c>
       <c r="Q155" t="n">
-        <v>478192</v>
+        <v>478104</v>
       </c>
       <c r="R155" t="n">
-        <v>6827690</v>
+        <v>6827495</v>
       </c>
       <c r="S155" t="n">
         <v>10</v>
@@ -16398,7 +16397,7 @@
     </row>
     <row r="156">
       <c r="A156" t="n">
-        <v>120074886</v>
+        <v>120074931</v>
       </c>
       <c r="B156" t="n">
         <v>79160</v>
@@ -16438,10 +16437,10 @@
         </is>
       </c>
       <c r="Q156" t="n">
-        <v>478125</v>
+        <v>478261</v>
       </c>
       <c r="R156" t="n">
-        <v>6827604</v>
+        <v>6827822</v>
       </c>
       <c r="S156" t="n">
         <v>10</v>
@@ -16500,10 +16499,10 @@
     </row>
     <row r="157">
       <c r="A157" t="n">
-        <v>120075159</v>
+        <v>120075039</v>
       </c>
       <c r="B157" t="n">
-        <v>78542</v>
+        <v>78278</v>
       </c>
       <c r="C157" t="inlineStr">
         <is>
@@ -16516,21 +16515,21 @@
         </is>
       </c>
       <c r="E157" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G157" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H157" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I157" t="inlineStr"/>
@@ -16540,10 +16539,10 @@
         </is>
       </c>
       <c r="Q157" t="n">
-        <v>478100</v>
+        <v>478238</v>
       </c>
       <c r="R157" t="n">
-        <v>6827729</v>
+        <v>6827752</v>
       </c>
       <c r="S157" t="n">
         <v>10</v>
@@ -16602,7 +16601,7 @@
     </row>
     <row r="158">
       <c r="A158" t="n">
-        <v>120075040</v>
+        <v>120075029</v>
       </c>
       <c r="B158" t="n">
         <v>78278</v>
@@ -16642,10 +16641,10 @@
         </is>
       </c>
       <c r="Q158" t="n">
-        <v>478250</v>
+        <v>478115</v>
       </c>
       <c r="R158" t="n">
-        <v>6827802</v>
+        <v>6827564</v>
       </c>
       <c r="S158" t="n">
         <v>10</v>
@@ -16704,10 +16703,10 @@
     </row>
     <row r="159">
       <c r="A159" t="n">
-        <v>120074944</v>
+        <v>120075045</v>
       </c>
       <c r="B159" t="n">
-        <v>79160</v>
+        <v>78278</v>
       </c>
       <c r="C159" t="inlineStr">
         <is>
@@ -16720,21 +16719,21 @@
         </is>
       </c>
       <c r="E159" t="n">
-        <v>6453</v>
+        <v>6446</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G159" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H159" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I159" t="inlineStr"/>
@@ -16744,10 +16743,10 @@
         </is>
       </c>
       <c r="Q159" t="n">
-        <v>478056</v>
+        <v>478070</v>
       </c>
       <c r="R159" t="n">
-        <v>6827785</v>
+        <v>6827723</v>
       </c>
       <c r="S159" t="n">
         <v>10</v>
@@ -16806,10 +16805,10 @@
     </row>
     <row r="160">
       <c r="A160" t="n">
-        <v>120075025</v>
+        <v>120074933</v>
       </c>
       <c r="B160" t="n">
-        <v>78278</v>
+        <v>79160</v>
       </c>
       <c r="C160" t="inlineStr">
         <is>
@@ -16822,21 +16821,21 @@
         </is>
       </c>
       <c r="E160" t="n">
-        <v>6446</v>
+        <v>6453</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G160" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H160" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I160" t="inlineStr"/>
@@ -16846,10 +16845,10 @@
         </is>
       </c>
       <c r="Q160" t="n">
-        <v>478171</v>
+        <v>478189</v>
       </c>
       <c r="R160" t="n">
-        <v>6827642</v>
+        <v>6827761</v>
       </c>
       <c r="S160" t="n">
         <v>10</v>
@@ -16908,10 +16907,10 @@
     </row>
     <row r="161">
       <c r="A161" t="n">
-        <v>120075039</v>
+        <v>120075217</v>
       </c>
       <c r="B161" t="n">
-        <v>78278</v>
+        <v>78187</v>
       </c>
       <c r="C161" t="inlineStr">
         <is>
@@ -16924,21 +16923,21 @@
         </is>
       </c>
       <c r="E161" t="n">
-        <v>6446</v>
+        <v>353</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G161" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H161" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I161" t="inlineStr"/>
@@ -16948,10 +16947,10 @@
         </is>
       </c>
       <c r="Q161" t="n">
-        <v>478238</v>
+        <v>478264</v>
       </c>
       <c r="R161" t="n">
-        <v>6827752</v>
+        <v>6827839</v>
       </c>
       <c r="S161" t="n">
         <v>10</v>
@@ -17010,10 +17009,10 @@
     </row>
     <row r="162">
       <c r="A162" t="n">
-        <v>120075035</v>
+        <v>120074986</v>
       </c>
       <c r="B162" t="n">
-        <v>78278</v>
+        <v>79624</v>
       </c>
       <c r="C162" t="inlineStr">
         <is>
@@ -17026,21 +17025,21 @@
         </is>
       </c>
       <c r="E162" t="n">
-        <v>6446</v>
+        <v>2081</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G162" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H162" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I162" t="inlineStr"/>
@@ -17050,10 +17049,10 @@
         </is>
       </c>
       <c r="Q162" t="n">
-        <v>478273</v>
+        <v>478096</v>
       </c>
       <c r="R162" t="n">
-        <v>6827711</v>
+        <v>6827549</v>
       </c>
       <c r="S162" t="n">
         <v>10</v>
@@ -17214,10 +17213,10 @@
     </row>
     <row r="164">
       <c r="A164" t="n">
-        <v>120074889</v>
+        <v>120075075</v>
       </c>
       <c r="B164" t="n">
-        <v>79160</v>
+        <v>78542</v>
       </c>
       <c r="C164" t="inlineStr">
         <is>
@@ -17230,21 +17229,21 @@
         </is>
       </c>
       <c r="E164" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G164" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H164" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I164" t="inlineStr"/>
@@ -17254,10 +17253,10 @@
         </is>
       </c>
       <c r="Q164" t="n">
-        <v>478163</v>
+        <v>478139</v>
       </c>
       <c r="R164" t="n">
-        <v>6827536</v>
+        <v>6827554</v>
       </c>
       <c r="S164" t="n">
         <v>10</v>
@@ -17316,7 +17315,7 @@
     </row>
     <row r="165">
       <c r="A165" t="n">
-        <v>120075161</v>
+        <v>120075160</v>
       </c>
       <c r="B165" t="n">
         <v>78542</v>
@@ -17356,10 +17355,10 @@
         </is>
       </c>
       <c r="Q165" t="n">
-        <v>478082</v>
+        <v>478097</v>
       </c>
       <c r="R165" t="n">
-        <v>6827766</v>
+        <v>6827744</v>
       </c>
       <c r="S165" t="n">
         <v>10</v>
@@ -17418,7 +17417,7 @@
     </row>
     <row r="166">
       <c r="A166" t="n">
-        <v>120075121</v>
+        <v>120075164</v>
       </c>
       <c r="B166" t="n">
         <v>78542</v>
@@ -17458,10 +17457,10 @@
         </is>
       </c>
       <c r="Q166" t="n">
-        <v>478232</v>
+        <v>478092</v>
       </c>
       <c r="R166" t="n">
-        <v>6827659</v>
+        <v>6827810</v>
       </c>
       <c r="S166" t="n">
         <v>10</v>
@@ -17520,10 +17519,10 @@
     </row>
     <row r="167">
       <c r="A167" t="n">
-        <v>120075015</v>
+        <v>120075168</v>
       </c>
       <c r="B167" t="n">
-        <v>79623</v>
+        <v>78542</v>
       </c>
       <c r="C167" t="inlineStr">
         <is>
@@ -17536,21 +17535,21 @@
         </is>
       </c>
       <c r="E167" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G167" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H167" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I167" t="inlineStr"/>
@@ -17560,10 +17559,10 @@
         </is>
       </c>
       <c r="Q167" t="n">
-        <v>478114</v>
+        <v>478086</v>
       </c>
       <c r="R167" t="n">
-        <v>6827633</v>
+        <v>6827868</v>
       </c>
       <c r="S167" t="n">
         <v>10</v>
@@ -17622,10 +17621,10 @@
     </row>
     <row r="168">
       <c r="A168" t="n">
-        <v>120075239</v>
+        <v>120075078</v>
       </c>
       <c r="B168" t="n">
-        <v>77474</v>
+        <v>78542</v>
       </c>
       <c r="C168" t="inlineStr">
         <is>
@@ -17638,21 +17637,21 @@
         </is>
       </c>
       <c r="E168" t="n">
-        <v>6487</v>
+        <v>6425</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
-          <t>Blågrå svartspik</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G168" t="inlineStr">
         <is>
-          <t>Chaenothecopsis fennica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H168" t="inlineStr">
         <is>
-          <t>(Laurila) Tibell</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I168" t="inlineStr"/>
@@ -17662,10 +17661,10 @@
         </is>
       </c>
       <c r="Q168" t="n">
-        <v>478137</v>
+        <v>478116</v>
       </c>
       <c r="R168" t="n">
-        <v>6827554</v>
+        <v>6827567</v>
       </c>
       <c r="S168" t="n">
         <v>10</v>
@@ -17724,7 +17723,7 @@
     </row>
     <row r="169">
       <c r="A169" t="n">
-        <v>120075061</v>
+        <v>120075172</v>
       </c>
       <c r="B169" t="n">
         <v>78542</v>
@@ -17764,10 +17763,10 @@
         </is>
       </c>
       <c r="Q169" t="n">
-        <v>478160</v>
+        <v>478055</v>
       </c>
       <c r="R169" t="n">
-        <v>6827710</v>
+        <v>6827768</v>
       </c>
       <c r="S169" t="n">
         <v>10</v>
@@ -17826,10 +17825,10 @@
     </row>
     <row r="170">
       <c r="A170" t="n">
-        <v>120075010</v>
+        <v>120074938</v>
       </c>
       <c r="B170" t="n">
-        <v>78279</v>
+        <v>79160</v>
       </c>
       <c r="C170" t="inlineStr">
         <is>
@@ -17842,21 +17841,21 @@
         </is>
       </c>
       <c r="E170" t="n">
-        <v>228912</v>
+        <v>6453</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G170" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H170" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I170" t="inlineStr"/>
@@ -17866,10 +17865,10 @@
         </is>
       </c>
       <c r="Q170" t="n">
-        <v>478074</v>
+        <v>478097</v>
       </c>
       <c r="R170" t="n">
-        <v>6827772</v>
+        <v>6827756</v>
       </c>
       <c r="S170" t="n">
         <v>10</v>
@@ -17928,10 +17927,10 @@
     </row>
     <row r="171">
       <c r="A171" t="n">
-        <v>120075197</v>
+        <v>120075035</v>
       </c>
       <c r="B171" t="n">
-        <v>91858</v>
+        <v>78278</v>
       </c>
       <c r="C171" t="inlineStr">
         <is>
@@ -17940,47 +17939,38 @@
       </c>
       <c r="D171" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E171" t="n">
-        <v>4364</v>
+        <v>6446</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G171" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H171" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I171" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J171" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I171" t="inlineStr"/>
       <c r="P171" t="inlineStr">
         <is>
           <t>Hevoslamm, Dlr</t>
         </is>
       </c>
       <c r="Q171" t="n">
-        <v>478077</v>
+        <v>478273</v>
       </c>
       <c r="R171" t="n">
-        <v>6827805</v>
+        <v>6827711</v>
       </c>
       <c r="S171" t="n">
         <v>10</v>
@@ -18039,10 +18029,10 @@
     </row>
     <row r="172">
       <c r="A172" t="n">
-        <v>120074915</v>
+        <v>120074941</v>
       </c>
       <c r="B172" t="n">
-        <v>78576</v>
+        <v>79160</v>
       </c>
       <c r="C172" t="inlineStr">
         <is>
@@ -18055,21 +18045,21 @@
         </is>
       </c>
       <c r="E172" t="n">
-        <v>185</v>
+        <v>6453</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G172" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H172" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I172" t="inlineStr"/>
@@ -18079,10 +18069,10 @@
         </is>
       </c>
       <c r="Q172" t="n">
-        <v>478102</v>
+        <v>478069</v>
       </c>
       <c r="R172" t="n">
-        <v>6827555</v>
+        <v>6827854</v>
       </c>
       <c r="S172" t="n">
         <v>10</v>
@@ -18141,10 +18131,10 @@
     </row>
     <row r="173">
       <c r="A173" t="n">
-        <v>120074925</v>
+        <v>120075037</v>
       </c>
       <c r="B173" t="n">
-        <v>78576</v>
+        <v>78278</v>
       </c>
       <c r="C173" t="inlineStr">
         <is>
@@ -18157,21 +18147,21 @@
         </is>
       </c>
       <c r="E173" t="n">
-        <v>185</v>
+        <v>6446</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G173" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H173" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I173" t="inlineStr"/>
@@ -18181,10 +18171,10 @@
         </is>
       </c>
       <c r="Q173" t="n">
-        <v>478088</v>
+        <v>478265</v>
       </c>
       <c r="R173" t="n">
-        <v>6827834</v>
+        <v>6827716</v>
       </c>
       <c r="S173" t="n">
         <v>10</v>
@@ -18243,10 +18233,10 @@
     </row>
     <row r="174">
       <c r="A174" t="n">
-        <v>120075227</v>
+        <v>120074927</v>
       </c>
       <c r="B174" t="n">
-        <v>78187</v>
+        <v>78576</v>
       </c>
       <c r="C174" t="inlineStr">
         <is>
@@ -18259,21 +18249,21 @@
         </is>
       </c>
       <c r="E174" t="n">
-        <v>353</v>
+        <v>185</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G174" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H174" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I174" t="inlineStr"/>
@@ -18283,10 +18273,10 @@
         </is>
       </c>
       <c r="Q174" t="n">
-        <v>478088</v>
+        <v>478073</v>
       </c>
       <c r="R174" t="n">
-        <v>6827834</v>
+        <v>6827836</v>
       </c>
       <c r="S174" t="n">
         <v>10</v>
@@ -18345,10 +18335,10 @@
     </row>
     <row r="175">
       <c r="A175" t="n">
-        <v>120075202</v>
+        <v>120074956</v>
       </c>
       <c r="B175" t="n">
-        <v>78187</v>
+        <v>57320</v>
       </c>
       <c r="C175" t="inlineStr">
         <is>
@@ -18361,34 +18351,39 @@
         </is>
       </c>
       <c r="E175" t="n">
-        <v>353</v>
+        <v>100109</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G175" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H175" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I175" t="inlineStr"/>
+      <c r="M175" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P175" t="inlineStr">
         <is>
           <t>Hevoslamm, Dlr</t>
         </is>
       </c>
       <c r="Q175" t="n">
-        <v>478218</v>
+        <v>478278</v>
       </c>
       <c r="R175" t="n">
-        <v>6827721</v>
+        <v>6827832</v>
       </c>
       <c r="S175" t="n">
         <v>10</v>
@@ -18421,6 +18416,11 @@
       <c r="AA175" t="inlineStr">
         <is>
           <t>2024-09-27</t>
+        </is>
+      </c>
+      <c r="AC175" t="inlineStr">
+        <is>
+          <t>Färska ringhack (tall)</t>
         </is>
       </c>
       <c r="AD175" t="b">
@@ -18447,10 +18447,10 @@
     </row>
     <row r="176">
       <c r="A176" t="n">
-        <v>120074939</v>
+        <v>120075047</v>
       </c>
       <c r="B176" t="n">
-        <v>79160</v>
+        <v>78278</v>
       </c>
       <c r="C176" t="inlineStr">
         <is>
@@ -18463,21 +18463,21 @@
         </is>
       </c>
       <c r="E176" t="n">
-        <v>6453</v>
+        <v>6446</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G176" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H176" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I176" t="inlineStr"/>
@@ -18487,10 +18487,10 @@
         </is>
       </c>
       <c r="Q176" t="n">
-        <v>478091</v>
+        <v>478212</v>
       </c>
       <c r="R176" t="n">
-        <v>6827838</v>
+        <v>6827573</v>
       </c>
       <c r="S176" t="n">
         <v>10</v>
@@ -18549,10 +18549,10 @@
     </row>
     <row r="177">
       <c r="A177" t="n">
-        <v>120075027</v>
+        <v>120075204</v>
       </c>
       <c r="B177" t="n">
-        <v>78278</v>
+        <v>78187</v>
       </c>
       <c r="C177" t="inlineStr">
         <is>
@@ -18565,21 +18565,21 @@
         </is>
       </c>
       <c r="E177" t="n">
-        <v>6446</v>
+        <v>353</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G177" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H177" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I177" t="inlineStr"/>
@@ -18589,10 +18589,10 @@
         </is>
       </c>
       <c r="Q177" t="n">
-        <v>478144</v>
+        <v>478115</v>
       </c>
       <c r="R177" t="n">
-        <v>6827593</v>
+        <v>6827614</v>
       </c>
       <c r="S177" t="n">
         <v>10</v>
@@ -18651,10 +18651,10 @@
     </row>
     <row r="178">
       <c r="A178" t="n">
-        <v>120074941</v>
+        <v>120074925</v>
       </c>
       <c r="B178" t="n">
-        <v>79160</v>
+        <v>78576</v>
       </c>
       <c r="C178" t="inlineStr">
         <is>
@@ -18667,21 +18667,21 @@
         </is>
       </c>
       <c r="E178" t="n">
-        <v>6453</v>
+        <v>185</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G178" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H178" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I178" t="inlineStr"/>
@@ -18691,10 +18691,10 @@
         </is>
       </c>
       <c r="Q178" t="n">
-        <v>478069</v>
+        <v>478088</v>
       </c>
       <c r="R178" t="n">
-        <v>6827854</v>
+        <v>6827834</v>
       </c>
       <c r="S178" t="n">
         <v>10</v>
@@ -18753,7 +18753,7 @@
     </row>
     <row r="179">
       <c r="A179" t="n">
-        <v>120075088</v>
+        <v>120075192</v>
       </c>
       <c r="B179" t="n">
         <v>78542</v>
@@ -18793,10 +18793,10 @@
         </is>
       </c>
       <c r="Q179" t="n">
-        <v>478151</v>
+        <v>478282</v>
       </c>
       <c r="R179" t="n">
-        <v>6827509</v>
+        <v>6827683</v>
       </c>
       <c r="S179" t="n">
         <v>10</v>
@@ -18855,10 +18855,10 @@
     </row>
     <row r="180">
       <c r="A180" t="n">
-        <v>120074891</v>
+        <v>120075177</v>
       </c>
       <c r="B180" t="n">
-        <v>79160</v>
+        <v>78542</v>
       </c>
       <c r="C180" t="inlineStr">
         <is>
@@ -18871,21 +18871,21 @@
         </is>
       </c>
       <c r="E180" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G180" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H180" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I180" t="inlineStr"/>
@@ -18895,10 +18895,10 @@
         </is>
       </c>
       <c r="Q180" t="n">
-        <v>478212</v>
+        <v>478075</v>
       </c>
       <c r="R180" t="n">
-        <v>6827573</v>
+        <v>6827717</v>
       </c>
       <c r="S180" t="n">
         <v>10</v>
@@ -18957,7 +18957,7 @@
     </row>
     <row r="181">
       <c r="A181" t="n">
-        <v>120075165</v>
+        <v>120075140</v>
       </c>
       <c r="B181" t="n">
         <v>78542</v>
@@ -18997,10 +18997,10 @@
         </is>
       </c>
       <c r="Q181" t="n">
-        <v>478078</v>
+        <v>478310</v>
       </c>
       <c r="R181" t="n">
-        <v>6827834</v>
+        <v>6827797</v>
       </c>
       <c r="S181" t="n">
         <v>10</v>

--- a/artfynd/A 32983-2023 artfynd.xlsx
+++ b/artfynd/A 32983-2023 artfynd.xlsx
@@ -7815,7 +7815,7 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>120075226</v>
+        <v>120075232</v>
       </c>
       <c r="B72" t="n">
         <v>78187</v>
@@ -7855,10 +7855,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>478098</v>
+        <v>478051</v>
       </c>
       <c r="R72" t="n">
-        <v>6827815</v>
+        <v>6827739</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -7917,10 +7917,10 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>120075088</v>
+        <v>120074912</v>
       </c>
       <c r="B73" t="n">
-        <v>78542</v>
+        <v>78576</v>
       </c>
       <c r="C73" t="inlineStr">
         <is>
@@ -7933,21 +7933,21 @@
         </is>
       </c>
       <c r="E73" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
@@ -7957,10 +7957,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>478151</v>
+        <v>478149</v>
       </c>
       <c r="R73" t="n">
-        <v>6827509</v>
+        <v>6827714</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -8019,10 +8019,10 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>120075128</v>
+        <v>120074904</v>
       </c>
       <c r="B74" t="n">
-        <v>78542</v>
+        <v>79160</v>
       </c>
       <c r="C74" t="inlineStr">
         <is>
@@ -8035,21 +8035,21 @@
         </is>
       </c>
       <c r="E74" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
@@ -8059,10 +8059,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>478275</v>
+        <v>478262</v>
       </c>
       <c r="R74" t="n">
-        <v>6827710</v>
+        <v>6827730</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -8121,10 +8121,10 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>120075077</v>
+        <v>120074905</v>
       </c>
       <c r="B75" t="n">
-        <v>78542</v>
+        <v>79160</v>
       </c>
       <c r="C75" t="inlineStr">
         <is>
@@ -8137,21 +8137,21 @@
         </is>
       </c>
       <c r="E75" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
@@ -8161,10 +8161,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>478124</v>
+        <v>478285</v>
       </c>
       <c r="R75" t="n">
-        <v>6827560</v>
+        <v>6827770</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -8223,10 +8223,10 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>120075145</v>
+        <v>120075028</v>
       </c>
       <c r="B76" t="n">
-        <v>78542</v>
+        <v>78278</v>
       </c>
       <c r="C76" t="inlineStr">
         <is>
@@ -8239,21 +8239,21 @@
         </is>
       </c>
       <c r="E76" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
@@ -8263,10 +8263,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>478226</v>
+        <v>478137</v>
       </c>
       <c r="R76" t="n">
-        <v>6827777</v>
+        <v>6827553</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -8325,10 +8325,10 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>120075048</v>
+        <v>120074945</v>
       </c>
       <c r="B77" t="n">
-        <v>56524</v>
+        <v>79160</v>
       </c>
       <c r="C77" t="inlineStr">
         <is>
@@ -8341,39 +8341,34 @@
         </is>
       </c>
       <c r="E77" t="n">
-        <v>102612</v>
+        <v>6453</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
-      <c r="M77" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
       <c r="P77" t="inlineStr">
         <is>
           <t>Hevoslamm, Dlr</t>
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>478070</v>
+        <v>478061</v>
       </c>
       <c r="R77" t="n">
-        <v>6827723</v>
+        <v>6827770</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -8432,10 +8427,10 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>120075232</v>
+        <v>120074996</v>
       </c>
       <c r="B78" t="n">
-        <v>78187</v>
+        <v>78279</v>
       </c>
       <c r="C78" t="inlineStr">
         <is>
@@ -8448,21 +8443,21 @@
         </is>
       </c>
       <c r="E78" t="n">
-        <v>353</v>
+        <v>228912</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
@@ -8472,10 +8467,10 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>478051</v>
+        <v>478165</v>
       </c>
       <c r="R78" t="n">
-        <v>6827739</v>
+        <v>6827712</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -8534,10 +8529,10 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>120074912</v>
+        <v>120075003</v>
       </c>
       <c r="B79" t="n">
-        <v>78576</v>
+        <v>78279</v>
       </c>
       <c r="C79" t="inlineStr">
         <is>
@@ -8550,21 +8545,21 @@
         </is>
       </c>
       <c r="E79" t="n">
-        <v>185</v>
+        <v>228912</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
@@ -8574,10 +8569,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>478149</v>
+        <v>478137</v>
       </c>
       <c r="R79" t="n">
-        <v>6827714</v>
+        <v>6827553</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -8636,10 +8631,10 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>120074904</v>
+        <v>120075226</v>
       </c>
       <c r="B80" t="n">
-        <v>79160</v>
+        <v>78187</v>
       </c>
       <c r="C80" t="inlineStr">
         <is>
@@ -8652,21 +8647,21 @@
         </is>
       </c>
       <c r="E80" t="n">
-        <v>6453</v>
+        <v>353</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
@@ -8676,10 +8671,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>478262</v>
+        <v>478098</v>
       </c>
       <c r="R80" t="n">
-        <v>6827730</v>
+        <v>6827815</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -8738,10 +8733,10 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>120074905</v>
+        <v>120075088</v>
       </c>
       <c r="B81" t="n">
-        <v>79160</v>
+        <v>78542</v>
       </c>
       <c r="C81" t="inlineStr">
         <is>
@@ -8754,21 +8749,21 @@
         </is>
       </c>
       <c r="E81" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
@@ -8778,10 +8773,10 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>478285</v>
+        <v>478151</v>
       </c>
       <c r="R81" t="n">
-        <v>6827770</v>
+        <v>6827509</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -8840,10 +8835,10 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>120075028</v>
+        <v>120075128</v>
       </c>
       <c r="B82" t="n">
-        <v>78278</v>
+        <v>78542</v>
       </c>
       <c r="C82" t="inlineStr">
         <is>
@@ -8856,21 +8851,21 @@
         </is>
       </c>
       <c r="E82" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
@@ -8880,10 +8875,10 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>478137</v>
+        <v>478275</v>
       </c>
       <c r="R82" t="n">
-        <v>6827553</v>
+        <v>6827710</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -8942,10 +8937,10 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>120074945</v>
+        <v>120075077</v>
       </c>
       <c r="B83" t="n">
-        <v>79160</v>
+        <v>78542</v>
       </c>
       <c r="C83" t="inlineStr">
         <is>
@@ -8958,21 +8953,21 @@
         </is>
       </c>
       <c r="E83" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
@@ -8982,10 +8977,10 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>478061</v>
+        <v>478124</v>
       </c>
       <c r="R83" t="n">
-        <v>6827770</v>
+        <v>6827560</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -9044,10 +9039,10 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>120074996</v>
+        <v>120075145</v>
       </c>
       <c r="B84" t="n">
-        <v>78279</v>
+        <v>78542</v>
       </c>
       <c r="C84" t="inlineStr">
         <is>
@@ -9060,21 +9055,21 @@
         </is>
       </c>
       <c r="E84" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
@@ -9084,10 +9079,10 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>478165</v>
+        <v>478226</v>
       </c>
       <c r="R84" t="n">
-        <v>6827712</v>
+        <v>6827777</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -9146,10 +9141,10 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>120075003</v>
+        <v>120075048</v>
       </c>
       <c r="B85" t="n">
-        <v>78279</v>
+        <v>56524</v>
       </c>
       <c r="C85" t="inlineStr">
         <is>
@@ -9162,34 +9157,39 @@
         </is>
       </c>
       <c r="E85" t="n">
-        <v>228912</v>
+        <v>102612</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
+      <c r="M85" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="P85" t="inlineStr">
         <is>
           <t>Hevoslamm, Dlr</t>
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>478137</v>
+        <v>478070</v>
       </c>
       <c r="R85" t="n">
-        <v>6827553</v>
+        <v>6827723</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -10685,7 +10685,7 @@
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>120074934</v>
+        <v>120074944</v>
       </c>
       <c r="B100" t="n">
         <v>79160</v>
@@ -10725,10 +10725,10 @@
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>478169</v>
+        <v>478056</v>
       </c>
       <c r="R100" t="n">
-        <v>6827760</v>
+        <v>6827785</v>
       </c>
       <c r="S100" t="n">
         <v>10</v>
@@ -10787,7 +10787,7 @@
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>120074944</v>
+        <v>120074934</v>
       </c>
       <c r="B101" t="n">
         <v>79160</v>
@@ -10827,10 +10827,10 @@
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>478056</v>
+        <v>478169</v>
       </c>
       <c r="R101" t="n">
-        <v>6827785</v>
+        <v>6827760</v>
       </c>
       <c r="S101" t="n">
         <v>10</v>
@@ -11807,10 +11807,10 @@
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>120075208</v>
+        <v>120075135</v>
       </c>
       <c r="B111" t="n">
-        <v>78187</v>
+        <v>78542</v>
       </c>
       <c r="C111" t="inlineStr">
         <is>
@@ -11823,21 +11823,21 @@
         </is>
       </c>
       <c r="E111" t="n">
-        <v>353</v>
+        <v>6425</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I111" t="inlineStr"/>
@@ -11847,10 +11847,10 @@
         </is>
       </c>
       <c r="Q111" t="n">
-        <v>478158</v>
+        <v>478291</v>
       </c>
       <c r="R111" t="n">
-        <v>6827519</v>
+        <v>6827744</v>
       </c>
       <c r="S111" t="n">
         <v>10</v>
@@ -11909,10 +11909,10 @@
     </row>
     <row r="112">
       <c r="A112" t="n">
-        <v>120075236</v>
+        <v>120075133</v>
       </c>
       <c r="B112" t="n">
-        <v>78187</v>
+        <v>78542</v>
       </c>
       <c r="C112" t="inlineStr">
         <is>
@@ -11925,21 +11925,21 @@
         </is>
       </c>
       <c r="E112" t="n">
-        <v>353</v>
+        <v>6425</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I112" t="inlineStr"/>
@@ -11949,10 +11949,10 @@
         </is>
       </c>
       <c r="Q112" t="n">
-        <v>478062</v>
+        <v>478258</v>
       </c>
       <c r="R112" t="n">
-        <v>6827740</v>
+        <v>6827753</v>
       </c>
       <c r="S112" t="n">
         <v>10</v>
@@ -12011,7 +12011,7 @@
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>120075135</v>
+        <v>120075163</v>
       </c>
       <c r="B113" t="n">
         <v>78542</v>
@@ -12051,10 +12051,10 @@
         </is>
       </c>
       <c r="Q113" t="n">
-        <v>478291</v>
+        <v>478102</v>
       </c>
       <c r="R113" t="n">
-        <v>6827744</v>
+        <v>6827800</v>
       </c>
       <c r="S113" t="n">
         <v>10</v>
@@ -12113,7 +12113,7 @@
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>120075133</v>
+        <v>120075063</v>
       </c>
       <c r="B114" t="n">
         <v>78542</v>
@@ -12153,10 +12153,10 @@
         </is>
       </c>
       <c r="Q114" t="n">
-        <v>478258</v>
+        <v>478201</v>
       </c>
       <c r="R114" t="n">
-        <v>6827753</v>
+        <v>6827693</v>
       </c>
       <c r="S114" t="n">
         <v>10</v>
@@ -12215,10 +12215,10 @@
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>120075163</v>
+        <v>120075208</v>
       </c>
       <c r="B115" t="n">
-        <v>78542</v>
+        <v>78187</v>
       </c>
       <c r="C115" t="inlineStr">
         <is>
@@ -12231,21 +12231,21 @@
         </is>
       </c>
       <c r="E115" t="n">
-        <v>6425</v>
+        <v>353</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I115" t="inlineStr"/>
@@ -12255,10 +12255,10 @@
         </is>
       </c>
       <c r="Q115" t="n">
-        <v>478102</v>
+        <v>478158</v>
       </c>
       <c r="R115" t="n">
-        <v>6827800</v>
+        <v>6827519</v>
       </c>
       <c r="S115" t="n">
         <v>10</v>
@@ -12317,10 +12317,10 @@
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>120075063</v>
+        <v>120075236</v>
       </c>
       <c r="B116" t="n">
-        <v>78542</v>
+        <v>78187</v>
       </c>
       <c r="C116" t="inlineStr">
         <is>
@@ -12333,21 +12333,21 @@
         </is>
       </c>
       <c r="E116" t="n">
-        <v>6425</v>
+        <v>353</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I116" t="inlineStr"/>
@@ -12357,10 +12357,10 @@
         </is>
       </c>
       <c r="Q116" t="n">
-        <v>478201</v>
+        <v>478062</v>
       </c>
       <c r="R116" t="n">
-        <v>6827693</v>
+        <v>6827740</v>
       </c>
       <c r="S116" t="n">
         <v>10</v>
@@ -13745,10 +13745,10 @@
     </row>
     <row r="130">
       <c r="A130" t="n">
-        <v>120075205</v>
+        <v>120074929</v>
       </c>
       <c r="B130" t="n">
-        <v>78187</v>
+        <v>78576</v>
       </c>
       <c r="C130" t="inlineStr">
         <is>
@@ -13761,21 +13761,21 @@
         </is>
       </c>
       <c r="E130" t="n">
-        <v>353</v>
+        <v>185</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H130" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I130" t="inlineStr"/>
@@ -13785,10 +13785,10 @@
         </is>
       </c>
       <c r="Q130" t="n">
-        <v>478117</v>
+        <v>478045</v>
       </c>
       <c r="R130" t="n">
-        <v>6827612</v>
+        <v>6827724</v>
       </c>
       <c r="S130" t="n">
         <v>10</v>
@@ -13847,10 +13847,10 @@
     </row>
     <row r="131">
       <c r="A131" t="n">
-        <v>120075202</v>
+        <v>120074914</v>
       </c>
       <c r="B131" t="n">
-        <v>78187</v>
+        <v>78576</v>
       </c>
       <c r="C131" t="inlineStr">
         <is>
@@ -13863,21 +13863,21 @@
         </is>
       </c>
       <c r="E131" t="n">
-        <v>353</v>
+        <v>185</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H131" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I131" t="inlineStr"/>
@@ -13887,10 +13887,10 @@
         </is>
       </c>
       <c r="Q131" t="n">
-        <v>478218</v>
+        <v>478169</v>
       </c>
       <c r="R131" t="n">
-        <v>6827721</v>
+        <v>6827680</v>
       </c>
       <c r="S131" t="n">
         <v>10</v>
@@ -13949,10 +13949,10 @@
     </row>
     <row r="132">
       <c r="A132" t="n">
-        <v>120074929</v>
+        <v>120075205</v>
       </c>
       <c r="B132" t="n">
-        <v>78576</v>
+        <v>78187</v>
       </c>
       <c r="C132" t="inlineStr">
         <is>
@@ -13965,21 +13965,21 @@
         </is>
       </c>
       <c r="E132" t="n">
-        <v>185</v>
+        <v>353</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H132" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I132" t="inlineStr"/>
@@ -13989,10 +13989,10 @@
         </is>
       </c>
       <c r="Q132" t="n">
-        <v>478045</v>
+        <v>478117</v>
       </c>
       <c r="R132" t="n">
-        <v>6827724</v>
+        <v>6827612</v>
       </c>
       <c r="S132" t="n">
         <v>10</v>
@@ -14051,10 +14051,10 @@
     </row>
     <row r="133">
       <c r="A133" t="n">
-        <v>120074914</v>
+        <v>120075202</v>
       </c>
       <c r="B133" t="n">
-        <v>78576</v>
+        <v>78187</v>
       </c>
       <c r="C133" t="inlineStr">
         <is>
@@ -14067,21 +14067,21 @@
         </is>
       </c>
       <c r="E133" t="n">
-        <v>185</v>
+        <v>353</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H133" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I133" t="inlineStr"/>
@@ -14091,10 +14091,10 @@
         </is>
       </c>
       <c r="Q133" t="n">
-        <v>478169</v>
+        <v>478218</v>
       </c>
       <c r="R133" t="n">
-        <v>6827680</v>
+        <v>6827721</v>
       </c>
       <c r="S133" t="n">
         <v>10</v>

--- a/artfynd/A 32983-2023 artfynd.xlsx
+++ b/artfynd/A 32983-2023 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>120075012</v>
+        <v>120075226</v>
       </c>
       <c r="B2" t="n">
-        <v>78279</v>
+        <v>78187</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>228912</v>
+        <v>353</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>478055</v>
+        <v>478098</v>
       </c>
       <c r="R2" t="n">
-        <v>6827786</v>
+        <v>6827815</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -777,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>120075159</v>
+        <v>120075215</v>
       </c>
       <c r="B3" t="n">
-        <v>78542</v>
+        <v>78187</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -793,21 +793,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>353</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -817,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>478100</v>
+        <v>478239</v>
       </c>
       <c r="R3" t="n">
-        <v>6827729</v>
+        <v>6827752</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -879,10 +879,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>120075146</v>
+        <v>120075042</v>
       </c>
       <c r="B4" t="n">
-        <v>78542</v>
+        <v>78278</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -895,21 +895,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -919,10 +919,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>478154</v>
+        <v>478074</v>
       </c>
       <c r="R4" t="n">
-        <v>6827747</v>
+        <v>6827775</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -981,10 +981,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>120075161</v>
+        <v>120074883</v>
       </c>
       <c r="B5" t="n">
-        <v>78542</v>
+        <v>79160</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -997,21 +997,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1021,10 +1021,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>478082</v>
+        <v>478142</v>
       </c>
       <c r="R5" t="n">
-        <v>6827766</v>
+        <v>6827623</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1083,10 +1083,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>120075201</v>
+        <v>120075239</v>
       </c>
       <c r="B6" t="n">
-        <v>78187</v>
+        <v>77474</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1099,21 +1099,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>353</v>
+        <v>6487</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Blågrå svartspik</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Chaenothecopsis fennica</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Laurila) Tibell</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1123,10 +1123,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>478182</v>
+        <v>478137</v>
       </c>
       <c r="R6" t="n">
-        <v>6827728</v>
+        <v>6827554</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1185,10 +1185,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>120074922</v>
+        <v>120074942</v>
       </c>
       <c r="B7" t="n">
-        <v>78576</v>
+        <v>79160</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1201,21 +1201,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>185</v>
+        <v>6453</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1225,10 +1225,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>478103</v>
+        <v>478065</v>
       </c>
       <c r="R7" t="n">
-        <v>6827718</v>
+        <v>6827842</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1287,10 +1287,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>120075165</v>
+        <v>120075007</v>
       </c>
       <c r="B8" t="n">
-        <v>78542</v>
+        <v>78279</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1303,21 +1303,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1327,10 +1327,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>478078</v>
+        <v>478285</v>
       </c>
       <c r="R8" t="n">
-        <v>6827834</v>
+        <v>6827770</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1389,7 +1389,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>120075166</v>
+        <v>120075139</v>
       </c>
       <c r="B9" t="n">
         <v>78542</v>
@@ -1429,10 +1429,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>478092</v>
+        <v>478294</v>
       </c>
       <c r="R9" t="n">
-        <v>6827839</v>
+        <v>6827803</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1491,7 +1491,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>120075090</v>
+        <v>120075143</v>
       </c>
       <c r="B10" t="n">
         <v>78542</v>
@@ -1531,10 +1531,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>478161</v>
+        <v>478301</v>
       </c>
       <c r="R10" t="n">
-        <v>6827528</v>
+        <v>6827814</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1593,7 +1593,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>120075094</v>
+        <v>120075167</v>
       </c>
       <c r="B11" t="n">
         <v>78542</v>
@@ -1633,10 +1633,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>478205</v>
+        <v>478105</v>
       </c>
       <c r="R11" t="n">
-        <v>6827556</v>
+        <v>6827851</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1695,7 +1695,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>120075083</v>
+        <v>120075120</v>
       </c>
       <c r="B12" t="n">
         <v>78542</v>
@@ -1735,10 +1735,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>478097</v>
+        <v>478223</v>
       </c>
       <c r="R12" t="n">
-        <v>6827527</v>
+        <v>6827657</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1797,7 +1797,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>120075171</v>
+        <v>120075069</v>
       </c>
       <c r="B13" t="n">
         <v>78542</v>
@@ -1837,10 +1837,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>478073</v>
+        <v>478157</v>
       </c>
       <c r="R13" t="n">
-        <v>6827831</v>
+        <v>6827611</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1899,10 +1899,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>120074888</v>
+        <v>120075168</v>
       </c>
       <c r="B14" t="n">
-        <v>79160</v>
+        <v>78542</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1915,21 +1915,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1939,10 +1939,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>478139</v>
+        <v>478086</v>
       </c>
       <c r="R14" t="n">
-        <v>6827554</v>
+        <v>6827868</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2001,10 +2001,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>120074885</v>
+        <v>120075074</v>
       </c>
       <c r="B15" t="n">
-        <v>79160</v>
+        <v>78542</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2017,21 +2017,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2041,10 +2041,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>478115</v>
+        <v>478138</v>
       </c>
       <c r="R15" t="n">
-        <v>6827614</v>
+        <v>6827599</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2103,10 +2103,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>120074952</v>
+        <v>120075073</v>
       </c>
       <c r="B16" t="n">
-        <v>79131</v>
+        <v>78542</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2119,21 +2119,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>229821</v>
+        <v>6425</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2143,10 +2143,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>478120</v>
+        <v>478116</v>
       </c>
       <c r="R16" t="n">
-        <v>6827605</v>
+        <v>6827617</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2205,10 +2205,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>120074886</v>
+        <v>120075128</v>
       </c>
       <c r="B17" t="n">
-        <v>79160</v>
+        <v>78542</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2221,21 +2221,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2245,10 +2245,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>478125</v>
+        <v>478275</v>
       </c>
       <c r="R17" t="n">
-        <v>6827604</v>
+        <v>6827710</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2307,10 +2307,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>120074943</v>
+        <v>120075197</v>
       </c>
       <c r="B18" t="n">
-        <v>79160</v>
+        <v>91858</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2319,38 +2319,47 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6453</v>
+        <v>4364</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr"/>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="P18" t="inlineStr">
         <is>
           <t>Hevoslamm, Dlr</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>478073</v>
+        <v>478077</v>
       </c>
       <c r="R18" t="n">
-        <v>6827827</v>
+        <v>6827805</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2409,10 +2418,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>120075242</v>
+        <v>120075025</v>
       </c>
       <c r="B19" t="n">
-        <v>77926</v>
+        <v>78278</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2425,21 +2434,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6437</v>
+        <v>6446</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2449,10 +2458,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>478136</v>
+        <v>478171</v>
       </c>
       <c r="R19" t="n">
-        <v>6827556</v>
+        <v>6827642</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2511,10 +2520,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>120075065</v>
+        <v>120074939</v>
       </c>
       <c r="B20" t="n">
-        <v>78542</v>
+        <v>79160</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2527,21 +2536,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2551,10 +2560,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>478169</v>
+        <v>478091</v>
       </c>
       <c r="R20" t="n">
-        <v>6827679</v>
+        <v>6827838</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2613,10 +2622,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>120075203</v>
+        <v>120074887</v>
       </c>
       <c r="B21" t="n">
-        <v>78187</v>
+        <v>79160</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2629,21 +2638,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>353</v>
+        <v>6453</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2653,10 +2662,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>478125</v>
+        <v>478144</v>
       </c>
       <c r="R21" t="n">
-        <v>6827631</v>
+        <v>6827593</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2715,10 +2724,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>120075225</v>
+        <v>120075027</v>
       </c>
       <c r="B22" t="n">
-        <v>78187</v>
+        <v>78278</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2731,21 +2740,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>353</v>
+        <v>6446</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2755,10 +2764,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>478075</v>
+        <v>478144</v>
       </c>
       <c r="R22" t="n">
-        <v>6827798</v>
+        <v>6827593</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2817,10 +2826,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>120075162</v>
+        <v>120075047</v>
       </c>
       <c r="B23" t="n">
-        <v>78542</v>
+        <v>78278</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -2833,21 +2842,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2857,10 +2866,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>478080</v>
+        <v>478212</v>
       </c>
       <c r="R23" t="n">
-        <v>6827808</v>
+        <v>6827573</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2919,10 +2928,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>120075089</v>
+        <v>120075054</v>
       </c>
       <c r="B24" t="n">
-        <v>78542</v>
+        <v>90598</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -2935,21 +2944,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -2959,10 +2968,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>478153</v>
+        <v>478126</v>
       </c>
       <c r="R24" t="n">
-        <v>6827517</v>
+        <v>6827477</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3021,10 +3030,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>120075147</v>
+        <v>120075013</v>
       </c>
       <c r="B25" t="n">
-        <v>78542</v>
+        <v>78279</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3037,21 +3046,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3061,10 +3070,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>478153</v>
+        <v>478239</v>
       </c>
       <c r="R25" t="n">
-        <v>6827728</v>
+        <v>6827752</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3123,7 +3132,7 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>120074998</v>
+        <v>120075008</v>
       </c>
       <c r="B26" t="n">
         <v>78279</v>
@@ -3163,10 +3172,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>478172</v>
+        <v>478299</v>
       </c>
       <c r="R26" t="n">
-        <v>6827640</v>
+        <v>6827805</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3225,10 +3234,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>120075009</v>
+        <v>120074952</v>
       </c>
       <c r="B27" t="n">
-        <v>78279</v>
+        <v>79131</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3241,21 +3250,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>228912</v>
+        <v>229821</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3265,10 +3274,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>478151</v>
+        <v>478120</v>
       </c>
       <c r="R27" t="n">
-        <v>6827745</v>
+        <v>6827605</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3327,10 +3336,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>120074907</v>
+        <v>120075225</v>
       </c>
       <c r="B28" t="n">
-        <v>79160</v>
+        <v>78187</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3343,21 +3352,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6453</v>
+        <v>353</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3367,10 +3376,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>478263</v>
+        <v>478075</v>
       </c>
       <c r="R28" t="n">
-        <v>6827838</v>
+        <v>6827798</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3429,10 +3438,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>120074935</v>
+        <v>120075227</v>
       </c>
       <c r="B29" t="n">
-        <v>79160</v>
+        <v>78187</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3445,21 +3454,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6453</v>
+        <v>353</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3469,10 +3478,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>478150</v>
+        <v>478088</v>
       </c>
       <c r="R29" t="n">
-        <v>6827745</v>
+        <v>6827834</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3531,7 +3540,7 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>120075095</v>
+        <v>120075177</v>
       </c>
       <c r="B30" t="n">
         <v>78542</v>
@@ -3571,10 +3580,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>478219</v>
+        <v>478075</v>
       </c>
       <c r="R30" t="n">
-        <v>6827572</v>
+        <v>6827717</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3633,7 +3642,7 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>120075138</v>
+        <v>120075130</v>
       </c>
       <c r="B31" t="n">
         <v>78542</v>
@@ -3673,10 +3682,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>478294</v>
+        <v>478264</v>
       </c>
       <c r="R31" t="n">
-        <v>6827781</v>
+        <v>6827733</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3735,10 +3744,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>120075067</v>
+        <v>120075219</v>
       </c>
       <c r="B32" t="n">
-        <v>78542</v>
+        <v>78187</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -3751,21 +3760,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6425</v>
+        <v>353</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3775,10 +3784,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>478164</v>
+        <v>478169</v>
       </c>
       <c r="R32" t="n">
-        <v>6827661</v>
+        <v>6827760</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3837,10 +3846,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>120075175</v>
+        <v>120075208</v>
       </c>
       <c r="B33" t="n">
-        <v>78542</v>
+        <v>78187</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -3853,21 +3862,21 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6425</v>
+        <v>353</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -3877,10 +3886,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>478059</v>
+        <v>478158</v>
       </c>
       <c r="R33" t="n">
-        <v>6827739</v>
+        <v>6827519</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -3939,10 +3948,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>120075143</v>
+        <v>120074886</v>
       </c>
       <c r="B34" t="n">
-        <v>78542</v>
+        <v>79160</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -3955,21 +3964,21 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -3979,10 +3988,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>478301</v>
+        <v>478125</v>
       </c>
       <c r="R34" t="n">
-        <v>6827814</v>
+        <v>6827604</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4041,10 +4050,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>120075064</v>
+        <v>120074941</v>
       </c>
       <c r="B35" t="n">
-        <v>78542</v>
+        <v>79160</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4057,21 +4066,21 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4081,10 +4090,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>478192</v>
+        <v>478069</v>
       </c>
       <c r="R35" t="n">
-        <v>6827690</v>
+        <v>6827854</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4143,10 +4152,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>120075040</v>
+        <v>120074961</v>
       </c>
       <c r="B36" t="n">
-        <v>78278</v>
+        <v>90600</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4159,21 +4168,21 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6446</v>
+        <v>5442</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4183,10 +4192,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>478250</v>
+        <v>478230</v>
       </c>
       <c r="R36" t="n">
-        <v>6827802</v>
+        <v>6827780</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4245,10 +4254,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>120075231</v>
+        <v>120074917</v>
       </c>
       <c r="B37" t="n">
-        <v>78187</v>
+        <v>78576</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4261,21 +4270,21 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>353</v>
+        <v>185</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4285,10 +4294,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>478067</v>
+        <v>478095</v>
       </c>
       <c r="R37" t="n">
-        <v>6827863</v>
+        <v>6827533</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4347,7 +4356,7 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>120075214</v>
+        <v>120075217</v>
       </c>
       <c r="B38" t="n">
         <v>78187</v>
@@ -4387,10 +4396,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>478266</v>
+        <v>478264</v>
       </c>
       <c r="R38" t="n">
-        <v>6827724</v>
+        <v>6827839</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4449,10 +4458,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>120075206</v>
+        <v>120074930</v>
       </c>
       <c r="B39" t="n">
-        <v>78187</v>
+        <v>79160</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4465,21 +4474,21 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>353</v>
+        <v>6453</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4489,10 +4498,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>478125</v>
+        <v>478299</v>
       </c>
       <c r="R39" t="n">
-        <v>6827604</v>
+        <v>6827805</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4551,10 +4560,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>120074928</v>
+        <v>120074931</v>
       </c>
       <c r="B40" t="n">
-        <v>78576</v>
+        <v>79160</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -4567,21 +4576,21 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>185</v>
+        <v>6453</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4591,10 +4600,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>478059</v>
+        <v>478261</v>
       </c>
       <c r="R40" t="n">
-        <v>6827740</v>
+        <v>6827822</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4755,10 +4764,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>120075207</v>
+        <v>120075135</v>
       </c>
       <c r="B42" t="n">
-        <v>78187</v>
+        <v>78542</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -4771,21 +4780,21 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>353</v>
+        <v>6425</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -4795,10 +4804,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>478157</v>
+        <v>478291</v>
       </c>
       <c r="R42" t="n">
-        <v>6827509</v>
+        <v>6827744</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4857,10 +4866,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>120075054</v>
+        <v>120075127</v>
       </c>
       <c r="B43" t="n">
-        <v>90598</v>
+        <v>78542</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -4873,21 +4882,21 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -4897,10 +4906,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>478126</v>
+        <v>478292</v>
       </c>
       <c r="R43" t="n">
-        <v>6827477</v>
+        <v>6827708</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -4959,7 +4968,7 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>120075132</v>
+        <v>120075070</v>
       </c>
       <c r="B44" t="n">
         <v>78542</v>
@@ -4999,10 +5008,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>478240</v>
+        <v>478135</v>
       </c>
       <c r="R44" t="n">
-        <v>6827754</v>
+        <v>6827625</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5061,7 +5070,7 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>120075061</v>
+        <v>120075063</v>
       </c>
       <c r="B45" t="n">
         <v>78542</v>
@@ -5101,10 +5110,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>478160</v>
+        <v>478201</v>
       </c>
       <c r="R45" t="n">
-        <v>6827710</v>
+        <v>6827693</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5163,10 +5172,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>120075130</v>
+        <v>120074948</v>
       </c>
       <c r="B46" t="n">
-        <v>78542</v>
+        <v>79160</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -5179,21 +5188,21 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5203,10 +5212,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>478264</v>
+        <v>478070</v>
       </c>
       <c r="R46" t="n">
-        <v>6827733</v>
+        <v>6827723</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5265,10 +5274,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>120075082</v>
+        <v>120075035</v>
       </c>
       <c r="B47" t="n">
-        <v>78542</v>
+        <v>78278</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -5281,21 +5290,21 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5305,10 +5314,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>478097</v>
+        <v>478273</v>
       </c>
       <c r="R47" t="n">
-        <v>6827544</v>
+        <v>6827711</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5367,10 +5376,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>120075120</v>
+        <v>120074889</v>
       </c>
       <c r="B48" t="n">
-        <v>78542</v>
+        <v>79160</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -5383,21 +5392,21 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5407,10 +5416,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>478223</v>
+        <v>478163</v>
       </c>
       <c r="R48" t="n">
-        <v>6827657</v>
+        <v>6827536</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5469,10 +5478,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>120075198</v>
+        <v>120074906</v>
       </c>
       <c r="B49" t="n">
-        <v>91858</v>
+        <v>79160</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -5481,25 +5490,25 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>4364</v>
+        <v>6453</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5509,10 +5518,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>478163</v>
+        <v>478294</v>
       </c>
       <c r="R49" t="n">
-        <v>6827530</v>
+        <v>6827790</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5571,10 +5580,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>120074915</v>
+        <v>120074904</v>
       </c>
       <c r="B50" t="n">
-        <v>78576</v>
+        <v>79160</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -5587,21 +5596,21 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>185</v>
+        <v>6453</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -5611,10 +5620,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>478102</v>
+        <v>478262</v>
       </c>
       <c r="R50" t="n">
-        <v>6827555</v>
+        <v>6827730</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5673,7 +5682,7 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>120074947</v>
+        <v>120074945</v>
       </c>
       <c r="B51" t="n">
         <v>79160</v>
@@ -5716,7 +5725,7 @@
         <v>478061</v>
       </c>
       <c r="R51" t="n">
-        <v>6827751</v>
+        <v>6827770</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5775,10 +5784,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>120075038</v>
+        <v>120075196</v>
       </c>
       <c r="B52" t="n">
-        <v>78278</v>
+        <v>78542</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -5791,21 +5800,21 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -5815,10 +5824,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>478261</v>
+        <v>478288</v>
       </c>
       <c r="R52" t="n">
-        <v>6827731</v>
+        <v>6827682</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -5877,7 +5886,7 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>120075081</v>
+        <v>120075071</v>
       </c>
       <c r="B53" t="n">
         <v>78542</v>
@@ -5917,10 +5926,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>478096</v>
+        <v>478116</v>
       </c>
       <c r="R53" t="n">
-        <v>6827550</v>
+        <v>6827633</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -5979,7 +5988,7 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>120075173</v>
+        <v>120075088</v>
       </c>
       <c r="B54" t="n">
         <v>78542</v>
@@ -6019,10 +6028,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>478052</v>
+        <v>478151</v>
       </c>
       <c r="R54" t="n">
-        <v>6827754</v>
+        <v>6827509</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6183,7 +6192,7 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>120075070</v>
+        <v>120075097</v>
       </c>
       <c r="B56" t="n">
         <v>78542</v>
@@ -6223,10 +6232,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>478135</v>
+        <v>478248</v>
       </c>
       <c r="R56" t="n">
-        <v>6827625</v>
+        <v>6827593</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6285,10 +6294,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>120075174</v>
+        <v>120074914</v>
       </c>
       <c r="B57" t="n">
-        <v>78542</v>
+        <v>78576</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
@@ -6301,21 +6310,21 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -6325,10 +6334,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>478057</v>
+        <v>478169</v>
       </c>
       <c r="R57" t="n">
-        <v>6827749</v>
+        <v>6827680</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6387,10 +6396,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>120074887</v>
+        <v>120074999</v>
       </c>
       <c r="B58" t="n">
-        <v>79160</v>
+        <v>78279</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
@@ -6403,21 +6412,21 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>6453</v>
+        <v>228912</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
@@ -6427,10 +6436,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>478144</v>
+        <v>478161</v>
       </c>
       <c r="R58" t="n">
-        <v>6827593</v>
+        <v>6827592</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6489,10 +6498,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>120075027</v>
+        <v>120075001</v>
       </c>
       <c r="B59" t="n">
-        <v>78278</v>
+        <v>78279</v>
       </c>
       <c r="C59" t="inlineStr">
         <is>
@@ -6505,21 +6514,21 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>6446</v>
+        <v>228912</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
@@ -6529,10 +6538,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>478144</v>
+        <v>478125</v>
       </c>
       <c r="R59" t="n">
-        <v>6827593</v>
+        <v>6827604</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6591,10 +6600,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>120075074</v>
+        <v>120075009</v>
       </c>
       <c r="B60" t="n">
-        <v>78542</v>
+        <v>78279</v>
       </c>
       <c r="C60" t="inlineStr">
         <is>
@@ -6607,21 +6616,21 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
@@ -6631,10 +6640,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>478138</v>
+        <v>478151</v>
       </c>
       <c r="R60" t="n">
-        <v>6827599</v>
+        <v>6827745</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -6693,10 +6702,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>120074881</v>
+        <v>120075207</v>
       </c>
       <c r="B61" t="n">
-        <v>79160</v>
+        <v>78187</v>
       </c>
       <c r="C61" t="inlineStr">
         <is>
@@ -6709,21 +6718,21 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>6453</v>
+        <v>353</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
@@ -6733,10 +6742,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>478184</v>
+        <v>478157</v>
       </c>
       <c r="R61" t="n">
-        <v>6827728</v>
+        <v>6827509</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -6795,10 +6804,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>120074997</v>
+        <v>120074907</v>
       </c>
       <c r="B62" t="n">
-        <v>78279</v>
+        <v>79160</v>
       </c>
       <c r="C62" t="inlineStr">
         <is>
@@ -6811,21 +6820,21 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>228912</v>
+        <v>6453</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
@@ -6835,10 +6844,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>478218</v>
+        <v>478263</v>
       </c>
       <c r="R62" t="n">
-        <v>6827733</v>
+        <v>6827838</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -6897,10 +6906,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>120075196</v>
+        <v>120075015</v>
       </c>
       <c r="B63" t="n">
-        <v>78542</v>
+        <v>79623</v>
       </c>
       <c r="C63" t="inlineStr">
         <is>
@@ -6913,21 +6922,21 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
@@ -6937,10 +6946,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>478288</v>
+        <v>478114</v>
       </c>
       <c r="R63" t="n">
-        <v>6827682</v>
+        <v>6827633</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -6999,10 +7008,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>120075085</v>
+        <v>120075029</v>
       </c>
       <c r="B64" t="n">
-        <v>78542</v>
+        <v>78278</v>
       </c>
       <c r="C64" t="inlineStr">
         <is>
@@ -7015,21 +7024,21 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
@@ -7039,10 +7048,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>478094</v>
+        <v>478115</v>
       </c>
       <c r="R64" t="n">
-        <v>6827504</v>
+        <v>6827564</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -7101,7 +7110,7 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>120075142</v>
+        <v>120075162</v>
       </c>
       <c r="B65" t="n">
         <v>78542</v>
@@ -7141,10 +7150,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>478313</v>
+        <v>478080</v>
       </c>
       <c r="R65" t="n">
-        <v>6827798</v>
+        <v>6827808</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7203,10 +7212,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>120075069</v>
+        <v>120074932</v>
       </c>
       <c r="B66" t="n">
-        <v>78542</v>
+        <v>79160</v>
       </c>
       <c r="C66" t="inlineStr">
         <is>
@@ -7219,21 +7228,21 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
@@ -7243,10 +7252,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>478157</v>
+        <v>478250</v>
       </c>
       <c r="R66" t="n">
-        <v>6827611</v>
+        <v>6827802</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7305,7 +7314,7 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>120075167</v>
+        <v>120075090</v>
       </c>
       <c r="B67" t="n">
         <v>78542</v>
@@ -7345,10 +7354,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>478105</v>
+        <v>478161</v>
       </c>
       <c r="R67" t="n">
-        <v>6827851</v>
+        <v>6827528</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7407,7 +7416,7 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>120075073</v>
+        <v>120075144</v>
       </c>
       <c r="B68" t="n">
         <v>78542</v>
@@ -7447,10 +7456,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>478116</v>
+        <v>478261</v>
       </c>
       <c r="R68" t="n">
-        <v>6827617</v>
+        <v>6827822</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7509,10 +7518,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>120075097</v>
+        <v>120075206</v>
       </c>
       <c r="B69" t="n">
-        <v>78542</v>
+        <v>78187</v>
       </c>
       <c r="C69" t="inlineStr">
         <is>
@@ -7525,21 +7534,21 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>6425</v>
+        <v>353</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
@@ -7549,10 +7558,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>478248</v>
+        <v>478125</v>
       </c>
       <c r="R69" t="n">
-        <v>6827593</v>
+        <v>6827604</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -7611,7 +7620,7 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>120075227</v>
+        <v>120075236</v>
       </c>
       <c r="B70" t="n">
         <v>78187</v>
@@ -7651,10 +7660,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>478088</v>
+        <v>478062</v>
       </c>
       <c r="R70" t="n">
-        <v>6827834</v>
+        <v>6827740</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -7713,10 +7722,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>120075042</v>
+        <v>120075145</v>
       </c>
       <c r="B71" t="n">
-        <v>78278</v>
+        <v>78542</v>
       </c>
       <c r="C71" t="inlineStr">
         <is>
@@ -7729,21 +7738,21 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
@@ -7753,10 +7762,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>478074</v>
+        <v>478226</v>
       </c>
       <c r="R71" t="n">
-        <v>6827775</v>
+        <v>6827777</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -7815,10 +7824,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>120075232</v>
+        <v>120074888</v>
       </c>
       <c r="B72" t="n">
-        <v>78187</v>
+        <v>79160</v>
       </c>
       <c r="C72" t="inlineStr">
         <is>
@@ -7831,21 +7840,21 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>353</v>
+        <v>6453</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
@@ -7855,10 +7864,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>478051</v>
+        <v>478139</v>
       </c>
       <c r="R72" t="n">
-        <v>6827739</v>
+        <v>6827554</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -7917,7 +7926,7 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>120074912</v>
+        <v>120074928</v>
       </c>
       <c r="B73" t="n">
         <v>78576</v>
@@ -7957,10 +7966,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>478149</v>
+        <v>478059</v>
       </c>
       <c r="R73" t="n">
-        <v>6827714</v>
+        <v>6827740</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -8019,10 +8028,10 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>120074904</v>
+        <v>120075161</v>
       </c>
       <c r="B74" t="n">
-        <v>79160</v>
+        <v>78542</v>
       </c>
       <c r="C74" t="inlineStr">
         <is>
@@ -8035,21 +8044,21 @@
         </is>
       </c>
       <c r="E74" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
@@ -8059,10 +8068,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>478262</v>
+        <v>478082</v>
       </c>
       <c r="R74" t="n">
-        <v>6827730</v>
+        <v>6827766</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -8121,10 +8130,10 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>120074905</v>
+        <v>120075078</v>
       </c>
       <c r="B75" t="n">
-        <v>79160</v>
+        <v>78542</v>
       </c>
       <c r="C75" t="inlineStr">
         <is>
@@ -8137,21 +8146,21 @@
         </is>
       </c>
       <c r="E75" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
@@ -8161,10 +8170,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>478285</v>
+        <v>478116</v>
       </c>
       <c r="R75" t="n">
-        <v>6827770</v>
+        <v>6827567</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -8223,10 +8232,10 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>120075028</v>
+        <v>120074882</v>
       </c>
       <c r="B76" t="n">
-        <v>78278</v>
+        <v>79160</v>
       </c>
       <c r="C76" t="inlineStr">
         <is>
@@ -8239,21 +8248,21 @@
         </is>
       </c>
       <c r="E76" t="n">
-        <v>6446</v>
+        <v>6453</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
@@ -8263,10 +8272,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>478137</v>
+        <v>478162</v>
       </c>
       <c r="R76" t="n">
-        <v>6827553</v>
+        <v>6827593</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -8325,10 +8334,10 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>120074945</v>
+        <v>120075048</v>
       </c>
       <c r="B77" t="n">
-        <v>79160</v>
+        <v>56524</v>
       </c>
       <c r="C77" t="inlineStr">
         <is>
@@ -8341,34 +8350,39 @@
         </is>
       </c>
       <c r="E77" t="n">
-        <v>6453</v>
+        <v>102612</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
+      <c r="M77" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="P77" t="inlineStr">
         <is>
           <t>Hevoslamm, Dlr</t>
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>478061</v>
+        <v>478070</v>
       </c>
       <c r="R77" t="n">
-        <v>6827770</v>
+        <v>6827723</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -8427,7 +8441,7 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>120074996</v>
+        <v>120074998</v>
       </c>
       <c r="B78" t="n">
         <v>78279</v>
@@ -8467,10 +8481,10 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>478165</v>
+        <v>478172</v>
       </c>
       <c r="R78" t="n">
-        <v>6827712</v>
+        <v>6827640</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -8631,10 +8645,10 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>120075226</v>
+        <v>120075000</v>
       </c>
       <c r="B80" t="n">
-        <v>78187</v>
+        <v>78279</v>
       </c>
       <c r="C80" t="inlineStr">
         <is>
@@ -8647,21 +8661,21 @@
         </is>
       </c>
       <c r="E80" t="n">
-        <v>353</v>
+        <v>228912</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
@@ -8671,10 +8685,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>478098</v>
+        <v>478121</v>
       </c>
       <c r="R80" t="n">
-        <v>6827815</v>
+        <v>6827607</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -8733,10 +8747,10 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>120075088</v>
+        <v>120074946</v>
       </c>
       <c r="B81" t="n">
-        <v>78542</v>
+        <v>79160</v>
       </c>
       <c r="C81" t="inlineStr">
         <is>
@@ -8749,21 +8763,21 @@
         </is>
       </c>
       <c r="E81" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
@@ -8773,10 +8787,10 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>478151</v>
+        <v>478056</v>
       </c>
       <c r="R81" t="n">
-        <v>6827509</v>
+        <v>6827754</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -8835,10 +8849,10 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>120075128</v>
+        <v>120075204</v>
       </c>
       <c r="B82" t="n">
-        <v>78542</v>
+        <v>78187</v>
       </c>
       <c r="C82" t="inlineStr">
         <is>
@@ -8851,21 +8865,21 @@
         </is>
       </c>
       <c r="E82" t="n">
-        <v>6425</v>
+        <v>353</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
@@ -8875,10 +8889,10 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>478275</v>
+        <v>478115</v>
       </c>
       <c r="R82" t="n">
-        <v>6827710</v>
+        <v>6827614</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -8937,10 +8951,10 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>120075077</v>
+        <v>120075205</v>
       </c>
       <c r="B83" t="n">
-        <v>78542</v>
+        <v>78187</v>
       </c>
       <c r="C83" t="inlineStr">
         <is>
@@ -8953,21 +8967,21 @@
         </is>
       </c>
       <c r="E83" t="n">
-        <v>6425</v>
+        <v>353</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
@@ -8977,10 +8991,10 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>478124</v>
+        <v>478117</v>
       </c>
       <c r="R83" t="n">
-        <v>6827560</v>
+        <v>6827612</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -9039,7 +9053,7 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>120075145</v>
+        <v>120075064</v>
       </c>
       <c r="B84" t="n">
         <v>78542</v>
@@ -9079,10 +9093,10 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>478226</v>
+        <v>478192</v>
       </c>
       <c r="R84" t="n">
-        <v>6827777</v>
+        <v>6827690</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -9141,10 +9155,10 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>120075048</v>
+        <v>120075230</v>
       </c>
       <c r="B85" t="n">
-        <v>56524</v>
+        <v>78187</v>
       </c>
       <c r="C85" t="inlineStr">
         <is>
@@ -9157,39 +9171,34 @@
         </is>
       </c>
       <c r="E85" t="n">
-        <v>102612</v>
+        <v>353</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
-      <c r="M85" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
       <c r="P85" t="inlineStr">
         <is>
           <t>Hevoslamm, Dlr</t>
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>478070</v>
+        <v>478064</v>
       </c>
       <c r="R85" t="n">
-        <v>6827723</v>
+        <v>6827866</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -9248,10 +9257,10 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>120075215</v>
+        <v>120074905</v>
       </c>
       <c r="B86" t="n">
-        <v>78187</v>
+        <v>79160</v>
       </c>
       <c r="C86" t="inlineStr">
         <is>
@@ -9264,21 +9273,21 @@
         </is>
       </c>
       <c r="E86" t="n">
-        <v>353</v>
+        <v>6453</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I86" t="inlineStr"/>
@@ -9288,10 +9297,10 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>478239</v>
+        <v>478285</v>
       </c>
       <c r="R86" t="n">
-        <v>6827752</v>
+        <v>6827770</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>
@@ -9350,10 +9359,10 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>120074961</v>
+        <v>120075163</v>
       </c>
       <c r="B87" t="n">
-        <v>90600</v>
+        <v>78542</v>
       </c>
       <c r="C87" t="inlineStr">
         <is>
@@ -9366,21 +9375,21 @@
         </is>
       </c>
       <c r="E87" t="n">
-        <v>5442</v>
+        <v>6425</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I87" t="inlineStr"/>
@@ -9390,10 +9399,10 @@
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>478230</v>
+        <v>478102</v>
       </c>
       <c r="R87" t="n">
-        <v>6827780</v>
+        <v>6827800</v>
       </c>
       <c r="S87" t="n">
         <v>10</v>
@@ -9452,7 +9461,7 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>120075176</v>
+        <v>120075137</v>
       </c>
       <c r="B88" t="n">
         <v>78542</v>
@@ -9492,10 +9501,10 @@
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>478066</v>
+        <v>478288</v>
       </c>
       <c r="R88" t="n">
-        <v>6827732</v>
+        <v>6827763</v>
       </c>
       <c r="S88" t="n">
         <v>10</v>
@@ -9554,10 +9563,10 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>120075239</v>
+        <v>120075142</v>
       </c>
       <c r="B89" t="n">
-        <v>77474</v>
+        <v>78542</v>
       </c>
       <c r="C89" t="inlineStr">
         <is>
@@ -9570,21 +9579,21 @@
         </is>
       </c>
       <c r="E89" t="n">
-        <v>6487</v>
+        <v>6425</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Blågrå svartspik</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Chaenothecopsis fennica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>(Laurila) Tibell</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I89" t="inlineStr"/>
@@ -9594,10 +9603,10 @@
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>478137</v>
+        <v>478313</v>
       </c>
       <c r="R89" t="n">
-        <v>6827554</v>
+        <v>6827798</v>
       </c>
       <c r="S89" t="n">
         <v>10</v>
@@ -9656,10 +9665,10 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>120074930</v>
+        <v>120075174</v>
       </c>
       <c r="B90" t="n">
-        <v>79160</v>
+        <v>78542</v>
       </c>
       <c r="C90" t="inlineStr">
         <is>
@@ -9672,21 +9681,21 @@
         </is>
       </c>
       <c r="E90" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I90" t="inlineStr"/>
@@ -9696,10 +9705,10 @@
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>478299</v>
+        <v>478057</v>
       </c>
       <c r="R90" t="n">
-        <v>6827805</v>
+        <v>6827749</v>
       </c>
       <c r="S90" t="n">
         <v>10</v>
@@ -9758,10 +9767,10 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>120074999</v>
+        <v>120075066</v>
       </c>
       <c r="B91" t="n">
-        <v>78279</v>
+        <v>78542</v>
       </c>
       <c r="C91" t="inlineStr">
         <is>
@@ -9774,21 +9783,21 @@
         </is>
       </c>
       <c r="E91" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I91" t="inlineStr"/>
@@ -9798,10 +9807,10 @@
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>478161</v>
+        <v>478160</v>
       </c>
       <c r="R91" t="n">
-        <v>6827592</v>
+        <v>6827680</v>
       </c>
       <c r="S91" t="n">
         <v>10</v>
@@ -9860,10 +9869,10 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>120075197</v>
+        <v>120074996</v>
       </c>
       <c r="B92" t="n">
-        <v>91858</v>
+        <v>78279</v>
       </c>
       <c r="C92" t="inlineStr">
         <is>
@@ -9872,47 +9881,38 @@
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E92" t="n">
-        <v>4364</v>
+        <v>228912</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I92" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J92" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I92" t="inlineStr"/>
       <c r="P92" t="inlineStr">
         <is>
           <t>Hevoslamm, Dlr</t>
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>478077</v>
+        <v>478165</v>
       </c>
       <c r="R92" t="n">
-        <v>6827805</v>
+        <v>6827712</v>
       </c>
       <c r="S92" t="n">
         <v>10</v>
@@ -9971,10 +9971,10 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>120075219</v>
+        <v>120074912</v>
       </c>
       <c r="B93" t="n">
-        <v>78187</v>
+        <v>78576</v>
       </c>
       <c r="C93" t="inlineStr">
         <is>
@@ -9987,21 +9987,21 @@
         </is>
       </c>
       <c r="E93" t="n">
-        <v>353</v>
+        <v>185</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I93" t="inlineStr"/>
@@ -10011,10 +10011,10 @@
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>478169</v>
+        <v>478149</v>
       </c>
       <c r="R93" t="n">
-        <v>6827760</v>
+        <v>6827714</v>
       </c>
       <c r="S93" t="n">
         <v>10</v>
@@ -10073,7 +10073,7 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>120075216</v>
+        <v>120075223</v>
       </c>
       <c r="B94" t="n">
         <v>78187</v>
@@ -10113,10 +10113,10 @@
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>478294</v>
+        <v>478076</v>
       </c>
       <c r="R94" t="n">
-        <v>6827790</v>
+        <v>6827777</v>
       </c>
       <c r="S94" t="n">
         <v>10</v>
@@ -10175,10 +10175,10 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>120075137</v>
+        <v>120075026</v>
       </c>
       <c r="B95" t="n">
-        <v>78542</v>
+        <v>78278</v>
       </c>
       <c r="C95" t="inlineStr">
         <is>
@@ -10191,21 +10191,21 @@
         </is>
       </c>
       <c r="E95" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I95" t="inlineStr"/>
@@ -10215,10 +10215,10 @@
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>478288</v>
+        <v>478161</v>
       </c>
       <c r="R95" t="n">
-        <v>6827763</v>
+        <v>6827592</v>
       </c>
       <c r="S95" t="n">
         <v>10</v>
@@ -10277,10 +10277,10 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>120075066</v>
+        <v>120074938</v>
       </c>
       <c r="B96" t="n">
-        <v>78542</v>
+        <v>79160</v>
       </c>
       <c r="C96" t="inlineStr">
         <is>
@@ -10293,21 +10293,21 @@
         </is>
       </c>
       <c r="E96" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I96" t="inlineStr"/>
@@ -10317,10 +10317,10 @@
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>478160</v>
+        <v>478097</v>
       </c>
       <c r="R96" t="n">
-        <v>6827680</v>
+        <v>6827756</v>
       </c>
       <c r="S96" t="n">
         <v>10</v>
@@ -10379,10 +10379,10 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>120074939</v>
+        <v>120075024</v>
       </c>
       <c r="B97" t="n">
-        <v>79160</v>
+        <v>78278</v>
       </c>
       <c r="C97" t="inlineStr">
         <is>
@@ -10395,21 +10395,21 @@
         </is>
       </c>
       <c r="E97" t="n">
-        <v>6453</v>
+        <v>6446</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I97" t="inlineStr"/>
@@ -10419,10 +10419,10 @@
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>478091</v>
+        <v>478165</v>
       </c>
       <c r="R97" t="n">
-        <v>6827838</v>
+        <v>6827712</v>
       </c>
       <c r="S97" t="n">
         <v>10</v>
@@ -10481,10 +10481,10 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>120074932</v>
+        <v>120075028</v>
       </c>
       <c r="B98" t="n">
-        <v>79160</v>
+        <v>78278</v>
       </c>
       <c r="C98" t="inlineStr">
         <is>
@@ -10497,21 +10497,21 @@
         </is>
       </c>
       <c r="E98" t="n">
-        <v>6453</v>
+        <v>6446</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I98" t="inlineStr"/>
@@ -10521,10 +10521,10 @@
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>478250</v>
+        <v>478137</v>
       </c>
       <c r="R98" t="n">
-        <v>6827802</v>
+        <v>6827553</v>
       </c>
       <c r="S98" t="n">
         <v>10</v>
@@ -10583,10 +10583,10 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>120075157</v>
+        <v>120075037</v>
       </c>
       <c r="B99" t="n">
-        <v>78542</v>
+        <v>78278</v>
       </c>
       <c r="C99" t="inlineStr">
         <is>
@@ -10599,21 +10599,21 @@
         </is>
       </c>
       <c r="E99" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I99" t="inlineStr"/>
@@ -10623,10 +10623,10 @@
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>478103</v>
+        <v>478265</v>
       </c>
       <c r="R99" t="n">
-        <v>6827718</v>
+        <v>6827716</v>
       </c>
       <c r="S99" t="n">
         <v>10</v>
@@ -10685,10 +10685,10 @@
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>120074944</v>
+        <v>120075242</v>
       </c>
       <c r="B100" t="n">
-        <v>79160</v>
+        <v>77926</v>
       </c>
       <c r="C100" t="inlineStr">
         <is>
@@ -10701,21 +10701,21 @@
         </is>
       </c>
       <c r="E100" t="n">
-        <v>6453</v>
+        <v>6437</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I100" t="inlineStr"/>
@@ -10725,10 +10725,10 @@
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>478056</v>
+        <v>478136</v>
       </c>
       <c r="R100" t="n">
-        <v>6827785</v>
+        <v>6827556</v>
       </c>
       <c r="S100" t="n">
         <v>10</v>
@@ -10787,10 +10787,10 @@
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>120074934</v>
+        <v>120075012</v>
       </c>
       <c r="B101" t="n">
-        <v>79160</v>
+        <v>78279</v>
       </c>
       <c r="C101" t="inlineStr">
         <is>
@@ -10803,21 +10803,21 @@
         </is>
       </c>
       <c r="E101" t="n">
-        <v>6453</v>
+        <v>228912</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I101" t="inlineStr"/>
@@ -10827,10 +10827,10 @@
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>478169</v>
+        <v>478055</v>
       </c>
       <c r="R101" t="n">
-        <v>6827760</v>
+        <v>6827786</v>
       </c>
       <c r="S101" t="n">
         <v>10</v>
@@ -10889,10 +10889,10 @@
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>120075224</v>
+        <v>120075011</v>
       </c>
       <c r="B102" t="n">
-        <v>78187</v>
+        <v>78279</v>
       </c>
       <c r="C102" t="inlineStr">
         <is>
@@ -10905,21 +10905,21 @@
         </is>
       </c>
       <c r="E102" t="n">
-        <v>353</v>
+        <v>228912</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I102" t="inlineStr"/>
@@ -10929,10 +10929,10 @@
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>478081</v>
+        <v>478103</v>
       </c>
       <c r="R102" t="n">
-        <v>6827789</v>
+        <v>6827803</v>
       </c>
       <c r="S102" t="n">
         <v>10</v>
@@ -10991,10 +10991,10 @@
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>120074917</v>
+        <v>120075010</v>
       </c>
       <c r="B103" t="n">
-        <v>78576</v>
+        <v>78279</v>
       </c>
       <c r="C103" t="inlineStr">
         <is>
@@ -11007,21 +11007,21 @@
         </is>
       </c>
       <c r="E103" t="n">
-        <v>185</v>
+        <v>228912</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I103" t="inlineStr"/>
@@ -11031,10 +11031,10 @@
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>478095</v>
+        <v>478074</v>
       </c>
       <c r="R103" t="n">
-        <v>6827533</v>
+        <v>6827772</v>
       </c>
       <c r="S103" t="n">
         <v>10</v>
@@ -11093,10 +11093,10 @@
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>120075071</v>
+        <v>120075201</v>
       </c>
       <c r="B104" t="n">
-        <v>78542</v>
+        <v>78187</v>
       </c>
       <c r="C104" t="inlineStr">
         <is>
@@ -11109,21 +11109,21 @@
         </is>
       </c>
       <c r="E104" t="n">
-        <v>6425</v>
+        <v>353</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I104" t="inlineStr"/>
@@ -11133,10 +11133,10 @@
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>478116</v>
+        <v>478182</v>
       </c>
       <c r="R104" t="n">
-        <v>6827633</v>
+        <v>6827728</v>
       </c>
       <c r="S104" t="n">
         <v>10</v>
@@ -11195,10 +11195,10 @@
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>120075015</v>
+        <v>120075202</v>
       </c>
       <c r="B105" t="n">
-        <v>79623</v>
+        <v>78187</v>
       </c>
       <c r="C105" t="inlineStr">
         <is>
@@ -11211,21 +11211,21 @@
         </is>
       </c>
       <c r="E105" t="n">
-        <v>6458</v>
+        <v>353</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I105" t="inlineStr"/>
@@ -11235,10 +11235,10 @@
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>478114</v>
+        <v>478218</v>
       </c>
       <c r="R105" t="n">
-        <v>6827633</v>
+        <v>6827721</v>
       </c>
       <c r="S105" t="n">
         <v>10</v>
@@ -11297,10 +11297,10 @@
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>120074882</v>
+        <v>120075231</v>
       </c>
       <c r="B106" t="n">
-        <v>79160</v>
+        <v>78187</v>
       </c>
       <c r="C106" t="inlineStr">
         <is>
@@ -11313,21 +11313,21 @@
         </is>
       </c>
       <c r="E106" t="n">
-        <v>6453</v>
+        <v>353</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I106" t="inlineStr"/>
@@ -11337,10 +11337,10 @@
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>478162</v>
+        <v>478067</v>
       </c>
       <c r="R106" t="n">
-        <v>6827593</v>
+        <v>6827863</v>
       </c>
       <c r="S106" t="n">
         <v>10</v>
@@ -11399,7 +11399,7 @@
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>120075025</v>
+        <v>120075046</v>
       </c>
       <c r="B107" t="n">
         <v>78278</v>
@@ -11439,10 +11439,10 @@
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>478171</v>
+        <v>478285</v>
       </c>
       <c r="R107" t="n">
-        <v>6827642</v>
+        <v>6827770</v>
       </c>
       <c r="S107" t="n">
         <v>10</v>
@@ -11501,10 +11501,10 @@
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>120075087</v>
+        <v>120075040</v>
       </c>
       <c r="B108" t="n">
-        <v>78542</v>
+        <v>78278</v>
       </c>
       <c r="C108" t="inlineStr">
         <is>
@@ -11517,21 +11517,21 @@
         </is>
       </c>
       <c r="E108" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I108" t="inlineStr"/>
@@ -11541,10 +11541,10 @@
         </is>
       </c>
       <c r="Q108" t="n">
-        <v>478145</v>
+        <v>478250</v>
       </c>
       <c r="R108" t="n">
-        <v>6827485</v>
+        <v>6827802</v>
       </c>
       <c r="S108" t="n">
         <v>10</v>
@@ -11603,7 +11603,7 @@
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>120074906</v>
+        <v>120074935</v>
       </c>
       <c r="B109" t="n">
         <v>79160</v>
@@ -11643,10 +11643,10 @@
         </is>
       </c>
       <c r="Q109" t="n">
-        <v>478294</v>
+        <v>478150</v>
       </c>
       <c r="R109" t="n">
-        <v>6827790</v>
+        <v>6827745</v>
       </c>
       <c r="S109" t="n">
         <v>10</v>
@@ -11705,10 +11705,10 @@
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>120075013</v>
+        <v>120075176</v>
       </c>
       <c r="B110" t="n">
-        <v>78279</v>
+        <v>78542</v>
       </c>
       <c r="C110" t="inlineStr">
         <is>
@@ -11721,21 +11721,21 @@
         </is>
       </c>
       <c r="E110" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I110" t="inlineStr"/>
@@ -11745,10 +11745,10 @@
         </is>
       </c>
       <c r="Q110" t="n">
-        <v>478239</v>
+        <v>478066</v>
       </c>
       <c r="R110" t="n">
-        <v>6827752</v>
+        <v>6827732</v>
       </c>
       <c r="S110" t="n">
         <v>10</v>
@@ -11807,7 +11807,7 @@
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>120075135</v>
+        <v>120075081</v>
       </c>
       <c r="B111" t="n">
         <v>78542</v>
@@ -11847,10 +11847,10 @@
         </is>
       </c>
       <c r="Q111" t="n">
-        <v>478291</v>
+        <v>478096</v>
       </c>
       <c r="R111" t="n">
-        <v>6827744</v>
+        <v>6827550</v>
       </c>
       <c r="S111" t="n">
         <v>10</v>
@@ -11909,7 +11909,7 @@
     </row>
     <row r="112">
       <c r="A112" t="n">
-        <v>120075133</v>
+        <v>120075159</v>
       </c>
       <c r="B112" t="n">
         <v>78542</v>
@@ -11949,10 +11949,10 @@
         </is>
       </c>
       <c r="Q112" t="n">
-        <v>478258</v>
+        <v>478100</v>
       </c>
       <c r="R112" t="n">
-        <v>6827753</v>
+        <v>6827729</v>
       </c>
       <c r="S112" t="n">
         <v>10</v>
@@ -12011,7 +12011,7 @@
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>120075163</v>
+        <v>120075173</v>
       </c>
       <c r="B113" t="n">
         <v>78542</v>
@@ -12051,10 +12051,10 @@
         </is>
       </c>
       <c r="Q113" t="n">
-        <v>478102</v>
+        <v>478052</v>
       </c>
       <c r="R113" t="n">
-        <v>6827800</v>
+        <v>6827754</v>
       </c>
       <c r="S113" t="n">
         <v>10</v>
@@ -12113,10 +12113,10 @@
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>120075063</v>
+        <v>120074956</v>
       </c>
       <c r="B114" t="n">
-        <v>78542</v>
+        <v>57320</v>
       </c>
       <c r="C114" t="inlineStr">
         <is>
@@ -12129,34 +12129,39 @@
         </is>
       </c>
       <c r="E114" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I114" t="inlineStr"/>
+      <c r="M114" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P114" t="inlineStr">
         <is>
           <t>Hevoslamm, Dlr</t>
         </is>
       </c>
       <c r="Q114" t="n">
-        <v>478201</v>
+        <v>478278</v>
       </c>
       <c r="R114" t="n">
-        <v>6827693</v>
+        <v>6827832</v>
       </c>
       <c r="S114" t="n">
         <v>10</v>
@@ -12189,6 +12194,11 @@
       <c r="AA114" t="inlineStr">
         <is>
           <t>2024-09-27</t>
+        </is>
+      </c>
+      <c r="AC114" t="inlineStr">
+        <is>
+          <t>Färska ringhack (tall)</t>
         </is>
       </c>
       <c r="AD114" t="b">
@@ -12215,10 +12225,10 @@
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>120075208</v>
+        <v>120075085</v>
       </c>
       <c r="B115" t="n">
-        <v>78187</v>
+        <v>78542</v>
       </c>
       <c r="C115" t="inlineStr">
         <is>
@@ -12231,21 +12241,21 @@
         </is>
       </c>
       <c r="E115" t="n">
-        <v>353</v>
+        <v>6425</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I115" t="inlineStr"/>
@@ -12255,10 +12265,10 @@
         </is>
       </c>
       <c r="Q115" t="n">
-        <v>478158</v>
+        <v>478094</v>
       </c>
       <c r="R115" t="n">
-        <v>6827519</v>
+        <v>6827504</v>
       </c>
       <c r="S115" t="n">
         <v>10</v>
@@ -12317,10 +12327,10 @@
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>120075236</v>
+        <v>120075133</v>
       </c>
       <c r="B116" t="n">
-        <v>78187</v>
+        <v>78542</v>
       </c>
       <c r="C116" t="inlineStr">
         <is>
@@ -12333,21 +12343,21 @@
         </is>
       </c>
       <c r="E116" t="n">
-        <v>353</v>
+        <v>6425</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I116" t="inlineStr"/>
@@ -12357,10 +12367,10 @@
         </is>
       </c>
       <c r="Q116" t="n">
-        <v>478062</v>
+        <v>478258</v>
       </c>
       <c r="R116" t="n">
-        <v>6827740</v>
+        <v>6827753</v>
       </c>
       <c r="S116" t="n">
         <v>10</v>
@@ -12419,10 +12429,10 @@
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>120075026</v>
+        <v>120075089</v>
       </c>
       <c r="B117" t="n">
-        <v>78278</v>
+        <v>78542</v>
       </c>
       <c r="C117" t="inlineStr">
         <is>
@@ -12435,21 +12445,21 @@
         </is>
       </c>
       <c r="E117" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I117" t="inlineStr"/>
@@ -12459,10 +12469,10 @@
         </is>
       </c>
       <c r="Q117" t="n">
-        <v>478161</v>
+        <v>478153</v>
       </c>
       <c r="R117" t="n">
-        <v>6827592</v>
+        <v>6827517</v>
       </c>
       <c r="S117" t="n">
         <v>10</v>
@@ -12521,10 +12531,10 @@
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>120075044</v>
+        <v>120075075</v>
       </c>
       <c r="B118" t="n">
-        <v>78278</v>
+        <v>78542</v>
       </c>
       <c r="C118" t="inlineStr">
         <is>
@@ -12537,21 +12547,21 @@
         </is>
       </c>
       <c r="E118" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I118" t="inlineStr"/>
@@ -12561,10 +12571,10 @@
         </is>
       </c>
       <c r="Q118" t="n">
-        <v>478060</v>
+        <v>478139</v>
       </c>
       <c r="R118" t="n">
-        <v>6827770</v>
+        <v>6827554</v>
       </c>
       <c r="S118" t="n">
         <v>10</v>
@@ -12623,10 +12633,10 @@
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>120075000</v>
+        <v>120074885</v>
       </c>
       <c r="B119" t="n">
-        <v>78279</v>
+        <v>79160</v>
       </c>
       <c r="C119" t="inlineStr">
         <is>
@@ -12639,21 +12649,21 @@
         </is>
       </c>
       <c r="E119" t="n">
-        <v>228912</v>
+        <v>6453</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I119" t="inlineStr"/>
@@ -12663,10 +12673,10 @@
         </is>
       </c>
       <c r="Q119" t="n">
-        <v>478121</v>
+        <v>478115</v>
       </c>
       <c r="R119" t="n">
-        <v>6827607</v>
+        <v>6827614</v>
       </c>
       <c r="S119" t="n">
         <v>10</v>
@@ -12725,10 +12735,10 @@
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>120075008</v>
+        <v>120075045</v>
       </c>
       <c r="B120" t="n">
-        <v>78279</v>
+        <v>78278</v>
       </c>
       <c r="C120" t="inlineStr">
         <is>
@@ -12741,21 +12751,21 @@
         </is>
       </c>
       <c r="E120" t="n">
-        <v>228912</v>
+        <v>6446</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I120" t="inlineStr"/>
@@ -12765,10 +12775,10 @@
         </is>
       </c>
       <c r="Q120" t="n">
-        <v>478299</v>
+        <v>478070</v>
       </c>
       <c r="R120" t="n">
-        <v>6827805</v>
+        <v>6827723</v>
       </c>
       <c r="S120" t="n">
         <v>10</v>
@@ -12827,10 +12837,10 @@
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>120075230</v>
+        <v>120075157</v>
       </c>
       <c r="B121" t="n">
-        <v>78187</v>
+        <v>78542</v>
       </c>
       <c r="C121" t="inlineStr">
         <is>
@@ -12843,21 +12853,21 @@
         </is>
       </c>
       <c r="E121" t="n">
-        <v>353</v>
+        <v>6425</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I121" t="inlineStr"/>
@@ -12867,10 +12877,10 @@
         </is>
       </c>
       <c r="Q121" t="n">
-        <v>478064</v>
+        <v>478103</v>
       </c>
       <c r="R121" t="n">
-        <v>6827866</v>
+        <v>6827718</v>
       </c>
       <c r="S121" t="n">
         <v>10</v>
@@ -12929,10 +12939,10 @@
     </row>
     <row r="122">
       <c r="A122" t="n">
-        <v>120074889</v>
+        <v>120075129</v>
       </c>
       <c r="B122" t="n">
-        <v>79160</v>
+        <v>78542</v>
       </c>
       <c r="C122" t="inlineStr">
         <is>
@@ -12945,21 +12955,21 @@
         </is>
       </c>
       <c r="E122" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I122" t="inlineStr"/>
@@ -12969,10 +12979,10 @@
         </is>
       </c>
       <c r="Q122" t="n">
-        <v>478163</v>
+        <v>478265</v>
       </c>
       <c r="R122" t="n">
-        <v>6827536</v>
+        <v>6827707</v>
       </c>
       <c r="S122" t="n">
         <v>10</v>
@@ -13031,10 +13041,10 @@
     </row>
     <row r="123">
       <c r="A123" t="n">
-        <v>120075060</v>
+        <v>120074881</v>
       </c>
       <c r="B123" t="n">
-        <v>78542</v>
+        <v>79160</v>
       </c>
       <c r="C123" t="inlineStr">
         <is>
@@ -13047,21 +13057,21 @@
         </is>
       </c>
       <c r="E123" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I123" t="inlineStr"/>
@@ -13071,10 +13081,10 @@
         </is>
       </c>
       <c r="Q123" t="n">
-        <v>478087</v>
+        <v>478184</v>
       </c>
       <c r="R123" t="n">
-        <v>6827718</v>
+        <v>6827728</v>
       </c>
       <c r="S123" t="n">
         <v>10</v>
@@ -13133,10 +13143,10 @@
     </row>
     <row r="124">
       <c r="A124" t="n">
-        <v>120075062</v>
+        <v>120074943</v>
       </c>
       <c r="B124" t="n">
-        <v>78542</v>
+        <v>79160</v>
       </c>
       <c r="C124" t="inlineStr">
         <is>
@@ -13149,21 +13159,21 @@
         </is>
       </c>
       <c r="E124" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I124" t="inlineStr"/>
@@ -13173,10 +13183,10 @@
         </is>
       </c>
       <c r="Q124" t="n">
-        <v>478221</v>
+        <v>478073</v>
       </c>
       <c r="R124" t="n">
-        <v>6827719</v>
+        <v>6827827</v>
       </c>
       <c r="S124" t="n">
         <v>10</v>
@@ -13235,10 +13245,10 @@
     </row>
     <row r="125">
       <c r="A125" t="n">
-        <v>120074948</v>
+        <v>120075004</v>
       </c>
       <c r="B125" t="n">
-        <v>79160</v>
+        <v>78279</v>
       </c>
       <c r="C125" t="inlineStr">
         <is>
@@ -13251,21 +13261,21 @@
         </is>
       </c>
       <c r="E125" t="n">
-        <v>6453</v>
+        <v>228912</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I125" t="inlineStr"/>
@@ -13275,10 +13285,10 @@
         </is>
       </c>
       <c r="Q125" t="n">
-        <v>478070</v>
+        <v>478212</v>
       </c>
       <c r="R125" t="n">
-        <v>6827723</v>
+        <v>6827573</v>
       </c>
       <c r="S125" t="n">
         <v>10</v>
@@ -13337,10 +13347,10 @@
     </row>
     <row r="126">
       <c r="A126" t="n">
-        <v>120075024</v>
+        <v>120075067</v>
       </c>
       <c r="B126" t="n">
-        <v>78278</v>
+        <v>78542</v>
       </c>
       <c r="C126" t="inlineStr">
         <is>
@@ -13353,21 +13363,21 @@
         </is>
       </c>
       <c r="E126" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H126" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I126" t="inlineStr"/>
@@ -13377,10 +13387,10 @@
         </is>
       </c>
       <c r="Q126" t="n">
-        <v>478165</v>
+        <v>478164</v>
       </c>
       <c r="R126" t="n">
-        <v>6827712</v>
+        <v>6827661</v>
       </c>
       <c r="S126" t="n">
         <v>10</v>
@@ -13439,10 +13449,10 @@
     </row>
     <row r="127">
       <c r="A127" t="n">
-        <v>120074946</v>
+        <v>120075175</v>
       </c>
       <c r="B127" t="n">
-        <v>79160</v>
+        <v>78542</v>
       </c>
       <c r="C127" t="inlineStr">
         <is>
@@ -13455,21 +13465,21 @@
         </is>
       </c>
       <c r="E127" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H127" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I127" t="inlineStr"/>
@@ -13479,10 +13489,10 @@
         </is>
       </c>
       <c r="Q127" t="n">
-        <v>478056</v>
+        <v>478059</v>
       </c>
       <c r="R127" t="n">
-        <v>6827754</v>
+        <v>6827739</v>
       </c>
       <c r="S127" t="n">
         <v>10</v>
@@ -13541,10 +13551,10 @@
     </row>
     <row r="128">
       <c r="A128" t="n">
-        <v>120075010</v>
+        <v>120075234</v>
       </c>
       <c r="B128" t="n">
-        <v>78279</v>
+        <v>78187</v>
       </c>
       <c r="C128" t="inlineStr">
         <is>
@@ -13557,21 +13567,21 @@
         </is>
       </c>
       <c r="E128" t="n">
-        <v>228912</v>
+        <v>353</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H128" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I128" t="inlineStr"/>
@@ -13581,10 +13591,10 @@
         </is>
       </c>
       <c r="Q128" t="n">
-        <v>478074</v>
+        <v>478069</v>
       </c>
       <c r="R128" t="n">
-        <v>6827772</v>
+        <v>6827741</v>
       </c>
       <c r="S128" t="n">
         <v>10</v>
@@ -13643,10 +13653,10 @@
     </row>
     <row r="129">
       <c r="A129" t="n">
-        <v>120075004</v>
+        <v>120075192</v>
       </c>
       <c r="B129" t="n">
-        <v>78279</v>
+        <v>78542</v>
       </c>
       <c r="C129" t="inlineStr">
         <is>
@@ -13659,21 +13669,21 @@
         </is>
       </c>
       <c r="E129" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H129" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I129" t="inlineStr"/>
@@ -13683,10 +13693,10 @@
         </is>
       </c>
       <c r="Q129" t="n">
-        <v>478212</v>
+        <v>478282</v>
       </c>
       <c r="R129" t="n">
-        <v>6827573</v>
+        <v>6827683</v>
       </c>
       <c r="S129" t="n">
         <v>10</v>
@@ -13745,10 +13755,10 @@
     </row>
     <row r="130">
       <c r="A130" t="n">
-        <v>120074929</v>
+        <v>120075132</v>
       </c>
       <c r="B130" t="n">
-        <v>78576</v>
+        <v>78542</v>
       </c>
       <c r="C130" t="inlineStr">
         <is>
@@ -13761,21 +13771,21 @@
         </is>
       </c>
       <c r="E130" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H130" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I130" t="inlineStr"/>
@@ -13785,10 +13795,10 @@
         </is>
       </c>
       <c r="Q130" t="n">
-        <v>478045</v>
+        <v>478240</v>
       </c>
       <c r="R130" t="n">
-        <v>6827724</v>
+        <v>6827754</v>
       </c>
       <c r="S130" t="n">
         <v>10</v>
@@ -13847,10 +13857,10 @@
     </row>
     <row r="131">
       <c r="A131" t="n">
-        <v>120074914</v>
+        <v>120075146</v>
       </c>
       <c r="B131" t="n">
-        <v>78576</v>
+        <v>78542</v>
       </c>
       <c r="C131" t="inlineStr">
         <is>
@@ -13863,21 +13873,21 @@
         </is>
       </c>
       <c r="E131" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H131" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I131" t="inlineStr"/>
@@ -13887,10 +13897,10 @@
         </is>
       </c>
       <c r="Q131" t="n">
-        <v>478169</v>
+        <v>478154</v>
       </c>
       <c r="R131" t="n">
-        <v>6827680</v>
+        <v>6827747</v>
       </c>
       <c r="S131" t="n">
         <v>10</v>
@@ -13949,10 +13959,10 @@
     </row>
     <row r="132">
       <c r="A132" t="n">
-        <v>120075205</v>
+        <v>120075083</v>
       </c>
       <c r="B132" t="n">
-        <v>78187</v>
+        <v>78542</v>
       </c>
       <c r="C132" t="inlineStr">
         <is>
@@ -13965,21 +13975,21 @@
         </is>
       </c>
       <c r="E132" t="n">
-        <v>353</v>
+        <v>6425</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H132" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I132" t="inlineStr"/>
@@ -13989,10 +13999,10 @@
         </is>
       </c>
       <c r="Q132" t="n">
-        <v>478117</v>
+        <v>478097</v>
       </c>
       <c r="R132" t="n">
-        <v>6827612</v>
+        <v>6827527</v>
       </c>
       <c r="S132" t="n">
         <v>10</v>
@@ -14051,10 +14061,10 @@
     </row>
     <row r="133">
       <c r="A133" t="n">
-        <v>120075202</v>
+        <v>120074997</v>
       </c>
       <c r="B133" t="n">
-        <v>78187</v>
+        <v>78279</v>
       </c>
       <c r="C133" t="inlineStr">
         <is>
@@ -14067,21 +14077,21 @@
         </is>
       </c>
       <c r="E133" t="n">
-        <v>353</v>
+        <v>228912</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H133" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I133" t="inlineStr"/>
@@ -14094,7 +14104,7 @@
         <v>478218</v>
       </c>
       <c r="R133" t="n">
-        <v>6827721</v>
+        <v>6827733</v>
       </c>
       <c r="S133" t="n">
         <v>10</v>
@@ -14153,7 +14163,7 @@
     </row>
     <row r="134">
       <c r="A134" t="n">
-        <v>120075144</v>
+        <v>120075065</v>
       </c>
       <c r="B134" t="n">
         <v>78542</v>
@@ -14193,10 +14203,10 @@
         </is>
       </c>
       <c r="Q134" t="n">
-        <v>478261</v>
+        <v>478169</v>
       </c>
       <c r="R134" t="n">
-        <v>6827822</v>
+        <v>6827679</v>
       </c>
       <c r="S134" t="n">
         <v>10</v>
@@ -14255,10 +14265,10 @@
     </row>
     <row r="135">
       <c r="A135" t="n">
-        <v>120074883</v>
+        <v>120075160</v>
       </c>
       <c r="B135" t="n">
-        <v>79160</v>
+        <v>78542</v>
       </c>
       <c r="C135" t="inlineStr">
         <is>
@@ -14271,21 +14281,21 @@
         </is>
       </c>
       <c r="E135" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H135" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I135" t="inlineStr"/>
@@ -14295,10 +14305,10 @@
         </is>
       </c>
       <c r="Q135" t="n">
-        <v>478142</v>
+        <v>478097</v>
       </c>
       <c r="R135" t="n">
-        <v>6827623</v>
+        <v>6827744</v>
       </c>
       <c r="S135" t="n">
         <v>10</v>
@@ -14357,10 +14367,10 @@
     </row>
     <row r="136">
       <c r="A136" t="n">
-        <v>120075043</v>
+        <v>120074929</v>
       </c>
       <c r="B136" t="n">
-        <v>78278</v>
+        <v>78576</v>
       </c>
       <c r="C136" t="inlineStr">
         <is>
@@ -14373,21 +14383,21 @@
         </is>
       </c>
       <c r="E136" t="n">
-        <v>6446</v>
+        <v>185</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H136" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I136" t="inlineStr"/>
@@ -14397,10 +14407,10 @@
         </is>
       </c>
       <c r="Q136" t="n">
-        <v>478103</v>
+        <v>478045</v>
       </c>
       <c r="R136" t="n">
-        <v>6827803</v>
+        <v>6827724</v>
       </c>
       <c r="S136" t="n">
         <v>10</v>
@@ -14459,10 +14469,10 @@
     </row>
     <row r="137">
       <c r="A137" t="n">
-        <v>120074891</v>
+        <v>120074922</v>
       </c>
       <c r="B137" t="n">
-        <v>79160</v>
+        <v>78576</v>
       </c>
       <c r="C137" t="inlineStr">
         <is>
@@ -14475,21 +14485,21 @@
         </is>
       </c>
       <c r="E137" t="n">
-        <v>6453</v>
+        <v>185</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H137" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I137" t="inlineStr"/>
@@ -14499,10 +14509,10 @@
         </is>
       </c>
       <c r="Q137" t="n">
-        <v>478212</v>
+        <v>478103</v>
       </c>
       <c r="R137" t="n">
-        <v>6827573</v>
+        <v>6827718</v>
       </c>
       <c r="S137" t="n">
         <v>10</v>
@@ -14561,10 +14571,10 @@
     </row>
     <row r="138">
       <c r="A138" t="n">
-        <v>120075007</v>
+        <v>120074944</v>
       </c>
       <c r="B138" t="n">
-        <v>78279</v>
+        <v>79160</v>
       </c>
       <c r="C138" t="inlineStr">
         <is>
@@ -14577,21 +14587,21 @@
         </is>
       </c>
       <c r="E138" t="n">
-        <v>228912</v>
+        <v>6453</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H138" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I138" t="inlineStr"/>
@@ -14601,10 +14611,10 @@
         </is>
       </c>
       <c r="Q138" t="n">
-        <v>478285</v>
+        <v>478056</v>
       </c>
       <c r="R138" t="n">
-        <v>6827770</v>
+        <v>6827785</v>
       </c>
       <c r="S138" t="n">
         <v>10</v>
@@ -14663,10 +14673,10 @@
     </row>
     <row r="139">
       <c r="A139" t="n">
-        <v>120075234</v>
+        <v>120074891</v>
       </c>
       <c r="B139" t="n">
-        <v>78187</v>
+        <v>79160</v>
       </c>
       <c r="C139" t="inlineStr">
         <is>
@@ -14679,21 +14689,21 @@
         </is>
       </c>
       <c r="E139" t="n">
-        <v>353</v>
+        <v>6453</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H139" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I139" t="inlineStr"/>
@@ -14703,10 +14713,10 @@
         </is>
       </c>
       <c r="Q139" t="n">
-        <v>478069</v>
+        <v>478212</v>
       </c>
       <c r="R139" t="n">
-        <v>6827741</v>
+        <v>6827573</v>
       </c>
       <c r="S139" t="n">
         <v>10</v>
@@ -14765,10 +14775,10 @@
     </row>
     <row r="140">
       <c r="A140" t="n">
-        <v>120075223</v>
+        <v>120075084</v>
       </c>
       <c r="B140" t="n">
-        <v>78187</v>
+        <v>78542</v>
       </c>
       <c r="C140" t="inlineStr">
         <is>
@@ -14781,21 +14791,21 @@
         </is>
       </c>
       <c r="E140" t="n">
-        <v>353</v>
+        <v>6425</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H140" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I140" t="inlineStr"/>
@@ -14805,10 +14815,10 @@
         </is>
       </c>
       <c r="Q140" t="n">
-        <v>478076</v>
+        <v>478098</v>
       </c>
       <c r="R140" t="n">
-        <v>6827777</v>
+        <v>6827520</v>
       </c>
       <c r="S140" t="n">
         <v>10</v>
@@ -14867,7 +14877,7 @@
     </row>
     <row r="141">
       <c r="A141" t="n">
-        <v>120075084</v>
+        <v>120075087</v>
       </c>
       <c r="B141" t="n">
         <v>78542</v>
@@ -14907,10 +14917,10 @@
         </is>
       </c>
       <c r="Q141" t="n">
-        <v>478098</v>
+        <v>478145</v>
       </c>
       <c r="R141" t="n">
-        <v>6827520</v>
+        <v>6827485</v>
       </c>
       <c r="S141" t="n">
         <v>10</v>
@@ -14969,10 +14979,10 @@
     </row>
     <row r="142">
       <c r="A142" t="n">
-        <v>120075129</v>
+        <v>120075214</v>
       </c>
       <c r="B142" t="n">
-        <v>78542</v>
+        <v>78187</v>
       </c>
       <c r="C142" t="inlineStr">
         <is>
@@ -14985,21 +14995,21 @@
         </is>
       </c>
       <c r="E142" t="n">
-        <v>6425</v>
+        <v>353</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H142" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I142" t="inlineStr"/>
@@ -15009,10 +15019,10 @@
         </is>
       </c>
       <c r="Q142" t="n">
-        <v>478265</v>
+        <v>478266</v>
       </c>
       <c r="R142" t="n">
-        <v>6827707</v>
+        <v>6827724</v>
       </c>
       <c r="S142" t="n">
         <v>10</v>
@@ -15071,10 +15081,10 @@
     </row>
     <row r="143">
       <c r="A143" t="n">
-        <v>120075016</v>
+        <v>120074915</v>
       </c>
       <c r="B143" t="n">
-        <v>79623</v>
+        <v>78576</v>
       </c>
       <c r="C143" t="inlineStr">
         <is>
@@ -15087,21 +15097,21 @@
         </is>
       </c>
       <c r="E143" t="n">
-        <v>6458</v>
+        <v>185</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H143" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I143" t="inlineStr"/>
@@ -15111,10 +15121,10 @@
         </is>
       </c>
       <c r="Q143" t="n">
-        <v>478096</v>
+        <v>478102</v>
       </c>
       <c r="R143" t="n">
-        <v>6827549</v>
+        <v>6827555</v>
       </c>
       <c r="S143" t="n">
         <v>10</v>
@@ -15173,10 +15183,10 @@
     </row>
     <row r="144">
       <c r="A144" t="n">
-        <v>120075046</v>
+        <v>120075216</v>
       </c>
       <c r="B144" t="n">
-        <v>78278</v>
+        <v>78187</v>
       </c>
       <c r="C144" t="inlineStr">
         <is>
@@ -15189,21 +15199,21 @@
         </is>
       </c>
       <c r="E144" t="n">
-        <v>6446</v>
+        <v>353</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H144" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I144" t="inlineStr"/>
@@ -15213,10 +15223,10 @@
         </is>
       </c>
       <c r="Q144" t="n">
-        <v>478285</v>
+        <v>478294</v>
       </c>
       <c r="R144" t="n">
-        <v>6827770</v>
+        <v>6827790</v>
       </c>
       <c r="S144" t="n">
         <v>10</v>
@@ -15275,10 +15285,10 @@
     </row>
     <row r="145">
       <c r="A145" t="n">
-        <v>120074892</v>
+        <v>120074925</v>
       </c>
       <c r="B145" t="n">
-        <v>79160</v>
+        <v>78576</v>
       </c>
       <c r="C145" t="inlineStr">
         <is>
@@ -15291,21 +15301,21 @@
         </is>
       </c>
       <c r="E145" t="n">
-        <v>6453</v>
+        <v>185</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H145" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I145" t="inlineStr"/>
@@ -15315,10 +15325,10 @@
         </is>
       </c>
       <c r="Q145" t="n">
-        <v>478243</v>
+        <v>478088</v>
       </c>
       <c r="R145" t="n">
-        <v>6827585</v>
+        <v>6827834</v>
       </c>
       <c r="S145" t="n">
         <v>10</v>
@@ -15377,10 +15387,10 @@
     </row>
     <row r="146">
       <c r="A146" t="n">
-        <v>120075121</v>
+        <v>120074892</v>
       </c>
       <c r="B146" t="n">
-        <v>78542</v>
+        <v>79160</v>
       </c>
       <c r="C146" t="inlineStr">
         <is>
@@ -15393,21 +15403,21 @@
         </is>
       </c>
       <c r="E146" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H146" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I146" t="inlineStr"/>
@@ -15417,10 +15427,10 @@
         </is>
       </c>
       <c r="Q146" t="n">
-        <v>478232</v>
+        <v>478243</v>
       </c>
       <c r="R146" t="n">
-        <v>6827659</v>
+        <v>6827585</v>
       </c>
       <c r="S146" t="n">
         <v>10</v>
@@ -15479,10 +15489,10 @@
     </row>
     <row r="147">
       <c r="A147" t="n">
-        <v>120074942</v>
+        <v>120075039</v>
       </c>
       <c r="B147" t="n">
-        <v>79160</v>
+        <v>78278</v>
       </c>
       <c r="C147" t="inlineStr">
         <is>
@@ -15495,21 +15505,21 @@
         </is>
       </c>
       <c r="E147" t="n">
-        <v>6453</v>
+        <v>6446</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G147" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H147" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I147" t="inlineStr"/>
@@ -15519,10 +15529,10 @@
         </is>
       </c>
       <c r="Q147" t="n">
-        <v>478065</v>
+        <v>478238</v>
       </c>
       <c r="R147" t="n">
-        <v>6827842</v>
+        <v>6827752</v>
       </c>
       <c r="S147" t="n">
         <v>10</v>
@@ -15581,10 +15591,10 @@
     </row>
     <row r="148">
       <c r="A148" t="n">
-        <v>120075011</v>
+        <v>120075060</v>
       </c>
       <c r="B148" t="n">
-        <v>78279</v>
+        <v>78542</v>
       </c>
       <c r="C148" t="inlineStr">
         <is>
@@ -15597,21 +15607,21 @@
         </is>
       </c>
       <c r="E148" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G148" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H148" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I148" t="inlineStr"/>
@@ -15621,10 +15631,10 @@
         </is>
       </c>
       <c r="Q148" t="n">
-        <v>478103</v>
+        <v>478087</v>
       </c>
       <c r="R148" t="n">
-        <v>6827803</v>
+        <v>6827718</v>
       </c>
       <c r="S148" t="n">
         <v>10</v>
@@ -15683,10 +15693,10 @@
     </row>
     <row r="149">
       <c r="A149" t="n">
-        <v>120075001</v>
+        <v>120075164</v>
       </c>
       <c r="B149" t="n">
-        <v>78279</v>
+        <v>78542</v>
       </c>
       <c r="C149" t="inlineStr">
         <is>
@@ -15699,21 +15709,21 @@
         </is>
       </c>
       <c r="E149" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G149" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H149" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I149" t="inlineStr"/>
@@ -15723,10 +15733,10 @@
         </is>
       </c>
       <c r="Q149" t="n">
-        <v>478125</v>
+        <v>478092</v>
       </c>
       <c r="R149" t="n">
-        <v>6827604</v>
+        <v>6827810</v>
       </c>
       <c r="S149" t="n">
         <v>10</v>
@@ -15785,7 +15795,7 @@
     </row>
     <row r="150">
       <c r="A150" t="n">
-        <v>120075139</v>
+        <v>120075131</v>
       </c>
       <c r="B150" t="n">
         <v>78542</v>
@@ -15825,10 +15835,10 @@
         </is>
       </c>
       <c r="Q150" t="n">
-        <v>478294</v>
+        <v>478258</v>
       </c>
       <c r="R150" t="n">
-        <v>6827803</v>
+        <v>6827731</v>
       </c>
       <c r="S150" t="n">
         <v>10</v>
@@ -15887,10 +15897,10 @@
     </row>
     <row r="151">
       <c r="A151" t="n">
-        <v>120075136</v>
+        <v>120075198</v>
       </c>
       <c r="B151" t="n">
-        <v>78542</v>
+        <v>91858</v>
       </c>
       <c r="C151" t="inlineStr">
         <is>
@@ -15899,25 +15909,25 @@
       </c>
       <c r="D151" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E151" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G151" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H151" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I151" t="inlineStr"/>
@@ -15927,10 +15937,10 @@
         </is>
       </c>
       <c r="Q151" t="n">
-        <v>478290</v>
+        <v>478163</v>
       </c>
       <c r="R151" t="n">
-        <v>6827758</v>
+        <v>6827530</v>
       </c>
       <c r="S151" t="n">
         <v>10</v>
@@ -15989,10 +15999,10 @@
     </row>
     <row r="152">
       <c r="A152" t="n">
-        <v>120075131</v>
+        <v>120074986</v>
       </c>
       <c r="B152" t="n">
-        <v>78542</v>
+        <v>79624</v>
       </c>
       <c r="C152" t="inlineStr">
         <is>
@@ -16005,21 +16015,21 @@
         </is>
       </c>
       <c r="E152" t="n">
-        <v>6425</v>
+        <v>2081</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G152" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H152" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I152" t="inlineStr"/>
@@ -16029,10 +16039,10 @@
         </is>
       </c>
       <c r="Q152" t="n">
-        <v>478258</v>
+        <v>478096</v>
       </c>
       <c r="R152" t="n">
-        <v>6827731</v>
+        <v>6827549</v>
       </c>
       <c r="S152" t="n">
         <v>10</v>
@@ -16091,10 +16101,10 @@
     </row>
     <row r="153">
       <c r="A153" t="n">
-        <v>120075068</v>
+        <v>120074947</v>
       </c>
       <c r="B153" t="n">
-        <v>78542</v>
+        <v>79160</v>
       </c>
       <c r="C153" t="inlineStr">
         <is>
@@ -16107,21 +16117,21 @@
         </is>
       </c>
       <c r="E153" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G153" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H153" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I153" t="inlineStr"/>
@@ -16131,10 +16141,10 @@
         </is>
       </c>
       <c r="Q153" t="n">
-        <v>478174</v>
+        <v>478061</v>
       </c>
       <c r="R153" t="n">
-        <v>6827656</v>
+        <v>6827751</v>
       </c>
       <c r="S153" t="n">
         <v>10</v>
@@ -16193,10 +16203,10 @@
     </row>
     <row r="154">
       <c r="A154" t="n">
-        <v>120075092</v>
+        <v>120074934</v>
       </c>
       <c r="B154" t="n">
-        <v>78542</v>
+        <v>79160</v>
       </c>
       <c r="C154" t="inlineStr">
         <is>
@@ -16209,21 +16219,21 @@
         </is>
       </c>
       <c r="E154" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G154" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H154" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I154" t="inlineStr"/>
@@ -16233,10 +16243,10 @@
         </is>
       </c>
       <c r="Q154" t="n">
-        <v>478167</v>
+        <v>478169</v>
       </c>
       <c r="R154" t="n">
-        <v>6827561</v>
+        <v>6827760</v>
       </c>
       <c r="S154" t="n">
         <v>10</v>
@@ -16295,10 +16305,10 @@
     </row>
     <row r="155">
       <c r="A155" t="n">
-        <v>120075086</v>
+        <v>120075038</v>
       </c>
       <c r="B155" t="n">
-        <v>78542</v>
+        <v>78278</v>
       </c>
       <c r="C155" t="inlineStr">
         <is>
@@ -16311,21 +16321,21 @@
         </is>
       </c>
       <c r="E155" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G155" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H155" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I155" t="inlineStr"/>
@@ -16335,10 +16345,10 @@
         </is>
       </c>
       <c r="Q155" t="n">
-        <v>478104</v>
+        <v>478261</v>
       </c>
       <c r="R155" t="n">
-        <v>6827495</v>
+        <v>6827731</v>
       </c>
       <c r="S155" t="n">
         <v>10</v>
@@ -16397,10 +16407,10 @@
     </row>
     <row r="156">
       <c r="A156" t="n">
-        <v>120074931</v>
+        <v>120075136</v>
       </c>
       <c r="B156" t="n">
-        <v>79160</v>
+        <v>78542</v>
       </c>
       <c r="C156" t="inlineStr">
         <is>
@@ -16413,21 +16423,21 @@
         </is>
       </c>
       <c r="E156" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G156" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H156" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I156" t="inlineStr"/>
@@ -16437,10 +16447,10 @@
         </is>
       </c>
       <c r="Q156" t="n">
-        <v>478261</v>
+        <v>478290</v>
       </c>
       <c r="R156" t="n">
-        <v>6827822</v>
+        <v>6827758</v>
       </c>
       <c r="S156" t="n">
         <v>10</v>
@@ -16499,10 +16509,10 @@
     </row>
     <row r="157">
       <c r="A157" t="n">
-        <v>120075039</v>
+        <v>120075147</v>
       </c>
       <c r="B157" t="n">
-        <v>78278</v>
+        <v>78542</v>
       </c>
       <c r="C157" t="inlineStr">
         <is>
@@ -16515,21 +16525,21 @@
         </is>
       </c>
       <c r="E157" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G157" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H157" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I157" t="inlineStr"/>
@@ -16539,10 +16549,10 @@
         </is>
       </c>
       <c r="Q157" t="n">
-        <v>478238</v>
+        <v>478153</v>
       </c>
       <c r="R157" t="n">
-        <v>6827752</v>
+        <v>6827728</v>
       </c>
       <c r="S157" t="n">
         <v>10</v>
@@ -16601,10 +16611,10 @@
     </row>
     <row r="158">
       <c r="A158" t="n">
-        <v>120075029</v>
+        <v>120075094</v>
       </c>
       <c r="B158" t="n">
-        <v>78278</v>
+        <v>78542</v>
       </c>
       <c r="C158" t="inlineStr">
         <is>
@@ -16617,21 +16627,21 @@
         </is>
       </c>
       <c r="E158" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G158" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H158" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I158" t="inlineStr"/>
@@ -16641,10 +16651,10 @@
         </is>
       </c>
       <c r="Q158" t="n">
-        <v>478115</v>
+        <v>478205</v>
       </c>
       <c r="R158" t="n">
-        <v>6827564</v>
+        <v>6827556</v>
       </c>
       <c r="S158" t="n">
         <v>10</v>
@@ -16703,10 +16713,10 @@
     </row>
     <row r="159">
       <c r="A159" t="n">
-        <v>120075045</v>
+        <v>120075138</v>
       </c>
       <c r="B159" t="n">
-        <v>78278</v>
+        <v>78542</v>
       </c>
       <c r="C159" t="inlineStr">
         <is>
@@ -16719,21 +16729,21 @@
         </is>
       </c>
       <c r="E159" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G159" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H159" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I159" t="inlineStr"/>
@@ -16743,10 +16753,10 @@
         </is>
       </c>
       <c r="Q159" t="n">
-        <v>478070</v>
+        <v>478294</v>
       </c>
       <c r="R159" t="n">
-        <v>6827723</v>
+        <v>6827781</v>
       </c>
       <c r="S159" t="n">
         <v>10</v>
@@ -16805,10 +16815,10 @@
     </row>
     <row r="160">
       <c r="A160" t="n">
-        <v>120074933</v>
+        <v>120075121</v>
       </c>
       <c r="B160" t="n">
-        <v>79160</v>
+        <v>78542</v>
       </c>
       <c r="C160" t="inlineStr">
         <is>
@@ -16821,21 +16831,21 @@
         </is>
       </c>
       <c r="E160" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G160" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H160" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I160" t="inlineStr"/>
@@ -16845,10 +16855,10 @@
         </is>
       </c>
       <c r="Q160" t="n">
-        <v>478189</v>
+        <v>478232</v>
       </c>
       <c r="R160" t="n">
-        <v>6827761</v>
+        <v>6827659</v>
       </c>
       <c r="S160" t="n">
         <v>10</v>
@@ -16907,7 +16917,7 @@
     </row>
     <row r="161">
       <c r="A161" t="n">
-        <v>120075217</v>
+        <v>120075232</v>
       </c>
       <c r="B161" t="n">
         <v>78187</v>
@@ -16947,10 +16957,10 @@
         </is>
       </c>
       <c r="Q161" t="n">
-        <v>478264</v>
+        <v>478051</v>
       </c>
       <c r="R161" t="n">
-        <v>6827839</v>
+        <v>6827739</v>
       </c>
       <c r="S161" t="n">
         <v>10</v>
@@ -17009,10 +17019,10 @@
     </row>
     <row r="162">
       <c r="A162" t="n">
-        <v>120074986</v>
+        <v>120075016</v>
       </c>
       <c r="B162" t="n">
-        <v>79624</v>
+        <v>79623</v>
       </c>
       <c r="C162" t="inlineStr">
         <is>
@@ -17025,21 +17035,21 @@
         </is>
       </c>
       <c r="E162" t="n">
-        <v>2081</v>
+        <v>6458</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G162" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H162" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I162" t="inlineStr"/>
@@ -17111,10 +17121,10 @@
     </row>
     <row r="163">
       <c r="A163" t="n">
-        <v>120075127</v>
+        <v>120075203</v>
       </c>
       <c r="B163" t="n">
-        <v>78542</v>
+        <v>78187</v>
       </c>
       <c r="C163" t="inlineStr">
         <is>
@@ -17127,21 +17137,21 @@
         </is>
       </c>
       <c r="E163" t="n">
-        <v>6425</v>
+        <v>353</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G163" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H163" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I163" t="inlineStr"/>
@@ -17151,10 +17161,10 @@
         </is>
       </c>
       <c r="Q163" t="n">
-        <v>478292</v>
+        <v>478125</v>
       </c>
       <c r="R163" t="n">
-        <v>6827708</v>
+        <v>6827631</v>
       </c>
       <c r="S163" t="n">
         <v>10</v>
@@ -17213,10 +17223,10 @@
     </row>
     <row r="164">
       <c r="A164" t="n">
-        <v>120075075</v>
+        <v>120074933</v>
       </c>
       <c r="B164" t="n">
-        <v>78542</v>
+        <v>79160</v>
       </c>
       <c r="C164" t="inlineStr">
         <is>
@@ -17229,21 +17239,21 @@
         </is>
       </c>
       <c r="E164" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G164" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H164" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I164" t="inlineStr"/>
@@ -17253,10 +17263,10 @@
         </is>
       </c>
       <c r="Q164" t="n">
-        <v>478139</v>
+        <v>478189</v>
       </c>
       <c r="R164" t="n">
-        <v>6827554</v>
+        <v>6827761</v>
       </c>
       <c r="S164" t="n">
         <v>10</v>
@@ -17315,7 +17325,7 @@
     </row>
     <row r="165">
       <c r="A165" t="n">
-        <v>120075160</v>
+        <v>120075082</v>
       </c>
       <c r="B165" t="n">
         <v>78542</v>
@@ -17358,7 +17368,7 @@
         <v>478097</v>
       </c>
       <c r="R165" t="n">
-        <v>6827744</v>
+        <v>6827544</v>
       </c>
       <c r="S165" t="n">
         <v>10</v>
@@ -17417,7 +17427,7 @@
     </row>
     <row r="166">
       <c r="A166" t="n">
-        <v>120075164</v>
+        <v>120075077</v>
       </c>
       <c r="B166" t="n">
         <v>78542</v>
@@ -17457,10 +17467,10 @@
         </is>
       </c>
       <c r="Q166" t="n">
-        <v>478092</v>
+        <v>478124</v>
       </c>
       <c r="R166" t="n">
-        <v>6827810</v>
+        <v>6827560</v>
       </c>
       <c r="S166" t="n">
         <v>10</v>
@@ -17519,7 +17529,7 @@
     </row>
     <row r="167">
       <c r="A167" t="n">
-        <v>120075168</v>
+        <v>120075068</v>
       </c>
       <c r="B167" t="n">
         <v>78542</v>
@@ -17559,10 +17569,10 @@
         </is>
       </c>
       <c r="Q167" t="n">
-        <v>478086</v>
+        <v>478174</v>
       </c>
       <c r="R167" t="n">
-        <v>6827868</v>
+        <v>6827656</v>
       </c>
       <c r="S167" t="n">
         <v>10</v>
@@ -17621,7 +17631,7 @@
     </row>
     <row r="168">
       <c r="A168" t="n">
-        <v>120075078</v>
+        <v>120075171</v>
       </c>
       <c r="B168" t="n">
         <v>78542</v>
@@ -17661,10 +17671,10 @@
         </is>
       </c>
       <c r="Q168" t="n">
-        <v>478116</v>
+        <v>478073</v>
       </c>
       <c r="R168" t="n">
-        <v>6827567</v>
+        <v>6827831</v>
       </c>
       <c r="S168" t="n">
         <v>10</v>
@@ -17723,7 +17733,7 @@
     </row>
     <row r="169">
       <c r="A169" t="n">
-        <v>120075172</v>
+        <v>120075086</v>
       </c>
       <c r="B169" t="n">
         <v>78542</v>
@@ -17763,10 +17773,10 @@
         </is>
       </c>
       <c r="Q169" t="n">
-        <v>478055</v>
+        <v>478104</v>
       </c>
       <c r="R169" t="n">
-        <v>6827768</v>
+        <v>6827495</v>
       </c>
       <c r="S169" t="n">
         <v>10</v>
@@ -17825,10 +17835,10 @@
     </row>
     <row r="170">
       <c r="A170" t="n">
-        <v>120074938</v>
+        <v>120074927</v>
       </c>
       <c r="B170" t="n">
-        <v>79160</v>
+        <v>78576</v>
       </c>
       <c r="C170" t="inlineStr">
         <is>
@@ -17841,21 +17851,21 @@
         </is>
       </c>
       <c r="E170" t="n">
-        <v>6453</v>
+        <v>185</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G170" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H170" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I170" t="inlineStr"/>
@@ -17865,10 +17875,10 @@
         </is>
       </c>
       <c r="Q170" t="n">
-        <v>478097</v>
+        <v>478073</v>
       </c>
       <c r="R170" t="n">
-        <v>6827756</v>
+        <v>6827836</v>
       </c>
       <c r="S170" t="n">
         <v>10</v>
@@ -17927,7 +17937,7 @@
     </row>
     <row r="171">
       <c r="A171" t="n">
-        <v>120075035</v>
+        <v>120075044</v>
       </c>
       <c r="B171" t="n">
         <v>78278</v>
@@ -17967,10 +17977,10 @@
         </is>
       </c>
       <c r="Q171" t="n">
-        <v>478273</v>
+        <v>478060</v>
       </c>
       <c r="R171" t="n">
-        <v>6827711</v>
+        <v>6827770</v>
       </c>
       <c r="S171" t="n">
         <v>10</v>
@@ -18029,10 +18039,10 @@
     </row>
     <row r="172">
       <c r="A172" t="n">
-        <v>120074941</v>
+        <v>120075043</v>
       </c>
       <c r="B172" t="n">
-        <v>79160</v>
+        <v>78278</v>
       </c>
       <c r="C172" t="inlineStr">
         <is>
@@ -18045,21 +18055,21 @@
         </is>
       </c>
       <c r="E172" t="n">
-        <v>6453</v>
+        <v>6446</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G172" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H172" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I172" t="inlineStr"/>
@@ -18069,10 +18079,10 @@
         </is>
       </c>
       <c r="Q172" t="n">
-        <v>478069</v>
+        <v>478103</v>
       </c>
       <c r="R172" t="n">
-        <v>6827854</v>
+        <v>6827803</v>
       </c>
       <c r="S172" t="n">
         <v>10</v>
@@ -18131,10 +18141,10 @@
     </row>
     <row r="173">
       <c r="A173" t="n">
-        <v>120075037</v>
+        <v>120075165</v>
       </c>
       <c r="B173" t="n">
-        <v>78278</v>
+        <v>78542</v>
       </c>
       <c r="C173" t="inlineStr">
         <is>
@@ -18147,21 +18157,21 @@
         </is>
       </c>
       <c r="E173" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G173" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H173" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I173" t="inlineStr"/>
@@ -18171,10 +18181,10 @@
         </is>
       </c>
       <c r="Q173" t="n">
-        <v>478265</v>
+        <v>478078</v>
       </c>
       <c r="R173" t="n">
-        <v>6827716</v>
+        <v>6827834</v>
       </c>
       <c r="S173" t="n">
         <v>10</v>
@@ -18233,10 +18243,10 @@
     </row>
     <row r="174">
       <c r="A174" t="n">
-        <v>120074927</v>
+        <v>120075166</v>
       </c>
       <c r="B174" t="n">
-        <v>78576</v>
+        <v>78542</v>
       </c>
       <c r="C174" t="inlineStr">
         <is>
@@ -18249,21 +18259,21 @@
         </is>
       </c>
       <c r="E174" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G174" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H174" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I174" t="inlineStr"/>
@@ -18273,10 +18283,10 @@
         </is>
       </c>
       <c r="Q174" t="n">
-        <v>478073</v>
+        <v>478092</v>
       </c>
       <c r="R174" t="n">
-        <v>6827836</v>
+        <v>6827839</v>
       </c>
       <c r="S174" t="n">
         <v>10</v>
@@ -18335,10 +18345,10 @@
     </row>
     <row r="175">
       <c r="A175" t="n">
-        <v>120074956</v>
+        <v>120075095</v>
       </c>
       <c r="B175" t="n">
-        <v>57320</v>
+        <v>78542</v>
       </c>
       <c r="C175" t="inlineStr">
         <is>
@@ -18351,39 +18361,34 @@
         </is>
       </c>
       <c r="E175" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G175" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H175" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I175" t="inlineStr"/>
-      <c r="M175" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P175" t="inlineStr">
         <is>
           <t>Hevoslamm, Dlr</t>
         </is>
       </c>
       <c r="Q175" t="n">
-        <v>478278</v>
+        <v>478219</v>
       </c>
       <c r="R175" t="n">
-        <v>6827832</v>
+        <v>6827572</v>
       </c>
       <c r="S175" t="n">
         <v>10</v>
@@ -18416,11 +18421,6 @@
       <c r="AA175" t="inlineStr">
         <is>
           <t>2024-09-27</t>
-        </is>
-      </c>
-      <c r="AC175" t="inlineStr">
-        <is>
-          <t>Färska ringhack (tall)</t>
         </is>
       </c>
       <c r="AD175" t="b">
@@ -18447,10 +18447,10 @@
     </row>
     <row r="176">
       <c r="A176" t="n">
-        <v>120075047</v>
+        <v>120075061</v>
       </c>
       <c r="B176" t="n">
-        <v>78278</v>
+        <v>78542</v>
       </c>
       <c r="C176" t="inlineStr">
         <is>
@@ -18463,21 +18463,21 @@
         </is>
       </c>
       <c r="E176" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G176" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H176" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I176" t="inlineStr"/>
@@ -18487,10 +18487,10 @@
         </is>
       </c>
       <c r="Q176" t="n">
-        <v>478212</v>
+        <v>478160</v>
       </c>
       <c r="R176" t="n">
-        <v>6827573</v>
+        <v>6827710</v>
       </c>
       <c r="S176" t="n">
         <v>10</v>
@@ -18549,10 +18549,10 @@
     </row>
     <row r="177">
       <c r="A177" t="n">
-        <v>120075204</v>
+        <v>120075140</v>
       </c>
       <c r="B177" t="n">
-        <v>78187</v>
+        <v>78542</v>
       </c>
       <c r="C177" t="inlineStr">
         <is>
@@ -18565,21 +18565,21 @@
         </is>
       </c>
       <c r="E177" t="n">
-        <v>353</v>
+        <v>6425</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G177" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H177" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I177" t="inlineStr"/>
@@ -18589,10 +18589,10 @@
         </is>
       </c>
       <c r="Q177" t="n">
-        <v>478115</v>
+        <v>478310</v>
       </c>
       <c r="R177" t="n">
-        <v>6827614</v>
+        <v>6827797</v>
       </c>
       <c r="S177" t="n">
         <v>10</v>
@@ -18651,10 +18651,10 @@
     </row>
     <row r="178">
       <c r="A178" t="n">
-        <v>120074925</v>
+        <v>120075092</v>
       </c>
       <c r="B178" t="n">
-        <v>78576</v>
+        <v>78542</v>
       </c>
       <c r="C178" t="inlineStr">
         <is>
@@ -18667,21 +18667,21 @@
         </is>
       </c>
       <c r="E178" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G178" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H178" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I178" t="inlineStr"/>
@@ -18691,10 +18691,10 @@
         </is>
       </c>
       <c r="Q178" t="n">
-        <v>478088</v>
+        <v>478167</v>
       </c>
       <c r="R178" t="n">
-        <v>6827834</v>
+        <v>6827561</v>
       </c>
       <c r="S178" t="n">
         <v>10</v>
@@ -18753,7 +18753,7 @@
     </row>
     <row r="179">
       <c r="A179" t="n">
-        <v>120075192</v>
+        <v>120075062</v>
       </c>
       <c r="B179" t="n">
         <v>78542</v>
@@ -18793,10 +18793,10 @@
         </is>
       </c>
       <c r="Q179" t="n">
-        <v>478282</v>
+        <v>478221</v>
       </c>
       <c r="R179" t="n">
-        <v>6827683</v>
+        <v>6827719</v>
       </c>
       <c r="S179" t="n">
         <v>10</v>
@@ -18855,7 +18855,7 @@
     </row>
     <row r="180">
       <c r="A180" t="n">
-        <v>120075177</v>
+        <v>120075172</v>
       </c>
       <c r="B180" t="n">
         <v>78542</v>
@@ -18895,10 +18895,10 @@
         </is>
       </c>
       <c r="Q180" t="n">
-        <v>478075</v>
+        <v>478055</v>
       </c>
       <c r="R180" t="n">
-        <v>6827717</v>
+        <v>6827768</v>
       </c>
       <c r="S180" t="n">
         <v>10</v>
@@ -18957,10 +18957,10 @@
     </row>
     <row r="181">
       <c r="A181" t="n">
-        <v>120075140</v>
+        <v>120075224</v>
       </c>
       <c r="B181" t="n">
-        <v>78542</v>
+        <v>78187</v>
       </c>
       <c r="C181" t="inlineStr">
         <is>
@@ -18973,21 +18973,21 @@
         </is>
       </c>
       <c r="E181" t="n">
-        <v>6425</v>
+        <v>353</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G181" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H181" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I181" t="inlineStr"/>
@@ -18997,10 +18997,10 @@
         </is>
       </c>
       <c r="Q181" t="n">
-        <v>478310</v>
+        <v>478081</v>
       </c>
       <c r="R181" t="n">
-        <v>6827797</v>
+        <v>6827789</v>
       </c>
       <c r="S181" t="n">
         <v>10</v>

--- a/artfynd/A 32983-2023 artfynd.xlsx
+++ b/artfynd/A 32983-2023 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>120075226</v>
+        <v>120074912</v>
       </c>
       <c r="B2" t="n">
-        <v>78187</v>
+        <v>78576</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>353</v>
+        <v>185</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>478098</v>
+        <v>478149</v>
       </c>
       <c r="R2" t="n">
-        <v>6827815</v>
+        <v>6827714</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -777,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>120075215</v>
+        <v>120075198</v>
       </c>
       <c r="B3" t="n">
-        <v>78187</v>
+        <v>91858</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -789,25 +789,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>353</v>
+        <v>4364</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -817,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>478239</v>
+        <v>478163</v>
       </c>
       <c r="R3" t="n">
-        <v>6827752</v>
+        <v>6827530</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -879,10 +879,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>120075042</v>
+        <v>120075147</v>
       </c>
       <c r="B4" t="n">
-        <v>78278</v>
+        <v>78542</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -895,21 +895,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -919,10 +919,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>478074</v>
+        <v>478153</v>
       </c>
       <c r="R4" t="n">
-        <v>6827775</v>
+        <v>6827728</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -981,7 +981,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>120074883</v>
+        <v>120074892</v>
       </c>
       <c r="B5" t="n">
         <v>79160</v>
@@ -1021,10 +1021,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>478142</v>
+        <v>478243</v>
       </c>
       <c r="R5" t="n">
-        <v>6827623</v>
+        <v>6827585</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1083,10 +1083,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>120075239</v>
+        <v>120074931</v>
       </c>
       <c r="B6" t="n">
-        <v>77474</v>
+        <v>79160</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1099,21 +1099,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6487</v>
+        <v>6453</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Blågrå svartspik</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Chaenothecopsis fennica</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Laurila) Tibell</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1123,10 +1123,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>478137</v>
+        <v>478261</v>
       </c>
       <c r="R6" t="n">
-        <v>6827554</v>
+        <v>6827822</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1185,7 +1185,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>120074942</v>
+        <v>120074904</v>
       </c>
       <c r="B7" t="n">
         <v>79160</v>
@@ -1225,10 +1225,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>478065</v>
+        <v>478262</v>
       </c>
       <c r="R7" t="n">
-        <v>6827842</v>
+        <v>6827730</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1287,10 +1287,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>120075007</v>
+        <v>120075088</v>
       </c>
       <c r="B8" t="n">
-        <v>78279</v>
+        <v>78542</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1303,21 +1303,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1327,10 +1327,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>478285</v>
+        <v>478151</v>
       </c>
       <c r="R8" t="n">
-        <v>6827770</v>
+        <v>6827509</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1389,10 +1389,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>120075139</v>
+        <v>120075043</v>
       </c>
       <c r="B9" t="n">
-        <v>78542</v>
+        <v>78278</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1405,21 +1405,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1429,7 +1429,7 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>478294</v>
+        <v>478103</v>
       </c>
       <c r="R9" t="n">
         <v>6827803</v>
@@ -1491,7 +1491,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>120075143</v>
+        <v>120075140</v>
       </c>
       <c r="B10" t="n">
         <v>78542</v>
@@ -1531,10 +1531,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>478301</v>
+        <v>478310</v>
       </c>
       <c r="R10" t="n">
-        <v>6827814</v>
+        <v>6827797</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1593,10 +1593,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>120075167</v>
+        <v>120074942</v>
       </c>
       <c r="B11" t="n">
-        <v>78542</v>
+        <v>79160</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1609,21 +1609,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1633,10 +1633,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>478105</v>
+        <v>478065</v>
       </c>
       <c r="R11" t="n">
-        <v>6827851</v>
+        <v>6827842</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1695,7 +1695,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>120075120</v>
+        <v>120075062</v>
       </c>
       <c r="B12" t="n">
         <v>78542</v>
@@ -1735,10 +1735,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>478223</v>
+        <v>478221</v>
       </c>
       <c r="R12" t="n">
-        <v>6827657</v>
+        <v>6827719</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1797,10 +1797,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>120075069</v>
+        <v>120075000</v>
       </c>
       <c r="B13" t="n">
-        <v>78542</v>
+        <v>78279</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1813,21 +1813,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1837,10 +1837,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>478157</v>
+        <v>478121</v>
       </c>
       <c r="R13" t="n">
-        <v>6827611</v>
+        <v>6827607</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1899,10 +1899,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>120075168</v>
+        <v>120075009</v>
       </c>
       <c r="B14" t="n">
-        <v>78542</v>
+        <v>78279</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1915,21 +1915,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1939,10 +1939,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>478086</v>
+        <v>478151</v>
       </c>
       <c r="R14" t="n">
-        <v>6827868</v>
+        <v>6827745</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2001,7 +2001,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>120075074</v>
+        <v>120075139</v>
       </c>
       <c r="B15" t="n">
         <v>78542</v>
@@ -2041,10 +2041,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>478138</v>
+        <v>478294</v>
       </c>
       <c r="R15" t="n">
-        <v>6827599</v>
+        <v>6827803</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2103,7 +2103,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>120075073</v>
+        <v>120075137</v>
       </c>
       <c r="B16" t="n">
         <v>78542</v>
@@ -2143,10 +2143,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>478116</v>
+        <v>478288</v>
       </c>
       <c r="R16" t="n">
-        <v>6827617</v>
+        <v>6827763</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2205,7 +2205,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>120075128</v>
+        <v>120075177</v>
       </c>
       <c r="B17" t="n">
         <v>78542</v>
@@ -2245,10 +2245,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>478275</v>
+        <v>478075</v>
       </c>
       <c r="R17" t="n">
-        <v>6827710</v>
+        <v>6827717</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2307,10 +2307,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>120075197</v>
+        <v>120075015</v>
       </c>
       <c r="B18" t="n">
-        <v>91858</v>
+        <v>79623</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2319,47 +2319,38 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>4364</v>
+        <v>6458</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J18" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
           <t>Hevoslamm, Dlr</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>478077</v>
+        <v>478114</v>
       </c>
       <c r="R18" t="n">
-        <v>6827805</v>
+        <v>6827633</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2418,10 +2409,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>120075025</v>
+        <v>120074905</v>
       </c>
       <c r="B19" t="n">
-        <v>78278</v>
+        <v>79160</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2434,21 +2425,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6446</v>
+        <v>6453</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2458,10 +2449,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>478171</v>
+        <v>478285</v>
       </c>
       <c r="R19" t="n">
-        <v>6827642</v>
+        <v>6827770</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2520,10 +2511,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>120074939</v>
+        <v>120075172</v>
       </c>
       <c r="B20" t="n">
-        <v>79160</v>
+        <v>78542</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2536,21 +2527,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2560,10 +2551,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>478091</v>
+        <v>478055</v>
       </c>
       <c r="R20" t="n">
-        <v>6827838</v>
+        <v>6827768</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2622,10 +2613,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>120074887</v>
+        <v>120075230</v>
       </c>
       <c r="B21" t="n">
-        <v>79160</v>
+        <v>78187</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2638,21 +2629,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6453</v>
+        <v>353</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2662,10 +2653,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>478144</v>
+        <v>478064</v>
       </c>
       <c r="R21" t="n">
-        <v>6827593</v>
+        <v>6827866</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2724,10 +2715,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>120075027</v>
+        <v>120075161</v>
       </c>
       <c r="B22" t="n">
-        <v>78278</v>
+        <v>78542</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2740,21 +2731,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2764,10 +2755,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>478144</v>
+        <v>478082</v>
       </c>
       <c r="R22" t="n">
-        <v>6827593</v>
+        <v>6827766</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2826,10 +2817,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>120075047</v>
+        <v>120075145</v>
       </c>
       <c r="B23" t="n">
-        <v>78278</v>
+        <v>78542</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -2842,21 +2833,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2866,10 +2857,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>478212</v>
+        <v>478226</v>
       </c>
       <c r="R23" t="n">
-        <v>6827573</v>
+        <v>6827777</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2928,10 +2919,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>120075054</v>
+        <v>120075001</v>
       </c>
       <c r="B24" t="n">
-        <v>90598</v>
+        <v>78279</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -2944,21 +2935,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>5432</v>
+        <v>228912</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -2968,10 +2959,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>478126</v>
+        <v>478125</v>
       </c>
       <c r="R24" t="n">
-        <v>6827477</v>
+        <v>6827604</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3030,10 +3021,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>120075013</v>
+        <v>120075204</v>
       </c>
       <c r="B25" t="n">
-        <v>78279</v>
+        <v>78187</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3046,21 +3037,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>228912</v>
+        <v>353</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3070,10 +3061,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>478239</v>
+        <v>478115</v>
       </c>
       <c r="R25" t="n">
-        <v>6827752</v>
+        <v>6827614</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3132,10 +3123,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>120075008</v>
+        <v>120074925</v>
       </c>
       <c r="B26" t="n">
-        <v>78279</v>
+        <v>78576</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3148,21 +3139,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>228912</v>
+        <v>185</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3172,10 +3163,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>478299</v>
+        <v>478088</v>
       </c>
       <c r="R26" t="n">
-        <v>6827805</v>
+        <v>6827834</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3234,10 +3225,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>120074952</v>
+        <v>120075202</v>
       </c>
       <c r="B27" t="n">
-        <v>79131</v>
+        <v>78187</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3250,21 +3241,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>229821</v>
+        <v>353</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3274,10 +3265,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>478120</v>
+        <v>478218</v>
       </c>
       <c r="R27" t="n">
-        <v>6827605</v>
+        <v>6827721</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3336,10 +3327,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>120075225</v>
+        <v>120074888</v>
       </c>
       <c r="B28" t="n">
-        <v>78187</v>
+        <v>79160</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3352,21 +3343,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>353</v>
+        <v>6453</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3376,10 +3367,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>478075</v>
+        <v>478139</v>
       </c>
       <c r="R28" t="n">
-        <v>6827798</v>
+        <v>6827554</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3438,10 +3429,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>120075227</v>
+        <v>120075078</v>
       </c>
       <c r="B29" t="n">
-        <v>78187</v>
+        <v>78542</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3454,21 +3445,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>353</v>
+        <v>6425</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3478,10 +3469,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>478088</v>
+        <v>478116</v>
       </c>
       <c r="R29" t="n">
-        <v>6827834</v>
+        <v>6827567</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3540,10 +3531,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>120075177</v>
+        <v>120074891</v>
       </c>
       <c r="B30" t="n">
-        <v>78542</v>
+        <v>79160</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3556,21 +3547,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3580,10 +3571,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>478075</v>
+        <v>478212</v>
       </c>
       <c r="R30" t="n">
-        <v>6827717</v>
+        <v>6827573</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3642,10 +3633,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>120075130</v>
+        <v>120075037</v>
       </c>
       <c r="B31" t="n">
-        <v>78542</v>
+        <v>78278</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3658,21 +3649,21 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3682,10 +3673,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>478264</v>
+        <v>478265</v>
       </c>
       <c r="R31" t="n">
-        <v>6827733</v>
+        <v>6827716</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3744,7 +3735,7 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>120075219</v>
+        <v>120075207</v>
       </c>
       <c r="B32" t="n">
         <v>78187</v>
@@ -3784,10 +3775,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>478169</v>
+        <v>478157</v>
       </c>
       <c r="R32" t="n">
-        <v>6827760</v>
+        <v>6827509</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3846,10 +3837,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>120075208</v>
+        <v>120075089</v>
       </c>
       <c r="B33" t="n">
-        <v>78187</v>
+        <v>78542</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -3862,21 +3853,21 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>353</v>
+        <v>6425</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -3886,10 +3877,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>478158</v>
+        <v>478153</v>
       </c>
       <c r="R33" t="n">
-        <v>6827519</v>
+        <v>6827517</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -3948,10 +3939,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>120074886</v>
+        <v>120075242</v>
       </c>
       <c r="B34" t="n">
-        <v>79160</v>
+        <v>77926</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -3964,21 +3955,21 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6453</v>
+        <v>6437</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -3988,10 +3979,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>478125</v>
+        <v>478136</v>
       </c>
       <c r="R34" t="n">
-        <v>6827604</v>
+        <v>6827556</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4050,7 +4041,7 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>120074941</v>
+        <v>120074948</v>
       </c>
       <c r="B35" t="n">
         <v>79160</v>
@@ -4090,10 +4081,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>478069</v>
+        <v>478070</v>
       </c>
       <c r="R35" t="n">
-        <v>6827854</v>
+        <v>6827723</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4152,10 +4143,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>120074961</v>
+        <v>120075173</v>
       </c>
       <c r="B36" t="n">
-        <v>90600</v>
+        <v>78542</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4168,21 +4159,21 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>5442</v>
+        <v>6425</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4192,10 +4183,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>478230</v>
+        <v>478052</v>
       </c>
       <c r="R36" t="n">
-        <v>6827780</v>
+        <v>6827754</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4254,10 +4245,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>120074917</v>
+        <v>120075164</v>
       </c>
       <c r="B37" t="n">
-        <v>78576</v>
+        <v>78542</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4270,21 +4261,21 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4294,10 +4285,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>478095</v>
+        <v>478092</v>
       </c>
       <c r="R37" t="n">
-        <v>6827533</v>
+        <v>6827810</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4356,10 +4347,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>120075217</v>
+        <v>120075129</v>
       </c>
       <c r="B38" t="n">
-        <v>78187</v>
+        <v>78542</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4372,21 +4363,21 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>353</v>
+        <v>6425</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4396,10 +4387,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>478264</v>
+        <v>478265</v>
       </c>
       <c r="R38" t="n">
-        <v>6827839</v>
+        <v>6827707</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4458,7 +4449,7 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>120074930</v>
+        <v>120074946</v>
       </c>
       <c r="B39" t="n">
         <v>79160</v>
@@ -4498,10 +4489,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>478299</v>
+        <v>478056</v>
       </c>
       <c r="R39" t="n">
-        <v>6827805</v>
+        <v>6827754</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4560,10 +4551,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>120074931</v>
+        <v>120075048</v>
       </c>
       <c r="B40" t="n">
-        <v>79160</v>
+        <v>56524</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -4576,34 +4567,39 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6453</v>
+        <v>102612</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
+      <c r="M40" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="P40" t="inlineStr">
         <is>
           <t>Hevoslamm, Dlr</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>478261</v>
+        <v>478070</v>
       </c>
       <c r="R40" t="n">
-        <v>6827822</v>
+        <v>6827723</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4662,10 +4658,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>120075019</v>
+        <v>120075061</v>
       </c>
       <c r="B41" t="n">
-        <v>79623</v>
+        <v>78542</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -4678,21 +4674,21 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4702,10 +4698,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>478227</v>
+        <v>478160</v>
       </c>
       <c r="R41" t="n">
-        <v>6827655</v>
+        <v>6827710</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4764,10 +4760,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>120075135</v>
+        <v>120074944</v>
       </c>
       <c r="B42" t="n">
-        <v>78542</v>
+        <v>79160</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -4780,21 +4776,21 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -4804,10 +4800,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>478291</v>
+        <v>478056</v>
       </c>
       <c r="R42" t="n">
-        <v>6827744</v>
+        <v>6827785</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4866,7 +4862,7 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>120075127</v>
+        <v>120075060</v>
       </c>
       <c r="B43" t="n">
         <v>78542</v>
@@ -4906,10 +4902,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>478292</v>
+        <v>478087</v>
       </c>
       <c r="R43" t="n">
-        <v>6827708</v>
+        <v>6827718</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -4968,7 +4964,7 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>120075070</v>
+        <v>120075167</v>
       </c>
       <c r="B44" t="n">
         <v>78542</v>
@@ -5008,10 +5004,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>478135</v>
+        <v>478105</v>
       </c>
       <c r="R44" t="n">
-        <v>6827625</v>
+        <v>6827851</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5070,7 +5066,7 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>120075063</v>
+        <v>120075130</v>
       </c>
       <c r="B45" t="n">
         <v>78542</v>
@@ -5110,10 +5106,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>478201</v>
+        <v>478264</v>
       </c>
       <c r="R45" t="n">
-        <v>6827693</v>
+        <v>6827733</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5172,10 +5168,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>120074948</v>
+        <v>120075131</v>
       </c>
       <c r="B46" t="n">
-        <v>79160</v>
+        <v>78542</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -5188,21 +5184,21 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5212,10 +5208,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>478070</v>
+        <v>478258</v>
       </c>
       <c r="R46" t="n">
-        <v>6827723</v>
+        <v>6827731</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5274,10 +5270,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>120075035</v>
+        <v>120075074</v>
       </c>
       <c r="B47" t="n">
-        <v>78278</v>
+        <v>78542</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -5290,21 +5286,21 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5314,10 +5310,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>478273</v>
+        <v>478138</v>
       </c>
       <c r="R47" t="n">
-        <v>6827711</v>
+        <v>6827599</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5376,10 +5372,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>120074889</v>
+        <v>120075063</v>
       </c>
       <c r="B48" t="n">
-        <v>79160</v>
+        <v>78542</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -5392,21 +5388,21 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5416,10 +5412,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>478163</v>
+        <v>478201</v>
       </c>
       <c r="R48" t="n">
-        <v>6827536</v>
+        <v>6827693</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5478,10 +5474,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>120074906</v>
+        <v>120075068</v>
       </c>
       <c r="B49" t="n">
-        <v>79160</v>
+        <v>78542</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -5494,21 +5490,21 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5518,10 +5514,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>478294</v>
+        <v>478174</v>
       </c>
       <c r="R49" t="n">
-        <v>6827790</v>
+        <v>6827656</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5580,10 +5576,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>120074904</v>
+        <v>120074999</v>
       </c>
       <c r="B50" t="n">
-        <v>79160</v>
+        <v>78279</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -5596,21 +5592,21 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>6453</v>
+        <v>228912</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -5620,10 +5616,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>478262</v>
+        <v>478161</v>
       </c>
       <c r="R50" t="n">
-        <v>6827730</v>
+        <v>6827592</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5682,10 +5678,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>120074945</v>
+        <v>120074917</v>
       </c>
       <c r="B51" t="n">
-        <v>79160</v>
+        <v>78576</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -5698,21 +5694,21 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>6453</v>
+        <v>185</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -5722,10 +5718,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>478061</v>
+        <v>478095</v>
       </c>
       <c r="R51" t="n">
-        <v>6827770</v>
+        <v>6827533</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5784,10 +5780,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>120075196</v>
+        <v>120075215</v>
       </c>
       <c r="B52" t="n">
-        <v>78542</v>
+        <v>78187</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -5800,21 +5796,21 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>6425</v>
+        <v>353</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -5824,10 +5820,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>478288</v>
+        <v>478239</v>
       </c>
       <c r="R52" t="n">
-        <v>6827682</v>
+        <v>6827752</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -5886,10 +5882,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>120075071</v>
+        <v>120074986</v>
       </c>
       <c r="B53" t="n">
-        <v>78542</v>
+        <v>79624</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -5902,21 +5898,21 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>6425</v>
+        <v>2081</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -5926,10 +5922,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>478116</v>
+        <v>478096</v>
       </c>
       <c r="R53" t="n">
-        <v>6827633</v>
+        <v>6827549</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -5988,10 +5984,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>120075088</v>
+        <v>120074883</v>
       </c>
       <c r="B54" t="n">
-        <v>78542</v>
+        <v>79160</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
@@ -6004,21 +6000,21 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -6028,10 +6024,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>478151</v>
+        <v>478142</v>
       </c>
       <c r="R54" t="n">
-        <v>6827509</v>
+        <v>6827623</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6090,10 +6086,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>120075134</v>
+        <v>120074886</v>
       </c>
       <c r="B55" t="n">
-        <v>78542</v>
+        <v>79160</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
@@ -6106,21 +6102,21 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -6130,10 +6126,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>478266</v>
+        <v>478125</v>
       </c>
       <c r="R55" t="n">
-        <v>6827765</v>
+        <v>6827604</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6192,7 +6188,7 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>120075097</v>
+        <v>120075174</v>
       </c>
       <c r="B56" t="n">
         <v>78542</v>
@@ -6232,10 +6228,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>478248</v>
+        <v>478057</v>
       </c>
       <c r="R56" t="n">
-        <v>6827593</v>
+        <v>6827749</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6294,10 +6290,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>120074914</v>
+        <v>120074943</v>
       </c>
       <c r="B57" t="n">
-        <v>78576</v>
+        <v>79160</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
@@ -6310,21 +6306,21 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>185</v>
+        <v>6453</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -6334,10 +6330,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>478169</v>
+        <v>478073</v>
       </c>
       <c r="R57" t="n">
-        <v>6827680</v>
+        <v>6827827</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6396,10 +6392,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>120074999</v>
+        <v>120075086</v>
       </c>
       <c r="B58" t="n">
-        <v>78279</v>
+        <v>78542</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
@@ -6412,21 +6408,21 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
@@ -6436,10 +6432,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>478161</v>
+        <v>478104</v>
       </c>
       <c r="R58" t="n">
-        <v>6827592</v>
+        <v>6827495</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6498,7 +6494,7 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>120075001</v>
+        <v>120075003</v>
       </c>
       <c r="B59" t="n">
         <v>78279</v>
@@ -6538,10 +6534,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>478125</v>
+        <v>478137</v>
       </c>
       <c r="R59" t="n">
-        <v>6827604</v>
+        <v>6827553</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6600,10 +6596,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>120075009</v>
+        <v>120075132</v>
       </c>
       <c r="B60" t="n">
-        <v>78279</v>
+        <v>78542</v>
       </c>
       <c r="C60" t="inlineStr">
         <is>
@@ -6616,21 +6612,21 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
@@ -6640,10 +6636,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>478151</v>
+        <v>478240</v>
       </c>
       <c r="R60" t="n">
-        <v>6827745</v>
+        <v>6827754</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -6702,10 +6698,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>120075207</v>
+        <v>120075004</v>
       </c>
       <c r="B61" t="n">
-        <v>78187</v>
+        <v>78279</v>
       </c>
       <c r="C61" t="inlineStr">
         <is>
@@ -6718,21 +6714,21 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>353</v>
+        <v>228912</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
@@ -6742,10 +6738,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>478157</v>
+        <v>478212</v>
       </c>
       <c r="R61" t="n">
-        <v>6827509</v>
+        <v>6827573</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -6804,10 +6800,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>120074907</v>
+        <v>120075216</v>
       </c>
       <c r="B62" t="n">
-        <v>79160</v>
+        <v>78187</v>
       </c>
       <c r="C62" t="inlineStr">
         <is>
@@ -6820,21 +6816,21 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>6453</v>
+        <v>353</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
@@ -6844,10 +6840,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>478263</v>
+        <v>478294</v>
       </c>
       <c r="R62" t="n">
-        <v>6827838</v>
+        <v>6827790</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -6906,10 +6902,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>120075015</v>
+        <v>120075219</v>
       </c>
       <c r="B63" t="n">
-        <v>79623</v>
+        <v>78187</v>
       </c>
       <c r="C63" t="inlineStr">
         <is>
@@ -6922,21 +6918,21 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>6458</v>
+        <v>353</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
@@ -6946,10 +6942,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>478114</v>
+        <v>478169</v>
       </c>
       <c r="R63" t="n">
-        <v>6827633</v>
+        <v>6827760</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -7008,10 +7004,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>120075029</v>
+        <v>120075192</v>
       </c>
       <c r="B64" t="n">
-        <v>78278</v>
+        <v>78542</v>
       </c>
       <c r="C64" t="inlineStr">
         <is>
@@ -7024,21 +7020,21 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
@@ -7048,10 +7044,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>478115</v>
+        <v>478282</v>
       </c>
       <c r="R64" t="n">
-        <v>6827564</v>
+        <v>6827683</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -7110,7 +7106,7 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>120075162</v>
+        <v>120075165</v>
       </c>
       <c r="B65" t="n">
         <v>78542</v>
@@ -7150,10 +7146,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>478080</v>
+        <v>478078</v>
       </c>
       <c r="R65" t="n">
-        <v>6827808</v>
+        <v>6827834</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7212,10 +7208,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>120074932</v>
+        <v>120075163</v>
       </c>
       <c r="B66" t="n">
-        <v>79160</v>
+        <v>78542</v>
       </c>
       <c r="C66" t="inlineStr">
         <is>
@@ -7228,21 +7224,21 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
@@ -7252,10 +7248,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>478250</v>
+        <v>478102</v>
       </c>
       <c r="R66" t="n">
-        <v>6827802</v>
+        <v>6827800</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7314,7 +7310,7 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>120075090</v>
+        <v>120075075</v>
       </c>
       <c r="B67" t="n">
         <v>78542</v>
@@ -7354,10 +7350,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>478161</v>
+        <v>478139</v>
       </c>
       <c r="R67" t="n">
-        <v>6827528</v>
+        <v>6827554</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7416,10 +7412,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>120075144</v>
+        <v>120074947</v>
       </c>
       <c r="B68" t="n">
-        <v>78542</v>
+        <v>79160</v>
       </c>
       <c r="C68" t="inlineStr">
         <is>
@@ -7432,21 +7428,21 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
@@ -7456,10 +7452,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>478261</v>
+        <v>478061</v>
       </c>
       <c r="R68" t="n">
-        <v>6827822</v>
+        <v>6827751</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7518,10 +7514,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>120075206</v>
+        <v>120074941</v>
       </c>
       <c r="B69" t="n">
-        <v>78187</v>
+        <v>79160</v>
       </c>
       <c r="C69" t="inlineStr">
         <is>
@@ -7534,21 +7530,21 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>353</v>
+        <v>6453</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
@@ -7558,10 +7554,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>478125</v>
+        <v>478069</v>
       </c>
       <c r="R69" t="n">
-        <v>6827604</v>
+        <v>6827854</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -7620,7 +7616,7 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>120075236</v>
+        <v>120075224</v>
       </c>
       <c r="B70" t="n">
         <v>78187</v>
@@ -7660,10 +7656,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>478062</v>
+        <v>478081</v>
       </c>
       <c r="R70" t="n">
-        <v>6827740</v>
+        <v>6827789</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -7722,10 +7718,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>120075145</v>
+        <v>120074914</v>
       </c>
       <c r="B71" t="n">
-        <v>78542</v>
+        <v>78576</v>
       </c>
       <c r="C71" t="inlineStr">
         <is>
@@ -7738,21 +7734,21 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
@@ -7762,10 +7758,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>478226</v>
+        <v>478169</v>
       </c>
       <c r="R71" t="n">
-        <v>6827777</v>
+        <v>6827680</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -7824,10 +7820,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>120074888</v>
+        <v>120074922</v>
       </c>
       <c r="B72" t="n">
-        <v>79160</v>
+        <v>78576</v>
       </c>
       <c r="C72" t="inlineStr">
         <is>
@@ -7840,21 +7836,21 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>6453</v>
+        <v>185</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
@@ -7864,10 +7860,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>478139</v>
+        <v>478103</v>
       </c>
       <c r="R72" t="n">
-        <v>6827554</v>
+        <v>6827718</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -7926,10 +7922,10 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>120074928</v>
+        <v>120075097</v>
       </c>
       <c r="B73" t="n">
-        <v>78576</v>
+        <v>78542</v>
       </c>
       <c r="C73" t="inlineStr">
         <is>
@@ -7942,21 +7938,21 @@
         </is>
       </c>
       <c r="E73" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
@@ -7966,10 +7962,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>478059</v>
+        <v>478248</v>
       </c>
       <c r="R73" t="n">
-        <v>6827740</v>
+        <v>6827593</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -8028,10 +8024,10 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>120075161</v>
+        <v>120075227</v>
       </c>
       <c r="B74" t="n">
-        <v>78542</v>
+        <v>78187</v>
       </c>
       <c r="C74" t="inlineStr">
         <is>
@@ -8044,21 +8040,21 @@
         </is>
       </c>
       <c r="E74" t="n">
-        <v>6425</v>
+        <v>353</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
@@ -8068,10 +8064,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>478082</v>
+        <v>478088</v>
       </c>
       <c r="R74" t="n">
-        <v>6827766</v>
+        <v>6827834</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -8130,10 +8126,10 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>120075078</v>
+        <v>120075206</v>
       </c>
       <c r="B75" t="n">
-        <v>78542</v>
+        <v>78187</v>
       </c>
       <c r="C75" t="inlineStr">
         <is>
@@ -8146,21 +8142,21 @@
         </is>
       </c>
       <c r="E75" t="n">
-        <v>6425</v>
+        <v>353</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
@@ -8170,10 +8166,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>478116</v>
+        <v>478125</v>
       </c>
       <c r="R75" t="n">
-        <v>6827567</v>
+        <v>6827604</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -8232,10 +8228,10 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>120074882</v>
+        <v>120075142</v>
       </c>
       <c r="B76" t="n">
-        <v>79160</v>
+        <v>78542</v>
       </c>
       <c r="C76" t="inlineStr">
         <is>
@@ -8248,21 +8244,21 @@
         </is>
       </c>
       <c r="E76" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
@@ -8272,10 +8268,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>478162</v>
+        <v>478313</v>
       </c>
       <c r="R76" t="n">
-        <v>6827593</v>
+        <v>6827798</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -8334,10 +8330,10 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>120075048</v>
+        <v>120075039</v>
       </c>
       <c r="B77" t="n">
-        <v>56524</v>
+        <v>78278</v>
       </c>
       <c r="C77" t="inlineStr">
         <is>
@@ -8350,39 +8346,34 @@
         </is>
       </c>
       <c r="E77" t="n">
-        <v>102612</v>
+        <v>6446</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
-      <c r="M77" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
       <c r="P77" t="inlineStr">
         <is>
           <t>Hevoslamm, Dlr</t>
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>478070</v>
+        <v>478238</v>
       </c>
       <c r="R77" t="n">
-        <v>6827723</v>
+        <v>6827752</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -8441,10 +8432,10 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>120074998</v>
+        <v>120075047</v>
       </c>
       <c r="B78" t="n">
-        <v>78279</v>
+        <v>78278</v>
       </c>
       <c r="C78" t="inlineStr">
         <is>
@@ -8457,21 +8448,21 @@
         </is>
       </c>
       <c r="E78" t="n">
-        <v>228912</v>
+        <v>6446</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
@@ -8481,10 +8472,10 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>478172</v>
+        <v>478212</v>
       </c>
       <c r="R78" t="n">
-        <v>6827640</v>
+        <v>6827573</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -8543,7 +8534,7 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>120075003</v>
+        <v>120074997</v>
       </c>
       <c r="B79" t="n">
         <v>78279</v>
@@ -8583,10 +8574,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>478137</v>
+        <v>478218</v>
       </c>
       <c r="R79" t="n">
-        <v>6827553</v>
+        <v>6827733</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -8645,7 +8636,7 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>120075000</v>
+        <v>120075012</v>
       </c>
       <c r="B80" t="n">
         <v>78279</v>
@@ -8685,10 +8676,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>478121</v>
+        <v>478055</v>
       </c>
       <c r="R80" t="n">
-        <v>6827607</v>
+        <v>6827786</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -8747,10 +8738,10 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>120074946</v>
+        <v>120075225</v>
       </c>
       <c r="B81" t="n">
-        <v>79160</v>
+        <v>78187</v>
       </c>
       <c r="C81" t="inlineStr">
         <is>
@@ -8763,21 +8754,21 @@
         </is>
       </c>
       <c r="E81" t="n">
-        <v>6453</v>
+        <v>353</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
@@ -8787,10 +8778,10 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>478056</v>
+        <v>478075</v>
       </c>
       <c r="R81" t="n">
-        <v>6827754</v>
+        <v>6827798</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -8849,7 +8840,7 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>120075204</v>
+        <v>120075203</v>
       </c>
       <c r="B82" t="n">
         <v>78187</v>
@@ -8889,10 +8880,10 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>478115</v>
+        <v>478125</v>
       </c>
       <c r="R82" t="n">
-        <v>6827614</v>
+        <v>6827631</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -8951,10 +8942,10 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>120075205</v>
+        <v>120075197</v>
       </c>
       <c r="B83" t="n">
-        <v>78187</v>
+        <v>91858</v>
       </c>
       <c r="C83" t="inlineStr">
         <is>
@@ -8963,38 +8954,47 @@
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E83" t="n">
-        <v>353</v>
+        <v>4364</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I83" t="inlineStr"/>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I83" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J83" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="P83" t="inlineStr">
         <is>
           <t>Hevoslamm, Dlr</t>
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>478117</v>
+        <v>478077</v>
       </c>
       <c r="R83" t="n">
-        <v>6827612</v>
+        <v>6827805</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -9053,7 +9053,7 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>120075064</v>
+        <v>120075070</v>
       </c>
       <c r="B84" t="n">
         <v>78542</v>
@@ -9093,10 +9093,10 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>478192</v>
+        <v>478135</v>
       </c>
       <c r="R84" t="n">
-        <v>6827690</v>
+        <v>6827625</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -9155,10 +9155,10 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>120075230</v>
+        <v>120075159</v>
       </c>
       <c r="B85" t="n">
-        <v>78187</v>
+        <v>78542</v>
       </c>
       <c r="C85" t="inlineStr">
         <is>
@@ -9171,21 +9171,21 @@
         </is>
       </c>
       <c r="E85" t="n">
-        <v>353</v>
+        <v>6425</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
@@ -9195,10 +9195,10 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>478064</v>
+        <v>478100</v>
       </c>
       <c r="R85" t="n">
-        <v>6827866</v>
+        <v>6827729</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -9257,10 +9257,10 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>120074905</v>
+        <v>120075143</v>
       </c>
       <c r="B86" t="n">
-        <v>79160</v>
+        <v>78542</v>
       </c>
       <c r="C86" t="inlineStr">
         <is>
@@ -9273,21 +9273,21 @@
         </is>
       </c>
       <c r="E86" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I86" t="inlineStr"/>
@@ -9297,10 +9297,10 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>478285</v>
+        <v>478301</v>
       </c>
       <c r="R86" t="n">
-        <v>6827770</v>
+        <v>6827814</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>
@@ -9359,7 +9359,7 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>120075163</v>
+        <v>120075083</v>
       </c>
       <c r="B87" t="n">
         <v>78542</v>
@@ -9399,10 +9399,10 @@
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>478102</v>
+        <v>478097</v>
       </c>
       <c r="R87" t="n">
-        <v>6827800</v>
+        <v>6827527</v>
       </c>
       <c r="S87" t="n">
         <v>10</v>
@@ -9461,7 +9461,7 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>120075137</v>
+        <v>120075144</v>
       </c>
       <c r="B88" t="n">
         <v>78542</v>
@@ -9501,10 +9501,10 @@
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>478288</v>
+        <v>478261</v>
       </c>
       <c r="R88" t="n">
-        <v>6827763</v>
+        <v>6827822</v>
       </c>
       <c r="S88" t="n">
         <v>10</v>
@@ -9563,10 +9563,10 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>120075142</v>
+        <v>120074933</v>
       </c>
       <c r="B89" t="n">
-        <v>78542</v>
+        <v>79160</v>
       </c>
       <c r="C89" t="inlineStr">
         <is>
@@ -9579,21 +9579,21 @@
         </is>
       </c>
       <c r="E89" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I89" t="inlineStr"/>
@@ -9603,10 +9603,10 @@
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>478313</v>
+        <v>478189</v>
       </c>
       <c r="R89" t="n">
-        <v>6827798</v>
+        <v>6827761</v>
       </c>
       <c r="S89" t="n">
         <v>10</v>
@@ -9665,10 +9665,10 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>120075174</v>
+        <v>120075007</v>
       </c>
       <c r="B90" t="n">
-        <v>78542</v>
+        <v>78279</v>
       </c>
       <c r="C90" t="inlineStr">
         <is>
@@ -9681,21 +9681,21 @@
         </is>
       </c>
       <c r="E90" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I90" t="inlineStr"/>
@@ -9705,10 +9705,10 @@
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>478057</v>
+        <v>478285</v>
       </c>
       <c r="R90" t="n">
-        <v>6827749</v>
+        <v>6827770</v>
       </c>
       <c r="S90" t="n">
         <v>10</v>
@@ -9767,7 +9767,7 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>120075066</v>
+        <v>120075176</v>
       </c>
       <c r="B91" t="n">
         <v>78542</v>
@@ -9807,10 +9807,10 @@
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>478160</v>
+        <v>478066</v>
       </c>
       <c r="R91" t="n">
-        <v>6827680</v>
+        <v>6827732</v>
       </c>
       <c r="S91" t="n">
         <v>10</v>
@@ -9869,10 +9869,10 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>120074996</v>
+        <v>120075064</v>
       </c>
       <c r="B92" t="n">
-        <v>78279</v>
+        <v>78542</v>
       </c>
       <c r="C92" t="inlineStr">
         <is>
@@ -9885,21 +9885,21 @@
         </is>
       </c>
       <c r="E92" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I92" t="inlineStr"/>
@@ -9909,10 +9909,10 @@
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>478165</v>
+        <v>478192</v>
       </c>
       <c r="R92" t="n">
-        <v>6827712</v>
+        <v>6827690</v>
       </c>
       <c r="S92" t="n">
         <v>10</v>
@@ -9971,10 +9971,10 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>120074912</v>
+        <v>120075067</v>
       </c>
       <c r="B93" t="n">
-        <v>78576</v>
+        <v>78542</v>
       </c>
       <c r="C93" t="inlineStr">
         <is>
@@ -9987,21 +9987,21 @@
         </is>
       </c>
       <c r="E93" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I93" t="inlineStr"/>
@@ -10011,10 +10011,10 @@
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>478149</v>
+        <v>478164</v>
       </c>
       <c r="R93" t="n">
-        <v>6827714</v>
+        <v>6827661</v>
       </c>
       <c r="S93" t="n">
         <v>10</v>
@@ -10073,10 +10073,10 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>120075223</v>
+        <v>120074928</v>
       </c>
       <c r="B94" t="n">
-        <v>78187</v>
+        <v>78576</v>
       </c>
       <c r="C94" t="inlineStr">
         <is>
@@ -10089,21 +10089,21 @@
         </is>
       </c>
       <c r="E94" t="n">
-        <v>353</v>
+        <v>185</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I94" t="inlineStr"/>
@@ -10113,10 +10113,10 @@
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>478076</v>
+        <v>478059</v>
       </c>
       <c r="R94" t="n">
-        <v>6827777</v>
+        <v>6827740</v>
       </c>
       <c r="S94" t="n">
         <v>10</v>
@@ -10175,10 +10175,10 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>120075026</v>
+        <v>120074929</v>
       </c>
       <c r="B95" t="n">
-        <v>78278</v>
+        <v>78576</v>
       </c>
       <c r="C95" t="inlineStr">
         <is>
@@ -10191,21 +10191,21 @@
         </is>
       </c>
       <c r="E95" t="n">
-        <v>6446</v>
+        <v>185</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I95" t="inlineStr"/>
@@ -10215,10 +10215,10 @@
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>478161</v>
+        <v>478045</v>
       </c>
       <c r="R95" t="n">
-        <v>6827592</v>
+        <v>6827724</v>
       </c>
       <c r="S95" t="n">
         <v>10</v>
@@ -10277,10 +10277,10 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>120074938</v>
+        <v>120075008</v>
       </c>
       <c r="B96" t="n">
-        <v>79160</v>
+        <v>78279</v>
       </c>
       <c r="C96" t="inlineStr">
         <is>
@@ -10293,21 +10293,21 @@
         </is>
       </c>
       <c r="E96" t="n">
-        <v>6453</v>
+        <v>228912</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I96" t="inlineStr"/>
@@ -10317,10 +10317,10 @@
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>478097</v>
+        <v>478299</v>
       </c>
       <c r="R96" t="n">
-        <v>6827756</v>
+        <v>6827805</v>
       </c>
       <c r="S96" t="n">
         <v>10</v>
@@ -10379,10 +10379,10 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>120075024</v>
+        <v>120075226</v>
       </c>
       <c r="B97" t="n">
-        <v>78278</v>
+        <v>78187</v>
       </c>
       <c r="C97" t="inlineStr">
         <is>
@@ -10395,21 +10395,21 @@
         </is>
       </c>
       <c r="E97" t="n">
-        <v>6446</v>
+        <v>353</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I97" t="inlineStr"/>
@@ -10419,10 +10419,10 @@
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>478165</v>
+        <v>478098</v>
       </c>
       <c r="R97" t="n">
-        <v>6827712</v>
+        <v>6827815</v>
       </c>
       <c r="S97" t="n">
         <v>10</v>
@@ -10481,7 +10481,7 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>120075028</v>
+        <v>120075042</v>
       </c>
       <c r="B98" t="n">
         <v>78278</v>
@@ -10521,10 +10521,10 @@
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>478137</v>
+        <v>478074</v>
       </c>
       <c r="R98" t="n">
-        <v>6827553</v>
+        <v>6827775</v>
       </c>
       <c r="S98" t="n">
         <v>10</v>
@@ -10583,7 +10583,7 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>120075037</v>
+        <v>120075045</v>
       </c>
       <c r="B99" t="n">
         <v>78278</v>
@@ -10623,10 +10623,10 @@
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>478265</v>
+        <v>478070</v>
       </c>
       <c r="R99" t="n">
-        <v>6827716</v>
+        <v>6827723</v>
       </c>
       <c r="S99" t="n">
         <v>10</v>
@@ -10685,10 +10685,10 @@
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>120075242</v>
+        <v>120075019</v>
       </c>
       <c r="B100" t="n">
-        <v>77926</v>
+        <v>79623</v>
       </c>
       <c r="C100" t="inlineStr">
         <is>
@@ -10701,21 +10701,21 @@
         </is>
       </c>
       <c r="E100" t="n">
-        <v>6437</v>
+        <v>6458</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I100" t="inlineStr"/>
@@ -10725,10 +10725,10 @@
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>478136</v>
+        <v>478227</v>
       </c>
       <c r="R100" t="n">
-        <v>6827556</v>
+        <v>6827655</v>
       </c>
       <c r="S100" t="n">
         <v>10</v>
@@ -10787,10 +10787,10 @@
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>120075012</v>
+        <v>120075082</v>
       </c>
       <c r="B101" t="n">
-        <v>78279</v>
+        <v>78542</v>
       </c>
       <c r="C101" t="inlineStr">
         <is>
@@ -10803,21 +10803,21 @@
         </is>
       </c>
       <c r="E101" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I101" t="inlineStr"/>
@@ -10827,10 +10827,10 @@
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>478055</v>
+        <v>478097</v>
       </c>
       <c r="R101" t="n">
-        <v>6827786</v>
+        <v>6827544</v>
       </c>
       <c r="S101" t="n">
         <v>10</v>
@@ -10889,7 +10889,7 @@
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>120075011</v>
+        <v>120074998</v>
       </c>
       <c r="B102" t="n">
         <v>78279</v>
@@ -10929,10 +10929,10 @@
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>478103</v>
+        <v>478172</v>
       </c>
       <c r="R102" t="n">
-        <v>6827803</v>
+        <v>6827640</v>
       </c>
       <c r="S102" t="n">
         <v>10</v>
@@ -10991,7 +10991,7 @@
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>120075010</v>
+        <v>120075013</v>
       </c>
       <c r="B103" t="n">
         <v>78279</v>
@@ -11031,10 +11031,10 @@
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>478074</v>
+        <v>478239</v>
       </c>
       <c r="R103" t="n">
-        <v>6827772</v>
+        <v>6827752</v>
       </c>
       <c r="S103" t="n">
         <v>10</v>
@@ -11195,10 +11195,10 @@
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>120075202</v>
+        <v>120075135</v>
       </c>
       <c r="B105" t="n">
-        <v>78187</v>
+        <v>78542</v>
       </c>
       <c r="C105" t="inlineStr">
         <is>
@@ -11211,21 +11211,21 @@
         </is>
       </c>
       <c r="E105" t="n">
-        <v>353</v>
+        <v>6425</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I105" t="inlineStr"/>
@@ -11235,10 +11235,10 @@
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>478218</v>
+        <v>478291</v>
       </c>
       <c r="R105" t="n">
-        <v>6827721</v>
+        <v>6827744</v>
       </c>
       <c r="S105" t="n">
         <v>10</v>
@@ -11297,10 +11297,10 @@
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>120075231</v>
+        <v>120075166</v>
       </c>
       <c r="B106" t="n">
-        <v>78187</v>
+        <v>78542</v>
       </c>
       <c r="C106" t="inlineStr">
         <is>
@@ -11313,21 +11313,21 @@
         </is>
       </c>
       <c r="E106" t="n">
-        <v>353</v>
+        <v>6425</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I106" t="inlineStr"/>
@@ -11337,10 +11337,10 @@
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>478067</v>
+        <v>478092</v>
       </c>
       <c r="R106" t="n">
-        <v>6827863</v>
+        <v>6827839</v>
       </c>
       <c r="S106" t="n">
         <v>10</v>
@@ -11399,10 +11399,10 @@
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>120075046</v>
+        <v>120074934</v>
       </c>
       <c r="B107" t="n">
-        <v>78278</v>
+        <v>79160</v>
       </c>
       <c r="C107" t="inlineStr">
         <is>
@@ -11415,21 +11415,21 @@
         </is>
       </c>
       <c r="E107" t="n">
-        <v>6446</v>
+        <v>6453</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I107" t="inlineStr"/>
@@ -11439,10 +11439,10 @@
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>478285</v>
+        <v>478169</v>
       </c>
       <c r="R107" t="n">
-        <v>6827770</v>
+        <v>6827760</v>
       </c>
       <c r="S107" t="n">
         <v>10</v>
@@ -11501,10 +11501,10 @@
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>120075040</v>
+        <v>120075084</v>
       </c>
       <c r="B108" t="n">
-        <v>78278</v>
+        <v>78542</v>
       </c>
       <c r="C108" t="inlineStr">
         <is>
@@ -11517,21 +11517,21 @@
         </is>
       </c>
       <c r="E108" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I108" t="inlineStr"/>
@@ -11541,10 +11541,10 @@
         </is>
       </c>
       <c r="Q108" t="n">
-        <v>478250</v>
+        <v>478098</v>
       </c>
       <c r="R108" t="n">
-        <v>6827802</v>
+        <v>6827520</v>
       </c>
       <c r="S108" t="n">
         <v>10</v>
@@ -11603,10 +11603,10 @@
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>120074935</v>
+        <v>120075029</v>
       </c>
       <c r="B109" t="n">
-        <v>79160</v>
+        <v>78278</v>
       </c>
       <c r="C109" t="inlineStr">
         <is>
@@ -11619,21 +11619,21 @@
         </is>
       </c>
       <c r="E109" t="n">
-        <v>6453</v>
+        <v>6446</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I109" t="inlineStr"/>
@@ -11643,10 +11643,10 @@
         </is>
       </c>
       <c r="Q109" t="n">
-        <v>478150</v>
+        <v>478115</v>
       </c>
       <c r="R109" t="n">
-        <v>6827745</v>
+        <v>6827564</v>
       </c>
       <c r="S109" t="n">
         <v>10</v>
@@ -11705,10 +11705,10 @@
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>120075176</v>
+        <v>120075024</v>
       </c>
       <c r="B110" t="n">
-        <v>78542</v>
+        <v>78278</v>
       </c>
       <c r="C110" t="inlineStr">
         <is>
@@ -11721,21 +11721,21 @@
         </is>
       </c>
       <c r="E110" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I110" t="inlineStr"/>
@@ -11745,10 +11745,10 @@
         </is>
       </c>
       <c r="Q110" t="n">
-        <v>478066</v>
+        <v>478165</v>
       </c>
       <c r="R110" t="n">
-        <v>6827732</v>
+        <v>6827712</v>
       </c>
       <c r="S110" t="n">
         <v>10</v>
@@ -11807,10 +11807,10 @@
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>120075081</v>
+        <v>120074882</v>
       </c>
       <c r="B111" t="n">
-        <v>78542</v>
+        <v>79160</v>
       </c>
       <c r="C111" t="inlineStr">
         <is>
@@ -11823,21 +11823,21 @@
         </is>
       </c>
       <c r="E111" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I111" t="inlineStr"/>
@@ -11847,10 +11847,10 @@
         </is>
       </c>
       <c r="Q111" t="n">
-        <v>478096</v>
+        <v>478162</v>
       </c>
       <c r="R111" t="n">
-        <v>6827550</v>
+        <v>6827593</v>
       </c>
       <c r="S111" t="n">
         <v>10</v>
@@ -11909,10 +11909,10 @@
     </row>
     <row r="112">
       <c r="A112" t="n">
-        <v>120075159</v>
+        <v>120075027</v>
       </c>
       <c r="B112" t="n">
-        <v>78542</v>
+        <v>78278</v>
       </c>
       <c r="C112" t="inlineStr">
         <is>
@@ -11925,21 +11925,21 @@
         </is>
       </c>
       <c r="E112" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I112" t="inlineStr"/>
@@ -11949,10 +11949,10 @@
         </is>
       </c>
       <c r="Q112" t="n">
-        <v>478100</v>
+        <v>478144</v>
       </c>
       <c r="R112" t="n">
-        <v>6827729</v>
+        <v>6827593</v>
       </c>
       <c r="S112" t="n">
         <v>10</v>
@@ -12011,10 +12011,10 @@
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>120075173</v>
+        <v>120075054</v>
       </c>
       <c r="B113" t="n">
-        <v>78542</v>
+        <v>90598</v>
       </c>
       <c r="C113" t="inlineStr">
         <is>
@@ -12027,21 +12027,21 @@
         </is>
       </c>
       <c r="E113" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I113" t="inlineStr"/>
@@ -12051,10 +12051,10 @@
         </is>
       </c>
       <c r="Q113" t="n">
-        <v>478052</v>
+        <v>478126</v>
       </c>
       <c r="R113" t="n">
-        <v>6827754</v>
+        <v>6827477</v>
       </c>
       <c r="S113" t="n">
         <v>10</v>
@@ -12113,10 +12113,10 @@
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>120074956</v>
+        <v>120075205</v>
       </c>
       <c r="B114" t="n">
-        <v>57320</v>
+        <v>78187</v>
       </c>
       <c r="C114" t="inlineStr">
         <is>
@@ -12129,39 +12129,34 @@
         </is>
       </c>
       <c r="E114" t="n">
-        <v>100109</v>
+        <v>353</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I114" t="inlineStr"/>
-      <c r="M114" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P114" t="inlineStr">
         <is>
           <t>Hevoslamm, Dlr</t>
         </is>
       </c>
       <c r="Q114" t="n">
-        <v>478278</v>
+        <v>478117</v>
       </c>
       <c r="R114" t="n">
-        <v>6827832</v>
+        <v>6827612</v>
       </c>
       <c r="S114" t="n">
         <v>10</v>
@@ -12194,11 +12189,6 @@
       <c r="AA114" t="inlineStr">
         <is>
           <t>2024-09-27</t>
-        </is>
-      </c>
-      <c r="AC114" t="inlineStr">
-        <is>
-          <t>Färska ringhack (tall)</t>
         </is>
       </c>
       <c r="AD114" t="b">
@@ -12225,10 +12215,10 @@
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>120075085</v>
+        <v>120075231</v>
       </c>
       <c r="B115" t="n">
-        <v>78542</v>
+        <v>78187</v>
       </c>
       <c r="C115" t="inlineStr">
         <is>
@@ -12241,21 +12231,21 @@
         </is>
       </c>
       <c r="E115" t="n">
-        <v>6425</v>
+        <v>353</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I115" t="inlineStr"/>
@@ -12265,10 +12255,10 @@
         </is>
       </c>
       <c r="Q115" t="n">
-        <v>478094</v>
+        <v>478067</v>
       </c>
       <c r="R115" t="n">
-        <v>6827504</v>
+        <v>6827863</v>
       </c>
       <c r="S115" t="n">
         <v>10</v>
@@ -12327,10 +12317,10 @@
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>120075133</v>
+        <v>120074907</v>
       </c>
       <c r="B116" t="n">
-        <v>78542</v>
+        <v>79160</v>
       </c>
       <c r="C116" t="inlineStr">
         <is>
@@ -12343,21 +12333,21 @@
         </is>
       </c>
       <c r="E116" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I116" t="inlineStr"/>
@@ -12367,10 +12357,10 @@
         </is>
       </c>
       <c r="Q116" t="n">
-        <v>478258</v>
+        <v>478263</v>
       </c>
       <c r="R116" t="n">
-        <v>6827753</v>
+        <v>6827838</v>
       </c>
       <c r="S116" t="n">
         <v>10</v>
@@ -12429,10 +12419,10 @@
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>120075089</v>
+        <v>120074952</v>
   